--- a/20_設計書/ログインシステム.xlsx
+++ b/20_設計書/ログインシステム.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\ログインシステム\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A13A9E-6BAA-464D-9F22-3B2557749566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA66545-AF00-4F4D-8A16-4752ABA4D7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="SSR認証フロー" sheetId="81" r:id="rId7"/>
     <sheet name="エラー処理" sheetId="78" r:id="rId8"/>
     <sheet name="認証失敗時画面遷移" sheetId="80" r:id="rId9"/>
+    <sheet name="シーケンス図" sheetId="82" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_2a1_" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
@@ -55,11 +56,12 @@
     <definedName name="IBD00110チェック仕様" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="IBE09000チェック仕様" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ooo" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">API一覧!$A$1:$H$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">API一覧!$A$1:$H$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">API詳細!$A$1:$F$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">API入出力項目一覧!$A$1:$J$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">SSR認証フロー!$A$1:$H$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">SSR認証フロー!$A$1:$H$100</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">エラー処理!$A$1:$F$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">シーケンス図!$A$1:$H$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">ログイン処理!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">認証失敗時画面遷移!$A$1:$G$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$I$36</definedName>
@@ -78,6 +80,7 @@
     <definedName name="画面遷移new" localSheetId="5" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
     <definedName name="画面遷移new" localSheetId="6" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
     <definedName name="画面遷移new" localSheetId="7" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
+    <definedName name="画面遷移new" localSheetId="9" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
     <definedName name="画面遷移new" localSheetId="2" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
     <definedName name="画面遷移new" localSheetId="8" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
     <definedName name="画面遷移new" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
@@ -100,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="256">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -1098,6 +1101,44 @@
     <t>追加項目⑤</t>
     <phoneticPr fontId="52"/>
   </si>
+  <si>
+    <t>認証フロー図</t>
+    <rPh sb="0" eb="2">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>利用者</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>新ヒロセWEB</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>環境証明書システム</t>
+    <rPh sb="0" eb="5">
+      <t>カンキョウショウメイショ</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>認証API</t>
+    <rPh sb="0" eb="2">
+      <t>ニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
 </sst>
 </file>
 
@@ -1108,7 +1149,7 @@
     <numFmt numFmtId="177" formatCode="0.00_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1514,8 +1555,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1603,6 +1651,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2334,7 +2388,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2395,166 +2449,10 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="183" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="55" fillId="12" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="13" borderId="15" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="14" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="8" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="13" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="58" fillId="16" borderId="3" xfId="183" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="16" borderId="3" xfId="183" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="16" borderId="3" xfId="183" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="56" fillId="0" borderId="8" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2569,6 +2467,171 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="183" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="9" xfId="183" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="183" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="3" xfId="183" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="55" fillId="12" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="15" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="14" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="8" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="13" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="186">
@@ -3190,6 +3253,2908 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>986118</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>81616</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3443380</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>86472</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC5FF3FD-754D-77D5-8C28-1CA72F809A24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1781736" y="3353734"/>
+          <a:ext cx="2457262" cy="957356"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ブラウザ画面要求</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>978086</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>47998</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3435348</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>46504</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6841B936-5E11-4C01-B61C-10AFE768B285}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1773704" y="5034616"/>
+          <a:ext cx="2457262" cy="951006"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>環境証明書システムサーバー処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>982942</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>47996</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3440204</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>68727</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF0F5044-4565-469E-903B-0B8FC6BD7CDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1778560" y="6749114"/>
+          <a:ext cx="2457262" cy="973231"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>トークンを利用してセッション確認</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>AP</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>呼び出し</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>982942</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>64253</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3440204</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>104034</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44D4CD1D-C73A-465E-AF27-5532BD32A5A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1778560" y="8479871"/>
+          <a:ext cx="2457262" cy="992281"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>認証</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>API</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>セッション確認</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>982942</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>152597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3440204</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>36803</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD7E99B0-DD15-45D9-8065-B32BE0B1FEEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1778560" y="10282715"/>
+          <a:ext cx="2457262" cy="1027206"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>結果返却</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>OK/NG</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>982942</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>103110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3440204</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>177816</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46AF4646-E8A8-442B-926B-DADB967BA733}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1778560" y="12138228"/>
+          <a:ext cx="2457262" cy="1027206"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>HTML</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>生成</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>対象画面表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2209892</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>83297</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2211574</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4E054F-B333-8ACC-ACF2-E3B41C819BF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3005510" y="4307915"/>
+          <a:ext cx="1682" cy="723526"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>49679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2209892</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>44821</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0BEF063-7EFF-43D4-ACDB-1022BE6A7A33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="2"/>
+          <a:endCxn id="9" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3004016" y="5988797"/>
+          <a:ext cx="1494" cy="757142"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>65552</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>67428</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5308BC0E-5C03-47C0-A0AA-9E35F0B53A97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="2"/>
+          <a:endCxn id="12" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3004016" y="7719170"/>
+          <a:ext cx="0" cy="763876"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>107209</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>152597</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1412BE1-C35E-4DC7-B864-DF9A3DB0ADC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="12" idx="2"/>
+          <a:endCxn id="15" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3004016" y="9475327"/>
+          <a:ext cx="0" cy="807388"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>36803</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>106285</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線矢印コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14D7972-BCD6-42F1-B816-AB18B8A7D98E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="2"/>
+          <a:endCxn id="18" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3004016" y="11309921"/>
+          <a:ext cx="0" cy="831482"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4458453</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>103110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2133605</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>177816</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="正方形/長方形 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF4852F-E459-4DFA-8FB9-D533A453D204}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5254071" y="12138228"/>
+          <a:ext cx="2504887" cy="1027206"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>セッション切れ画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>HTML</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>生成</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2212224</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>8031</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>904501</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>103110</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="47" name="グループ化 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{231594EE-7E71-B1A5-71E5-D3D1E54798B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2996636" y="11833972"/>
+          <a:ext cx="3525747" cy="483550"/>
+          <a:chOff x="3007842" y="11662149"/>
+          <a:chExt cx="3522012" cy="476079"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="37" name="直線コネクタ 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9525D04-33CA-0C08-9739-E419222A2D9D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3007842" y="11662149"/>
+            <a:ext cx="3522012" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E486688-7150-492D-A7DA-5BB636DAD0C5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:endCxn id="39" idx="0"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="6509690" y="11662149"/>
+            <a:ext cx="4103" cy="476079"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>982942</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>58099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3440204</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>132805</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="正方形/長方形 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA839B33-8639-4F36-9D71-84F64E959A2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1778560" y="13998217"/>
+          <a:ext cx="2457262" cy="1027206"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ブラウザへ返却</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>180991</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2208398</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>58099</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="49" name="直線矢印コネクタ 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{180D35E4-05F4-4261-BD70-E7972AE4F6AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="2"/>
+          <a:endCxn id="48" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3004016" y="13168609"/>
+          <a:ext cx="0" cy="829608"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4477501</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>64449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2114553</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>135980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="正方形/長方形 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F2DC1AF-AA5E-41DD-A893-5EA471DFD47B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5273119" y="14004567"/>
+          <a:ext cx="2466787" cy="1024031"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>HTML</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>生成</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>対象画面表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>881160</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>180991</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>881162</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>67624</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="直線矢印コネクタ 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2FFF934-AD5A-4434-A63D-7D7BB361BE4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="39" idx="2"/>
+          <a:endCxn id="51" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6506513" y="13168609"/>
+          <a:ext cx="2" cy="839133"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1842620</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2244351</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="正方形/長方形 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CB3C7E6-D5F1-F65F-8972-0194B2EAC55A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2638238" y="11754971"/>
+          <a:ext cx="401731" cy="280147"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2700617</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3102348</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>38474</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B9BD688-19BC-4891-97A1-D01793B92126}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3496235" y="11418795"/>
+          <a:ext cx="401731" cy="273797"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>NG</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9329</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5DC0599-F248-69F6-8EA0-480007E11277}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="734728" y="211035"/>
+          <a:ext cx="0" cy="7832912"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9329</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52848CB7-BF06-43CB-8FB5-B0FE8AEA46EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="731553" y="214210"/>
+          <a:ext cx="0" cy="7832912"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>731557</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>172946</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>896472</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>94503</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB41A88E-8B1E-4741-8E2D-D5A4EA59573E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="731557" y="755652"/>
+          <a:ext cx="1644091" cy="302557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>①認証済み利用者がアクセス</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1040467</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>105709</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>187325</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>105709</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BF5B133-0D41-71CE-54EF-A5F425D18409}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2519643" y="878915"/>
+          <a:ext cx="323476" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9329</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直線コネクタ 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CF5B1D0-112C-4B80-8CFA-7DC1349BB169}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3387347" y="214210"/>
+          <a:ext cx="0" cy="7832912"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>753969</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>48000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>414617</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC47358D-032C-4883-A2DE-03B6B04E915F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3409763" y="1213412"/>
+          <a:ext cx="1139825" cy="232147"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>②認証情報を連携</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>588867</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>128310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>239990</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>128310</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDD64CC8-A5D6-47E4-AA4A-B05BDC9B3FDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4723838" y="1293722"/>
+          <a:ext cx="323476" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9329</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>734728</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2296DE5-44E0-4FF5-8E09-DAA60D9C41F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3387347" y="214210"/>
+          <a:ext cx="0" cy="7832912"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>134472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>425824</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA91DB71-2CC3-4BEF-B5E2-1E47FE5BA253}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5559799" y="1490384"/>
+          <a:ext cx="1152525" cy="280145"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>③ログイン</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>API</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>実行</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>105522</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>46504</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>413123</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>46504</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B31AA3BE-FD2F-4541-A113-A8BDB8F3F79B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7310904" y="1604122"/>
+          <a:ext cx="307601" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>656479</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>182470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685240</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>131296</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C81115C9-67F5-4C32-AAE1-67E40591CB40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5463803" y="2121088"/>
+          <a:ext cx="1507937" cy="329826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="200"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>④トークン／ユーザ情報</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="200"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>返却</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>111872</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1492</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="正方形/長方形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA73E118-831B-4F1D-8C8B-896B3DA74018}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5556624" y="2621990"/>
+          <a:ext cx="1491876" cy="270620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>⑤セッション確認 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>API</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>実行</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>750794</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>47999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>493059</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>131294</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C0F23E3-FCF2-40D8-8F8A-8BA7CFE9E1D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5558118" y="3129617"/>
+          <a:ext cx="1221441" cy="273795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>⑥セッション結果返却</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>734732</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>116728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>986118</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCE86D13-7090-43B5-9FAD-BAAF64FFBC27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="734732" y="3579346"/>
+          <a:ext cx="1730562" cy="293032"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>⑦対象画面表示／エラー表示</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>125132</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>98051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>448608</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>98051</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線矢印コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{296ADAFD-2815-4AF8-9545-8983F56B1111}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4932456" y="2417669"/>
+          <a:ext cx="323476" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>99547</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>30815</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>423023</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>30815</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{082A3DB3-33F6-4141-B4F1-B74CE9EBAEBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7304929" y="2731433"/>
+          <a:ext cx="323476" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>75266</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>75640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>75640</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE7BC7E6-0BC4-48A4-81C8-7900AA417265}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7280648" y="2204758"/>
+          <a:ext cx="305734" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>75267</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>163233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>163233</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="直線矢印コネクタ 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B54522E7-64BF-48FF-8A83-CCFBFE32398F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7280649" y="3244851"/>
+          <a:ext cx="305734" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1139826</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>36793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>526676</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>36793</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="直線矢印コネクタ 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{591BF08F-C6A7-4E73-BFF0-0B2C81548BAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2619002" y="3689911"/>
+          <a:ext cx="2714998" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office ​​テーマ">
   <a:themeElements>
@@ -3559,16 +6524,16 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="21" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B22" s="22" t="str">
+      <c r="B22" s="31" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 12日 dr1.0</v>
-      </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
+        <v>2026年 06月 16日 dr1.0</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="24" spans="2:8" ht="14.25" customHeight="1"/>
@@ -3576,15 +6541,15 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="27" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="28" spans="2:8" ht="14.25" customHeight="1">
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25" t="s">
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="G28" s="25"/>
+      <c r="G28" s="34"/>
     </row>
     <row r="29" spans="2:8" ht="14.25" customHeight="1">
       <c r="C29" s="3" t="s">
@@ -3619,11 +6584,11 @@
     </row>
     <row r="32" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="33" spans="3:20" ht="14.25" customHeight="1">
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
@@ -3670,7 +6635,7 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
       <c r="S38" s="16"/>
-      <c r="T38" s="24"/>
+      <c r="T38" s="33"/>
     </row>
     <row r="39" spans="3:20" ht="14.25" customHeight="1">
       <c r="K39" s="17"/>
@@ -3682,7 +6647,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="14"/>
       <c r="S39" s="19"/>
-      <c r="T39" s="27"/>
+      <c r="T39" s="36"/>
     </row>
     <row r="40" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="41" spans="3:20" ht="14.25" customHeight="1">
@@ -3706,7 +6671,7 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
       <c r="S42" s="16"/>
-      <c r="T42" s="24"/>
+      <c r="T42" s="33"/>
     </row>
     <row r="43" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K43" s="17"/>
@@ -3714,7 +6679,7 @@
       <c r="N43" s="12"/>
       <c r="R43" s="14"/>
       <c r="S43" s="19"/>
-      <c r="T43" s="24"/>
+      <c r="T43" s="33"/>
     </row>
     <row r="44" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K44" s="1"/>
@@ -3750,7 +6715,7 @@
       <c r="Q46" s="15"/>
       <c r="R46" s="14"/>
       <c r="S46" s="16"/>
-      <c r="T46" s="24"/>
+      <c r="T46" s="33"/>
     </row>
     <row r="47" spans="3:20" ht="14.25" customHeight="1">
       <c r="K47" s="17"/>
@@ -3762,7 +6727,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="14"/>
       <c r="S47" s="19"/>
-      <c r="T47" s="24"/>
+      <c r="T47" s="33"/>
     </row>
     <row r="48" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="49" spans="11:20" ht="14.25" customHeight="1">
@@ -3787,7 +6752,7 @@
       <c r="Q50" s="15"/>
       <c r="R50" s="14"/>
       <c r="S50" s="16"/>
-      <c r="T50" s="24"/>
+      <c r="T50" s="33"/>
     </row>
     <row r="51" spans="11:20" ht="14.25" customHeight="1">
       <c r="K51" s="17"/>
@@ -3799,7 +6764,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="14"/>
       <c r="S51" s="19"/>
-      <c r="T51" s="24"/>
+      <c r="T51" s="33"/>
     </row>
     <row r="52" spans="11:20" ht="14.25" customHeight="1"/>
     <row r="53" spans="11:20" ht="14.25" customHeight="1">
@@ -3824,7 +6789,7 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="24"/>
+      <c r="T54" s="33"/>
     </row>
     <row r="55" spans="11:20">
       <c r="K55" s="17"/>
@@ -3836,7 +6801,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="14"/>
       <c r="S55" s="19"/>
-      <c r="T55" s="27"/>
+      <c r="T55" s="36"/>
     </row>
     <row r="57" spans="11:20">
       <c r="K57" s="11"/>
@@ -3860,7 +6825,7 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
       <c r="S58" s="16"/>
-      <c r="T58" s="24"/>
+      <c r="T58" s="33"/>
     </row>
     <row r="59" spans="11:20">
       <c r="K59" s="17"/>
@@ -3872,7 +6837,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="14"/>
       <c r="S59" s="19"/>
-      <c r="T59" s="27"/>
+      <c r="T59" s="36"/>
     </row>
     <row r="61" spans="11:20">
       <c r="K61" s="11"/>
@@ -3896,7 +6861,7 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
       <c r="S62" s="16"/>
-      <c r="T62" s="24"/>
+      <c r="T62" s="33"/>
     </row>
     <row r="63" spans="11:20">
       <c r="K63" s="17"/>
@@ -3908,7 +6873,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="14"/>
       <c r="S63" s="19"/>
-      <c r="T63" s="27"/>
+      <c r="T63" s="36"/>
     </row>
     <row r="65" spans="11:20">
       <c r="K65" s="11"/>
@@ -3932,7 +6897,7 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
       <c r="S66" s="16"/>
-      <c r="T66" s="24"/>
+      <c r="T66" s="33"/>
     </row>
     <row r="67" spans="11:20">
       <c r="K67" s="17"/>
@@ -3944,7 +6909,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="14"/>
       <c r="S67" s="19"/>
-      <c r="T67" s="27"/>
+      <c r="T67" s="36"/>
     </row>
     <row r="69" spans="11:20">
       <c r="K69" s="11"/>
@@ -3968,7 +6933,7 @@
       <c r="Q70" s="15"/>
       <c r="R70" s="14"/>
       <c r="S70" s="16"/>
-      <c r="T70" s="24"/>
+      <c r="T70" s="33"/>
     </row>
     <row r="71" spans="11:20">
       <c r="K71" s="17"/>
@@ -3980,7 +6945,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="14"/>
       <c r="S71" s="19"/>
-      <c r="T71" s="27"/>
+      <c r="T71" s="36"/>
     </row>
     <row r="73" spans="11:20">
       <c r="K73" s="11"/>
@@ -4004,7 +6969,7 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
       <c r="S74" s="16"/>
-      <c r="T74" s="24"/>
+      <c r="T74" s="33"/>
     </row>
     <row r="75" spans="11:20">
       <c r="K75" s="17"/>
@@ -4016,7 +6981,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="14"/>
       <c r="S75" s="19"/>
-      <c r="T75" s="27"/>
+      <c r="T75" s="36"/>
     </row>
     <row r="77" spans="11:20">
       <c r="K77" s="11"/>
@@ -4040,7 +7005,7 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
       <c r="S78" s="16"/>
-      <c r="T78" s="24"/>
+      <c r="T78" s="33"/>
     </row>
     <row r="79" spans="11:20">
       <c r="K79" s="17"/>
@@ -4052,7 +7017,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="14"/>
       <c r="S79" s="19"/>
-      <c r="T79" s="27"/>
+      <c r="T79" s="36"/>
     </row>
     <row r="81" spans="11:20">
       <c r="K81" s="11"/>
@@ -4076,7 +7041,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
       <c r="S82" s="16"/>
-      <c r="T82" s="24"/>
+      <c r="T82" s="33"/>
     </row>
     <row r="83" spans="11:20">
       <c r="K83" s="17"/>
@@ -4088,7 +7053,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="14"/>
       <c r="S83" s="19"/>
-      <c r="T83" s="27"/>
+      <c r="T83" s="36"/>
     </row>
     <row r="85" spans="11:20">
       <c r="K85" s="11"/>
@@ -4112,7 +7077,7 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
       <c r="S86" s="16"/>
-      <c r="T86" s="24"/>
+      <c r="T86" s="33"/>
     </row>
     <row r="87" spans="11:20">
       <c r="K87" s="17"/>
@@ -4124,7 +7089,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="14"/>
       <c r="S87" s="19"/>
-      <c r="T87" s="27"/>
+      <c r="T87" s="36"/>
     </row>
     <row r="89" spans="11:20">
       <c r="K89" s="11"/>
@@ -4148,7 +7113,7 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="24"/>
+      <c r="T90" s="33"/>
     </row>
     <row r="91" spans="11:20">
       <c r="K91" s="17"/>
@@ -4160,7 +7125,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="14"/>
       <c r="S91" s="19"/>
-      <c r="T91" s="27"/>
+      <c r="T91" s="36"/>
     </row>
     <row r="93" spans="11:20">
       <c r="K93" s="11"/>
@@ -4184,7 +7149,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="24"/>
+      <c r="T94" s="33"/>
     </row>
     <row r="95" spans="11:20">
       <c r="K95" s="17"/>
@@ -4196,7 +7161,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="14"/>
       <c r="S95" s="19"/>
-      <c r="T95" s="27"/>
+      <c r="T95" s="36"/>
     </row>
     <row r="97" spans="11:20">
       <c r="K97" s="11"/>
@@ -4220,7 +7185,7 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
       <c r="S98" s="16"/>
-      <c r="T98" s="24"/>
+      <c r="T98" s="33"/>
     </row>
     <row r="99" spans="11:20">
       <c r="K99" s="17"/>
@@ -4232,7 +7197,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="14"/>
       <c r="S99" s="19"/>
-      <c r="T99" s="27"/>
+      <c r="T99" s="36"/>
     </row>
     <row r="101" spans="11:20">
       <c r="K101" s="11"/>
@@ -4256,7 +7221,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
       <c r="S102" s="16"/>
-      <c r="T102" s="24"/>
+      <c r="T102" s="33"/>
     </row>
     <row r="103" spans="11:20">
       <c r="K103" s="17"/>
@@ -4268,7 +7233,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="14"/>
       <c r="S103" s="19"/>
-      <c r="T103" s="27"/>
+      <c r="T103" s="36"/>
     </row>
     <row r="105" spans="11:20">
       <c r="K105" s="11"/>
@@ -4292,7 +7257,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
       <c r="S106" s="16"/>
-      <c r="T106" s="24"/>
+      <c r="T106" s="33"/>
     </row>
     <row r="107" spans="11:20">
       <c r="K107" s="17"/>
@@ -4304,7 +7269,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="14"/>
       <c r="S107" s="19"/>
-      <c r="T107" s="27"/>
+      <c r="T107" s="36"/>
     </row>
     <row r="109" spans="11:20">
       <c r="K109" s="11"/>
@@ -4328,7 +7293,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
       <c r="S110" s="16"/>
-      <c r="T110" s="24"/>
+      <c r="T110" s="33"/>
     </row>
     <row r="111" spans="11:20">
       <c r="K111" s="17"/>
@@ -4340,7 +7305,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="14"/>
       <c r="S111" s="19"/>
-      <c r="T111" s="27"/>
+      <c r="T111" s="36"/>
     </row>
     <row r="113" spans="11:20">
       <c r="K113" s="11"/>
@@ -4364,7 +7329,7 @@
       <c r="Q114" s="15"/>
       <c r="R114" s="14"/>
       <c r="S114" s="16"/>
-      <c r="T114" s="24"/>
+      <c r="T114" s="33"/>
     </row>
     <row r="115" spans="11:20">
       <c r="K115" s="17"/>
@@ -4376,7 +7341,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="14"/>
       <c r="S115" s="19"/>
-      <c r="T115" s="27"/>
+      <c r="T115" s="36"/>
     </row>
     <row r="117" spans="11:20">
       <c r="K117" s="11"/>
@@ -4400,7 +7365,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
       <c r="S118" s="16"/>
-      <c r="T118" s="24"/>
+      <c r="T118" s="33"/>
     </row>
     <row r="119" spans="11:20">
       <c r="K119" s="17"/>
@@ -4412,7 +7377,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="14"/>
       <c r="S119" s="19"/>
-      <c r="T119" s="27"/>
+      <c r="T119" s="36"/>
     </row>
     <row r="121" spans="11:20">
       <c r="K121" s="11"/>
@@ -4436,7 +7401,7 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
       <c r="S122" s="16"/>
-      <c r="T122" s="24"/>
+      <c r="T122" s="33"/>
     </row>
     <row r="123" spans="11:20">
       <c r="K123" s="17"/>
@@ -4448,7 +7413,7 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="14"/>
       <c r="S123" s="19"/>
-      <c r="T123" s="27"/>
+      <c r="T123" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -4489,6 +7454,387 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6210DB27-2A46-4C1D-9432-BA72DC80E8A7}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.1796875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" style="21" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="21.1796875" style="21" customWidth="1"/>
+    <col min="8" max="167" width="2.453125" style="21"/>
+    <col min="168" max="168" width="4" style="21" customWidth="1"/>
+    <col min="169" max="200" width="2.453125" style="21"/>
+    <col min="201" max="201" width="2.453125" style="21" customWidth="1"/>
+    <col min="202" max="423" width="2.453125" style="21"/>
+    <col min="424" max="424" width="4" style="21" customWidth="1"/>
+    <col min="425" max="456" width="2.453125" style="21"/>
+    <col min="457" max="457" width="2.453125" style="21" customWidth="1"/>
+    <col min="458" max="679" width="2.453125" style="21"/>
+    <col min="680" max="680" width="4" style="21" customWidth="1"/>
+    <col min="681" max="712" width="2.453125" style="21"/>
+    <col min="713" max="713" width="2.453125" style="21" customWidth="1"/>
+    <col min="714" max="935" width="2.453125" style="21"/>
+    <col min="936" max="936" width="4" style="21" customWidth="1"/>
+    <col min="937" max="968" width="2.453125" style="21"/>
+    <col min="969" max="969" width="2.453125" style="21" customWidth="1"/>
+    <col min="970" max="1191" width="2.453125" style="21"/>
+    <col min="1192" max="1192" width="4" style="21" customWidth="1"/>
+    <col min="1193" max="1224" width="2.453125" style="21"/>
+    <col min="1225" max="1225" width="2.453125" style="21" customWidth="1"/>
+    <col min="1226" max="1447" width="2.453125" style="21"/>
+    <col min="1448" max="1448" width="4" style="21" customWidth="1"/>
+    <col min="1449" max="1480" width="2.453125" style="21"/>
+    <col min="1481" max="1481" width="2.453125" style="21" customWidth="1"/>
+    <col min="1482" max="1703" width="2.453125" style="21"/>
+    <col min="1704" max="1704" width="4" style="21" customWidth="1"/>
+    <col min="1705" max="1736" width="2.453125" style="21"/>
+    <col min="1737" max="1737" width="2.453125" style="21" customWidth="1"/>
+    <col min="1738" max="1959" width="2.453125" style="21"/>
+    <col min="1960" max="1960" width="4" style="21" customWidth="1"/>
+    <col min="1961" max="1992" width="2.453125" style="21"/>
+    <col min="1993" max="1993" width="2.453125" style="21" customWidth="1"/>
+    <col min="1994" max="2215" width="2.453125" style="21"/>
+    <col min="2216" max="2216" width="4" style="21" customWidth="1"/>
+    <col min="2217" max="2248" width="2.453125" style="21"/>
+    <col min="2249" max="2249" width="2.453125" style="21" customWidth="1"/>
+    <col min="2250" max="2471" width="2.453125" style="21"/>
+    <col min="2472" max="2472" width="4" style="21" customWidth="1"/>
+    <col min="2473" max="2504" width="2.453125" style="21"/>
+    <col min="2505" max="2505" width="2.453125" style="21" customWidth="1"/>
+    <col min="2506" max="2727" width="2.453125" style="21"/>
+    <col min="2728" max="2728" width="4" style="21" customWidth="1"/>
+    <col min="2729" max="2760" width="2.453125" style="21"/>
+    <col min="2761" max="2761" width="2.453125" style="21" customWidth="1"/>
+    <col min="2762" max="2983" width="2.453125" style="21"/>
+    <col min="2984" max="2984" width="4" style="21" customWidth="1"/>
+    <col min="2985" max="3016" width="2.453125" style="21"/>
+    <col min="3017" max="3017" width="2.453125" style="21" customWidth="1"/>
+    <col min="3018" max="3239" width="2.453125" style="21"/>
+    <col min="3240" max="3240" width="4" style="21" customWidth="1"/>
+    <col min="3241" max="3272" width="2.453125" style="21"/>
+    <col min="3273" max="3273" width="2.453125" style="21" customWidth="1"/>
+    <col min="3274" max="3495" width="2.453125" style="21"/>
+    <col min="3496" max="3496" width="4" style="21" customWidth="1"/>
+    <col min="3497" max="3528" width="2.453125" style="21"/>
+    <col min="3529" max="3529" width="2.453125" style="21" customWidth="1"/>
+    <col min="3530" max="3751" width="2.453125" style="21"/>
+    <col min="3752" max="3752" width="4" style="21" customWidth="1"/>
+    <col min="3753" max="3784" width="2.453125" style="21"/>
+    <col min="3785" max="3785" width="2.453125" style="21" customWidth="1"/>
+    <col min="3786" max="4007" width="2.453125" style="21"/>
+    <col min="4008" max="4008" width="4" style="21" customWidth="1"/>
+    <col min="4009" max="4040" width="2.453125" style="21"/>
+    <col min="4041" max="4041" width="2.453125" style="21" customWidth="1"/>
+    <col min="4042" max="4263" width="2.453125" style="21"/>
+    <col min="4264" max="4264" width="4" style="21" customWidth="1"/>
+    <col min="4265" max="4296" width="2.453125" style="21"/>
+    <col min="4297" max="4297" width="2.453125" style="21" customWidth="1"/>
+    <col min="4298" max="4519" width="2.453125" style="21"/>
+    <col min="4520" max="4520" width="4" style="21" customWidth="1"/>
+    <col min="4521" max="4552" width="2.453125" style="21"/>
+    <col min="4553" max="4553" width="2.453125" style="21" customWidth="1"/>
+    <col min="4554" max="4775" width="2.453125" style="21"/>
+    <col min="4776" max="4776" width="4" style="21" customWidth="1"/>
+    <col min="4777" max="4808" width="2.453125" style="21"/>
+    <col min="4809" max="4809" width="2.453125" style="21" customWidth="1"/>
+    <col min="4810" max="5031" width="2.453125" style="21"/>
+    <col min="5032" max="5032" width="4" style="21" customWidth="1"/>
+    <col min="5033" max="5064" width="2.453125" style="21"/>
+    <col min="5065" max="5065" width="2.453125" style="21" customWidth="1"/>
+    <col min="5066" max="5287" width="2.453125" style="21"/>
+    <col min="5288" max="5288" width="4" style="21" customWidth="1"/>
+    <col min="5289" max="5320" width="2.453125" style="21"/>
+    <col min="5321" max="5321" width="2.453125" style="21" customWidth="1"/>
+    <col min="5322" max="5543" width="2.453125" style="21"/>
+    <col min="5544" max="5544" width="4" style="21" customWidth="1"/>
+    <col min="5545" max="5576" width="2.453125" style="21"/>
+    <col min="5577" max="5577" width="2.453125" style="21" customWidth="1"/>
+    <col min="5578" max="5799" width="2.453125" style="21"/>
+    <col min="5800" max="5800" width="4" style="21" customWidth="1"/>
+    <col min="5801" max="5832" width="2.453125" style="21"/>
+    <col min="5833" max="5833" width="2.453125" style="21" customWidth="1"/>
+    <col min="5834" max="6055" width="2.453125" style="21"/>
+    <col min="6056" max="6056" width="4" style="21" customWidth="1"/>
+    <col min="6057" max="6088" width="2.453125" style="21"/>
+    <col min="6089" max="6089" width="2.453125" style="21" customWidth="1"/>
+    <col min="6090" max="6311" width="2.453125" style="21"/>
+    <col min="6312" max="6312" width="4" style="21" customWidth="1"/>
+    <col min="6313" max="6344" width="2.453125" style="21"/>
+    <col min="6345" max="6345" width="2.453125" style="21" customWidth="1"/>
+    <col min="6346" max="6567" width="2.453125" style="21"/>
+    <col min="6568" max="6568" width="4" style="21" customWidth="1"/>
+    <col min="6569" max="6600" width="2.453125" style="21"/>
+    <col min="6601" max="6601" width="2.453125" style="21" customWidth="1"/>
+    <col min="6602" max="6823" width="2.453125" style="21"/>
+    <col min="6824" max="6824" width="4" style="21" customWidth="1"/>
+    <col min="6825" max="6856" width="2.453125" style="21"/>
+    <col min="6857" max="6857" width="2.453125" style="21" customWidth="1"/>
+    <col min="6858" max="7079" width="2.453125" style="21"/>
+    <col min="7080" max="7080" width="4" style="21" customWidth="1"/>
+    <col min="7081" max="7112" width="2.453125" style="21"/>
+    <col min="7113" max="7113" width="2.453125" style="21" customWidth="1"/>
+    <col min="7114" max="7335" width="2.453125" style="21"/>
+    <col min="7336" max="7336" width="4" style="21" customWidth="1"/>
+    <col min="7337" max="7368" width="2.453125" style="21"/>
+    <col min="7369" max="7369" width="2.453125" style="21" customWidth="1"/>
+    <col min="7370" max="7591" width="2.453125" style="21"/>
+    <col min="7592" max="7592" width="4" style="21" customWidth="1"/>
+    <col min="7593" max="7624" width="2.453125" style="21"/>
+    <col min="7625" max="7625" width="2.453125" style="21" customWidth="1"/>
+    <col min="7626" max="7847" width="2.453125" style="21"/>
+    <col min="7848" max="7848" width="4" style="21" customWidth="1"/>
+    <col min="7849" max="7880" width="2.453125" style="21"/>
+    <col min="7881" max="7881" width="2.453125" style="21" customWidth="1"/>
+    <col min="7882" max="8103" width="2.453125" style="21"/>
+    <col min="8104" max="8104" width="4" style="21" customWidth="1"/>
+    <col min="8105" max="8136" width="2.453125" style="21"/>
+    <col min="8137" max="8137" width="2.453125" style="21" customWidth="1"/>
+    <col min="8138" max="8359" width="2.453125" style="21"/>
+    <col min="8360" max="8360" width="4" style="21" customWidth="1"/>
+    <col min="8361" max="8392" width="2.453125" style="21"/>
+    <col min="8393" max="8393" width="2.453125" style="21" customWidth="1"/>
+    <col min="8394" max="8615" width="2.453125" style="21"/>
+    <col min="8616" max="8616" width="4" style="21" customWidth="1"/>
+    <col min="8617" max="8648" width="2.453125" style="21"/>
+    <col min="8649" max="8649" width="2.453125" style="21" customWidth="1"/>
+    <col min="8650" max="8871" width="2.453125" style="21"/>
+    <col min="8872" max="8872" width="4" style="21" customWidth="1"/>
+    <col min="8873" max="8904" width="2.453125" style="21"/>
+    <col min="8905" max="8905" width="2.453125" style="21" customWidth="1"/>
+    <col min="8906" max="9127" width="2.453125" style="21"/>
+    <col min="9128" max="9128" width="4" style="21" customWidth="1"/>
+    <col min="9129" max="9160" width="2.453125" style="21"/>
+    <col min="9161" max="9161" width="2.453125" style="21" customWidth="1"/>
+    <col min="9162" max="9383" width="2.453125" style="21"/>
+    <col min="9384" max="9384" width="4" style="21" customWidth="1"/>
+    <col min="9385" max="9416" width="2.453125" style="21"/>
+    <col min="9417" max="9417" width="2.453125" style="21" customWidth="1"/>
+    <col min="9418" max="9639" width="2.453125" style="21"/>
+    <col min="9640" max="9640" width="4" style="21" customWidth="1"/>
+    <col min="9641" max="9672" width="2.453125" style="21"/>
+    <col min="9673" max="9673" width="2.453125" style="21" customWidth="1"/>
+    <col min="9674" max="9895" width="2.453125" style="21"/>
+    <col min="9896" max="9896" width="4" style="21" customWidth="1"/>
+    <col min="9897" max="9928" width="2.453125" style="21"/>
+    <col min="9929" max="9929" width="2.453125" style="21" customWidth="1"/>
+    <col min="9930" max="10151" width="2.453125" style="21"/>
+    <col min="10152" max="10152" width="4" style="21" customWidth="1"/>
+    <col min="10153" max="10184" width="2.453125" style="21"/>
+    <col min="10185" max="10185" width="2.453125" style="21" customWidth="1"/>
+    <col min="10186" max="10407" width="2.453125" style="21"/>
+    <col min="10408" max="10408" width="4" style="21" customWidth="1"/>
+    <col min="10409" max="10440" width="2.453125" style="21"/>
+    <col min="10441" max="10441" width="2.453125" style="21" customWidth="1"/>
+    <col min="10442" max="10663" width="2.453125" style="21"/>
+    <col min="10664" max="10664" width="4" style="21" customWidth="1"/>
+    <col min="10665" max="10696" width="2.453125" style="21"/>
+    <col min="10697" max="10697" width="2.453125" style="21" customWidth="1"/>
+    <col min="10698" max="10919" width="2.453125" style="21"/>
+    <col min="10920" max="10920" width="4" style="21" customWidth="1"/>
+    <col min="10921" max="10952" width="2.453125" style="21"/>
+    <col min="10953" max="10953" width="2.453125" style="21" customWidth="1"/>
+    <col min="10954" max="11175" width="2.453125" style="21"/>
+    <col min="11176" max="11176" width="4" style="21" customWidth="1"/>
+    <col min="11177" max="11208" width="2.453125" style="21"/>
+    <col min="11209" max="11209" width="2.453125" style="21" customWidth="1"/>
+    <col min="11210" max="11431" width="2.453125" style="21"/>
+    <col min="11432" max="11432" width="4" style="21" customWidth="1"/>
+    <col min="11433" max="11464" width="2.453125" style="21"/>
+    <col min="11465" max="11465" width="2.453125" style="21" customWidth="1"/>
+    <col min="11466" max="11687" width="2.453125" style="21"/>
+    <col min="11688" max="11688" width="4" style="21" customWidth="1"/>
+    <col min="11689" max="11720" width="2.453125" style="21"/>
+    <col min="11721" max="11721" width="2.453125" style="21" customWidth="1"/>
+    <col min="11722" max="11943" width="2.453125" style="21"/>
+    <col min="11944" max="11944" width="4" style="21" customWidth="1"/>
+    <col min="11945" max="11976" width="2.453125" style="21"/>
+    <col min="11977" max="11977" width="2.453125" style="21" customWidth="1"/>
+    <col min="11978" max="12199" width="2.453125" style="21"/>
+    <col min="12200" max="12200" width="4" style="21" customWidth="1"/>
+    <col min="12201" max="12232" width="2.453125" style="21"/>
+    <col min="12233" max="12233" width="2.453125" style="21" customWidth="1"/>
+    <col min="12234" max="12455" width="2.453125" style="21"/>
+    <col min="12456" max="12456" width="4" style="21" customWidth="1"/>
+    <col min="12457" max="12488" width="2.453125" style="21"/>
+    <col min="12489" max="12489" width="2.453125" style="21" customWidth="1"/>
+    <col min="12490" max="12711" width="2.453125" style="21"/>
+    <col min="12712" max="12712" width="4" style="21" customWidth="1"/>
+    <col min="12713" max="12744" width="2.453125" style="21"/>
+    <col min="12745" max="12745" width="2.453125" style="21" customWidth="1"/>
+    <col min="12746" max="12967" width="2.453125" style="21"/>
+    <col min="12968" max="12968" width="4" style="21" customWidth="1"/>
+    <col min="12969" max="13000" width="2.453125" style="21"/>
+    <col min="13001" max="13001" width="2.453125" style="21" customWidth="1"/>
+    <col min="13002" max="13223" width="2.453125" style="21"/>
+    <col min="13224" max="13224" width="4" style="21" customWidth="1"/>
+    <col min="13225" max="13256" width="2.453125" style="21"/>
+    <col min="13257" max="13257" width="2.453125" style="21" customWidth="1"/>
+    <col min="13258" max="13479" width="2.453125" style="21"/>
+    <col min="13480" max="13480" width="4" style="21" customWidth="1"/>
+    <col min="13481" max="13512" width="2.453125" style="21"/>
+    <col min="13513" max="13513" width="2.453125" style="21" customWidth="1"/>
+    <col min="13514" max="13735" width="2.453125" style="21"/>
+    <col min="13736" max="13736" width="4" style="21" customWidth="1"/>
+    <col min="13737" max="13768" width="2.453125" style="21"/>
+    <col min="13769" max="13769" width="2.453125" style="21" customWidth="1"/>
+    <col min="13770" max="13991" width="2.453125" style="21"/>
+    <col min="13992" max="13992" width="4" style="21" customWidth="1"/>
+    <col min="13993" max="14024" width="2.453125" style="21"/>
+    <col min="14025" max="14025" width="2.453125" style="21" customWidth="1"/>
+    <col min="14026" max="14247" width="2.453125" style="21"/>
+    <col min="14248" max="14248" width="4" style="21" customWidth="1"/>
+    <col min="14249" max="14280" width="2.453125" style="21"/>
+    <col min="14281" max="14281" width="2.453125" style="21" customWidth="1"/>
+    <col min="14282" max="14503" width="2.453125" style="21"/>
+    <col min="14504" max="14504" width="4" style="21" customWidth="1"/>
+    <col min="14505" max="14536" width="2.453125" style="21"/>
+    <col min="14537" max="14537" width="2.453125" style="21" customWidth="1"/>
+    <col min="14538" max="14759" width="2.453125" style="21"/>
+    <col min="14760" max="14760" width="4" style="21" customWidth="1"/>
+    <col min="14761" max="14792" width="2.453125" style="21"/>
+    <col min="14793" max="14793" width="2.453125" style="21" customWidth="1"/>
+    <col min="14794" max="15015" width="2.453125" style="21"/>
+    <col min="15016" max="15016" width="4" style="21" customWidth="1"/>
+    <col min="15017" max="15048" width="2.453125" style="21"/>
+    <col min="15049" max="15049" width="2.453125" style="21" customWidth="1"/>
+    <col min="15050" max="15271" width="2.453125" style="21"/>
+    <col min="15272" max="15272" width="4" style="21" customWidth="1"/>
+    <col min="15273" max="15304" width="2.453125" style="21"/>
+    <col min="15305" max="15305" width="2.453125" style="21" customWidth="1"/>
+    <col min="15306" max="15527" width="2.453125" style="21"/>
+    <col min="15528" max="15528" width="4" style="21" customWidth="1"/>
+    <col min="15529" max="15560" width="2.453125" style="21"/>
+    <col min="15561" max="15561" width="2.453125" style="21" customWidth="1"/>
+    <col min="15562" max="15783" width="2.453125" style="21"/>
+    <col min="15784" max="15784" width="4" style="21" customWidth="1"/>
+    <col min="15785" max="15816" width="2.453125" style="21"/>
+    <col min="15817" max="15817" width="2.453125" style="21" customWidth="1"/>
+    <col min="15818" max="16039" width="2.453125" style="21"/>
+    <col min="16040" max="16040" width="4" style="21" customWidth="1"/>
+    <col min="16041" max="16072" width="2.453125" style="21"/>
+    <col min="16073" max="16073" width="2.453125" style="21" customWidth="1"/>
+    <col min="16074" max="16384" width="2.453125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" customHeight="1">
+      <c r="A1" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="28"/>
+      <c r="E1" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" s="28"/>
+      <c r="G1" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="28"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" customHeight="1">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" customHeight="1">
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="52"/>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FD982979:FK982984 OZ982979:PG982984 YV982979:ZC982984 AIR982979:AIY982984 ASN982979:ASU982984 BCJ982979:BCQ982984 BMF982979:BMM982984 BWB982979:BWI982984 CFX982979:CGE982984 CPT982979:CQA982984 CZP982979:CZW982984 DJL982979:DJS982984 DTH982979:DTO982984 EDD982979:EDK982984 EMZ982979:ENG982984 EWV982979:EXC982984 FGR982979:FGY982984 FQN982979:FQU982984 GAJ982979:GAQ982984 GKF982979:GKM982984 GUB982979:GUI982984 HDX982979:HEE982984 HNT982979:HOA982984 HXP982979:HXW982984 IHL982979:IHS982984 IRH982979:IRO982984 JBD982979:JBK982984 JKZ982979:JLG982984 JUV982979:JVC982984 KER982979:KEY982984 KON982979:KOU982984 KYJ982979:KYQ982984 LIF982979:LIM982984 LSB982979:LSI982984 MBX982979:MCE982984 MLT982979:MMA982984 MVP982979:MVW982984 NFL982979:NFS982984 NPH982979:NPO982984 NZD982979:NZK982984 OIZ982979:OJG982984 OSV982979:OTC982984 PCR982979:PCY982984 PMN982979:PMU982984 PWJ982979:PWQ982984 QGF982979:QGM982984 QQB982979:QQI982984 QZX982979:RAE982984 RJT982979:RKA982984 RTP982979:RTW982984 SDL982979:SDS982984 SNH982979:SNO982984 SXD982979:SXK982984 TGZ982979:THG982984 TQV982979:TRC982984 UAR982979:UAY982984 UKN982979:UKU982984 UUJ982979:UUQ982984 VEF982979:VEM982984 VOB982979:VOI982984 VXX982979:VYE982984 WHT982979:WIA982984 WRP982979:WRW982984 FD65475:FK65480 OZ65475:PG65480 YV65475:ZC65480 AIR65475:AIY65480 ASN65475:ASU65480 BCJ65475:BCQ65480 BMF65475:BMM65480 BWB65475:BWI65480 CFX65475:CGE65480 CPT65475:CQA65480 CZP65475:CZW65480 DJL65475:DJS65480 DTH65475:DTO65480 EDD65475:EDK65480 EMZ65475:ENG65480 EWV65475:EXC65480 FGR65475:FGY65480 FQN65475:FQU65480 GAJ65475:GAQ65480 GKF65475:GKM65480 GUB65475:GUI65480 HDX65475:HEE65480 HNT65475:HOA65480 HXP65475:HXW65480 IHL65475:IHS65480 IRH65475:IRO65480 JBD65475:JBK65480 JKZ65475:JLG65480 JUV65475:JVC65480 KER65475:KEY65480 KON65475:KOU65480 KYJ65475:KYQ65480 LIF65475:LIM65480 LSB65475:LSI65480 MBX65475:MCE65480 MLT65475:MMA65480 MVP65475:MVW65480 NFL65475:NFS65480 NPH65475:NPO65480 NZD65475:NZK65480 OIZ65475:OJG65480 OSV65475:OTC65480 PCR65475:PCY65480 PMN65475:PMU65480 PWJ65475:PWQ65480 QGF65475:QGM65480 QQB65475:QQI65480 QZX65475:RAE65480 RJT65475:RKA65480 RTP65475:RTW65480 SDL65475:SDS65480 SNH65475:SNO65480 SXD65475:SXK65480 TGZ65475:THG65480 TQV65475:TRC65480 UAR65475:UAY65480 UKN65475:UKU65480 UUJ65475:UUQ65480 VEF65475:VEM65480 VOB65475:VOI65480 VXX65475:VYE65480 WHT65475:WIA65480 WRP65475:WRW65480 FD131011:FK131016 OZ131011:PG131016 YV131011:ZC131016 AIR131011:AIY131016 ASN131011:ASU131016 BCJ131011:BCQ131016 BMF131011:BMM131016 BWB131011:BWI131016 CFX131011:CGE131016 CPT131011:CQA131016 CZP131011:CZW131016 DJL131011:DJS131016 DTH131011:DTO131016 EDD131011:EDK131016 EMZ131011:ENG131016 EWV131011:EXC131016 FGR131011:FGY131016 FQN131011:FQU131016 GAJ131011:GAQ131016 GKF131011:GKM131016 GUB131011:GUI131016 HDX131011:HEE131016 HNT131011:HOA131016 HXP131011:HXW131016 IHL131011:IHS131016 IRH131011:IRO131016 JBD131011:JBK131016 JKZ131011:JLG131016 JUV131011:JVC131016 KER131011:KEY131016 KON131011:KOU131016 KYJ131011:KYQ131016 LIF131011:LIM131016 LSB131011:LSI131016 MBX131011:MCE131016 MLT131011:MMA131016 MVP131011:MVW131016 NFL131011:NFS131016 NPH131011:NPO131016 NZD131011:NZK131016 OIZ131011:OJG131016 OSV131011:OTC131016 PCR131011:PCY131016 PMN131011:PMU131016 PWJ131011:PWQ131016 QGF131011:QGM131016 QQB131011:QQI131016 QZX131011:RAE131016 RJT131011:RKA131016 RTP131011:RTW131016 SDL131011:SDS131016 SNH131011:SNO131016 SXD131011:SXK131016 TGZ131011:THG131016 TQV131011:TRC131016 UAR131011:UAY131016 UKN131011:UKU131016 UUJ131011:UUQ131016 VEF131011:VEM131016 VOB131011:VOI131016 VXX131011:VYE131016 WHT131011:WIA131016 WRP131011:WRW131016 FD196547:FK196552 OZ196547:PG196552 YV196547:ZC196552 AIR196547:AIY196552 ASN196547:ASU196552 BCJ196547:BCQ196552 BMF196547:BMM196552 BWB196547:BWI196552 CFX196547:CGE196552 CPT196547:CQA196552 CZP196547:CZW196552 DJL196547:DJS196552 DTH196547:DTO196552 EDD196547:EDK196552 EMZ196547:ENG196552 EWV196547:EXC196552 FGR196547:FGY196552 FQN196547:FQU196552 GAJ196547:GAQ196552 GKF196547:GKM196552 GUB196547:GUI196552 HDX196547:HEE196552 HNT196547:HOA196552 HXP196547:HXW196552 IHL196547:IHS196552 IRH196547:IRO196552 JBD196547:JBK196552 JKZ196547:JLG196552 JUV196547:JVC196552 KER196547:KEY196552 KON196547:KOU196552 KYJ196547:KYQ196552 LIF196547:LIM196552 LSB196547:LSI196552 MBX196547:MCE196552 MLT196547:MMA196552 MVP196547:MVW196552 NFL196547:NFS196552 NPH196547:NPO196552 NZD196547:NZK196552 OIZ196547:OJG196552 OSV196547:OTC196552 PCR196547:PCY196552 PMN196547:PMU196552 PWJ196547:PWQ196552 QGF196547:QGM196552 QQB196547:QQI196552 QZX196547:RAE196552 RJT196547:RKA196552 RTP196547:RTW196552 SDL196547:SDS196552 SNH196547:SNO196552 SXD196547:SXK196552 TGZ196547:THG196552 TQV196547:TRC196552 UAR196547:UAY196552 UKN196547:UKU196552 UUJ196547:UUQ196552 VEF196547:VEM196552 VOB196547:VOI196552 VXX196547:VYE196552 WHT196547:WIA196552 WRP196547:WRW196552 FD262083:FK262088 OZ262083:PG262088 YV262083:ZC262088 AIR262083:AIY262088 ASN262083:ASU262088 BCJ262083:BCQ262088 BMF262083:BMM262088 BWB262083:BWI262088 CFX262083:CGE262088 CPT262083:CQA262088 CZP262083:CZW262088 DJL262083:DJS262088 DTH262083:DTO262088 EDD262083:EDK262088 EMZ262083:ENG262088 EWV262083:EXC262088 FGR262083:FGY262088 FQN262083:FQU262088 GAJ262083:GAQ262088 GKF262083:GKM262088 GUB262083:GUI262088 HDX262083:HEE262088 HNT262083:HOA262088 HXP262083:HXW262088 IHL262083:IHS262088 IRH262083:IRO262088 JBD262083:JBK262088 JKZ262083:JLG262088 JUV262083:JVC262088 KER262083:KEY262088 KON262083:KOU262088 KYJ262083:KYQ262088 LIF262083:LIM262088 LSB262083:LSI262088 MBX262083:MCE262088 MLT262083:MMA262088 MVP262083:MVW262088 NFL262083:NFS262088 NPH262083:NPO262088 NZD262083:NZK262088 OIZ262083:OJG262088 OSV262083:OTC262088 PCR262083:PCY262088 PMN262083:PMU262088 PWJ262083:PWQ262088 QGF262083:QGM262088 QQB262083:QQI262088 QZX262083:RAE262088 RJT262083:RKA262088 RTP262083:RTW262088 SDL262083:SDS262088 SNH262083:SNO262088 SXD262083:SXK262088 TGZ262083:THG262088 TQV262083:TRC262088 UAR262083:UAY262088 UKN262083:UKU262088 UUJ262083:UUQ262088 VEF262083:VEM262088 VOB262083:VOI262088 VXX262083:VYE262088 WHT262083:WIA262088 WRP262083:WRW262088 FD327619:FK327624 OZ327619:PG327624 YV327619:ZC327624 AIR327619:AIY327624 ASN327619:ASU327624 BCJ327619:BCQ327624 BMF327619:BMM327624 BWB327619:BWI327624 CFX327619:CGE327624 CPT327619:CQA327624 CZP327619:CZW327624 DJL327619:DJS327624 DTH327619:DTO327624 EDD327619:EDK327624 EMZ327619:ENG327624 EWV327619:EXC327624 FGR327619:FGY327624 FQN327619:FQU327624 GAJ327619:GAQ327624 GKF327619:GKM327624 GUB327619:GUI327624 HDX327619:HEE327624 HNT327619:HOA327624 HXP327619:HXW327624 IHL327619:IHS327624 IRH327619:IRO327624 JBD327619:JBK327624 JKZ327619:JLG327624 JUV327619:JVC327624 KER327619:KEY327624 KON327619:KOU327624 KYJ327619:KYQ327624 LIF327619:LIM327624 LSB327619:LSI327624 MBX327619:MCE327624 MLT327619:MMA327624 MVP327619:MVW327624 NFL327619:NFS327624 NPH327619:NPO327624 NZD327619:NZK327624 OIZ327619:OJG327624 OSV327619:OTC327624 PCR327619:PCY327624 PMN327619:PMU327624 PWJ327619:PWQ327624 QGF327619:QGM327624 QQB327619:QQI327624 QZX327619:RAE327624 RJT327619:RKA327624 RTP327619:RTW327624 SDL327619:SDS327624 SNH327619:SNO327624 SXD327619:SXK327624 TGZ327619:THG327624 TQV327619:TRC327624 UAR327619:UAY327624 UKN327619:UKU327624 UUJ327619:UUQ327624 VEF327619:VEM327624 VOB327619:VOI327624 VXX327619:VYE327624 WHT327619:WIA327624 WRP327619:WRW327624 FD393155:FK393160 OZ393155:PG393160 YV393155:ZC393160 AIR393155:AIY393160 ASN393155:ASU393160 BCJ393155:BCQ393160 BMF393155:BMM393160 BWB393155:BWI393160 CFX393155:CGE393160 CPT393155:CQA393160 CZP393155:CZW393160 DJL393155:DJS393160 DTH393155:DTO393160 EDD393155:EDK393160 EMZ393155:ENG393160 EWV393155:EXC393160 FGR393155:FGY393160 FQN393155:FQU393160 GAJ393155:GAQ393160 GKF393155:GKM393160 GUB393155:GUI393160 HDX393155:HEE393160 HNT393155:HOA393160 HXP393155:HXW393160 IHL393155:IHS393160 IRH393155:IRO393160 JBD393155:JBK393160 JKZ393155:JLG393160 JUV393155:JVC393160 KER393155:KEY393160 KON393155:KOU393160 KYJ393155:KYQ393160 LIF393155:LIM393160 LSB393155:LSI393160 MBX393155:MCE393160 MLT393155:MMA393160 MVP393155:MVW393160 NFL393155:NFS393160 NPH393155:NPO393160 NZD393155:NZK393160 OIZ393155:OJG393160 OSV393155:OTC393160 PCR393155:PCY393160 PMN393155:PMU393160 PWJ393155:PWQ393160 QGF393155:QGM393160 QQB393155:QQI393160 QZX393155:RAE393160 RJT393155:RKA393160 RTP393155:RTW393160 SDL393155:SDS393160 SNH393155:SNO393160 SXD393155:SXK393160 TGZ393155:THG393160 TQV393155:TRC393160 UAR393155:UAY393160 UKN393155:UKU393160 UUJ393155:UUQ393160 VEF393155:VEM393160 VOB393155:VOI393160 VXX393155:VYE393160 WHT393155:WIA393160 WRP393155:WRW393160 FD458691:FK458696 OZ458691:PG458696 YV458691:ZC458696 AIR458691:AIY458696 ASN458691:ASU458696 BCJ458691:BCQ458696 BMF458691:BMM458696 BWB458691:BWI458696 CFX458691:CGE458696 CPT458691:CQA458696 CZP458691:CZW458696 DJL458691:DJS458696 DTH458691:DTO458696 EDD458691:EDK458696 EMZ458691:ENG458696 EWV458691:EXC458696 FGR458691:FGY458696 FQN458691:FQU458696 GAJ458691:GAQ458696 GKF458691:GKM458696 GUB458691:GUI458696 HDX458691:HEE458696 HNT458691:HOA458696 HXP458691:HXW458696 IHL458691:IHS458696 IRH458691:IRO458696 JBD458691:JBK458696 JKZ458691:JLG458696 JUV458691:JVC458696 KER458691:KEY458696 KON458691:KOU458696 KYJ458691:KYQ458696 LIF458691:LIM458696 LSB458691:LSI458696 MBX458691:MCE458696 MLT458691:MMA458696 MVP458691:MVW458696 NFL458691:NFS458696 NPH458691:NPO458696 NZD458691:NZK458696 OIZ458691:OJG458696 OSV458691:OTC458696 PCR458691:PCY458696 PMN458691:PMU458696 PWJ458691:PWQ458696 QGF458691:QGM458696 QQB458691:QQI458696 QZX458691:RAE458696 RJT458691:RKA458696 RTP458691:RTW458696 SDL458691:SDS458696 SNH458691:SNO458696 SXD458691:SXK458696 TGZ458691:THG458696 TQV458691:TRC458696 UAR458691:UAY458696 UKN458691:UKU458696 UUJ458691:UUQ458696 VEF458691:VEM458696 VOB458691:VOI458696 VXX458691:VYE458696 WHT458691:WIA458696 WRP458691:WRW458696 FD524227:FK524232 OZ524227:PG524232 YV524227:ZC524232 AIR524227:AIY524232 ASN524227:ASU524232 BCJ524227:BCQ524232 BMF524227:BMM524232 BWB524227:BWI524232 CFX524227:CGE524232 CPT524227:CQA524232 CZP524227:CZW524232 DJL524227:DJS524232 DTH524227:DTO524232 EDD524227:EDK524232 EMZ524227:ENG524232 EWV524227:EXC524232 FGR524227:FGY524232 FQN524227:FQU524232 GAJ524227:GAQ524232 GKF524227:GKM524232 GUB524227:GUI524232 HDX524227:HEE524232 HNT524227:HOA524232 HXP524227:HXW524232 IHL524227:IHS524232 IRH524227:IRO524232 JBD524227:JBK524232 JKZ524227:JLG524232 JUV524227:JVC524232 KER524227:KEY524232 KON524227:KOU524232 KYJ524227:KYQ524232 LIF524227:LIM524232 LSB524227:LSI524232 MBX524227:MCE524232 MLT524227:MMA524232 MVP524227:MVW524232 NFL524227:NFS524232 NPH524227:NPO524232 NZD524227:NZK524232 OIZ524227:OJG524232 OSV524227:OTC524232 PCR524227:PCY524232 PMN524227:PMU524232 PWJ524227:PWQ524232 QGF524227:QGM524232 QQB524227:QQI524232 QZX524227:RAE524232 RJT524227:RKA524232 RTP524227:RTW524232 SDL524227:SDS524232 SNH524227:SNO524232 SXD524227:SXK524232 TGZ524227:THG524232 TQV524227:TRC524232 UAR524227:UAY524232 UKN524227:UKU524232 UUJ524227:UUQ524232 VEF524227:VEM524232 VOB524227:VOI524232 VXX524227:VYE524232 WHT524227:WIA524232 WRP524227:WRW524232 FD589763:FK589768 OZ589763:PG589768 YV589763:ZC589768 AIR589763:AIY589768 ASN589763:ASU589768 BCJ589763:BCQ589768 BMF589763:BMM589768 BWB589763:BWI589768 CFX589763:CGE589768 CPT589763:CQA589768 CZP589763:CZW589768 DJL589763:DJS589768 DTH589763:DTO589768 EDD589763:EDK589768 EMZ589763:ENG589768 EWV589763:EXC589768 FGR589763:FGY589768 FQN589763:FQU589768 GAJ589763:GAQ589768 GKF589763:GKM589768 GUB589763:GUI589768 HDX589763:HEE589768 HNT589763:HOA589768 HXP589763:HXW589768 IHL589763:IHS589768 IRH589763:IRO589768 JBD589763:JBK589768 JKZ589763:JLG589768 JUV589763:JVC589768 KER589763:KEY589768 KON589763:KOU589768 KYJ589763:KYQ589768 LIF589763:LIM589768 LSB589763:LSI589768 MBX589763:MCE589768 MLT589763:MMA589768 MVP589763:MVW589768 NFL589763:NFS589768 NPH589763:NPO589768 NZD589763:NZK589768 OIZ589763:OJG589768 OSV589763:OTC589768 PCR589763:PCY589768 PMN589763:PMU589768 PWJ589763:PWQ589768 QGF589763:QGM589768 QQB589763:QQI589768 QZX589763:RAE589768 RJT589763:RKA589768 RTP589763:RTW589768 SDL589763:SDS589768 SNH589763:SNO589768 SXD589763:SXK589768 TGZ589763:THG589768 TQV589763:TRC589768 UAR589763:UAY589768 UKN589763:UKU589768 UUJ589763:UUQ589768 VEF589763:VEM589768 VOB589763:VOI589768 VXX589763:VYE589768 WHT589763:WIA589768 WRP589763:WRW589768 FD655299:FK655304 OZ655299:PG655304 YV655299:ZC655304 AIR655299:AIY655304 ASN655299:ASU655304 BCJ655299:BCQ655304 BMF655299:BMM655304 BWB655299:BWI655304 CFX655299:CGE655304 CPT655299:CQA655304 CZP655299:CZW655304 DJL655299:DJS655304 DTH655299:DTO655304 EDD655299:EDK655304 EMZ655299:ENG655304 EWV655299:EXC655304 FGR655299:FGY655304 FQN655299:FQU655304 GAJ655299:GAQ655304 GKF655299:GKM655304 GUB655299:GUI655304 HDX655299:HEE655304 HNT655299:HOA655304 HXP655299:HXW655304 IHL655299:IHS655304 IRH655299:IRO655304 JBD655299:JBK655304 JKZ655299:JLG655304 JUV655299:JVC655304 KER655299:KEY655304 KON655299:KOU655304 KYJ655299:KYQ655304 LIF655299:LIM655304 LSB655299:LSI655304 MBX655299:MCE655304 MLT655299:MMA655304 MVP655299:MVW655304 NFL655299:NFS655304 NPH655299:NPO655304 NZD655299:NZK655304 OIZ655299:OJG655304 OSV655299:OTC655304 PCR655299:PCY655304 PMN655299:PMU655304 PWJ655299:PWQ655304 QGF655299:QGM655304 QQB655299:QQI655304 QZX655299:RAE655304 RJT655299:RKA655304 RTP655299:RTW655304 SDL655299:SDS655304 SNH655299:SNO655304 SXD655299:SXK655304 TGZ655299:THG655304 TQV655299:TRC655304 UAR655299:UAY655304 UKN655299:UKU655304 UUJ655299:UUQ655304 VEF655299:VEM655304 VOB655299:VOI655304 VXX655299:VYE655304 WHT655299:WIA655304 WRP655299:WRW655304 FD720835:FK720840 OZ720835:PG720840 YV720835:ZC720840 AIR720835:AIY720840 ASN720835:ASU720840 BCJ720835:BCQ720840 BMF720835:BMM720840 BWB720835:BWI720840 CFX720835:CGE720840 CPT720835:CQA720840 CZP720835:CZW720840 DJL720835:DJS720840 DTH720835:DTO720840 EDD720835:EDK720840 EMZ720835:ENG720840 EWV720835:EXC720840 FGR720835:FGY720840 FQN720835:FQU720840 GAJ720835:GAQ720840 GKF720835:GKM720840 GUB720835:GUI720840 HDX720835:HEE720840 HNT720835:HOA720840 HXP720835:HXW720840 IHL720835:IHS720840 IRH720835:IRO720840 JBD720835:JBK720840 JKZ720835:JLG720840 JUV720835:JVC720840 KER720835:KEY720840 KON720835:KOU720840 KYJ720835:KYQ720840 LIF720835:LIM720840 LSB720835:LSI720840 MBX720835:MCE720840 MLT720835:MMA720840 MVP720835:MVW720840 NFL720835:NFS720840 NPH720835:NPO720840 NZD720835:NZK720840 OIZ720835:OJG720840 OSV720835:OTC720840 PCR720835:PCY720840 PMN720835:PMU720840 PWJ720835:PWQ720840 QGF720835:QGM720840 QQB720835:QQI720840 QZX720835:RAE720840 RJT720835:RKA720840 RTP720835:RTW720840 SDL720835:SDS720840 SNH720835:SNO720840 SXD720835:SXK720840 TGZ720835:THG720840 TQV720835:TRC720840 UAR720835:UAY720840 UKN720835:UKU720840 UUJ720835:UUQ720840 VEF720835:VEM720840 VOB720835:VOI720840 VXX720835:VYE720840 WHT720835:WIA720840 WRP720835:WRW720840 FD786371:FK786376 OZ786371:PG786376 YV786371:ZC786376 AIR786371:AIY786376 ASN786371:ASU786376 BCJ786371:BCQ786376 BMF786371:BMM786376 BWB786371:BWI786376 CFX786371:CGE786376 CPT786371:CQA786376 CZP786371:CZW786376 DJL786371:DJS786376 DTH786371:DTO786376 EDD786371:EDK786376 EMZ786371:ENG786376 EWV786371:EXC786376 FGR786371:FGY786376 FQN786371:FQU786376 GAJ786371:GAQ786376 GKF786371:GKM786376 GUB786371:GUI786376 HDX786371:HEE786376 HNT786371:HOA786376 HXP786371:HXW786376 IHL786371:IHS786376 IRH786371:IRO786376 JBD786371:JBK786376 JKZ786371:JLG786376 JUV786371:JVC786376 KER786371:KEY786376 KON786371:KOU786376 KYJ786371:KYQ786376 LIF786371:LIM786376 LSB786371:LSI786376 MBX786371:MCE786376 MLT786371:MMA786376 MVP786371:MVW786376 NFL786371:NFS786376 NPH786371:NPO786376 NZD786371:NZK786376 OIZ786371:OJG786376 OSV786371:OTC786376 PCR786371:PCY786376 PMN786371:PMU786376 PWJ786371:PWQ786376 QGF786371:QGM786376 QQB786371:QQI786376 QZX786371:RAE786376 RJT786371:RKA786376 RTP786371:RTW786376 SDL786371:SDS786376 SNH786371:SNO786376 SXD786371:SXK786376 TGZ786371:THG786376 TQV786371:TRC786376 UAR786371:UAY786376 UKN786371:UKU786376 UUJ786371:UUQ786376 VEF786371:VEM786376 VOB786371:VOI786376 VXX786371:VYE786376 WHT786371:WIA786376 WRP786371:WRW786376 FD851907:FK851912 OZ851907:PG851912 YV851907:ZC851912 AIR851907:AIY851912 ASN851907:ASU851912 BCJ851907:BCQ851912 BMF851907:BMM851912 BWB851907:BWI851912 CFX851907:CGE851912 CPT851907:CQA851912 CZP851907:CZW851912 DJL851907:DJS851912 DTH851907:DTO851912 EDD851907:EDK851912 EMZ851907:ENG851912 EWV851907:EXC851912 FGR851907:FGY851912 FQN851907:FQU851912 GAJ851907:GAQ851912 GKF851907:GKM851912 GUB851907:GUI851912 HDX851907:HEE851912 HNT851907:HOA851912 HXP851907:HXW851912 IHL851907:IHS851912 IRH851907:IRO851912 JBD851907:JBK851912 JKZ851907:JLG851912 JUV851907:JVC851912 KER851907:KEY851912 KON851907:KOU851912 KYJ851907:KYQ851912 LIF851907:LIM851912 LSB851907:LSI851912 MBX851907:MCE851912 MLT851907:MMA851912 MVP851907:MVW851912 NFL851907:NFS851912 NPH851907:NPO851912 NZD851907:NZK851912 OIZ851907:OJG851912 OSV851907:OTC851912 PCR851907:PCY851912 PMN851907:PMU851912 PWJ851907:PWQ851912 QGF851907:QGM851912 QQB851907:QQI851912 QZX851907:RAE851912 RJT851907:RKA851912 RTP851907:RTW851912 SDL851907:SDS851912 SNH851907:SNO851912 SXD851907:SXK851912 TGZ851907:THG851912 TQV851907:TRC851912 UAR851907:UAY851912 UKN851907:UKU851912 UUJ851907:UUQ851912 VEF851907:VEM851912 VOB851907:VOI851912 VXX851907:VYE851912 WHT851907:WIA851912 WRP851907:WRW851912 FD917443:FK917448 OZ917443:PG917448 YV917443:ZC917448 AIR917443:AIY917448 ASN917443:ASU917448 BCJ917443:BCQ917448 BMF917443:BMM917448 BWB917443:BWI917448 CFX917443:CGE917448 CPT917443:CQA917448 CZP917443:CZW917448 DJL917443:DJS917448 DTH917443:DTO917448 EDD917443:EDK917448 EMZ917443:ENG917448 EWV917443:EXC917448 FGR917443:FGY917448 FQN917443:FQU917448 GAJ917443:GAQ917448 GKF917443:GKM917448 GUB917443:GUI917448 HDX917443:HEE917448 HNT917443:HOA917448 HXP917443:HXW917448 IHL917443:IHS917448 IRH917443:IRO917448 JBD917443:JBK917448 JKZ917443:JLG917448 JUV917443:JVC917448 KER917443:KEY917448 KON917443:KOU917448 KYJ917443:KYQ917448 LIF917443:LIM917448 LSB917443:LSI917448 MBX917443:MCE917448 MLT917443:MMA917448 MVP917443:MVW917448 NFL917443:NFS917448 NPH917443:NPO917448 NZD917443:NZK917448 OIZ917443:OJG917448 OSV917443:OTC917448 PCR917443:PCY917448 PMN917443:PMU917448 PWJ917443:PWQ917448 QGF917443:QGM917448 QQB917443:QQI917448 QZX917443:RAE917448 RJT917443:RKA917448 RTP917443:RTW917448 SDL917443:SDS917448 SNH917443:SNO917448 SXD917443:SXK917448 TGZ917443:THG917448 TQV917443:TRC917448 UAR917443:UAY917448 UKN917443:UKU917448 UUJ917443:UUQ917448 VEF917443:VEM917448 VOB917443:VOI917448 VXX917443:VYE917448 WHT917443:WIA917448 WRP917443:WRW917448" xr:uid="{BE7BF132-F066-4604-9695-32F2E292FD1C}">
+      <formula1>"サーバ,クライアント"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WRB982938:WRP982975 VNN982938:VOB982975 VDR982938:VEF982975 UTV982938:UUJ982975 UJZ982938:UKN982975 UAD982938:UAR982975 TQH982938:TQV982975 TGL982938:TGZ982975 SWP982938:SXD982975 SMT982938:SNH982975 SCX982938:SDL982975 RTB982938:RTP982975 RJF982938:RJT982975 QZJ982938:QZX982975 QPN982938:QQB982975 QFR982938:QGF982975 PVV982938:PWJ982975 PLZ982938:PMN982975 PCD982938:PCR982975 OSH982938:OSV982975 OIL982938:OIZ982975 NYP982938:NZD982975 NOT982938:NPH982975 NEX982938:NFL982975 MVB982938:MVP982975 MLF982938:MLT982975 MBJ982938:MBX982975 LRN982938:LSB982975 LHR982938:LIF982975 KXV982938:KYJ982975 KNZ982938:KON982975 KED982938:KER982975 JUH982938:JUV982975 JKL982938:JKZ982975 JAP982938:JBD982975 IQT982938:IRH982975 IGX982938:IHL982975 HXB982938:HXP982975 HNF982938:HNT982975 HDJ982938:HDX982975 GTN982938:GUB982975 GJR982938:GKF982975 FZV982938:GAJ982975 FPZ982938:FQN982975 FGD982938:FGR982975 EWH982938:EWV982975 EML982938:EMZ982975 ECP982938:EDD982975 DST982938:DTH982975 DIX982938:DJL982975 CZB982938:CZP982975 CPF982938:CPT982975 CFJ982938:CFX982975 BVN982938:BWB982975 BLR982938:BMF982975 BBV982938:BCJ982975 ARZ982938:ASN982975 AID982938:AIR982975 YH982938:YV982975 OL982938:OZ982975 EP982938:FD982975 WRB917402:WRP917439 WHF917402:WHT917439 VXJ917402:VXX917439 VNN917402:VOB917439 VDR917402:VEF917439 UTV917402:UUJ917439 UJZ917402:UKN917439 UAD917402:UAR917439 TQH917402:TQV917439 TGL917402:TGZ917439 SWP917402:SXD917439 SMT917402:SNH917439 SCX917402:SDL917439 RTB917402:RTP917439 RJF917402:RJT917439 QZJ917402:QZX917439 QPN917402:QQB917439 QFR917402:QGF917439 PVV917402:PWJ917439 PLZ917402:PMN917439 PCD917402:PCR917439 OSH917402:OSV917439 OIL917402:OIZ917439 NYP917402:NZD917439 NOT917402:NPH917439 NEX917402:NFL917439 MVB917402:MVP917439 MLF917402:MLT917439 MBJ917402:MBX917439 LRN917402:LSB917439 LHR917402:LIF917439 KXV917402:KYJ917439 KNZ917402:KON917439 KED917402:KER917439 JUH917402:JUV917439 JKL917402:JKZ917439 JAP917402:JBD917439 IQT917402:IRH917439 IGX917402:IHL917439 HXB917402:HXP917439 HNF917402:HNT917439 HDJ917402:HDX917439 GTN917402:GUB917439 GJR917402:GKF917439 FZV917402:GAJ917439 FPZ917402:FQN917439 FGD917402:FGR917439 EWH917402:EWV917439 EML917402:EMZ917439 ECP917402:EDD917439 DST917402:DTH917439 DIX917402:DJL917439 CZB917402:CZP917439 CPF917402:CPT917439 CFJ917402:CFX917439 BVN917402:BWB917439 BLR917402:BMF917439 BBV917402:BCJ917439 ARZ917402:ASN917439 AID917402:AIR917439 YH917402:YV917439 OL917402:OZ917439 EP917402:FD917439 WRB851866:WRP851903 WHF851866:WHT851903 VXJ851866:VXX851903 VNN851866:VOB851903 VDR851866:VEF851903 UTV851866:UUJ851903 UJZ851866:UKN851903 UAD851866:UAR851903 TQH851866:TQV851903 TGL851866:TGZ851903 SWP851866:SXD851903 SMT851866:SNH851903 SCX851866:SDL851903 RTB851866:RTP851903 RJF851866:RJT851903 QZJ851866:QZX851903 QPN851866:QQB851903 QFR851866:QGF851903 PVV851866:PWJ851903 PLZ851866:PMN851903 PCD851866:PCR851903 OSH851866:OSV851903 OIL851866:OIZ851903 NYP851866:NZD851903 NOT851866:NPH851903 NEX851866:NFL851903 MVB851866:MVP851903 MLF851866:MLT851903 MBJ851866:MBX851903 LRN851866:LSB851903 LHR851866:LIF851903 KXV851866:KYJ851903 KNZ851866:KON851903 KED851866:KER851903 JUH851866:JUV851903 JKL851866:JKZ851903 JAP851866:JBD851903 IQT851866:IRH851903 IGX851866:IHL851903 HXB851866:HXP851903 HNF851866:HNT851903 HDJ851866:HDX851903 GTN851866:GUB851903 GJR851866:GKF851903 FZV851866:GAJ851903 FPZ851866:FQN851903 FGD851866:FGR851903 EWH851866:EWV851903 EML851866:EMZ851903 ECP851866:EDD851903 DST851866:DTH851903 DIX851866:DJL851903 CZB851866:CZP851903 CPF851866:CPT851903 CFJ851866:CFX851903 BVN851866:BWB851903 BLR851866:BMF851903 BBV851866:BCJ851903 ARZ851866:ASN851903 AID851866:AIR851903 YH851866:YV851903 OL851866:OZ851903 EP851866:FD851903 WRB786330:WRP786367 WHF786330:WHT786367 VXJ786330:VXX786367 VNN786330:VOB786367 VDR786330:VEF786367 UTV786330:UUJ786367 UJZ786330:UKN786367 UAD786330:UAR786367 TQH786330:TQV786367 TGL786330:TGZ786367 SWP786330:SXD786367 SMT786330:SNH786367 SCX786330:SDL786367 RTB786330:RTP786367 RJF786330:RJT786367 QZJ786330:QZX786367 QPN786330:QQB786367 QFR786330:QGF786367 PVV786330:PWJ786367 PLZ786330:PMN786367 PCD786330:PCR786367 OSH786330:OSV786367 OIL786330:OIZ786367 NYP786330:NZD786367 NOT786330:NPH786367 NEX786330:NFL786367 MVB786330:MVP786367 MLF786330:MLT786367 MBJ786330:MBX786367 LRN786330:LSB786367 LHR786330:LIF786367 KXV786330:KYJ786367 KNZ786330:KON786367 KED786330:KER786367 JUH786330:JUV786367 JKL786330:JKZ786367 JAP786330:JBD786367 IQT786330:IRH786367 IGX786330:IHL786367 HXB786330:HXP786367 HNF786330:HNT786367 HDJ786330:HDX786367 GTN786330:GUB786367 GJR786330:GKF786367 FZV786330:GAJ786367 FPZ786330:FQN786367 FGD786330:FGR786367 EWH786330:EWV786367 EML786330:EMZ786367 ECP786330:EDD786367 DST786330:DTH786367 DIX786330:DJL786367 CZB786330:CZP786367 CPF786330:CPT786367 CFJ786330:CFX786367 BVN786330:BWB786367 BLR786330:BMF786367 BBV786330:BCJ786367 ARZ786330:ASN786367 AID786330:AIR786367 YH786330:YV786367 OL786330:OZ786367 EP786330:FD786367 WRB720794:WRP720831 WHF720794:WHT720831 VXJ720794:VXX720831 VNN720794:VOB720831 VDR720794:VEF720831 UTV720794:UUJ720831 UJZ720794:UKN720831 UAD720794:UAR720831 TQH720794:TQV720831 TGL720794:TGZ720831 SWP720794:SXD720831 SMT720794:SNH720831 SCX720794:SDL720831 RTB720794:RTP720831 RJF720794:RJT720831 QZJ720794:QZX720831 QPN720794:QQB720831 QFR720794:QGF720831 PVV720794:PWJ720831 PLZ720794:PMN720831 PCD720794:PCR720831 OSH720794:OSV720831 OIL720794:OIZ720831 NYP720794:NZD720831 NOT720794:NPH720831 NEX720794:NFL720831 MVB720794:MVP720831 MLF720794:MLT720831 MBJ720794:MBX720831 LRN720794:LSB720831 LHR720794:LIF720831 KXV720794:KYJ720831 KNZ720794:KON720831 KED720794:KER720831 JUH720794:JUV720831 JKL720794:JKZ720831 JAP720794:JBD720831 IQT720794:IRH720831 IGX720794:IHL720831 HXB720794:HXP720831 HNF720794:HNT720831 HDJ720794:HDX720831 GTN720794:GUB720831 GJR720794:GKF720831 FZV720794:GAJ720831 FPZ720794:FQN720831 FGD720794:FGR720831 EWH720794:EWV720831 EML720794:EMZ720831 ECP720794:EDD720831 DST720794:DTH720831 DIX720794:DJL720831 CZB720794:CZP720831 CPF720794:CPT720831 CFJ720794:CFX720831 BVN720794:BWB720831 BLR720794:BMF720831 BBV720794:BCJ720831 ARZ720794:ASN720831 AID720794:AIR720831 YH720794:YV720831 OL720794:OZ720831 EP720794:FD720831 WRB655258:WRP655295 WHF655258:WHT655295 VXJ655258:VXX655295 VNN655258:VOB655295 VDR655258:VEF655295 UTV655258:UUJ655295 UJZ655258:UKN655295 UAD655258:UAR655295 TQH655258:TQV655295 TGL655258:TGZ655295 SWP655258:SXD655295 SMT655258:SNH655295 SCX655258:SDL655295 RTB655258:RTP655295 RJF655258:RJT655295 QZJ655258:QZX655295 QPN655258:QQB655295 QFR655258:QGF655295 PVV655258:PWJ655295 PLZ655258:PMN655295 PCD655258:PCR655295 OSH655258:OSV655295 OIL655258:OIZ655295 NYP655258:NZD655295 NOT655258:NPH655295 NEX655258:NFL655295 MVB655258:MVP655295 MLF655258:MLT655295 MBJ655258:MBX655295 LRN655258:LSB655295 LHR655258:LIF655295 KXV655258:KYJ655295 KNZ655258:KON655295 KED655258:KER655295 JUH655258:JUV655295 JKL655258:JKZ655295 JAP655258:JBD655295 IQT655258:IRH655295 IGX655258:IHL655295 HXB655258:HXP655295 HNF655258:HNT655295 HDJ655258:HDX655295 GTN655258:GUB655295 GJR655258:GKF655295 FZV655258:GAJ655295 FPZ655258:FQN655295 FGD655258:FGR655295 EWH655258:EWV655295 EML655258:EMZ655295 ECP655258:EDD655295 DST655258:DTH655295 DIX655258:DJL655295 CZB655258:CZP655295 CPF655258:CPT655295 CFJ655258:CFX655295 BVN655258:BWB655295 BLR655258:BMF655295 BBV655258:BCJ655295 ARZ655258:ASN655295 AID655258:AIR655295 YH655258:YV655295 OL655258:OZ655295 EP655258:FD655295 WRB589722:WRP589759 WHF589722:WHT589759 VXJ589722:VXX589759 VNN589722:VOB589759 VDR589722:VEF589759 UTV589722:UUJ589759 UJZ589722:UKN589759 UAD589722:UAR589759 TQH589722:TQV589759 TGL589722:TGZ589759 SWP589722:SXD589759 SMT589722:SNH589759 SCX589722:SDL589759 RTB589722:RTP589759 RJF589722:RJT589759 QZJ589722:QZX589759 QPN589722:QQB589759 QFR589722:QGF589759 PVV589722:PWJ589759 PLZ589722:PMN589759 PCD589722:PCR589759 OSH589722:OSV589759 OIL589722:OIZ589759 NYP589722:NZD589759 NOT589722:NPH589759 NEX589722:NFL589759 MVB589722:MVP589759 MLF589722:MLT589759 MBJ589722:MBX589759 LRN589722:LSB589759 LHR589722:LIF589759 KXV589722:KYJ589759 KNZ589722:KON589759 KED589722:KER589759 JUH589722:JUV589759 JKL589722:JKZ589759 JAP589722:JBD589759 IQT589722:IRH589759 IGX589722:IHL589759 HXB589722:HXP589759 HNF589722:HNT589759 HDJ589722:HDX589759 GTN589722:GUB589759 GJR589722:GKF589759 FZV589722:GAJ589759 FPZ589722:FQN589759 FGD589722:FGR589759 EWH589722:EWV589759 EML589722:EMZ589759 ECP589722:EDD589759 DST589722:DTH589759 DIX589722:DJL589759 CZB589722:CZP589759 CPF589722:CPT589759 CFJ589722:CFX589759 BVN589722:BWB589759 BLR589722:BMF589759 BBV589722:BCJ589759 ARZ589722:ASN589759 AID589722:AIR589759 YH589722:YV589759 OL589722:OZ589759 EP589722:FD589759 WRB524186:WRP524223 WHF524186:WHT524223 VXJ524186:VXX524223 VNN524186:VOB524223 VDR524186:VEF524223 UTV524186:UUJ524223 UJZ524186:UKN524223 UAD524186:UAR524223 TQH524186:TQV524223 TGL524186:TGZ524223 SWP524186:SXD524223 SMT524186:SNH524223 SCX524186:SDL524223 RTB524186:RTP524223 RJF524186:RJT524223 QZJ524186:QZX524223 QPN524186:QQB524223 QFR524186:QGF524223 PVV524186:PWJ524223 PLZ524186:PMN524223 PCD524186:PCR524223 OSH524186:OSV524223 OIL524186:OIZ524223 NYP524186:NZD524223 NOT524186:NPH524223 NEX524186:NFL524223 MVB524186:MVP524223 MLF524186:MLT524223 MBJ524186:MBX524223 LRN524186:LSB524223 LHR524186:LIF524223 KXV524186:KYJ524223 KNZ524186:KON524223 KED524186:KER524223 JUH524186:JUV524223 JKL524186:JKZ524223 JAP524186:JBD524223 IQT524186:IRH524223 IGX524186:IHL524223 HXB524186:HXP524223 HNF524186:HNT524223 HDJ524186:HDX524223 GTN524186:GUB524223 GJR524186:GKF524223 FZV524186:GAJ524223 FPZ524186:FQN524223 FGD524186:FGR524223 EWH524186:EWV524223 EML524186:EMZ524223 ECP524186:EDD524223 DST524186:DTH524223 DIX524186:DJL524223 CZB524186:CZP524223 CPF524186:CPT524223 CFJ524186:CFX524223 BVN524186:BWB524223 BLR524186:BMF524223 BBV524186:BCJ524223 ARZ524186:ASN524223 AID524186:AIR524223 YH524186:YV524223 OL524186:OZ524223 EP524186:FD524223 WRB458650:WRP458687 WHF458650:WHT458687 VXJ458650:VXX458687 VNN458650:VOB458687 VDR458650:VEF458687 UTV458650:UUJ458687 UJZ458650:UKN458687 UAD458650:UAR458687 TQH458650:TQV458687 TGL458650:TGZ458687 SWP458650:SXD458687 SMT458650:SNH458687 SCX458650:SDL458687 RTB458650:RTP458687 RJF458650:RJT458687 QZJ458650:QZX458687 QPN458650:QQB458687 QFR458650:QGF458687 PVV458650:PWJ458687 PLZ458650:PMN458687 PCD458650:PCR458687 OSH458650:OSV458687 OIL458650:OIZ458687 NYP458650:NZD458687 NOT458650:NPH458687 NEX458650:NFL458687 MVB458650:MVP458687 MLF458650:MLT458687 MBJ458650:MBX458687 LRN458650:LSB458687 LHR458650:LIF458687 KXV458650:KYJ458687 KNZ458650:KON458687 KED458650:KER458687 JUH458650:JUV458687 JKL458650:JKZ458687 JAP458650:JBD458687 IQT458650:IRH458687 IGX458650:IHL458687 HXB458650:HXP458687 HNF458650:HNT458687 HDJ458650:HDX458687 GTN458650:GUB458687 GJR458650:GKF458687 FZV458650:GAJ458687 FPZ458650:FQN458687 FGD458650:FGR458687 EWH458650:EWV458687 EML458650:EMZ458687 ECP458650:EDD458687 DST458650:DTH458687 DIX458650:DJL458687 CZB458650:CZP458687 CPF458650:CPT458687 CFJ458650:CFX458687 BVN458650:BWB458687 BLR458650:BMF458687 BBV458650:BCJ458687 ARZ458650:ASN458687 AID458650:AIR458687 YH458650:YV458687 OL458650:OZ458687 EP458650:FD458687 WRB393114:WRP393151 WHF393114:WHT393151 VXJ393114:VXX393151 VNN393114:VOB393151 VDR393114:VEF393151 UTV393114:UUJ393151 UJZ393114:UKN393151 UAD393114:UAR393151 TQH393114:TQV393151 TGL393114:TGZ393151 SWP393114:SXD393151 SMT393114:SNH393151 SCX393114:SDL393151 RTB393114:RTP393151 RJF393114:RJT393151 QZJ393114:QZX393151 QPN393114:QQB393151 QFR393114:QGF393151 PVV393114:PWJ393151 PLZ393114:PMN393151 PCD393114:PCR393151 OSH393114:OSV393151 OIL393114:OIZ393151 NYP393114:NZD393151 NOT393114:NPH393151 NEX393114:NFL393151 MVB393114:MVP393151 MLF393114:MLT393151 MBJ393114:MBX393151 LRN393114:LSB393151 LHR393114:LIF393151 KXV393114:KYJ393151 KNZ393114:KON393151 KED393114:KER393151 JUH393114:JUV393151 JKL393114:JKZ393151 JAP393114:JBD393151 IQT393114:IRH393151 IGX393114:IHL393151 HXB393114:HXP393151 HNF393114:HNT393151 HDJ393114:HDX393151 GTN393114:GUB393151 GJR393114:GKF393151 FZV393114:GAJ393151 FPZ393114:FQN393151 FGD393114:FGR393151 EWH393114:EWV393151 EML393114:EMZ393151 ECP393114:EDD393151 DST393114:DTH393151 DIX393114:DJL393151 CZB393114:CZP393151 CPF393114:CPT393151 CFJ393114:CFX393151 BVN393114:BWB393151 BLR393114:BMF393151 BBV393114:BCJ393151 ARZ393114:ASN393151 AID393114:AIR393151 YH393114:YV393151 OL393114:OZ393151 EP393114:FD393151 WRB327578:WRP327615 WHF327578:WHT327615 VXJ327578:VXX327615 VNN327578:VOB327615 VDR327578:VEF327615 UTV327578:UUJ327615 UJZ327578:UKN327615 UAD327578:UAR327615 TQH327578:TQV327615 TGL327578:TGZ327615 SWP327578:SXD327615 SMT327578:SNH327615 SCX327578:SDL327615 RTB327578:RTP327615 RJF327578:RJT327615 QZJ327578:QZX327615 QPN327578:QQB327615 QFR327578:QGF327615 PVV327578:PWJ327615 PLZ327578:PMN327615 PCD327578:PCR327615 OSH327578:OSV327615 OIL327578:OIZ327615 NYP327578:NZD327615 NOT327578:NPH327615 NEX327578:NFL327615 MVB327578:MVP327615 MLF327578:MLT327615 MBJ327578:MBX327615 LRN327578:LSB327615 LHR327578:LIF327615 KXV327578:KYJ327615 KNZ327578:KON327615 KED327578:KER327615 JUH327578:JUV327615 JKL327578:JKZ327615 JAP327578:JBD327615 IQT327578:IRH327615 IGX327578:IHL327615 HXB327578:HXP327615 HNF327578:HNT327615 HDJ327578:HDX327615 GTN327578:GUB327615 GJR327578:GKF327615 FZV327578:GAJ327615 FPZ327578:FQN327615 FGD327578:FGR327615 EWH327578:EWV327615 EML327578:EMZ327615 ECP327578:EDD327615 DST327578:DTH327615 DIX327578:DJL327615 CZB327578:CZP327615 CPF327578:CPT327615 CFJ327578:CFX327615 BVN327578:BWB327615 BLR327578:BMF327615 BBV327578:BCJ327615 ARZ327578:ASN327615 AID327578:AIR327615 YH327578:YV327615 OL327578:OZ327615 EP327578:FD327615 WRB262042:WRP262079 WHF262042:WHT262079 VXJ262042:VXX262079 VNN262042:VOB262079 VDR262042:VEF262079 UTV262042:UUJ262079 UJZ262042:UKN262079 UAD262042:UAR262079 TQH262042:TQV262079 TGL262042:TGZ262079 SWP262042:SXD262079 SMT262042:SNH262079 SCX262042:SDL262079 RTB262042:RTP262079 RJF262042:RJT262079 QZJ262042:QZX262079 QPN262042:QQB262079 QFR262042:QGF262079 PVV262042:PWJ262079 PLZ262042:PMN262079 PCD262042:PCR262079 OSH262042:OSV262079 OIL262042:OIZ262079 NYP262042:NZD262079 NOT262042:NPH262079 NEX262042:NFL262079 MVB262042:MVP262079 MLF262042:MLT262079 MBJ262042:MBX262079 LRN262042:LSB262079 LHR262042:LIF262079 KXV262042:KYJ262079 KNZ262042:KON262079 KED262042:KER262079 JUH262042:JUV262079 JKL262042:JKZ262079 JAP262042:JBD262079 IQT262042:IRH262079 IGX262042:IHL262079 HXB262042:HXP262079 HNF262042:HNT262079 HDJ262042:HDX262079 GTN262042:GUB262079 GJR262042:GKF262079 FZV262042:GAJ262079 FPZ262042:FQN262079 FGD262042:FGR262079 EWH262042:EWV262079 EML262042:EMZ262079 ECP262042:EDD262079 DST262042:DTH262079 DIX262042:DJL262079 CZB262042:CZP262079 CPF262042:CPT262079 CFJ262042:CFX262079 BVN262042:BWB262079 BLR262042:BMF262079 BBV262042:BCJ262079 ARZ262042:ASN262079 AID262042:AIR262079 YH262042:YV262079 OL262042:OZ262079 EP262042:FD262079 WRB196506:WRP196543 WHF196506:WHT196543 VXJ196506:VXX196543 VNN196506:VOB196543 VDR196506:VEF196543 UTV196506:UUJ196543 UJZ196506:UKN196543 UAD196506:UAR196543 TQH196506:TQV196543 TGL196506:TGZ196543 SWP196506:SXD196543 SMT196506:SNH196543 SCX196506:SDL196543 RTB196506:RTP196543 RJF196506:RJT196543 QZJ196506:QZX196543 QPN196506:QQB196543 QFR196506:QGF196543 PVV196506:PWJ196543 PLZ196506:PMN196543 PCD196506:PCR196543 OSH196506:OSV196543 OIL196506:OIZ196543 NYP196506:NZD196543 NOT196506:NPH196543 NEX196506:NFL196543 MVB196506:MVP196543 MLF196506:MLT196543 MBJ196506:MBX196543 LRN196506:LSB196543 LHR196506:LIF196543 KXV196506:KYJ196543 KNZ196506:KON196543 KED196506:KER196543 JUH196506:JUV196543 JKL196506:JKZ196543 JAP196506:JBD196543 IQT196506:IRH196543 IGX196506:IHL196543 HXB196506:HXP196543 HNF196506:HNT196543 HDJ196506:HDX196543 GTN196506:GUB196543 GJR196506:GKF196543 FZV196506:GAJ196543 FPZ196506:FQN196543 FGD196506:FGR196543 EWH196506:EWV196543 EML196506:EMZ196543 ECP196506:EDD196543 DST196506:DTH196543 DIX196506:DJL196543 CZB196506:CZP196543 CPF196506:CPT196543 CFJ196506:CFX196543 BVN196506:BWB196543 BLR196506:BMF196543 BBV196506:BCJ196543 ARZ196506:ASN196543 AID196506:AIR196543 YH196506:YV196543 OL196506:OZ196543 EP196506:FD196543 WRB130970:WRP131007 WHF130970:WHT131007 VXJ130970:VXX131007 VNN130970:VOB131007 VDR130970:VEF131007 UTV130970:UUJ131007 UJZ130970:UKN131007 UAD130970:UAR131007 TQH130970:TQV131007 TGL130970:TGZ131007 SWP130970:SXD131007 SMT130970:SNH131007 SCX130970:SDL131007 RTB130970:RTP131007 RJF130970:RJT131007 QZJ130970:QZX131007 QPN130970:QQB131007 QFR130970:QGF131007 PVV130970:PWJ131007 PLZ130970:PMN131007 PCD130970:PCR131007 OSH130970:OSV131007 OIL130970:OIZ131007 NYP130970:NZD131007 NOT130970:NPH131007 NEX130970:NFL131007 MVB130970:MVP131007 MLF130970:MLT131007 MBJ130970:MBX131007 LRN130970:LSB131007 LHR130970:LIF131007 KXV130970:KYJ131007 KNZ130970:KON131007 KED130970:KER131007 JUH130970:JUV131007 JKL130970:JKZ131007 JAP130970:JBD131007 IQT130970:IRH131007 IGX130970:IHL131007 HXB130970:HXP131007 HNF130970:HNT131007 HDJ130970:HDX131007 GTN130970:GUB131007 GJR130970:GKF131007 FZV130970:GAJ131007 FPZ130970:FQN131007 FGD130970:FGR131007 EWH130970:EWV131007 EML130970:EMZ131007 ECP130970:EDD131007 DST130970:DTH131007 DIX130970:DJL131007 CZB130970:CZP131007 CPF130970:CPT131007 CFJ130970:CFX131007 BVN130970:BWB131007 BLR130970:BMF131007 BBV130970:BCJ131007 ARZ130970:ASN131007 AID130970:AIR131007 YH130970:YV131007 OL130970:OZ131007 EP130970:FD131007 WRB65434:WRP65471 WHF65434:WHT65471 VXJ65434:VXX65471 VNN65434:VOB65471 VDR65434:VEF65471 UTV65434:UUJ65471 UJZ65434:UKN65471 UAD65434:UAR65471 TQH65434:TQV65471 TGL65434:TGZ65471 SWP65434:SXD65471 SMT65434:SNH65471 SCX65434:SDL65471 RTB65434:RTP65471 RJF65434:RJT65471 QZJ65434:QZX65471 QPN65434:QQB65471 QFR65434:QGF65471 PVV65434:PWJ65471 PLZ65434:PMN65471 PCD65434:PCR65471 OSH65434:OSV65471 OIL65434:OIZ65471 NYP65434:NZD65471 NOT65434:NPH65471 NEX65434:NFL65471 MVB65434:MVP65471 MLF65434:MLT65471 MBJ65434:MBX65471 LRN65434:LSB65471 LHR65434:LIF65471 KXV65434:KYJ65471 KNZ65434:KON65471 KED65434:KER65471 JUH65434:JUV65471 JKL65434:JKZ65471 JAP65434:JBD65471 IQT65434:IRH65471 IGX65434:IHL65471 HXB65434:HXP65471 HNF65434:HNT65471 HDJ65434:HDX65471 GTN65434:GUB65471 GJR65434:GKF65471 FZV65434:GAJ65471 FPZ65434:FQN65471 FGD65434:FGR65471 EWH65434:EWV65471 EML65434:EMZ65471 ECP65434:EDD65471 DST65434:DTH65471 DIX65434:DJL65471 CZB65434:CZP65471 CPF65434:CPT65471 CFJ65434:CFX65471 BVN65434:BWB65471 BLR65434:BMF65471 BBV65434:BCJ65471 ARZ65434:ASN65471 AID65434:AIR65471 YH65434:YV65471 OL65434:OZ65471 EP65434:FD65471 WHF982938:WHT982975 VXJ982938:VXX982975 WHF2:WHT9 WRB2:WRP9 EP2:FD9 OL2:OZ9 YH2:YV9 AID2:AIR9 ARZ2:ASN9 BBV2:BCJ9 BLR2:BMF9 BVN2:BWB9 CFJ2:CFX9 CPF2:CPT9 CZB2:CZP9 DIX2:DJL9 DST2:DTH9 ECP2:EDD9 EML2:EMZ9 EWH2:EWV9 FGD2:FGR9 FPZ2:FQN9 FZV2:GAJ9 GJR2:GKF9 GTN2:GUB9 HDJ2:HDX9 HNF2:HNT9 HXB2:HXP9 IGX2:IHL9 IQT2:IRH9 JAP2:JBD9 JKL2:JKZ9 JUH2:JUV9 KED2:KER9 KNZ2:KON9 KXV2:KYJ9 LHR2:LIF9 LRN2:LSB9 MBJ2:MBX9 MLF2:MLT9 MVB2:MVP9 NEX2:NFL9 NOT2:NPH9 NYP2:NZD9 OIL2:OIZ9 OSH2:OSV9 PCD2:PCR9 PLZ2:PMN9 PVV2:PWJ9 QFR2:QGF9 QPN2:QQB9 QZJ2:QZX9 RJF2:RJT9 RTB2:RTP9 SCX2:SDL9 SMT2:SNH9 SWP2:SXD9 TGL2:TGZ9 TQH2:TQV9 UAD2:UAR9 UJZ2:UKN9 UTV2:UUJ9 VDR2:VEF9 VNN2:VOB9 VXJ2:VXX9" xr:uid="{610DDBB8-CBFC-40EB-B430-B67C890308BC}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT65488:FW65491 PP65488:PS65491 ZL65488:ZO65491 AJH65488:AJK65491 ATD65488:ATG65491 BCZ65488:BDC65491 BMV65488:BMY65491 BWR65488:BWU65491 CGN65488:CGQ65491 CQJ65488:CQM65491 DAF65488:DAI65491 DKB65488:DKE65491 DTX65488:DUA65491 EDT65488:EDW65491 ENP65488:ENS65491 EXL65488:EXO65491 FHH65488:FHK65491 FRD65488:FRG65491 GAZ65488:GBC65491 GKV65488:GKY65491 GUR65488:GUU65491 HEN65488:HEQ65491 HOJ65488:HOM65491 HYF65488:HYI65491 IIB65488:IIE65491 IRX65488:ISA65491 JBT65488:JBW65491 JLP65488:JLS65491 JVL65488:JVO65491 KFH65488:KFK65491 KPD65488:KPG65491 KYZ65488:KZC65491 LIV65488:LIY65491 LSR65488:LSU65491 MCN65488:MCQ65491 MMJ65488:MMM65491 MWF65488:MWI65491 NGB65488:NGE65491 NPX65488:NQA65491 NZT65488:NZW65491 OJP65488:OJS65491 OTL65488:OTO65491 PDH65488:PDK65491 PND65488:PNG65491 PWZ65488:PXC65491 QGV65488:QGY65491 QQR65488:QQU65491 RAN65488:RAQ65491 RKJ65488:RKM65491 RUF65488:RUI65491 SEB65488:SEE65491 SNX65488:SOA65491 SXT65488:SXW65491 THP65488:THS65491 TRL65488:TRO65491 UBH65488:UBK65491 ULD65488:ULG65491 UUZ65488:UVC65491 VEV65488:VEY65491 VOR65488:VOU65491 VYN65488:VYQ65491 WIJ65488:WIM65491 WSF65488:WSI65491 FT131024:FW131027 PP131024:PS131027 ZL131024:ZO131027 AJH131024:AJK131027 ATD131024:ATG131027 BCZ131024:BDC131027 BMV131024:BMY131027 BWR131024:BWU131027 CGN131024:CGQ131027 CQJ131024:CQM131027 DAF131024:DAI131027 DKB131024:DKE131027 DTX131024:DUA131027 EDT131024:EDW131027 ENP131024:ENS131027 EXL131024:EXO131027 FHH131024:FHK131027 FRD131024:FRG131027 GAZ131024:GBC131027 GKV131024:GKY131027 GUR131024:GUU131027 HEN131024:HEQ131027 HOJ131024:HOM131027 HYF131024:HYI131027 IIB131024:IIE131027 IRX131024:ISA131027 JBT131024:JBW131027 JLP131024:JLS131027 JVL131024:JVO131027 KFH131024:KFK131027 KPD131024:KPG131027 KYZ131024:KZC131027 LIV131024:LIY131027 LSR131024:LSU131027 MCN131024:MCQ131027 MMJ131024:MMM131027 MWF131024:MWI131027 NGB131024:NGE131027 NPX131024:NQA131027 NZT131024:NZW131027 OJP131024:OJS131027 OTL131024:OTO131027 PDH131024:PDK131027 PND131024:PNG131027 PWZ131024:PXC131027 QGV131024:QGY131027 QQR131024:QQU131027 RAN131024:RAQ131027 RKJ131024:RKM131027 RUF131024:RUI131027 SEB131024:SEE131027 SNX131024:SOA131027 SXT131024:SXW131027 THP131024:THS131027 TRL131024:TRO131027 UBH131024:UBK131027 ULD131024:ULG131027 UUZ131024:UVC131027 VEV131024:VEY131027 VOR131024:VOU131027 VYN131024:VYQ131027 WIJ131024:WIM131027 WSF131024:WSI131027 FT196560:FW196563 PP196560:PS196563 ZL196560:ZO196563 AJH196560:AJK196563 ATD196560:ATG196563 BCZ196560:BDC196563 BMV196560:BMY196563 BWR196560:BWU196563 CGN196560:CGQ196563 CQJ196560:CQM196563 DAF196560:DAI196563 DKB196560:DKE196563 DTX196560:DUA196563 EDT196560:EDW196563 ENP196560:ENS196563 EXL196560:EXO196563 FHH196560:FHK196563 FRD196560:FRG196563 GAZ196560:GBC196563 GKV196560:GKY196563 GUR196560:GUU196563 HEN196560:HEQ196563 HOJ196560:HOM196563 HYF196560:HYI196563 IIB196560:IIE196563 IRX196560:ISA196563 JBT196560:JBW196563 JLP196560:JLS196563 JVL196560:JVO196563 KFH196560:KFK196563 KPD196560:KPG196563 KYZ196560:KZC196563 LIV196560:LIY196563 LSR196560:LSU196563 MCN196560:MCQ196563 MMJ196560:MMM196563 MWF196560:MWI196563 NGB196560:NGE196563 NPX196560:NQA196563 NZT196560:NZW196563 OJP196560:OJS196563 OTL196560:OTO196563 PDH196560:PDK196563 PND196560:PNG196563 PWZ196560:PXC196563 QGV196560:QGY196563 QQR196560:QQU196563 RAN196560:RAQ196563 RKJ196560:RKM196563 RUF196560:RUI196563 SEB196560:SEE196563 SNX196560:SOA196563 SXT196560:SXW196563 THP196560:THS196563 TRL196560:TRO196563 UBH196560:UBK196563 ULD196560:ULG196563 UUZ196560:UVC196563 VEV196560:VEY196563 VOR196560:VOU196563 VYN196560:VYQ196563 WIJ196560:WIM196563 WSF196560:WSI196563 FT262096:FW262099 PP262096:PS262099 ZL262096:ZO262099 AJH262096:AJK262099 ATD262096:ATG262099 BCZ262096:BDC262099 BMV262096:BMY262099 BWR262096:BWU262099 CGN262096:CGQ262099 CQJ262096:CQM262099 DAF262096:DAI262099 DKB262096:DKE262099 DTX262096:DUA262099 EDT262096:EDW262099 ENP262096:ENS262099 EXL262096:EXO262099 FHH262096:FHK262099 FRD262096:FRG262099 GAZ262096:GBC262099 GKV262096:GKY262099 GUR262096:GUU262099 HEN262096:HEQ262099 HOJ262096:HOM262099 HYF262096:HYI262099 IIB262096:IIE262099 IRX262096:ISA262099 JBT262096:JBW262099 JLP262096:JLS262099 JVL262096:JVO262099 KFH262096:KFK262099 KPD262096:KPG262099 KYZ262096:KZC262099 LIV262096:LIY262099 LSR262096:LSU262099 MCN262096:MCQ262099 MMJ262096:MMM262099 MWF262096:MWI262099 NGB262096:NGE262099 NPX262096:NQA262099 NZT262096:NZW262099 OJP262096:OJS262099 OTL262096:OTO262099 PDH262096:PDK262099 PND262096:PNG262099 PWZ262096:PXC262099 QGV262096:QGY262099 QQR262096:QQU262099 RAN262096:RAQ262099 RKJ262096:RKM262099 RUF262096:RUI262099 SEB262096:SEE262099 SNX262096:SOA262099 SXT262096:SXW262099 THP262096:THS262099 TRL262096:TRO262099 UBH262096:UBK262099 ULD262096:ULG262099 UUZ262096:UVC262099 VEV262096:VEY262099 VOR262096:VOU262099 VYN262096:VYQ262099 WIJ262096:WIM262099 WSF262096:WSI262099 FT327632:FW327635 PP327632:PS327635 ZL327632:ZO327635 AJH327632:AJK327635 ATD327632:ATG327635 BCZ327632:BDC327635 BMV327632:BMY327635 BWR327632:BWU327635 CGN327632:CGQ327635 CQJ327632:CQM327635 DAF327632:DAI327635 DKB327632:DKE327635 DTX327632:DUA327635 EDT327632:EDW327635 ENP327632:ENS327635 EXL327632:EXO327635 FHH327632:FHK327635 FRD327632:FRG327635 GAZ327632:GBC327635 GKV327632:GKY327635 GUR327632:GUU327635 HEN327632:HEQ327635 HOJ327632:HOM327635 HYF327632:HYI327635 IIB327632:IIE327635 IRX327632:ISA327635 JBT327632:JBW327635 JLP327632:JLS327635 JVL327632:JVO327635 KFH327632:KFK327635 KPD327632:KPG327635 KYZ327632:KZC327635 LIV327632:LIY327635 LSR327632:LSU327635 MCN327632:MCQ327635 MMJ327632:MMM327635 MWF327632:MWI327635 NGB327632:NGE327635 NPX327632:NQA327635 NZT327632:NZW327635 OJP327632:OJS327635 OTL327632:OTO327635 PDH327632:PDK327635 PND327632:PNG327635 PWZ327632:PXC327635 QGV327632:QGY327635 QQR327632:QQU327635 RAN327632:RAQ327635 RKJ327632:RKM327635 RUF327632:RUI327635 SEB327632:SEE327635 SNX327632:SOA327635 SXT327632:SXW327635 THP327632:THS327635 TRL327632:TRO327635 UBH327632:UBK327635 ULD327632:ULG327635 UUZ327632:UVC327635 VEV327632:VEY327635 VOR327632:VOU327635 VYN327632:VYQ327635 WIJ327632:WIM327635 WSF327632:WSI327635 FT393168:FW393171 PP393168:PS393171 ZL393168:ZO393171 AJH393168:AJK393171 ATD393168:ATG393171 BCZ393168:BDC393171 BMV393168:BMY393171 BWR393168:BWU393171 CGN393168:CGQ393171 CQJ393168:CQM393171 DAF393168:DAI393171 DKB393168:DKE393171 DTX393168:DUA393171 EDT393168:EDW393171 ENP393168:ENS393171 EXL393168:EXO393171 FHH393168:FHK393171 FRD393168:FRG393171 GAZ393168:GBC393171 GKV393168:GKY393171 GUR393168:GUU393171 HEN393168:HEQ393171 HOJ393168:HOM393171 HYF393168:HYI393171 IIB393168:IIE393171 IRX393168:ISA393171 JBT393168:JBW393171 JLP393168:JLS393171 JVL393168:JVO393171 KFH393168:KFK393171 KPD393168:KPG393171 KYZ393168:KZC393171 LIV393168:LIY393171 LSR393168:LSU393171 MCN393168:MCQ393171 MMJ393168:MMM393171 MWF393168:MWI393171 NGB393168:NGE393171 NPX393168:NQA393171 NZT393168:NZW393171 OJP393168:OJS393171 OTL393168:OTO393171 PDH393168:PDK393171 PND393168:PNG393171 PWZ393168:PXC393171 QGV393168:QGY393171 QQR393168:QQU393171 RAN393168:RAQ393171 RKJ393168:RKM393171 RUF393168:RUI393171 SEB393168:SEE393171 SNX393168:SOA393171 SXT393168:SXW393171 THP393168:THS393171 TRL393168:TRO393171 UBH393168:UBK393171 ULD393168:ULG393171 UUZ393168:UVC393171 VEV393168:VEY393171 VOR393168:VOU393171 VYN393168:VYQ393171 WIJ393168:WIM393171 WSF393168:WSI393171 FT458704:FW458707 PP458704:PS458707 ZL458704:ZO458707 AJH458704:AJK458707 ATD458704:ATG458707 BCZ458704:BDC458707 BMV458704:BMY458707 BWR458704:BWU458707 CGN458704:CGQ458707 CQJ458704:CQM458707 DAF458704:DAI458707 DKB458704:DKE458707 DTX458704:DUA458707 EDT458704:EDW458707 ENP458704:ENS458707 EXL458704:EXO458707 FHH458704:FHK458707 FRD458704:FRG458707 GAZ458704:GBC458707 GKV458704:GKY458707 GUR458704:GUU458707 HEN458704:HEQ458707 HOJ458704:HOM458707 HYF458704:HYI458707 IIB458704:IIE458707 IRX458704:ISA458707 JBT458704:JBW458707 JLP458704:JLS458707 JVL458704:JVO458707 KFH458704:KFK458707 KPD458704:KPG458707 KYZ458704:KZC458707 LIV458704:LIY458707 LSR458704:LSU458707 MCN458704:MCQ458707 MMJ458704:MMM458707 MWF458704:MWI458707 NGB458704:NGE458707 NPX458704:NQA458707 NZT458704:NZW458707 OJP458704:OJS458707 OTL458704:OTO458707 PDH458704:PDK458707 PND458704:PNG458707 PWZ458704:PXC458707 QGV458704:QGY458707 QQR458704:QQU458707 RAN458704:RAQ458707 RKJ458704:RKM458707 RUF458704:RUI458707 SEB458704:SEE458707 SNX458704:SOA458707 SXT458704:SXW458707 THP458704:THS458707 TRL458704:TRO458707 UBH458704:UBK458707 ULD458704:ULG458707 UUZ458704:UVC458707 VEV458704:VEY458707 VOR458704:VOU458707 VYN458704:VYQ458707 WIJ458704:WIM458707 WSF458704:WSI458707 FT524240:FW524243 PP524240:PS524243 ZL524240:ZO524243 AJH524240:AJK524243 ATD524240:ATG524243 BCZ524240:BDC524243 BMV524240:BMY524243 BWR524240:BWU524243 CGN524240:CGQ524243 CQJ524240:CQM524243 DAF524240:DAI524243 DKB524240:DKE524243 DTX524240:DUA524243 EDT524240:EDW524243 ENP524240:ENS524243 EXL524240:EXO524243 FHH524240:FHK524243 FRD524240:FRG524243 GAZ524240:GBC524243 GKV524240:GKY524243 GUR524240:GUU524243 HEN524240:HEQ524243 HOJ524240:HOM524243 HYF524240:HYI524243 IIB524240:IIE524243 IRX524240:ISA524243 JBT524240:JBW524243 JLP524240:JLS524243 JVL524240:JVO524243 KFH524240:KFK524243 KPD524240:KPG524243 KYZ524240:KZC524243 LIV524240:LIY524243 LSR524240:LSU524243 MCN524240:MCQ524243 MMJ524240:MMM524243 MWF524240:MWI524243 NGB524240:NGE524243 NPX524240:NQA524243 NZT524240:NZW524243 OJP524240:OJS524243 OTL524240:OTO524243 PDH524240:PDK524243 PND524240:PNG524243 PWZ524240:PXC524243 QGV524240:QGY524243 QQR524240:QQU524243 RAN524240:RAQ524243 RKJ524240:RKM524243 RUF524240:RUI524243 SEB524240:SEE524243 SNX524240:SOA524243 SXT524240:SXW524243 THP524240:THS524243 TRL524240:TRO524243 UBH524240:UBK524243 ULD524240:ULG524243 UUZ524240:UVC524243 VEV524240:VEY524243 VOR524240:VOU524243 VYN524240:VYQ524243 WIJ524240:WIM524243 WSF524240:WSI524243 FT589776:FW589779 PP589776:PS589779 ZL589776:ZO589779 AJH589776:AJK589779 ATD589776:ATG589779 BCZ589776:BDC589779 BMV589776:BMY589779 BWR589776:BWU589779 CGN589776:CGQ589779 CQJ589776:CQM589779 DAF589776:DAI589779 DKB589776:DKE589779 DTX589776:DUA589779 EDT589776:EDW589779 ENP589776:ENS589779 EXL589776:EXO589779 FHH589776:FHK589779 FRD589776:FRG589779 GAZ589776:GBC589779 GKV589776:GKY589779 GUR589776:GUU589779 HEN589776:HEQ589779 HOJ589776:HOM589779 HYF589776:HYI589779 IIB589776:IIE589779 IRX589776:ISA589779 JBT589776:JBW589779 JLP589776:JLS589779 JVL589776:JVO589779 KFH589776:KFK589779 KPD589776:KPG589779 KYZ589776:KZC589779 LIV589776:LIY589779 LSR589776:LSU589779 MCN589776:MCQ589779 MMJ589776:MMM589779 MWF589776:MWI589779 NGB589776:NGE589779 NPX589776:NQA589779 NZT589776:NZW589779 OJP589776:OJS589779 OTL589776:OTO589779 PDH589776:PDK589779 PND589776:PNG589779 PWZ589776:PXC589779 QGV589776:QGY589779 QQR589776:QQU589779 RAN589776:RAQ589779 RKJ589776:RKM589779 RUF589776:RUI589779 SEB589776:SEE589779 SNX589776:SOA589779 SXT589776:SXW589779 THP589776:THS589779 TRL589776:TRO589779 UBH589776:UBK589779 ULD589776:ULG589779 UUZ589776:UVC589779 VEV589776:VEY589779 VOR589776:VOU589779 VYN589776:VYQ589779 WIJ589776:WIM589779 WSF589776:WSI589779 FT655312:FW655315 PP655312:PS655315 ZL655312:ZO655315 AJH655312:AJK655315 ATD655312:ATG655315 BCZ655312:BDC655315 BMV655312:BMY655315 BWR655312:BWU655315 CGN655312:CGQ655315 CQJ655312:CQM655315 DAF655312:DAI655315 DKB655312:DKE655315 DTX655312:DUA655315 EDT655312:EDW655315 ENP655312:ENS655315 EXL655312:EXO655315 FHH655312:FHK655315 FRD655312:FRG655315 GAZ655312:GBC655315 GKV655312:GKY655315 GUR655312:GUU655315 HEN655312:HEQ655315 HOJ655312:HOM655315 HYF655312:HYI655315 IIB655312:IIE655315 IRX655312:ISA655315 JBT655312:JBW655315 JLP655312:JLS655315 JVL655312:JVO655315 KFH655312:KFK655315 KPD655312:KPG655315 KYZ655312:KZC655315 LIV655312:LIY655315 LSR655312:LSU655315 MCN655312:MCQ655315 MMJ655312:MMM655315 MWF655312:MWI655315 NGB655312:NGE655315 NPX655312:NQA655315 NZT655312:NZW655315 OJP655312:OJS655315 OTL655312:OTO655315 PDH655312:PDK655315 PND655312:PNG655315 PWZ655312:PXC655315 QGV655312:QGY655315 QQR655312:QQU655315 RAN655312:RAQ655315 RKJ655312:RKM655315 RUF655312:RUI655315 SEB655312:SEE655315 SNX655312:SOA655315 SXT655312:SXW655315 THP655312:THS655315 TRL655312:TRO655315 UBH655312:UBK655315 ULD655312:ULG655315 UUZ655312:UVC655315 VEV655312:VEY655315 VOR655312:VOU655315 VYN655312:VYQ655315 WIJ655312:WIM655315 WSF655312:WSI655315 FT720848:FW720851 PP720848:PS720851 ZL720848:ZO720851 AJH720848:AJK720851 ATD720848:ATG720851 BCZ720848:BDC720851 BMV720848:BMY720851 BWR720848:BWU720851 CGN720848:CGQ720851 CQJ720848:CQM720851 DAF720848:DAI720851 DKB720848:DKE720851 DTX720848:DUA720851 EDT720848:EDW720851 ENP720848:ENS720851 EXL720848:EXO720851 FHH720848:FHK720851 FRD720848:FRG720851 GAZ720848:GBC720851 GKV720848:GKY720851 GUR720848:GUU720851 HEN720848:HEQ720851 HOJ720848:HOM720851 HYF720848:HYI720851 IIB720848:IIE720851 IRX720848:ISA720851 JBT720848:JBW720851 JLP720848:JLS720851 JVL720848:JVO720851 KFH720848:KFK720851 KPD720848:KPG720851 KYZ720848:KZC720851 LIV720848:LIY720851 LSR720848:LSU720851 MCN720848:MCQ720851 MMJ720848:MMM720851 MWF720848:MWI720851 NGB720848:NGE720851 NPX720848:NQA720851 NZT720848:NZW720851 OJP720848:OJS720851 OTL720848:OTO720851 PDH720848:PDK720851 PND720848:PNG720851 PWZ720848:PXC720851 QGV720848:QGY720851 QQR720848:QQU720851 RAN720848:RAQ720851 RKJ720848:RKM720851 RUF720848:RUI720851 SEB720848:SEE720851 SNX720848:SOA720851 SXT720848:SXW720851 THP720848:THS720851 TRL720848:TRO720851 UBH720848:UBK720851 ULD720848:ULG720851 UUZ720848:UVC720851 VEV720848:VEY720851 VOR720848:VOU720851 VYN720848:VYQ720851 WIJ720848:WIM720851 WSF720848:WSI720851 FT786384:FW786387 PP786384:PS786387 ZL786384:ZO786387 AJH786384:AJK786387 ATD786384:ATG786387 BCZ786384:BDC786387 BMV786384:BMY786387 BWR786384:BWU786387 CGN786384:CGQ786387 CQJ786384:CQM786387 DAF786384:DAI786387 DKB786384:DKE786387 DTX786384:DUA786387 EDT786384:EDW786387 ENP786384:ENS786387 EXL786384:EXO786387 FHH786384:FHK786387 FRD786384:FRG786387 GAZ786384:GBC786387 GKV786384:GKY786387 GUR786384:GUU786387 HEN786384:HEQ786387 HOJ786384:HOM786387 HYF786384:HYI786387 IIB786384:IIE786387 IRX786384:ISA786387 JBT786384:JBW786387 JLP786384:JLS786387 JVL786384:JVO786387 KFH786384:KFK786387 KPD786384:KPG786387 KYZ786384:KZC786387 LIV786384:LIY786387 LSR786384:LSU786387 MCN786384:MCQ786387 MMJ786384:MMM786387 MWF786384:MWI786387 NGB786384:NGE786387 NPX786384:NQA786387 NZT786384:NZW786387 OJP786384:OJS786387 OTL786384:OTO786387 PDH786384:PDK786387 PND786384:PNG786387 PWZ786384:PXC786387 QGV786384:QGY786387 QQR786384:QQU786387 RAN786384:RAQ786387 RKJ786384:RKM786387 RUF786384:RUI786387 SEB786384:SEE786387 SNX786384:SOA786387 SXT786384:SXW786387 THP786384:THS786387 TRL786384:TRO786387 UBH786384:UBK786387 ULD786384:ULG786387 UUZ786384:UVC786387 VEV786384:VEY786387 VOR786384:VOU786387 VYN786384:VYQ786387 WIJ786384:WIM786387 WSF786384:WSI786387 FT851920:FW851923 PP851920:PS851923 ZL851920:ZO851923 AJH851920:AJK851923 ATD851920:ATG851923 BCZ851920:BDC851923 BMV851920:BMY851923 BWR851920:BWU851923 CGN851920:CGQ851923 CQJ851920:CQM851923 DAF851920:DAI851923 DKB851920:DKE851923 DTX851920:DUA851923 EDT851920:EDW851923 ENP851920:ENS851923 EXL851920:EXO851923 FHH851920:FHK851923 FRD851920:FRG851923 GAZ851920:GBC851923 GKV851920:GKY851923 GUR851920:GUU851923 HEN851920:HEQ851923 HOJ851920:HOM851923 HYF851920:HYI851923 IIB851920:IIE851923 IRX851920:ISA851923 JBT851920:JBW851923 JLP851920:JLS851923 JVL851920:JVO851923 KFH851920:KFK851923 KPD851920:KPG851923 KYZ851920:KZC851923 LIV851920:LIY851923 LSR851920:LSU851923 MCN851920:MCQ851923 MMJ851920:MMM851923 MWF851920:MWI851923 NGB851920:NGE851923 NPX851920:NQA851923 NZT851920:NZW851923 OJP851920:OJS851923 OTL851920:OTO851923 PDH851920:PDK851923 PND851920:PNG851923 PWZ851920:PXC851923 QGV851920:QGY851923 QQR851920:QQU851923 RAN851920:RAQ851923 RKJ851920:RKM851923 RUF851920:RUI851923 SEB851920:SEE851923 SNX851920:SOA851923 SXT851920:SXW851923 THP851920:THS851923 TRL851920:TRO851923 UBH851920:UBK851923 ULD851920:ULG851923 UUZ851920:UVC851923 VEV851920:VEY851923 VOR851920:VOU851923 VYN851920:VYQ851923 WIJ851920:WIM851923 WSF851920:WSI851923 FT917456:FW917459 PP917456:PS917459 ZL917456:ZO917459 AJH917456:AJK917459 ATD917456:ATG917459 BCZ917456:BDC917459 BMV917456:BMY917459 BWR917456:BWU917459 CGN917456:CGQ917459 CQJ917456:CQM917459 DAF917456:DAI917459 DKB917456:DKE917459 DTX917456:DUA917459 EDT917456:EDW917459 ENP917456:ENS917459 EXL917456:EXO917459 FHH917456:FHK917459 FRD917456:FRG917459 GAZ917456:GBC917459 GKV917456:GKY917459 GUR917456:GUU917459 HEN917456:HEQ917459 HOJ917456:HOM917459 HYF917456:HYI917459 IIB917456:IIE917459 IRX917456:ISA917459 JBT917456:JBW917459 JLP917456:JLS917459 JVL917456:JVO917459 KFH917456:KFK917459 KPD917456:KPG917459 KYZ917456:KZC917459 LIV917456:LIY917459 LSR917456:LSU917459 MCN917456:MCQ917459 MMJ917456:MMM917459 MWF917456:MWI917459 NGB917456:NGE917459 NPX917456:NQA917459 NZT917456:NZW917459 OJP917456:OJS917459 OTL917456:OTO917459 PDH917456:PDK917459 PND917456:PNG917459 PWZ917456:PXC917459 QGV917456:QGY917459 QQR917456:QQU917459 RAN917456:RAQ917459 RKJ917456:RKM917459 RUF917456:RUI917459 SEB917456:SEE917459 SNX917456:SOA917459 SXT917456:SXW917459 THP917456:THS917459 TRL917456:TRO917459 UBH917456:UBK917459 ULD917456:ULG917459 UUZ917456:UVC917459 VEV917456:VEY917459 VOR917456:VOU917459 VYN917456:VYQ917459 WIJ917456:WIM917459 WSF917456:WSI917459 FT982992:FW982995 PP982992:PS982995 ZL982992:ZO982995 AJH982992:AJK982995 ATD982992:ATG982995 BCZ982992:BDC982995 BMV982992:BMY982995 BWR982992:BWU982995 CGN982992:CGQ982995 CQJ982992:CQM982995 DAF982992:DAI982995 DKB982992:DKE982995 DTX982992:DUA982995 EDT982992:EDW982995 ENP982992:ENS982995 EXL982992:EXO982995 FHH982992:FHK982995 FRD982992:FRG982995 GAZ982992:GBC982995 GKV982992:GKY982995 GUR982992:GUU982995 HEN982992:HEQ982995 HOJ982992:HOM982995 HYF982992:HYI982995 IIB982992:IIE982995 IRX982992:ISA982995 JBT982992:JBW982995 JLP982992:JLS982995 JVL982992:JVO982995 KFH982992:KFK982995 KPD982992:KPG982995 KYZ982992:KZC982995 LIV982992:LIY982995 LSR982992:LSU982995 MCN982992:MCQ982995 MMJ982992:MMM982995 MWF982992:MWI982995 NGB982992:NGE982995 NPX982992:NQA982995 NZT982992:NZW982995 OJP982992:OJS982995 OTL982992:OTO982995 PDH982992:PDK982995 PND982992:PNG982995 PWZ982992:PXC982995 QGV982992:QGY982995 QQR982992:QQU982995 RAN982992:RAQ982995 RKJ982992:RKM982995 RUF982992:RUI982995 SEB982992:SEE982995 SNX982992:SOA982995 SXT982992:SXW982995 THP982992:THS982995 TRL982992:TRO982995 UBH982992:UBK982995 ULD982992:ULG982995 UUZ982992:UVC982995 VEV982992:VEY982995 VOR982992:VOU982995 VYN982992:VYQ982995 WIJ982992:WIM982995 WSF982992:WSI982995 FO65482:FR65482 PK65482:PN65482 ZG65482:ZJ65482 AJC65482:AJF65482 ASY65482:ATB65482 BCU65482:BCX65482 BMQ65482:BMT65482 BWM65482:BWP65482 CGI65482:CGL65482 CQE65482:CQH65482 DAA65482:DAD65482 DJW65482:DJZ65482 DTS65482:DTV65482 EDO65482:EDR65482 ENK65482:ENN65482 EXG65482:EXJ65482 FHC65482:FHF65482 FQY65482:FRB65482 GAU65482:GAX65482 GKQ65482:GKT65482 GUM65482:GUP65482 HEI65482:HEL65482 HOE65482:HOH65482 HYA65482:HYD65482 IHW65482:IHZ65482 IRS65482:IRV65482 JBO65482:JBR65482 JLK65482:JLN65482 JVG65482:JVJ65482 KFC65482:KFF65482 KOY65482:KPB65482 KYU65482:KYX65482 LIQ65482:LIT65482 LSM65482:LSP65482 MCI65482:MCL65482 MME65482:MMH65482 MWA65482:MWD65482 NFW65482:NFZ65482 NPS65482:NPV65482 NZO65482:NZR65482 OJK65482:OJN65482 OTG65482:OTJ65482 PDC65482:PDF65482 PMY65482:PNB65482 PWU65482:PWX65482 QGQ65482:QGT65482 QQM65482:QQP65482 RAI65482:RAL65482 RKE65482:RKH65482 RUA65482:RUD65482 SDW65482:SDZ65482 SNS65482:SNV65482 SXO65482:SXR65482 THK65482:THN65482 TRG65482:TRJ65482 UBC65482:UBF65482 UKY65482:ULB65482 UUU65482:UUX65482 VEQ65482:VET65482 VOM65482:VOP65482 VYI65482:VYL65482 WIE65482:WIH65482 WSA65482:WSD65482 FO131018:FR131018 PK131018:PN131018 ZG131018:ZJ131018 AJC131018:AJF131018 ASY131018:ATB131018 BCU131018:BCX131018 BMQ131018:BMT131018 BWM131018:BWP131018 CGI131018:CGL131018 CQE131018:CQH131018 DAA131018:DAD131018 DJW131018:DJZ131018 DTS131018:DTV131018 EDO131018:EDR131018 ENK131018:ENN131018 EXG131018:EXJ131018 FHC131018:FHF131018 FQY131018:FRB131018 GAU131018:GAX131018 GKQ131018:GKT131018 GUM131018:GUP131018 HEI131018:HEL131018 HOE131018:HOH131018 HYA131018:HYD131018 IHW131018:IHZ131018 IRS131018:IRV131018 JBO131018:JBR131018 JLK131018:JLN131018 JVG131018:JVJ131018 KFC131018:KFF131018 KOY131018:KPB131018 KYU131018:KYX131018 LIQ131018:LIT131018 LSM131018:LSP131018 MCI131018:MCL131018 MME131018:MMH131018 MWA131018:MWD131018 NFW131018:NFZ131018 NPS131018:NPV131018 NZO131018:NZR131018 OJK131018:OJN131018 OTG131018:OTJ131018 PDC131018:PDF131018 PMY131018:PNB131018 PWU131018:PWX131018 QGQ131018:QGT131018 QQM131018:QQP131018 RAI131018:RAL131018 RKE131018:RKH131018 RUA131018:RUD131018 SDW131018:SDZ131018 SNS131018:SNV131018 SXO131018:SXR131018 THK131018:THN131018 TRG131018:TRJ131018 UBC131018:UBF131018 UKY131018:ULB131018 UUU131018:UUX131018 VEQ131018:VET131018 VOM131018:VOP131018 VYI131018:VYL131018 WIE131018:WIH131018 WSA131018:WSD131018 FO196554:FR196554 PK196554:PN196554 ZG196554:ZJ196554 AJC196554:AJF196554 ASY196554:ATB196554 BCU196554:BCX196554 BMQ196554:BMT196554 BWM196554:BWP196554 CGI196554:CGL196554 CQE196554:CQH196554 DAA196554:DAD196554 DJW196554:DJZ196554 DTS196554:DTV196554 EDO196554:EDR196554 ENK196554:ENN196554 EXG196554:EXJ196554 FHC196554:FHF196554 FQY196554:FRB196554 GAU196554:GAX196554 GKQ196554:GKT196554 GUM196554:GUP196554 HEI196554:HEL196554 HOE196554:HOH196554 HYA196554:HYD196554 IHW196554:IHZ196554 IRS196554:IRV196554 JBO196554:JBR196554 JLK196554:JLN196554 JVG196554:JVJ196554 KFC196554:KFF196554 KOY196554:KPB196554 KYU196554:KYX196554 LIQ196554:LIT196554 LSM196554:LSP196554 MCI196554:MCL196554 MME196554:MMH196554 MWA196554:MWD196554 NFW196554:NFZ196554 NPS196554:NPV196554 NZO196554:NZR196554 OJK196554:OJN196554 OTG196554:OTJ196554 PDC196554:PDF196554 PMY196554:PNB196554 PWU196554:PWX196554 QGQ196554:QGT196554 QQM196554:QQP196554 RAI196554:RAL196554 RKE196554:RKH196554 RUA196554:RUD196554 SDW196554:SDZ196554 SNS196554:SNV196554 SXO196554:SXR196554 THK196554:THN196554 TRG196554:TRJ196554 UBC196554:UBF196554 UKY196554:ULB196554 UUU196554:UUX196554 VEQ196554:VET196554 VOM196554:VOP196554 VYI196554:VYL196554 WIE196554:WIH196554 WSA196554:WSD196554 FO262090:FR262090 PK262090:PN262090 ZG262090:ZJ262090 AJC262090:AJF262090 ASY262090:ATB262090 BCU262090:BCX262090 BMQ262090:BMT262090 BWM262090:BWP262090 CGI262090:CGL262090 CQE262090:CQH262090 DAA262090:DAD262090 DJW262090:DJZ262090 DTS262090:DTV262090 EDO262090:EDR262090 ENK262090:ENN262090 EXG262090:EXJ262090 FHC262090:FHF262090 FQY262090:FRB262090 GAU262090:GAX262090 GKQ262090:GKT262090 GUM262090:GUP262090 HEI262090:HEL262090 HOE262090:HOH262090 HYA262090:HYD262090 IHW262090:IHZ262090 IRS262090:IRV262090 JBO262090:JBR262090 JLK262090:JLN262090 JVG262090:JVJ262090 KFC262090:KFF262090 KOY262090:KPB262090 KYU262090:KYX262090 LIQ262090:LIT262090 LSM262090:LSP262090 MCI262090:MCL262090 MME262090:MMH262090 MWA262090:MWD262090 NFW262090:NFZ262090 NPS262090:NPV262090 NZO262090:NZR262090 OJK262090:OJN262090 OTG262090:OTJ262090 PDC262090:PDF262090 PMY262090:PNB262090 PWU262090:PWX262090 QGQ262090:QGT262090 QQM262090:QQP262090 RAI262090:RAL262090 RKE262090:RKH262090 RUA262090:RUD262090 SDW262090:SDZ262090 SNS262090:SNV262090 SXO262090:SXR262090 THK262090:THN262090 TRG262090:TRJ262090 UBC262090:UBF262090 UKY262090:ULB262090 UUU262090:UUX262090 VEQ262090:VET262090 VOM262090:VOP262090 VYI262090:VYL262090 WIE262090:WIH262090 WSA262090:WSD262090 FO327626:FR327626 PK327626:PN327626 ZG327626:ZJ327626 AJC327626:AJF327626 ASY327626:ATB327626 BCU327626:BCX327626 BMQ327626:BMT327626 BWM327626:BWP327626 CGI327626:CGL327626 CQE327626:CQH327626 DAA327626:DAD327626 DJW327626:DJZ327626 DTS327626:DTV327626 EDO327626:EDR327626 ENK327626:ENN327626 EXG327626:EXJ327626 FHC327626:FHF327626 FQY327626:FRB327626 GAU327626:GAX327626 GKQ327626:GKT327626 GUM327626:GUP327626 HEI327626:HEL327626 HOE327626:HOH327626 HYA327626:HYD327626 IHW327626:IHZ327626 IRS327626:IRV327626 JBO327626:JBR327626 JLK327626:JLN327626 JVG327626:JVJ327626 KFC327626:KFF327626 KOY327626:KPB327626 KYU327626:KYX327626 LIQ327626:LIT327626 LSM327626:LSP327626 MCI327626:MCL327626 MME327626:MMH327626 MWA327626:MWD327626 NFW327626:NFZ327626 NPS327626:NPV327626 NZO327626:NZR327626 OJK327626:OJN327626 OTG327626:OTJ327626 PDC327626:PDF327626 PMY327626:PNB327626 PWU327626:PWX327626 QGQ327626:QGT327626 QQM327626:QQP327626 RAI327626:RAL327626 RKE327626:RKH327626 RUA327626:RUD327626 SDW327626:SDZ327626 SNS327626:SNV327626 SXO327626:SXR327626 THK327626:THN327626 TRG327626:TRJ327626 UBC327626:UBF327626 UKY327626:ULB327626 UUU327626:UUX327626 VEQ327626:VET327626 VOM327626:VOP327626 VYI327626:VYL327626 WIE327626:WIH327626 WSA327626:WSD327626 FO393162:FR393162 PK393162:PN393162 ZG393162:ZJ393162 AJC393162:AJF393162 ASY393162:ATB393162 BCU393162:BCX393162 BMQ393162:BMT393162 BWM393162:BWP393162 CGI393162:CGL393162 CQE393162:CQH393162 DAA393162:DAD393162 DJW393162:DJZ393162 DTS393162:DTV393162 EDO393162:EDR393162 ENK393162:ENN393162 EXG393162:EXJ393162 FHC393162:FHF393162 FQY393162:FRB393162 GAU393162:GAX393162 GKQ393162:GKT393162 GUM393162:GUP393162 HEI393162:HEL393162 HOE393162:HOH393162 HYA393162:HYD393162 IHW393162:IHZ393162 IRS393162:IRV393162 JBO393162:JBR393162 JLK393162:JLN393162 JVG393162:JVJ393162 KFC393162:KFF393162 KOY393162:KPB393162 KYU393162:KYX393162 LIQ393162:LIT393162 LSM393162:LSP393162 MCI393162:MCL393162 MME393162:MMH393162 MWA393162:MWD393162 NFW393162:NFZ393162 NPS393162:NPV393162 NZO393162:NZR393162 OJK393162:OJN393162 OTG393162:OTJ393162 PDC393162:PDF393162 PMY393162:PNB393162 PWU393162:PWX393162 QGQ393162:QGT393162 QQM393162:QQP393162 RAI393162:RAL393162 RKE393162:RKH393162 RUA393162:RUD393162 SDW393162:SDZ393162 SNS393162:SNV393162 SXO393162:SXR393162 THK393162:THN393162 TRG393162:TRJ393162 UBC393162:UBF393162 UKY393162:ULB393162 UUU393162:UUX393162 VEQ393162:VET393162 VOM393162:VOP393162 VYI393162:VYL393162 WIE393162:WIH393162 WSA393162:WSD393162 FO458698:FR458698 PK458698:PN458698 ZG458698:ZJ458698 AJC458698:AJF458698 ASY458698:ATB458698 BCU458698:BCX458698 BMQ458698:BMT458698 BWM458698:BWP458698 CGI458698:CGL458698 CQE458698:CQH458698 DAA458698:DAD458698 DJW458698:DJZ458698 DTS458698:DTV458698 EDO458698:EDR458698 ENK458698:ENN458698 EXG458698:EXJ458698 FHC458698:FHF458698 FQY458698:FRB458698 GAU458698:GAX458698 GKQ458698:GKT458698 GUM458698:GUP458698 HEI458698:HEL458698 HOE458698:HOH458698 HYA458698:HYD458698 IHW458698:IHZ458698 IRS458698:IRV458698 JBO458698:JBR458698 JLK458698:JLN458698 JVG458698:JVJ458698 KFC458698:KFF458698 KOY458698:KPB458698 KYU458698:KYX458698 LIQ458698:LIT458698 LSM458698:LSP458698 MCI458698:MCL458698 MME458698:MMH458698 MWA458698:MWD458698 NFW458698:NFZ458698 NPS458698:NPV458698 NZO458698:NZR458698 OJK458698:OJN458698 OTG458698:OTJ458698 PDC458698:PDF458698 PMY458698:PNB458698 PWU458698:PWX458698 QGQ458698:QGT458698 QQM458698:QQP458698 RAI458698:RAL458698 RKE458698:RKH458698 RUA458698:RUD458698 SDW458698:SDZ458698 SNS458698:SNV458698 SXO458698:SXR458698 THK458698:THN458698 TRG458698:TRJ458698 UBC458698:UBF458698 UKY458698:ULB458698 UUU458698:UUX458698 VEQ458698:VET458698 VOM458698:VOP458698 VYI458698:VYL458698 WIE458698:WIH458698 WSA458698:WSD458698 FO524234:FR524234 PK524234:PN524234 ZG524234:ZJ524234 AJC524234:AJF524234 ASY524234:ATB524234 BCU524234:BCX524234 BMQ524234:BMT524234 BWM524234:BWP524234 CGI524234:CGL524234 CQE524234:CQH524234 DAA524234:DAD524234 DJW524234:DJZ524234 DTS524234:DTV524234 EDO524234:EDR524234 ENK524234:ENN524234 EXG524234:EXJ524234 FHC524234:FHF524234 FQY524234:FRB524234 GAU524234:GAX524234 GKQ524234:GKT524234 GUM524234:GUP524234 HEI524234:HEL524234 HOE524234:HOH524234 HYA524234:HYD524234 IHW524234:IHZ524234 IRS524234:IRV524234 JBO524234:JBR524234 JLK524234:JLN524234 JVG524234:JVJ524234 KFC524234:KFF524234 KOY524234:KPB524234 KYU524234:KYX524234 LIQ524234:LIT524234 LSM524234:LSP524234 MCI524234:MCL524234 MME524234:MMH524234 MWA524234:MWD524234 NFW524234:NFZ524234 NPS524234:NPV524234 NZO524234:NZR524234 OJK524234:OJN524234 OTG524234:OTJ524234 PDC524234:PDF524234 PMY524234:PNB524234 PWU524234:PWX524234 QGQ524234:QGT524234 QQM524234:QQP524234 RAI524234:RAL524234 RKE524234:RKH524234 RUA524234:RUD524234 SDW524234:SDZ524234 SNS524234:SNV524234 SXO524234:SXR524234 THK524234:THN524234 TRG524234:TRJ524234 UBC524234:UBF524234 UKY524234:ULB524234 UUU524234:UUX524234 VEQ524234:VET524234 VOM524234:VOP524234 VYI524234:VYL524234 WIE524234:WIH524234 WSA524234:WSD524234 FO589770:FR589770 PK589770:PN589770 ZG589770:ZJ589770 AJC589770:AJF589770 ASY589770:ATB589770 BCU589770:BCX589770 BMQ589770:BMT589770 BWM589770:BWP589770 CGI589770:CGL589770 CQE589770:CQH589770 DAA589770:DAD589770 DJW589770:DJZ589770 DTS589770:DTV589770 EDO589770:EDR589770 ENK589770:ENN589770 EXG589770:EXJ589770 FHC589770:FHF589770 FQY589770:FRB589770 GAU589770:GAX589770 GKQ589770:GKT589770 GUM589770:GUP589770 HEI589770:HEL589770 HOE589770:HOH589770 HYA589770:HYD589770 IHW589770:IHZ589770 IRS589770:IRV589770 JBO589770:JBR589770 JLK589770:JLN589770 JVG589770:JVJ589770 KFC589770:KFF589770 KOY589770:KPB589770 KYU589770:KYX589770 LIQ589770:LIT589770 LSM589770:LSP589770 MCI589770:MCL589770 MME589770:MMH589770 MWA589770:MWD589770 NFW589770:NFZ589770 NPS589770:NPV589770 NZO589770:NZR589770 OJK589770:OJN589770 OTG589770:OTJ589770 PDC589770:PDF589770 PMY589770:PNB589770 PWU589770:PWX589770 QGQ589770:QGT589770 QQM589770:QQP589770 RAI589770:RAL589770 RKE589770:RKH589770 RUA589770:RUD589770 SDW589770:SDZ589770 SNS589770:SNV589770 SXO589770:SXR589770 THK589770:THN589770 TRG589770:TRJ589770 UBC589770:UBF589770 UKY589770:ULB589770 UUU589770:UUX589770 VEQ589770:VET589770 VOM589770:VOP589770 VYI589770:VYL589770 WIE589770:WIH589770 WSA589770:WSD589770 FO655306:FR655306 PK655306:PN655306 ZG655306:ZJ655306 AJC655306:AJF655306 ASY655306:ATB655306 BCU655306:BCX655306 BMQ655306:BMT655306 BWM655306:BWP655306 CGI655306:CGL655306 CQE655306:CQH655306 DAA655306:DAD655306 DJW655306:DJZ655306 DTS655306:DTV655306 EDO655306:EDR655306 ENK655306:ENN655306 EXG655306:EXJ655306 FHC655306:FHF655306 FQY655306:FRB655306 GAU655306:GAX655306 GKQ655306:GKT655306 GUM655306:GUP655306 HEI655306:HEL655306 HOE655306:HOH655306 HYA655306:HYD655306 IHW655306:IHZ655306 IRS655306:IRV655306 JBO655306:JBR655306 JLK655306:JLN655306 JVG655306:JVJ655306 KFC655306:KFF655306 KOY655306:KPB655306 KYU655306:KYX655306 LIQ655306:LIT655306 LSM655306:LSP655306 MCI655306:MCL655306 MME655306:MMH655306 MWA655306:MWD655306 NFW655306:NFZ655306 NPS655306:NPV655306 NZO655306:NZR655306 OJK655306:OJN655306 OTG655306:OTJ655306 PDC655306:PDF655306 PMY655306:PNB655306 PWU655306:PWX655306 QGQ655306:QGT655306 QQM655306:QQP655306 RAI655306:RAL655306 RKE655306:RKH655306 RUA655306:RUD655306 SDW655306:SDZ655306 SNS655306:SNV655306 SXO655306:SXR655306 THK655306:THN655306 TRG655306:TRJ655306 UBC655306:UBF655306 UKY655306:ULB655306 UUU655306:UUX655306 VEQ655306:VET655306 VOM655306:VOP655306 VYI655306:VYL655306 WIE655306:WIH655306 WSA655306:WSD655306 FO720842:FR720842 PK720842:PN720842 ZG720842:ZJ720842 AJC720842:AJF720842 ASY720842:ATB720842 BCU720842:BCX720842 BMQ720842:BMT720842 BWM720842:BWP720842 CGI720842:CGL720842 CQE720842:CQH720842 DAA720842:DAD720842 DJW720842:DJZ720842 DTS720842:DTV720842 EDO720842:EDR720842 ENK720842:ENN720842 EXG720842:EXJ720842 FHC720842:FHF720842 FQY720842:FRB720842 GAU720842:GAX720842 GKQ720842:GKT720842 GUM720842:GUP720842 HEI720842:HEL720842 HOE720842:HOH720842 HYA720842:HYD720842 IHW720842:IHZ720842 IRS720842:IRV720842 JBO720842:JBR720842 JLK720842:JLN720842 JVG720842:JVJ720842 KFC720842:KFF720842 KOY720842:KPB720842 KYU720842:KYX720842 LIQ720842:LIT720842 LSM720842:LSP720842 MCI720842:MCL720842 MME720842:MMH720842 MWA720842:MWD720842 NFW720842:NFZ720842 NPS720842:NPV720842 NZO720842:NZR720842 OJK720842:OJN720842 OTG720842:OTJ720842 PDC720842:PDF720842 PMY720842:PNB720842 PWU720842:PWX720842 QGQ720842:QGT720842 QQM720842:QQP720842 RAI720842:RAL720842 RKE720842:RKH720842 RUA720842:RUD720842 SDW720842:SDZ720842 SNS720842:SNV720842 SXO720842:SXR720842 THK720842:THN720842 TRG720842:TRJ720842 UBC720842:UBF720842 UKY720842:ULB720842 UUU720842:UUX720842 VEQ720842:VET720842 VOM720842:VOP720842 VYI720842:VYL720842 WIE720842:WIH720842 WSA720842:WSD720842 FO786378:FR786378 PK786378:PN786378 ZG786378:ZJ786378 AJC786378:AJF786378 ASY786378:ATB786378 BCU786378:BCX786378 BMQ786378:BMT786378 BWM786378:BWP786378 CGI786378:CGL786378 CQE786378:CQH786378 DAA786378:DAD786378 DJW786378:DJZ786378 DTS786378:DTV786378 EDO786378:EDR786378 ENK786378:ENN786378 EXG786378:EXJ786378 FHC786378:FHF786378 FQY786378:FRB786378 GAU786378:GAX786378 GKQ786378:GKT786378 GUM786378:GUP786378 HEI786378:HEL786378 HOE786378:HOH786378 HYA786378:HYD786378 IHW786378:IHZ786378 IRS786378:IRV786378 JBO786378:JBR786378 JLK786378:JLN786378 JVG786378:JVJ786378 KFC786378:KFF786378 KOY786378:KPB786378 KYU786378:KYX786378 LIQ786378:LIT786378 LSM786378:LSP786378 MCI786378:MCL786378 MME786378:MMH786378 MWA786378:MWD786378 NFW786378:NFZ786378 NPS786378:NPV786378 NZO786378:NZR786378 OJK786378:OJN786378 OTG786378:OTJ786378 PDC786378:PDF786378 PMY786378:PNB786378 PWU786378:PWX786378 QGQ786378:QGT786378 QQM786378:QQP786378 RAI786378:RAL786378 RKE786378:RKH786378 RUA786378:RUD786378 SDW786378:SDZ786378 SNS786378:SNV786378 SXO786378:SXR786378 THK786378:THN786378 TRG786378:TRJ786378 UBC786378:UBF786378 UKY786378:ULB786378 UUU786378:UUX786378 VEQ786378:VET786378 VOM786378:VOP786378 VYI786378:VYL786378 WIE786378:WIH786378 WSA786378:WSD786378 FO851914:FR851914 PK851914:PN851914 ZG851914:ZJ851914 AJC851914:AJF851914 ASY851914:ATB851914 BCU851914:BCX851914 BMQ851914:BMT851914 BWM851914:BWP851914 CGI851914:CGL851914 CQE851914:CQH851914 DAA851914:DAD851914 DJW851914:DJZ851914 DTS851914:DTV851914 EDO851914:EDR851914 ENK851914:ENN851914 EXG851914:EXJ851914 FHC851914:FHF851914 FQY851914:FRB851914 GAU851914:GAX851914 GKQ851914:GKT851914 GUM851914:GUP851914 HEI851914:HEL851914 HOE851914:HOH851914 HYA851914:HYD851914 IHW851914:IHZ851914 IRS851914:IRV851914 JBO851914:JBR851914 JLK851914:JLN851914 JVG851914:JVJ851914 KFC851914:KFF851914 KOY851914:KPB851914 KYU851914:KYX851914 LIQ851914:LIT851914 LSM851914:LSP851914 MCI851914:MCL851914 MME851914:MMH851914 MWA851914:MWD851914 NFW851914:NFZ851914 NPS851914:NPV851914 NZO851914:NZR851914 OJK851914:OJN851914 OTG851914:OTJ851914 PDC851914:PDF851914 PMY851914:PNB851914 PWU851914:PWX851914 QGQ851914:QGT851914 QQM851914:QQP851914 RAI851914:RAL851914 RKE851914:RKH851914 RUA851914:RUD851914 SDW851914:SDZ851914 SNS851914:SNV851914 SXO851914:SXR851914 THK851914:THN851914 TRG851914:TRJ851914 UBC851914:UBF851914 UKY851914:ULB851914 UUU851914:UUX851914 VEQ851914:VET851914 VOM851914:VOP851914 VYI851914:VYL851914 WIE851914:WIH851914 WSA851914:WSD851914 FO917450:FR917450 PK917450:PN917450 ZG917450:ZJ917450 AJC917450:AJF917450 ASY917450:ATB917450 BCU917450:BCX917450 BMQ917450:BMT917450 BWM917450:BWP917450 CGI917450:CGL917450 CQE917450:CQH917450 DAA917450:DAD917450 DJW917450:DJZ917450 DTS917450:DTV917450 EDO917450:EDR917450 ENK917450:ENN917450 EXG917450:EXJ917450 FHC917450:FHF917450 FQY917450:FRB917450 GAU917450:GAX917450 GKQ917450:GKT917450 GUM917450:GUP917450 HEI917450:HEL917450 HOE917450:HOH917450 HYA917450:HYD917450 IHW917450:IHZ917450 IRS917450:IRV917450 JBO917450:JBR917450 JLK917450:JLN917450 JVG917450:JVJ917450 KFC917450:KFF917450 KOY917450:KPB917450 KYU917450:KYX917450 LIQ917450:LIT917450 LSM917450:LSP917450 MCI917450:MCL917450 MME917450:MMH917450 MWA917450:MWD917450 NFW917450:NFZ917450 NPS917450:NPV917450 NZO917450:NZR917450 OJK917450:OJN917450 OTG917450:OTJ917450 PDC917450:PDF917450 PMY917450:PNB917450 PWU917450:PWX917450 QGQ917450:QGT917450 QQM917450:QQP917450 RAI917450:RAL917450 RKE917450:RKH917450 RUA917450:RUD917450 SDW917450:SDZ917450 SNS917450:SNV917450 SXO917450:SXR917450 THK917450:THN917450 TRG917450:TRJ917450 UBC917450:UBF917450 UKY917450:ULB917450 UUU917450:UUX917450 VEQ917450:VET917450 VOM917450:VOP917450 VYI917450:VYL917450 WIE917450:WIH917450 WSA917450:WSD917450 FO982986:FR982986 PK982986:PN982986 ZG982986:ZJ982986 AJC982986:AJF982986 ASY982986:ATB982986 BCU982986:BCX982986 BMQ982986:BMT982986 BWM982986:BWP982986 CGI982986:CGL982986 CQE982986:CQH982986 DAA982986:DAD982986 DJW982986:DJZ982986 DTS982986:DTV982986 EDO982986:EDR982986 ENK982986:ENN982986 EXG982986:EXJ982986 FHC982986:FHF982986 FQY982986:FRB982986 GAU982986:GAX982986 GKQ982986:GKT982986 GUM982986:GUP982986 HEI982986:HEL982986 HOE982986:HOH982986 HYA982986:HYD982986 IHW982986:IHZ982986 IRS982986:IRV982986 JBO982986:JBR982986 JLK982986:JLN982986 JVG982986:JVJ982986 KFC982986:KFF982986 KOY982986:KPB982986 KYU982986:KYX982986 LIQ982986:LIT982986 LSM982986:LSP982986 MCI982986:MCL982986 MME982986:MMH982986 MWA982986:MWD982986 NFW982986:NFZ982986 NPS982986:NPV982986 NZO982986:NZR982986 OJK982986:OJN982986 OTG982986:OTJ982986 PDC982986:PDF982986 PMY982986:PNB982986 PWU982986:PWX982986 QGQ982986:QGT982986 QQM982986:QQP982986 RAI982986:RAL982986 RKE982986:RKH982986 RUA982986:RUD982986 SDW982986:SDZ982986 SNS982986:SNV982986 SXO982986:SXR982986 THK982986:THN982986 TRG982986:TRJ982986 UBC982986:UBF982986 UKY982986:ULB982986 UUU982986:UUX982986 VEQ982986:VET982986 VOM982986:VOP982986 VYI982986:VYL982986 WIE982986:WIH982986 WSA982986:WSD982986 FJ982985:FM982985 PF982985:PI982985 ZB982985:ZE982985 AIX982985:AJA982985 AST982985:ASW982985 BCP982985:BCS982985 BML982985:BMO982985 BWH982985:BWK982985 CGD982985:CGG982985 CPZ982985:CQC982985 CZV982985:CZY982985 DJR982985:DJU982985 DTN982985:DTQ982985 EDJ982985:EDM982985 ENF982985:ENI982985 EXB982985:EXE982985 FGX982985:FHA982985 FQT982985:FQW982985 GAP982985:GAS982985 GKL982985:GKO982985 GUH982985:GUK982985 HED982985:HEG982985 HNZ982985:HOC982985 HXV982985:HXY982985 IHR982985:IHU982985 IRN982985:IRQ982985 JBJ982985:JBM982985 JLF982985:JLI982985 JVB982985:JVE982985 KEX982985:KFA982985 KOT982985:KOW982985 KYP982985:KYS982985 LIL982985:LIO982985 LSH982985:LSK982985 MCD982985:MCG982985 MLZ982985:MMC982985 MVV982985:MVY982985 NFR982985:NFU982985 NPN982985:NPQ982985 NZJ982985:NZM982985 OJF982985:OJI982985 OTB982985:OTE982985 PCX982985:PDA982985 PMT982985:PMW982985 PWP982985:PWS982985 QGL982985:QGO982985 QQH982985:QQK982985 RAD982985:RAG982985 RJZ982985:RKC982985 RTV982985:RTY982985 SDR982985:SDU982985 SNN982985:SNQ982985 SXJ982985:SXM982985 THF982985:THI982985 TRB982985:TRE982985 UAX982985:UBA982985 UKT982985:UKW982985 UUP982985:UUS982985 VEL982985:VEO982985 VOH982985:VOK982985 VYD982985:VYG982985 WHZ982985:WIC982985 WRV982985:WRY982985 FJ65481:FM65481 PF65481:PI65481 ZB65481:ZE65481 AIX65481:AJA65481 AST65481:ASW65481 BCP65481:BCS65481 BML65481:BMO65481 BWH65481:BWK65481 CGD65481:CGG65481 CPZ65481:CQC65481 CZV65481:CZY65481 DJR65481:DJU65481 DTN65481:DTQ65481 EDJ65481:EDM65481 ENF65481:ENI65481 EXB65481:EXE65481 FGX65481:FHA65481 FQT65481:FQW65481 GAP65481:GAS65481 GKL65481:GKO65481 GUH65481:GUK65481 HED65481:HEG65481 HNZ65481:HOC65481 HXV65481:HXY65481 IHR65481:IHU65481 IRN65481:IRQ65481 JBJ65481:JBM65481 JLF65481:JLI65481 JVB65481:JVE65481 KEX65481:KFA65481 KOT65481:KOW65481 KYP65481:KYS65481 LIL65481:LIO65481 LSH65481:LSK65481 MCD65481:MCG65481 MLZ65481:MMC65481 MVV65481:MVY65481 NFR65481:NFU65481 NPN65481:NPQ65481 NZJ65481:NZM65481 OJF65481:OJI65481 OTB65481:OTE65481 PCX65481:PDA65481 PMT65481:PMW65481 PWP65481:PWS65481 QGL65481:QGO65481 QQH65481:QQK65481 RAD65481:RAG65481 RJZ65481:RKC65481 RTV65481:RTY65481 SDR65481:SDU65481 SNN65481:SNQ65481 SXJ65481:SXM65481 THF65481:THI65481 TRB65481:TRE65481 UAX65481:UBA65481 UKT65481:UKW65481 UUP65481:UUS65481 VEL65481:VEO65481 VOH65481:VOK65481 VYD65481:VYG65481 WHZ65481:WIC65481 WRV65481:WRY65481 FJ131017:FM131017 PF131017:PI131017 ZB131017:ZE131017 AIX131017:AJA131017 AST131017:ASW131017 BCP131017:BCS131017 BML131017:BMO131017 BWH131017:BWK131017 CGD131017:CGG131017 CPZ131017:CQC131017 CZV131017:CZY131017 DJR131017:DJU131017 DTN131017:DTQ131017 EDJ131017:EDM131017 ENF131017:ENI131017 EXB131017:EXE131017 FGX131017:FHA131017 FQT131017:FQW131017 GAP131017:GAS131017 GKL131017:GKO131017 GUH131017:GUK131017 HED131017:HEG131017 HNZ131017:HOC131017 HXV131017:HXY131017 IHR131017:IHU131017 IRN131017:IRQ131017 JBJ131017:JBM131017 JLF131017:JLI131017 JVB131017:JVE131017 KEX131017:KFA131017 KOT131017:KOW131017 KYP131017:KYS131017 LIL131017:LIO131017 LSH131017:LSK131017 MCD131017:MCG131017 MLZ131017:MMC131017 MVV131017:MVY131017 NFR131017:NFU131017 NPN131017:NPQ131017 NZJ131017:NZM131017 OJF131017:OJI131017 OTB131017:OTE131017 PCX131017:PDA131017 PMT131017:PMW131017 PWP131017:PWS131017 QGL131017:QGO131017 QQH131017:QQK131017 RAD131017:RAG131017 RJZ131017:RKC131017 RTV131017:RTY131017 SDR131017:SDU131017 SNN131017:SNQ131017 SXJ131017:SXM131017 THF131017:THI131017 TRB131017:TRE131017 UAX131017:UBA131017 UKT131017:UKW131017 UUP131017:UUS131017 VEL131017:VEO131017 VOH131017:VOK131017 VYD131017:VYG131017 WHZ131017:WIC131017 WRV131017:WRY131017 FJ196553:FM196553 PF196553:PI196553 ZB196553:ZE196553 AIX196553:AJA196553 AST196553:ASW196553 BCP196553:BCS196553 BML196553:BMO196553 BWH196553:BWK196553 CGD196553:CGG196553 CPZ196553:CQC196553 CZV196553:CZY196553 DJR196553:DJU196553 DTN196553:DTQ196553 EDJ196553:EDM196553 ENF196553:ENI196553 EXB196553:EXE196553 FGX196553:FHA196553 FQT196553:FQW196553 GAP196553:GAS196553 GKL196553:GKO196553 GUH196553:GUK196553 HED196553:HEG196553 HNZ196553:HOC196553 HXV196553:HXY196553 IHR196553:IHU196553 IRN196553:IRQ196553 JBJ196553:JBM196553 JLF196553:JLI196553 JVB196553:JVE196553 KEX196553:KFA196553 KOT196553:KOW196553 KYP196553:KYS196553 LIL196553:LIO196553 LSH196553:LSK196553 MCD196553:MCG196553 MLZ196553:MMC196553 MVV196553:MVY196553 NFR196553:NFU196553 NPN196553:NPQ196553 NZJ196553:NZM196553 OJF196553:OJI196553 OTB196553:OTE196553 PCX196553:PDA196553 PMT196553:PMW196553 PWP196553:PWS196553 QGL196553:QGO196553 QQH196553:QQK196553 RAD196553:RAG196553 RJZ196553:RKC196553 RTV196553:RTY196553 SDR196553:SDU196553 SNN196553:SNQ196553 SXJ196553:SXM196553 THF196553:THI196553 TRB196553:TRE196553 UAX196553:UBA196553 UKT196553:UKW196553 UUP196553:UUS196553 VEL196553:VEO196553 VOH196553:VOK196553 VYD196553:VYG196553 WHZ196553:WIC196553 WRV196553:WRY196553 FJ262089:FM262089 PF262089:PI262089 ZB262089:ZE262089 AIX262089:AJA262089 AST262089:ASW262089 BCP262089:BCS262089 BML262089:BMO262089 BWH262089:BWK262089 CGD262089:CGG262089 CPZ262089:CQC262089 CZV262089:CZY262089 DJR262089:DJU262089 DTN262089:DTQ262089 EDJ262089:EDM262089 ENF262089:ENI262089 EXB262089:EXE262089 FGX262089:FHA262089 FQT262089:FQW262089 GAP262089:GAS262089 GKL262089:GKO262089 GUH262089:GUK262089 HED262089:HEG262089 HNZ262089:HOC262089 HXV262089:HXY262089 IHR262089:IHU262089 IRN262089:IRQ262089 JBJ262089:JBM262089 JLF262089:JLI262089 JVB262089:JVE262089 KEX262089:KFA262089 KOT262089:KOW262089 KYP262089:KYS262089 LIL262089:LIO262089 LSH262089:LSK262089 MCD262089:MCG262089 MLZ262089:MMC262089 MVV262089:MVY262089 NFR262089:NFU262089 NPN262089:NPQ262089 NZJ262089:NZM262089 OJF262089:OJI262089 OTB262089:OTE262089 PCX262089:PDA262089 PMT262089:PMW262089 PWP262089:PWS262089 QGL262089:QGO262089 QQH262089:QQK262089 RAD262089:RAG262089 RJZ262089:RKC262089 RTV262089:RTY262089 SDR262089:SDU262089 SNN262089:SNQ262089 SXJ262089:SXM262089 THF262089:THI262089 TRB262089:TRE262089 UAX262089:UBA262089 UKT262089:UKW262089 UUP262089:UUS262089 VEL262089:VEO262089 VOH262089:VOK262089 VYD262089:VYG262089 WHZ262089:WIC262089 WRV262089:WRY262089 FJ327625:FM327625 PF327625:PI327625 ZB327625:ZE327625 AIX327625:AJA327625 AST327625:ASW327625 BCP327625:BCS327625 BML327625:BMO327625 BWH327625:BWK327625 CGD327625:CGG327625 CPZ327625:CQC327625 CZV327625:CZY327625 DJR327625:DJU327625 DTN327625:DTQ327625 EDJ327625:EDM327625 ENF327625:ENI327625 EXB327625:EXE327625 FGX327625:FHA327625 FQT327625:FQW327625 GAP327625:GAS327625 GKL327625:GKO327625 GUH327625:GUK327625 HED327625:HEG327625 HNZ327625:HOC327625 HXV327625:HXY327625 IHR327625:IHU327625 IRN327625:IRQ327625 JBJ327625:JBM327625 JLF327625:JLI327625 JVB327625:JVE327625 KEX327625:KFA327625 KOT327625:KOW327625 KYP327625:KYS327625 LIL327625:LIO327625 LSH327625:LSK327625 MCD327625:MCG327625 MLZ327625:MMC327625 MVV327625:MVY327625 NFR327625:NFU327625 NPN327625:NPQ327625 NZJ327625:NZM327625 OJF327625:OJI327625 OTB327625:OTE327625 PCX327625:PDA327625 PMT327625:PMW327625 PWP327625:PWS327625 QGL327625:QGO327625 QQH327625:QQK327625 RAD327625:RAG327625 RJZ327625:RKC327625 RTV327625:RTY327625 SDR327625:SDU327625 SNN327625:SNQ327625 SXJ327625:SXM327625 THF327625:THI327625 TRB327625:TRE327625 UAX327625:UBA327625 UKT327625:UKW327625 UUP327625:UUS327625 VEL327625:VEO327625 VOH327625:VOK327625 VYD327625:VYG327625 WHZ327625:WIC327625 WRV327625:WRY327625 FJ393161:FM393161 PF393161:PI393161 ZB393161:ZE393161 AIX393161:AJA393161 AST393161:ASW393161 BCP393161:BCS393161 BML393161:BMO393161 BWH393161:BWK393161 CGD393161:CGG393161 CPZ393161:CQC393161 CZV393161:CZY393161 DJR393161:DJU393161 DTN393161:DTQ393161 EDJ393161:EDM393161 ENF393161:ENI393161 EXB393161:EXE393161 FGX393161:FHA393161 FQT393161:FQW393161 GAP393161:GAS393161 GKL393161:GKO393161 GUH393161:GUK393161 HED393161:HEG393161 HNZ393161:HOC393161 HXV393161:HXY393161 IHR393161:IHU393161 IRN393161:IRQ393161 JBJ393161:JBM393161 JLF393161:JLI393161 JVB393161:JVE393161 KEX393161:KFA393161 KOT393161:KOW393161 KYP393161:KYS393161 LIL393161:LIO393161 LSH393161:LSK393161 MCD393161:MCG393161 MLZ393161:MMC393161 MVV393161:MVY393161 NFR393161:NFU393161 NPN393161:NPQ393161 NZJ393161:NZM393161 OJF393161:OJI393161 OTB393161:OTE393161 PCX393161:PDA393161 PMT393161:PMW393161 PWP393161:PWS393161 QGL393161:QGO393161 QQH393161:QQK393161 RAD393161:RAG393161 RJZ393161:RKC393161 RTV393161:RTY393161 SDR393161:SDU393161 SNN393161:SNQ393161 SXJ393161:SXM393161 THF393161:THI393161 TRB393161:TRE393161 UAX393161:UBA393161 UKT393161:UKW393161 UUP393161:UUS393161 VEL393161:VEO393161 VOH393161:VOK393161 VYD393161:VYG393161 WHZ393161:WIC393161 WRV393161:WRY393161 FJ458697:FM458697 PF458697:PI458697 ZB458697:ZE458697 AIX458697:AJA458697 AST458697:ASW458697 BCP458697:BCS458697 BML458697:BMO458697 BWH458697:BWK458697 CGD458697:CGG458697 CPZ458697:CQC458697 CZV458697:CZY458697 DJR458697:DJU458697 DTN458697:DTQ458697 EDJ458697:EDM458697 ENF458697:ENI458697 EXB458697:EXE458697 FGX458697:FHA458697 FQT458697:FQW458697 GAP458697:GAS458697 GKL458697:GKO458697 GUH458697:GUK458697 HED458697:HEG458697 HNZ458697:HOC458697 HXV458697:HXY458697 IHR458697:IHU458697 IRN458697:IRQ458697 JBJ458697:JBM458697 JLF458697:JLI458697 JVB458697:JVE458697 KEX458697:KFA458697 KOT458697:KOW458697 KYP458697:KYS458697 LIL458697:LIO458697 LSH458697:LSK458697 MCD458697:MCG458697 MLZ458697:MMC458697 MVV458697:MVY458697 NFR458697:NFU458697 NPN458697:NPQ458697 NZJ458697:NZM458697 OJF458697:OJI458697 OTB458697:OTE458697 PCX458697:PDA458697 PMT458697:PMW458697 PWP458697:PWS458697 QGL458697:QGO458697 QQH458697:QQK458697 RAD458697:RAG458697 RJZ458697:RKC458697 RTV458697:RTY458697 SDR458697:SDU458697 SNN458697:SNQ458697 SXJ458697:SXM458697 THF458697:THI458697 TRB458697:TRE458697 UAX458697:UBA458697 UKT458697:UKW458697 UUP458697:UUS458697 VEL458697:VEO458697 VOH458697:VOK458697 VYD458697:VYG458697 WHZ458697:WIC458697 WRV458697:WRY458697 FJ524233:FM524233 PF524233:PI524233 ZB524233:ZE524233 AIX524233:AJA524233 AST524233:ASW524233 BCP524233:BCS524233 BML524233:BMO524233 BWH524233:BWK524233 CGD524233:CGG524233 CPZ524233:CQC524233 CZV524233:CZY524233 DJR524233:DJU524233 DTN524233:DTQ524233 EDJ524233:EDM524233 ENF524233:ENI524233 EXB524233:EXE524233 FGX524233:FHA524233 FQT524233:FQW524233 GAP524233:GAS524233 GKL524233:GKO524233 GUH524233:GUK524233 HED524233:HEG524233 HNZ524233:HOC524233 HXV524233:HXY524233 IHR524233:IHU524233 IRN524233:IRQ524233 JBJ524233:JBM524233 JLF524233:JLI524233 JVB524233:JVE524233 KEX524233:KFA524233 KOT524233:KOW524233 KYP524233:KYS524233 LIL524233:LIO524233 LSH524233:LSK524233 MCD524233:MCG524233 MLZ524233:MMC524233 MVV524233:MVY524233 NFR524233:NFU524233 NPN524233:NPQ524233 NZJ524233:NZM524233 OJF524233:OJI524233 OTB524233:OTE524233 PCX524233:PDA524233 PMT524233:PMW524233 PWP524233:PWS524233 QGL524233:QGO524233 QQH524233:QQK524233 RAD524233:RAG524233 RJZ524233:RKC524233 RTV524233:RTY524233 SDR524233:SDU524233 SNN524233:SNQ524233 SXJ524233:SXM524233 THF524233:THI524233 TRB524233:TRE524233 UAX524233:UBA524233 UKT524233:UKW524233 UUP524233:UUS524233 VEL524233:VEO524233 VOH524233:VOK524233 VYD524233:VYG524233 WHZ524233:WIC524233 WRV524233:WRY524233 FJ589769:FM589769 PF589769:PI589769 ZB589769:ZE589769 AIX589769:AJA589769 AST589769:ASW589769 BCP589769:BCS589769 BML589769:BMO589769 BWH589769:BWK589769 CGD589769:CGG589769 CPZ589769:CQC589769 CZV589769:CZY589769 DJR589769:DJU589769 DTN589769:DTQ589769 EDJ589769:EDM589769 ENF589769:ENI589769 EXB589769:EXE589769 FGX589769:FHA589769 FQT589769:FQW589769 GAP589769:GAS589769 GKL589769:GKO589769 GUH589769:GUK589769 HED589769:HEG589769 HNZ589769:HOC589769 HXV589769:HXY589769 IHR589769:IHU589769 IRN589769:IRQ589769 JBJ589769:JBM589769 JLF589769:JLI589769 JVB589769:JVE589769 KEX589769:KFA589769 KOT589769:KOW589769 KYP589769:KYS589769 LIL589769:LIO589769 LSH589769:LSK589769 MCD589769:MCG589769 MLZ589769:MMC589769 MVV589769:MVY589769 NFR589769:NFU589769 NPN589769:NPQ589769 NZJ589769:NZM589769 OJF589769:OJI589769 OTB589769:OTE589769 PCX589769:PDA589769 PMT589769:PMW589769 PWP589769:PWS589769 QGL589769:QGO589769 QQH589769:QQK589769 RAD589769:RAG589769 RJZ589769:RKC589769 RTV589769:RTY589769 SDR589769:SDU589769 SNN589769:SNQ589769 SXJ589769:SXM589769 THF589769:THI589769 TRB589769:TRE589769 UAX589769:UBA589769 UKT589769:UKW589769 UUP589769:UUS589769 VEL589769:VEO589769 VOH589769:VOK589769 VYD589769:VYG589769 WHZ589769:WIC589769 WRV589769:WRY589769 FJ655305:FM655305 PF655305:PI655305 ZB655305:ZE655305 AIX655305:AJA655305 AST655305:ASW655305 BCP655305:BCS655305 BML655305:BMO655305 BWH655305:BWK655305 CGD655305:CGG655305 CPZ655305:CQC655305 CZV655305:CZY655305 DJR655305:DJU655305 DTN655305:DTQ655305 EDJ655305:EDM655305 ENF655305:ENI655305 EXB655305:EXE655305 FGX655305:FHA655305 FQT655305:FQW655305 GAP655305:GAS655305 GKL655305:GKO655305 GUH655305:GUK655305 HED655305:HEG655305 HNZ655305:HOC655305 HXV655305:HXY655305 IHR655305:IHU655305 IRN655305:IRQ655305 JBJ655305:JBM655305 JLF655305:JLI655305 JVB655305:JVE655305 KEX655305:KFA655305 KOT655305:KOW655305 KYP655305:KYS655305 LIL655305:LIO655305 LSH655305:LSK655305 MCD655305:MCG655305 MLZ655305:MMC655305 MVV655305:MVY655305 NFR655305:NFU655305 NPN655305:NPQ655305 NZJ655305:NZM655305 OJF655305:OJI655305 OTB655305:OTE655305 PCX655305:PDA655305 PMT655305:PMW655305 PWP655305:PWS655305 QGL655305:QGO655305 QQH655305:QQK655305 RAD655305:RAG655305 RJZ655305:RKC655305 RTV655305:RTY655305 SDR655305:SDU655305 SNN655305:SNQ655305 SXJ655305:SXM655305 THF655305:THI655305 TRB655305:TRE655305 UAX655305:UBA655305 UKT655305:UKW655305 UUP655305:UUS655305 VEL655305:VEO655305 VOH655305:VOK655305 VYD655305:VYG655305 WHZ655305:WIC655305 WRV655305:WRY655305 FJ720841:FM720841 PF720841:PI720841 ZB720841:ZE720841 AIX720841:AJA720841 AST720841:ASW720841 BCP720841:BCS720841 BML720841:BMO720841 BWH720841:BWK720841 CGD720841:CGG720841 CPZ720841:CQC720841 CZV720841:CZY720841 DJR720841:DJU720841 DTN720841:DTQ720841 EDJ720841:EDM720841 ENF720841:ENI720841 EXB720841:EXE720841 FGX720841:FHA720841 FQT720841:FQW720841 GAP720841:GAS720841 GKL720841:GKO720841 GUH720841:GUK720841 HED720841:HEG720841 HNZ720841:HOC720841 HXV720841:HXY720841 IHR720841:IHU720841 IRN720841:IRQ720841 JBJ720841:JBM720841 JLF720841:JLI720841 JVB720841:JVE720841 KEX720841:KFA720841 KOT720841:KOW720841 KYP720841:KYS720841 LIL720841:LIO720841 LSH720841:LSK720841 MCD720841:MCG720841 MLZ720841:MMC720841 MVV720841:MVY720841 NFR720841:NFU720841 NPN720841:NPQ720841 NZJ720841:NZM720841 OJF720841:OJI720841 OTB720841:OTE720841 PCX720841:PDA720841 PMT720841:PMW720841 PWP720841:PWS720841 QGL720841:QGO720841 QQH720841:QQK720841 RAD720841:RAG720841 RJZ720841:RKC720841 RTV720841:RTY720841 SDR720841:SDU720841 SNN720841:SNQ720841 SXJ720841:SXM720841 THF720841:THI720841 TRB720841:TRE720841 UAX720841:UBA720841 UKT720841:UKW720841 UUP720841:UUS720841 VEL720841:VEO720841 VOH720841:VOK720841 VYD720841:VYG720841 WHZ720841:WIC720841 WRV720841:WRY720841 FJ786377:FM786377 PF786377:PI786377 ZB786377:ZE786377 AIX786377:AJA786377 AST786377:ASW786377 BCP786377:BCS786377 BML786377:BMO786377 BWH786377:BWK786377 CGD786377:CGG786377 CPZ786377:CQC786377 CZV786377:CZY786377 DJR786377:DJU786377 DTN786377:DTQ786377 EDJ786377:EDM786377 ENF786377:ENI786377 EXB786377:EXE786377 FGX786377:FHA786377 FQT786377:FQW786377 GAP786377:GAS786377 GKL786377:GKO786377 GUH786377:GUK786377 HED786377:HEG786377 HNZ786377:HOC786377 HXV786377:HXY786377 IHR786377:IHU786377 IRN786377:IRQ786377 JBJ786377:JBM786377 JLF786377:JLI786377 JVB786377:JVE786377 KEX786377:KFA786377 KOT786377:KOW786377 KYP786377:KYS786377 LIL786377:LIO786377 LSH786377:LSK786377 MCD786377:MCG786377 MLZ786377:MMC786377 MVV786377:MVY786377 NFR786377:NFU786377 NPN786377:NPQ786377 NZJ786377:NZM786377 OJF786377:OJI786377 OTB786377:OTE786377 PCX786377:PDA786377 PMT786377:PMW786377 PWP786377:PWS786377 QGL786377:QGO786377 QQH786377:QQK786377 RAD786377:RAG786377 RJZ786377:RKC786377 RTV786377:RTY786377 SDR786377:SDU786377 SNN786377:SNQ786377 SXJ786377:SXM786377 THF786377:THI786377 TRB786377:TRE786377 UAX786377:UBA786377 UKT786377:UKW786377 UUP786377:UUS786377 VEL786377:VEO786377 VOH786377:VOK786377 VYD786377:VYG786377 WHZ786377:WIC786377 WRV786377:WRY786377 FJ851913:FM851913 PF851913:PI851913 ZB851913:ZE851913 AIX851913:AJA851913 AST851913:ASW851913 BCP851913:BCS851913 BML851913:BMO851913 BWH851913:BWK851913 CGD851913:CGG851913 CPZ851913:CQC851913 CZV851913:CZY851913 DJR851913:DJU851913 DTN851913:DTQ851913 EDJ851913:EDM851913 ENF851913:ENI851913 EXB851913:EXE851913 FGX851913:FHA851913 FQT851913:FQW851913 GAP851913:GAS851913 GKL851913:GKO851913 GUH851913:GUK851913 HED851913:HEG851913 HNZ851913:HOC851913 HXV851913:HXY851913 IHR851913:IHU851913 IRN851913:IRQ851913 JBJ851913:JBM851913 JLF851913:JLI851913 JVB851913:JVE851913 KEX851913:KFA851913 KOT851913:KOW851913 KYP851913:KYS851913 LIL851913:LIO851913 LSH851913:LSK851913 MCD851913:MCG851913 MLZ851913:MMC851913 MVV851913:MVY851913 NFR851913:NFU851913 NPN851913:NPQ851913 NZJ851913:NZM851913 OJF851913:OJI851913 OTB851913:OTE851913 PCX851913:PDA851913 PMT851913:PMW851913 PWP851913:PWS851913 QGL851913:QGO851913 QQH851913:QQK851913 RAD851913:RAG851913 RJZ851913:RKC851913 RTV851913:RTY851913 SDR851913:SDU851913 SNN851913:SNQ851913 SXJ851913:SXM851913 THF851913:THI851913 TRB851913:TRE851913 UAX851913:UBA851913 UKT851913:UKW851913 UUP851913:UUS851913 VEL851913:VEO851913 VOH851913:VOK851913 VYD851913:VYG851913 WHZ851913:WIC851913 WRV851913:WRY851913 FJ917449:FM917449 PF917449:PI917449 ZB917449:ZE917449 AIX917449:AJA917449 AST917449:ASW917449 BCP917449:BCS917449 BML917449:BMO917449 BWH917449:BWK917449 CGD917449:CGG917449 CPZ917449:CQC917449 CZV917449:CZY917449 DJR917449:DJU917449 DTN917449:DTQ917449 EDJ917449:EDM917449 ENF917449:ENI917449 EXB917449:EXE917449 FGX917449:FHA917449 FQT917449:FQW917449 GAP917449:GAS917449 GKL917449:GKO917449 GUH917449:GUK917449 HED917449:HEG917449 HNZ917449:HOC917449 HXV917449:HXY917449 IHR917449:IHU917449 IRN917449:IRQ917449 JBJ917449:JBM917449 JLF917449:JLI917449 JVB917449:JVE917449 KEX917449:KFA917449 KOT917449:KOW917449 KYP917449:KYS917449 LIL917449:LIO917449 LSH917449:LSK917449 MCD917449:MCG917449 MLZ917449:MMC917449 MVV917449:MVY917449 NFR917449:NFU917449 NPN917449:NPQ917449 NZJ917449:NZM917449 OJF917449:OJI917449 OTB917449:OTE917449 PCX917449:PDA917449 PMT917449:PMW917449 PWP917449:PWS917449 QGL917449:QGO917449 QQH917449:QQK917449 RAD917449:RAG917449 RJZ917449:RKC917449 RTV917449:RTY917449 SDR917449:SDU917449 SNN917449:SNQ917449 SXJ917449:SXM917449 THF917449:THI917449 TRB917449:TRE917449 UAX917449:UBA917449 UKT917449:UKW917449 UUP917449:UUS917449 VEL917449:VEO917449 VOH917449:VOK917449 VYD917449:VYG917449 WHZ917449:WIC917449 WRV917449:WRY917449" xr:uid="{B6B85443-0900-4054-AC55-9B2176606AF1}">
+      <formula1>"○"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FS65482:FV65482 PO65482:PR65482 ZK65482:ZN65482 AJG65482:AJJ65482 ATC65482:ATF65482 BCY65482:BDB65482 BMU65482:BMX65482 BWQ65482:BWT65482 CGM65482:CGP65482 CQI65482:CQL65482 DAE65482:DAH65482 DKA65482:DKD65482 DTW65482:DTZ65482 EDS65482:EDV65482 ENO65482:ENR65482 EXK65482:EXN65482 FHG65482:FHJ65482 FRC65482:FRF65482 GAY65482:GBB65482 GKU65482:GKX65482 GUQ65482:GUT65482 HEM65482:HEP65482 HOI65482:HOL65482 HYE65482:HYH65482 IIA65482:IID65482 IRW65482:IRZ65482 JBS65482:JBV65482 JLO65482:JLR65482 JVK65482:JVN65482 KFG65482:KFJ65482 KPC65482:KPF65482 KYY65482:KZB65482 LIU65482:LIX65482 LSQ65482:LST65482 MCM65482:MCP65482 MMI65482:MML65482 MWE65482:MWH65482 NGA65482:NGD65482 NPW65482:NPZ65482 NZS65482:NZV65482 OJO65482:OJR65482 OTK65482:OTN65482 PDG65482:PDJ65482 PNC65482:PNF65482 PWY65482:PXB65482 QGU65482:QGX65482 QQQ65482:QQT65482 RAM65482:RAP65482 RKI65482:RKL65482 RUE65482:RUH65482 SEA65482:SED65482 SNW65482:SNZ65482 SXS65482:SXV65482 THO65482:THR65482 TRK65482:TRN65482 UBG65482:UBJ65482 ULC65482:ULF65482 UUY65482:UVB65482 VEU65482:VEX65482 VOQ65482:VOT65482 VYM65482:VYP65482 WII65482:WIL65482 WSE65482:WSH65482 FS131018:FV131018 PO131018:PR131018 ZK131018:ZN131018 AJG131018:AJJ131018 ATC131018:ATF131018 BCY131018:BDB131018 BMU131018:BMX131018 BWQ131018:BWT131018 CGM131018:CGP131018 CQI131018:CQL131018 DAE131018:DAH131018 DKA131018:DKD131018 DTW131018:DTZ131018 EDS131018:EDV131018 ENO131018:ENR131018 EXK131018:EXN131018 FHG131018:FHJ131018 FRC131018:FRF131018 GAY131018:GBB131018 GKU131018:GKX131018 GUQ131018:GUT131018 HEM131018:HEP131018 HOI131018:HOL131018 HYE131018:HYH131018 IIA131018:IID131018 IRW131018:IRZ131018 JBS131018:JBV131018 JLO131018:JLR131018 JVK131018:JVN131018 KFG131018:KFJ131018 KPC131018:KPF131018 KYY131018:KZB131018 LIU131018:LIX131018 LSQ131018:LST131018 MCM131018:MCP131018 MMI131018:MML131018 MWE131018:MWH131018 NGA131018:NGD131018 NPW131018:NPZ131018 NZS131018:NZV131018 OJO131018:OJR131018 OTK131018:OTN131018 PDG131018:PDJ131018 PNC131018:PNF131018 PWY131018:PXB131018 QGU131018:QGX131018 QQQ131018:QQT131018 RAM131018:RAP131018 RKI131018:RKL131018 RUE131018:RUH131018 SEA131018:SED131018 SNW131018:SNZ131018 SXS131018:SXV131018 THO131018:THR131018 TRK131018:TRN131018 UBG131018:UBJ131018 ULC131018:ULF131018 UUY131018:UVB131018 VEU131018:VEX131018 VOQ131018:VOT131018 VYM131018:VYP131018 WII131018:WIL131018 WSE131018:WSH131018 FS196554:FV196554 PO196554:PR196554 ZK196554:ZN196554 AJG196554:AJJ196554 ATC196554:ATF196554 BCY196554:BDB196554 BMU196554:BMX196554 BWQ196554:BWT196554 CGM196554:CGP196554 CQI196554:CQL196554 DAE196554:DAH196554 DKA196554:DKD196554 DTW196554:DTZ196554 EDS196554:EDV196554 ENO196554:ENR196554 EXK196554:EXN196554 FHG196554:FHJ196554 FRC196554:FRF196554 GAY196554:GBB196554 GKU196554:GKX196554 GUQ196554:GUT196554 HEM196554:HEP196554 HOI196554:HOL196554 HYE196554:HYH196554 IIA196554:IID196554 IRW196554:IRZ196554 JBS196554:JBV196554 JLO196554:JLR196554 JVK196554:JVN196554 KFG196554:KFJ196554 KPC196554:KPF196554 KYY196554:KZB196554 LIU196554:LIX196554 LSQ196554:LST196554 MCM196554:MCP196554 MMI196554:MML196554 MWE196554:MWH196554 NGA196554:NGD196554 NPW196554:NPZ196554 NZS196554:NZV196554 OJO196554:OJR196554 OTK196554:OTN196554 PDG196554:PDJ196554 PNC196554:PNF196554 PWY196554:PXB196554 QGU196554:QGX196554 QQQ196554:QQT196554 RAM196554:RAP196554 RKI196554:RKL196554 RUE196554:RUH196554 SEA196554:SED196554 SNW196554:SNZ196554 SXS196554:SXV196554 THO196554:THR196554 TRK196554:TRN196554 UBG196554:UBJ196554 ULC196554:ULF196554 UUY196554:UVB196554 VEU196554:VEX196554 VOQ196554:VOT196554 VYM196554:VYP196554 WII196554:WIL196554 WSE196554:WSH196554 FS262090:FV262090 PO262090:PR262090 ZK262090:ZN262090 AJG262090:AJJ262090 ATC262090:ATF262090 BCY262090:BDB262090 BMU262090:BMX262090 BWQ262090:BWT262090 CGM262090:CGP262090 CQI262090:CQL262090 DAE262090:DAH262090 DKA262090:DKD262090 DTW262090:DTZ262090 EDS262090:EDV262090 ENO262090:ENR262090 EXK262090:EXN262090 FHG262090:FHJ262090 FRC262090:FRF262090 GAY262090:GBB262090 GKU262090:GKX262090 GUQ262090:GUT262090 HEM262090:HEP262090 HOI262090:HOL262090 HYE262090:HYH262090 IIA262090:IID262090 IRW262090:IRZ262090 JBS262090:JBV262090 JLO262090:JLR262090 JVK262090:JVN262090 KFG262090:KFJ262090 KPC262090:KPF262090 KYY262090:KZB262090 LIU262090:LIX262090 LSQ262090:LST262090 MCM262090:MCP262090 MMI262090:MML262090 MWE262090:MWH262090 NGA262090:NGD262090 NPW262090:NPZ262090 NZS262090:NZV262090 OJO262090:OJR262090 OTK262090:OTN262090 PDG262090:PDJ262090 PNC262090:PNF262090 PWY262090:PXB262090 QGU262090:QGX262090 QQQ262090:QQT262090 RAM262090:RAP262090 RKI262090:RKL262090 RUE262090:RUH262090 SEA262090:SED262090 SNW262090:SNZ262090 SXS262090:SXV262090 THO262090:THR262090 TRK262090:TRN262090 UBG262090:UBJ262090 ULC262090:ULF262090 UUY262090:UVB262090 VEU262090:VEX262090 VOQ262090:VOT262090 VYM262090:VYP262090 WII262090:WIL262090 WSE262090:WSH262090 FS327626:FV327626 PO327626:PR327626 ZK327626:ZN327626 AJG327626:AJJ327626 ATC327626:ATF327626 BCY327626:BDB327626 BMU327626:BMX327626 BWQ327626:BWT327626 CGM327626:CGP327626 CQI327626:CQL327626 DAE327626:DAH327626 DKA327626:DKD327626 DTW327626:DTZ327626 EDS327626:EDV327626 ENO327626:ENR327626 EXK327626:EXN327626 FHG327626:FHJ327626 FRC327626:FRF327626 GAY327626:GBB327626 GKU327626:GKX327626 GUQ327626:GUT327626 HEM327626:HEP327626 HOI327626:HOL327626 HYE327626:HYH327626 IIA327626:IID327626 IRW327626:IRZ327626 JBS327626:JBV327626 JLO327626:JLR327626 JVK327626:JVN327626 KFG327626:KFJ327626 KPC327626:KPF327626 KYY327626:KZB327626 LIU327626:LIX327626 LSQ327626:LST327626 MCM327626:MCP327626 MMI327626:MML327626 MWE327626:MWH327626 NGA327626:NGD327626 NPW327626:NPZ327626 NZS327626:NZV327626 OJO327626:OJR327626 OTK327626:OTN327626 PDG327626:PDJ327626 PNC327626:PNF327626 PWY327626:PXB327626 QGU327626:QGX327626 QQQ327626:QQT327626 RAM327626:RAP327626 RKI327626:RKL327626 RUE327626:RUH327626 SEA327626:SED327626 SNW327626:SNZ327626 SXS327626:SXV327626 THO327626:THR327626 TRK327626:TRN327626 UBG327626:UBJ327626 ULC327626:ULF327626 UUY327626:UVB327626 VEU327626:VEX327626 VOQ327626:VOT327626 VYM327626:VYP327626 WII327626:WIL327626 WSE327626:WSH327626 FS393162:FV393162 PO393162:PR393162 ZK393162:ZN393162 AJG393162:AJJ393162 ATC393162:ATF393162 BCY393162:BDB393162 BMU393162:BMX393162 BWQ393162:BWT393162 CGM393162:CGP393162 CQI393162:CQL393162 DAE393162:DAH393162 DKA393162:DKD393162 DTW393162:DTZ393162 EDS393162:EDV393162 ENO393162:ENR393162 EXK393162:EXN393162 FHG393162:FHJ393162 FRC393162:FRF393162 GAY393162:GBB393162 GKU393162:GKX393162 GUQ393162:GUT393162 HEM393162:HEP393162 HOI393162:HOL393162 HYE393162:HYH393162 IIA393162:IID393162 IRW393162:IRZ393162 JBS393162:JBV393162 JLO393162:JLR393162 JVK393162:JVN393162 KFG393162:KFJ393162 KPC393162:KPF393162 KYY393162:KZB393162 LIU393162:LIX393162 LSQ393162:LST393162 MCM393162:MCP393162 MMI393162:MML393162 MWE393162:MWH393162 NGA393162:NGD393162 NPW393162:NPZ393162 NZS393162:NZV393162 OJO393162:OJR393162 OTK393162:OTN393162 PDG393162:PDJ393162 PNC393162:PNF393162 PWY393162:PXB393162 QGU393162:QGX393162 QQQ393162:QQT393162 RAM393162:RAP393162 RKI393162:RKL393162 RUE393162:RUH393162 SEA393162:SED393162 SNW393162:SNZ393162 SXS393162:SXV393162 THO393162:THR393162 TRK393162:TRN393162 UBG393162:UBJ393162 ULC393162:ULF393162 UUY393162:UVB393162 VEU393162:VEX393162 VOQ393162:VOT393162 VYM393162:VYP393162 WII393162:WIL393162 WSE393162:WSH393162 FS458698:FV458698 PO458698:PR458698 ZK458698:ZN458698 AJG458698:AJJ458698 ATC458698:ATF458698 BCY458698:BDB458698 BMU458698:BMX458698 BWQ458698:BWT458698 CGM458698:CGP458698 CQI458698:CQL458698 DAE458698:DAH458698 DKA458698:DKD458698 DTW458698:DTZ458698 EDS458698:EDV458698 ENO458698:ENR458698 EXK458698:EXN458698 FHG458698:FHJ458698 FRC458698:FRF458698 GAY458698:GBB458698 GKU458698:GKX458698 GUQ458698:GUT458698 HEM458698:HEP458698 HOI458698:HOL458698 HYE458698:HYH458698 IIA458698:IID458698 IRW458698:IRZ458698 JBS458698:JBV458698 JLO458698:JLR458698 JVK458698:JVN458698 KFG458698:KFJ458698 KPC458698:KPF458698 KYY458698:KZB458698 LIU458698:LIX458698 LSQ458698:LST458698 MCM458698:MCP458698 MMI458698:MML458698 MWE458698:MWH458698 NGA458698:NGD458698 NPW458698:NPZ458698 NZS458698:NZV458698 OJO458698:OJR458698 OTK458698:OTN458698 PDG458698:PDJ458698 PNC458698:PNF458698 PWY458698:PXB458698 QGU458698:QGX458698 QQQ458698:QQT458698 RAM458698:RAP458698 RKI458698:RKL458698 RUE458698:RUH458698 SEA458698:SED458698 SNW458698:SNZ458698 SXS458698:SXV458698 THO458698:THR458698 TRK458698:TRN458698 UBG458698:UBJ458698 ULC458698:ULF458698 UUY458698:UVB458698 VEU458698:VEX458698 VOQ458698:VOT458698 VYM458698:VYP458698 WII458698:WIL458698 WSE458698:WSH458698 FS524234:FV524234 PO524234:PR524234 ZK524234:ZN524234 AJG524234:AJJ524234 ATC524234:ATF524234 BCY524234:BDB524234 BMU524234:BMX524234 BWQ524234:BWT524234 CGM524234:CGP524234 CQI524234:CQL524234 DAE524234:DAH524234 DKA524234:DKD524234 DTW524234:DTZ524234 EDS524234:EDV524234 ENO524234:ENR524234 EXK524234:EXN524234 FHG524234:FHJ524234 FRC524234:FRF524234 GAY524234:GBB524234 GKU524234:GKX524234 GUQ524234:GUT524234 HEM524234:HEP524234 HOI524234:HOL524234 HYE524234:HYH524234 IIA524234:IID524234 IRW524234:IRZ524234 JBS524234:JBV524234 JLO524234:JLR524234 JVK524234:JVN524234 KFG524234:KFJ524234 KPC524234:KPF524234 KYY524234:KZB524234 LIU524234:LIX524234 LSQ524234:LST524234 MCM524234:MCP524234 MMI524234:MML524234 MWE524234:MWH524234 NGA524234:NGD524234 NPW524234:NPZ524234 NZS524234:NZV524234 OJO524234:OJR524234 OTK524234:OTN524234 PDG524234:PDJ524234 PNC524234:PNF524234 PWY524234:PXB524234 QGU524234:QGX524234 QQQ524234:QQT524234 RAM524234:RAP524234 RKI524234:RKL524234 RUE524234:RUH524234 SEA524234:SED524234 SNW524234:SNZ524234 SXS524234:SXV524234 THO524234:THR524234 TRK524234:TRN524234 UBG524234:UBJ524234 ULC524234:ULF524234 UUY524234:UVB524234 VEU524234:VEX524234 VOQ524234:VOT524234 VYM524234:VYP524234 WII524234:WIL524234 WSE524234:WSH524234 FS589770:FV589770 PO589770:PR589770 ZK589770:ZN589770 AJG589770:AJJ589770 ATC589770:ATF589770 BCY589770:BDB589770 BMU589770:BMX589770 BWQ589770:BWT589770 CGM589770:CGP589770 CQI589770:CQL589770 DAE589770:DAH589770 DKA589770:DKD589770 DTW589770:DTZ589770 EDS589770:EDV589770 ENO589770:ENR589770 EXK589770:EXN589770 FHG589770:FHJ589770 FRC589770:FRF589770 GAY589770:GBB589770 GKU589770:GKX589770 GUQ589770:GUT589770 HEM589770:HEP589770 HOI589770:HOL589770 HYE589770:HYH589770 IIA589770:IID589770 IRW589770:IRZ589770 JBS589770:JBV589770 JLO589770:JLR589770 JVK589770:JVN589770 KFG589770:KFJ589770 KPC589770:KPF589770 KYY589770:KZB589770 LIU589770:LIX589770 LSQ589770:LST589770 MCM589770:MCP589770 MMI589770:MML589770 MWE589770:MWH589770 NGA589770:NGD589770 NPW589770:NPZ589770 NZS589770:NZV589770 OJO589770:OJR589770 OTK589770:OTN589770 PDG589770:PDJ589770 PNC589770:PNF589770 PWY589770:PXB589770 QGU589770:QGX589770 QQQ589770:QQT589770 RAM589770:RAP589770 RKI589770:RKL589770 RUE589770:RUH589770 SEA589770:SED589770 SNW589770:SNZ589770 SXS589770:SXV589770 THO589770:THR589770 TRK589770:TRN589770 UBG589770:UBJ589770 ULC589770:ULF589770 UUY589770:UVB589770 VEU589770:VEX589770 VOQ589770:VOT589770 VYM589770:VYP589770 WII589770:WIL589770 WSE589770:WSH589770 FS655306:FV655306 PO655306:PR655306 ZK655306:ZN655306 AJG655306:AJJ655306 ATC655306:ATF655306 BCY655306:BDB655306 BMU655306:BMX655306 BWQ655306:BWT655306 CGM655306:CGP655306 CQI655306:CQL655306 DAE655306:DAH655306 DKA655306:DKD655306 DTW655306:DTZ655306 EDS655306:EDV655306 ENO655306:ENR655306 EXK655306:EXN655306 FHG655306:FHJ655306 FRC655306:FRF655306 GAY655306:GBB655306 GKU655306:GKX655306 GUQ655306:GUT655306 HEM655306:HEP655306 HOI655306:HOL655306 HYE655306:HYH655306 IIA655306:IID655306 IRW655306:IRZ655306 JBS655306:JBV655306 JLO655306:JLR655306 JVK655306:JVN655306 KFG655306:KFJ655306 KPC655306:KPF655306 KYY655306:KZB655306 LIU655306:LIX655306 LSQ655306:LST655306 MCM655306:MCP655306 MMI655306:MML655306 MWE655306:MWH655306 NGA655306:NGD655306 NPW655306:NPZ655306 NZS655306:NZV655306 OJO655306:OJR655306 OTK655306:OTN655306 PDG655306:PDJ655306 PNC655306:PNF655306 PWY655306:PXB655306 QGU655306:QGX655306 QQQ655306:QQT655306 RAM655306:RAP655306 RKI655306:RKL655306 RUE655306:RUH655306 SEA655306:SED655306 SNW655306:SNZ655306 SXS655306:SXV655306 THO655306:THR655306 TRK655306:TRN655306 UBG655306:UBJ655306 ULC655306:ULF655306 UUY655306:UVB655306 VEU655306:VEX655306 VOQ655306:VOT655306 VYM655306:VYP655306 WII655306:WIL655306 WSE655306:WSH655306 FS720842:FV720842 PO720842:PR720842 ZK720842:ZN720842 AJG720842:AJJ720842 ATC720842:ATF720842 BCY720842:BDB720842 BMU720842:BMX720842 BWQ720842:BWT720842 CGM720842:CGP720842 CQI720842:CQL720842 DAE720842:DAH720842 DKA720842:DKD720842 DTW720842:DTZ720842 EDS720842:EDV720842 ENO720842:ENR720842 EXK720842:EXN720842 FHG720842:FHJ720842 FRC720842:FRF720842 GAY720842:GBB720842 GKU720842:GKX720842 GUQ720842:GUT720842 HEM720842:HEP720842 HOI720842:HOL720842 HYE720842:HYH720842 IIA720842:IID720842 IRW720842:IRZ720842 JBS720842:JBV720842 JLO720842:JLR720842 JVK720842:JVN720842 KFG720842:KFJ720842 KPC720842:KPF720842 KYY720842:KZB720842 LIU720842:LIX720842 LSQ720842:LST720842 MCM720842:MCP720842 MMI720842:MML720842 MWE720842:MWH720842 NGA720842:NGD720842 NPW720842:NPZ720842 NZS720842:NZV720842 OJO720842:OJR720842 OTK720842:OTN720842 PDG720842:PDJ720842 PNC720842:PNF720842 PWY720842:PXB720842 QGU720842:QGX720842 QQQ720842:QQT720842 RAM720842:RAP720842 RKI720842:RKL720842 RUE720842:RUH720842 SEA720842:SED720842 SNW720842:SNZ720842 SXS720842:SXV720842 THO720842:THR720842 TRK720842:TRN720842 UBG720842:UBJ720842 ULC720842:ULF720842 UUY720842:UVB720842 VEU720842:VEX720842 VOQ720842:VOT720842 VYM720842:VYP720842 WII720842:WIL720842 WSE720842:WSH720842 FS786378:FV786378 PO786378:PR786378 ZK786378:ZN786378 AJG786378:AJJ786378 ATC786378:ATF786378 BCY786378:BDB786378 BMU786378:BMX786378 BWQ786378:BWT786378 CGM786378:CGP786378 CQI786378:CQL786378 DAE786378:DAH786378 DKA786378:DKD786378 DTW786378:DTZ786378 EDS786378:EDV786378 ENO786378:ENR786378 EXK786378:EXN786378 FHG786378:FHJ786378 FRC786378:FRF786378 GAY786378:GBB786378 GKU786378:GKX786378 GUQ786378:GUT786378 HEM786378:HEP786378 HOI786378:HOL786378 HYE786378:HYH786378 IIA786378:IID786378 IRW786378:IRZ786378 JBS786378:JBV786378 JLO786378:JLR786378 JVK786378:JVN786378 KFG786378:KFJ786378 KPC786378:KPF786378 KYY786378:KZB786378 LIU786378:LIX786378 LSQ786378:LST786378 MCM786378:MCP786378 MMI786378:MML786378 MWE786378:MWH786378 NGA786378:NGD786378 NPW786378:NPZ786378 NZS786378:NZV786378 OJO786378:OJR786378 OTK786378:OTN786378 PDG786378:PDJ786378 PNC786378:PNF786378 PWY786378:PXB786378 QGU786378:QGX786378 QQQ786378:QQT786378 RAM786378:RAP786378 RKI786378:RKL786378 RUE786378:RUH786378 SEA786378:SED786378 SNW786378:SNZ786378 SXS786378:SXV786378 THO786378:THR786378 TRK786378:TRN786378 UBG786378:UBJ786378 ULC786378:ULF786378 UUY786378:UVB786378 VEU786378:VEX786378 VOQ786378:VOT786378 VYM786378:VYP786378 WII786378:WIL786378 WSE786378:WSH786378 FS851914:FV851914 PO851914:PR851914 ZK851914:ZN851914 AJG851914:AJJ851914 ATC851914:ATF851914 BCY851914:BDB851914 BMU851914:BMX851914 BWQ851914:BWT851914 CGM851914:CGP851914 CQI851914:CQL851914 DAE851914:DAH851914 DKA851914:DKD851914 DTW851914:DTZ851914 EDS851914:EDV851914 ENO851914:ENR851914 EXK851914:EXN851914 FHG851914:FHJ851914 FRC851914:FRF851914 GAY851914:GBB851914 GKU851914:GKX851914 GUQ851914:GUT851914 HEM851914:HEP851914 HOI851914:HOL851914 HYE851914:HYH851914 IIA851914:IID851914 IRW851914:IRZ851914 JBS851914:JBV851914 JLO851914:JLR851914 JVK851914:JVN851914 KFG851914:KFJ851914 KPC851914:KPF851914 KYY851914:KZB851914 LIU851914:LIX851914 LSQ851914:LST851914 MCM851914:MCP851914 MMI851914:MML851914 MWE851914:MWH851914 NGA851914:NGD851914 NPW851914:NPZ851914 NZS851914:NZV851914 OJO851914:OJR851914 OTK851914:OTN851914 PDG851914:PDJ851914 PNC851914:PNF851914 PWY851914:PXB851914 QGU851914:QGX851914 QQQ851914:QQT851914 RAM851914:RAP851914 RKI851914:RKL851914 RUE851914:RUH851914 SEA851914:SED851914 SNW851914:SNZ851914 SXS851914:SXV851914 THO851914:THR851914 TRK851914:TRN851914 UBG851914:UBJ851914 ULC851914:ULF851914 UUY851914:UVB851914 VEU851914:VEX851914 VOQ851914:VOT851914 VYM851914:VYP851914 WII851914:WIL851914 WSE851914:WSH851914 FS917450:FV917450 PO917450:PR917450 ZK917450:ZN917450 AJG917450:AJJ917450 ATC917450:ATF917450 BCY917450:BDB917450 BMU917450:BMX917450 BWQ917450:BWT917450 CGM917450:CGP917450 CQI917450:CQL917450 DAE917450:DAH917450 DKA917450:DKD917450 DTW917450:DTZ917450 EDS917450:EDV917450 ENO917450:ENR917450 EXK917450:EXN917450 FHG917450:FHJ917450 FRC917450:FRF917450 GAY917450:GBB917450 GKU917450:GKX917450 GUQ917450:GUT917450 HEM917450:HEP917450 HOI917450:HOL917450 HYE917450:HYH917450 IIA917450:IID917450 IRW917450:IRZ917450 JBS917450:JBV917450 JLO917450:JLR917450 JVK917450:JVN917450 KFG917450:KFJ917450 KPC917450:KPF917450 KYY917450:KZB917450 LIU917450:LIX917450 LSQ917450:LST917450 MCM917450:MCP917450 MMI917450:MML917450 MWE917450:MWH917450 NGA917450:NGD917450 NPW917450:NPZ917450 NZS917450:NZV917450 OJO917450:OJR917450 OTK917450:OTN917450 PDG917450:PDJ917450 PNC917450:PNF917450 PWY917450:PXB917450 QGU917450:QGX917450 QQQ917450:QQT917450 RAM917450:RAP917450 RKI917450:RKL917450 RUE917450:RUH917450 SEA917450:SED917450 SNW917450:SNZ917450 SXS917450:SXV917450 THO917450:THR917450 TRK917450:TRN917450 UBG917450:UBJ917450 ULC917450:ULF917450 UUY917450:UVB917450 VEU917450:VEX917450 VOQ917450:VOT917450 VYM917450:VYP917450 WII917450:WIL917450 WSE917450:WSH917450 FS982986:FV982986 PO982986:PR982986 ZK982986:ZN982986 AJG982986:AJJ982986 ATC982986:ATF982986 BCY982986:BDB982986 BMU982986:BMX982986 BWQ982986:BWT982986 CGM982986:CGP982986 CQI982986:CQL982986 DAE982986:DAH982986 DKA982986:DKD982986 DTW982986:DTZ982986 EDS982986:EDV982986 ENO982986:ENR982986 EXK982986:EXN982986 FHG982986:FHJ982986 FRC982986:FRF982986 GAY982986:GBB982986 GKU982986:GKX982986 GUQ982986:GUT982986 HEM982986:HEP982986 HOI982986:HOL982986 HYE982986:HYH982986 IIA982986:IID982986 IRW982986:IRZ982986 JBS982986:JBV982986 JLO982986:JLR982986 JVK982986:JVN982986 KFG982986:KFJ982986 KPC982986:KPF982986 KYY982986:KZB982986 LIU982986:LIX982986 LSQ982986:LST982986 MCM982986:MCP982986 MMI982986:MML982986 MWE982986:MWH982986 NGA982986:NGD982986 NPW982986:NPZ982986 NZS982986:NZV982986 OJO982986:OJR982986 OTK982986:OTN982986 PDG982986:PDJ982986 PNC982986:PNF982986 PWY982986:PXB982986 QGU982986:QGX982986 QQQ982986:QQT982986 RAM982986:RAP982986 RKI982986:RKL982986 RUE982986:RUH982986 SEA982986:SED982986 SNW982986:SNZ982986 SXS982986:SXV982986 THO982986:THR982986 TRK982986:TRN982986 UBG982986:UBJ982986 ULC982986:ULF982986 UUY982986:UVB982986 VEU982986:VEX982986 VOQ982986:VOT982986 VYM982986:VYP982986 WII982986:WIL982986 WSE982986:WSH982986 FN982985:FQ982985 PJ982985:PM982985 ZF982985:ZI982985 AJB982985:AJE982985 ASX982985:ATA982985 BCT982985:BCW982985 BMP982985:BMS982985 BWL982985:BWO982985 CGH982985:CGK982985 CQD982985:CQG982985 CZZ982985:DAC982985 DJV982985:DJY982985 DTR982985:DTU982985 EDN982985:EDQ982985 ENJ982985:ENM982985 EXF982985:EXI982985 FHB982985:FHE982985 FQX982985:FRA982985 GAT982985:GAW982985 GKP982985:GKS982985 GUL982985:GUO982985 HEH982985:HEK982985 HOD982985:HOG982985 HXZ982985:HYC982985 IHV982985:IHY982985 IRR982985:IRU982985 JBN982985:JBQ982985 JLJ982985:JLM982985 JVF982985:JVI982985 KFB982985:KFE982985 KOX982985:KPA982985 KYT982985:KYW982985 LIP982985:LIS982985 LSL982985:LSO982985 MCH982985:MCK982985 MMD982985:MMG982985 MVZ982985:MWC982985 NFV982985:NFY982985 NPR982985:NPU982985 NZN982985:NZQ982985 OJJ982985:OJM982985 OTF982985:OTI982985 PDB982985:PDE982985 PMX982985:PNA982985 PWT982985:PWW982985 QGP982985:QGS982985 QQL982985:QQO982985 RAH982985:RAK982985 RKD982985:RKG982985 RTZ982985:RUC982985 SDV982985:SDY982985 SNR982985:SNU982985 SXN982985:SXQ982985 THJ982985:THM982985 TRF982985:TRI982985 UBB982985:UBE982985 UKX982985:ULA982985 UUT982985:UUW982985 VEP982985:VES982985 VOL982985:VOO982985 VYH982985:VYK982985 WID982985:WIG982985 WRZ982985:WSC982985 FN65481:FQ65481 PJ65481:PM65481 ZF65481:ZI65481 AJB65481:AJE65481 ASX65481:ATA65481 BCT65481:BCW65481 BMP65481:BMS65481 BWL65481:BWO65481 CGH65481:CGK65481 CQD65481:CQG65481 CZZ65481:DAC65481 DJV65481:DJY65481 DTR65481:DTU65481 EDN65481:EDQ65481 ENJ65481:ENM65481 EXF65481:EXI65481 FHB65481:FHE65481 FQX65481:FRA65481 GAT65481:GAW65481 GKP65481:GKS65481 GUL65481:GUO65481 HEH65481:HEK65481 HOD65481:HOG65481 HXZ65481:HYC65481 IHV65481:IHY65481 IRR65481:IRU65481 JBN65481:JBQ65481 JLJ65481:JLM65481 JVF65481:JVI65481 KFB65481:KFE65481 KOX65481:KPA65481 KYT65481:KYW65481 LIP65481:LIS65481 LSL65481:LSO65481 MCH65481:MCK65481 MMD65481:MMG65481 MVZ65481:MWC65481 NFV65481:NFY65481 NPR65481:NPU65481 NZN65481:NZQ65481 OJJ65481:OJM65481 OTF65481:OTI65481 PDB65481:PDE65481 PMX65481:PNA65481 PWT65481:PWW65481 QGP65481:QGS65481 QQL65481:QQO65481 RAH65481:RAK65481 RKD65481:RKG65481 RTZ65481:RUC65481 SDV65481:SDY65481 SNR65481:SNU65481 SXN65481:SXQ65481 THJ65481:THM65481 TRF65481:TRI65481 UBB65481:UBE65481 UKX65481:ULA65481 UUT65481:UUW65481 VEP65481:VES65481 VOL65481:VOO65481 VYH65481:VYK65481 WID65481:WIG65481 WRZ65481:WSC65481 FN131017:FQ131017 PJ131017:PM131017 ZF131017:ZI131017 AJB131017:AJE131017 ASX131017:ATA131017 BCT131017:BCW131017 BMP131017:BMS131017 BWL131017:BWO131017 CGH131017:CGK131017 CQD131017:CQG131017 CZZ131017:DAC131017 DJV131017:DJY131017 DTR131017:DTU131017 EDN131017:EDQ131017 ENJ131017:ENM131017 EXF131017:EXI131017 FHB131017:FHE131017 FQX131017:FRA131017 GAT131017:GAW131017 GKP131017:GKS131017 GUL131017:GUO131017 HEH131017:HEK131017 HOD131017:HOG131017 HXZ131017:HYC131017 IHV131017:IHY131017 IRR131017:IRU131017 JBN131017:JBQ131017 JLJ131017:JLM131017 JVF131017:JVI131017 KFB131017:KFE131017 KOX131017:KPA131017 KYT131017:KYW131017 LIP131017:LIS131017 LSL131017:LSO131017 MCH131017:MCK131017 MMD131017:MMG131017 MVZ131017:MWC131017 NFV131017:NFY131017 NPR131017:NPU131017 NZN131017:NZQ131017 OJJ131017:OJM131017 OTF131017:OTI131017 PDB131017:PDE131017 PMX131017:PNA131017 PWT131017:PWW131017 QGP131017:QGS131017 QQL131017:QQO131017 RAH131017:RAK131017 RKD131017:RKG131017 RTZ131017:RUC131017 SDV131017:SDY131017 SNR131017:SNU131017 SXN131017:SXQ131017 THJ131017:THM131017 TRF131017:TRI131017 UBB131017:UBE131017 UKX131017:ULA131017 UUT131017:UUW131017 VEP131017:VES131017 VOL131017:VOO131017 VYH131017:VYK131017 WID131017:WIG131017 WRZ131017:WSC131017 FN196553:FQ196553 PJ196553:PM196553 ZF196553:ZI196553 AJB196553:AJE196553 ASX196553:ATA196553 BCT196553:BCW196553 BMP196553:BMS196553 BWL196553:BWO196553 CGH196553:CGK196553 CQD196553:CQG196553 CZZ196553:DAC196553 DJV196553:DJY196553 DTR196553:DTU196553 EDN196553:EDQ196553 ENJ196553:ENM196553 EXF196553:EXI196553 FHB196553:FHE196553 FQX196553:FRA196553 GAT196553:GAW196553 GKP196553:GKS196553 GUL196553:GUO196553 HEH196553:HEK196553 HOD196553:HOG196553 HXZ196553:HYC196553 IHV196553:IHY196553 IRR196553:IRU196553 JBN196553:JBQ196553 JLJ196553:JLM196553 JVF196553:JVI196553 KFB196553:KFE196553 KOX196553:KPA196553 KYT196553:KYW196553 LIP196553:LIS196553 LSL196553:LSO196553 MCH196553:MCK196553 MMD196553:MMG196553 MVZ196553:MWC196553 NFV196553:NFY196553 NPR196553:NPU196553 NZN196553:NZQ196553 OJJ196553:OJM196553 OTF196553:OTI196553 PDB196553:PDE196553 PMX196553:PNA196553 PWT196553:PWW196553 QGP196553:QGS196553 QQL196553:QQO196553 RAH196553:RAK196553 RKD196553:RKG196553 RTZ196553:RUC196553 SDV196553:SDY196553 SNR196553:SNU196553 SXN196553:SXQ196553 THJ196553:THM196553 TRF196553:TRI196553 UBB196553:UBE196553 UKX196553:ULA196553 UUT196553:UUW196553 VEP196553:VES196553 VOL196553:VOO196553 VYH196553:VYK196553 WID196553:WIG196553 WRZ196553:WSC196553 FN262089:FQ262089 PJ262089:PM262089 ZF262089:ZI262089 AJB262089:AJE262089 ASX262089:ATA262089 BCT262089:BCW262089 BMP262089:BMS262089 BWL262089:BWO262089 CGH262089:CGK262089 CQD262089:CQG262089 CZZ262089:DAC262089 DJV262089:DJY262089 DTR262089:DTU262089 EDN262089:EDQ262089 ENJ262089:ENM262089 EXF262089:EXI262089 FHB262089:FHE262089 FQX262089:FRA262089 GAT262089:GAW262089 GKP262089:GKS262089 GUL262089:GUO262089 HEH262089:HEK262089 HOD262089:HOG262089 HXZ262089:HYC262089 IHV262089:IHY262089 IRR262089:IRU262089 JBN262089:JBQ262089 JLJ262089:JLM262089 JVF262089:JVI262089 KFB262089:KFE262089 KOX262089:KPA262089 KYT262089:KYW262089 LIP262089:LIS262089 LSL262089:LSO262089 MCH262089:MCK262089 MMD262089:MMG262089 MVZ262089:MWC262089 NFV262089:NFY262089 NPR262089:NPU262089 NZN262089:NZQ262089 OJJ262089:OJM262089 OTF262089:OTI262089 PDB262089:PDE262089 PMX262089:PNA262089 PWT262089:PWW262089 QGP262089:QGS262089 QQL262089:QQO262089 RAH262089:RAK262089 RKD262089:RKG262089 RTZ262089:RUC262089 SDV262089:SDY262089 SNR262089:SNU262089 SXN262089:SXQ262089 THJ262089:THM262089 TRF262089:TRI262089 UBB262089:UBE262089 UKX262089:ULA262089 UUT262089:UUW262089 VEP262089:VES262089 VOL262089:VOO262089 VYH262089:VYK262089 WID262089:WIG262089 WRZ262089:WSC262089 FN327625:FQ327625 PJ327625:PM327625 ZF327625:ZI327625 AJB327625:AJE327625 ASX327625:ATA327625 BCT327625:BCW327625 BMP327625:BMS327625 BWL327625:BWO327625 CGH327625:CGK327625 CQD327625:CQG327625 CZZ327625:DAC327625 DJV327625:DJY327625 DTR327625:DTU327625 EDN327625:EDQ327625 ENJ327625:ENM327625 EXF327625:EXI327625 FHB327625:FHE327625 FQX327625:FRA327625 GAT327625:GAW327625 GKP327625:GKS327625 GUL327625:GUO327625 HEH327625:HEK327625 HOD327625:HOG327625 HXZ327625:HYC327625 IHV327625:IHY327625 IRR327625:IRU327625 JBN327625:JBQ327625 JLJ327625:JLM327625 JVF327625:JVI327625 KFB327625:KFE327625 KOX327625:KPA327625 KYT327625:KYW327625 LIP327625:LIS327625 LSL327625:LSO327625 MCH327625:MCK327625 MMD327625:MMG327625 MVZ327625:MWC327625 NFV327625:NFY327625 NPR327625:NPU327625 NZN327625:NZQ327625 OJJ327625:OJM327625 OTF327625:OTI327625 PDB327625:PDE327625 PMX327625:PNA327625 PWT327625:PWW327625 QGP327625:QGS327625 QQL327625:QQO327625 RAH327625:RAK327625 RKD327625:RKG327625 RTZ327625:RUC327625 SDV327625:SDY327625 SNR327625:SNU327625 SXN327625:SXQ327625 THJ327625:THM327625 TRF327625:TRI327625 UBB327625:UBE327625 UKX327625:ULA327625 UUT327625:UUW327625 VEP327625:VES327625 VOL327625:VOO327625 VYH327625:VYK327625 WID327625:WIG327625 WRZ327625:WSC327625 FN393161:FQ393161 PJ393161:PM393161 ZF393161:ZI393161 AJB393161:AJE393161 ASX393161:ATA393161 BCT393161:BCW393161 BMP393161:BMS393161 BWL393161:BWO393161 CGH393161:CGK393161 CQD393161:CQG393161 CZZ393161:DAC393161 DJV393161:DJY393161 DTR393161:DTU393161 EDN393161:EDQ393161 ENJ393161:ENM393161 EXF393161:EXI393161 FHB393161:FHE393161 FQX393161:FRA393161 GAT393161:GAW393161 GKP393161:GKS393161 GUL393161:GUO393161 HEH393161:HEK393161 HOD393161:HOG393161 HXZ393161:HYC393161 IHV393161:IHY393161 IRR393161:IRU393161 JBN393161:JBQ393161 JLJ393161:JLM393161 JVF393161:JVI393161 KFB393161:KFE393161 KOX393161:KPA393161 KYT393161:KYW393161 LIP393161:LIS393161 LSL393161:LSO393161 MCH393161:MCK393161 MMD393161:MMG393161 MVZ393161:MWC393161 NFV393161:NFY393161 NPR393161:NPU393161 NZN393161:NZQ393161 OJJ393161:OJM393161 OTF393161:OTI393161 PDB393161:PDE393161 PMX393161:PNA393161 PWT393161:PWW393161 QGP393161:QGS393161 QQL393161:QQO393161 RAH393161:RAK393161 RKD393161:RKG393161 RTZ393161:RUC393161 SDV393161:SDY393161 SNR393161:SNU393161 SXN393161:SXQ393161 THJ393161:THM393161 TRF393161:TRI393161 UBB393161:UBE393161 UKX393161:ULA393161 UUT393161:UUW393161 VEP393161:VES393161 VOL393161:VOO393161 VYH393161:VYK393161 WID393161:WIG393161 WRZ393161:WSC393161 FN458697:FQ458697 PJ458697:PM458697 ZF458697:ZI458697 AJB458697:AJE458697 ASX458697:ATA458697 BCT458697:BCW458697 BMP458697:BMS458697 BWL458697:BWO458697 CGH458697:CGK458697 CQD458697:CQG458697 CZZ458697:DAC458697 DJV458697:DJY458697 DTR458697:DTU458697 EDN458697:EDQ458697 ENJ458697:ENM458697 EXF458697:EXI458697 FHB458697:FHE458697 FQX458697:FRA458697 GAT458697:GAW458697 GKP458697:GKS458697 GUL458697:GUO458697 HEH458697:HEK458697 HOD458697:HOG458697 HXZ458697:HYC458697 IHV458697:IHY458697 IRR458697:IRU458697 JBN458697:JBQ458697 JLJ458697:JLM458697 JVF458697:JVI458697 KFB458697:KFE458697 KOX458697:KPA458697 KYT458697:KYW458697 LIP458697:LIS458697 LSL458697:LSO458697 MCH458697:MCK458697 MMD458697:MMG458697 MVZ458697:MWC458697 NFV458697:NFY458697 NPR458697:NPU458697 NZN458697:NZQ458697 OJJ458697:OJM458697 OTF458697:OTI458697 PDB458697:PDE458697 PMX458697:PNA458697 PWT458697:PWW458697 QGP458697:QGS458697 QQL458697:QQO458697 RAH458697:RAK458697 RKD458697:RKG458697 RTZ458697:RUC458697 SDV458697:SDY458697 SNR458697:SNU458697 SXN458697:SXQ458697 THJ458697:THM458697 TRF458697:TRI458697 UBB458697:UBE458697 UKX458697:ULA458697 UUT458697:UUW458697 VEP458697:VES458697 VOL458697:VOO458697 VYH458697:VYK458697 WID458697:WIG458697 WRZ458697:WSC458697 FN524233:FQ524233 PJ524233:PM524233 ZF524233:ZI524233 AJB524233:AJE524233 ASX524233:ATA524233 BCT524233:BCW524233 BMP524233:BMS524233 BWL524233:BWO524233 CGH524233:CGK524233 CQD524233:CQG524233 CZZ524233:DAC524233 DJV524233:DJY524233 DTR524233:DTU524233 EDN524233:EDQ524233 ENJ524233:ENM524233 EXF524233:EXI524233 FHB524233:FHE524233 FQX524233:FRA524233 GAT524233:GAW524233 GKP524233:GKS524233 GUL524233:GUO524233 HEH524233:HEK524233 HOD524233:HOG524233 HXZ524233:HYC524233 IHV524233:IHY524233 IRR524233:IRU524233 JBN524233:JBQ524233 JLJ524233:JLM524233 JVF524233:JVI524233 KFB524233:KFE524233 KOX524233:KPA524233 KYT524233:KYW524233 LIP524233:LIS524233 LSL524233:LSO524233 MCH524233:MCK524233 MMD524233:MMG524233 MVZ524233:MWC524233 NFV524233:NFY524233 NPR524233:NPU524233 NZN524233:NZQ524233 OJJ524233:OJM524233 OTF524233:OTI524233 PDB524233:PDE524233 PMX524233:PNA524233 PWT524233:PWW524233 QGP524233:QGS524233 QQL524233:QQO524233 RAH524233:RAK524233 RKD524233:RKG524233 RTZ524233:RUC524233 SDV524233:SDY524233 SNR524233:SNU524233 SXN524233:SXQ524233 THJ524233:THM524233 TRF524233:TRI524233 UBB524233:UBE524233 UKX524233:ULA524233 UUT524233:UUW524233 VEP524233:VES524233 VOL524233:VOO524233 VYH524233:VYK524233 WID524233:WIG524233 WRZ524233:WSC524233 FN589769:FQ589769 PJ589769:PM589769 ZF589769:ZI589769 AJB589769:AJE589769 ASX589769:ATA589769 BCT589769:BCW589769 BMP589769:BMS589769 BWL589769:BWO589769 CGH589769:CGK589769 CQD589769:CQG589769 CZZ589769:DAC589769 DJV589769:DJY589769 DTR589769:DTU589769 EDN589769:EDQ589769 ENJ589769:ENM589769 EXF589769:EXI589769 FHB589769:FHE589769 FQX589769:FRA589769 GAT589769:GAW589769 GKP589769:GKS589769 GUL589769:GUO589769 HEH589769:HEK589769 HOD589769:HOG589769 HXZ589769:HYC589769 IHV589769:IHY589769 IRR589769:IRU589769 JBN589769:JBQ589769 JLJ589769:JLM589769 JVF589769:JVI589769 KFB589769:KFE589769 KOX589769:KPA589769 KYT589769:KYW589769 LIP589769:LIS589769 LSL589769:LSO589769 MCH589769:MCK589769 MMD589769:MMG589769 MVZ589769:MWC589769 NFV589769:NFY589769 NPR589769:NPU589769 NZN589769:NZQ589769 OJJ589769:OJM589769 OTF589769:OTI589769 PDB589769:PDE589769 PMX589769:PNA589769 PWT589769:PWW589769 QGP589769:QGS589769 QQL589769:QQO589769 RAH589769:RAK589769 RKD589769:RKG589769 RTZ589769:RUC589769 SDV589769:SDY589769 SNR589769:SNU589769 SXN589769:SXQ589769 THJ589769:THM589769 TRF589769:TRI589769 UBB589769:UBE589769 UKX589769:ULA589769 UUT589769:UUW589769 VEP589769:VES589769 VOL589769:VOO589769 VYH589769:VYK589769 WID589769:WIG589769 WRZ589769:WSC589769 FN655305:FQ655305 PJ655305:PM655305 ZF655305:ZI655305 AJB655305:AJE655305 ASX655305:ATA655305 BCT655305:BCW655305 BMP655305:BMS655305 BWL655305:BWO655305 CGH655305:CGK655305 CQD655305:CQG655305 CZZ655305:DAC655305 DJV655305:DJY655305 DTR655305:DTU655305 EDN655305:EDQ655305 ENJ655305:ENM655305 EXF655305:EXI655305 FHB655305:FHE655305 FQX655305:FRA655305 GAT655305:GAW655305 GKP655305:GKS655305 GUL655305:GUO655305 HEH655305:HEK655305 HOD655305:HOG655305 HXZ655305:HYC655305 IHV655305:IHY655305 IRR655305:IRU655305 JBN655305:JBQ655305 JLJ655305:JLM655305 JVF655305:JVI655305 KFB655305:KFE655305 KOX655305:KPA655305 KYT655305:KYW655305 LIP655305:LIS655305 LSL655305:LSO655305 MCH655305:MCK655305 MMD655305:MMG655305 MVZ655305:MWC655305 NFV655305:NFY655305 NPR655305:NPU655305 NZN655305:NZQ655305 OJJ655305:OJM655305 OTF655305:OTI655305 PDB655305:PDE655305 PMX655305:PNA655305 PWT655305:PWW655305 QGP655305:QGS655305 QQL655305:QQO655305 RAH655305:RAK655305 RKD655305:RKG655305 RTZ655305:RUC655305 SDV655305:SDY655305 SNR655305:SNU655305 SXN655305:SXQ655305 THJ655305:THM655305 TRF655305:TRI655305 UBB655305:UBE655305 UKX655305:ULA655305 UUT655305:UUW655305 VEP655305:VES655305 VOL655305:VOO655305 VYH655305:VYK655305 WID655305:WIG655305 WRZ655305:WSC655305 FN720841:FQ720841 PJ720841:PM720841 ZF720841:ZI720841 AJB720841:AJE720841 ASX720841:ATA720841 BCT720841:BCW720841 BMP720841:BMS720841 BWL720841:BWO720841 CGH720841:CGK720841 CQD720841:CQG720841 CZZ720841:DAC720841 DJV720841:DJY720841 DTR720841:DTU720841 EDN720841:EDQ720841 ENJ720841:ENM720841 EXF720841:EXI720841 FHB720841:FHE720841 FQX720841:FRA720841 GAT720841:GAW720841 GKP720841:GKS720841 GUL720841:GUO720841 HEH720841:HEK720841 HOD720841:HOG720841 HXZ720841:HYC720841 IHV720841:IHY720841 IRR720841:IRU720841 JBN720841:JBQ720841 JLJ720841:JLM720841 JVF720841:JVI720841 KFB720841:KFE720841 KOX720841:KPA720841 KYT720841:KYW720841 LIP720841:LIS720841 LSL720841:LSO720841 MCH720841:MCK720841 MMD720841:MMG720841 MVZ720841:MWC720841 NFV720841:NFY720841 NPR720841:NPU720841 NZN720841:NZQ720841 OJJ720841:OJM720841 OTF720841:OTI720841 PDB720841:PDE720841 PMX720841:PNA720841 PWT720841:PWW720841 QGP720841:QGS720841 QQL720841:QQO720841 RAH720841:RAK720841 RKD720841:RKG720841 RTZ720841:RUC720841 SDV720841:SDY720841 SNR720841:SNU720841 SXN720841:SXQ720841 THJ720841:THM720841 TRF720841:TRI720841 UBB720841:UBE720841 UKX720841:ULA720841 UUT720841:UUW720841 VEP720841:VES720841 VOL720841:VOO720841 VYH720841:VYK720841 WID720841:WIG720841 WRZ720841:WSC720841 FN786377:FQ786377 PJ786377:PM786377 ZF786377:ZI786377 AJB786377:AJE786377 ASX786377:ATA786377 BCT786377:BCW786377 BMP786377:BMS786377 BWL786377:BWO786377 CGH786377:CGK786377 CQD786377:CQG786377 CZZ786377:DAC786377 DJV786377:DJY786377 DTR786377:DTU786377 EDN786377:EDQ786377 ENJ786377:ENM786377 EXF786377:EXI786377 FHB786377:FHE786377 FQX786377:FRA786377 GAT786377:GAW786377 GKP786377:GKS786377 GUL786377:GUO786377 HEH786377:HEK786377 HOD786377:HOG786377 HXZ786377:HYC786377 IHV786377:IHY786377 IRR786377:IRU786377 JBN786377:JBQ786377 JLJ786377:JLM786377 JVF786377:JVI786377 KFB786377:KFE786377 KOX786377:KPA786377 KYT786377:KYW786377 LIP786377:LIS786377 LSL786377:LSO786377 MCH786377:MCK786377 MMD786377:MMG786377 MVZ786377:MWC786377 NFV786377:NFY786377 NPR786377:NPU786377 NZN786377:NZQ786377 OJJ786377:OJM786377 OTF786377:OTI786377 PDB786377:PDE786377 PMX786377:PNA786377 PWT786377:PWW786377 QGP786377:QGS786377 QQL786377:QQO786377 RAH786377:RAK786377 RKD786377:RKG786377 RTZ786377:RUC786377 SDV786377:SDY786377 SNR786377:SNU786377 SXN786377:SXQ786377 THJ786377:THM786377 TRF786377:TRI786377 UBB786377:UBE786377 UKX786377:ULA786377 UUT786377:UUW786377 VEP786377:VES786377 VOL786377:VOO786377 VYH786377:VYK786377 WID786377:WIG786377 WRZ786377:WSC786377 FN851913:FQ851913 PJ851913:PM851913 ZF851913:ZI851913 AJB851913:AJE851913 ASX851913:ATA851913 BCT851913:BCW851913 BMP851913:BMS851913 BWL851913:BWO851913 CGH851913:CGK851913 CQD851913:CQG851913 CZZ851913:DAC851913 DJV851913:DJY851913 DTR851913:DTU851913 EDN851913:EDQ851913 ENJ851913:ENM851913 EXF851913:EXI851913 FHB851913:FHE851913 FQX851913:FRA851913 GAT851913:GAW851913 GKP851913:GKS851913 GUL851913:GUO851913 HEH851913:HEK851913 HOD851913:HOG851913 HXZ851913:HYC851913 IHV851913:IHY851913 IRR851913:IRU851913 JBN851913:JBQ851913 JLJ851913:JLM851913 JVF851913:JVI851913 KFB851913:KFE851913 KOX851913:KPA851913 KYT851913:KYW851913 LIP851913:LIS851913 LSL851913:LSO851913 MCH851913:MCK851913 MMD851913:MMG851913 MVZ851913:MWC851913 NFV851913:NFY851913 NPR851913:NPU851913 NZN851913:NZQ851913 OJJ851913:OJM851913 OTF851913:OTI851913 PDB851913:PDE851913 PMX851913:PNA851913 PWT851913:PWW851913 QGP851913:QGS851913 QQL851913:QQO851913 RAH851913:RAK851913 RKD851913:RKG851913 RTZ851913:RUC851913 SDV851913:SDY851913 SNR851913:SNU851913 SXN851913:SXQ851913 THJ851913:THM851913 TRF851913:TRI851913 UBB851913:UBE851913 UKX851913:ULA851913 UUT851913:UUW851913 VEP851913:VES851913 VOL851913:VOO851913 VYH851913:VYK851913 WID851913:WIG851913 WRZ851913:WSC851913 FN917449:FQ917449 PJ917449:PM917449 ZF917449:ZI917449 AJB917449:AJE917449 ASX917449:ATA917449 BCT917449:BCW917449 BMP917449:BMS917449 BWL917449:BWO917449 CGH917449:CGK917449 CQD917449:CQG917449 CZZ917449:DAC917449 DJV917449:DJY917449 DTR917449:DTU917449 EDN917449:EDQ917449 ENJ917449:ENM917449 EXF917449:EXI917449 FHB917449:FHE917449 FQX917449:FRA917449 GAT917449:GAW917449 GKP917449:GKS917449 GUL917449:GUO917449 HEH917449:HEK917449 HOD917449:HOG917449 HXZ917449:HYC917449 IHV917449:IHY917449 IRR917449:IRU917449 JBN917449:JBQ917449 JLJ917449:JLM917449 JVF917449:JVI917449 KFB917449:KFE917449 KOX917449:KPA917449 KYT917449:KYW917449 LIP917449:LIS917449 LSL917449:LSO917449 MCH917449:MCK917449 MMD917449:MMG917449 MVZ917449:MWC917449 NFV917449:NFY917449 NPR917449:NPU917449 NZN917449:NZQ917449 OJJ917449:OJM917449 OTF917449:OTI917449 PDB917449:PDE917449 PMX917449:PNA917449 PWT917449:PWW917449 QGP917449:QGS917449 QQL917449:QQO917449 RAH917449:RAK917449 RKD917449:RKG917449 RTZ917449:RUC917449 SDV917449:SDY917449 SNR917449:SNU917449 SXN917449:SXQ917449 THJ917449:THM917449 TRF917449:TRI917449 UBB917449:UBE917449 UKX917449:ULA917449 UUT917449:UUW917449 VEP917449:VES917449 VOL917449:VOO917449 VYH917449:VYK917449 WID917449:WIG917449 WRZ917449:WSC917449" xr:uid="{E6B354DD-799D-4BB1-AA82-5BEB1A4B5F7E}">
+      <formula1>"○, ○（オンライン処理設計書なし）"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
@@ -4501,1894 +7847,1894 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="51" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="66" t="s">
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="51" t="s">
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="70" t="s">
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
-      <c r="AD1" s="70"/>
-      <c r="AE1" s="70"/>
-      <c r="AF1" s="70"/>
-      <c r="AG1" s="70"/>
-      <c r="AH1" s="70"/>
-      <c r="AI1" s="70"/>
-      <c r="AJ1" s="70"/>
-      <c r="AK1" s="55" t="s">
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="56" t="s">
+      <c r="AL1" s="64"/>
+      <c r="AM1" s="64"/>
+      <c r="AN1" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="AO1" s="56"/>
-      <c r="AP1" s="56"/>
-      <c r="AQ1" s="55" t="s">
+      <c r="AO1" s="65"/>
+      <c r="AP1" s="65"/>
+      <c r="AQ1" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="55"/>
-      <c r="AS1" s="55"/>
-      <c r="AT1" s="58">
+      <c r="AR1" s="64"/>
+      <c r="AS1" s="64"/>
+      <c r="AT1" s="67">
         <f>AL7</f>
-        <v>46188</v>
-      </c>
-      <c r="AU1" s="58"/>
-      <c r="AV1" s="58"/>
-      <c r="AW1" s="58"/>
-      <c r="AX1" s="47" t="s">
+        <v>46189</v>
+      </c>
+      <c r="AU1" s="67"/>
+      <c r="AV1" s="67"/>
+      <c r="AW1" s="67"/>
+      <c r="AX1" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="48"/>
-      <c r="AZ1" s="48"/>
-      <c r="BA1" s="49"/>
+      <c r="AY1" s="57"/>
+      <c r="AZ1" s="57"/>
+      <c r="BA1" s="58"/>
     </row>
     <row r="2" spans="1:53">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="52" t="s">
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="70"/>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="70"/>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="55" t="s">
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="79"/>
+      <c r="AG2" s="79"/>
+      <c r="AH2" s="79"/>
+      <c r="AI2" s="79"/>
+      <c r="AJ2" s="79"/>
+      <c r="AK2" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="56" t="s">
+      <c r="AL2" s="64"/>
+      <c r="AM2" s="64"/>
+      <c r="AN2" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="AO2" s="56"/>
-      <c r="AP2" s="56"/>
-      <c r="AQ2" s="55" t="s">
+      <c r="AO2" s="65"/>
+      <c r="AP2" s="65"/>
+      <c r="AQ2" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="58">
-        <v>46185</v>
-      </c>
-      <c r="AU2" s="58"/>
-      <c r="AV2" s="58"/>
-      <c r="AW2" s="58"/>
-      <c r="AX2" s="59" t="s">
+      <c r="AR2" s="64"/>
+      <c r="AS2" s="64"/>
+      <c r="AT2" s="67">
+        <v>46189</v>
+      </c>
+      <c r="AU2" s="67"/>
+      <c r="AV2" s="67"/>
+      <c r="AW2" s="67"/>
+      <c r="AX2" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="AY2" s="60"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="61"/>
+      <c r="AY2" s="69"/>
+      <c r="AZ2" s="69"/>
+      <c r="BA2" s="70"/>
     </row>
     <row r="3" spans="1:53" ht="12" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="51" t="s">
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="66"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="66"/>
-      <c r="W3" s="66"/>
-      <c r="X3" s="51" t="s">
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="67" t="s">
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="67"/>
-      <c r="AG3" s="67"/>
-      <c r="AH3" s="67"/>
-      <c r="AI3" s="67"/>
-      <c r="AJ3" s="67"/>
-      <c r="AK3" s="67"/>
-      <c r="AL3" s="67"/>
-      <c r="AM3" s="67"/>
-      <c r="AN3" s="67"/>
-      <c r="AO3" s="67"/>
-      <c r="AP3" s="67"/>
-      <c r="AQ3" s="55" t="s">
+      <c r="AB3" s="76"/>
+      <c r="AC3" s="76"/>
+      <c r="AD3" s="76"/>
+      <c r="AE3" s="76"/>
+      <c r="AF3" s="76"/>
+      <c r="AG3" s="76"/>
+      <c r="AH3" s="76"/>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="76"/>
+      <c r="AK3" s="76"/>
+      <c r="AL3" s="76"/>
+      <c r="AM3" s="76"/>
+      <c r="AN3" s="76"/>
+      <c r="AO3" s="76"/>
+      <c r="AP3" s="76"/>
+      <c r="AQ3" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="55"/>
-      <c r="AS3" s="55"/>
-      <c r="AT3" s="71" t="str">
+      <c r="AR3" s="64"/>
+      <c r="AS3" s="64"/>
+      <c r="AT3" s="80" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
         <v>dr1.0</v>
       </c>
-      <c r="AU3" s="71"/>
-      <c r="AV3" s="71"/>
-      <c r="AW3" s="71"/>
-      <c r="AX3" s="62"/>
-      <c r="AY3" s="63"/>
-      <c r="AZ3" s="63"/>
-      <c r="BA3" s="64"/>
+      <c r="AU3" s="80"/>
+      <c r="AV3" s="80"/>
+      <c r="AW3" s="80"/>
+      <c r="AX3" s="71"/>
+      <c r="AY3" s="72"/>
+      <c r="AZ3" s="72"/>
+      <c r="BA3" s="73"/>
     </row>
     <row r="4" spans="1:53" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:53" ht="14">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="69"/>
-      <c r="W5" s="69"/>
-      <c r="X5" s="69"/>
-      <c r="Y5" s="69"/>
-      <c r="Z5" s="69"/>
-      <c r="AA5" s="69"/>
-      <c r="AB5" s="69"/>
-      <c r="AC5" s="69"/>
-      <c r="AD5" s="69"/>
-      <c r="AE5" s="69"/>
-      <c r="AF5" s="69"/>
-      <c r="AG5" s="69"/>
-      <c r="AH5" s="69"/>
-      <c r="AI5" s="69"/>
-      <c r="AJ5" s="69"/>
-      <c r="AK5" s="69"/>
-      <c r="AL5" s="69"/>
-      <c r="AM5" s="69"/>
-      <c r="AN5" s="69"/>
-      <c r="AO5" s="69"/>
-      <c r="AP5" s="69"/>
-      <c r="AQ5" s="69"/>
-      <c r="AR5" s="69"/>
-      <c r="AS5" s="69"/>
-      <c r="AT5" s="69"/>
-      <c r="AU5" s="69"/>
-      <c r="AV5" s="69"/>
-      <c r="AW5" s="69"/>
-      <c r="AX5" s="69"/>
-      <c r="AY5" s="69"/>
-      <c r="AZ5" s="69"/>
-      <c r="BA5" s="69"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
+      <c r="W5" s="78"/>
+      <c r="X5" s="78"/>
+      <c r="Y5" s="78"/>
+      <c r="Z5" s="78"/>
+      <c r="AA5" s="78"/>
+      <c r="AB5" s="78"/>
+      <c r="AC5" s="78"/>
+      <c r="AD5" s="78"/>
+      <c r="AE5" s="78"/>
+      <c r="AF5" s="78"/>
+      <c r="AG5" s="78"/>
+      <c r="AH5" s="78"/>
+      <c r="AI5" s="78"/>
+      <c r="AJ5" s="78"/>
+      <c r="AK5" s="78"/>
+      <c r="AL5" s="78"/>
+      <c r="AM5" s="78"/>
+      <c r="AN5" s="78"/>
+      <c r="AO5" s="78"/>
+      <c r="AP5" s="78"/>
+      <c r="AQ5" s="78"/>
+      <c r="AR5" s="78"/>
+      <c r="AS5" s="78"/>
+      <c r="AT5" s="78"/>
+      <c r="AU5" s="78"/>
+      <c r="AV5" s="78"/>
+      <c r="AW5" s="78"/>
+      <c r="AX5" s="78"/>
+      <c r="AY5" s="78"/>
+      <c r="AZ5" s="78"/>
+      <c r="BA5" s="78"/>
     </row>
     <row r="6" spans="1:53">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="57" t="s">
+      <c r="B6" s="82"/>
+      <c r="C6" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57" t="s">
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="57"/>
-      <c r="X6" s="57"/>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="57"/>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="57"/>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="57"/>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="57"/>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="57"/>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="57"/>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="57" t="s">
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66"/>
+      <c r="U6" s="66"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="66"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="66"/>
+      <c r="Z6" s="66"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="AM6" s="57"/>
-      <c r="AN6" s="57"/>
-      <c r="AO6" s="57"/>
-      <c r="AP6" s="57" t="s">
+      <c r="AM6" s="66"/>
+      <c r="AN6" s="66"/>
+      <c r="AO6" s="66"/>
+      <c r="AP6" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="AQ6" s="57"/>
-      <c r="AR6" s="57"/>
-      <c r="AS6" s="57" t="s">
+      <c r="AQ6" s="66"/>
+      <c r="AR6" s="66"/>
+      <c r="AS6" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="AT6" s="57"/>
-      <c r="AU6" s="57"/>
-      <c r="AV6" s="57" t="s">
+      <c r="AT6" s="66"/>
+      <c r="AU6" s="66"/>
+      <c r="AV6" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="AW6" s="57"/>
-      <c r="AX6" s="57"/>
-      <c r="AY6" s="57"/>
-      <c r="AZ6" s="57"/>
-      <c r="BA6" s="57"/>
+      <c r="AW6" s="66"/>
+      <c r="AX6" s="66"/>
+      <c r="AY6" s="66"/>
+      <c r="AZ6" s="66"/>
+      <c r="BA6" s="66"/>
     </row>
     <row r="7" spans="1:53">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="34">
-        <v>46188</v>
-      </c>
-      <c r="AM7" s="35"/>
-      <c r="AN7" s="35"/>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="30" t="s">
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="39"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="39"/>
+      <c r="AE7" s="39"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="39"/>
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="39"/>
+      <c r="AJ7" s="39"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="43">
+        <v>46189</v>
+      </c>
+      <c r="AM7" s="44"/>
+      <c r="AN7" s="44"/>
+      <c r="AO7" s="44"/>
+      <c r="AP7" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
+      <c r="AQ7" s="39"/>
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="39"/>
+      <c r="AT7" s="39"/>
+      <c r="AU7" s="39"/>
+      <c r="AV7" s="39"/>
+      <c r="AW7" s="39"/>
+      <c r="AX7" s="39"/>
+      <c r="AY7" s="39"/>
+      <c r="AZ7" s="39"/>
+      <c r="BA7" s="39"/>
     </row>
     <row r="8" spans="1:53" ht="44.5" customHeight="1">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="42"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="42"/>
-      <c r="W8" s="42"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="42"/>
-      <c r="Z8" s="42"/>
-      <c r="AA8" s="42"/>
-      <c r="AB8" s="42"/>
-      <c r="AC8" s="42"/>
-      <c r="AD8" s="42"/>
-      <c r="AE8" s="42"/>
-      <c r="AF8" s="42"/>
-      <c r="AG8" s="42"/>
-      <c r="AH8" s="42"/>
-      <c r="AI8" s="42"/>
-      <c r="AJ8" s="42"/>
-      <c r="AK8" s="43"/>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="30"/>
-      <c r="AR8" s="30"/>
-      <c r="AS8" s="30"/>
-      <c r="AT8" s="30"/>
-      <c r="AU8" s="30"/>
-      <c r="AV8" s="30"/>
-      <c r="AW8" s="30"/>
-      <c r="AX8" s="30"/>
-      <c r="AY8" s="30"/>
-      <c r="AZ8" s="30"/>
-      <c r="BA8" s="30"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="51"/>
+      <c r="AC8" s="51"/>
+      <c r="AD8" s="51"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="51"/>
+      <c r="AH8" s="51"/>
+      <c r="AI8" s="51"/>
+      <c r="AJ8" s="51"/>
+      <c r="AK8" s="52"/>
+      <c r="AL8" s="45"/>
+      <c r="AM8" s="46"/>
+      <c r="AN8" s="46"/>
+      <c r="AO8" s="47"/>
+      <c r="AP8" s="39"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="39"/>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="39"/>
+      <c r="AZ8" s="39"/>
+      <c r="BA8" s="39"/>
     </row>
     <row r="9" spans="1:53" ht="23.5" customHeight="1">
-      <c r="A9" s="44"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="42"/>
-      <c r="W9" s="42"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="42"/>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="42"/>
-      <c r="AB9" s="42"/>
-      <c r="AC9" s="42"/>
-      <c r="AD9" s="42"/>
-      <c r="AE9" s="42"/>
-      <c r="AF9" s="42"/>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="42"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="42"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="38"/>
-      <c r="AP9" s="30"/>
-      <c r="AQ9" s="30"/>
-      <c r="AR9" s="30"/>
-      <c r="AS9" s="30"/>
-      <c r="AT9" s="30"/>
-      <c r="AU9" s="30"/>
-      <c r="AV9" s="30"/>
-      <c r="AW9" s="30"/>
-      <c r="AX9" s="30"/>
-      <c r="AY9" s="30"/>
-      <c r="AZ9" s="30"/>
-      <c r="BA9" s="30"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="51"/>
+      <c r="AB9" s="51"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="51"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="51"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="51"/>
+      <c r="AJ9" s="51"/>
+      <c r="AK9" s="52"/>
+      <c r="AL9" s="45"/>
+      <c r="AM9" s="46"/>
+      <c r="AN9" s="46"/>
+      <c r="AO9" s="47"/>
+      <c r="AP9" s="39"/>
+      <c r="AQ9" s="39"/>
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="39"/>
+      <c r="AT9" s="39"/>
+      <c r="AU9" s="39"/>
+      <c r="AV9" s="39"/>
+      <c r="AW9" s="39"/>
+      <c r="AX9" s="39"/>
+      <c r="AY9" s="39"/>
+      <c r="AZ9" s="39"/>
+      <c r="BA9" s="39"/>
     </row>
     <row r="10" spans="1:53" ht="51" customHeight="1">
-      <c r="A10" s="44"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="28"/>
-      <c r="AM10" s="29"/>
-      <c r="AN10" s="29"/>
-      <c r="AO10" s="29"/>
-      <c r="AP10" s="30"/>
-      <c r="AQ10" s="30"/>
-      <c r="AR10" s="30"/>
-      <c r="AS10" s="30"/>
-      <c r="AT10" s="30"/>
-      <c r="AU10" s="30"/>
-      <c r="AV10" s="30"/>
-      <c r="AW10" s="30"/>
-      <c r="AX10" s="30"/>
-      <c r="AY10" s="30"/>
-      <c r="AZ10" s="30"/>
-      <c r="BA10" s="30"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
+      <c r="AB10" s="39"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="39"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="39"/>
+      <c r="AK10" s="39"/>
+      <c r="AL10" s="37"/>
+      <c r="AM10" s="38"/>
+      <c r="AN10" s="38"/>
+      <c r="AO10" s="38"/>
+      <c r="AP10" s="39"/>
+      <c r="AQ10" s="39"/>
+      <c r="AR10" s="39"/>
+      <c r="AS10" s="39"/>
+      <c r="AT10" s="39"/>
+      <c r="AU10" s="39"/>
+      <c r="AV10" s="39"/>
+      <c r="AW10" s="39"/>
+      <c r="AX10" s="39"/>
+      <c r="AY10" s="39"/>
+      <c r="AZ10" s="39"/>
+      <c r="BA10" s="39"/>
     </row>
     <row r="11" spans="1:53" ht="37.5" customHeight="1">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="30"/>
-      <c r="AK11" s="30"/>
-      <c r="AL11" s="28"/>
-      <c r="AM11" s="29"/>
-      <c r="AN11" s="29"/>
-      <c r="AO11" s="29"/>
-      <c r="AP11" s="30"/>
-      <c r="AQ11" s="30"/>
-      <c r="AR11" s="30"/>
-      <c r="AS11" s="30"/>
-      <c r="AT11" s="30"/>
-      <c r="AU11" s="30"/>
-      <c r="AV11" s="30"/>
-      <c r="AW11" s="30"/>
-      <c r="AX11" s="30"/>
-      <c r="AY11" s="30"/>
-      <c r="AZ11" s="30"/>
-      <c r="BA11" s="30"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="39"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="39"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="39"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="39"/>
+      <c r="AL11" s="37"/>
+      <c r="AM11" s="38"/>
+      <c r="AN11" s="38"/>
+      <c r="AO11" s="38"/>
+      <c r="AP11" s="39"/>
+      <c r="AQ11" s="39"/>
+      <c r="AR11" s="39"/>
+      <c r="AS11" s="39"/>
+      <c r="AT11" s="39"/>
+      <c r="AU11" s="39"/>
+      <c r="AV11" s="39"/>
+      <c r="AW11" s="39"/>
+      <c r="AX11" s="39"/>
+      <c r="AY11" s="39"/>
+      <c r="AZ11" s="39"/>
+      <c r="BA11" s="39"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="30"/>
-      <c r="AK12" s="30"/>
-      <c r="AL12" s="28"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="30"/>
-      <c r="AQ12" s="30"/>
-      <c r="AR12" s="30"/>
-      <c r="AS12" s="30"/>
-      <c r="AT12" s="30"/>
-      <c r="AU12" s="30"/>
-      <c r="AV12" s="30"/>
-      <c r="AW12" s="30"/>
-      <c r="AX12" s="30"/>
-      <c r="AY12" s="30"/>
-      <c r="AZ12" s="30"/>
-      <c r="BA12" s="30"/>
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="37"/>
+      <c r="AM12" s="38"/>
+      <c r="AN12" s="38"/>
+      <c r="AO12" s="38"/>
+      <c r="AP12" s="39"/>
+      <c r="AQ12" s="39"/>
+      <c r="AR12" s="39"/>
+      <c r="AS12" s="39"/>
+      <c r="AT12" s="39"/>
+      <c r="AU12" s="39"/>
+      <c r="AV12" s="39"/>
+      <c r="AW12" s="39"/>
+      <c r="AX12" s="39"/>
+      <c r="AY12" s="39"/>
+      <c r="AZ12" s="39"/>
+      <c r="BA12" s="39"/>
     </row>
     <row r="13" spans="1:53">
-      <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
-      <c r="AH13" s="30"/>
-      <c r="AI13" s="30"/>
-      <c r="AJ13" s="30"/>
-      <c r="AK13" s="30"/>
-      <c r="AL13" s="39"/>
-      <c r="AM13" s="40"/>
-      <c r="AN13" s="40"/>
-      <c r="AO13" s="40"/>
-      <c r="AP13" s="30"/>
-      <c r="AQ13" s="30"/>
-      <c r="AR13" s="30"/>
-      <c r="AS13" s="32"/>
-      <c r="AT13" s="32"/>
-      <c r="AU13" s="32"/>
-      <c r="AV13" s="32"/>
-      <c r="AW13" s="32"/>
-      <c r="AX13" s="32"/>
-      <c r="AY13" s="32"/>
-      <c r="AZ13" s="32"/>
-      <c r="BA13" s="32"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="39"/>
+      <c r="AG13" s="39"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="39"/>
+      <c r="AL13" s="48"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="39"/>
+      <c r="AQ13" s="39"/>
+      <c r="AR13" s="39"/>
+      <c r="AS13" s="41"/>
+      <c r="AT13" s="41"/>
+      <c r="AU13" s="41"/>
+      <c r="AV13" s="41"/>
+      <c r="AW13" s="41"/>
+      <c r="AX13" s="41"/>
+      <c r="AY13" s="41"/>
+      <c r="AZ13" s="41"/>
+      <c r="BA13" s="41"/>
     </row>
     <row r="14" spans="1:53">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
-      <c r="AC14" s="30"/>
-      <c r="AD14" s="30"/>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30"/>
-      <c r="AG14" s="30"/>
-      <c r="AH14" s="30"/>
-      <c r="AI14" s="30"/>
-      <c r="AJ14" s="30"/>
-      <c r="AK14" s="30"/>
-      <c r="AL14" s="28"/>
-      <c r="AM14" s="29"/>
-      <c r="AN14" s="29"/>
-      <c r="AO14" s="29"/>
-      <c r="AP14" s="30"/>
-      <c r="AQ14" s="30"/>
-      <c r="AR14" s="30"/>
-      <c r="AS14" s="30"/>
-      <c r="AT14" s="30"/>
-      <c r="AU14" s="30"/>
-      <c r="AV14" s="30"/>
-      <c r="AW14" s="30"/>
-      <c r="AX14" s="30"/>
-      <c r="AY14" s="30"/>
-      <c r="AZ14" s="30"/>
-      <c r="BA14" s="30"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="39"/>
+      <c r="AB14" s="39"/>
+      <c r="AC14" s="39"/>
+      <c r="AD14" s="39"/>
+      <c r="AE14" s="39"/>
+      <c r="AF14" s="39"/>
+      <c r="AG14" s="39"/>
+      <c r="AH14" s="39"/>
+      <c r="AI14" s="39"/>
+      <c r="AJ14" s="39"/>
+      <c r="AK14" s="39"/>
+      <c r="AL14" s="37"/>
+      <c r="AM14" s="38"/>
+      <c r="AN14" s="38"/>
+      <c r="AO14" s="38"/>
+      <c r="AP14" s="39"/>
+      <c r="AQ14" s="39"/>
+      <c r="AR14" s="39"/>
+      <c r="AS14" s="39"/>
+      <c r="AT14" s="39"/>
+      <c r="AU14" s="39"/>
+      <c r="AV14" s="39"/>
+      <c r="AW14" s="39"/>
+      <c r="AX14" s="39"/>
+      <c r="AY14" s="39"/>
+      <c r="AZ14" s="39"/>
+      <c r="BA14" s="39"/>
     </row>
     <row r="15" spans="1:53">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="30"/>
-      <c r="AD15" s="30"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
-      <c r="AH15" s="30"/>
-      <c r="AI15" s="30"/>
-      <c r="AJ15" s="30"/>
-      <c r="AK15" s="30"/>
-      <c r="AL15" s="28"/>
-      <c r="AM15" s="29"/>
-      <c r="AN15" s="29"/>
-      <c r="AO15" s="29"/>
-      <c r="AP15" s="30"/>
-      <c r="AQ15" s="30"/>
-      <c r="AR15" s="30"/>
-      <c r="AS15" s="30"/>
-      <c r="AT15" s="30"/>
-      <c r="AU15" s="30"/>
-      <c r="AV15" s="30"/>
-      <c r="AW15" s="30"/>
-      <c r="AX15" s="30"/>
-      <c r="AY15" s="30"/>
-      <c r="AZ15" s="30"/>
-      <c r="BA15" s="30"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="39"/>
+      <c r="AL15" s="37"/>
+      <c r="AM15" s="38"/>
+      <c r="AN15" s="38"/>
+      <c r="AO15" s="38"/>
+      <c r="AP15" s="39"/>
+      <c r="AQ15" s="39"/>
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="39"/>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="39"/>
+      <c r="AV15" s="39"/>
+      <c r="AW15" s="39"/>
+      <c r="AX15" s="39"/>
+      <c r="AY15" s="39"/>
+      <c r="AZ15" s="39"/>
+      <c r="BA15" s="39"/>
     </row>
     <row r="16" spans="1:53">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
-      <c r="AC16" s="30"/>
-      <c r="AD16" s="30"/>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="30"/>
-      <c r="AH16" s="30"/>
-      <c r="AI16" s="30"/>
-      <c r="AJ16" s="30"/>
-      <c r="AK16" s="30"/>
-      <c r="AL16" s="28"/>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="29"/>
-      <c r="AP16" s="30"/>
-      <c r="AQ16" s="30"/>
-      <c r="AR16" s="30"/>
-      <c r="AS16" s="30"/>
-      <c r="AT16" s="30"/>
-      <c r="AU16" s="30"/>
-      <c r="AV16" s="30"/>
-      <c r="AW16" s="30"/>
-      <c r="AX16" s="30"/>
-      <c r="AY16" s="30"/>
-      <c r="AZ16" s="30"/>
-      <c r="BA16" s="30"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="39"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="39"/>
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="39"/>
+      <c r="AA16" s="39"/>
+      <c r="AB16" s="39"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="39"/>
+      <c r="AE16" s="39"/>
+      <c r="AF16" s="39"/>
+      <c r="AG16" s="39"/>
+      <c r="AH16" s="39"/>
+      <c r="AI16" s="39"/>
+      <c r="AJ16" s="39"/>
+      <c r="AK16" s="39"/>
+      <c r="AL16" s="37"/>
+      <c r="AM16" s="38"/>
+      <c r="AN16" s="38"/>
+      <c r="AO16" s="38"/>
+      <c r="AP16" s="39"/>
+      <c r="AQ16" s="39"/>
+      <c r="AR16" s="39"/>
+      <c r="AS16" s="39"/>
+      <c r="AT16" s="39"/>
+      <c r="AU16" s="39"/>
+      <c r="AV16" s="39"/>
+      <c r="AW16" s="39"/>
+      <c r="AX16" s="39"/>
+      <c r="AY16" s="39"/>
+      <c r="AZ16" s="39"/>
+      <c r="BA16" s="39"/>
     </row>
     <row r="17" spans="1:53">
-      <c r="A17" s="46"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="33"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="33"/>
-      <c r="AH17" s="33"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="33"/>
-      <c r="AK17" s="33"/>
-      <c r="AL17" s="28"/>
-      <c r="AM17" s="29"/>
-      <c r="AN17" s="29"/>
-      <c r="AO17" s="29"/>
-      <c r="AP17" s="30"/>
-      <c r="AQ17" s="33"/>
-      <c r="AR17" s="33"/>
-      <c r="AS17" s="33"/>
-      <c r="AT17" s="33"/>
-      <c r="AU17" s="33"/>
-      <c r="AV17" s="33"/>
-      <c r="AW17" s="33"/>
-      <c r="AX17" s="33"/>
-      <c r="AY17" s="33"/>
-      <c r="AZ17" s="33"/>
-      <c r="BA17" s="33"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="42"/>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="42"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="42"/>
+      <c r="AG17" s="42"/>
+      <c r="AH17" s="42"/>
+      <c r="AI17" s="42"/>
+      <c r="AJ17" s="42"/>
+      <c r="AK17" s="42"/>
+      <c r="AL17" s="37"/>
+      <c r="AM17" s="38"/>
+      <c r="AN17" s="38"/>
+      <c r="AO17" s="38"/>
+      <c r="AP17" s="39"/>
+      <c r="AQ17" s="42"/>
+      <c r="AR17" s="42"/>
+      <c r="AS17" s="42"/>
+      <c r="AT17" s="42"/>
+      <c r="AU17" s="42"/>
+      <c r="AV17" s="42"/>
+      <c r="AW17" s="42"/>
+      <c r="AX17" s="42"/>
+      <c r="AY17" s="42"/>
+      <c r="AZ17" s="42"/>
+      <c r="BA17" s="42"/>
     </row>
     <row r="18" spans="1:53">
-      <c r="A18" s="46"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="33"/>
-      <c r="AE18" s="33"/>
-      <c r="AF18" s="33"/>
-      <c r="AG18" s="33"/>
-      <c r="AH18" s="33"/>
-      <c r="AI18" s="33"/>
-      <c r="AJ18" s="33"/>
-      <c r="AK18" s="33"/>
-      <c r="AL18" s="28"/>
-      <c r="AM18" s="29"/>
-      <c r="AN18" s="29"/>
-      <c r="AO18" s="29"/>
-      <c r="AP18" s="30"/>
-      <c r="AQ18" s="33"/>
-      <c r="AR18" s="33"/>
-      <c r="AS18" s="33"/>
-      <c r="AT18" s="33"/>
-      <c r="AU18" s="33"/>
-      <c r="AV18" s="33"/>
-      <c r="AW18" s="33"/>
-      <c r="AX18" s="33"/>
-      <c r="AY18" s="33"/>
-      <c r="AZ18" s="33"/>
-      <c r="BA18" s="33"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="42"/>
+      <c r="AD18" s="42"/>
+      <c r="AE18" s="42"/>
+      <c r="AF18" s="42"/>
+      <c r="AG18" s="42"/>
+      <c r="AH18" s="42"/>
+      <c r="AI18" s="42"/>
+      <c r="AJ18" s="42"/>
+      <c r="AK18" s="42"/>
+      <c r="AL18" s="37"/>
+      <c r="AM18" s="38"/>
+      <c r="AN18" s="38"/>
+      <c r="AO18" s="38"/>
+      <c r="AP18" s="39"/>
+      <c r="AQ18" s="42"/>
+      <c r="AR18" s="42"/>
+      <c r="AS18" s="42"/>
+      <c r="AT18" s="42"/>
+      <c r="AU18" s="42"/>
+      <c r="AV18" s="42"/>
+      <c r="AW18" s="42"/>
+      <c r="AX18" s="42"/>
+      <c r="AY18" s="42"/>
+      <c r="AZ18" s="42"/>
+      <c r="BA18" s="42"/>
     </row>
     <row r="19" spans="1:53">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
-      <c r="AC19" s="30"/>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="30"/>
-      <c r="AK19" s="30"/>
-      <c r="AL19" s="28"/>
-      <c r="AM19" s="28"/>
-      <c r="AN19" s="28"/>
-      <c r="AO19" s="28"/>
-      <c r="AP19" s="30"/>
-      <c r="AQ19" s="30"/>
-      <c r="AR19" s="30"/>
-      <c r="AS19" s="30"/>
-      <c r="AT19" s="30"/>
-      <c r="AU19" s="30"/>
-      <c r="AV19" s="30"/>
-      <c r="AW19" s="30"/>
-      <c r="AX19" s="30"/>
-      <c r="AY19" s="30"/>
-      <c r="AZ19" s="30"/>
-      <c r="BA19" s="30"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="39"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="39"/>
+      <c r="X19" s="39"/>
+      <c r="Y19" s="39"/>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="39"/>
+      <c r="AB19" s="39"/>
+      <c r="AC19" s="39"/>
+      <c r="AD19" s="39"/>
+      <c r="AE19" s="39"/>
+      <c r="AF19" s="39"/>
+      <c r="AG19" s="39"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="39"/>
+      <c r="AK19" s="39"/>
+      <c r="AL19" s="37"/>
+      <c r="AM19" s="37"/>
+      <c r="AN19" s="37"/>
+      <c r="AO19" s="37"/>
+      <c r="AP19" s="39"/>
+      <c r="AQ19" s="39"/>
+      <c r="AR19" s="39"/>
+      <c r="AS19" s="39"/>
+      <c r="AT19" s="39"/>
+      <c r="AU19" s="39"/>
+      <c r="AV19" s="39"/>
+      <c r="AW19" s="39"/>
+      <c r="AX19" s="39"/>
+      <c r="AY19" s="39"/>
+      <c r="AZ19" s="39"/>
+      <c r="BA19" s="39"/>
     </row>
     <row r="20" spans="1:53">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="30"/>
-      <c r="AJ20" s="30"/>
-      <c r="AK20" s="30"/>
-      <c r="AL20" s="28"/>
-      <c r="AM20" s="28"/>
-      <c r="AN20" s="28"/>
-      <c r="AO20" s="28"/>
-      <c r="AP20" s="30"/>
-      <c r="AQ20" s="30"/>
-      <c r="AR20" s="30"/>
-      <c r="AS20" s="30"/>
-      <c r="AT20" s="30"/>
-      <c r="AU20" s="30"/>
-      <c r="AV20" s="30"/>
-      <c r="AW20" s="30"/>
-      <c r="AX20" s="30"/>
-      <c r="AY20" s="30"/>
-      <c r="AZ20" s="30"/>
-      <c r="BA20" s="30"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="39"/>
+      <c r="AE20" s="39"/>
+      <c r="AF20" s="39"/>
+      <c r="AG20" s="39"/>
+      <c r="AH20" s="39"/>
+      <c r="AI20" s="39"/>
+      <c r="AJ20" s="39"/>
+      <c r="AK20" s="39"/>
+      <c r="AL20" s="37"/>
+      <c r="AM20" s="37"/>
+      <c r="AN20" s="37"/>
+      <c r="AO20" s="37"/>
+      <c r="AP20" s="39"/>
+      <c r="AQ20" s="39"/>
+      <c r="AR20" s="39"/>
+      <c r="AS20" s="39"/>
+      <c r="AT20" s="39"/>
+      <c r="AU20" s="39"/>
+      <c r="AV20" s="39"/>
+      <c r="AW20" s="39"/>
+      <c r="AX20" s="39"/>
+      <c r="AY20" s="39"/>
+      <c r="AZ20" s="39"/>
+      <c r="BA20" s="39"/>
     </row>
     <row r="21" spans="1:53" ht="13.5" customHeight="1">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33"/>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="33"/>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="33"/>
-      <c r="AH21" s="33"/>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="33"/>
-      <c r="AK21" s="33"/>
-      <c r="AL21" s="28"/>
-      <c r="AM21" s="28"/>
-      <c r="AN21" s="28"/>
-      <c r="AO21" s="28"/>
-      <c r="AP21" s="30"/>
-      <c r="AQ21" s="30"/>
-      <c r="AR21" s="30"/>
-      <c r="AS21" s="30"/>
-      <c r="AT21" s="30"/>
-      <c r="AU21" s="30"/>
-      <c r="AV21" s="30"/>
-      <c r="AW21" s="30"/>
-      <c r="AX21" s="30"/>
-      <c r="AY21" s="30"/>
-      <c r="AZ21" s="30"/>
-      <c r="BA21" s="30"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="42"/>
+      <c r="Y21" s="42"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="42"/>
+      <c r="AC21" s="42"/>
+      <c r="AD21" s="42"/>
+      <c r="AE21" s="42"/>
+      <c r="AF21" s="42"/>
+      <c r="AG21" s="42"/>
+      <c r="AH21" s="42"/>
+      <c r="AI21" s="42"/>
+      <c r="AJ21" s="42"/>
+      <c r="AK21" s="42"/>
+      <c r="AL21" s="37"/>
+      <c r="AM21" s="37"/>
+      <c r="AN21" s="37"/>
+      <c r="AO21" s="37"/>
+      <c r="AP21" s="39"/>
+      <c r="AQ21" s="39"/>
+      <c r="AR21" s="39"/>
+      <c r="AS21" s="39"/>
+      <c r="AT21" s="39"/>
+      <c r="AU21" s="39"/>
+      <c r="AV21" s="39"/>
+      <c r="AW21" s="39"/>
+      <c r="AX21" s="39"/>
+      <c r="AY21" s="39"/>
+      <c r="AZ21" s="39"/>
+      <c r="BA21" s="39"/>
     </row>
     <row r="22" spans="1:53">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
-      <c r="AL22" s="28"/>
-      <c r="AM22" s="28"/>
-      <c r="AN22" s="28"/>
-      <c r="AO22" s="28"/>
-      <c r="AP22" s="30"/>
-      <c r="AQ22" s="30"/>
-      <c r="AR22" s="30"/>
-      <c r="AS22" s="30"/>
-      <c r="AT22" s="30"/>
-      <c r="AU22" s="30"/>
-      <c r="AV22" s="30"/>
-      <c r="AW22" s="30"/>
-      <c r="AX22" s="30"/>
-      <c r="AY22" s="30"/>
-      <c r="AZ22" s="30"/>
-      <c r="BA22" s="30"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="39"/>
+      <c r="AA22" s="39"/>
+      <c r="AB22" s="39"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="39"/>
+      <c r="AE22" s="39"/>
+      <c r="AF22" s="39"/>
+      <c r="AG22" s="39"/>
+      <c r="AH22" s="39"/>
+      <c r="AI22" s="39"/>
+      <c r="AJ22" s="39"/>
+      <c r="AK22" s="39"/>
+      <c r="AL22" s="37"/>
+      <c r="AM22" s="37"/>
+      <c r="AN22" s="37"/>
+      <c r="AO22" s="37"/>
+      <c r="AP22" s="39"/>
+      <c r="AQ22" s="39"/>
+      <c r="AR22" s="39"/>
+      <c r="AS22" s="39"/>
+      <c r="AT22" s="39"/>
+      <c r="AU22" s="39"/>
+      <c r="AV22" s="39"/>
+      <c r="AW22" s="39"/>
+      <c r="AX22" s="39"/>
+      <c r="AY22" s="39"/>
+      <c r="AZ22" s="39"/>
+      <c r="BA22" s="39"/>
     </row>
     <row r="23" spans="1:53">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33"/>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
-      <c r="AA23" s="33"/>
-      <c r="AB23" s="33"/>
-      <c r="AC23" s="33"/>
-      <c r="AD23" s="33"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="33"/>
-      <c r="AG23" s="33"/>
-      <c r="AH23" s="33"/>
-      <c r="AI23" s="33"/>
-      <c r="AJ23" s="33"/>
-      <c r="AK23" s="33"/>
-      <c r="AL23" s="28"/>
-      <c r="AM23" s="28"/>
-      <c r="AN23" s="28"/>
-      <c r="AO23" s="28"/>
-      <c r="AP23" s="30"/>
-      <c r="AQ23" s="30"/>
-      <c r="AR23" s="30"/>
-      <c r="AS23" s="30"/>
-      <c r="AT23" s="30"/>
-      <c r="AU23" s="30"/>
-      <c r="AV23" s="30"/>
-      <c r="AW23" s="30"/>
-      <c r="AX23" s="30"/>
-      <c r="AY23" s="30"/>
-      <c r="AZ23" s="30"/>
-      <c r="BA23" s="30"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="42"/>
+      <c r="W23" s="42"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="42"/>
+      <c r="Z23" s="42"/>
+      <c r="AA23" s="42"/>
+      <c r="AB23" s="42"/>
+      <c r="AC23" s="42"/>
+      <c r="AD23" s="42"/>
+      <c r="AE23" s="42"/>
+      <c r="AF23" s="42"/>
+      <c r="AG23" s="42"/>
+      <c r="AH23" s="42"/>
+      <c r="AI23" s="42"/>
+      <c r="AJ23" s="42"/>
+      <c r="AK23" s="42"/>
+      <c r="AL23" s="37"/>
+      <c r="AM23" s="37"/>
+      <c r="AN23" s="37"/>
+      <c r="AO23" s="37"/>
+      <c r="AP23" s="39"/>
+      <c r="AQ23" s="39"/>
+      <c r="AR23" s="39"/>
+      <c r="AS23" s="39"/>
+      <c r="AT23" s="39"/>
+      <c r="AU23" s="39"/>
+      <c r="AV23" s="39"/>
+      <c r="AW23" s="39"/>
+      <c r="AX23" s="39"/>
+      <c r="AY23" s="39"/>
+      <c r="AZ23" s="39"/>
+      <c r="BA23" s="39"/>
     </row>
     <row r="24" spans="1:53">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
-      <c r="AE24" s="30"/>
-      <c r="AF24" s="30"/>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="30"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="30"/>
-      <c r="AL24" s="28"/>
-      <c r="AM24" s="28"/>
-      <c r="AN24" s="28"/>
-      <c r="AO24" s="28"/>
-      <c r="AP24" s="30"/>
-      <c r="AQ24" s="30"/>
-      <c r="AR24" s="30"/>
-      <c r="AS24" s="30"/>
-      <c r="AT24" s="30"/>
-      <c r="AU24" s="30"/>
-      <c r="AV24" s="30"/>
-      <c r="AW24" s="30"/>
-      <c r="AX24" s="30"/>
-      <c r="AY24" s="30"/>
-      <c r="AZ24" s="30"/>
-      <c r="BA24" s="30"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="39"/>
+      <c r="V24" s="39"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="39"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="39"/>
+      <c r="AE24" s="39"/>
+      <c r="AF24" s="39"/>
+      <c r="AG24" s="39"/>
+      <c r="AH24" s="39"/>
+      <c r="AI24" s="39"/>
+      <c r="AJ24" s="39"/>
+      <c r="AK24" s="39"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="37"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="39"/>
+      <c r="AQ24" s="39"/>
+      <c r="AR24" s="39"/>
+      <c r="AS24" s="39"/>
+      <c r="AT24" s="39"/>
+      <c r="AU24" s="39"/>
+      <c r="AV24" s="39"/>
+      <c r="AW24" s="39"/>
+      <c r="AX24" s="39"/>
+      <c r="AY24" s="39"/>
+      <c r="AZ24" s="39"/>
+      <c r="BA24" s="39"/>
     </row>
     <row r="25" spans="1:53">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="30"/>
-      <c r="AD25" s="30"/>
-      <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
-      <c r="AG25" s="30"/>
-      <c r="AH25" s="30"/>
-      <c r="AI25" s="30"/>
-      <c r="AJ25" s="30"/>
-      <c r="AK25" s="30"/>
-      <c r="AL25" s="28"/>
-      <c r="AM25" s="29"/>
-      <c r="AN25" s="29"/>
-      <c r="AO25" s="29"/>
-      <c r="AP25" s="30"/>
-      <c r="AQ25" s="30"/>
-      <c r="AR25" s="30"/>
-      <c r="AS25" s="30"/>
-      <c r="AT25" s="30"/>
-      <c r="AU25" s="30"/>
-      <c r="AV25" s="30"/>
-      <c r="AW25" s="30"/>
-      <c r="AX25" s="30"/>
-      <c r="AY25" s="30"/>
-      <c r="AZ25" s="30"/>
-      <c r="BA25" s="30"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="39"/>
+      <c r="S25" s="39"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="39"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="39"/>
+      <c r="Z25" s="39"/>
+      <c r="AA25" s="39"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="39"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="39"/>
+      <c r="AF25" s="39"/>
+      <c r="AG25" s="39"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="39"/>
+      <c r="AJ25" s="39"/>
+      <c r="AK25" s="39"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="38"/>
+      <c r="AN25" s="38"/>
+      <c r="AO25" s="38"/>
+      <c r="AP25" s="39"/>
+      <c r="AQ25" s="39"/>
+      <c r="AR25" s="39"/>
+      <c r="AS25" s="39"/>
+      <c r="AT25" s="39"/>
+      <c r="AU25" s="39"/>
+      <c r="AV25" s="39"/>
+      <c r="AW25" s="39"/>
+      <c r="AX25" s="39"/>
+      <c r="AY25" s="39"/>
+      <c r="AZ25" s="39"/>
+      <c r="BA25" s="39"/>
     </row>
     <row r="26" spans="1:53">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="28"/>
-      <c r="AM26" s="29"/>
-      <c r="AN26" s="29"/>
-      <c r="AO26" s="29"/>
-      <c r="AP26" s="30"/>
-      <c r="AQ26" s="30"/>
-      <c r="AR26" s="30"/>
-      <c r="AS26" s="30"/>
-      <c r="AT26" s="30"/>
-      <c r="AU26" s="30"/>
-      <c r="AV26" s="30"/>
-      <c r="AW26" s="30"/>
-      <c r="AX26" s="30"/>
-      <c r="AY26" s="30"/>
-      <c r="AZ26" s="30"/>
-      <c r="BA26" s="30"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="39"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="39"/>
+      <c r="AE26" s="39"/>
+      <c r="AF26" s="39"/>
+      <c r="AG26" s="39"/>
+      <c r="AH26" s="39"/>
+      <c r="AI26" s="39"/>
+      <c r="AJ26" s="39"/>
+      <c r="AK26" s="39"/>
+      <c r="AL26" s="37"/>
+      <c r="AM26" s="38"/>
+      <c r="AN26" s="38"/>
+      <c r="AO26" s="38"/>
+      <c r="AP26" s="39"/>
+      <c r="AQ26" s="39"/>
+      <c r="AR26" s="39"/>
+      <c r="AS26" s="39"/>
+      <c r="AT26" s="39"/>
+      <c r="AU26" s="39"/>
+      <c r="AV26" s="39"/>
+      <c r="AW26" s="39"/>
+      <c r="AX26" s="39"/>
+      <c r="AY26" s="39"/>
+      <c r="AZ26" s="39"/>
+      <c r="BA26" s="39"/>
     </row>
     <row r="27" spans="1:53">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="28"/>
-      <c r="AM27" s="29"/>
-      <c r="AN27" s="29"/>
-      <c r="AO27" s="29"/>
-      <c r="AP27" s="30"/>
-      <c r="AQ27" s="30"/>
-      <c r="AR27" s="30"/>
-      <c r="AS27" s="30"/>
-      <c r="AT27" s="30"/>
-      <c r="AU27" s="30"/>
-      <c r="AV27" s="30"/>
-      <c r="AW27" s="30"/>
-      <c r="AX27" s="30"/>
-      <c r="AY27" s="30"/>
-      <c r="AZ27" s="30"/>
-      <c r="BA27" s="30"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="39"/>
+      <c r="V27" s="39"/>
+      <c r="W27" s="39"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="39"/>
+      <c r="Z27" s="39"/>
+      <c r="AA27" s="39"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="39"/>
+      <c r="AD27" s="39"/>
+      <c r="AE27" s="39"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="39"/>
+      <c r="AH27" s="39"/>
+      <c r="AI27" s="39"/>
+      <c r="AJ27" s="39"/>
+      <c r="AK27" s="39"/>
+      <c r="AL27" s="37"/>
+      <c r="AM27" s="38"/>
+      <c r="AN27" s="38"/>
+      <c r="AO27" s="38"/>
+      <c r="AP27" s="39"/>
+      <c r="AQ27" s="39"/>
+      <c r="AR27" s="39"/>
+      <c r="AS27" s="39"/>
+      <c r="AT27" s="39"/>
+      <c r="AU27" s="39"/>
+      <c r="AV27" s="39"/>
+      <c r="AW27" s="39"/>
+      <c r="AX27" s="39"/>
+      <c r="AY27" s="39"/>
+      <c r="AZ27" s="39"/>
+      <c r="BA27" s="39"/>
     </row>
     <row r="28" spans="1:53">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AH28" s="30"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="30"/>
-      <c r="AK28" s="30"/>
-      <c r="AL28" s="28"/>
-      <c r="AM28" s="29"/>
-      <c r="AN28" s="29"/>
-      <c r="AO28" s="29"/>
-      <c r="AP28" s="30"/>
-      <c r="AQ28" s="30"/>
-      <c r="AR28" s="30"/>
-      <c r="AS28" s="30"/>
-      <c r="AT28" s="30"/>
-      <c r="AU28" s="30"/>
-      <c r="AV28" s="30"/>
-      <c r="AW28" s="30"/>
-      <c r="AX28" s="30"/>
-      <c r="AY28" s="30"/>
-      <c r="AZ28" s="30"/>
-      <c r="BA28" s="30"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="39"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="39"/>
+      <c r="AA28" s="39"/>
+      <c r="AB28" s="39"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="39"/>
+      <c r="AE28" s="39"/>
+      <c r="AF28" s="39"/>
+      <c r="AG28" s="39"/>
+      <c r="AH28" s="39"/>
+      <c r="AI28" s="39"/>
+      <c r="AJ28" s="39"/>
+      <c r="AK28" s="39"/>
+      <c r="AL28" s="37"/>
+      <c r="AM28" s="38"/>
+      <c r="AN28" s="38"/>
+      <c r="AO28" s="38"/>
+      <c r="AP28" s="39"/>
+      <c r="AQ28" s="39"/>
+      <c r="AR28" s="39"/>
+      <c r="AS28" s="39"/>
+      <c r="AT28" s="39"/>
+      <c r="AU28" s="39"/>
+      <c r="AV28" s="39"/>
+      <c r="AW28" s="39"/>
+      <c r="AX28" s="39"/>
+      <c r="AY28" s="39"/>
+      <c r="AZ28" s="39"/>
+      <c r="BA28" s="39"/>
     </row>
     <row r="29" spans="1:53">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-      <c r="AH29" s="30"/>
-      <c r="AI29" s="30"/>
-      <c r="AJ29" s="30"/>
-      <c r="AK29" s="30"/>
-      <c r="AL29" s="28"/>
-      <c r="AM29" s="29"/>
-      <c r="AN29" s="29"/>
-      <c r="AO29" s="29"/>
-      <c r="AP29" s="30"/>
-      <c r="AQ29" s="30"/>
-      <c r="AR29" s="30"/>
-      <c r="AS29" s="30"/>
-      <c r="AT29" s="30"/>
-      <c r="AU29" s="30"/>
-      <c r="AV29" s="30"/>
-      <c r="AW29" s="30"/>
-      <c r="AX29" s="30"/>
-      <c r="AY29" s="30"/>
-      <c r="AZ29" s="30"/>
-      <c r="BA29" s="30"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="39"/>
+      <c r="AE29" s="39"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="39"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="39"/>
+      <c r="AK29" s="39"/>
+      <c r="AL29" s="37"/>
+      <c r="AM29" s="38"/>
+      <c r="AN29" s="38"/>
+      <c r="AO29" s="38"/>
+      <c r="AP29" s="39"/>
+      <c r="AQ29" s="39"/>
+      <c r="AR29" s="39"/>
+      <c r="AS29" s="39"/>
+      <c r="AT29" s="39"/>
+      <c r="AU29" s="39"/>
+      <c r="AV29" s="39"/>
+      <c r="AW29" s="39"/>
+      <c r="AX29" s="39"/>
+      <c r="AY29" s="39"/>
+      <c r="AZ29" s="39"/>
+      <c r="BA29" s="39"/>
     </row>
     <row r="30" spans="1:53">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
-      <c r="AH30" s="30"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="30"/>
-      <c r="AK30" s="30"/>
-      <c r="AL30" s="29"/>
-      <c r="AM30" s="29"/>
-      <c r="AN30" s="29"/>
-      <c r="AO30" s="29"/>
-      <c r="AP30" s="30"/>
-      <c r="AQ30" s="30"/>
-      <c r="AR30" s="30"/>
-      <c r="AS30" s="30"/>
-      <c r="AT30" s="30"/>
-      <c r="AU30" s="30"/>
-      <c r="AV30" s="30"/>
-      <c r="AW30" s="30"/>
-      <c r="AX30" s="30"/>
-      <c r="AY30" s="30"/>
-      <c r="AZ30" s="30"/>
-      <c r="BA30" s="30"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="39"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="39"/>
+      <c r="V30" s="39"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="39"/>
+      <c r="Z30" s="39"/>
+      <c r="AA30" s="39"/>
+      <c r="AB30" s="39"/>
+      <c r="AC30" s="39"/>
+      <c r="AD30" s="39"/>
+      <c r="AE30" s="39"/>
+      <c r="AF30" s="39"/>
+      <c r="AG30" s="39"/>
+      <c r="AH30" s="39"/>
+      <c r="AI30" s="39"/>
+      <c r="AJ30" s="39"/>
+      <c r="AK30" s="39"/>
+      <c r="AL30" s="38"/>
+      <c r="AM30" s="38"/>
+      <c r="AN30" s="38"/>
+      <c r="AO30" s="38"/>
+      <c r="AP30" s="39"/>
+      <c r="AQ30" s="39"/>
+      <c r="AR30" s="39"/>
+      <c r="AS30" s="39"/>
+      <c r="AT30" s="39"/>
+      <c r="AU30" s="39"/>
+      <c r="AV30" s="39"/>
+      <c r="AW30" s="39"/>
+      <c r="AX30" s="39"/>
+      <c r="AY30" s="39"/>
+      <c r="AZ30" s="39"/>
+      <c r="BA30" s="39"/>
     </row>
     <row r="31" spans="1:53">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
-      <c r="AC31" s="30"/>
-      <c r="AD31" s="30"/>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
-      <c r="AG31" s="30"/>
-      <c r="AH31" s="30"/>
-      <c r="AI31" s="30"/>
-      <c r="AJ31" s="30"/>
-      <c r="AK31" s="30"/>
-      <c r="AL31" s="29"/>
-      <c r="AM31" s="29"/>
-      <c r="AN31" s="29"/>
-      <c r="AO31" s="29"/>
-      <c r="AP31" s="30"/>
-      <c r="AQ31" s="30"/>
-      <c r="AR31" s="30"/>
-      <c r="AS31" s="30"/>
-      <c r="AT31" s="30"/>
-      <c r="AU31" s="30"/>
-      <c r="AV31" s="30"/>
-      <c r="AW31" s="30"/>
-      <c r="AX31" s="30"/>
-      <c r="AY31" s="30"/>
-      <c r="AZ31" s="30"/>
-      <c r="BA31" s="30"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="39"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="39"/>
+      <c r="AB31" s="39"/>
+      <c r="AC31" s="39"/>
+      <c r="AD31" s="39"/>
+      <c r="AE31" s="39"/>
+      <c r="AF31" s="39"/>
+      <c r="AG31" s="39"/>
+      <c r="AH31" s="39"/>
+      <c r="AI31" s="39"/>
+      <c r="AJ31" s="39"/>
+      <c r="AK31" s="39"/>
+      <c r="AL31" s="38"/>
+      <c r="AM31" s="38"/>
+      <c r="AN31" s="38"/>
+      <c r="AO31" s="38"/>
+      <c r="AP31" s="39"/>
+      <c r="AQ31" s="39"/>
+      <c r="AR31" s="39"/>
+      <c r="AS31" s="39"/>
+      <c r="AT31" s="39"/>
+      <c r="AU31" s="39"/>
+      <c r="AV31" s="39"/>
+      <c r="AW31" s="39"/>
+      <c r="AX31" s="39"/>
+      <c r="AY31" s="39"/>
+      <c r="AZ31" s="39"/>
+      <c r="BA31" s="39"/>
     </row>
     <row r="32" spans="1:53">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
-      <c r="AG32" s="30"/>
-      <c r="AH32" s="30"/>
-      <c r="AI32" s="30"/>
-      <c r="AJ32" s="30"/>
-      <c r="AK32" s="30"/>
-      <c r="AL32" s="29"/>
-      <c r="AM32" s="29"/>
-      <c r="AN32" s="29"/>
-      <c r="AO32" s="29"/>
-      <c r="AP32" s="30"/>
-      <c r="AQ32" s="30"/>
-      <c r="AR32" s="30"/>
-      <c r="AS32" s="30"/>
-      <c r="AT32" s="30"/>
-      <c r="AU32" s="30"/>
-      <c r="AV32" s="30"/>
-      <c r="AW32" s="30"/>
-      <c r="AX32" s="30"/>
-      <c r="AY32" s="30"/>
-      <c r="AZ32" s="30"/>
-      <c r="BA32" s="30"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="39"/>
+      <c r="S32" s="39"/>
+      <c r="T32" s="39"/>
+      <c r="U32" s="39"/>
+      <c r="V32" s="39"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="39"/>
+      <c r="Y32" s="39"/>
+      <c r="Z32" s="39"/>
+      <c r="AA32" s="39"/>
+      <c r="AB32" s="39"/>
+      <c r="AC32" s="39"/>
+      <c r="AD32" s="39"/>
+      <c r="AE32" s="39"/>
+      <c r="AF32" s="39"/>
+      <c r="AG32" s="39"/>
+      <c r="AH32" s="39"/>
+      <c r="AI32" s="39"/>
+      <c r="AJ32" s="39"/>
+      <c r="AK32" s="39"/>
+      <c r="AL32" s="38"/>
+      <c r="AM32" s="38"/>
+      <c r="AN32" s="38"/>
+      <c r="AO32" s="38"/>
+      <c r="AP32" s="39"/>
+      <c r="AQ32" s="39"/>
+      <c r="AR32" s="39"/>
+      <c r="AS32" s="39"/>
+      <c r="AT32" s="39"/>
+      <c r="AU32" s="39"/>
+      <c r="AV32" s="39"/>
+      <c r="AW32" s="39"/>
+      <c r="AX32" s="39"/>
+      <c r="AY32" s="39"/>
+      <c r="AZ32" s="39"/>
+      <c r="BA32" s="39"/>
     </row>
     <row r="33" spans="1:53">
-      <c r="A33" s="29"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
-      <c r="AC33" s="30"/>
-      <c r="AD33" s="30"/>
-      <c r="AE33" s="30"/>
-      <c r="AF33" s="30"/>
-      <c r="AG33" s="30"/>
-      <c r="AH33" s="30"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="29"/>
-      <c r="AM33" s="29"/>
-      <c r="AN33" s="29"/>
-      <c r="AO33" s="29"/>
-      <c r="AP33" s="30"/>
-      <c r="AQ33" s="30"/>
-      <c r="AR33" s="30"/>
-      <c r="AS33" s="30"/>
-      <c r="AT33" s="30"/>
-      <c r="AU33" s="30"/>
-      <c r="AV33" s="30"/>
-      <c r="AW33" s="30"/>
-      <c r="AX33" s="30"/>
-      <c r="AY33" s="30"/>
-      <c r="AZ33" s="30"/>
-      <c r="BA33" s="30"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="39"/>
+      <c r="R33" s="39"/>
+      <c r="S33" s="39"/>
+      <c r="T33" s="39"/>
+      <c r="U33" s="39"/>
+      <c r="V33" s="39"/>
+      <c r="W33" s="39"/>
+      <c r="X33" s="39"/>
+      <c r="Y33" s="39"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="39"/>
+      <c r="AD33" s="39"/>
+      <c r="AE33" s="39"/>
+      <c r="AF33" s="39"/>
+      <c r="AG33" s="39"/>
+      <c r="AH33" s="39"/>
+      <c r="AI33" s="39"/>
+      <c r="AJ33" s="39"/>
+      <c r="AK33" s="39"/>
+      <c r="AL33" s="38"/>
+      <c r="AM33" s="38"/>
+      <c r="AN33" s="38"/>
+      <c r="AO33" s="38"/>
+      <c r="AP33" s="39"/>
+      <c r="AQ33" s="39"/>
+      <c r="AR33" s="39"/>
+      <c r="AS33" s="39"/>
+      <c r="AT33" s="39"/>
+      <c r="AU33" s="39"/>
+      <c r="AV33" s="39"/>
+      <c r="AW33" s="39"/>
+      <c r="AX33" s="39"/>
+      <c r="AY33" s="39"/>
+      <c r="AZ33" s="39"/>
+      <c r="BA33" s="39"/>
     </row>
     <row r="34" spans="1:53">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="29"/>
-      <c r="AM34" s="29"/>
-      <c r="AN34" s="29"/>
-      <c r="AO34" s="29"/>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="30"/>
-      <c r="AR34" s="30"/>
-      <c r="AS34" s="30"/>
-      <c r="AT34" s="30"/>
-      <c r="AU34" s="30"/>
-      <c r="AV34" s="30"/>
-      <c r="AW34" s="30"/>
-      <c r="AX34" s="30"/>
-      <c r="AY34" s="30"/>
-      <c r="AZ34" s="30"/>
-      <c r="BA34" s="30"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="39"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="39"/>
+      <c r="U34" s="39"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="39"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="39"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="39"/>
+      <c r="AB34" s="39"/>
+      <c r="AC34" s="39"/>
+      <c r="AD34" s="39"/>
+      <c r="AE34" s="39"/>
+      <c r="AF34" s="39"/>
+      <c r="AG34" s="39"/>
+      <c r="AH34" s="39"/>
+      <c r="AI34" s="39"/>
+      <c r="AJ34" s="39"/>
+      <c r="AK34" s="39"/>
+      <c r="AL34" s="38"/>
+      <c r="AM34" s="38"/>
+      <c r="AN34" s="38"/>
+      <c r="AO34" s="38"/>
+      <c r="AP34" s="39"/>
+      <c r="AQ34" s="39"/>
+      <c r="AR34" s="39"/>
+      <c r="AS34" s="39"/>
+      <c r="AT34" s="39"/>
+      <c r="AU34" s="39"/>
+      <c r="AV34" s="39"/>
+      <c r="AW34" s="39"/>
+      <c r="AX34" s="39"/>
+      <c r="AY34" s="39"/>
+      <c r="AZ34" s="39"/>
+      <c r="BA34" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="229">
@@ -6899,162 +10245,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="79"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="3" spans="1:4" ht="29.5" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="79"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:4" ht="15.5" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="27" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20" customHeight="1">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="77"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
@@ -7085,7 +10431,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="21" customWidth="1"/>
@@ -7351,209 +10697,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G2" s="27" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29.5" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="27" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="27" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="79" t="s">
+      <c r="F5" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="79" t="s">
+      <c r="G5" s="27" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.5" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="76"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.5" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-    </row>
-    <row r="10" spans="1:7" ht="20" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A13" s="77"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FE983023:FL983028 PA983023:PH983028 YW983023:ZD983028 AIS983023:AIZ983028 ASO983023:ASV983028 BCK983023:BCR983028 BMG983023:BMN983028 BWC983023:BWJ983028 CFY983023:CGF983028 CPU983023:CQB983028 CZQ983023:CZX983028 DJM983023:DJT983028 DTI983023:DTP983028 EDE983023:EDL983028 ENA983023:ENH983028 EWW983023:EXD983028 FGS983023:FGZ983028 FQO983023:FQV983028 GAK983023:GAR983028 GKG983023:GKN983028 GUC983023:GUJ983028 HDY983023:HEF983028 HNU983023:HOB983028 HXQ983023:HXX983028 IHM983023:IHT983028 IRI983023:IRP983028 JBE983023:JBL983028 JLA983023:JLH983028 JUW983023:JVD983028 KES983023:KEZ983028 KOO983023:KOV983028 KYK983023:KYR983028 LIG983023:LIN983028 LSC983023:LSJ983028 MBY983023:MCF983028 MLU983023:MMB983028 MVQ983023:MVX983028 NFM983023:NFT983028 NPI983023:NPP983028 NZE983023:NZL983028 OJA983023:OJH983028 OSW983023:OTD983028 PCS983023:PCZ983028 PMO983023:PMV983028 PWK983023:PWR983028 QGG983023:QGN983028 QQC983023:QQJ983028 QZY983023:RAF983028 RJU983023:RKB983028 RTQ983023:RTX983028 SDM983023:SDT983028 SNI983023:SNP983028 SXE983023:SXL983028 THA983023:THH983028 TQW983023:TRD983028 UAS983023:UAZ983028 UKO983023:UKV983028 UUK983023:UUR983028 VEG983023:VEN983028 VOC983023:VOJ983028 VXY983023:VYF983028 WHU983023:WIB983028 WRQ983023:WRX983028 FE65519:FL65524 PA65519:PH65524 YW65519:ZD65524 AIS65519:AIZ65524 ASO65519:ASV65524 BCK65519:BCR65524 BMG65519:BMN65524 BWC65519:BWJ65524 CFY65519:CGF65524 CPU65519:CQB65524 CZQ65519:CZX65524 DJM65519:DJT65524 DTI65519:DTP65524 EDE65519:EDL65524 ENA65519:ENH65524 EWW65519:EXD65524 FGS65519:FGZ65524 FQO65519:FQV65524 GAK65519:GAR65524 GKG65519:GKN65524 GUC65519:GUJ65524 HDY65519:HEF65524 HNU65519:HOB65524 HXQ65519:HXX65524 IHM65519:IHT65524 IRI65519:IRP65524 JBE65519:JBL65524 JLA65519:JLH65524 JUW65519:JVD65524 KES65519:KEZ65524 KOO65519:KOV65524 KYK65519:KYR65524 LIG65519:LIN65524 LSC65519:LSJ65524 MBY65519:MCF65524 MLU65519:MMB65524 MVQ65519:MVX65524 NFM65519:NFT65524 NPI65519:NPP65524 NZE65519:NZL65524 OJA65519:OJH65524 OSW65519:OTD65524 PCS65519:PCZ65524 PMO65519:PMV65524 PWK65519:PWR65524 QGG65519:QGN65524 QQC65519:QQJ65524 QZY65519:RAF65524 RJU65519:RKB65524 RTQ65519:RTX65524 SDM65519:SDT65524 SNI65519:SNP65524 SXE65519:SXL65524 THA65519:THH65524 TQW65519:TRD65524 UAS65519:UAZ65524 UKO65519:UKV65524 UUK65519:UUR65524 VEG65519:VEN65524 VOC65519:VOJ65524 VXY65519:VYF65524 WHU65519:WIB65524 WRQ65519:WRX65524 FE131055:FL131060 PA131055:PH131060 YW131055:ZD131060 AIS131055:AIZ131060 ASO131055:ASV131060 BCK131055:BCR131060 BMG131055:BMN131060 BWC131055:BWJ131060 CFY131055:CGF131060 CPU131055:CQB131060 CZQ131055:CZX131060 DJM131055:DJT131060 DTI131055:DTP131060 EDE131055:EDL131060 ENA131055:ENH131060 EWW131055:EXD131060 FGS131055:FGZ131060 FQO131055:FQV131060 GAK131055:GAR131060 GKG131055:GKN131060 GUC131055:GUJ131060 HDY131055:HEF131060 HNU131055:HOB131060 HXQ131055:HXX131060 IHM131055:IHT131060 IRI131055:IRP131060 JBE131055:JBL131060 JLA131055:JLH131060 JUW131055:JVD131060 KES131055:KEZ131060 KOO131055:KOV131060 KYK131055:KYR131060 LIG131055:LIN131060 LSC131055:LSJ131060 MBY131055:MCF131060 MLU131055:MMB131060 MVQ131055:MVX131060 NFM131055:NFT131060 NPI131055:NPP131060 NZE131055:NZL131060 OJA131055:OJH131060 OSW131055:OTD131060 PCS131055:PCZ131060 PMO131055:PMV131060 PWK131055:PWR131060 QGG131055:QGN131060 QQC131055:QQJ131060 QZY131055:RAF131060 RJU131055:RKB131060 RTQ131055:RTX131060 SDM131055:SDT131060 SNI131055:SNP131060 SXE131055:SXL131060 THA131055:THH131060 TQW131055:TRD131060 UAS131055:UAZ131060 UKO131055:UKV131060 UUK131055:UUR131060 VEG131055:VEN131060 VOC131055:VOJ131060 VXY131055:VYF131060 WHU131055:WIB131060 WRQ131055:WRX131060 FE196591:FL196596 PA196591:PH196596 YW196591:ZD196596 AIS196591:AIZ196596 ASO196591:ASV196596 BCK196591:BCR196596 BMG196591:BMN196596 BWC196591:BWJ196596 CFY196591:CGF196596 CPU196591:CQB196596 CZQ196591:CZX196596 DJM196591:DJT196596 DTI196591:DTP196596 EDE196591:EDL196596 ENA196591:ENH196596 EWW196591:EXD196596 FGS196591:FGZ196596 FQO196591:FQV196596 GAK196591:GAR196596 GKG196591:GKN196596 GUC196591:GUJ196596 HDY196591:HEF196596 HNU196591:HOB196596 HXQ196591:HXX196596 IHM196591:IHT196596 IRI196591:IRP196596 JBE196591:JBL196596 JLA196591:JLH196596 JUW196591:JVD196596 KES196591:KEZ196596 KOO196591:KOV196596 KYK196591:KYR196596 LIG196591:LIN196596 LSC196591:LSJ196596 MBY196591:MCF196596 MLU196591:MMB196596 MVQ196591:MVX196596 NFM196591:NFT196596 NPI196591:NPP196596 NZE196591:NZL196596 OJA196591:OJH196596 OSW196591:OTD196596 PCS196591:PCZ196596 PMO196591:PMV196596 PWK196591:PWR196596 QGG196591:QGN196596 QQC196591:QQJ196596 QZY196591:RAF196596 RJU196591:RKB196596 RTQ196591:RTX196596 SDM196591:SDT196596 SNI196591:SNP196596 SXE196591:SXL196596 THA196591:THH196596 TQW196591:TRD196596 UAS196591:UAZ196596 UKO196591:UKV196596 UUK196591:UUR196596 VEG196591:VEN196596 VOC196591:VOJ196596 VXY196591:VYF196596 WHU196591:WIB196596 WRQ196591:WRX196596 FE262127:FL262132 PA262127:PH262132 YW262127:ZD262132 AIS262127:AIZ262132 ASO262127:ASV262132 BCK262127:BCR262132 BMG262127:BMN262132 BWC262127:BWJ262132 CFY262127:CGF262132 CPU262127:CQB262132 CZQ262127:CZX262132 DJM262127:DJT262132 DTI262127:DTP262132 EDE262127:EDL262132 ENA262127:ENH262132 EWW262127:EXD262132 FGS262127:FGZ262132 FQO262127:FQV262132 GAK262127:GAR262132 GKG262127:GKN262132 GUC262127:GUJ262132 HDY262127:HEF262132 HNU262127:HOB262132 HXQ262127:HXX262132 IHM262127:IHT262132 IRI262127:IRP262132 JBE262127:JBL262132 JLA262127:JLH262132 JUW262127:JVD262132 KES262127:KEZ262132 KOO262127:KOV262132 KYK262127:KYR262132 LIG262127:LIN262132 LSC262127:LSJ262132 MBY262127:MCF262132 MLU262127:MMB262132 MVQ262127:MVX262132 NFM262127:NFT262132 NPI262127:NPP262132 NZE262127:NZL262132 OJA262127:OJH262132 OSW262127:OTD262132 PCS262127:PCZ262132 PMO262127:PMV262132 PWK262127:PWR262132 QGG262127:QGN262132 QQC262127:QQJ262132 QZY262127:RAF262132 RJU262127:RKB262132 RTQ262127:RTX262132 SDM262127:SDT262132 SNI262127:SNP262132 SXE262127:SXL262132 THA262127:THH262132 TQW262127:TRD262132 UAS262127:UAZ262132 UKO262127:UKV262132 UUK262127:UUR262132 VEG262127:VEN262132 VOC262127:VOJ262132 VXY262127:VYF262132 WHU262127:WIB262132 WRQ262127:WRX262132 FE327663:FL327668 PA327663:PH327668 YW327663:ZD327668 AIS327663:AIZ327668 ASO327663:ASV327668 BCK327663:BCR327668 BMG327663:BMN327668 BWC327663:BWJ327668 CFY327663:CGF327668 CPU327663:CQB327668 CZQ327663:CZX327668 DJM327663:DJT327668 DTI327663:DTP327668 EDE327663:EDL327668 ENA327663:ENH327668 EWW327663:EXD327668 FGS327663:FGZ327668 FQO327663:FQV327668 GAK327663:GAR327668 GKG327663:GKN327668 GUC327663:GUJ327668 HDY327663:HEF327668 HNU327663:HOB327668 HXQ327663:HXX327668 IHM327663:IHT327668 IRI327663:IRP327668 JBE327663:JBL327668 JLA327663:JLH327668 JUW327663:JVD327668 KES327663:KEZ327668 KOO327663:KOV327668 KYK327663:KYR327668 LIG327663:LIN327668 LSC327663:LSJ327668 MBY327663:MCF327668 MLU327663:MMB327668 MVQ327663:MVX327668 NFM327663:NFT327668 NPI327663:NPP327668 NZE327663:NZL327668 OJA327663:OJH327668 OSW327663:OTD327668 PCS327663:PCZ327668 PMO327663:PMV327668 PWK327663:PWR327668 QGG327663:QGN327668 QQC327663:QQJ327668 QZY327663:RAF327668 RJU327663:RKB327668 RTQ327663:RTX327668 SDM327663:SDT327668 SNI327663:SNP327668 SXE327663:SXL327668 THA327663:THH327668 TQW327663:TRD327668 UAS327663:UAZ327668 UKO327663:UKV327668 UUK327663:UUR327668 VEG327663:VEN327668 VOC327663:VOJ327668 VXY327663:VYF327668 WHU327663:WIB327668 WRQ327663:WRX327668 FE393199:FL393204 PA393199:PH393204 YW393199:ZD393204 AIS393199:AIZ393204 ASO393199:ASV393204 BCK393199:BCR393204 BMG393199:BMN393204 BWC393199:BWJ393204 CFY393199:CGF393204 CPU393199:CQB393204 CZQ393199:CZX393204 DJM393199:DJT393204 DTI393199:DTP393204 EDE393199:EDL393204 ENA393199:ENH393204 EWW393199:EXD393204 FGS393199:FGZ393204 FQO393199:FQV393204 GAK393199:GAR393204 GKG393199:GKN393204 GUC393199:GUJ393204 HDY393199:HEF393204 HNU393199:HOB393204 HXQ393199:HXX393204 IHM393199:IHT393204 IRI393199:IRP393204 JBE393199:JBL393204 JLA393199:JLH393204 JUW393199:JVD393204 KES393199:KEZ393204 KOO393199:KOV393204 KYK393199:KYR393204 LIG393199:LIN393204 LSC393199:LSJ393204 MBY393199:MCF393204 MLU393199:MMB393204 MVQ393199:MVX393204 NFM393199:NFT393204 NPI393199:NPP393204 NZE393199:NZL393204 OJA393199:OJH393204 OSW393199:OTD393204 PCS393199:PCZ393204 PMO393199:PMV393204 PWK393199:PWR393204 QGG393199:QGN393204 QQC393199:QQJ393204 QZY393199:RAF393204 RJU393199:RKB393204 RTQ393199:RTX393204 SDM393199:SDT393204 SNI393199:SNP393204 SXE393199:SXL393204 THA393199:THH393204 TQW393199:TRD393204 UAS393199:UAZ393204 UKO393199:UKV393204 UUK393199:UUR393204 VEG393199:VEN393204 VOC393199:VOJ393204 VXY393199:VYF393204 WHU393199:WIB393204 WRQ393199:WRX393204 FE458735:FL458740 PA458735:PH458740 YW458735:ZD458740 AIS458735:AIZ458740 ASO458735:ASV458740 BCK458735:BCR458740 BMG458735:BMN458740 BWC458735:BWJ458740 CFY458735:CGF458740 CPU458735:CQB458740 CZQ458735:CZX458740 DJM458735:DJT458740 DTI458735:DTP458740 EDE458735:EDL458740 ENA458735:ENH458740 EWW458735:EXD458740 FGS458735:FGZ458740 FQO458735:FQV458740 GAK458735:GAR458740 GKG458735:GKN458740 GUC458735:GUJ458740 HDY458735:HEF458740 HNU458735:HOB458740 HXQ458735:HXX458740 IHM458735:IHT458740 IRI458735:IRP458740 JBE458735:JBL458740 JLA458735:JLH458740 JUW458735:JVD458740 KES458735:KEZ458740 KOO458735:KOV458740 KYK458735:KYR458740 LIG458735:LIN458740 LSC458735:LSJ458740 MBY458735:MCF458740 MLU458735:MMB458740 MVQ458735:MVX458740 NFM458735:NFT458740 NPI458735:NPP458740 NZE458735:NZL458740 OJA458735:OJH458740 OSW458735:OTD458740 PCS458735:PCZ458740 PMO458735:PMV458740 PWK458735:PWR458740 QGG458735:QGN458740 QQC458735:QQJ458740 QZY458735:RAF458740 RJU458735:RKB458740 RTQ458735:RTX458740 SDM458735:SDT458740 SNI458735:SNP458740 SXE458735:SXL458740 THA458735:THH458740 TQW458735:TRD458740 UAS458735:UAZ458740 UKO458735:UKV458740 UUK458735:UUR458740 VEG458735:VEN458740 VOC458735:VOJ458740 VXY458735:VYF458740 WHU458735:WIB458740 WRQ458735:WRX458740 FE524271:FL524276 PA524271:PH524276 YW524271:ZD524276 AIS524271:AIZ524276 ASO524271:ASV524276 BCK524271:BCR524276 BMG524271:BMN524276 BWC524271:BWJ524276 CFY524271:CGF524276 CPU524271:CQB524276 CZQ524271:CZX524276 DJM524271:DJT524276 DTI524271:DTP524276 EDE524271:EDL524276 ENA524271:ENH524276 EWW524271:EXD524276 FGS524271:FGZ524276 FQO524271:FQV524276 GAK524271:GAR524276 GKG524271:GKN524276 GUC524271:GUJ524276 HDY524271:HEF524276 HNU524271:HOB524276 HXQ524271:HXX524276 IHM524271:IHT524276 IRI524271:IRP524276 JBE524271:JBL524276 JLA524271:JLH524276 JUW524271:JVD524276 KES524271:KEZ524276 KOO524271:KOV524276 KYK524271:KYR524276 LIG524271:LIN524276 LSC524271:LSJ524276 MBY524271:MCF524276 MLU524271:MMB524276 MVQ524271:MVX524276 NFM524271:NFT524276 NPI524271:NPP524276 NZE524271:NZL524276 OJA524271:OJH524276 OSW524271:OTD524276 PCS524271:PCZ524276 PMO524271:PMV524276 PWK524271:PWR524276 QGG524271:QGN524276 QQC524271:QQJ524276 QZY524271:RAF524276 RJU524271:RKB524276 RTQ524271:RTX524276 SDM524271:SDT524276 SNI524271:SNP524276 SXE524271:SXL524276 THA524271:THH524276 TQW524271:TRD524276 UAS524271:UAZ524276 UKO524271:UKV524276 UUK524271:UUR524276 VEG524271:VEN524276 VOC524271:VOJ524276 VXY524271:VYF524276 WHU524271:WIB524276 WRQ524271:WRX524276 FE589807:FL589812 PA589807:PH589812 YW589807:ZD589812 AIS589807:AIZ589812 ASO589807:ASV589812 BCK589807:BCR589812 BMG589807:BMN589812 BWC589807:BWJ589812 CFY589807:CGF589812 CPU589807:CQB589812 CZQ589807:CZX589812 DJM589807:DJT589812 DTI589807:DTP589812 EDE589807:EDL589812 ENA589807:ENH589812 EWW589807:EXD589812 FGS589807:FGZ589812 FQO589807:FQV589812 GAK589807:GAR589812 GKG589807:GKN589812 GUC589807:GUJ589812 HDY589807:HEF589812 HNU589807:HOB589812 HXQ589807:HXX589812 IHM589807:IHT589812 IRI589807:IRP589812 JBE589807:JBL589812 JLA589807:JLH589812 JUW589807:JVD589812 KES589807:KEZ589812 KOO589807:KOV589812 KYK589807:KYR589812 LIG589807:LIN589812 LSC589807:LSJ589812 MBY589807:MCF589812 MLU589807:MMB589812 MVQ589807:MVX589812 NFM589807:NFT589812 NPI589807:NPP589812 NZE589807:NZL589812 OJA589807:OJH589812 OSW589807:OTD589812 PCS589807:PCZ589812 PMO589807:PMV589812 PWK589807:PWR589812 QGG589807:QGN589812 QQC589807:QQJ589812 QZY589807:RAF589812 RJU589807:RKB589812 RTQ589807:RTX589812 SDM589807:SDT589812 SNI589807:SNP589812 SXE589807:SXL589812 THA589807:THH589812 TQW589807:TRD589812 UAS589807:UAZ589812 UKO589807:UKV589812 UUK589807:UUR589812 VEG589807:VEN589812 VOC589807:VOJ589812 VXY589807:VYF589812 WHU589807:WIB589812 WRQ589807:WRX589812 FE655343:FL655348 PA655343:PH655348 YW655343:ZD655348 AIS655343:AIZ655348 ASO655343:ASV655348 BCK655343:BCR655348 BMG655343:BMN655348 BWC655343:BWJ655348 CFY655343:CGF655348 CPU655343:CQB655348 CZQ655343:CZX655348 DJM655343:DJT655348 DTI655343:DTP655348 EDE655343:EDL655348 ENA655343:ENH655348 EWW655343:EXD655348 FGS655343:FGZ655348 FQO655343:FQV655348 GAK655343:GAR655348 GKG655343:GKN655348 GUC655343:GUJ655348 HDY655343:HEF655348 HNU655343:HOB655348 HXQ655343:HXX655348 IHM655343:IHT655348 IRI655343:IRP655348 JBE655343:JBL655348 JLA655343:JLH655348 JUW655343:JVD655348 KES655343:KEZ655348 KOO655343:KOV655348 KYK655343:KYR655348 LIG655343:LIN655348 LSC655343:LSJ655348 MBY655343:MCF655348 MLU655343:MMB655348 MVQ655343:MVX655348 NFM655343:NFT655348 NPI655343:NPP655348 NZE655343:NZL655348 OJA655343:OJH655348 OSW655343:OTD655348 PCS655343:PCZ655348 PMO655343:PMV655348 PWK655343:PWR655348 QGG655343:QGN655348 QQC655343:QQJ655348 QZY655343:RAF655348 RJU655343:RKB655348 RTQ655343:RTX655348 SDM655343:SDT655348 SNI655343:SNP655348 SXE655343:SXL655348 THA655343:THH655348 TQW655343:TRD655348 UAS655343:UAZ655348 UKO655343:UKV655348 UUK655343:UUR655348 VEG655343:VEN655348 VOC655343:VOJ655348 VXY655343:VYF655348 WHU655343:WIB655348 WRQ655343:WRX655348 FE720879:FL720884 PA720879:PH720884 YW720879:ZD720884 AIS720879:AIZ720884 ASO720879:ASV720884 BCK720879:BCR720884 BMG720879:BMN720884 BWC720879:BWJ720884 CFY720879:CGF720884 CPU720879:CQB720884 CZQ720879:CZX720884 DJM720879:DJT720884 DTI720879:DTP720884 EDE720879:EDL720884 ENA720879:ENH720884 EWW720879:EXD720884 FGS720879:FGZ720884 FQO720879:FQV720884 GAK720879:GAR720884 GKG720879:GKN720884 GUC720879:GUJ720884 HDY720879:HEF720884 HNU720879:HOB720884 HXQ720879:HXX720884 IHM720879:IHT720884 IRI720879:IRP720884 JBE720879:JBL720884 JLA720879:JLH720884 JUW720879:JVD720884 KES720879:KEZ720884 KOO720879:KOV720884 KYK720879:KYR720884 LIG720879:LIN720884 LSC720879:LSJ720884 MBY720879:MCF720884 MLU720879:MMB720884 MVQ720879:MVX720884 NFM720879:NFT720884 NPI720879:NPP720884 NZE720879:NZL720884 OJA720879:OJH720884 OSW720879:OTD720884 PCS720879:PCZ720884 PMO720879:PMV720884 PWK720879:PWR720884 QGG720879:QGN720884 QQC720879:QQJ720884 QZY720879:RAF720884 RJU720879:RKB720884 RTQ720879:RTX720884 SDM720879:SDT720884 SNI720879:SNP720884 SXE720879:SXL720884 THA720879:THH720884 TQW720879:TRD720884 UAS720879:UAZ720884 UKO720879:UKV720884 UUK720879:UUR720884 VEG720879:VEN720884 VOC720879:VOJ720884 VXY720879:VYF720884 WHU720879:WIB720884 WRQ720879:WRX720884 FE786415:FL786420 PA786415:PH786420 YW786415:ZD786420 AIS786415:AIZ786420 ASO786415:ASV786420 BCK786415:BCR786420 BMG786415:BMN786420 BWC786415:BWJ786420 CFY786415:CGF786420 CPU786415:CQB786420 CZQ786415:CZX786420 DJM786415:DJT786420 DTI786415:DTP786420 EDE786415:EDL786420 ENA786415:ENH786420 EWW786415:EXD786420 FGS786415:FGZ786420 FQO786415:FQV786420 GAK786415:GAR786420 GKG786415:GKN786420 GUC786415:GUJ786420 HDY786415:HEF786420 HNU786415:HOB786420 HXQ786415:HXX786420 IHM786415:IHT786420 IRI786415:IRP786420 JBE786415:JBL786420 JLA786415:JLH786420 JUW786415:JVD786420 KES786415:KEZ786420 KOO786415:KOV786420 KYK786415:KYR786420 LIG786415:LIN786420 LSC786415:LSJ786420 MBY786415:MCF786420 MLU786415:MMB786420 MVQ786415:MVX786420 NFM786415:NFT786420 NPI786415:NPP786420 NZE786415:NZL786420 OJA786415:OJH786420 OSW786415:OTD786420 PCS786415:PCZ786420 PMO786415:PMV786420 PWK786415:PWR786420 QGG786415:QGN786420 QQC786415:QQJ786420 QZY786415:RAF786420 RJU786415:RKB786420 RTQ786415:RTX786420 SDM786415:SDT786420 SNI786415:SNP786420 SXE786415:SXL786420 THA786415:THH786420 TQW786415:TRD786420 UAS786415:UAZ786420 UKO786415:UKV786420 UUK786415:UUR786420 VEG786415:VEN786420 VOC786415:VOJ786420 VXY786415:VYF786420 WHU786415:WIB786420 WRQ786415:WRX786420 FE851951:FL851956 PA851951:PH851956 YW851951:ZD851956 AIS851951:AIZ851956 ASO851951:ASV851956 BCK851951:BCR851956 BMG851951:BMN851956 BWC851951:BWJ851956 CFY851951:CGF851956 CPU851951:CQB851956 CZQ851951:CZX851956 DJM851951:DJT851956 DTI851951:DTP851956 EDE851951:EDL851956 ENA851951:ENH851956 EWW851951:EXD851956 FGS851951:FGZ851956 FQO851951:FQV851956 GAK851951:GAR851956 GKG851951:GKN851956 GUC851951:GUJ851956 HDY851951:HEF851956 HNU851951:HOB851956 HXQ851951:HXX851956 IHM851951:IHT851956 IRI851951:IRP851956 JBE851951:JBL851956 JLA851951:JLH851956 JUW851951:JVD851956 KES851951:KEZ851956 KOO851951:KOV851956 KYK851951:KYR851956 LIG851951:LIN851956 LSC851951:LSJ851956 MBY851951:MCF851956 MLU851951:MMB851956 MVQ851951:MVX851956 NFM851951:NFT851956 NPI851951:NPP851956 NZE851951:NZL851956 OJA851951:OJH851956 OSW851951:OTD851956 PCS851951:PCZ851956 PMO851951:PMV851956 PWK851951:PWR851956 QGG851951:QGN851956 QQC851951:QQJ851956 QZY851951:RAF851956 RJU851951:RKB851956 RTQ851951:RTX851956 SDM851951:SDT851956 SNI851951:SNP851956 SXE851951:SXL851956 THA851951:THH851956 TQW851951:TRD851956 UAS851951:UAZ851956 UKO851951:UKV851956 UUK851951:UUR851956 VEG851951:VEN851956 VOC851951:VOJ851956 VXY851951:VYF851956 WHU851951:WIB851956 WRQ851951:WRX851956 FE917487:FL917492 PA917487:PH917492 YW917487:ZD917492 AIS917487:AIZ917492 ASO917487:ASV917492 BCK917487:BCR917492 BMG917487:BMN917492 BWC917487:BWJ917492 CFY917487:CGF917492 CPU917487:CQB917492 CZQ917487:CZX917492 DJM917487:DJT917492 DTI917487:DTP917492 EDE917487:EDL917492 ENA917487:ENH917492 EWW917487:EXD917492 FGS917487:FGZ917492 FQO917487:FQV917492 GAK917487:GAR917492 GKG917487:GKN917492 GUC917487:GUJ917492 HDY917487:HEF917492 HNU917487:HOB917492 HXQ917487:HXX917492 IHM917487:IHT917492 IRI917487:IRP917492 JBE917487:JBL917492 JLA917487:JLH917492 JUW917487:JVD917492 KES917487:KEZ917492 KOO917487:KOV917492 KYK917487:KYR917492 LIG917487:LIN917492 LSC917487:LSJ917492 MBY917487:MCF917492 MLU917487:MMB917492 MVQ917487:MVX917492 NFM917487:NFT917492 NPI917487:NPP917492 NZE917487:NZL917492 OJA917487:OJH917492 OSW917487:OTD917492 PCS917487:PCZ917492 PMO917487:PMV917492 PWK917487:PWR917492 QGG917487:QGN917492 QQC917487:QQJ917492 QZY917487:RAF917492 RJU917487:RKB917492 RTQ917487:RTX917492 SDM917487:SDT917492 SNI917487:SNP917492 SXE917487:SXL917492 THA917487:THH917492 TQW917487:TRD917492 UAS917487:UAZ917492 UKO917487:UKV917492 UUK917487:UUR917492 VEG917487:VEN917492 VOC917487:VOJ917492 VXY917487:VYF917492 WHU917487:WIB917492 WRQ917487:WRX917492" xr:uid="{0B4A9982-0581-4256-A7BD-537BA00C93C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FE983017:FL983022 PA983017:PH983022 YW983017:ZD983022 AIS983017:AIZ983022 ASO983017:ASV983022 BCK983017:BCR983022 BMG983017:BMN983022 BWC983017:BWJ983022 CFY983017:CGF983022 CPU983017:CQB983022 CZQ983017:CZX983022 DJM983017:DJT983022 DTI983017:DTP983022 EDE983017:EDL983022 ENA983017:ENH983022 EWW983017:EXD983022 FGS983017:FGZ983022 FQO983017:FQV983022 GAK983017:GAR983022 GKG983017:GKN983022 GUC983017:GUJ983022 HDY983017:HEF983022 HNU983017:HOB983022 HXQ983017:HXX983022 IHM983017:IHT983022 IRI983017:IRP983022 JBE983017:JBL983022 JLA983017:JLH983022 JUW983017:JVD983022 KES983017:KEZ983022 KOO983017:KOV983022 KYK983017:KYR983022 LIG983017:LIN983022 LSC983017:LSJ983022 MBY983017:MCF983022 MLU983017:MMB983022 MVQ983017:MVX983022 NFM983017:NFT983022 NPI983017:NPP983022 NZE983017:NZL983022 OJA983017:OJH983022 OSW983017:OTD983022 PCS983017:PCZ983022 PMO983017:PMV983022 PWK983017:PWR983022 QGG983017:QGN983022 QQC983017:QQJ983022 QZY983017:RAF983022 RJU983017:RKB983022 RTQ983017:RTX983022 SDM983017:SDT983022 SNI983017:SNP983022 SXE983017:SXL983022 THA983017:THH983022 TQW983017:TRD983022 UAS983017:UAZ983022 UKO983017:UKV983022 UUK983017:UUR983022 VEG983017:VEN983022 VOC983017:VOJ983022 VXY983017:VYF983022 WHU983017:WIB983022 WRQ983017:WRX983022 FE65513:FL65518 PA65513:PH65518 YW65513:ZD65518 AIS65513:AIZ65518 ASO65513:ASV65518 BCK65513:BCR65518 BMG65513:BMN65518 BWC65513:BWJ65518 CFY65513:CGF65518 CPU65513:CQB65518 CZQ65513:CZX65518 DJM65513:DJT65518 DTI65513:DTP65518 EDE65513:EDL65518 ENA65513:ENH65518 EWW65513:EXD65518 FGS65513:FGZ65518 FQO65513:FQV65518 GAK65513:GAR65518 GKG65513:GKN65518 GUC65513:GUJ65518 HDY65513:HEF65518 HNU65513:HOB65518 HXQ65513:HXX65518 IHM65513:IHT65518 IRI65513:IRP65518 JBE65513:JBL65518 JLA65513:JLH65518 JUW65513:JVD65518 KES65513:KEZ65518 KOO65513:KOV65518 KYK65513:KYR65518 LIG65513:LIN65518 LSC65513:LSJ65518 MBY65513:MCF65518 MLU65513:MMB65518 MVQ65513:MVX65518 NFM65513:NFT65518 NPI65513:NPP65518 NZE65513:NZL65518 OJA65513:OJH65518 OSW65513:OTD65518 PCS65513:PCZ65518 PMO65513:PMV65518 PWK65513:PWR65518 QGG65513:QGN65518 QQC65513:QQJ65518 QZY65513:RAF65518 RJU65513:RKB65518 RTQ65513:RTX65518 SDM65513:SDT65518 SNI65513:SNP65518 SXE65513:SXL65518 THA65513:THH65518 TQW65513:TRD65518 UAS65513:UAZ65518 UKO65513:UKV65518 UUK65513:UUR65518 VEG65513:VEN65518 VOC65513:VOJ65518 VXY65513:VYF65518 WHU65513:WIB65518 WRQ65513:WRX65518 FE131049:FL131054 PA131049:PH131054 YW131049:ZD131054 AIS131049:AIZ131054 ASO131049:ASV131054 BCK131049:BCR131054 BMG131049:BMN131054 BWC131049:BWJ131054 CFY131049:CGF131054 CPU131049:CQB131054 CZQ131049:CZX131054 DJM131049:DJT131054 DTI131049:DTP131054 EDE131049:EDL131054 ENA131049:ENH131054 EWW131049:EXD131054 FGS131049:FGZ131054 FQO131049:FQV131054 GAK131049:GAR131054 GKG131049:GKN131054 GUC131049:GUJ131054 HDY131049:HEF131054 HNU131049:HOB131054 HXQ131049:HXX131054 IHM131049:IHT131054 IRI131049:IRP131054 JBE131049:JBL131054 JLA131049:JLH131054 JUW131049:JVD131054 KES131049:KEZ131054 KOO131049:KOV131054 KYK131049:KYR131054 LIG131049:LIN131054 LSC131049:LSJ131054 MBY131049:MCF131054 MLU131049:MMB131054 MVQ131049:MVX131054 NFM131049:NFT131054 NPI131049:NPP131054 NZE131049:NZL131054 OJA131049:OJH131054 OSW131049:OTD131054 PCS131049:PCZ131054 PMO131049:PMV131054 PWK131049:PWR131054 QGG131049:QGN131054 QQC131049:QQJ131054 QZY131049:RAF131054 RJU131049:RKB131054 RTQ131049:RTX131054 SDM131049:SDT131054 SNI131049:SNP131054 SXE131049:SXL131054 THA131049:THH131054 TQW131049:TRD131054 UAS131049:UAZ131054 UKO131049:UKV131054 UUK131049:UUR131054 VEG131049:VEN131054 VOC131049:VOJ131054 VXY131049:VYF131054 WHU131049:WIB131054 WRQ131049:WRX131054 FE196585:FL196590 PA196585:PH196590 YW196585:ZD196590 AIS196585:AIZ196590 ASO196585:ASV196590 BCK196585:BCR196590 BMG196585:BMN196590 BWC196585:BWJ196590 CFY196585:CGF196590 CPU196585:CQB196590 CZQ196585:CZX196590 DJM196585:DJT196590 DTI196585:DTP196590 EDE196585:EDL196590 ENA196585:ENH196590 EWW196585:EXD196590 FGS196585:FGZ196590 FQO196585:FQV196590 GAK196585:GAR196590 GKG196585:GKN196590 GUC196585:GUJ196590 HDY196585:HEF196590 HNU196585:HOB196590 HXQ196585:HXX196590 IHM196585:IHT196590 IRI196585:IRP196590 JBE196585:JBL196590 JLA196585:JLH196590 JUW196585:JVD196590 KES196585:KEZ196590 KOO196585:KOV196590 KYK196585:KYR196590 LIG196585:LIN196590 LSC196585:LSJ196590 MBY196585:MCF196590 MLU196585:MMB196590 MVQ196585:MVX196590 NFM196585:NFT196590 NPI196585:NPP196590 NZE196585:NZL196590 OJA196585:OJH196590 OSW196585:OTD196590 PCS196585:PCZ196590 PMO196585:PMV196590 PWK196585:PWR196590 QGG196585:QGN196590 QQC196585:QQJ196590 QZY196585:RAF196590 RJU196585:RKB196590 RTQ196585:RTX196590 SDM196585:SDT196590 SNI196585:SNP196590 SXE196585:SXL196590 THA196585:THH196590 TQW196585:TRD196590 UAS196585:UAZ196590 UKO196585:UKV196590 UUK196585:UUR196590 VEG196585:VEN196590 VOC196585:VOJ196590 VXY196585:VYF196590 WHU196585:WIB196590 WRQ196585:WRX196590 FE262121:FL262126 PA262121:PH262126 YW262121:ZD262126 AIS262121:AIZ262126 ASO262121:ASV262126 BCK262121:BCR262126 BMG262121:BMN262126 BWC262121:BWJ262126 CFY262121:CGF262126 CPU262121:CQB262126 CZQ262121:CZX262126 DJM262121:DJT262126 DTI262121:DTP262126 EDE262121:EDL262126 ENA262121:ENH262126 EWW262121:EXD262126 FGS262121:FGZ262126 FQO262121:FQV262126 GAK262121:GAR262126 GKG262121:GKN262126 GUC262121:GUJ262126 HDY262121:HEF262126 HNU262121:HOB262126 HXQ262121:HXX262126 IHM262121:IHT262126 IRI262121:IRP262126 JBE262121:JBL262126 JLA262121:JLH262126 JUW262121:JVD262126 KES262121:KEZ262126 KOO262121:KOV262126 KYK262121:KYR262126 LIG262121:LIN262126 LSC262121:LSJ262126 MBY262121:MCF262126 MLU262121:MMB262126 MVQ262121:MVX262126 NFM262121:NFT262126 NPI262121:NPP262126 NZE262121:NZL262126 OJA262121:OJH262126 OSW262121:OTD262126 PCS262121:PCZ262126 PMO262121:PMV262126 PWK262121:PWR262126 QGG262121:QGN262126 QQC262121:QQJ262126 QZY262121:RAF262126 RJU262121:RKB262126 RTQ262121:RTX262126 SDM262121:SDT262126 SNI262121:SNP262126 SXE262121:SXL262126 THA262121:THH262126 TQW262121:TRD262126 UAS262121:UAZ262126 UKO262121:UKV262126 UUK262121:UUR262126 VEG262121:VEN262126 VOC262121:VOJ262126 VXY262121:VYF262126 WHU262121:WIB262126 WRQ262121:WRX262126 FE327657:FL327662 PA327657:PH327662 YW327657:ZD327662 AIS327657:AIZ327662 ASO327657:ASV327662 BCK327657:BCR327662 BMG327657:BMN327662 BWC327657:BWJ327662 CFY327657:CGF327662 CPU327657:CQB327662 CZQ327657:CZX327662 DJM327657:DJT327662 DTI327657:DTP327662 EDE327657:EDL327662 ENA327657:ENH327662 EWW327657:EXD327662 FGS327657:FGZ327662 FQO327657:FQV327662 GAK327657:GAR327662 GKG327657:GKN327662 GUC327657:GUJ327662 HDY327657:HEF327662 HNU327657:HOB327662 HXQ327657:HXX327662 IHM327657:IHT327662 IRI327657:IRP327662 JBE327657:JBL327662 JLA327657:JLH327662 JUW327657:JVD327662 KES327657:KEZ327662 KOO327657:KOV327662 KYK327657:KYR327662 LIG327657:LIN327662 LSC327657:LSJ327662 MBY327657:MCF327662 MLU327657:MMB327662 MVQ327657:MVX327662 NFM327657:NFT327662 NPI327657:NPP327662 NZE327657:NZL327662 OJA327657:OJH327662 OSW327657:OTD327662 PCS327657:PCZ327662 PMO327657:PMV327662 PWK327657:PWR327662 QGG327657:QGN327662 QQC327657:QQJ327662 QZY327657:RAF327662 RJU327657:RKB327662 RTQ327657:RTX327662 SDM327657:SDT327662 SNI327657:SNP327662 SXE327657:SXL327662 THA327657:THH327662 TQW327657:TRD327662 UAS327657:UAZ327662 UKO327657:UKV327662 UUK327657:UUR327662 VEG327657:VEN327662 VOC327657:VOJ327662 VXY327657:VYF327662 WHU327657:WIB327662 WRQ327657:WRX327662 FE393193:FL393198 PA393193:PH393198 YW393193:ZD393198 AIS393193:AIZ393198 ASO393193:ASV393198 BCK393193:BCR393198 BMG393193:BMN393198 BWC393193:BWJ393198 CFY393193:CGF393198 CPU393193:CQB393198 CZQ393193:CZX393198 DJM393193:DJT393198 DTI393193:DTP393198 EDE393193:EDL393198 ENA393193:ENH393198 EWW393193:EXD393198 FGS393193:FGZ393198 FQO393193:FQV393198 GAK393193:GAR393198 GKG393193:GKN393198 GUC393193:GUJ393198 HDY393193:HEF393198 HNU393193:HOB393198 HXQ393193:HXX393198 IHM393193:IHT393198 IRI393193:IRP393198 JBE393193:JBL393198 JLA393193:JLH393198 JUW393193:JVD393198 KES393193:KEZ393198 KOO393193:KOV393198 KYK393193:KYR393198 LIG393193:LIN393198 LSC393193:LSJ393198 MBY393193:MCF393198 MLU393193:MMB393198 MVQ393193:MVX393198 NFM393193:NFT393198 NPI393193:NPP393198 NZE393193:NZL393198 OJA393193:OJH393198 OSW393193:OTD393198 PCS393193:PCZ393198 PMO393193:PMV393198 PWK393193:PWR393198 QGG393193:QGN393198 QQC393193:QQJ393198 QZY393193:RAF393198 RJU393193:RKB393198 RTQ393193:RTX393198 SDM393193:SDT393198 SNI393193:SNP393198 SXE393193:SXL393198 THA393193:THH393198 TQW393193:TRD393198 UAS393193:UAZ393198 UKO393193:UKV393198 UUK393193:UUR393198 VEG393193:VEN393198 VOC393193:VOJ393198 VXY393193:VYF393198 WHU393193:WIB393198 WRQ393193:WRX393198 FE458729:FL458734 PA458729:PH458734 YW458729:ZD458734 AIS458729:AIZ458734 ASO458729:ASV458734 BCK458729:BCR458734 BMG458729:BMN458734 BWC458729:BWJ458734 CFY458729:CGF458734 CPU458729:CQB458734 CZQ458729:CZX458734 DJM458729:DJT458734 DTI458729:DTP458734 EDE458729:EDL458734 ENA458729:ENH458734 EWW458729:EXD458734 FGS458729:FGZ458734 FQO458729:FQV458734 GAK458729:GAR458734 GKG458729:GKN458734 GUC458729:GUJ458734 HDY458729:HEF458734 HNU458729:HOB458734 HXQ458729:HXX458734 IHM458729:IHT458734 IRI458729:IRP458734 JBE458729:JBL458734 JLA458729:JLH458734 JUW458729:JVD458734 KES458729:KEZ458734 KOO458729:KOV458734 KYK458729:KYR458734 LIG458729:LIN458734 LSC458729:LSJ458734 MBY458729:MCF458734 MLU458729:MMB458734 MVQ458729:MVX458734 NFM458729:NFT458734 NPI458729:NPP458734 NZE458729:NZL458734 OJA458729:OJH458734 OSW458729:OTD458734 PCS458729:PCZ458734 PMO458729:PMV458734 PWK458729:PWR458734 QGG458729:QGN458734 QQC458729:QQJ458734 QZY458729:RAF458734 RJU458729:RKB458734 RTQ458729:RTX458734 SDM458729:SDT458734 SNI458729:SNP458734 SXE458729:SXL458734 THA458729:THH458734 TQW458729:TRD458734 UAS458729:UAZ458734 UKO458729:UKV458734 UUK458729:UUR458734 VEG458729:VEN458734 VOC458729:VOJ458734 VXY458729:VYF458734 WHU458729:WIB458734 WRQ458729:WRX458734 FE524265:FL524270 PA524265:PH524270 YW524265:ZD524270 AIS524265:AIZ524270 ASO524265:ASV524270 BCK524265:BCR524270 BMG524265:BMN524270 BWC524265:BWJ524270 CFY524265:CGF524270 CPU524265:CQB524270 CZQ524265:CZX524270 DJM524265:DJT524270 DTI524265:DTP524270 EDE524265:EDL524270 ENA524265:ENH524270 EWW524265:EXD524270 FGS524265:FGZ524270 FQO524265:FQV524270 GAK524265:GAR524270 GKG524265:GKN524270 GUC524265:GUJ524270 HDY524265:HEF524270 HNU524265:HOB524270 HXQ524265:HXX524270 IHM524265:IHT524270 IRI524265:IRP524270 JBE524265:JBL524270 JLA524265:JLH524270 JUW524265:JVD524270 KES524265:KEZ524270 KOO524265:KOV524270 KYK524265:KYR524270 LIG524265:LIN524270 LSC524265:LSJ524270 MBY524265:MCF524270 MLU524265:MMB524270 MVQ524265:MVX524270 NFM524265:NFT524270 NPI524265:NPP524270 NZE524265:NZL524270 OJA524265:OJH524270 OSW524265:OTD524270 PCS524265:PCZ524270 PMO524265:PMV524270 PWK524265:PWR524270 QGG524265:QGN524270 QQC524265:QQJ524270 QZY524265:RAF524270 RJU524265:RKB524270 RTQ524265:RTX524270 SDM524265:SDT524270 SNI524265:SNP524270 SXE524265:SXL524270 THA524265:THH524270 TQW524265:TRD524270 UAS524265:UAZ524270 UKO524265:UKV524270 UUK524265:UUR524270 VEG524265:VEN524270 VOC524265:VOJ524270 VXY524265:VYF524270 WHU524265:WIB524270 WRQ524265:WRX524270 FE589801:FL589806 PA589801:PH589806 YW589801:ZD589806 AIS589801:AIZ589806 ASO589801:ASV589806 BCK589801:BCR589806 BMG589801:BMN589806 BWC589801:BWJ589806 CFY589801:CGF589806 CPU589801:CQB589806 CZQ589801:CZX589806 DJM589801:DJT589806 DTI589801:DTP589806 EDE589801:EDL589806 ENA589801:ENH589806 EWW589801:EXD589806 FGS589801:FGZ589806 FQO589801:FQV589806 GAK589801:GAR589806 GKG589801:GKN589806 GUC589801:GUJ589806 HDY589801:HEF589806 HNU589801:HOB589806 HXQ589801:HXX589806 IHM589801:IHT589806 IRI589801:IRP589806 JBE589801:JBL589806 JLA589801:JLH589806 JUW589801:JVD589806 KES589801:KEZ589806 KOO589801:KOV589806 KYK589801:KYR589806 LIG589801:LIN589806 LSC589801:LSJ589806 MBY589801:MCF589806 MLU589801:MMB589806 MVQ589801:MVX589806 NFM589801:NFT589806 NPI589801:NPP589806 NZE589801:NZL589806 OJA589801:OJH589806 OSW589801:OTD589806 PCS589801:PCZ589806 PMO589801:PMV589806 PWK589801:PWR589806 QGG589801:QGN589806 QQC589801:QQJ589806 QZY589801:RAF589806 RJU589801:RKB589806 RTQ589801:RTX589806 SDM589801:SDT589806 SNI589801:SNP589806 SXE589801:SXL589806 THA589801:THH589806 TQW589801:TRD589806 UAS589801:UAZ589806 UKO589801:UKV589806 UUK589801:UUR589806 VEG589801:VEN589806 VOC589801:VOJ589806 VXY589801:VYF589806 WHU589801:WIB589806 WRQ589801:WRX589806 FE655337:FL655342 PA655337:PH655342 YW655337:ZD655342 AIS655337:AIZ655342 ASO655337:ASV655342 BCK655337:BCR655342 BMG655337:BMN655342 BWC655337:BWJ655342 CFY655337:CGF655342 CPU655337:CQB655342 CZQ655337:CZX655342 DJM655337:DJT655342 DTI655337:DTP655342 EDE655337:EDL655342 ENA655337:ENH655342 EWW655337:EXD655342 FGS655337:FGZ655342 FQO655337:FQV655342 GAK655337:GAR655342 GKG655337:GKN655342 GUC655337:GUJ655342 HDY655337:HEF655342 HNU655337:HOB655342 HXQ655337:HXX655342 IHM655337:IHT655342 IRI655337:IRP655342 JBE655337:JBL655342 JLA655337:JLH655342 JUW655337:JVD655342 KES655337:KEZ655342 KOO655337:KOV655342 KYK655337:KYR655342 LIG655337:LIN655342 LSC655337:LSJ655342 MBY655337:MCF655342 MLU655337:MMB655342 MVQ655337:MVX655342 NFM655337:NFT655342 NPI655337:NPP655342 NZE655337:NZL655342 OJA655337:OJH655342 OSW655337:OTD655342 PCS655337:PCZ655342 PMO655337:PMV655342 PWK655337:PWR655342 QGG655337:QGN655342 QQC655337:QQJ655342 QZY655337:RAF655342 RJU655337:RKB655342 RTQ655337:RTX655342 SDM655337:SDT655342 SNI655337:SNP655342 SXE655337:SXL655342 THA655337:THH655342 TQW655337:TRD655342 UAS655337:UAZ655342 UKO655337:UKV655342 UUK655337:UUR655342 VEG655337:VEN655342 VOC655337:VOJ655342 VXY655337:VYF655342 WHU655337:WIB655342 WRQ655337:WRX655342 FE720873:FL720878 PA720873:PH720878 YW720873:ZD720878 AIS720873:AIZ720878 ASO720873:ASV720878 BCK720873:BCR720878 BMG720873:BMN720878 BWC720873:BWJ720878 CFY720873:CGF720878 CPU720873:CQB720878 CZQ720873:CZX720878 DJM720873:DJT720878 DTI720873:DTP720878 EDE720873:EDL720878 ENA720873:ENH720878 EWW720873:EXD720878 FGS720873:FGZ720878 FQO720873:FQV720878 GAK720873:GAR720878 GKG720873:GKN720878 GUC720873:GUJ720878 HDY720873:HEF720878 HNU720873:HOB720878 HXQ720873:HXX720878 IHM720873:IHT720878 IRI720873:IRP720878 JBE720873:JBL720878 JLA720873:JLH720878 JUW720873:JVD720878 KES720873:KEZ720878 KOO720873:KOV720878 KYK720873:KYR720878 LIG720873:LIN720878 LSC720873:LSJ720878 MBY720873:MCF720878 MLU720873:MMB720878 MVQ720873:MVX720878 NFM720873:NFT720878 NPI720873:NPP720878 NZE720873:NZL720878 OJA720873:OJH720878 OSW720873:OTD720878 PCS720873:PCZ720878 PMO720873:PMV720878 PWK720873:PWR720878 QGG720873:QGN720878 QQC720873:QQJ720878 QZY720873:RAF720878 RJU720873:RKB720878 RTQ720873:RTX720878 SDM720873:SDT720878 SNI720873:SNP720878 SXE720873:SXL720878 THA720873:THH720878 TQW720873:TRD720878 UAS720873:UAZ720878 UKO720873:UKV720878 UUK720873:UUR720878 VEG720873:VEN720878 VOC720873:VOJ720878 VXY720873:VYF720878 WHU720873:WIB720878 WRQ720873:WRX720878 FE786409:FL786414 PA786409:PH786414 YW786409:ZD786414 AIS786409:AIZ786414 ASO786409:ASV786414 BCK786409:BCR786414 BMG786409:BMN786414 BWC786409:BWJ786414 CFY786409:CGF786414 CPU786409:CQB786414 CZQ786409:CZX786414 DJM786409:DJT786414 DTI786409:DTP786414 EDE786409:EDL786414 ENA786409:ENH786414 EWW786409:EXD786414 FGS786409:FGZ786414 FQO786409:FQV786414 GAK786409:GAR786414 GKG786409:GKN786414 GUC786409:GUJ786414 HDY786409:HEF786414 HNU786409:HOB786414 HXQ786409:HXX786414 IHM786409:IHT786414 IRI786409:IRP786414 JBE786409:JBL786414 JLA786409:JLH786414 JUW786409:JVD786414 KES786409:KEZ786414 KOO786409:KOV786414 KYK786409:KYR786414 LIG786409:LIN786414 LSC786409:LSJ786414 MBY786409:MCF786414 MLU786409:MMB786414 MVQ786409:MVX786414 NFM786409:NFT786414 NPI786409:NPP786414 NZE786409:NZL786414 OJA786409:OJH786414 OSW786409:OTD786414 PCS786409:PCZ786414 PMO786409:PMV786414 PWK786409:PWR786414 QGG786409:QGN786414 QQC786409:QQJ786414 QZY786409:RAF786414 RJU786409:RKB786414 RTQ786409:RTX786414 SDM786409:SDT786414 SNI786409:SNP786414 SXE786409:SXL786414 THA786409:THH786414 TQW786409:TRD786414 UAS786409:UAZ786414 UKO786409:UKV786414 UUK786409:UUR786414 VEG786409:VEN786414 VOC786409:VOJ786414 VXY786409:VYF786414 WHU786409:WIB786414 WRQ786409:WRX786414 FE851945:FL851950 PA851945:PH851950 YW851945:ZD851950 AIS851945:AIZ851950 ASO851945:ASV851950 BCK851945:BCR851950 BMG851945:BMN851950 BWC851945:BWJ851950 CFY851945:CGF851950 CPU851945:CQB851950 CZQ851945:CZX851950 DJM851945:DJT851950 DTI851945:DTP851950 EDE851945:EDL851950 ENA851945:ENH851950 EWW851945:EXD851950 FGS851945:FGZ851950 FQO851945:FQV851950 GAK851945:GAR851950 GKG851945:GKN851950 GUC851945:GUJ851950 HDY851945:HEF851950 HNU851945:HOB851950 HXQ851945:HXX851950 IHM851945:IHT851950 IRI851945:IRP851950 JBE851945:JBL851950 JLA851945:JLH851950 JUW851945:JVD851950 KES851945:KEZ851950 KOO851945:KOV851950 KYK851945:KYR851950 LIG851945:LIN851950 LSC851945:LSJ851950 MBY851945:MCF851950 MLU851945:MMB851950 MVQ851945:MVX851950 NFM851945:NFT851950 NPI851945:NPP851950 NZE851945:NZL851950 OJA851945:OJH851950 OSW851945:OTD851950 PCS851945:PCZ851950 PMO851945:PMV851950 PWK851945:PWR851950 QGG851945:QGN851950 QQC851945:QQJ851950 QZY851945:RAF851950 RJU851945:RKB851950 RTQ851945:RTX851950 SDM851945:SDT851950 SNI851945:SNP851950 SXE851945:SXL851950 THA851945:THH851950 TQW851945:TRD851950 UAS851945:UAZ851950 UKO851945:UKV851950 UUK851945:UUR851950 VEG851945:VEN851950 VOC851945:VOJ851950 VXY851945:VYF851950 WHU851945:WIB851950 WRQ851945:WRX851950 FE917481:FL917486 PA917481:PH917486 YW917481:ZD917486 AIS917481:AIZ917486 ASO917481:ASV917486 BCK917481:BCR917486 BMG917481:BMN917486 BWC917481:BWJ917486 CFY917481:CGF917486 CPU917481:CQB917486 CZQ917481:CZX917486 DJM917481:DJT917486 DTI917481:DTP917486 EDE917481:EDL917486 ENA917481:ENH917486 EWW917481:EXD917486 FGS917481:FGZ917486 FQO917481:FQV917486 GAK917481:GAR917486 GKG917481:GKN917486 GUC917481:GUJ917486 HDY917481:HEF917486 HNU917481:HOB917486 HXQ917481:HXX917486 IHM917481:IHT917486 IRI917481:IRP917486 JBE917481:JBL917486 JLA917481:JLH917486 JUW917481:JVD917486 KES917481:KEZ917486 KOO917481:KOV917486 KYK917481:KYR917486 LIG917481:LIN917486 LSC917481:LSJ917486 MBY917481:MCF917486 MLU917481:MMB917486 MVQ917481:MVX917486 NFM917481:NFT917486 NPI917481:NPP917486 NZE917481:NZL917486 OJA917481:OJH917486 OSW917481:OTD917486 PCS917481:PCZ917486 PMO917481:PMV917486 PWK917481:PWR917486 QGG917481:QGN917486 QQC917481:QQJ917486 QZY917481:RAF917486 RJU917481:RKB917486 RTQ917481:RTX917486 SDM917481:SDT917486 SNI917481:SNP917486 SXE917481:SXL917486 THA917481:THH917486 TQW917481:TRD917486 UAS917481:UAZ917486 UKO917481:UKV917486 UUK917481:UUR917486 VEG917481:VEN917486 VOC917481:VOJ917486 VXY917481:VYF917486 WHU917481:WIB917486 WRQ917481:WRX917486" xr:uid="{0B4A9982-0581-4256-A7BD-537BA00C93C9}">
       <formula1>"サーバ,クライアント"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WRC982982:WRQ983019 VNO982982:VOC983019 VDS982982:VEG983019 UTW982982:UUK983019 UKA982982:UKO983019 UAE982982:UAS983019 TQI982982:TQW983019 TGM982982:THA983019 SWQ982982:SXE983019 SMU982982:SNI983019 SCY982982:SDM983019 RTC982982:RTQ983019 RJG982982:RJU983019 QZK982982:QZY983019 QPO982982:QQC983019 QFS982982:QGG983019 PVW982982:PWK983019 PMA982982:PMO983019 PCE982982:PCS983019 OSI982982:OSW983019 OIM982982:OJA983019 NYQ982982:NZE983019 NOU982982:NPI983019 NEY982982:NFM983019 MVC982982:MVQ983019 MLG982982:MLU983019 MBK982982:MBY983019 LRO982982:LSC983019 LHS982982:LIG983019 KXW982982:KYK983019 KOA982982:KOO983019 KEE982982:KES983019 JUI982982:JUW983019 JKM982982:JLA983019 JAQ982982:JBE983019 IQU982982:IRI983019 IGY982982:IHM983019 HXC982982:HXQ983019 HNG982982:HNU983019 HDK982982:HDY983019 GTO982982:GUC983019 GJS982982:GKG983019 FZW982982:GAK983019 FQA982982:FQO983019 FGE982982:FGS983019 EWI982982:EWW983019 EMM982982:ENA983019 ECQ982982:EDE983019 DSU982982:DTI983019 DIY982982:DJM983019 CZC982982:CZQ983019 CPG982982:CPU983019 CFK982982:CFY983019 BVO982982:BWC983019 BLS982982:BMG983019 BBW982982:BCK983019 ASA982982:ASO983019 AIE982982:AIS983019 YI982982:YW983019 OM982982:PA983019 EQ982982:FE983019 WRC917446:WRQ917483 WHG917446:WHU917483 VXK917446:VXY917483 VNO917446:VOC917483 VDS917446:VEG917483 UTW917446:UUK917483 UKA917446:UKO917483 UAE917446:UAS917483 TQI917446:TQW917483 TGM917446:THA917483 SWQ917446:SXE917483 SMU917446:SNI917483 SCY917446:SDM917483 RTC917446:RTQ917483 RJG917446:RJU917483 QZK917446:QZY917483 QPO917446:QQC917483 QFS917446:QGG917483 PVW917446:PWK917483 PMA917446:PMO917483 PCE917446:PCS917483 OSI917446:OSW917483 OIM917446:OJA917483 NYQ917446:NZE917483 NOU917446:NPI917483 NEY917446:NFM917483 MVC917446:MVQ917483 MLG917446:MLU917483 MBK917446:MBY917483 LRO917446:LSC917483 LHS917446:LIG917483 KXW917446:KYK917483 KOA917446:KOO917483 KEE917446:KES917483 JUI917446:JUW917483 JKM917446:JLA917483 JAQ917446:JBE917483 IQU917446:IRI917483 IGY917446:IHM917483 HXC917446:HXQ917483 HNG917446:HNU917483 HDK917446:HDY917483 GTO917446:GUC917483 GJS917446:GKG917483 FZW917446:GAK917483 FQA917446:FQO917483 FGE917446:FGS917483 EWI917446:EWW917483 EMM917446:ENA917483 ECQ917446:EDE917483 DSU917446:DTI917483 DIY917446:DJM917483 CZC917446:CZQ917483 CPG917446:CPU917483 CFK917446:CFY917483 BVO917446:BWC917483 BLS917446:BMG917483 BBW917446:BCK917483 ASA917446:ASO917483 AIE917446:AIS917483 YI917446:YW917483 OM917446:PA917483 EQ917446:FE917483 WRC851910:WRQ851947 WHG851910:WHU851947 VXK851910:VXY851947 VNO851910:VOC851947 VDS851910:VEG851947 UTW851910:UUK851947 UKA851910:UKO851947 UAE851910:UAS851947 TQI851910:TQW851947 TGM851910:THA851947 SWQ851910:SXE851947 SMU851910:SNI851947 SCY851910:SDM851947 RTC851910:RTQ851947 RJG851910:RJU851947 QZK851910:QZY851947 QPO851910:QQC851947 QFS851910:QGG851947 PVW851910:PWK851947 PMA851910:PMO851947 PCE851910:PCS851947 OSI851910:OSW851947 OIM851910:OJA851947 NYQ851910:NZE851947 NOU851910:NPI851947 NEY851910:NFM851947 MVC851910:MVQ851947 MLG851910:MLU851947 MBK851910:MBY851947 LRO851910:LSC851947 LHS851910:LIG851947 KXW851910:KYK851947 KOA851910:KOO851947 KEE851910:KES851947 JUI851910:JUW851947 JKM851910:JLA851947 JAQ851910:JBE851947 IQU851910:IRI851947 IGY851910:IHM851947 HXC851910:HXQ851947 HNG851910:HNU851947 HDK851910:HDY851947 GTO851910:GUC851947 GJS851910:GKG851947 FZW851910:GAK851947 FQA851910:FQO851947 FGE851910:FGS851947 EWI851910:EWW851947 EMM851910:ENA851947 ECQ851910:EDE851947 DSU851910:DTI851947 DIY851910:DJM851947 CZC851910:CZQ851947 CPG851910:CPU851947 CFK851910:CFY851947 BVO851910:BWC851947 BLS851910:BMG851947 BBW851910:BCK851947 ASA851910:ASO851947 AIE851910:AIS851947 YI851910:YW851947 OM851910:PA851947 EQ851910:FE851947 WRC786374:WRQ786411 WHG786374:WHU786411 VXK786374:VXY786411 VNO786374:VOC786411 VDS786374:VEG786411 UTW786374:UUK786411 UKA786374:UKO786411 UAE786374:UAS786411 TQI786374:TQW786411 TGM786374:THA786411 SWQ786374:SXE786411 SMU786374:SNI786411 SCY786374:SDM786411 RTC786374:RTQ786411 RJG786374:RJU786411 QZK786374:QZY786411 QPO786374:QQC786411 QFS786374:QGG786411 PVW786374:PWK786411 PMA786374:PMO786411 PCE786374:PCS786411 OSI786374:OSW786411 OIM786374:OJA786411 NYQ786374:NZE786411 NOU786374:NPI786411 NEY786374:NFM786411 MVC786374:MVQ786411 MLG786374:MLU786411 MBK786374:MBY786411 LRO786374:LSC786411 LHS786374:LIG786411 KXW786374:KYK786411 KOA786374:KOO786411 KEE786374:KES786411 JUI786374:JUW786411 JKM786374:JLA786411 JAQ786374:JBE786411 IQU786374:IRI786411 IGY786374:IHM786411 HXC786374:HXQ786411 HNG786374:HNU786411 HDK786374:HDY786411 GTO786374:GUC786411 GJS786374:GKG786411 FZW786374:GAK786411 FQA786374:FQO786411 FGE786374:FGS786411 EWI786374:EWW786411 EMM786374:ENA786411 ECQ786374:EDE786411 DSU786374:DTI786411 DIY786374:DJM786411 CZC786374:CZQ786411 CPG786374:CPU786411 CFK786374:CFY786411 BVO786374:BWC786411 BLS786374:BMG786411 BBW786374:BCK786411 ASA786374:ASO786411 AIE786374:AIS786411 YI786374:YW786411 OM786374:PA786411 EQ786374:FE786411 WRC720838:WRQ720875 WHG720838:WHU720875 VXK720838:VXY720875 VNO720838:VOC720875 VDS720838:VEG720875 UTW720838:UUK720875 UKA720838:UKO720875 UAE720838:UAS720875 TQI720838:TQW720875 TGM720838:THA720875 SWQ720838:SXE720875 SMU720838:SNI720875 SCY720838:SDM720875 RTC720838:RTQ720875 RJG720838:RJU720875 QZK720838:QZY720875 QPO720838:QQC720875 QFS720838:QGG720875 PVW720838:PWK720875 PMA720838:PMO720875 PCE720838:PCS720875 OSI720838:OSW720875 OIM720838:OJA720875 NYQ720838:NZE720875 NOU720838:NPI720875 NEY720838:NFM720875 MVC720838:MVQ720875 MLG720838:MLU720875 MBK720838:MBY720875 LRO720838:LSC720875 LHS720838:LIG720875 KXW720838:KYK720875 KOA720838:KOO720875 KEE720838:KES720875 JUI720838:JUW720875 JKM720838:JLA720875 JAQ720838:JBE720875 IQU720838:IRI720875 IGY720838:IHM720875 HXC720838:HXQ720875 HNG720838:HNU720875 HDK720838:HDY720875 GTO720838:GUC720875 GJS720838:GKG720875 FZW720838:GAK720875 FQA720838:FQO720875 FGE720838:FGS720875 EWI720838:EWW720875 EMM720838:ENA720875 ECQ720838:EDE720875 DSU720838:DTI720875 DIY720838:DJM720875 CZC720838:CZQ720875 CPG720838:CPU720875 CFK720838:CFY720875 BVO720838:BWC720875 BLS720838:BMG720875 BBW720838:BCK720875 ASA720838:ASO720875 AIE720838:AIS720875 YI720838:YW720875 OM720838:PA720875 EQ720838:FE720875 WRC655302:WRQ655339 WHG655302:WHU655339 VXK655302:VXY655339 VNO655302:VOC655339 VDS655302:VEG655339 UTW655302:UUK655339 UKA655302:UKO655339 UAE655302:UAS655339 TQI655302:TQW655339 TGM655302:THA655339 SWQ655302:SXE655339 SMU655302:SNI655339 SCY655302:SDM655339 RTC655302:RTQ655339 RJG655302:RJU655339 QZK655302:QZY655339 QPO655302:QQC655339 QFS655302:QGG655339 PVW655302:PWK655339 PMA655302:PMO655339 PCE655302:PCS655339 OSI655302:OSW655339 OIM655302:OJA655339 NYQ655302:NZE655339 NOU655302:NPI655339 NEY655302:NFM655339 MVC655302:MVQ655339 MLG655302:MLU655339 MBK655302:MBY655339 LRO655302:LSC655339 LHS655302:LIG655339 KXW655302:KYK655339 KOA655302:KOO655339 KEE655302:KES655339 JUI655302:JUW655339 JKM655302:JLA655339 JAQ655302:JBE655339 IQU655302:IRI655339 IGY655302:IHM655339 HXC655302:HXQ655339 HNG655302:HNU655339 HDK655302:HDY655339 GTO655302:GUC655339 GJS655302:GKG655339 FZW655302:GAK655339 FQA655302:FQO655339 FGE655302:FGS655339 EWI655302:EWW655339 EMM655302:ENA655339 ECQ655302:EDE655339 DSU655302:DTI655339 DIY655302:DJM655339 CZC655302:CZQ655339 CPG655302:CPU655339 CFK655302:CFY655339 BVO655302:BWC655339 BLS655302:BMG655339 BBW655302:BCK655339 ASA655302:ASO655339 AIE655302:AIS655339 YI655302:YW655339 OM655302:PA655339 EQ655302:FE655339 WRC589766:WRQ589803 WHG589766:WHU589803 VXK589766:VXY589803 VNO589766:VOC589803 VDS589766:VEG589803 UTW589766:UUK589803 UKA589766:UKO589803 UAE589766:UAS589803 TQI589766:TQW589803 TGM589766:THA589803 SWQ589766:SXE589803 SMU589766:SNI589803 SCY589766:SDM589803 RTC589766:RTQ589803 RJG589766:RJU589803 QZK589766:QZY589803 QPO589766:QQC589803 QFS589766:QGG589803 PVW589766:PWK589803 PMA589766:PMO589803 PCE589766:PCS589803 OSI589766:OSW589803 OIM589766:OJA589803 NYQ589766:NZE589803 NOU589766:NPI589803 NEY589766:NFM589803 MVC589766:MVQ589803 MLG589766:MLU589803 MBK589766:MBY589803 LRO589766:LSC589803 LHS589766:LIG589803 KXW589766:KYK589803 KOA589766:KOO589803 KEE589766:KES589803 JUI589766:JUW589803 JKM589766:JLA589803 JAQ589766:JBE589803 IQU589766:IRI589803 IGY589766:IHM589803 HXC589766:HXQ589803 HNG589766:HNU589803 HDK589766:HDY589803 GTO589766:GUC589803 GJS589766:GKG589803 FZW589766:GAK589803 FQA589766:FQO589803 FGE589766:FGS589803 EWI589766:EWW589803 EMM589766:ENA589803 ECQ589766:EDE589803 DSU589766:DTI589803 DIY589766:DJM589803 CZC589766:CZQ589803 CPG589766:CPU589803 CFK589766:CFY589803 BVO589766:BWC589803 BLS589766:BMG589803 BBW589766:BCK589803 ASA589766:ASO589803 AIE589766:AIS589803 YI589766:YW589803 OM589766:PA589803 EQ589766:FE589803 WRC524230:WRQ524267 WHG524230:WHU524267 VXK524230:VXY524267 VNO524230:VOC524267 VDS524230:VEG524267 UTW524230:UUK524267 UKA524230:UKO524267 UAE524230:UAS524267 TQI524230:TQW524267 TGM524230:THA524267 SWQ524230:SXE524267 SMU524230:SNI524267 SCY524230:SDM524267 RTC524230:RTQ524267 RJG524230:RJU524267 QZK524230:QZY524267 QPO524230:QQC524267 QFS524230:QGG524267 PVW524230:PWK524267 PMA524230:PMO524267 PCE524230:PCS524267 OSI524230:OSW524267 OIM524230:OJA524267 NYQ524230:NZE524267 NOU524230:NPI524267 NEY524230:NFM524267 MVC524230:MVQ524267 MLG524230:MLU524267 MBK524230:MBY524267 LRO524230:LSC524267 LHS524230:LIG524267 KXW524230:KYK524267 KOA524230:KOO524267 KEE524230:KES524267 JUI524230:JUW524267 JKM524230:JLA524267 JAQ524230:JBE524267 IQU524230:IRI524267 IGY524230:IHM524267 HXC524230:HXQ524267 HNG524230:HNU524267 HDK524230:HDY524267 GTO524230:GUC524267 GJS524230:GKG524267 FZW524230:GAK524267 FQA524230:FQO524267 FGE524230:FGS524267 EWI524230:EWW524267 EMM524230:ENA524267 ECQ524230:EDE524267 DSU524230:DTI524267 DIY524230:DJM524267 CZC524230:CZQ524267 CPG524230:CPU524267 CFK524230:CFY524267 BVO524230:BWC524267 BLS524230:BMG524267 BBW524230:BCK524267 ASA524230:ASO524267 AIE524230:AIS524267 YI524230:YW524267 OM524230:PA524267 EQ524230:FE524267 WRC458694:WRQ458731 WHG458694:WHU458731 VXK458694:VXY458731 VNO458694:VOC458731 VDS458694:VEG458731 UTW458694:UUK458731 UKA458694:UKO458731 UAE458694:UAS458731 TQI458694:TQW458731 TGM458694:THA458731 SWQ458694:SXE458731 SMU458694:SNI458731 SCY458694:SDM458731 RTC458694:RTQ458731 RJG458694:RJU458731 QZK458694:QZY458731 QPO458694:QQC458731 QFS458694:QGG458731 PVW458694:PWK458731 PMA458694:PMO458731 PCE458694:PCS458731 OSI458694:OSW458731 OIM458694:OJA458731 NYQ458694:NZE458731 NOU458694:NPI458731 NEY458694:NFM458731 MVC458694:MVQ458731 MLG458694:MLU458731 MBK458694:MBY458731 LRO458694:LSC458731 LHS458694:LIG458731 KXW458694:KYK458731 KOA458694:KOO458731 KEE458694:KES458731 JUI458694:JUW458731 JKM458694:JLA458731 JAQ458694:JBE458731 IQU458694:IRI458731 IGY458694:IHM458731 HXC458694:HXQ458731 HNG458694:HNU458731 HDK458694:HDY458731 GTO458694:GUC458731 GJS458694:GKG458731 FZW458694:GAK458731 FQA458694:FQO458731 FGE458694:FGS458731 EWI458694:EWW458731 EMM458694:ENA458731 ECQ458694:EDE458731 DSU458694:DTI458731 DIY458694:DJM458731 CZC458694:CZQ458731 CPG458694:CPU458731 CFK458694:CFY458731 BVO458694:BWC458731 BLS458694:BMG458731 BBW458694:BCK458731 ASA458694:ASO458731 AIE458694:AIS458731 YI458694:YW458731 OM458694:PA458731 EQ458694:FE458731 WRC393158:WRQ393195 WHG393158:WHU393195 VXK393158:VXY393195 VNO393158:VOC393195 VDS393158:VEG393195 UTW393158:UUK393195 UKA393158:UKO393195 UAE393158:UAS393195 TQI393158:TQW393195 TGM393158:THA393195 SWQ393158:SXE393195 SMU393158:SNI393195 SCY393158:SDM393195 RTC393158:RTQ393195 RJG393158:RJU393195 QZK393158:QZY393195 QPO393158:QQC393195 QFS393158:QGG393195 PVW393158:PWK393195 PMA393158:PMO393195 PCE393158:PCS393195 OSI393158:OSW393195 OIM393158:OJA393195 NYQ393158:NZE393195 NOU393158:NPI393195 NEY393158:NFM393195 MVC393158:MVQ393195 MLG393158:MLU393195 MBK393158:MBY393195 LRO393158:LSC393195 LHS393158:LIG393195 KXW393158:KYK393195 KOA393158:KOO393195 KEE393158:KES393195 JUI393158:JUW393195 JKM393158:JLA393195 JAQ393158:JBE393195 IQU393158:IRI393195 IGY393158:IHM393195 HXC393158:HXQ393195 HNG393158:HNU393195 HDK393158:HDY393195 GTO393158:GUC393195 GJS393158:GKG393195 FZW393158:GAK393195 FQA393158:FQO393195 FGE393158:FGS393195 EWI393158:EWW393195 EMM393158:ENA393195 ECQ393158:EDE393195 DSU393158:DTI393195 DIY393158:DJM393195 CZC393158:CZQ393195 CPG393158:CPU393195 CFK393158:CFY393195 BVO393158:BWC393195 BLS393158:BMG393195 BBW393158:BCK393195 ASA393158:ASO393195 AIE393158:AIS393195 YI393158:YW393195 OM393158:PA393195 EQ393158:FE393195 WRC327622:WRQ327659 WHG327622:WHU327659 VXK327622:VXY327659 VNO327622:VOC327659 VDS327622:VEG327659 UTW327622:UUK327659 UKA327622:UKO327659 UAE327622:UAS327659 TQI327622:TQW327659 TGM327622:THA327659 SWQ327622:SXE327659 SMU327622:SNI327659 SCY327622:SDM327659 RTC327622:RTQ327659 RJG327622:RJU327659 QZK327622:QZY327659 QPO327622:QQC327659 QFS327622:QGG327659 PVW327622:PWK327659 PMA327622:PMO327659 PCE327622:PCS327659 OSI327622:OSW327659 OIM327622:OJA327659 NYQ327622:NZE327659 NOU327622:NPI327659 NEY327622:NFM327659 MVC327622:MVQ327659 MLG327622:MLU327659 MBK327622:MBY327659 LRO327622:LSC327659 LHS327622:LIG327659 KXW327622:KYK327659 KOA327622:KOO327659 KEE327622:KES327659 JUI327622:JUW327659 JKM327622:JLA327659 JAQ327622:JBE327659 IQU327622:IRI327659 IGY327622:IHM327659 HXC327622:HXQ327659 HNG327622:HNU327659 HDK327622:HDY327659 GTO327622:GUC327659 GJS327622:GKG327659 FZW327622:GAK327659 FQA327622:FQO327659 FGE327622:FGS327659 EWI327622:EWW327659 EMM327622:ENA327659 ECQ327622:EDE327659 DSU327622:DTI327659 DIY327622:DJM327659 CZC327622:CZQ327659 CPG327622:CPU327659 CFK327622:CFY327659 BVO327622:BWC327659 BLS327622:BMG327659 BBW327622:BCK327659 ASA327622:ASO327659 AIE327622:AIS327659 YI327622:YW327659 OM327622:PA327659 EQ327622:FE327659 WRC262086:WRQ262123 WHG262086:WHU262123 VXK262086:VXY262123 VNO262086:VOC262123 VDS262086:VEG262123 UTW262086:UUK262123 UKA262086:UKO262123 UAE262086:UAS262123 TQI262086:TQW262123 TGM262086:THA262123 SWQ262086:SXE262123 SMU262086:SNI262123 SCY262086:SDM262123 RTC262086:RTQ262123 RJG262086:RJU262123 QZK262086:QZY262123 QPO262086:QQC262123 QFS262086:QGG262123 PVW262086:PWK262123 PMA262086:PMO262123 PCE262086:PCS262123 OSI262086:OSW262123 OIM262086:OJA262123 NYQ262086:NZE262123 NOU262086:NPI262123 NEY262086:NFM262123 MVC262086:MVQ262123 MLG262086:MLU262123 MBK262086:MBY262123 LRO262086:LSC262123 LHS262086:LIG262123 KXW262086:KYK262123 KOA262086:KOO262123 KEE262086:KES262123 JUI262086:JUW262123 JKM262086:JLA262123 JAQ262086:JBE262123 IQU262086:IRI262123 IGY262086:IHM262123 HXC262086:HXQ262123 HNG262086:HNU262123 HDK262086:HDY262123 GTO262086:GUC262123 GJS262086:GKG262123 FZW262086:GAK262123 FQA262086:FQO262123 FGE262086:FGS262123 EWI262086:EWW262123 EMM262086:ENA262123 ECQ262086:EDE262123 DSU262086:DTI262123 DIY262086:DJM262123 CZC262086:CZQ262123 CPG262086:CPU262123 CFK262086:CFY262123 BVO262086:BWC262123 BLS262086:BMG262123 BBW262086:BCK262123 ASA262086:ASO262123 AIE262086:AIS262123 YI262086:YW262123 OM262086:PA262123 EQ262086:FE262123 WRC196550:WRQ196587 WHG196550:WHU196587 VXK196550:VXY196587 VNO196550:VOC196587 VDS196550:VEG196587 UTW196550:UUK196587 UKA196550:UKO196587 UAE196550:UAS196587 TQI196550:TQW196587 TGM196550:THA196587 SWQ196550:SXE196587 SMU196550:SNI196587 SCY196550:SDM196587 RTC196550:RTQ196587 RJG196550:RJU196587 QZK196550:QZY196587 QPO196550:QQC196587 QFS196550:QGG196587 PVW196550:PWK196587 PMA196550:PMO196587 PCE196550:PCS196587 OSI196550:OSW196587 OIM196550:OJA196587 NYQ196550:NZE196587 NOU196550:NPI196587 NEY196550:NFM196587 MVC196550:MVQ196587 MLG196550:MLU196587 MBK196550:MBY196587 LRO196550:LSC196587 LHS196550:LIG196587 KXW196550:KYK196587 KOA196550:KOO196587 KEE196550:KES196587 JUI196550:JUW196587 JKM196550:JLA196587 JAQ196550:JBE196587 IQU196550:IRI196587 IGY196550:IHM196587 HXC196550:HXQ196587 HNG196550:HNU196587 HDK196550:HDY196587 GTO196550:GUC196587 GJS196550:GKG196587 FZW196550:GAK196587 FQA196550:FQO196587 FGE196550:FGS196587 EWI196550:EWW196587 EMM196550:ENA196587 ECQ196550:EDE196587 DSU196550:DTI196587 DIY196550:DJM196587 CZC196550:CZQ196587 CPG196550:CPU196587 CFK196550:CFY196587 BVO196550:BWC196587 BLS196550:BMG196587 BBW196550:BCK196587 ASA196550:ASO196587 AIE196550:AIS196587 YI196550:YW196587 OM196550:PA196587 EQ196550:FE196587 WRC131014:WRQ131051 WHG131014:WHU131051 VXK131014:VXY131051 VNO131014:VOC131051 VDS131014:VEG131051 UTW131014:UUK131051 UKA131014:UKO131051 UAE131014:UAS131051 TQI131014:TQW131051 TGM131014:THA131051 SWQ131014:SXE131051 SMU131014:SNI131051 SCY131014:SDM131051 RTC131014:RTQ131051 RJG131014:RJU131051 QZK131014:QZY131051 QPO131014:QQC131051 QFS131014:QGG131051 PVW131014:PWK131051 PMA131014:PMO131051 PCE131014:PCS131051 OSI131014:OSW131051 OIM131014:OJA131051 NYQ131014:NZE131051 NOU131014:NPI131051 NEY131014:NFM131051 MVC131014:MVQ131051 MLG131014:MLU131051 MBK131014:MBY131051 LRO131014:LSC131051 LHS131014:LIG131051 KXW131014:KYK131051 KOA131014:KOO131051 KEE131014:KES131051 JUI131014:JUW131051 JKM131014:JLA131051 JAQ131014:JBE131051 IQU131014:IRI131051 IGY131014:IHM131051 HXC131014:HXQ131051 HNG131014:HNU131051 HDK131014:HDY131051 GTO131014:GUC131051 GJS131014:GKG131051 FZW131014:GAK131051 FQA131014:FQO131051 FGE131014:FGS131051 EWI131014:EWW131051 EMM131014:ENA131051 ECQ131014:EDE131051 DSU131014:DTI131051 DIY131014:DJM131051 CZC131014:CZQ131051 CPG131014:CPU131051 CFK131014:CFY131051 BVO131014:BWC131051 BLS131014:BMG131051 BBW131014:BCK131051 ASA131014:ASO131051 AIE131014:AIS131051 YI131014:YW131051 OM131014:PA131051 EQ131014:FE131051 WRC65478:WRQ65515 WHG65478:WHU65515 VXK65478:VXY65515 VNO65478:VOC65515 VDS65478:VEG65515 UTW65478:UUK65515 UKA65478:UKO65515 UAE65478:UAS65515 TQI65478:TQW65515 TGM65478:THA65515 SWQ65478:SXE65515 SMU65478:SNI65515 SCY65478:SDM65515 RTC65478:RTQ65515 RJG65478:RJU65515 QZK65478:QZY65515 QPO65478:QQC65515 QFS65478:QGG65515 PVW65478:PWK65515 PMA65478:PMO65515 PCE65478:PCS65515 OSI65478:OSW65515 OIM65478:OJA65515 NYQ65478:NZE65515 NOU65478:NPI65515 NEY65478:NFM65515 MVC65478:MVQ65515 MLG65478:MLU65515 MBK65478:MBY65515 LRO65478:LSC65515 LHS65478:LIG65515 KXW65478:KYK65515 KOA65478:KOO65515 KEE65478:KES65515 JUI65478:JUW65515 JKM65478:JLA65515 JAQ65478:JBE65515 IQU65478:IRI65515 IGY65478:IHM65515 HXC65478:HXQ65515 HNG65478:HNU65515 HDK65478:HDY65515 GTO65478:GUC65515 GJS65478:GKG65515 FZW65478:GAK65515 FQA65478:FQO65515 FGE65478:FGS65515 EWI65478:EWW65515 EMM65478:ENA65515 ECQ65478:EDE65515 DSU65478:DTI65515 DIY65478:DJM65515 CZC65478:CZQ65515 CPG65478:CPU65515 CFK65478:CFY65515 BVO65478:BWC65515 BLS65478:BMG65515 BBW65478:BCK65515 ASA65478:ASO65515 AIE65478:AIS65515 YI65478:YW65515 OM65478:PA65515 EQ65478:FE65515 WHG982982:WHU983019 VXK982982:VXY983019 WHG2:WHU13 WRC2:WRQ13 EQ2:FE13 OM2:PA13 YI2:YW13 AIE2:AIS13 ASA2:ASO13 BBW2:BCK13 BLS2:BMG13 BVO2:BWC13 CFK2:CFY13 CPG2:CPU13 CZC2:CZQ13 DIY2:DJM13 DSU2:DTI13 ECQ2:EDE13 EMM2:ENA13 EWI2:EWW13 FGE2:FGS13 FQA2:FQO13 FZW2:GAK13 GJS2:GKG13 GTO2:GUC13 HDK2:HDY13 HNG2:HNU13 HXC2:HXQ13 IGY2:IHM13 IQU2:IRI13 JAQ2:JBE13 JKM2:JLA13 JUI2:JUW13 KEE2:KES13 KOA2:KOO13 KXW2:KYK13 LHS2:LIG13 LRO2:LSC13 MBK2:MBY13 MLG2:MLU13 MVC2:MVQ13 NEY2:NFM13 NOU2:NPI13 NYQ2:NZE13 OIM2:OJA13 OSI2:OSW13 PCE2:PCS13 PMA2:PMO13 PVW2:PWK13 QFS2:QGG13 QPO2:QQC13 QZK2:QZY13 RJG2:RJU13 RTC2:RTQ13 SCY2:SDM13 SMU2:SNI13 SWQ2:SXE13 TGM2:THA13 TQI2:TQW13 UAE2:UAS13 UKA2:UKO13 UTW2:UUK13 VDS2:VEG13 VNO2:VOC13 VXK2:VXY13" xr:uid="{67EFF628-81BF-4B74-9C52-DD1574F85ABA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WRC982976:WRQ983013 VNO982976:VOC983013 VDS982976:VEG983013 UTW982976:UUK983013 UKA982976:UKO983013 UAE982976:UAS983013 TQI982976:TQW983013 TGM982976:THA983013 SWQ982976:SXE983013 SMU982976:SNI983013 SCY982976:SDM983013 RTC982976:RTQ983013 RJG982976:RJU983013 QZK982976:QZY983013 QPO982976:QQC983013 QFS982976:QGG983013 PVW982976:PWK983013 PMA982976:PMO983013 PCE982976:PCS983013 OSI982976:OSW983013 OIM982976:OJA983013 NYQ982976:NZE983013 NOU982976:NPI983013 NEY982976:NFM983013 MVC982976:MVQ983013 MLG982976:MLU983013 MBK982976:MBY983013 LRO982976:LSC983013 LHS982976:LIG983013 KXW982976:KYK983013 KOA982976:KOO983013 KEE982976:KES983013 JUI982976:JUW983013 JKM982976:JLA983013 JAQ982976:JBE983013 IQU982976:IRI983013 IGY982976:IHM983013 HXC982976:HXQ983013 HNG982976:HNU983013 HDK982976:HDY983013 GTO982976:GUC983013 GJS982976:GKG983013 FZW982976:GAK983013 FQA982976:FQO983013 FGE982976:FGS983013 EWI982976:EWW983013 EMM982976:ENA983013 ECQ982976:EDE983013 DSU982976:DTI983013 DIY982976:DJM983013 CZC982976:CZQ983013 CPG982976:CPU983013 CFK982976:CFY983013 BVO982976:BWC983013 BLS982976:BMG983013 BBW982976:BCK983013 ASA982976:ASO983013 AIE982976:AIS983013 YI982976:YW983013 OM982976:PA983013 EQ982976:FE983013 WRC917440:WRQ917477 WHG917440:WHU917477 VXK917440:VXY917477 VNO917440:VOC917477 VDS917440:VEG917477 UTW917440:UUK917477 UKA917440:UKO917477 UAE917440:UAS917477 TQI917440:TQW917477 TGM917440:THA917477 SWQ917440:SXE917477 SMU917440:SNI917477 SCY917440:SDM917477 RTC917440:RTQ917477 RJG917440:RJU917477 QZK917440:QZY917477 QPO917440:QQC917477 QFS917440:QGG917477 PVW917440:PWK917477 PMA917440:PMO917477 PCE917440:PCS917477 OSI917440:OSW917477 OIM917440:OJA917477 NYQ917440:NZE917477 NOU917440:NPI917477 NEY917440:NFM917477 MVC917440:MVQ917477 MLG917440:MLU917477 MBK917440:MBY917477 LRO917440:LSC917477 LHS917440:LIG917477 KXW917440:KYK917477 KOA917440:KOO917477 KEE917440:KES917477 JUI917440:JUW917477 JKM917440:JLA917477 JAQ917440:JBE917477 IQU917440:IRI917477 IGY917440:IHM917477 HXC917440:HXQ917477 HNG917440:HNU917477 HDK917440:HDY917477 GTO917440:GUC917477 GJS917440:GKG917477 FZW917440:GAK917477 FQA917440:FQO917477 FGE917440:FGS917477 EWI917440:EWW917477 EMM917440:ENA917477 ECQ917440:EDE917477 DSU917440:DTI917477 DIY917440:DJM917477 CZC917440:CZQ917477 CPG917440:CPU917477 CFK917440:CFY917477 BVO917440:BWC917477 BLS917440:BMG917477 BBW917440:BCK917477 ASA917440:ASO917477 AIE917440:AIS917477 YI917440:YW917477 OM917440:PA917477 EQ917440:FE917477 WRC851904:WRQ851941 WHG851904:WHU851941 VXK851904:VXY851941 VNO851904:VOC851941 VDS851904:VEG851941 UTW851904:UUK851941 UKA851904:UKO851941 UAE851904:UAS851941 TQI851904:TQW851941 TGM851904:THA851941 SWQ851904:SXE851941 SMU851904:SNI851941 SCY851904:SDM851941 RTC851904:RTQ851941 RJG851904:RJU851941 QZK851904:QZY851941 QPO851904:QQC851941 QFS851904:QGG851941 PVW851904:PWK851941 PMA851904:PMO851941 PCE851904:PCS851941 OSI851904:OSW851941 OIM851904:OJA851941 NYQ851904:NZE851941 NOU851904:NPI851941 NEY851904:NFM851941 MVC851904:MVQ851941 MLG851904:MLU851941 MBK851904:MBY851941 LRO851904:LSC851941 LHS851904:LIG851941 KXW851904:KYK851941 KOA851904:KOO851941 KEE851904:KES851941 JUI851904:JUW851941 JKM851904:JLA851941 JAQ851904:JBE851941 IQU851904:IRI851941 IGY851904:IHM851941 HXC851904:HXQ851941 HNG851904:HNU851941 HDK851904:HDY851941 GTO851904:GUC851941 GJS851904:GKG851941 FZW851904:GAK851941 FQA851904:FQO851941 FGE851904:FGS851941 EWI851904:EWW851941 EMM851904:ENA851941 ECQ851904:EDE851941 DSU851904:DTI851941 DIY851904:DJM851941 CZC851904:CZQ851941 CPG851904:CPU851941 CFK851904:CFY851941 BVO851904:BWC851941 BLS851904:BMG851941 BBW851904:BCK851941 ASA851904:ASO851941 AIE851904:AIS851941 YI851904:YW851941 OM851904:PA851941 EQ851904:FE851941 WRC786368:WRQ786405 WHG786368:WHU786405 VXK786368:VXY786405 VNO786368:VOC786405 VDS786368:VEG786405 UTW786368:UUK786405 UKA786368:UKO786405 UAE786368:UAS786405 TQI786368:TQW786405 TGM786368:THA786405 SWQ786368:SXE786405 SMU786368:SNI786405 SCY786368:SDM786405 RTC786368:RTQ786405 RJG786368:RJU786405 QZK786368:QZY786405 QPO786368:QQC786405 QFS786368:QGG786405 PVW786368:PWK786405 PMA786368:PMO786405 PCE786368:PCS786405 OSI786368:OSW786405 OIM786368:OJA786405 NYQ786368:NZE786405 NOU786368:NPI786405 NEY786368:NFM786405 MVC786368:MVQ786405 MLG786368:MLU786405 MBK786368:MBY786405 LRO786368:LSC786405 LHS786368:LIG786405 KXW786368:KYK786405 KOA786368:KOO786405 KEE786368:KES786405 JUI786368:JUW786405 JKM786368:JLA786405 JAQ786368:JBE786405 IQU786368:IRI786405 IGY786368:IHM786405 HXC786368:HXQ786405 HNG786368:HNU786405 HDK786368:HDY786405 GTO786368:GUC786405 GJS786368:GKG786405 FZW786368:GAK786405 FQA786368:FQO786405 FGE786368:FGS786405 EWI786368:EWW786405 EMM786368:ENA786405 ECQ786368:EDE786405 DSU786368:DTI786405 DIY786368:DJM786405 CZC786368:CZQ786405 CPG786368:CPU786405 CFK786368:CFY786405 BVO786368:BWC786405 BLS786368:BMG786405 BBW786368:BCK786405 ASA786368:ASO786405 AIE786368:AIS786405 YI786368:YW786405 OM786368:PA786405 EQ786368:FE786405 WRC720832:WRQ720869 WHG720832:WHU720869 VXK720832:VXY720869 VNO720832:VOC720869 VDS720832:VEG720869 UTW720832:UUK720869 UKA720832:UKO720869 UAE720832:UAS720869 TQI720832:TQW720869 TGM720832:THA720869 SWQ720832:SXE720869 SMU720832:SNI720869 SCY720832:SDM720869 RTC720832:RTQ720869 RJG720832:RJU720869 QZK720832:QZY720869 QPO720832:QQC720869 QFS720832:QGG720869 PVW720832:PWK720869 PMA720832:PMO720869 PCE720832:PCS720869 OSI720832:OSW720869 OIM720832:OJA720869 NYQ720832:NZE720869 NOU720832:NPI720869 NEY720832:NFM720869 MVC720832:MVQ720869 MLG720832:MLU720869 MBK720832:MBY720869 LRO720832:LSC720869 LHS720832:LIG720869 KXW720832:KYK720869 KOA720832:KOO720869 KEE720832:KES720869 JUI720832:JUW720869 JKM720832:JLA720869 JAQ720832:JBE720869 IQU720832:IRI720869 IGY720832:IHM720869 HXC720832:HXQ720869 HNG720832:HNU720869 HDK720832:HDY720869 GTO720832:GUC720869 GJS720832:GKG720869 FZW720832:GAK720869 FQA720832:FQO720869 FGE720832:FGS720869 EWI720832:EWW720869 EMM720832:ENA720869 ECQ720832:EDE720869 DSU720832:DTI720869 DIY720832:DJM720869 CZC720832:CZQ720869 CPG720832:CPU720869 CFK720832:CFY720869 BVO720832:BWC720869 BLS720832:BMG720869 BBW720832:BCK720869 ASA720832:ASO720869 AIE720832:AIS720869 YI720832:YW720869 OM720832:PA720869 EQ720832:FE720869 WRC655296:WRQ655333 WHG655296:WHU655333 VXK655296:VXY655333 VNO655296:VOC655333 VDS655296:VEG655333 UTW655296:UUK655333 UKA655296:UKO655333 UAE655296:UAS655333 TQI655296:TQW655333 TGM655296:THA655333 SWQ655296:SXE655333 SMU655296:SNI655333 SCY655296:SDM655333 RTC655296:RTQ655333 RJG655296:RJU655333 QZK655296:QZY655333 QPO655296:QQC655333 QFS655296:QGG655333 PVW655296:PWK655333 PMA655296:PMO655333 PCE655296:PCS655333 OSI655296:OSW655333 OIM655296:OJA655333 NYQ655296:NZE655333 NOU655296:NPI655333 NEY655296:NFM655333 MVC655296:MVQ655333 MLG655296:MLU655333 MBK655296:MBY655333 LRO655296:LSC655333 LHS655296:LIG655333 KXW655296:KYK655333 KOA655296:KOO655333 KEE655296:KES655333 JUI655296:JUW655333 JKM655296:JLA655333 JAQ655296:JBE655333 IQU655296:IRI655333 IGY655296:IHM655333 HXC655296:HXQ655333 HNG655296:HNU655333 HDK655296:HDY655333 GTO655296:GUC655333 GJS655296:GKG655333 FZW655296:GAK655333 FQA655296:FQO655333 FGE655296:FGS655333 EWI655296:EWW655333 EMM655296:ENA655333 ECQ655296:EDE655333 DSU655296:DTI655333 DIY655296:DJM655333 CZC655296:CZQ655333 CPG655296:CPU655333 CFK655296:CFY655333 BVO655296:BWC655333 BLS655296:BMG655333 BBW655296:BCK655333 ASA655296:ASO655333 AIE655296:AIS655333 YI655296:YW655333 OM655296:PA655333 EQ655296:FE655333 WRC589760:WRQ589797 WHG589760:WHU589797 VXK589760:VXY589797 VNO589760:VOC589797 VDS589760:VEG589797 UTW589760:UUK589797 UKA589760:UKO589797 UAE589760:UAS589797 TQI589760:TQW589797 TGM589760:THA589797 SWQ589760:SXE589797 SMU589760:SNI589797 SCY589760:SDM589797 RTC589760:RTQ589797 RJG589760:RJU589797 QZK589760:QZY589797 QPO589760:QQC589797 QFS589760:QGG589797 PVW589760:PWK589797 PMA589760:PMO589797 PCE589760:PCS589797 OSI589760:OSW589797 OIM589760:OJA589797 NYQ589760:NZE589797 NOU589760:NPI589797 NEY589760:NFM589797 MVC589760:MVQ589797 MLG589760:MLU589797 MBK589760:MBY589797 LRO589760:LSC589797 LHS589760:LIG589797 KXW589760:KYK589797 KOA589760:KOO589797 KEE589760:KES589797 JUI589760:JUW589797 JKM589760:JLA589797 JAQ589760:JBE589797 IQU589760:IRI589797 IGY589760:IHM589797 HXC589760:HXQ589797 HNG589760:HNU589797 HDK589760:HDY589797 GTO589760:GUC589797 GJS589760:GKG589797 FZW589760:GAK589797 FQA589760:FQO589797 FGE589760:FGS589797 EWI589760:EWW589797 EMM589760:ENA589797 ECQ589760:EDE589797 DSU589760:DTI589797 DIY589760:DJM589797 CZC589760:CZQ589797 CPG589760:CPU589797 CFK589760:CFY589797 BVO589760:BWC589797 BLS589760:BMG589797 BBW589760:BCK589797 ASA589760:ASO589797 AIE589760:AIS589797 YI589760:YW589797 OM589760:PA589797 EQ589760:FE589797 WRC524224:WRQ524261 WHG524224:WHU524261 VXK524224:VXY524261 VNO524224:VOC524261 VDS524224:VEG524261 UTW524224:UUK524261 UKA524224:UKO524261 UAE524224:UAS524261 TQI524224:TQW524261 TGM524224:THA524261 SWQ524224:SXE524261 SMU524224:SNI524261 SCY524224:SDM524261 RTC524224:RTQ524261 RJG524224:RJU524261 QZK524224:QZY524261 QPO524224:QQC524261 QFS524224:QGG524261 PVW524224:PWK524261 PMA524224:PMO524261 PCE524224:PCS524261 OSI524224:OSW524261 OIM524224:OJA524261 NYQ524224:NZE524261 NOU524224:NPI524261 NEY524224:NFM524261 MVC524224:MVQ524261 MLG524224:MLU524261 MBK524224:MBY524261 LRO524224:LSC524261 LHS524224:LIG524261 KXW524224:KYK524261 KOA524224:KOO524261 KEE524224:KES524261 JUI524224:JUW524261 JKM524224:JLA524261 JAQ524224:JBE524261 IQU524224:IRI524261 IGY524224:IHM524261 HXC524224:HXQ524261 HNG524224:HNU524261 HDK524224:HDY524261 GTO524224:GUC524261 GJS524224:GKG524261 FZW524224:GAK524261 FQA524224:FQO524261 FGE524224:FGS524261 EWI524224:EWW524261 EMM524224:ENA524261 ECQ524224:EDE524261 DSU524224:DTI524261 DIY524224:DJM524261 CZC524224:CZQ524261 CPG524224:CPU524261 CFK524224:CFY524261 BVO524224:BWC524261 BLS524224:BMG524261 BBW524224:BCK524261 ASA524224:ASO524261 AIE524224:AIS524261 YI524224:YW524261 OM524224:PA524261 EQ524224:FE524261 WRC458688:WRQ458725 WHG458688:WHU458725 VXK458688:VXY458725 VNO458688:VOC458725 VDS458688:VEG458725 UTW458688:UUK458725 UKA458688:UKO458725 UAE458688:UAS458725 TQI458688:TQW458725 TGM458688:THA458725 SWQ458688:SXE458725 SMU458688:SNI458725 SCY458688:SDM458725 RTC458688:RTQ458725 RJG458688:RJU458725 QZK458688:QZY458725 QPO458688:QQC458725 QFS458688:QGG458725 PVW458688:PWK458725 PMA458688:PMO458725 PCE458688:PCS458725 OSI458688:OSW458725 OIM458688:OJA458725 NYQ458688:NZE458725 NOU458688:NPI458725 NEY458688:NFM458725 MVC458688:MVQ458725 MLG458688:MLU458725 MBK458688:MBY458725 LRO458688:LSC458725 LHS458688:LIG458725 KXW458688:KYK458725 KOA458688:KOO458725 KEE458688:KES458725 JUI458688:JUW458725 JKM458688:JLA458725 JAQ458688:JBE458725 IQU458688:IRI458725 IGY458688:IHM458725 HXC458688:HXQ458725 HNG458688:HNU458725 HDK458688:HDY458725 GTO458688:GUC458725 GJS458688:GKG458725 FZW458688:GAK458725 FQA458688:FQO458725 FGE458688:FGS458725 EWI458688:EWW458725 EMM458688:ENA458725 ECQ458688:EDE458725 DSU458688:DTI458725 DIY458688:DJM458725 CZC458688:CZQ458725 CPG458688:CPU458725 CFK458688:CFY458725 BVO458688:BWC458725 BLS458688:BMG458725 BBW458688:BCK458725 ASA458688:ASO458725 AIE458688:AIS458725 YI458688:YW458725 OM458688:PA458725 EQ458688:FE458725 WRC393152:WRQ393189 WHG393152:WHU393189 VXK393152:VXY393189 VNO393152:VOC393189 VDS393152:VEG393189 UTW393152:UUK393189 UKA393152:UKO393189 UAE393152:UAS393189 TQI393152:TQW393189 TGM393152:THA393189 SWQ393152:SXE393189 SMU393152:SNI393189 SCY393152:SDM393189 RTC393152:RTQ393189 RJG393152:RJU393189 QZK393152:QZY393189 QPO393152:QQC393189 QFS393152:QGG393189 PVW393152:PWK393189 PMA393152:PMO393189 PCE393152:PCS393189 OSI393152:OSW393189 OIM393152:OJA393189 NYQ393152:NZE393189 NOU393152:NPI393189 NEY393152:NFM393189 MVC393152:MVQ393189 MLG393152:MLU393189 MBK393152:MBY393189 LRO393152:LSC393189 LHS393152:LIG393189 KXW393152:KYK393189 KOA393152:KOO393189 KEE393152:KES393189 JUI393152:JUW393189 JKM393152:JLA393189 JAQ393152:JBE393189 IQU393152:IRI393189 IGY393152:IHM393189 HXC393152:HXQ393189 HNG393152:HNU393189 HDK393152:HDY393189 GTO393152:GUC393189 GJS393152:GKG393189 FZW393152:GAK393189 FQA393152:FQO393189 FGE393152:FGS393189 EWI393152:EWW393189 EMM393152:ENA393189 ECQ393152:EDE393189 DSU393152:DTI393189 DIY393152:DJM393189 CZC393152:CZQ393189 CPG393152:CPU393189 CFK393152:CFY393189 BVO393152:BWC393189 BLS393152:BMG393189 BBW393152:BCK393189 ASA393152:ASO393189 AIE393152:AIS393189 YI393152:YW393189 OM393152:PA393189 EQ393152:FE393189 WRC327616:WRQ327653 WHG327616:WHU327653 VXK327616:VXY327653 VNO327616:VOC327653 VDS327616:VEG327653 UTW327616:UUK327653 UKA327616:UKO327653 UAE327616:UAS327653 TQI327616:TQW327653 TGM327616:THA327653 SWQ327616:SXE327653 SMU327616:SNI327653 SCY327616:SDM327653 RTC327616:RTQ327653 RJG327616:RJU327653 QZK327616:QZY327653 QPO327616:QQC327653 QFS327616:QGG327653 PVW327616:PWK327653 PMA327616:PMO327653 PCE327616:PCS327653 OSI327616:OSW327653 OIM327616:OJA327653 NYQ327616:NZE327653 NOU327616:NPI327653 NEY327616:NFM327653 MVC327616:MVQ327653 MLG327616:MLU327653 MBK327616:MBY327653 LRO327616:LSC327653 LHS327616:LIG327653 KXW327616:KYK327653 KOA327616:KOO327653 KEE327616:KES327653 JUI327616:JUW327653 JKM327616:JLA327653 JAQ327616:JBE327653 IQU327616:IRI327653 IGY327616:IHM327653 HXC327616:HXQ327653 HNG327616:HNU327653 HDK327616:HDY327653 GTO327616:GUC327653 GJS327616:GKG327653 FZW327616:GAK327653 FQA327616:FQO327653 FGE327616:FGS327653 EWI327616:EWW327653 EMM327616:ENA327653 ECQ327616:EDE327653 DSU327616:DTI327653 DIY327616:DJM327653 CZC327616:CZQ327653 CPG327616:CPU327653 CFK327616:CFY327653 BVO327616:BWC327653 BLS327616:BMG327653 BBW327616:BCK327653 ASA327616:ASO327653 AIE327616:AIS327653 YI327616:YW327653 OM327616:PA327653 EQ327616:FE327653 WRC262080:WRQ262117 WHG262080:WHU262117 VXK262080:VXY262117 VNO262080:VOC262117 VDS262080:VEG262117 UTW262080:UUK262117 UKA262080:UKO262117 UAE262080:UAS262117 TQI262080:TQW262117 TGM262080:THA262117 SWQ262080:SXE262117 SMU262080:SNI262117 SCY262080:SDM262117 RTC262080:RTQ262117 RJG262080:RJU262117 QZK262080:QZY262117 QPO262080:QQC262117 QFS262080:QGG262117 PVW262080:PWK262117 PMA262080:PMO262117 PCE262080:PCS262117 OSI262080:OSW262117 OIM262080:OJA262117 NYQ262080:NZE262117 NOU262080:NPI262117 NEY262080:NFM262117 MVC262080:MVQ262117 MLG262080:MLU262117 MBK262080:MBY262117 LRO262080:LSC262117 LHS262080:LIG262117 KXW262080:KYK262117 KOA262080:KOO262117 KEE262080:KES262117 JUI262080:JUW262117 JKM262080:JLA262117 JAQ262080:JBE262117 IQU262080:IRI262117 IGY262080:IHM262117 HXC262080:HXQ262117 HNG262080:HNU262117 HDK262080:HDY262117 GTO262080:GUC262117 GJS262080:GKG262117 FZW262080:GAK262117 FQA262080:FQO262117 FGE262080:FGS262117 EWI262080:EWW262117 EMM262080:ENA262117 ECQ262080:EDE262117 DSU262080:DTI262117 DIY262080:DJM262117 CZC262080:CZQ262117 CPG262080:CPU262117 CFK262080:CFY262117 BVO262080:BWC262117 BLS262080:BMG262117 BBW262080:BCK262117 ASA262080:ASO262117 AIE262080:AIS262117 YI262080:YW262117 OM262080:PA262117 EQ262080:FE262117 WRC196544:WRQ196581 WHG196544:WHU196581 VXK196544:VXY196581 VNO196544:VOC196581 VDS196544:VEG196581 UTW196544:UUK196581 UKA196544:UKO196581 UAE196544:UAS196581 TQI196544:TQW196581 TGM196544:THA196581 SWQ196544:SXE196581 SMU196544:SNI196581 SCY196544:SDM196581 RTC196544:RTQ196581 RJG196544:RJU196581 QZK196544:QZY196581 QPO196544:QQC196581 QFS196544:QGG196581 PVW196544:PWK196581 PMA196544:PMO196581 PCE196544:PCS196581 OSI196544:OSW196581 OIM196544:OJA196581 NYQ196544:NZE196581 NOU196544:NPI196581 NEY196544:NFM196581 MVC196544:MVQ196581 MLG196544:MLU196581 MBK196544:MBY196581 LRO196544:LSC196581 LHS196544:LIG196581 KXW196544:KYK196581 KOA196544:KOO196581 KEE196544:KES196581 JUI196544:JUW196581 JKM196544:JLA196581 JAQ196544:JBE196581 IQU196544:IRI196581 IGY196544:IHM196581 HXC196544:HXQ196581 HNG196544:HNU196581 HDK196544:HDY196581 GTO196544:GUC196581 GJS196544:GKG196581 FZW196544:GAK196581 FQA196544:FQO196581 FGE196544:FGS196581 EWI196544:EWW196581 EMM196544:ENA196581 ECQ196544:EDE196581 DSU196544:DTI196581 DIY196544:DJM196581 CZC196544:CZQ196581 CPG196544:CPU196581 CFK196544:CFY196581 BVO196544:BWC196581 BLS196544:BMG196581 BBW196544:BCK196581 ASA196544:ASO196581 AIE196544:AIS196581 YI196544:YW196581 OM196544:PA196581 EQ196544:FE196581 WRC131008:WRQ131045 WHG131008:WHU131045 VXK131008:VXY131045 VNO131008:VOC131045 VDS131008:VEG131045 UTW131008:UUK131045 UKA131008:UKO131045 UAE131008:UAS131045 TQI131008:TQW131045 TGM131008:THA131045 SWQ131008:SXE131045 SMU131008:SNI131045 SCY131008:SDM131045 RTC131008:RTQ131045 RJG131008:RJU131045 QZK131008:QZY131045 QPO131008:QQC131045 QFS131008:QGG131045 PVW131008:PWK131045 PMA131008:PMO131045 PCE131008:PCS131045 OSI131008:OSW131045 OIM131008:OJA131045 NYQ131008:NZE131045 NOU131008:NPI131045 NEY131008:NFM131045 MVC131008:MVQ131045 MLG131008:MLU131045 MBK131008:MBY131045 LRO131008:LSC131045 LHS131008:LIG131045 KXW131008:KYK131045 KOA131008:KOO131045 KEE131008:KES131045 JUI131008:JUW131045 JKM131008:JLA131045 JAQ131008:JBE131045 IQU131008:IRI131045 IGY131008:IHM131045 HXC131008:HXQ131045 HNG131008:HNU131045 HDK131008:HDY131045 GTO131008:GUC131045 GJS131008:GKG131045 FZW131008:GAK131045 FQA131008:FQO131045 FGE131008:FGS131045 EWI131008:EWW131045 EMM131008:ENA131045 ECQ131008:EDE131045 DSU131008:DTI131045 DIY131008:DJM131045 CZC131008:CZQ131045 CPG131008:CPU131045 CFK131008:CFY131045 BVO131008:BWC131045 BLS131008:BMG131045 BBW131008:BCK131045 ASA131008:ASO131045 AIE131008:AIS131045 YI131008:YW131045 OM131008:PA131045 EQ131008:FE131045 WRC65472:WRQ65509 WHG65472:WHU65509 VXK65472:VXY65509 VNO65472:VOC65509 VDS65472:VEG65509 UTW65472:UUK65509 UKA65472:UKO65509 UAE65472:UAS65509 TQI65472:TQW65509 TGM65472:THA65509 SWQ65472:SXE65509 SMU65472:SNI65509 SCY65472:SDM65509 RTC65472:RTQ65509 RJG65472:RJU65509 QZK65472:QZY65509 QPO65472:QQC65509 QFS65472:QGG65509 PVW65472:PWK65509 PMA65472:PMO65509 PCE65472:PCS65509 OSI65472:OSW65509 OIM65472:OJA65509 NYQ65472:NZE65509 NOU65472:NPI65509 NEY65472:NFM65509 MVC65472:MVQ65509 MLG65472:MLU65509 MBK65472:MBY65509 LRO65472:LSC65509 LHS65472:LIG65509 KXW65472:KYK65509 KOA65472:KOO65509 KEE65472:KES65509 JUI65472:JUW65509 JKM65472:JLA65509 JAQ65472:JBE65509 IQU65472:IRI65509 IGY65472:IHM65509 HXC65472:HXQ65509 HNG65472:HNU65509 HDK65472:HDY65509 GTO65472:GUC65509 GJS65472:GKG65509 FZW65472:GAK65509 FQA65472:FQO65509 FGE65472:FGS65509 EWI65472:EWW65509 EMM65472:ENA65509 ECQ65472:EDE65509 DSU65472:DTI65509 DIY65472:DJM65509 CZC65472:CZQ65509 CPG65472:CPU65509 CFK65472:CFY65509 BVO65472:BWC65509 BLS65472:BMG65509 BBW65472:BCK65509 ASA65472:ASO65509 AIE65472:AIS65509 YI65472:YW65509 OM65472:PA65509 EQ65472:FE65509 WHG982976:WHU983013 VXK982976:VXY983013 WHG2:WHU7 WRC2:WRQ7 EQ2:FE7 OM2:PA7 YI2:YW7 AIE2:AIS7 ASA2:ASO7 BBW2:BCK7 BLS2:BMG7 BVO2:BWC7 CFK2:CFY7 CPG2:CPU7 CZC2:CZQ7 DIY2:DJM7 DSU2:DTI7 ECQ2:EDE7 EMM2:ENA7 EWI2:EWW7 FGE2:FGS7 FQA2:FQO7 FZW2:GAK7 GJS2:GKG7 GTO2:GUC7 HDK2:HDY7 HNG2:HNU7 HXC2:HXQ7 IGY2:IHM7 IQU2:IRI7 JAQ2:JBE7 JKM2:JLA7 JUI2:JUW7 KEE2:KES7 KOA2:KOO7 KXW2:KYK7 LHS2:LIG7 LRO2:LSC7 MBK2:MBY7 MLG2:MLU7 MVC2:MVQ7 NEY2:NFM7 NOU2:NPI7 NYQ2:NZE7 OIM2:OJA7 OSI2:OSW7 PCE2:PCS7 PMA2:PMO7 PVW2:PWK7 QFS2:QGG7 QPO2:QQC7 QZK2:QZY7 RJG2:RJU7 RTC2:RTQ7 SCY2:SDM7 SMU2:SNI7 SWQ2:SXE7 TGM2:THA7 TQI2:TQW7 UAE2:UAS7 UKA2:UKO7 UTW2:UUK7 VDS2:VEG7 VNO2:VOC7 VXK2:VXY7" xr:uid="{67EFF628-81BF-4B74-9C52-DD1574F85ABA}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FU65532:FX65535 PQ65532:PT65535 ZM65532:ZP65535 AJI65532:AJL65535 ATE65532:ATH65535 BDA65532:BDD65535 BMW65532:BMZ65535 BWS65532:BWV65535 CGO65532:CGR65535 CQK65532:CQN65535 DAG65532:DAJ65535 DKC65532:DKF65535 DTY65532:DUB65535 EDU65532:EDX65535 ENQ65532:ENT65535 EXM65532:EXP65535 FHI65532:FHL65535 FRE65532:FRH65535 GBA65532:GBD65535 GKW65532:GKZ65535 GUS65532:GUV65535 HEO65532:HER65535 HOK65532:HON65535 HYG65532:HYJ65535 IIC65532:IIF65535 IRY65532:ISB65535 JBU65532:JBX65535 JLQ65532:JLT65535 JVM65532:JVP65535 KFI65532:KFL65535 KPE65532:KPH65535 KZA65532:KZD65535 LIW65532:LIZ65535 LSS65532:LSV65535 MCO65532:MCR65535 MMK65532:MMN65535 MWG65532:MWJ65535 NGC65532:NGF65535 NPY65532:NQB65535 NZU65532:NZX65535 OJQ65532:OJT65535 OTM65532:OTP65535 PDI65532:PDL65535 PNE65532:PNH65535 PXA65532:PXD65535 QGW65532:QGZ65535 QQS65532:QQV65535 RAO65532:RAR65535 RKK65532:RKN65535 RUG65532:RUJ65535 SEC65532:SEF65535 SNY65532:SOB65535 SXU65532:SXX65535 THQ65532:THT65535 TRM65532:TRP65535 UBI65532:UBL65535 ULE65532:ULH65535 UVA65532:UVD65535 VEW65532:VEZ65535 VOS65532:VOV65535 VYO65532:VYR65535 WIK65532:WIN65535 WSG65532:WSJ65535 FU131068:FX131071 PQ131068:PT131071 ZM131068:ZP131071 AJI131068:AJL131071 ATE131068:ATH131071 BDA131068:BDD131071 BMW131068:BMZ131071 BWS131068:BWV131071 CGO131068:CGR131071 CQK131068:CQN131071 DAG131068:DAJ131071 DKC131068:DKF131071 DTY131068:DUB131071 EDU131068:EDX131071 ENQ131068:ENT131071 EXM131068:EXP131071 FHI131068:FHL131071 FRE131068:FRH131071 GBA131068:GBD131071 GKW131068:GKZ131071 GUS131068:GUV131071 HEO131068:HER131071 HOK131068:HON131071 HYG131068:HYJ131071 IIC131068:IIF131071 IRY131068:ISB131071 JBU131068:JBX131071 JLQ131068:JLT131071 JVM131068:JVP131071 KFI131068:KFL131071 KPE131068:KPH131071 KZA131068:KZD131071 LIW131068:LIZ131071 LSS131068:LSV131071 MCO131068:MCR131071 MMK131068:MMN131071 MWG131068:MWJ131071 NGC131068:NGF131071 NPY131068:NQB131071 NZU131068:NZX131071 OJQ131068:OJT131071 OTM131068:OTP131071 PDI131068:PDL131071 PNE131068:PNH131071 PXA131068:PXD131071 QGW131068:QGZ131071 QQS131068:QQV131071 RAO131068:RAR131071 RKK131068:RKN131071 RUG131068:RUJ131071 SEC131068:SEF131071 SNY131068:SOB131071 SXU131068:SXX131071 THQ131068:THT131071 TRM131068:TRP131071 UBI131068:UBL131071 ULE131068:ULH131071 UVA131068:UVD131071 VEW131068:VEZ131071 VOS131068:VOV131071 VYO131068:VYR131071 WIK131068:WIN131071 WSG131068:WSJ131071 FU196604:FX196607 PQ196604:PT196607 ZM196604:ZP196607 AJI196604:AJL196607 ATE196604:ATH196607 BDA196604:BDD196607 BMW196604:BMZ196607 BWS196604:BWV196607 CGO196604:CGR196607 CQK196604:CQN196607 DAG196604:DAJ196607 DKC196604:DKF196607 DTY196604:DUB196607 EDU196604:EDX196607 ENQ196604:ENT196607 EXM196604:EXP196607 FHI196604:FHL196607 FRE196604:FRH196607 GBA196604:GBD196607 GKW196604:GKZ196607 GUS196604:GUV196607 HEO196604:HER196607 HOK196604:HON196607 HYG196604:HYJ196607 IIC196604:IIF196607 IRY196604:ISB196607 JBU196604:JBX196607 JLQ196604:JLT196607 JVM196604:JVP196607 KFI196604:KFL196607 KPE196604:KPH196607 KZA196604:KZD196607 LIW196604:LIZ196607 LSS196604:LSV196607 MCO196604:MCR196607 MMK196604:MMN196607 MWG196604:MWJ196607 NGC196604:NGF196607 NPY196604:NQB196607 NZU196604:NZX196607 OJQ196604:OJT196607 OTM196604:OTP196607 PDI196604:PDL196607 PNE196604:PNH196607 PXA196604:PXD196607 QGW196604:QGZ196607 QQS196604:QQV196607 RAO196604:RAR196607 RKK196604:RKN196607 RUG196604:RUJ196607 SEC196604:SEF196607 SNY196604:SOB196607 SXU196604:SXX196607 THQ196604:THT196607 TRM196604:TRP196607 UBI196604:UBL196607 ULE196604:ULH196607 UVA196604:UVD196607 VEW196604:VEZ196607 VOS196604:VOV196607 VYO196604:VYR196607 WIK196604:WIN196607 WSG196604:WSJ196607 FU262140:FX262143 PQ262140:PT262143 ZM262140:ZP262143 AJI262140:AJL262143 ATE262140:ATH262143 BDA262140:BDD262143 BMW262140:BMZ262143 BWS262140:BWV262143 CGO262140:CGR262143 CQK262140:CQN262143 DAG262140:DAJ262143 DKC262140:DKF262143 DTY262140:DUB262143 EDU262140:EDX262143 ENQ262140:ENT262143 EXM262140:EXP262143 FHI262140:FHL262143 FRE262140:FRH262143 GBA262140:GBD262143 GKW262140:GKZ262143 GUS262140:GUV262143 HEO262140:HER262143 HOK262140:HON262143 HYG262140:HYJ262143 IIC262140:IIF262143 IRY262140:ISB262143 JBU262140:JBX262143 JLQ262140:JLT262143 JVM262140:JVP262143 KFI262140:KFL262143 KPE262140:KPH262143 KZA262140:KZD262143 LIW262140:LIZ262143 LSS262140:LSV262143 MCO262140:MCR262143 MMK262140:MMN262143 MWG262140:MWJ262143 NGC262140:NGF262143 NPY262140:NQB262143 NZU262140:NZX262143 OJQ262140:OJT262143 OTM262140:OTP262143 PDI262140:PDL262143 PNE262140:PNH262143 PXA262140:PXD262143 QGW262140:QGZ262143 QQS262140:QQV262143 RAO262140:RAR262143 RKK262140:RKN262143 RUG262140:RUJ262143 SEC262140:SEF262143 SNY262140:SOB262143 SXU262140:SXX262143 THQ262140:THT262143 TRM262140:TRP262143 UBI262140:UBL262143 ULE262140:ULH262143 UVA262140:UVD262143 VEW262140:VEZ262143 VOS262140:VOV262143 VYO262140:VYR262143 WIK262140:WIN262143 WSG262140:WSJ262143 FU327676:FX327679 PQ327676:PT327679 ZM327676:ZP327679 AJI327676:AJL327679 ATE327676:ATH327679 BDA327676:BDD327679 BMW327676:BMZ327679 BWS327676:BWV327679 CGO327676:CGR327679 CQK327676:CQN327679 DAG327676:DAJ327679 DKC327676:DKF327679 DTY327676:DUB327679 EDU327676:EDX327679 ENQ327676:ENT327679 EXM327676:EXP327679 FHI327676:FHL327679 FRE327676:FRH327679 GBA327676:GBD327679 GKW327676:GKZ327679 GUS327676:GUV327679 HEO327676:HER327679 HOK327676:HON327679 HYG327676:HYJ327679 IIC327676:IIF327679 IRY327676:ISB327679 JBU327676:JBX327679 JLQ327676:JLT327679 JVM327676:JVP327679 KFI327676:KFL327679 KPE327676:KPH327679 KZA327676:KZD327679 LIW327676:LIZ327679 LSS327676:LSV327679 MCO327676:MCR327679 MMK327676:MMN327679 MWG327676:MWJ327679 NGC327676:NGF327679 NPY327676:NQB327679 NZU327676:NZX327679 OJQ327676:OJT327679 OTM327676:OTP327679 PDI327676:PDL327679 PNE327676:PNH327679 PXA327676:PXD327679 QGW327676:QGZ327679 QQS327676:QQV327679 RAO327676:RAR327679 RKK327676:RKN327679 RUG327676:RUJ327679 SEC327676:SEF327679 SNY327676:SOB327679 SXU327676:SXX327679 THQ327676:THT327679 TRM327676:TRP327679 UBI327676:UBL327679 ULE327676:ULH327679 UVA327676:UVD327679 VEW327676:VEZ327679 VOS327676:VOV327679 VYO327676:VYR327679 WIK327676:WIN327679 WSG327676:WSJ327679 FU393212:FX393215 PQ393212:PT393215 ZM393212:ZP393215 AJI393212:AJL393215 ATE393212:ATH393215 BDA393212:BDD393215 BMW393212:BMZ393215 BWS393212:BWV393215 CGO393212:CGR393215 CQK393212:CQN393215 DAG393212:DAJ393215 DKC393212:DKF393215 DTY393212:DUB393215 EDU393212:EDX393215 ENQ393212:ENT393215 EXM393212:EXP393215 FHI393212:FHL393215 FRE393212:FRH393215 GBA393212:GBD393215 GKW393212:GKZ393215 GUS393212:GUV393215 HEO393212:HER393215 HOK393212:HON393215 HYG393212:HYJ393215 IIC393212:IIF393215 IRY393212:ISB393215 JBU393212:JBX393215 JLQ393212:JLT393215 JVM393212:JVP393215 KFI393212:KFL393215 KPE393212:KPH393215 KZA393212:KZD393215 LIW393212:LIZ393215 LSS393212:LSV393215 MCO393212:MCR393215 MMK393212:MMN393215 MWG393212:MWJ393215 NGC393212:NGF393215 NPY393212:NQB393215 NZU393212:NZX393215 OJQ393212:OJT393215 OTM393212:OTP393215 PDI393212:PDL393215 PNE393212:PNH393215 PXA393212:PXD393215 QGW393212:QGZ393215 QQS393212:QQV393215 RAO393212:RAR393215 RKK393212:RKN393215 RUG393212:RUJ393215 SEC393212:SEF393215 SNY393212:SOB393215 SXU393212:SXX393215 THQ393212:THT393215 TRM393212:TRP393215 UBI393212:UBL393215 ULE393212:ULH393215 UVA393212:UVD393215 VEW393212:VEZ393215 VOS393212:VOV393215 VYO393212:VYR393215 WIK393212:WIN393215 WSG393212:WSJ393215 FU458748:FX458751 PQ458748:PT458751 ZM458748:ZP458751 AJI458748:AJL458751 ATE458748:ATH458751 BDA458748:BDD458751 BMW458748:BMZ458751 BWS458748:BWV458751 CGO458748:CGR458751 CQK458748:CQN458751 DAG458748:DAJ458751 DKC458748:DKF458751 DTY458748:DUB458751 EDU458748:EDX458751 ENQ458748:ENT458751 EXM458748:EXP458751 FHI458748:FHL458751 FRE458748:FRH458751 GBA458748:GBD458751 GKW458748:GKZ458751 GUS458748:GUV458751 HEO458748:HER458751 HOK458748:HON458751 HYG458748:HYJ458751 IIC458748:IIF458751 IRY458748:ISB458751 JBU458748:JBX458751 JLQ458748:JLT458751 JVM458748:JVP458751 KFI458748:KFL458751 KPE458748:KPH458751 KZA458748:KZD458751 LIW458748:LIZ458751 LSS458748:LSV458751 MCO458748:MCR458751 MMK458748:MMN458751 MWG458748:MWJ458751 NGC458748:NGF458751 NPY458748:NQB458751 NZU458748:NZX458751 OJQ458748:OJT458751 OTM458748:OTP458751 PDI458748:PDL458751 PNE458748:PNH458751 PXA458748:PXD458751 QGW458748:QGZ458751 QQS458748:QQV458751 RAO458748:RAR458751 RKK458748:RKN458751 RUG458748:RUJ458751 SEC458748:SEF458751 SNY458748:SOB458751 SXU458748:SXX458751 THQ458748:THT458751 TRM458748:TRP458751 UBI458748:UBL458751 ULE458748:ULH458751 UVA458748:UVD458751 VEW458748:VEZ458751 VOS458748:VOV458751 VYO458748:VYR458751 WIK458748:WIN458751 WSG458748:WSJ458751 FU524284:FX524287 PQ524284:PT524287 ZM524284:ZP524287 AJI524284:AJL524287 ATE524284:ATH524287 BDA524284:BDD524287 BMW524284:BMZ524287 BWS524284:BWV524287 CGO524284:CGR524287 CQK524284:CQN524287 DAG524284:DAJ524287 DKC524284:DKF524287 DTY524284:DUB524287 EDU524284:EDX524287 ENQ524284:ENT524287 EXM524284:EXP524287 FHI524284:FHL524287 FRE524284:FRH524287 GBA524284:GBD524287 GKW524284:GKZ524287 GUS524284:GUV524287 HEO524284:HER524287 HOK524284:HON524287 HYG524284:HYJ524287 IIC524284:IIF524287 IRY524284:ISB524287 JBU524284:JBX524287 JLQ524284:JLT524287 JVM524284:JVP524287 KFI524284:KFL524287 KPE524284:KPH524287 KZA524284:KZD524287 LIW524284:LIZ524287 LSS524284:LSV524287 MCO524284:MCR524287 MMK524284:MMN524287 MWG524284:MWJ524287 NGC524284:NGF524287 NPY524284:NQB524287 NZU524284:NZX524287 OJQ524284:OJT524287 OTM524284:OTP524287 PDI524284:PDL524287 PNE524284:PNH524287 PXA524284:PXD524287 QGW524284:QGZ524287 QQS524284:QQV524287 RAO524284:RAR524287 RKK524284:RKN524287 RUG524284:RUJ524287 SEC524284:SEF524287 SNY524284:SOB524287 SXU524284:SXX524287 THQ524284:THT524287 TRM524284:TRP524287 UBI524284:UBL524287 ULE524284:ULH524287 UVA524284:UVD524287 VEW524284:VEZ524287 VOS524284:VOV524287 VYO524284:VYR524287 WIK524284:WIN524287 WSG524284:WSJ524287 FU589820:FX589823 PQ589820:PT589823 ZM589820:ZP589823 AJI589820:AJL589823 ATE589820:ATH589823 BDA589820:BDD589823 BMW589820:BMZ589823 BWS589820:BWV589823 CGO589820:CGR589823 CQK589820:CQN589823 DAG589820:DAJ589823 DKC589820:DKF589823 DTY589820:DUB589823 EDU589820:EDX589823 ENQ589820:ENT589823 EXM589820:EXP589823 FHI589820:FHL589823 FRE589820:FRH589823 GBA589820:GBD589823 GKW589820:GKZ589823 GUS589820:GUV589823 HEO589820:HER589823 HOK589820:HON589823 HYG589820:HYJ589823 IIC589820:IIF589823 IRY589820:ISB589823 JBU589820:JBX589823 JLQ589820:JLT589823 JVM589820:JVP589823 KFI589820:KFL589823 KPE589820:KPH589823 KZA589820:KZD589823 LIW589820:LIZ589823 LSS589820:LSV589823 MCO589820:MCR589823 MMK589820:MMN589823 MWG589820:MWJ589823 NGC589820:NGF589823 NPY589820:NQB589823 NZU589820:NZX589823 OJQ589820:OJT589823 OTM589820:OTP589823 PDI589820:PDL589823 PNE589820:PNH589823 PXA589820:PXD589823 QGW589820:QGZ589823 QQS589820:QQV589823 RAO589820:RAR589823 RKK589820:RKN589823 RUG589820:RUJ589823 SEC589820:SEF589823 SNY589820:SOB589823 SXU589820:SXX589823 THQ589820:THT589823 TRM589820:TRP589823 UBI589820:UBL589823 ULE589820:ULH589823 UVA589820:UVD589823 VEW589820:VEZ589823 VOS589820:VOV589823 VYO589820:VYR589823 WIK589820:WIN589823 WSG589820:WSJ589823 FU655356:FX655359 PQ655356:PT655359 ZM655356:ZP655359 AJI655356:AJL655359 ATE655356:ATH655359 BDA655356:BDD655359 BMW655356:BMZ655359 BWS655356:BWV655359 CGO655356:CGR655359 CQK655356:CQN655359 DAG655356:DAJ655359 DKC655356:DKF655359 DTY655356:DUB655359 EDU655356:EDX655359 ENQ655356:ENT655359 EXM655356:EXP655359 FHI655356:FHL655359 FRE655356:FRH655359 GBA655356:GBD655359 GKW655356:GKZ655359 GUS655356:GUV655359 HEO655356:HER655359 HOK655356:HON655359 HYG655356:HYJ655359 IIC655356:IIF655359 IRY655356:ISB655359 JBU655356:JBX655359 JLQ655356:JLT655359 JVM655356:JVP655359 KFI655356:KFL655359 KPE655356:KPH655359 KZA655356:KZD655359 LIW655356:LIZ655359 LSS655356:LSV655359 MCO655356:MCR655359 MMK655356:MMN655359 MWG655356:MWJ655359 NGC655356:NGF655359 NPY655356:NQB655359 NZU655356:NZX655359 OJQ655356:OJT655359 OTM655356:OTP655359 PDI655356:PDL655359 PNE655356:PNH655359 PXA655356:PXD655359 QGW655356:QGZ655359 QQS655356:QQV655359 RAO655356:RAR655359 RKK655356:RKN655359 RUG655356:RUJ655359 SEC655356:SEF655359 SNY655356:SOB655359 SXU655356:SXX655359 THQ655356:THT655359 TRM655356:TRP655359 UBI655356:UBL655359 ULE655356:ULH655359 UVA655356:UVD655359 VEW655356:VEZ655359 VOS655356:VOV655359 VYO655356:VYR655359 WIK655356:WIN655359 WSG655356:WSJ655359 FU720892:FX720895 PQ720892:PT720895 ZM720892:ZP720895 AJI720892:AJL720895 ATE720892:ATH720895 BDA720892:BDD720895 BMW720892:BMZ720895 BWS720892:BWV720895 CGO720892:CGR720895 CQK720892:CQN720895 DAG720892:DAJ720895 DKC720892:DKF720895 DTY720892:DUB720895 EDU720892:EDX720895 ENQ720892:ENT720895 EXM720892:EXP720895 FHI720892:FHL720895 FRE720892:FRH720895 GBA720892:GBD720895 GKW720892:GKZ720895 GUS720892:GUV720895 HEO720892:HER720895 HOK720892:HON720895 HYG720892:HYJ720895 IIC720892:IIF720895 IRY720892:ISB720895 JBU720892:JBX720895 JLQ720892:JLT720895 JVM720892:JVP720895 KFI720892:KFL720895 KPE720892:KPH720895 KZA720892:KZD720895 LIW720892:LIZ720895 LSS720892:LSV720895 MCO720892:MCR720895 MMK720892:MMN720895 MWG720892:MWJ720895 NGC720892:NGF720895 NPY720892:NQB720895 NZU720892:NZX720895 OJQ720892:OJT720895 OTM720892:OTP720895 PDI720892:PDL720895 PNE720892:PNH720895 PXA720892:PXD720895 QGW720892:QGZ720895 QQS720892:QQV720895 RAO720892:RAR720895 RKK720892:RKN720895 RUG720892:RUJ720895 SEC720892:SEF720895 SNY720892:SOB720895 SXU720892:SXX720895 THQ720892:THT720895 TRM720892:TRP720895 UBI720892:UBL720895 ULE720892:ULH720895 UVA720892:UVD720895 VEW720892:VEZ720895 VOS720892:VOV720895 VYO720892:VYR720895 WIK720892:WIN720895 WSG720892:WSJ720895 FU786428:FX786431 PQ786428:PT786431 ZM786428:ZP786431 AJI786428:AJL786431 ATE786428:ATH786431 BDA786428:BDD786431 BMW786428:BMZ786431 BWS786428:BWV786431 CGO786428:CGR786431 CQK786428:CQN786431 DAG786428:DAJ786431 DKC786428:DKF786431 DTY786428:DUB786431 EDU786428:EDX786431 ENQ786428:ENT786431 EXM786428:EXP786431 FHI786428:FHL786431 FRE786428:FRH786431 GBA786428:GBD786431 GKW786428:GKZ786431 GUS786428:GUV786431 HEO786428:HER786431 HOK786428:HON786431 HYG786428:HYJ786431 IIC786428:IIF786431 IRY786428:ISB786431 JBU786428:JBX786431 JLQ786428:JLT786431 JVM786428:JVP786431 KFI786428:KFL786431 KPE786428:KPH786431 KZA786428:KZD786431 LIW786428:LIZ786431 LSS786428:LSV786431 MCO786428:MCR786431 MMK786428:MMN786431 MWG786428:MWJ786431 NGC786428:NGF786431 NPY786428:NQB786431 NZU786428:NZX786431 OJQ786428:OJT786431 OTM786428:OTP786431 PDI786428:PDL786431 PNE786428:PNH786431 PXA786428:PXD786431 QGW786428:QGZ786431 QQS786428:QQV786431 RAO786428:RAR786431 RKK786428:RKN786431 RUG786428:RUJ786431 SEC786428:SEF786431 SNY786428:SOB786431 SXU786428:SXX786431 THQ786428:THT786431 TRM786428:TRP786431 UBI786428:UBL786431 ULE786428:ULH786431 UVA786428:UVD786431 VEW786428:VEZ786431 VOS786428:VOV786431 VYO786428:VYR786431 WIK786428:WIN786431 WSG786428:WSJ786431 FU851964:FX851967 PQ851964:PT851967 ZM851964:ZP851967 AJI851964:AJL851967 ATE851964:ATH851967 BDA851964:BDD851967 BMW851964:BMZ851967 BWS851964:BWV851967 CGO851964:CGR851967 CQK851964:CQN851967 DAG851964:DAJ851967 DKC851964:DKF851967 DTY851964:DUB851967 EDU851964:EDX851967 ENQ851964:ENT851967 EXM851964:EXP851967 FHI851964:FHL851967 FRE851964:FRH851967 GBA851964:GBD851967 GKW851964:GKZ851967 GUS851964:GUV851967 HEO851964:HER851967 HOK851964:HON851967 HYG851964:HYJ851967 IIC851964:IIF851967 IRY851964:ISB851967 JBU851964:JBX851967 JLQ851964:JLT851967 JVM851964:JVP851967 KFI851964:KFL851967 KPE851964:KPH851967 KZA851964:KZD851967 LIW851964:LIZ851967 LSS851964:LSV851967 MCO851964:MCR851967 MMK851964:MMN851967 MWG851964:MWJ851967 NGC851964:NGF851967 NPY851964:NQB851967 NZU851964:NZX851967 OJQ851964:OJT851967 OTM851964:OTP851967 PDI851964:PDL851967 PNE851964:PNH851967 PXA851964:PXD851967 QGW851964:QGZ851967 QQS851964:QQV851967 RAO851964:RAR851967 RKK851964:RKN851967 RUG851964:RUJ851967 SEC851964:SEF851967 SNY851964:SOB851967 SXU851964:SXX851967 THQ851964:THT851967 TRM851964:TRP851967 UBI851964:UBL851967 ULE851964:ULH851967 UVA851964:UVD851967 VEW851964:VEZ851967 VOS851964:VOV851967 VYO851964:VYR851967 WIK851964:WIN851967 WSG851964:WSJ851967 FU917500:FX917503 PQ917500:PT917503 ZM917500:ZP917503 AJI917500:AJL917503 ATE917500:ATH917503 BDA917500:BDD917503 BMW917500:BMZ917503 BWS917500:BWV917503 CGO917500:CGR917503 CQK917500:CQN917503 DAG917500:DAJ917503 DKC917500:DKF917503 DTY917500:DUB917503 EDU917500:EDX917503 ENQ917500:ENT917503 EXM917500:EXP917503 FHI917500:FHL917503 FRE917500:FRH917503 GBA917500:GBD917503 GKW917500:GKZ917503 GUS917500:GUV917503 HEO917500:HER917503 HOK917500:HON917503 HYG917500:HYJ917503 IIC917500:IIF917503 IRY917500:ISB917503 JBU917500:JBX917503 JLQ917500:JLT917503 JVM917500:JVP917503 KFI917500:KFL917503 KPE917500:KPH917503 KZA917500:KZD917503 LIW917500:LIZ917503 LSS917500:LSV917503 MCO917500:MCR917503 MMK917500:MMN917503 MWG917500:MWJ917503 NGC917500:NGF917503 NPY917500:NQB917503 NZU917500:NZX917503 OJQ917500:OJT917503 OTM917500:OTP917503 PDI917500:PDL917503 PNE917500:PNH917503 PXA917500:PXD917503 QGW917500:QGZ917503 QQS917500:QQV917503 RAO917500:RAR917503 RKK917500:RKN917503 RUG917500:RUJ917503 SEC917500:SEF917503 SNY917500:SOB917503 SXU917500:SXX917503 THQ917500:THT917503 TRM917500:TRP917503 UBI917500:UBL917503 ULE917500:ULH917503 UVA917500:UVD917503 VEW917500:VEZ917503 VOS917500:VOV917503 VYO917500:VYR917503 WIK917500:WIN917503 WSG917500:WSJ917503 FU983036:FX983039 PQ983036:PT983039 ZM983036:ZP983039 AJI983036:AJL983039 ATE983036:ATH983039 BDA983036:BDD983039 BMW983036:BMZ983039 BWS983036:BWV983039 CGO983036:CGR983039 CQK983036:CQN983039 DAG983036:DAJ983039 DKC983036:DKF983039 DTY983036:DUB983039 EDU983036:EDX983039 ENQ983036:ENT983039 EXM983036:EXP983039 FHI983036:FHL983039 FRE983036:FRH983039 GBA983036:GBD983039 GKW983036:GKZ983039 GUS983036:GUV983039 HEO983036:HER983039 HOK983036:HON983039 HYG983036:HYJ983039 IIC983036:IIF983039 IRY983036:ISB983039 JBU983036:JBX983039 JLQ983036:JLT983039 JVM983036:JVP983039 KFI983036:KFL983039 KPE983036:KPH983039 KZA983036:KZD983039 LIW983036:LIZ983039 LSS983036:LSV983039 MCO983036:MCR983039 MMK983036:MMN983039 MWG983036:MWJ983039 NGC983036:NGF983039 NPY983036:NQB983039 NZU983036:NZX983039 OJQ983036:OJT983039 OTM983036:OTP983039 PDI983036:PDL983039 PNE983036:PNH983039 PXA983036:PXD983039 QGW983036:QGZ983039 QQS983036:QQV983039 RAO983036:RAR983039 RKK983036:RKN983039 RUG983036:RUJ983039 SEC983036:SEF983039 SNY983036:SOB983039 SXU983036:SXX983039 THQ983036:THT983039 TRM983036:TRP983039 UBI983036:UBL983039 ULE983036:ULH983039 UVA983036:UVD983039 VEW983036:VEZ983039 VOS983036:VOV983039 VYO983036:VYR983039 WIK983036:WIN983039 WSG983036:WSJ983039 FP65526:FS65526 PL65526:PO65526 ZH65526:ZK65526 AJD65526:AJG65526 ASZ65526:ATC65526 BCV65526:BCY65526 BMR65526:BMU65526 BWN65526:BWQ65526 CGJ65526:CGM65526 CQF65526:CQI65526 DAB65526:DAE65526 DJX65526:DKA65526 DTT65526:DTW65526 EDP65526:EDS65526 ENL65526:ENO65526 EXH65526:EXK65526 FHD65526:FHG65526 FQZ65526:FRC65526 GAV65526:GAY65526 GKR65526:GKU65526 GUN65526:GUQ65526 HEJ65526:HEM65526 HOF65526:HOI65526 HYB65526:HYE65526 IHX65526:IIA65526 IRT65526:IRW65526 JBP65526:JBS65526 JLL65526:JLO65526 JVH65526:JVK65526 KFD65526:KFG65526 KOZ65526:KPC65526 KYV65526:KYY65526 LIR65526:LIU65526 LSN65526:LSQ65526 MCJ65526:MCM65526 MMF65526:MMI65526 MWB65526:MWE65526 NFX65526:NGA65526 NPT65526:NPW65526 NZP65526:NZS65526 OJL65526:OJO65526 OTH65526:OTK65526 PDD65526:PDG65526 PMZ65526:PNC65526 PWV65526:PWY65526 QGR65526:QGU65526 QQN65526:QQQ65526 RAJ65526:RAM65526 RKF65526:RKI65526 RUB65526:RUE65526 SDX65526:SEA65526 SNT65526:SNW65526 SXP65526:SXS65526 THL65526:THO65526 TRH65526:TRK65526 UBD65526:UBG65526 UKZ65526:ULC65526 UUV65526:UUY65526 VER65526:VEU65526 VON65526:VOQ65526 VYJ65526:VYM65526 WIF65526:WII65526 WSB65526:WSE65526 FP131062:FS131062 PL131062:PO131062 ZH131062:ZK131062 AJD131062:AJG131062 ASZ131062:ATC131062 BCV131062:BCY131062 BMR131062:BMU131062 BWN131062:BWQ131062 CGJ131062:CGM131062 CQF131062:CQI131062 DAB131062:DAE131062 DJX131062:DKA131062 DTT131062:DTW131062 EDP131062:EDS131062 ENL131062:ENO131062 EXH131062:EXK131062 FHD131062:FHG131062 FQZ131062:FRC131062 GAV131062:GAY131062 GKR131062:GKU131062 GUN131062:GUQ131062 HEJ131062:HEM131062 HOF131062:HOI131062 HYB131062:HYE131062 IHX131062:IIA131062 IRT131062:IRW131062 JBP131062:JBS131062 JLL131062:JLO131062 JVH131062:JVK131062 KFD131062:KFG131062 KOZ131062:KPC131062 KYV131062:KYY131062 LIR131062:LIU131062 LSN131062:LSQ131062 MCJ131062:MCM131062 MMF131062:MMI131062 MWB131062:MWE131062 NFX131062:NGA131062 NPT131062:NPW131062 NZP131062:NZS131062 OJL131062:OJO131062 OTH131062:OTK131062 PDD131062:PDG131062 PMZ131062:PNC131062 PWV131062:PWY131062 QGR131062:QGU131062 QQN131062:QQQ131062 RAJ131062:RAM131062 RKF131062:RKI131062 RUB131062:RUE131062 SDX131062:SEA131062 SNT131062:SNW131062 SXP131062:SXS131062 THL131062:THO131062 TRH131062:TRK131062 UBD131062:UBG131062 UKZ131062:ULC131062 UUV131062:UUY131062 VER131062:VEU131062 VON131062:VOQ131062 VYJ131062:VYM131062 WIF131062:WII131062 WSB131062:WSE131062 FP196598:FS196598 PL196598:PO196598 ZH196598:ZK196598 AJD196598:AJG196598 ASZ196598:ATC196598 BCV196598:BCY196598 BMR196598:BMU196598 BWN196598:BWQ196598 CGJ196598:CGM196598 CQF196598:CQI196598 DAB196598:DAE196598 DJX196598:DKA196598 DTT196598:DTW196598 EDP196598:EDS196598 ENL196598:ENO196598 EXH196598:EXK196598 FHD196598:FHG196598 FQZ196598:FRC196598 GAV196598:GAY196598 GKR196598:GKU196598 GUN196598:GUQ196598 HEJ196598:HEM196598 HOF196598:HOI196598 HYB196598:HYE196598 IHX196598:IIA196598 IRT196598:IRW196598 JBP196598:JBS196598 JLL196598:JLO196598 JVH196598:JVK196598 KFD196598:KFG196598 KOZ196598:KPC196598 KYV196598:KYY196598 LIR196598:LIU196598 LSN196598:LSQ196598 MCJ196598:MCM196598 MMF196598:MMI196598 MWB196598:MWE196598 NFX196598:NGA196598 NPT196598:NPW196598 NZP196598:NZS196598 OJL196598:OJO196598 OTH196598:OTK196598 PDD196598:PDG196598 PMZ196598:PNC196598 PWV196598:PWY196598 QGR196598:QGU196598 QQN196598:QQQ196598 RAJ196598:RAM196598 RKF196598:RKI196598 RUB196598:RUE196598 SDX196598:SEA196598 SNT196598:SNW196598 SXP196598:SXS196598 THL196598:THO196598 TRH196598:TRK196598 UBD196598:UBG196598 UKZ196598:ULC196598 UUV196598:UUY196598 VER196598:VEU196598 VON196598:VOQ196598 VYJ196598:VYM196598 WIF196598:WII196598 WSB196598:WSE196598 FP262134:FS262134 PL262134:PO262134 ZH262134:ZK262134 AJD262134:AJG262134 ASZ262134:ATC262134 BCV262134:BCY262134 BMR262134:BMU262134 BWN262134:BWQ262134 CGJ262134:CGM262134 CQF262134:CQI262134 DAB262134:DAE262134 DJX262134:DKA262134 DTT262134:DTW262134 EDP262134:EDS262134 ENL262134:ENO262134 EXH262134:EXK262134 FHD262134:FHG262134 FQZ262134:FRC262134 GAV262134:GAY262134 GKR262134:GKU262134 GUN262134:GUQ262134 HEJ262134:HEM262134 HOF262134:HOI262134 HYB262134:HYE262134 IHX262134:IIA262134 IRT262134:IRW262134 JBP262134:JBS262134 JLL262134:JLO262134 JVH262134:JVK262134 KFD262134:KFG262134 KOZ262134:KPC262134 KYV262134:KYY262134 LIR262134:LIU262134 LSN262134:LSQ262134 MCJ262134:MCM262134 MMF262134:MMI262134 MWB262134:MWE262134 NFX262134:NGA262134 NPT262134:NPW262134 NZP262134:NZS262134 OJL262134:OJO262134 OTH262134:OTK262134 PDD262134:PDG262134 PMZ262134:PNC262134 PWV262134:PWY262134 QGR262134:QGU262134 QQN262134:QQQ262134 RAJ262134:RAM262134 RKF262134:RKI262134 RUB262134:RUE262134 SDX262134:SEA262134 SNT262134:SNW262134 SXP262134:SXS262134 THL262134:THO262134 TRH262134:TRK262134 UBD262134:UBG262134 UKZ262134:ULC262134 UUV262134:UUY262134 VER262134:VEU262134 VON262134:VOQ262134 VYJ262134:VYM262134 WIF262134:WII262134 WSB262134:WSE262134 FP327670:FS327670 PL327670:PO327670 ZH327670:ZK327670 AJD327670:AJG327670 ASZ327670:ATC327670 BCV327670:BCY327670 BMR327670:BMU327670 BWN327670:BWQ327670 CGJ327670:CGM327670 CQF327670:CQI327670 DAB327670:DAE327670 DJX327670:DKA327670 DTT327670:DTW327670 EDP327670:EDS327670 ENL327670:ENO327670 EXH327670:EXK327670 FHD327670:FHG327670 FQZ327670:FRC327670 GAV327670:GAY327670 GKR327670:GKU327670 GUN327670:GUQ327670 HEJ327670:HEM327670 HOF327670:HOI327670 HYB327670:HYE327670 IHX327670:IIA327670 IRT327670:IRW327670 JBP327670:JBS327670 JLL327670:JLO327670 JVH327670:JVK327670 KFD327670:KFG327670 KOZ327670:KPC327670 KYV327670:KYY327670 LIR327670:LIU327670 LSN327670:LSQ327670 MCJ327670:MCM327670 MMF327670:MMI327670 MWB327670:MWE327670 NFX327670:NGA327670 NPT327670:NPW327670 NZP327670:NZS327670 OJL327670:OJO327670 OTH327670:OTK327670 PDD327670:PDG327670 PMZ327670:PNC327670 PWV327670:PWY327670 QGR327670:QGU327670 QQN327670:QQQ327670 RAJ327670:RAM327670 RKF327670:RKI327670 RUB327670:RUE327670 SDX327670:SEA327670 SNT327670:SNW327670 SXP327670:SXS327670 THL327670:THO327670 TRH327670:TRK327670 UBD327670:UBG327670 UKZ327670:ULC327670 UUV327670:UUY327670 VER327670:VEU327670 VON327670:VOQ327670 VYJ327670:VYM327670 WIF327670:WII327670 WSB327670:WSE327670 FP393206:FS393206 PL393206:PO393206 ZH393206:ZK393206 AJD393206:AJG393206 ASZ393206:ATC393206 BCV393206:BCY393206 BMR393206:BMU393206 BWN393206:BWQ393206 CGJ393206:CGM393206 CQF393206:CQI393206 DAB393206:DAE393206 DJX393206:DKA393206 DTT393206:DTW393206 EDP393206:EDS393206 ENL393206:ENO393206 EXH393206:EXK393206 FHD393206:FHG393206 FQZ393206:FRC393206 GAV393206:GAY393206 GKR393206:GKU393206 GUN393206:GUQ393206 HEJ393206:HEM393206 HOF393206:HOI393206 HYB393206:HYE393206 IHX393206:IIA393206 IRT393206:IRW393206 JBP393206:JBS393206 JLL393206:JLO393206 JVH393206:JVK393206 KFD393206:KFG393206 KOZ393206:KPC393206 KYV393206:KYY393206 LIR393206:LIU393206 LSN393206:LSQ393206 MCJ393206:MCM393206 MMF393206:MMI393206 MWB393206:MWE393206 NFX393206:NGA393206 NPT393206:NPW393206 NZP393206:NZS393206 OJL393206:OJO393206 OTH393206:OTK393206 PDD393206:PDG393206 PMZ393206:PNC393206 PWV393206:PWY393206 QGR393206:QGU393206 QQN393206:QQQ393206 RAJ393206:RAM393206 RKF393206:RKI393206 RUB393206:RUE393206 SDX393206:SEA393206 SNT393206:SNW393206 SXP393206:SXS393206 THL393206:THO393206 TRH393206:TRK393206 UBD393206:UBG393206 UKZ393206:ULC393206 UUV393206:UUY393206 VER393206:VEU393206 VON393206:VOQ393206 VYJ393206:VYM393206 WIF393206:WII393206 WSB393206:WSE393206 FP458742:FS458742 PL458742:PO458742 ZH458742:ZK458742 AJD458742:AJG458742 ASZ458742:ATC458742 BCV458742:BCY458742 BMR458742:BMU458742 BWN458742:BWQ458742 CGJ458742:CGM458742 CQF458742:CQI458742 DAB458742:DAE458742 DJX458742:DKA458742 DTT458742:DTW458742 EDP458742:EDS458742 ENL458742:ENO458742 EXH458742:EXK458742 FHD458742:FHG458742 FQZ458742:FRC458742 GAV458742:GAY458742 GKR458742:GKU458742 GUN458742:GUQ458742 HEJ458742:HEM458742 HOF458742:HOI458742 HYB458742:HYE458742 IHX458742:IIA458742 IRT458742:IRW458742 JBP458742:JBS458742 JLL458742:JLO458742 JVH458742:JVK458742 KFD458742:KFG458742 KOZ458742:KPC458742 KYV458742:KYY458742 LIR458742:LIU458742 LSN458742:LSQ458742 MCJ458742:MCM458742 MMF458742:MMI458742 MWB458742:MWE458742 NFX458742:NGA458742 NPT458742:NPW458742 NZP458742:NZS458742 OJL458742:OJO458742 OTH458742:OTK458742 PDD458742:PDG458742 PMZ458742:PNC458742 PWV458742:PWY458742 QGR458742:QGU458742 QQN458742:QQQ458742 RAJ458742:RAM458742 RKF458742:RKI458742 RUB458742:RUE458742 SDX458742:SEA458742 SNT458742:SNW458742 SXP458742:SXS458742 THL458742:THO458742 TRH458742:TRK458742 UBD458742:UBG458742 UKZ458742:ULC458742 UUV458742:UUY458742 VER458742:VEU458742 VON458742:VOQ458742 VYJ458742:VYM458742 WIF458742:WII458742 WSB458742:WSE458742 FP524278:FS524278 PL524278:PO524278 ZH524278:ZK524278 AJD524278:AJG524278 ASZ524278:ATC524278 BCV524278:BCY524278 BMR524278:BMU524278 BWN524278:BWQ524278 CGJ524278:CGM524278 CQF524278:CQI524278 DAB524278:DAE524278 DJX524278:DKA524278 DTT524278:DTW524278 EDP524278:EDS524278 ENL524278:ENO524278 EXH524278:EXK524278 FHD524278:FHG524278 FQZ524278:FRC524278 GAV524278:GAY524278 GKR524278:GKU524278 GUN524278:GUQ524278 HEJ524278:HEM524278 HOF524278:HOI524278 HYB524278:HYE524278 IHX524278:IIA524278 IRT524278:IRW524278 JBP524278:JBS524278 JLL524278:JLO524278 JVH524278:JVK524278 KFD524278:KFG524278 KOZ524278:KPC524278 KYV524278:KYY524278 LIR524278:LIU524278 LSN524278:LSQ524278 MCJ524278:MCM524278 MMF524278:MMI524278 MWB524278:MWE524278 NFX524278:NGA524278 NPT524278:NPW524278 NZP524278:NZS524278 OJL524278:OJO524278 OTH524278:OTK524278 PDD524278:PDG524278 PMZ524278:PNC524278 PWV524278:PWY524278 QGR524278:QGU524278 QQN524278:QQQ524278 RAJ524278:RAM524278 RKF524278:RKI524278 RUB524278:RUE524278 SDX524278:SEA524278 SNT524278:SNW524278 SXP524278:SXS524278 THL524278:THO524278 TRH524278:TRK524278 UBD524278:UBG524278 UKZ524278:ULC524278 UUV524278:UUY524278 VER524278:VEU524278 VON524278:VOQ524278 VYJ524278:VYM524278 WIF524278:WII524278 WSB524278:WSE524278 FP589814:FS589814 PL589814:PO589814 ZH589814:ZK589814 AJD589814:AJG589814 ASZ589814:ATC589814 BCV589814:BCY589814 BMR589814:BMU589814 BWN589814:BWQ589814 CGJ589814:CGM589814 CQF589814:CQI589814 DAB589814:DAE589814 DJX589814:DKA589814 DTT589814:DTW589814 EDP589814:EDS589814 ENL589814:ENO589814 EXH589814:EXK589814 FHD589814:FHG589814 FQZ589814:FRC589814 GAV589814:GAY589814 GKR589814:GKU589814 GUN589814:GUQ589814 HEJ589814:HEM589814 HOF589814:HOI589814 HYB589814:HYE589814 IHX589814:IIA589814 IRT589814:IRW589814 JBP589814:JBS589814 JLL589814:JLO589814 JVH589814:JVK589814 KFD589814:KFG589814 KOZ589814:KPC589814 KYV589814:KYY589814 LIR589814:LIU589814 LSN589814:LSQ589814 MCJ589814:MCM589814 MMF589814:MMI589814 MWB589814:MWE589814 NFX589814:NGA589814 NPT589814:NPW589814 NZP589814:NZS589814 OJL589814:OJO589814 OTH589814:OTK589814 PDD589814:PDG589814 PMZ589814:PNC589814 PWV589814:PWY589814 QGR589814:QGU589814 QQN589814:QQQ589814 RAJ589814:RAM589814 RKF589814:RKI589814 RUB589814:RUE589814 SDX589814:SEA589814 SNT589814:SNW589814 SXP589814:SXS589814 THL589814:THO589814 TRH589814:TRK589814 UBD589814:UBG589814 UKZ589814:ULC589814 UUV589814:UUY589814 VER589814:VEU589814 VON589814:VOQ589814 VYJ589814:VYM589814 WIF589814:WII589814 WSB589814:WSE589814 FP655350:FS655350 PL655350:PO655350 ZH655350:ZK655350 AJD655350:AJG655350 ASZ655350:ATC655350 BCV655350:BCY655350 BMR655350:BMU655350 BWN655350:BWQ655350 CGJ655350:CGM655350 CQF655350:CQI655350 DAB655350:DAE655350 DJX655350:DKA655350 DTT655350:DTW655350 EDP655350:EDS655350 ENL655350:ENO655350 EXH655350:EXK655350 FHD655350:FHG655350 FQZ655350:FRC655350 GAV655350:GAY655350 GKR655350:GKU655350 GUN655350:GUQ655350 HEJ655350:HEM655350 HOF655350:HOI655350 HYB655350:HYE655350 IHX655350:IIA655350 IRT655350:IRW655350 JBP655350:JBS655350 JLL655350:JLO655350 JVH655350:JVK655350 KFD655350:KFG655350 KOZ655350:KPC655350 KYV655350:KYY655350 LIR655350:LIU655350 LSN655350:LSQ655350 MCJ655350:MCM655350 MMF655350:MMI655350 MWB655350:MWE655350 NFX655350:NGA655350 NPT655350:NPW655350 NZP655350:NZS655350 OJL655350:OJO655350 OTH655350:OTK655350 PDD655350:PDG655350 PMZ655350:PNC655350 PWV655350:PWY655350 QGR655350:QGU655350 QQN655350:QQQ655350 RAJ655350:RAM655350 RKF655350:RKI655350 RUB655350:RUE655350 SDX655350:SEA655350 SNT655350:SNW655350 SXP655350:SXS655350 THL655350:THO655350 TRH655350:TRK655350 UBD655350:UBG655350 UKZ655350:ULC655350 UUV655350:UUY655350 VER655350:VEU655350 VON655350:VOQ655350 VYJ655350:VYM655350 WIF655350:WII655350 WSB655350:WSE655350 FP720886:FS720886 PL720886:PO720886 ZH720886:ZK720886 AJD720886:AJG720886 ASZ720886:ATC720886 BCV720886:BCY720886 BMR720886:BMU720886 BWN720886:BWQ720886 CGJ720886:CGM720886 CQF720886:CQI720886 DAB720886:DAE720886 DJX720886:DKA720886 DTT720886:DTW720886 EDP720886:EDS720886 ENL720886:ENO720886 EXH720886:EXK720886 FHD720886:FHG720886 FQZ720886:FRC720886 GAV720886:GAY720886 GKR720886:GKU720886 GUN720886:GUQ720886 HEJ720886:HEM720886 HOF720886:HOI720886 HYB720886:HYE720886 IHX720886:IIA720886 IRT720886:IRW720886 JBP720886:JBS720886 JLL720886:JLO720886 JVH720886:JVK720886 KFD720886:KFG720886 KOZ720886:KPC720886 KYV720886:KYY720886 LIR720886:LIU720886 LSN720886:LSQ720886 MCJ720886:MCM720886 MMF720886:MMI720886 MWB720886:MWE720886 NFX720886:NGA720886 NPT720886:NPW720886 NZP720886:NZS720886 OJL720886:OJO720886 OTH720886:OTK720886 PDD720886:PDG720886 PMZ720886:PNC720886 PWV720886:PWY720886 QGR720886:QGU720886 QQN720886:QQQ720886 RAJ720886:RAM720886 RKF720886:RKI720886 RUB720886:RUE720886 SDX720886:SEA720886 SNT720886:SNW720886 SXP720886:SXS720886 THL720886:THO720886 TRH720886:TRK720886 UBD720886:UBG720886 UKZ720886:ULC720886 UUV720886:UUY720886 VER720886:VEU720886 VON720886:VOQ720886 VYJ720886:VYM720886 WIF720886:WII720886 WSB720886:WSE720886 FP786422:FS786422 PL786422:PO786422 ZH786422:ZK786422 AJD786422:AJG786422 ASZ786422:ATC786422 BCV786422:BCY786422 BMR786422:BMU786422 BWN786422:BWQ786422 CGJ786422:CGM786422 CQF786422:CQI786422 DAB786422:DAE786422 DJX786422:DKA786422 DTT786422:DTW786422 EDP786422:EDS786422 ENL786422:ENO786422 EXH786422:EXK786422 FHD786422:FHG786422 FQZ786422:FRC786422 GAV786422:GAY786422 GKR786422:GKU786422 GUN786422:GUQ786422 HEJ786422:HEM786422 HOF786422:HOI786422 HYB786422:HYE786422 IHX786422:IIA786422 IRT786422:IRW786422 JBP786422:JBS786422 JLL786422:JLO786422 JVH786422:JVK786422 KFD786422:KFG786422 KOZ786422:KPC786422 KYV786422:KYY786422 LIR786422:LIU786422 LSN786422:LSQ786422 MCJ786422:MCM786422 MMF786422:MMI786422 MWB786422:MWE786422 NFX786422:NGA786422 NPT786422:NPW786422 NZP786422:NZS786422 OJL786422:OJO786422 OTH786422:OTK786422 PDD786422:PDG786422 PMZ786422:PNC786422 PWV786422:PWY786422 QGR786422:QGU786422 QQN786422:QQQ786422 RAJ786422:RAM786422 RKF786422:RKI786422 RUB786422:RUE786422 SDX786422:SEA786422 SNT786422:SNW786422 SXP786422:SXS786422 THL786422:THO786422 TRH786422:TRK786422 UBD786422:UBG786422 UKZ786422:ULC786422 UUV786422:UUY786422 VER786422:VEU786422 VON786422:VOQ786422 VYJ786422:VYM786422 WIF786422:WII786422 WSB786422:WSE786422 FP851958:FS851958 PL851958:PO851958 ZH851958:ZK851958 AJD851958:AJG851958 ASZ851958:ATC851958 BCV851958:BCY851958 BMR851958:BMU851958 BWN851958:BWQ851958 CGJ851958:CGM851958 CQF851958:CQI851958 DAB851958:DAE851958 DJX851958:DKA851958 DTT851958:DTW851958 EDP851958:EDS851958 ENL851958:ENO851958 EXH851958:EXK851958 FHD851958:FHG851958 FQZ851958:FRC851958 GAV851958:GAY851958 GKR851958:GKU851958 GUN851958:GUQ851958 HEJ851958:HEM851958 HOF851958:HOI851958 HYB851958:HYE851958 IHX851958:IIA851958 IRT851958:IRW851958 JBP851958:JBS851958 JLL851958:JLO851958 JVH851958:JVK851958 KFD851958:KFG851958 KOZ851958:KPC851958 KYV851958:KYY851958 LIR851958:LIU851958 LSN851958:LSQ851958 MCJ851958:MCM851958 MMF851958:MMI851958 MWB851958:MWE851958 NFX851958:NGA851958 NPT851958:NPW851958 NZP851958:NZS851958 OJL851958:OJO851958 OTH851958:OTK851958 PDD851958:PDG851958 PMZ851958:PNC851958 PWV851958:PWY851958 QGR851958:QGU851958 QQN851958:QQQ851958 RAJ851958:RAM851958 RKF851958:RKI851958 RUB851958:RUE851958 SDX851958:SEA851958 SNT851958:SNW851958 SXP851958:SXS851958 THL851958:THO851958 TRH851958:TRK851958 UBD851958:UBG851958 UKZ851958:ULC851958 UUV851958:UUY851958 VER851958:VEU851958 VON851958:VOQ851958 VYJ851958:VYM851958 WIF851958:WII851958 WSB851958:WSE851958 FP917494:FS917494 PL917494:PO917494 ZH917494:ZK917494 AJD917494:AJG917494 ASZ917494:ATC917494 BCV917494:BCY917494 BMR917494:BMU917494 BWN917494:BWQ917494 CGJ917494:CGM917494 CQF917494:CQI917494 DAB917494:DAE917494 DJX917494:DKA917494 DTT917494:DTW917494 EDP917494:EDS917494 ENL917494:ENO917494 EXH917494:EXK917494 FHD917494:FHG917494 FQZ917494:FRC917494 GAV917494:GAY917494 GKR917494:GKU917494 GUN917494:GUQ917494 HEJ917494:HEM917494 HOF917494:HOI917494 HYB917494:HYE917494 IHX917494:IIA917494 IRT917494:IRW917494 JBP917494:JBS917494 JLL917494:JLO917494 JVH917494:JVK917494 KFD917494:KFG917494 KOZ917494:KPC917494 KYV917494:KYY917494 LIR917494:LIU917494 LSN917494:LSQ917494 MCJ917494:MCM917494 MMF917494:MMI917494 MWB917494:MWE917494 NFX917494:NGA917494 NPT917494:NPW917494 NZP917494:NZS917494 OJL917494:OJO917494 OTH917494:OTK917494 PDD917494:PDG917494 PMZ917494:PNC917494 PWV917494:PWY917494 QGR917494:QGU917494 QQN917494:QQQ917494 RAJ917494:RAM917494 RKF917494:RKI917494 RUB917494:RUE917494 SDX917494:SEA917494 SNT917494:SNW917494 SXP917494:SXS917494 THL917494:THO917494 TRH917494:TRK917494 UBD917494:UBG917494 UKZ917494:ULC917494 UUV917494:UUY917494 VER917494:VEU917494 VON917494:VOQ917494 VYJ917494:VYM917494 WIF917494:WII917494 WSB917494:WSE917494 FP983030:FS983030 PL983030:PO983030 ZH983030:ZK983030 AJD983030:AJG983030 ASZ983030:ATC983030 BCV983030:BCY983030 BMR983030:BMU983030 BWN983030:BWQ983030 CGJ983030:CGM983030 CQF983030:CQI983030 DAB983030:DAE983030 DJX983030:DKA983030 DTT983030:DTW983030 EDP983030:EDS983030 ENL983030:ENO983030 EXH983030:EXK983030 FHD983030:FHG983030 FQZ983030:FRC983030 GAV983030:GAY983030 GKR983030:GKU983030 GUN983030:GUQ983030 HEJ983030:HEM983030 HOF983030:HOI983030 HYB983030:HYE983030 IHX983030:IIA983030 IRT983030:IRW983030 JBP983030:JBS983030 JLL983030:JLO983030 JVH983030:JVK983030 KFD983030:KFG983030 KOZ983030:KPC983030 KYV983030:KYY983030 LIR983030:LIU983030 LSN983030:LSQ983030 MCJ983030:MCM983030 MMF983030:MMI983030 MWB983030:MWE983030 NFX983030:NGA983030 NPT983030:NPW983030 NZP983030:NZS983030 OJL983030:OJO983030 OTH983030:OTK983030 PDD983030:PDG983030 PMZ983030:PNC983030 PWV983030:PWY983030 QGR983030:QGU983030 QQN983030:QQQ983030 RAJ983030:RAM983030 RKF983030:RKI983030 RUB983030:RUE983030 SDX983030:SEA983030 SNT983030:SNW983030 SXP983030:SXS983030 THL983030:THO983030 TRH983030:TRK983030 UBD983030:UBG983030 UKZ983030:ULC983030 UUV983030:UUY983030 VER983030:VEU983030 VON983030:VOQ983030 VYJ983030:VYM983030 WIF983030:WII983030 WSB983030:WSE983030 FK983029:FN983029 PG983029:PJ983029 ZC983029:ZF983029 AIY983029:AJB983029 ASU983029:ASX983029 BCQ983029:BCT983029 BMM983029:BMP983029 BWI983029:BWL983029 CGE983029:CGH983029 CQA983029:CQD983029 CZW983029:CZZ983029 DJS983029:DJV983029 DTO983029:DTR983029 EDK983029:EDN983029 ENG983029:ENJ983029 EXC983029:EXF983029 FGY983029:FHB983029 FQU983029:FQX983029 GAQ983029:GAT983029 GKM983029:GKP983029 GUI983029:GUL983029 HEE983029:HEH983029 HOA983029:HOD983029 HXW983029:HXZ983029 IHS983029:IHV983029 IRO983029:IRR983029 JBK983029:JBN983029 JLG983029:JLJ983029 JVC983029:JVF983029 KEY983029:KFB983029 KOU983029:KOX983029 KYQ983029:KYT983029 LIM983029:LIP983029 LSI983029:LSL983029 MCE983029:MCH983029 MMA983029:MMD983029 MVW983029:MVZ983029 NFS983029:NFV983029 NPO983029:NPR983029 NZK983029:NZN983029 OJG983029:OJJ983029 OTC983029:OTF983029 PCY983029:PDB983029 PMU983029:PMX983029 PWQ983029:PWT983029 QGM983029:QGP983029 QQI983029:QQL983029 RAE983029:RAH983029 RKA983029:RKD983029 RTW983029:RTZ983029 SDS983029:SDV983029 SNO983029:SNR983029 SXK983029:SXN983029 THG983029:THJ983029 TRC983029:TRF983029 UAY983029:UBB983029 UKU983029:UKX983029 UUQ983029:UUT983029 VEM983029:VEP983029 VOI983029:VOL983029 VYE983029:VYH983029 WIA983029:WID983029 WRW983029:WRZ983029 FK65525:FN65525 PG65525:PJ65525 ZC65525:ZF65525 AIY65525:AJB65525 ASU65525:ASX65525 BCQ65525:BCT65525 BMM65525:BMP65525 BWI65525:BWL65525 CGE65525:CGH65525 CQA65525:CQD65525 CZW65525:CZZ65525 DJS65525:DJV65525 DTO65525:DTR65525 EDK65525:EDN65525 ENG65525:ENJ65525 EXC65525:EXF65525 FGY65525:FHB65525 FQU65525:FQX65525 GAQ65525:GAT65525 GKM65525:GKP65525 GUI65525:GUL65525 HEE65525:HEH65525 HOA65525:HOD65525 HXW65525:HXZ65525 IHS65525:IHV65525 IRO65525:IRR65525 JBK65525:JBN65525 JLG65525:JLJ65525 JVC65525:JVF65525 KEY65525:KFB65525 KOU65525:KOX65525 KYQ65525:KYT65525 LIM65525:LIP65525 LSI65525:LSL65525 MCE65525:MCH65525 MMA65525:MMD65525 MVW65525:MVZ65525 NFS65525:NFV65525 NPO65525:NPR65525 NZK65525:NZN65525 OJG65525:OJJ65525 OTC65525:OTF65525 PCY65525:PDB65525 PMU65525:PMX65525 PWQ65525:PWT65525 QGM65525:QGP65525 QQI65525:QQL65525 RAE65525:RAH65525 RKA65525:RKD65525 RTW65525:RTZ65525 SDS65525:SDV65525 SNO65525:SNR65525 SXK65525:SXN65525 THG65525:THJ65525 TRC65525:TRF65525 UAY65525:UBB65525 UKU65525:UKX65525 UUQ65525:UUT65525 VEM65525:VEP65525 VOI65525:VOL65525 VYE65525:VYH65525 WIA65525:WID65525 WRW65525:WRZ65525 FK131061:FN131061 PG131061:PJ131061 ZC131061:ZF131061 AIY131061:AJB131061 ASU131061:ASX131061 BCQ131061:BCT131061 BMM131061:BMP131061 BWI131061:BWL131061 CGE131061:CGH131061 CQA131061:CQD131061 CZW131061:CZZ131061 DJS131061:DJV131061 DTO131061:DTR131061 EDK131061:EDN131061 ENG131061:ENJ131061 EXC131061:EXF131061 FGY131061:FHB131061 FQU131061:FQX131061 GAQ131061:GAT131061 GKM131061:GKP131061 GUI131061:GUL131061 HEE131061:HEH131061 HOA131061:HOD131061 HXW131061:HXZ131061 IHS131061:IHV131061 IRO131061:IRR131061 JBK131061:JBN131061 JLG131061:JLJ131061 JVC131061:JVF131061 KEY131061:KFB131061 KOU131061:KOX131061 KYQ131061:KYT131061 LIM131061:LIP131061 LSI131061:LSL131061 MCE131061:MCH131061 MMA131061:MMD131061 MVW131061:MVZ131061 NFS131061:NFV131061 NPO131061:NPR131061 NZK131061:NZN131061 OJG131061:OJJ131061 OTC131061:OTF131061 PCY131061:PDB131061 PMU131061:PMX131061 PWQ131061:PWT131061 QGM131061:QGP131061 QQI131061:QQL131061 RAE131061:RAH131061 RKA131061:RKD131061 RTW131061:RTZ131061 SDS131061:SDV131061 SNO131061:SNR131061 SXK131061:SXN131061 THG131061:THJ131061 TRC131061:TRF131061 UAY131061:UBB131061 UKU131061:UKX131061 UUQ131061:UUT131061 VEM131061:VEP131061 VOI131061:VOL131061 VYE131061:VYH131061 WIA131061:WID131061 WRW131061:WRZ131061 FK196597:FN196597 PG196597:PJ196597 ZC196597:ZF196597 AIY196597:AJB196597 ASU196597:ASX196597 BCQ196597:BCT196597 BMM196597:BMP196597 BWI196597:BWL196597 CGE196597:CGH196597 CQA196597:CQD196597 CZW196597:CZZ196597 DJS196597:DJV196597 DTO196597:DTR196597 EDK196597:EDN196597 ENG196597:ENJ196597 EXC196597:EXF196597 FGY196597:FHB196597 FQU196597:FQX196597 GAQ196597:GAT196597 GKM196597:GKP196597 GUI196597:GUL196597 HEE196597:HEH196597 HOA196597:HOD196597 HXW196597:HXZ196597 IHS196597:IHV196597 IRO196597:IRR196597 JBK196597:JBN196597 JLG196597:JLJ196597 JVC196597:JVF196597 KEY196597:KFB196597 KOU196597:KOX196597 KYQ196597:KYT196597 LIM196597:LIP196597 LSI196597:LSL196597 MCE196597:MCH196597 MMA196597:MMD196597 MVW196597:MVZ196597 NFS196597:NFV196597 NPO196597:NPR196597 NZK196597:NZN196597 OJG196597:OJJ196597 OTC196597:OTF196597 PCY196597:PDB196597 PMU196597:PMX196597 PWQ196597:PWT196597 QGM196597:QGP196597 QQI196597:QQL196597 RAE196597:RAH196597 RKA196597:RKD196597 RTW196597:RTZ196597 SDS196597:SDV196597 SNO196597:SNR196597 SXK196597:SXN196597 THG196597:THJ196597 TRC196597:TRF196597 UAY196597:UBB196597 UKU196597:UKX196597 UUQ196597:UUT196597 VEM196597:VEP196597 VOI196597:VOL196597 VYE196597:VYH196597 WIA196597:WID196597 WRW196597:WRZ196597 FK262133:FN262133 PG262133:PJ262133 ZC262133:ZF262133 AIY262133:AJB262133 ASU262133:ASX262133 BCQ262133:BCT262133 BMM262133:BMP262133 BWI262133:BWL262133 CGE262133:CGH262133 CQA262133:CQD262133 CZW262133:CZZ262133 DJS262133:DJV262133 DTO262133:DTR262133 EDK262133:EDN262133 ENG262133:ENJ262133 EXC262133:EXF262133 FGY262133:FHB262133 FQU262133:FQX262133 GAQ262133:GAT262133 GKM262133:GKP262133 GUI262133:GUL262133 HEE262133:HEH262133 HOA262133:HOD262133 HXW262133:HXZ262133 IHS262133:IHV262133 IRO262133:IRR262133 JBK262133:JBN262133 JLG262133:JLJ262133 JVC262133:JVF262133 KEY262133:KFB262133 KOU262133:KOX262133 KYQ262133:KYT262133 LIM262133:LIP262133 LSI262133:LSL262133 MCE262133:MCH262133 MMA262133:MMD262133 MVW262133:MVZ262133 NFS262133:NFV262133 NPO262133:NPR262133 NZK262133:NZN262133 OJG262133:OJJ262133 OTC262133:OTF262133 PCY262133:PDB262133 PMU262133:PMX262133 PWQ262133:PWT262133 QGM262133:QGP262133 QQI262133:QQL262133 RAE262133:RAH262133 RKA262133:RKD262133 RTW262133:RTZ262133 SDS262133:SDV262133 SNO262133:SNR262133 SXK262133:SXN262133 THG262133:THJ262133 TRC262133:TRF262133 UAY262133:UBB262133 UKU262133:UKX262133 UUQ262133:UUT262133 VEM262133:VEP262133 VOI262133:VOL262133 VYE262133:VYH262133 WIA262133:WID262133 WRW262133:WRZ262133 FK327669:FN327669 PG327669:PJ327669 ZC327669:ZF327669 AIY327669:AJB327669 ASU327669:ASX327669 BCQ327669:BCT327669 BMM327669:BMP327669 BWI327669:BWL327669 CGE327669:CGH327669 CQA327669:CQD327669 CZW327669:CZZ327669 DJS327669:DJV327669 DTO327669:DTR327669 EDK327669:EDN327669 ENG327669:ENJ327669 EXC327669:EXF327669 FGY327669:FHB327669 FQU327669:FQX327669 GAQ327669:GAT327669 GKM327669:GKP327669 GUI327669:GUL327669 HEE327669:HEH327669 HOA327669:HOD327669 HXW327669:HXZ327669 IHS327669:IHV327669 IRO327669:IRR327669 JBK327669:JBN327669 JLG327669:JLJ327669 JVC327669:JVF327669 KEY327669:KFB327669 KOU327669:KOX327669 KYQ327669:KYT327669 LIM327669:LIP327669 LSI327669:LSL327669 MCE327669:MCH327669 MMA327669:MMD327669 MVW327669:MVZ327669 NFS327669:NFV327669 NPO327669:NPR327669 NZK327669:NZN327669 OJG327669:OJJ327669 OTC327669:OTF327669 PCY327669:PDB327669 PMU327669:PMX327669 PWQ327669:PWT327669 QGM327669:QGP327669 QQI327669:QQL327669 RAE327669:RAH327669 RKA327669:RKD327669 RTW327669:RTZ327669 SDS327669:SDV327669 SNO327669:SNR327669 SXK327669:SXN327669 THG327669:THJ327669 TRC327669:TRF327669 UAY327669:UBB327669 UKU327669:UKX327669 UUQ327669:UUT327669 VEM327669:VEP327669 VOI327669:VOL327669 VYE327669:VYH327669 WIA327669:WID327669 WRW327669:WRZ327669 FK393205:FN393205 PG393205:PJ393205 ZC393205:ZF393205 AIY393205:AJB393205 ASU393205:ASX393205 BCQ393205:BCT393205 BMM393205:BMP393205 BWI393205:BWL393205 CGE393205:CGH393205 CQA393205:CQD393205 CZW393205:CZZ393205 DJS393205:DJV393205 DTO393205:DTR393205 EDK393205:EDN393205 ENG393205:ENJ393205 EXC393205:EXF393205 FGY393205:FHB393205 FQU393205:FQX393205 GAQ393205:GAT393205 GKM393205:GKP393205 GUI393205:GUL393205 HEE393205:HEH393205 HOA393205:HOD393205 HXW393205:HXZ393205 IHS393205:IHV393205 IRO393205:IRR393205 JBK393205:JBN393205 JLG393205:JLJ393205 JVC393205:JVF393205 KEY393205:KFB393205 KOU393205:KOX393205 KYQ393205:KYT393205 LIM393205:LIP393205 LSI393205:LSL393205 MCE393205:MCH393205 MMA393205:MMD393205 MVW393205:MVZ393205 NFS393205:NFV393205 NPO393205:NPR393205 NZK393205:NZN393205 OJG393205:OJJ393205 OTC393205:OTF393205 PCY393205:PDB393205 PMU393205:PMX393205 PWQ393205:PWT393205 QGM393205:QGP393205 QQI393205:QQL393205 RAE393205:RAH393205 RKA393205:RKD393205 RTW393205:RTZ393205 SDS393205:SDV393205 SNO393205:SNR393205 SXK393205:SXN393205 THG393205:THJ393205 TRC393205:TRF393205 UAY393205:UBB393205 UKU393205:UKX393205 UUQ393205:UUT393205 VEM393205:VEP393205 VOI393205:VOL393205 VYE393205:VYH393205 WIA393205:WID393205 WRW393205:WRZ393205 FK458741:FN458741 PG458741:PJ458741 ZC458741:ZF458741 AIY458741:AJB458741 ASU458741:ASX458741 BCQ458741:BCT458741 BMM458741:BMP458741 BWI458741:BWL458741 CGE458741:CGH458741 CQA458741:CQD458741 CZW458741:CZZ458741 DJS458741:DJV458741 DTO458741:DTR458741 EDK458741:EDN458741 ENG458741:ENJ458741 EXC458741:EXF458741 FGY458741:FHB458741 FQU458741:FQX458741 GAQ458741:GAT458741 GKM458741:GKP458741 GUI458741:GUL458741 HEE458741:HEH458741 HOA458741:HOD458741 HXW458741:HXZ458741 IHS458741:IHV458741 IRO458741:IRR458741 JBK458741:JBN458741 JLG458741:JLJ458741 JVC458741:JVF458741 KEY458741:KFB458741 KOU458741:KOX458741 KYQ458741:KYT458741 LIM458741:LIP458741 LSI458741:LSL458741 MCE458741:MCH458741 MMA458741:MMD458741 MVW458741:MVZ458741 NFS458741:NFV458741 NPO458741:NPR458741 NZK458741:NZN458741 OJG458741:OJJ458741 OTC458741:OTF458741 PCY458741:PDB458741 PMU458741:PMX458741 PWQ458741:PWT458741 QGM458741:QGP458741 QQI458741:QQL458741 RAE458741:RAH458741 RKA458741:RKD458741 RTW458741:RTZ458741 SDS458741:SDV458741 SNO458741:SNR458741 SXK458741:SXN458741 THG458741:THJ458741 TRC458741:TRF458741 UAY458741:UBB458741 UKU458741:UKX458741 UUQ458741:UUT458741 VEM458741:VEP458741 VOI458741:VOL458741 VYE458741:VYH458741 WIA458741:WID458741 WRW458741:WRZ458741 FK524277:FN524277 PG524277:PJ524277 ZC524277:ZF524277 AIY524277:AJB524277 ASU524277:ASX524277 BCQ524277:BCT524277 BMM524277:BMP524277 BWI524277:BWL524277 CGE524277:CGH524277 CQA524277:CQD524277 CZW524277:CZZ524277 DJS524277:DJV524277 DTO524277:DTR524277 EDK524277:EDN524277 ENG524277:ENJ524277 EXC524277:EXF524277 FGY524277:FHB524277 FQU524277:FQX524277 GAQ524277:GAT524277 GKM524277:GKP524277 GUI524277:GUL524277 HEE524277:HEH524277 HOA524277:HOD524277 HXW524277:HXZ524277 IHS524277:IHV524277 IRO524277:IRR524277 JBK524277:JBN524277 JLG524277:JLJ524277 JVC524277:JVF524277 KEY524277:KFB524277 KOU524277:KOX524277 KYQ524277:KYT524277 LIM524277:LIP524277 LSI524277:LSL524277 MCE524277:MCH524277 MMA524277:MMD524277 MVW524277:MVZ524277 NFS524277:NFV524277 NPO524277:NPR524277 NZK524277:NZN524277 OJG524277:OJJ524277 OTC524277:OTF524277 PCY524277:PDB524277 PMU524277:PMX524277 PWQ524277:PWT524277 QGM524277:QGP524277 QQI524277:QQL524277 RAE524277:RAH524277 RKA524277:RKD524277 RTW524277:RTZ524277 SDS524277:SDV524277 SNO524277:SNR524277 SXK524277:SXN524277 THG524277:THJ524277 TRC524277:TRF524277 UAY524277:UBB524277 UKU524277:UKX524277 UUQ524277:UUT524277 VEM524277:VEP524277 VOI524277:VOL524277 VYE524277:VYH524277 WIA524277:WID524277 WRW524277:WRZ524277 FK589813:FN589813 PG589813:PJ589813 ZC589813:ZF589813 AIY589813:AJB589813 ASU589813:ASX589813 BCQ589813:BCT589813 BMM589813:BMP589813 BWI589813:BWL589813 CGE589813:CGH589813 CQA589813:CQD589813 CZW589813:CZZ589813 DJS589813:DJV589813 DTO589813:DTR589813 EDK589813:EDN589813 ENG589813:ENJ589813 EXC589813:EXF589813 FGY589813:FHB589813 FQU589813:FQX589813 GAQ589813:GAT589813 GKM589813:GKP589813 GUI589813:GUL589813 HEE589813:HEH589813 HOA589813:HOD589813 HXW589813:HXZ589813 IHS589813:IHV589813 IRO589813:IRR589813 JBK589813:JBN589813 JLG589813:JLJ589813 JVC589813:JVF589813 KEY589813:KFB589813 KOU589813:KOX589813 KYQ589813:KYT589813 LIM589813:LIP589813 LSI589813:LSL589813 MCE589813:MCH589813 MMA589813:MMD589813 MVW589813:MVZ589813 NFS589813:NFV589813 NPO589813:NPR589813 NZK589813:NZN589813 OJG589813:OJJ589813 OTC589813:OTF589813 PCY589813:PDB589813 PMU589813:PMX589813 PWQ589813:PWT589813 QGM589813:QGP589813 QQI589813:QQL589813 RAE589813:RAH589813 RKA589813:RKD589813 RTW589813:RTZ589813 SDS589813:SDV589813 SNO589813:SNR589813 SXK589813:SXN589813 THG589813:THJ589813 TRC589813:TRF589813 UAY589813:UBB589813 UKU589813:UKX589813 UUQ589813:UUT589813 VEM589813:VEP589813 VOI589813:VOL589813 VYE589813:VYH589813 WIA589813:WID589813 WRW589813:WRZ589813 FK655349:FN655349 PG655349:PJ655349 ZC655349:ZF655349 AIY655349:AJB655349 ASU655349:ASX655349 BCQ655349:BCT655349 BMM655349:BMP655349 BWI655349:BWL655349 CGE655349:CGH655349 CQA655349:CQD655349 CZW655349:CZZ655349 DJS655349:DJV655349 DTO655349:DTR655349 EDK655349:EDN655349 ENG655349:ENJ655349 EXC655349:EXF655349 FGY655349:FHB655349 FQU655349:FQX655349 GAQ655349:GAT655349 GKM655349:GKP655349 GUI655349:GUL655349 HEE655349:HEH655349 HOA655349:HOD655349 HXW655349:HXZ655349 IHS655349:IHV655349 IRO655349:IRR655349 JBK655349:JBN655349 JLG655349:JLJ655349 JVC655349:JVF655349 KEY655349:KFB655349 KOU655349:KOX655349 KYQ655349:KYT655349 LIM655349:LIP655349 LSI655349:LSL655349 MCE655349:MCH655349 MMA655349:MMD655349 MVW655349:MVZ655349 NFS655349:NFV655349 NPO655349:NPR655349 NZK655349:NZN655349 OJG655349:OJJ655349 OTC655349:OTF655349 PCY655349:PDB655349 PMU655349:PMX655349 PWQ655349:PWT655349 QGM655349:QGP655349 QQI655349:QQL655349 RAE655349:RAH655349 RKA655349:RKD655349 RTW655349:RTZ655349 SDS655349:SDV655349 SNO655349:SNR655349 SXK655349:SXN655349 THG655349:THJ655349 TRC655349:TRF655349 UAY655349:UBB655349 UKU655349:UKX655349 UUQ655349:UUT655349 VEM655349:VEP655349 VOI655349:VOL655349 VYE655349:VYH655349 WIA655349:WID655349 WRW655349:WRZ655349 FK720885:FN720885 PG720885:PJ720885 ZC720885:ZF720885 AIY720885:AJB720885 ASU720885:ASX720885 BCQ720885:BCT720885 BMM720885:BMP720885 BWI720885:BWL720885 CGE720885:CGH720885 CQA720885:CQD720885 CZW720885:CZZ720885 DJS720885:DJV720885 DTO720885:DTR720885 EDK720885:EDN720885 ENG720885:ENJ720885 EXC720885:EXF720885 FGY720885:FHB720885 FQU720885:FQX720885 GAQ720885:GAT720885 GKM720885:GKP720885 GUI720885:GUL720885 HEE720885:HEH720885 HOA720885:HOD720885 HXW720885:HXZ720885 IHS720885:IHV720885 IRO720885:IRR720885 JBK720885:JBN720885 JLG720885:JLJ720885 JVC720885:JVF720885 KEY720885:KFB720885 KOU720885:KOX720885 KYQ720885:KYT720885 LIM720885:LIP720885 LSI720885:LSL720885 MCE720885:MCH720885 MMA720885:MMD720885 MVW720885:MVZ720885 NFS720885:NFV720885 NPO720885:NPR720885 NZK720885:NZN720885 OJG720885:OJJ720885 OTC720885:OTF720885 PCY720885:PDB720885 PMU720885:PMX720885 PWQ720885:PWT720885 QGM720885:QGP720885 QQI720885:QQL720885 RAE720885:RAH720885 RKA720885:RKD720885 RTW720885:RTZ720885 SDS720885:SDV720885 SNO720885:SNR720885 SXK720885:SXN720885 THG720885:THJ720885 TRC720885:TRF720885 UAY720885:UBB720885 UKU720885:UKX720885 UUQ720885:UUT720885 VEM720885:VEP720885 VOI720885:VOL720885 VYE720885:VYH720885 WIA720885:WID720885 WRW720885:WRZ720885 FK786421:FN786421 PG786421:PJ786421 ZC786421:ZF786421 AIY786421:AJB786421 ASU786421:ASX786421 BCQ786421:BCT786421 BMM786421:BMP786421 BWI786421:BWL786421 CGE786421:CGH786421 CQA786421:CQD786421 CZW786421:CZZ786421 DJS786421:DJV786421 DTO786421:DTR786421 EDK786421:EDN786421 ENG786421:ENJ786421 EXC786421:EXF786421 FGY786421:FHB786421 FQU786421:FQX786421 GAQ786421:GAT786421 GKM786421:GKP786421 GUI786421:GUL786421 HEE786421:HEH786421 HOA786421:HOD786421 HXW786421:HXZ786421 IHS786421:IHV786421 IRO786421:IRR786421 JBK786421:JBN786421 JLG786421:JLJ786421 JVC786421:JVF786421 KEY786421:KFB786421 KOU786421:KOX786421 KYQ786421:KYT786421 LIM786421:LIP786421 LSI786421:LSL786421 MCE786421:MCH786421 MMA786421:MMD786421 MVW786421:MVZ786421 NFS786421:NFV786421 NPO786421:NPR786421 NZK786421:NZN786421 OJG786421:OJJ786421 OTC786421:OTF786421 PCY786421:PDB786421 PMU786421:PMX786421 PWQ786421:PWT786421 QGM786421:QGP786421 QQI786421:QQL786421 RAE786421:RAH786421 RKA786421:RKD786421 RTW786421:RTZ786421 SDS786421:SDV786421 SNO786421:SNR786421 SXK786421:SXN786421 THG786421:THJ786421 TRC786421:TRF786421 UAY786421:UBB786421 UKU786421:UKX786421 UUQ786421:UUT786421 VEM786421:VEP786421 VOI786421:VOL786421 VYE786421:VYH786421 WIA786421:WID786421 WRW786421:WRZ786421 FK851957:FN851957 PG851957:PJ851957 ZC851957:ZF851957 AIY851957:AJB851957 ASU851957:ASX851957 BCQ851957:BCT851957 BMM851957:BMP851957 BWI851957:BWL851957 CGE851957:CGH851957 CQA851957:CQD851957 CZW851957:CZZ851957 DJS851957:DJV851957 DTO851957:DTR851957 EDK851957:EDN851957 ENG851957:ENJ851957 EXC851957:EXF851957 FGY851957:FHB851957 FQU851957:FQX851957 GAQ851957:GAT851957 GKM851957:GKP851957 GUI851957:GUL851957 HEE851957:HEH851957 HOA851957:HOD851957 HXW851957:HXZ851957 IHS851957:IHV851957 IRO851957:IRR851957 JBK851957:JBN851957 JLG851957:JLJ851957 JVC851957:JVF851957 KEY851957:KFB851957 KOU851957:KOX851957 KYQ851957:KYT851957 LIM851957:LIP851957 LSI851957:LSL851957 MCE851957:MCH851957 MMA851957:MMD851957 MVW851957:MVZ851957 NFS851957:NFV851957 NPO851957:NPR851957 NZK851957:NZN851957 OJG851957:OJJ851957 OTC851957:OTF851957 PCY851957:PDB851957 PMU851957:PMX851957 PWQ851957:PWT851957 QGM851957:QGP851957 QQI851957:QQL851957 RAE851957:RAH851957 RKA851957:RKD851957 RTW851957:RTZ851957 SDS851957:SDV851957 SNO851957:SNR851957 SXK851957:SXN851957 THG851957:THJ851957 TRC851957:TRF851957 UAY851957:UBB851957 UKU851957:UKX851957 UUQ851957:UUT851957 VEM851957:VEP851957 VOI851957:VOL851957 VYE851957:VYH851957 WIA851957:WID851957 WRW851957:WRZ851957 FK917493:FN917493 PG917493:PJ917493 ZC917493:ZF917493 AIY917493:AJB917493 ASU917493:ASX917493 BCQ917493:BCT917493 BMM917493:BMP917493 BWI917493:BWL917493 CGE917493:CGH917493 CQA917493:CQD917493 CZW917493:CZZ917493 DJS917493:DJV917493 DTO917493:DTR917493 EDK917493:EDN917493 ENG917493:ENJ917493 EXC917493:EXF917493 FGY917493:FHB917493 FQU917493:FQX917493 GAQ917493:GAT917493 GKM917493:GKP917493 GUI917493:GUL917493 HEE917493:HEH917493 HOA917493:HOD917493 HXW917493:HXZ917493 IHS917493:IHV917493 IRO917493:IRR917493 JBK917493:JBN917493 JLG917493:JLJ917493 JVC917493:JVF917493 KEY917493:KFB917493 KOU917493:KOX917493 KYQ917493:KYT917493 LIM917493:LIP917493 LSI917493:LSL917493 MCE917493:MCH917493 MMA917493:MMD917493 MVW917493:MVZ917493 NFS917493:NFV917493 NPO917493:NPR917493 NZK917493:NZN917493 OJG917493:OJJ917493 OTC917493:OTF917493 PCY917493:PDB917493 PMU917493:PMX917493 PWQ917493:PWT917493 QGM917493:QGP917493 QQI917493:QQL917493 RAE917493:RAH917493 RKA917493:RKD917493 RTW917493:RTZ917493 SDS917493:SDV917493 SNO917493:SNR917493 SXK917493:SXN917493 THG917493:THJ917493 TRC917493:TRF917493 UAY917493:UBB917493 UKU917493:UKX917493 UUQ917493:UUT917493 VEM917493:VEP917493 VOI917493:VOL917493 VYE917493:VYH917493 WIA917493:WID917493 WRW917493:WRZ917493" xr:uid="{14D49F8C-9954-484F-BBA9-C0A70DEAE551}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FU65526:FX65529 PQ65526:PT65529 ZM65526:ZP65529 AJI65526:AJL65529 ATE65526:ATH65529 BDA65526:BDD65529 BMW65526:BMZ65529 BWS65526:BWV65529 CGO65526:CGR65529 CQK65526:CQN65529 DAG65526:DAJ65529 DKC65526:DKF65529 DTY65526:DUB65529 EDU65526:EDX65529 ENQ65526:ENT65529 EXM65526:EXP65529 FHI65526:FHL65529 FRE65526:FRH65529 GBA65526:GBD65529 GKW65526:GKZ65529 GUS65526:GUV65529 HEO65526:HER65529 HOK65526:HON65529 HYG65526:HYJ65529 IIC65526:IIF65529 IRY65526:ISB65529 JBU65526:JBX65529 JLQ65526:JLT65529 JVM65526:JVP65529 KFI65526:KFL65529 KPE65526:KPH65529 KZA65526:KZD65529 LIW65526:LIZ65529 LSS65526:LSV65529 MCO65526:MCR65529 MMK65526:MMN65529 MWG65526:MWJ65529 NGC65526:NGF65529 NPY65526:NQB65529 NZU65526:NZX65529 OJQ65526:OJT65529 OTM65526:OTP65529 PDI65526:PDL65529 PNE65526:PNH65529 PXA65526:PXD65529 QGW65526:QGZ65529 QQS65526:QQV65529 RAO65526:RAR65529 RKK65526:RKN65529 RUG65526:RUJ65529 SEC65526:SEF65529 SNY65526:SOB65529 SXU65526:SXX65529 THQ65526:THT65529 TRM65526:TRP65529 UBI65526:UBL65529 ULE65526:ULH65529 UVA65526:UVD65529 VEW65526:VEZ65529 VOS65526:VOV65529 VYO65526:VYR65529 WIK65526:WIN65529 WSG65526:WSJ65529 FU131062:FX131065 PQ131062:PT131065 ZM131062:ZP131065 AJI131062:AJL131065 ATE131062:ATH131065 BDA131062:BDD131065 BMW131062:BMZ131065 BWS131062:BWV131065 CGO131062:CGR131065 CQK131062:CQN131065 DAG131062:DAJ131065 DKC131062:DKF131065 DTY131062:DUB131065 EDU131062:EDX131065 ENQ131062:ENT131065 EXM131062:EXP131065 FHI131062:FHL131065 FRE131062:FRH131065 GBA131062:GBD131065 GKW131062:GKZ131065 GUS131062:GUV131065 HEO131062:HER131065 HOK131062:HON131065 HYG131062:HYJ131065 IIC131062:IIF131065 IRY131062:ISB131065 JBU131062:JBX131065 JLQ131062:JLT131065 JVM131062:JVP131065 KFI131062:KFL131065 KPE131062:KPH131065 KZA131062:KZD131065 LIW131062:LIZ131065 LSS131062:LSV131065 MCO131062:MCR131065 MMK131062:MMN131065 MWG131062:MWJ131065 NGC131062:NGF131065 NPY131062:NQB131065 NZU131062:NZX131065 OJQ131062:OJT131065 OTM131062:OTP131065 PDI131062:PDL131065 PNE131062:PNH131065 PXA131062:PXD131065 QGW131062:QGZ131065 QQS131062:QQV131065 RAO131062:RAR131065 RKK131062:RKN131065 RUG131062:RUJ131065 SEC131062:SEF131065 SNY131062:SOB131065 SXU131062:SXX131065 THQ131062:THT131065 TRM131062:TRP131065 UBI131062:UBL131065 ULE131062:ULH131065 UVA131062:UVD131065 VEW131062:VEZ131065 VOS131062:VOV131065 VYO131062:VYR131065 WIK131062:WIN131065 WSG131062:WSJ131065 FU196598:FX196601 PQ196598:PT196601 ZM196598:ZP196601 AJI196598:AJL196601 ATE196598:ATH196601 BDA196598:BDD196601 BMW196598:BMZ196601 BWS196598:BWV196601 CGO196598:CGR196601 CQK196598:CQN196601 DAG196598:DAJ196601 DKC196598:DKF196601 DTY196598:DUB196601 EDU196598:EDX196601 ENQ196598:ENT196601 EXM196598:EXP196601 FHI196598:FHL196601 FRE196598:FRH196601 GBA196598:GBD196601 GKW196598:GKZ196601 GUS196598:GUV196601 HEO196598:HER196601 HOK196598:HON196601 HYG196598:HYJ196601 IIC196598:IIF196601 IRY196598:ISB196601 JBU196598:JBX196601 JLQ196598:JLT196601 JVM196598:JVP196601 KFI196598:KFL196601 KPE196598:KPH196601 KZA196598:KZD196601 LIW196598:LIZ196601 LSS196598:LSV196601 MCO196598:MCR196601 MMK196598:MMN196601 MWG196598:MWJ196601 NGC196598:NGF196601 NPY196598:NQB196601 NZU196598:NZX196601 OJQ196598:OJT196601 OTM196598:OTP196601 PDI196598:PDL196601 PNE196598:PNH196601 PXA196598:PXD196601 QGW196598:QGZ196601 QQS196598:QQV196601 RAO196598:RAR196601 RKK196598:RKN196601 RUG196598:RUJ196601 SEC196598:SEF196601 SNY196598:SOB196601 SXU196598:SXX196601 THQ196598:THT196601 TRM196598:TRP196601 UBI196598:UBL196601 ULE196598:ULH196601 UVA196598:UVD196601 VEW196598:VEZ196601 VOS196598:VOV196601 VYO196598:VYR196601 WIK196598:WIN196601 WSG196598:WSJ196601 FU262134:FX262137 PQ262134:PT262137 ZM262134:ZP262137 AJI262134:AJL262137 ATE262134:ATH262137 BDA262134:BDD262137 BMW262134:BMZ262137 BWS262134:BWV262137 CGO262134:CGR262137 CQK262134:CQN262137 DAG262134:DAJ262137 DKC262134:DKF262137 DTY262134:DUB262137 EDU262134:EDX262137 ENQ262134:ENT262137 EXM262134:EXP262137 FHI262134:FHL262137 FRE262134:FRH262137 GBA262134:GBD262137 GKW262134:GKZ262137 GUS262134:GUV262137 HEO262134:HER262137 HOK262134:HON262137 HYG262134:HYJ262137 IIC262134:IIF262137 IRY262134:ISB262137 JBU262134:JBX262137 JLQ262134:JLT262137 JVM262134:JVP262137 KFI262134:KFL262137 KPE262134:KPH262137 KZA262134:KZD262137 LIW262134:LIZ262137 LSS262134:LSV262137 MCO262134:MCR262137 MMK262134:MMN262137 MWG262134:MWJ262137 NGC262134:NGF262137 NPY262134:NQB262137 NZU262134:NZX262137 OJQ262134:OJT262137 OTM262134:OTP262137 PDI262134:PDL262137 PNE262134:PNH262137 PXA262134:PXD262137 QGW262134:QGZ262137 QQS262134:QQV262137 RAO262134:RAR262137 RKK262134:RKN262137 RUG262134:RUJ262137 SEC262134:SEF262137 SNY262134:SOB262137 SXU262134:SXX262137 THQ262134:THT262137 TRM262134:TRP262137 UBI262134:UBL262137 ULE262134:ULH262137 UVA262134:UVD262137 VEW262134:VEZ262137 VOS262134:VOV262137 VYO262134:VYR262137 WIK262134:WIN262137 WSG262134:WSJ262137 FU327670:FX327673 PQ327670:PT327673 ZM327670:ZP327673 AJI327670:AJL327673 ATE327670:ATH327673 BDA327670:BDD327673 BMW327670:BMZ327673 BWS327670:BWV327673 CGO327670:CGR327673 CQK327670:CQN327673 DAG327670:DAJ327673 DKC327670:DKF327673 DTY327670:DUB327673 EDU327670:EDX327673 ENQ327670:ENT327673 EXM327670:EXP327673 FHI327670:FHL327673 FRE327670:FRH327673 GBA327670:GBD327673 GKW327670:GKZ327673 GUS327670:GUV327673 HEO327670:HER327673 HOK327670:HON327673 HYG327670:HYJ327673 IIC327670:IIF327673 IRY327670:ISB327673 JBU327670:JBX327673 JLQ327670:JLT327673 JVM327670:JVP327673 KFI327670:KFL327673 KPE327670:KPH327673 KZA327670:KZD327673 LIW327670:LIZ327673 LSS327670:LSV327673 MCO327670:MCR327673 MMK327670:MMN327673 MWG327670:MWJ327673 NGC327670:NGF327673 NPY327670:NQB327673 NZU327670:NZX327673 OJQ327670:OJT327673 OTM327670:OTP327673 PDI327670:PDL327673 PNE327670:PNH327673 PXA327670:PXD327673 QGW327670:QGZ327673 QQS327670:QQV327673 RAO327670:RAR327673 RKK327670:RKN327673 RUG327670:RUJ327673 SEC327670:SEF327673 SNY327670:SOB327673 SXU327670:SXX327673 THQ327670:THT327673 TRM327670:TRP327673 UBI327670:UBL327673 ULE327670:ULH327673 UVA327670:UVD327673 VEW327670:VEZ327673 VOS327670:VOV327673 VYO327670:VYR327673 WIK327670:WIN327673 WSG327670:WSJ327673 FU393206:FX393209 PQ393206:PT393209 ZM393206:ZP393209 AJI393206:AJL393209 ATE393206:ATH393209 BDA393206:BDD393209 BMW393206:BMZ393209 BWS393206:BWV393209 CGO393206:CGR393209 CQK393206:CQN393209 DAG393206:DAJ393209 DKC393206:DKF393209 DTY393206:DUB393209 EDU393206:EDX393209 ENQ393206:ENT393209 EXM393206:EXP393209 FHI393206:FHL393209 FRE393206:FRH393209 GBA393206:GBD393209 GKW393206:GKZ393209 GUS393206:GUV393209 HEO393206:HER393209 HOK393206:HON393209 HYG393206:HYJ393209 IIC393206:IIF393209 IRY393206:ISB393209 JBU393206:JBX393209 JLQ393206:JLT393209 JVM393206:JVP393209 KFI393206:KFL393209 KPE393206:KPH393209 KZA393206:KZD393209 LIW393206:LIZ393209 LSS393206:LSV393209 MCO393206:MCR393209 MMK393206:MMN393209 MWG393206:MWJ393209 NGC393206:NGF393209 NPY393206:NQB393209 NZU393206:NZX393209 OJQ393206:OJT393209 OTM393206:OTP393209 PDI393206:PDL393209 PNE393206:PNH393209 PXA393206:PXD393209 QGW393206:QGZ393209 QQS393206:QQV393209 RAO393206:RAR393209 RKK393206:RKN393209 RUG393206:RUJ393209 SEC393206:SEF393209 SNY393206:SOB393209 SXU393206:SXX393209 THQ393206:THT393209 TRM393206:TRP393209 UBI393206:UBL393209 ULE393206:ULH393209 UVA393206:UVD393209 VEW393206:VEZ393209 VOS393206:VOV393209 VYO393206:VYR393209 WIK393206:WIN393209 WSG393206:WSJ393209 FU458742:FX458745 PQ458742:PT458745 ZM458742:ZP458745 AJI458742:AJL458745 ATE458742:ATH458745 BDA458742:BDD458745 BMW458742:BMZ458745 BWS458742:BWV458745 CGO458742:CGR458745 CQK458742:CQN458745 DAG458742:DAJ458745 DKC458742:DKF458745 DTY458742:DUB458745 EDU458742:EDX458745 ENQ458742:ENT458745 EXM458742:EXP458745 FHI458742:FHL458745 FRE458742:FRH458745 GBA458742:GBD458745 GKW458742:GKZ458745 GUS458742:GUV458745 HEO458742:HER458745 HOK458742:HON458745 HYG458742:HYJ458745 IIC458742:IIF458745 IRY458742:ISB458745 JBU458742:JBX458745 JLQ458742:JLT458745 JVM458742:JVP458745 KFI458742:KFL458745 KPE458742:KPH458745 KZA458742:KZD458745 LIW458742:LIZ458745 LSS458742:LSV458745 MCO458742:MCR458745 MMK458742:MMN458745 MWG458742:MWJ458745 NGC458742:NGF458745 NPY458742:NQB458745 NZU458742:NZX458745 OJQ458742:OJT458745 OTM458742:OTP458745 PDI458742:PDL458745 PNE458742:PNH458745 PXA458742:PXD458745 QGW458742:QGZ458745 QQS458742:QQV458745 RAO458742:RAR458745 RKK458742:RKN458745 RUG458742:RUJ458745 SEC458742:SEF458745 SNY458742:SOB458745 SXU458742:SXX458745 THQ458742:THT458745 TRM458742:TRP458745 UBI458742:UBL458745 ULE458742:ULH458745 UVA458742:UVD458745 VEW458742:VEZ458745 VOS458742:VOV458745 VYO458742:VYR458745 WIK458742:WIN458745 WSG458742:WSJ458745 FU524278:FX524281 PQ524278:PT524281 ZM524278:ZP524281 AJI524278:AJL524281 ATE524278:ATH524281 BDA524278:BDD524281 BMW524278:BMZ524281 BWS524278:BWV524281 CGO524278:CGR524281 CQK524278:CQN524281 DAG524278:DAJ524281 DKC524278:DKF524281 DTY524278:DUB524281 EDU524278:EDX524281 ENQ524278:ENT524281 EXM524278:EXP524281 FHI524278:FHL524281 FRE524278:FRH524281 GBA524278:GBD524281 GKW524278:GKZ524281 GUS524278:GUV524281 HEO524278:HER524281 HOK524278:HON524281 HYG524278:HYJ524281 IIC524278:IIF524281 IRY524278:ISB524281 JBU524278:JBX524281 JLQ524278:JLT524281 JVM524278:JVP524281 KFI524278:KFL524281 KPE524278:KPH524281 KZA524278:KZD524281 LIW524278:LIZ524281 LSS524278:LSV524281 MCO524278:MCR524281 MMK524278:MMN524281 MWG524278:MWJ524281 NGC524278:NGF524281 NPY524278:NQB524281 NZU524278:NZX524281 OJQ524278:OJT524281 OTM524278:OTP524281 PDI524278:PDL524281 PNE524278:PNH524281 PXA524278:PXD524281 QGW524278:QGZ524281 QQS524278:QQV524281 RAO524278:RAR524281 RKK524278:RKN524281 RUG524278:RUJ524281 SEC524278:SEF524281 SNY524278:SOB524281 SXU524278:SXX524281 THQ524278:THT524281 TRM524278:TRP524281 UBI524278:UBL524281 ULE524278:ULH524281 UVA524278:UVD524281 VEW524278:VEZ524281 VOS524278:VOV524281 VYO524278:VYR524281 WIK524278:WIN524281 WSG524278:WSJ524281 FU589814:FX589817 PQ589814:PT589817 ZM589814:ZP589817 AJI589814:AJL589817 ATE589814:ATH589817 BDA589814:BDD589817 BMW589814:BMZ589817 BWS589814:BWV589817 CGO589814:CGR589817 CQK589814:CQN589817 DAG589814:DAJ589817 DKC589814:DKF589817 DTY589814:DUB589817 EDU589814:EDX589817 ENQ589814:ENT589817 EXM589814:EXP589817 FHI589814:FHL589817 FRE589814:FRH589817 GBA589814:GBD589817 GKW589814:GKZ589817 GUS589814:GUV589817 HEO589814:HER589817 HOK589814:HON589817 HYG589814:HYJ589817 IIC589814:IIF589817 IRY589814:ISB589817 JBU589814:JBX589817 JLQ589814:JLT589817 JVM589814:JVP589817 KFI589814:KFL589817 KPE589814:KPH589817 KZA589814:KZD589817 LIW589814:LIZ589817 LSS589814:LSV589817 MCO589814:MCR589817 MMK589814:MMN589817 MWG589814:MWJ589817 NGC589814:NGF589817 NPY589814:NQB589817 NZU589814:NZX589817 OJQ589814:OJT589817 OTM589814:OTP589817 PDI589814:PDL589817 PNE589814:PNH589817 PXA589814:PXD589817 QGW589814:QGZ589817 QQS589814:QQV589817 RAO589814:RAR589817 RKK589814:RKN589817 RUG589814:RUJ589817 SEC589814:SEF589817 SNY589814:SOB589817 SXU589814:SXX589817 THQ589814:THT589817 TRM589814:TRP589817 UBI589814:UBL589817 ULE589814:ULH589817 UVA589814:UVD589817 VEW589814:VEZ589817 VOS589814:VOV589817 VYO589814:VYR589817 WIK589814:WIN589817 WSG589814:WSJ589817 FU655350:FX655353 PQ655350:PT655353 ZM655350:ZP655353 AJI655350:AJL655353 ATE655350:ATH655353 BDA655350:BDD655353 BMW655350:BMZ655353 BWS655350:BWV655353 CGO655350:CGR655353 CQK655350:CQN655353 DAG655350:DAJ655353 DKC655350:DKF655353 DTY655350:DUB655353 EDU655350:EDX655353 ENQ655350:ENT655353 EXM655350:EXP655353 FHI655350:FHL655353 FRE655350:FRH655353 GBA655350:GBD655353 GKW655350:GKZ655353 GUS655350:GUV655353 HEO655350:HER655353 HOK655350:HON655353 HYG655350:HYJ655353 IIC655350:IIF655353 IRY655350:ISB655353 JBU655350:JBX655353 JLQ655350:JLT655353 JVM655350:JVP655353 KFI655350:KFL655353 KPE655350:KPH655353 KZA655350:KZD655353 LIW655350:LIZ655353 LSS655350:LSV655353 MCO655350:MCR655353 MMK655350:MMN655353 MWG655350:MWJ655353 NGC655350:NGF655353 NPY655350:NQB655353 NZU655350:NZX655353 OJQ655350:OJT655353 OTM655350:OTP655353 PDI655350:PDL655353 PNE655350:PNH655353 PXA655350:PXD655353 QGW655350:QGZ655353 QQS655350:QQV655353 RAO655350:RAR655353 RKK655350:RKN655353 RUG655350:RUJ655353 SEC655350:SEF655353 SNY655350:SOB655353 SXU655350:SXX655353 THQ655350:THT655353 TRM655350:TRP655353 UBI655350:UBL655353 ULE655350:ULH655353 UVA655350:UVD655353 VEW655350:VEZ655353 VOS655350:VOV655353 VYO655350:VYR655353 WIK655350:WIN655353 WSG655350:WSJ655353 FU720886:FX720889 PQ720886:PT720889 ZM720886:ZP720889 AJI720886:AJL720889 ATE720886:ATH720889 BDA720886:BDD720889 BMW720886:BMZ720889 BWS720886:BWV720889 CGO720886:CGR720889 CQK720886:CQN720889 DAG720886:DAJ720889 DKC720886:DKF720889 DTY720886:DUB720889 EDU720886:EDX720889 ENQ720886:ENT720889 EXM720886:EXP720889 FHI720886:FHL720889 FRE720886:FRH720889 GBA720886:GBD720889 GKW720886:GKZ720889 GUS720886:GUV720889 HEO720886:HER720889 HOK720886:HON720889 HYG720886:HYJ720889 IIC720886:IIF720889 IRY720886:ISB720889 JBU720886:JBX720889 JLQ720886:JLT720889 JVM720886:JVP720889 KFI720886:KFL720889 KPE720886:KPH720889 KZA720886:KZD720889 LIW720886:LIZ720889 LSS720886:LSV720889 MCO720886:MCR720889 MMK720886:MMN720889 MWG720886:MWJ720889 NGC720886:NGF720889 NPY720886:NQB720889 NZU720886:NZX720889 OJQ720886:OJT720889 OTM720886:OTP720889 PDI720886:PDL720889 PNE720886:PNH720889 PXA720886:PXD720889 QGW720886:QGZ720889 QQS720886:QQV720889 RAO720886:RAR720889 RKK720886:RKN720889 RUG720886:RUJ720889 SEC720886:SEF720889 SNY720886:SOB720889 SXU720886:SXX720889 THQ720886:THT720889 TRM720886:TRP720889 UBI720886:UBL720889 ULE720886:ULH720889 UVA720886:UVD720889 VEW720886:VEZ720889 VOS720886:VOV720889 VYO720886:VYR720889 WIK720886:WIN720889 WSG720886:WSJ720889 FU786422:FX786425 PQ786422:PT786425 ZM786422:ZP786425 AJI786422:AJL786425 ATE786422:ATH786425 BDA786422:BDD786425 BMW786422:BMZ786425 BWS786422:BWV786425 CGO786422:CGR786425 CQK786422:CQN786425 DAG786422:DAJ786425 DKC786422:DKF786425 DTY786422:DUB786425 EDU786422:EDX786425 ENQ786422:ENT786425 EXM786422:EXP786425 FHI786422:FHL786425 FRE786422:FRH786425 GBA786422:GBD786425 GKW786422:GKZ786425 GUS786422:GUV786425 HEO786422:HER786425 HOK786422:HON786425 HYG786422:HYJ786425 IIC786422:IIF786425 IRY786422:ISB786425 JBU786422:JBX786425 JLQ786422:JLT786425 JVM786422:JVP786425 KFI786422:KFL786425 KPE786422:KPH786425 KZA786422:KZD786425 LIW786422:LIZ786425 LSS786422:LSV786425 MCO786422:MCR786425 MMK786422:MMN786425 MWG786422:MWJ786425 NGC786422:NGF786425 NPY786422:NQB786425 NZU786422:NZX786425 OJQ786422:OJT786425 OTM786422:OTP786425 PDI786422:PDL786425 PNE786422:PNH786425 PXA786422:PXD786425 QGW786422:QGZ786425 QQS786422:QQV786425 RAO786422:RAR786425 RKK786422:RKN786425 RUG786422:RUJ786425 SEC786422:SEF786425 SNY786422:SOB786425 SXU786422:SXX786425 THQ786422:THT786425 TRM786422:TRP786425 UBI786422:UBL786425 ULE786422:ULH786425 UVA786422:UVD786425 VEW786422:VEZ786425 VOS786422:VOV786425 VYO786422:VYR786425 WIK786422:WIN786425 WSG786422:WSJ786425 FU851958:FX851961 PQ851958:PT851961 ZM851958:ZP851961 AJI851958:AJL851961 ATE851958:ATH851961 BDA851958:BDD851961 BMW851958:BMZ851961 BWS851958:BWV851961 CGO851958:CGR851961 CQK851958:CQN851961 DAG851958:DAJ851961 DKC851958:DKF851961 DTY851958:DUB851961 EDU851958:EDX851961 ENQ851958:ENT851961 EXM851958:EXP851961 FHI851958:FHL851961 FRE851958:FRH851961 GBA851958:GBD851961 GKW851958:GKZ851961 GUS851958:GUV851961 HEO851958:HER851961 HOK851958:HON851961 HYG851958:HYJ851961 IIC851958:IIF851961 IRY851958:ISB851961 JBU851958:JBX851961 JLQ851958:JLT851961 JVM851958:JVP851961 KFI851958:KFL851961 KPE851958:KPH851961 KZA851958:KZD851961 LIW851958:LIZ851961 LSS851958:LSV851961 MCO851958:MCR851961 MMK851958:MMN851961 MWG851958:MWJ851961 NGC851958:NGF851961 NPY851958:NQB851961 NZU851958:NZX851961 OJQ851958:OJT851961 OTM851958:OTP851961 PDI851958:PDL851961 PNE851958:PNH851961 PXA851958:PXD851961 QGW851958:QGZ851961 QQS851958:QQV851961 RAO851958:RAR851961 RKK851958:RKN851961 RUG851958:RUJ851961 SEC851958:SEF851961 SNY851958:SOB851961 SXU851958:SXX851961 THQ851958:THT851961 TRM851958:TRP851961 UBI851958:UBL851961 ULE851958:ULH851961 UVA851958:UVD851961 VEW851958:VEZ851961 VOS851958:VOV851961 VYO851958:VYR851961 WIK851958:WIN851961 WSG851958:WSJ851961 FU917494:FX917497 PQ917494:PT917497 ZM917494:ZP917497 AJI917494:AJL917497 ATE917494:ATH917497 BDA917494:BDD917497 BMW917494:BMZ917497 BWS917494:BWV917497 CGO917494:CGR917497 CQK917494:CQN917497 DAG917494:DAJ917497 DKC917494:DKF917497 DTY917494:DUB917497 EDU917494:EDX917497 ENQ917494:ENT917497 EXM917494:EXP917497 FHI917494:FHL917497 FRE917494:FRH917497 GBA917494:GBD917497 GKW917494:GKZ917497 GUS917494:GUV917497 HEO917494:HER917497 HOK917494:HON917497 HYG917494:HYJ917497 IIC917494:IIF917497 IRY917494:ISB917497 JBU917494:JBX917497 JLQ917494:JLT917497 JVM917494:JVP917497 KFI917494:KFL917497 KPE917494:KPH917497 KZA917494:KZD917497 LIW917494:LIZ917497 LSS917494:LSV917497 MCO917494:MCR917497 MMK917494:MMN917497 MWG917494:MWJ917497 NGC917494:NGF917497 NPY917494:NQB917497 NZU917494:NZX917497 OJQ917494:OJT917497 OTM917494:OTP917497 PDI917494:PDL917497 PNE917494:PNH917497 PXA917494:PXD917497 QGW917494:QGZ917497 QQS917494:QQV917497 RAO917494:RAR917497 RKK917494:RKN917497 RUG917494:RUJ917497 SEC917494:SEF917497 SNY917494:SOB917497 SXU917494:SXX917497 THQ917494:THT917497 TRM917494:TRP917497 UBI917494:UBL917497 ULE917494:ULH917497 UVA917494:UVD917497 VEW917494:VEZ917497 VOS917494:VOV917497 VYO917494:VYR917497 WIK917494:WIN917497 WSG917494:WSJ917497 FU983030:FX983033 PQ983030:PT983033 ZM983030:ZP983033 AJI983030:AJL983033 ATE983030:ATH983033 BDA983030:BDD983033 BMW983030:BMZ983033 BWS983030:BWV983033 CGO983030:CGR983033 CQK983030:CQN983033 DAG983030:DAJ983033 DKC983030:DKF983033 DTY983030:DUB983033 EDU983030:EDX983033 ENQ983030:ENT983033 EXM983030:EXP983033 FHI983030:FHL983033 FRE983030:FRH983033 GBA983030:GBD983033 GKW983030:GKZ983033 GUS983030:GUV983033 HEO983030:HER983033 HOK983030:HON983033 HYG983030:HYJ983033 IIC983030:IIF983033 IRY983030:ISB983033 JBU983030:JBX983033 JLQ983030:JLT983033 JVM983030:JVP983033 KFI983030:KFL983033 KPE983030:KPH983033 KZA983030:KZD983033 LIW983030:LIZ983033 LSS983030:LSV983033 MCO983030:MCR983033 MMK983030:MMN983033 MWG983030:MWJ983033 NGC983030:NGF983033 NPY983030:NQB983033 NZU983030:NZX983033 OJQ983030:OJT983033 OTM983030:OTP983033 PDI983030:PDL983033 PNE983030:PNH983033 PXA983030:PXD983033 QGW983030:QGZ983033 QQS983030:QQV983033 RAO983030:RAR983033 RKK983030:RKN983033 RUG983030:RUJ983033 SEC983030:SEF983033 SNY983030:SOB983033 SXU983030:SXX983033 THQ983030:THT983033 TRM983030:TRP983033 UBI983030:UBL983033 ULE983030:ULH983033 UVA983030:UVD983033 VEW983030:VEZ983033 VOS983030:VOV983033 VYO983030:VYR983033 WIK983030:WIN983033 WSG983030:WSJ983033 FP65520:FS65520 PL65520:PO65520 ZH65520:ZK65520 AJD65520:AJG65520 ASZ65520:ATC65520 BCV65520:BCY65520 BMR65520:BMU65520 BWN65520:BWQ65520 CGJ65520:CGM65520 CQF65520:CQI65520 DAB65520:DAE65520 DJX65520:DKA65520 DTT65520:DTW65520 EDP65520:EDS65520 ENL65520:ENO65520 EXH65520:EXK65520 FHD65520:FHG65520 FQZ65520:FRC65520 GAV65520:GAY65520 GKR65520:GKU65520 GUN65520:GUQ65520 HEJ65520:HEM65520 HOF65520:HOI65520 HYB65520:HYE65520 IHX65520:IIA65520 IRT65520:IRW65520 JBP65520:JBS65520 JLL65520:JLO65520 JVH65520:JVK65520 KFD65520:KFG65520 KOZ65520:KPC65520 KYV65520:KYY65520 LIR65520:LIU65520 LSN65520:LSQ65520 MCJ65520:MCM65520 MMF65520:MMI65520 MWB65520:MWE65520 NFX65520:NGA65520 NPT65520:NPW65520 NZP65520:NZS65520 OJL65520:OJO65520 OTH65520:OTK65520 PDD65520:PDG65520 PMZ65520:PNC65520 PWV65520:PWY65520 QGR65520:QGU65520 QQN65520:QQQ65520 RAJ65520:RAM65520 RKF65520:RKI65520 RUB65520:RUE65520 SDX65520:SEA65520 SNT65520:SNW65520 SXP65520:SXS65520 THL65520:THO65520 TRH65520:TRK65520 UBD65520:UBG65520 UKZ65520:ULC65520 UUV65520:UUY65520 VER65520:VEU65520 VON65520:VOQ65520 VYJ65520:VYM65520 WIF65520:WII65520 WSB65520:WSE65520 FP131056:FS131056 PL131056:PO131056 ZH131056:ZK131056 AJD131056:AJG131056 ASZ131056:ATC131056 BCV131056:BCY131056 BMR131056:BMU131056 BWN131056:BWQ131056 CGJ131056:CGM131056 CQF131056:CQI131056 DAB131056:DAE131056 DJX131056:DKA131056 DTT131056:DTW131056 EDP131056:EDS131056 ENL131056:ENO131056 EXH131056:EXK131056 FHD131056:FHG131056 FQZ131056:FRC131056 GAV131056:GAY131056 GKR131056:GKU131056 GUN131056:GUQ131056 HEJ131056:HEM131056 HOF131056:HOI131056 HYB131056:HYE131056 IHX131056:IIA131056 IRT131056:IRW131056 JBP131056:JBS131056 JLL131056:JLO131056 JVH131056:JVK131056 KFD131056:KFG131056 KOZ131056:KPC131056 KYV131056:KYY131056 LIR131056:LIU131056 LSN131056:LSQ131056 MCJ131056:MCM131056 MMF131056:MMI131056 MWB131056:MWE131056 NFX131056:NGA131056 NPT131056:NPW131056 NZP131056:NZS131056 OJL131056:OJO131056 OTH131056:OTK131056 PDD131056:PDG131056 PMZ131056:PNC131056 PWV131056:PWY131056 QGR131056:QGU131056 QQN131056:QQQ131056 RAJ131056:RAM131056 RKF131056:RKI131056 RUB131056:RUE131056 SDX131056:SEA131056 SNT131056:SNW131056 SXP131056:SXS131056 THL131056:THO131056 TRH131056:TRK131056 UBD131056:UBG131056 UKZ131056:ULC131056 UUV131056:UUY131056 VER131056:VEU131056 VON131056:VOQ131056 VYJ131056:VYM131056 WIF131056:WII131056 WSB131056:WSE131056 FP196592:FS196592 PL196592:PO196592 ZH196592:ZK196592 AJD196592:AJG196592 ASZ196592:ATC196592 BCV196592:BCY196592 BMR196592:BMU196592 BWN196592:BWQ196592 CGJ196592:CGM196592 CQF196592:CQI196592 DAB196592:DAE196592 DJX196592:DKA196592 DTT196592:DTW196592 EDP196592:EDS196592 ENL196592:ENO196592 EXH196592:EXK196592 FHD196592:FHG196592 FQZ196592:FRC196592 GAV196592:GAY196592 GKR196592:GKU196592 GUN196592:GUQ196592 HEJ196592:HEM196592 HOF196592:HOI196592 HYB196592:HYE196592 IHX196592:IIA196592 IRT196592:IRW196592 JBP196592:JBS196592 JLL196592:JLO196592 JVH196592:JVK196592 KFD196592:KFG196592 KOZ196592:KPC196592 KYV196592:KYY196592 LIR196592:LIU196592 LSN196592:LSQ196592 MCJ196592:MCM196592 MMF196592:MMI196592 MWB196592:MWE196592 NFX196592:NGA196592 NPT196592:NPW196592 NZP196592:NZS196592 OJL196592:OJO196592 OTH196592:OTK196592 PDD196592:PDG196592 PMZ196592:PNC196592 PWV196592:PWY196592 QGR196592:QGU196592 QQN196592:QQQ196592 RAJ196592:RAM196592 RKF196592:RKI196592 RUB196592:RUE196592 SDX196592:SEA196592 SNT196592:SNW196592 SXP196592:SXS196592 THL196592:THO196592 TRH196592:TRK196592 UBD196592:UBG196592 UKZ196592:ULC196592 UUV196592:UUY196592 VER196592:VEU196592 VON196592:VOQ196592 VYJ196592:VYM196592 WIF196592:WII196592 WSB196592:WSE196592 FP262128:FS262128 PL262128:PO262128 ZH262128:ZK262128 AJD262128:AJG262128 ASZ262128:ATC262128 BCV262128:BCY262128 BMR262128:BMU262128 BWN262128:BWQ262128 CGJ262128:CGM262128 CQF262128:CQI262128 DAB262128:DAE262128 DJX262128:DKA262128 DTT262128:DTW262128 EDP262128:EDS262128 ENL262128:ENO262128 EXH262128:EXK262128 FHD262128:FHG262128 FQZ262128:FRC262128 GAV262128:GAY262128 GKR262128:GKU262128 GUN262128:GUQ262128 HEJ262128:HEM262128 HOF262128:HOI262128 HYB262128:HYE262128 IHX262128:IIA262128 IRT262128:IRW262128 JBP262128:JBS262128 JLL262128:JLO262128 JVH262128:JVK262128 KFD262128:KFG262128 KOZ262128:KPC262128 KYV262128:KYY262128 LIR262128:LIU262128 LSN262128:LSQ262128 MCJ262128:MCM262128 MMF262128:MMI262128 MWB262128:MWE262128 NFX262128:NGA262128 NPT262128:NPW262128 NZP262128:NZS262128 OJL262128:OJO262128 OTH262128:OTK262128 PDD262128:PDG262128 PMZ262128:PNC262128 PWV262128:PWY262128 QGR262128:QGU262128 QQN262128:QQQ262128 RAJ262128:RAM262128 RKF262128:RKI262128 RUB262128:RUE262128 SDX262128:SEA262128 SNT262128:SNW262128 SXP262128:SXS262128 THL262128:THO262128 TRH262128:TRK262128 UBD262128:UBG262128 UKZ262128:ULC262128 UUV262128:UUY262128 VER262128:VEU262128 VON262128:VOQ262128 VYJ262128:VYM262128 WIF262128:WII262128 WSB262128:WSE262128 FP327664:FS327664 PL327664:PO327664 ZH327664:ZK327664 AJD327664:AJG327664 ASZ327664:ATC327664 BCV327664:BCY327664 BMR327664:BMU327664 BWN327664:BWQ327664 CGJ327664:CGM327664 CQF327664:CQI327664 DAB327664:DAE327664 DJX327664:DKA327664 DTT327664:DTW327664 EDP327664:EDS327664 ENL327664:ENO327664 EXH327664:EXK327664 FHD327664:FHG327664 FQZ327664:FRC327664 GAV327664:GAY327664 GKR327664:GKU327664 GUN327664:GUQ327664 HEJ327664:HEM327664 HOF327664:HOI327664 HYB327664:HYE327664 IHX327664:IIA327664 IRT327664:IRW327664 JBP327664:JBS327664 JLL327664:JLO327664 JVH327664:JVK327664 KFD327664:KFG327664 KOZ327664:KPC327664 KYV327664:KYY327664 LIR327664:LIU327664 LSN327664:LSQ327664 MCJ327664:MCM327664 MMF327664:MMI327664 MWB327664:MWE327664 NFX327664:NGA327664 NPT327664:NPW327664 NZP327664:NZS327664 OJL327664:OJO327664 OTH327664:OTK327664 PDD327664:PDG327664 PMZ327664:PNC327664 PWV327664:PWY327664 QGR327664:QGU327664 QQN327664:QQQ327664 RAJ327664:RAM327664 RKF327664:RKI327664 RUB327664:RUE327664 SDX327664:SEA327664 SNT327664:SNW327664 SXP327664:SXS327664 THL327664:THO327664 TRH327664:TRK327664 UBD327664:UBG327664 UKZ327664:ULC327664 UUV327664:UUY327664 VER327664:VEU327664 VON327664:VOQ327664 VYJ327664:VYM327664 WIF327664:WII327664 WSB327664:WSE327664 FP393200:FS393200 PL393200:PO393200 ZH393200:ZK393200 AJD393200:AJG393200 ASZ393200:ATC393200 BCV393200:BCY393200 BMR393200:BMU393200 BWN393200:BWQ393200 CGJ393200:CGM393200 CQF393200:CQI393200 DAB393200:DAE393200 DJX393200:DKA393200 DTT393200:DTW393200 EDP393200:EDS393200 ENL393200:ENO393200 EXH393200:EXK393200 FHD393200:FHG393200 FQZ393200:FRC393200 GAV393200:GAY393200 GKR393200:GKU393200 GUN393200:GUQ393200 HEJ393200:HEM393200 HOF393200:HOI393200 HYB393200:HYE393200 IHX393200:IIA393200 IRT393200:IRW393200 JBP393200:JBS393200 JLL393200:JLO393200 JVH393200:JVK393200 KFD393200:KFG393200 KOZ393200:KPC393200 KYV393200:KYY393200 LIR393200:LIU393200 LSN393200:LSQ393200 MCJ393200:MCM393200 MMF393200:MMI393200 MWB393200:MWE393200 NFX393200:NGA393200 NPT393200:NPW393200 NZP393200:NZS393200 OJL393200:OJO393200 OTH393200:OTK393200 PDD393200:PDG393200 PMZ393200:PNC393200 PWV393200:PWY393200 QGR393200:QGU393200 QQN393200:QQQ393200 RAJ393200:RAM393200 RKF393200:RKI393200 RUB393200:RUE393200 SDX393200:SEA393200 SNT393200:SNW393200 SXP393200:SXS393200 THL393200:THO393200 TRH393200:TRK393200 UBD393200:UBG393200 UKZ393200:ULC393200 UUV393200:UUY393200 VER393200:VEU393200 VON393200:VOQ393200 VYJ393200:VYM393200 WIF393200:WII393200 WSB393200:WSE393200 FP458736:FS458736 PL458736:PO458736 ZH458736:ZK458736 AJD458736:AJG458736 ASZ458736:ATC458736 BCV458736:BCY458736 BMR458736:BMU458736 BWN458736:BWQ458736 CGJ458736:CGM458736 CQF458736:CQI458736 DAB458736:DAE458736 DJX458736:DKA458736 DTT458736:DTW458736 EDP458736:EDS458736 ENL458736:ENO458736 EXH458736:EXK458736 FHD458736:FHG458736 FQZ458736:FRC458736 GAV458736:GAY458736 GKR458736:GKU458736 GUN458736:GUQ458736 HEJ458736:HEM458736 HOF458736:HOI458736 HYB458736:HYE458736 IHX458736:IIA458736 IRT458736:IRW458736 JBP458736:JBS458736 JLL458736:JLO458736 JVH458736:JVK458736 KFD458736:KFG458736 KOZ458736:KPC458736 KYV458736:KYY458736 LIR458736:LIU458736 LSN458736:LSQ458736 MCJ458736:MCM458736 MMF458736:MMI458736 MWB458736:MWE458736 NFX458736:NGA458736 NPT458736:NPW458736 NZP458736:NZS458736 OJL458736:OJO458736 OTH458736:OTK458736 PDD458736:PDG458736 PMZ458736:PNC458736 PWV458736:PWY458736 QGR458736:QGU458736 QQN458736:QQQ458736 RAJ458736:RAM458736 RKF458736:RKI458736 RUB458736:RUE458736 SDX458736:SEA458736 SNT458736:SNW458736 SXP458736:SXS458736 THL458736:THO458736 TRH458736:TRK458736 UBD458736:UBG458736 UKZ458736:ULC458736 UUV458736:UUY458736 VER458736:VEU458736 VON458736:VOQ458736 VYJ458736:VYM458736 WIF458736:WII458736 WSB458736:WSE458736 FP524272:FS524272 PL524272:PO524272 ZH524272:ZK524272 AJD524272:AJG524272 ASZ524272:ATC524272 BCV524272:BCY524272 BMR524272:BMU524272 BWN524272:BWQ524272 CGJ524272:CGM524272 CQF524272:CQI524272 DAB524272:DAE524272 DJX524272:DKA524272 DTT524272:DTW524272 EDP524272:EDS524272 ENL524272:ENO524272 EXH524272:EXK524272 FHD524272:FHG524272 FQZ524272:FRC524272 GAV524272:GAY524272 GKR524272:GKU524272 GUN524272:GUQ524272 HEJ524272:HEM524272 HOF524272:HOI524272 HYB524272:HYE524272 IHX524272:IIA524272 IRT524272:IRW524272 JBP524272:JBS524272 JLL524272:JLO524272 JVH524272:JVK524272 KFD524272:KFG524272 KOZ524272:KPC524272 KYV524272:KYY524272 LIR524272:LIU524272 LSN524272:LSQ524272 MCJ524272:MCM524272 MMF524272:MMI524272 MWB524272:MWE524272 NFX524272:NGA524272 NPT524272:NPW524272 NZP524272:NZS524272 OJL524272:OJO524272 OTH524272:OTK524272 PDD524272:PDG524272 PMZ524272:PNC524272 PWV524272:PWY524272 QGR524272:QGU524272 QQN524272:QQQ524272 RAJ524272:RAM524272 RKF524272:RKI524272 RUB524272:RUE524272 SDX524272:SEA524272 SNT524272:SNW524272 SXP524272:SXS524272 THL524272:THO524272 TRH524272:TRK524272 UBD524272:UBG524272 UKZ524272:ULC524272 UUV524272:UUY524272 VER524272:VEU524272 VON524272:VOQ524272 VYJ524272:VYM524272 WIF524272:WII524272 WSB524272:WSE524272 FP589808:FS589808 PL589808:PO589808 ZH589808:ZK589808 AJD589808:AJG589808 ASZ589808:ATC589808 BCV589808:BCY589808 BMR589808:BMU589808 BWN589808:BWQ589808 CGJ589808:CGM589808 CQF589808:CQI589808 DAB589808:DAE589808 DJX589808:DKA589808 DTT589808:DTW589808 EDP589808:EDS589808 ENL589808:ENO589808 EXH589808:EXK589808 FHD589808:FHG589808 FQZ589808:FRC589808 GAV589808:GAY589808 GKR589808:GKU589808 GUN589808:GUQ589808 HEJ589808:HEM589808 HOF589808:HOI589808 HYB589808:HYE589808 IHX589808:IIA589808 IRT589808:IRW589808 JBP589808:JBS589808 JLL589808:JLO589808 JVH589808:JVK589808 KFD589808:KFG589808 KOZ589808:KPC589808 KYV589808:KYY589808 LIR589808:LIU589808 LSN589808:LSQ589808 MCJ589808:MCM589808 MMF589808:MMI589808 MWB589808:MWE589808 NFX589808:NGA589808 NPT589808:NPW589808 NZP589808:NZS589808 OJL589808:OJO589808 OTH589808:OTK589808 PDD589808:PDG589808 PMZ589808:PNC589808 PWV589808:PWY589808 QGR589808:QGU589808 QQN589808:QQQ589808 RAJ589808:RAM589808 RKF589808:RKI589808 RUB589808:RUE589808 SDX589808:SEA589808 SNT589808:SNW589808 SXP589808:SXS589808 THL589808:THO589808 TRH589808:TRK589808 UBD589808:UBG589808 UKZ589808:ULC589808 UUV589808:UUY589808 VER589808:VEU589808 VON589808:VOQ589808 VYJ589808:VYM589808 WIF589808:WII589808 WSB589808:WSE589808 FP655344:FS655344 PL655344:PO655344 ZH655344:ZK655344 AJD655344:AJG655344 ASZ655344:ATC655344 BCV655344:BCY655344 BMR655344:BMU655344 BWN655344:BWQ655344 CGJ655344:CGM655344 CQF655344:CQI655344 DAB655344:DAE655344 DJX655344:DKA655344 DTT655344:DTW655344 EDP655344:EDS655344 ENL655344:ENO655344 EXH655344:EXK655344 FHD655344:FHG655344 FQZ655344:FRC655344 GAV655344:GAY655344 GKR655344:GKU655344 GUN655344:GUQ655344 HEJ655344:HEM655344 HOF655344:HOI655344 HYB655344:HYE655344 IHX655344:IIA655344 IRT655344:IRW655344 JBP655344:JBS655344 JLL655344:JLO655344 JVH655344:JVK655344 KFD655344:KFG655344 KOZ655344:KPC655344 KYV655344:KYY655344 LIR655344:LIU655344 LSN655344:LSQ655344 MCJ655344:MCM655344 MMF655344:MMI655344 MWB655344:MWE655344 NFX655344:NGA655344 NPT655344:NPW655344 NZP655344:NZS655344 OJL655344:OJO655344 OTH655344:OTK655344 PDD655344:PDG655344 PMZ655344:PNC655344 PWV655344:PWY655344 QGR655344:QGU655344 QQN655344:QQQ655344 RAJ655344:RAM655344 RKF655344:RKI655344 RUB655344:RUE655344 SDX655344:SEA655344 SNT655344:SNW655344 SXP655344:SXS655344 THL655344:THO655344 TRH655344:TRK655344 UBD655344:UBG655344 UKZ655344:ULC655344 UUV655344:UUY655344 VER655344:VEU655344 VON655344:VOQ655344 VYJ655344:VYM655344 WIF655344:WII655344 WSB655344:WSE655344 FP720880:FS720880 PL720880:PO720880 ZH720880:ZK720880 AJD720880:AJG720880 ASZ720880:ATC720880 BCV720880:BCY720880 BMR720880:BMU720880 BWN720880:BWQ720880 CGJ720880:CGM720880 CQF720880:CQI720880 DAB720880:DAE720880 DJX720880:DKA720880 DTT720880:DTW720880 EDP720880:EDS720880 ENL720880:ENO720880 EXH720880:EXK720880 FHD720880:FHG720880 FQZ720880:FRC720880 GAV720880:GAY720880 GKR720880:GKU720880 GUN720880:GUQ720880 HEJ720880:HEM720880 HOF720880:HOI720880 HYB720880:HYE720880 IHX720880:IIA720880 IRT720880:IRW720880 JBP720880:JBS720880 JLL720880:JLO720880 JVH720880:JVK720880 KFD720880:KFG720880 KOZ720880:KPC720880 KYV720880:KYY720880 LIR720880:LIU720880 LSN720880:LSQ720880 MCJ720880:MCM720880 MMF720880:MMI720880 MWB720880:MWE720880 NFX720880:NGA720880 NPT720880:NPW720880 NZP720880:NZS720880 OJL720880:OJO720880 OTH720880:OTK720880 PDD720880:PDG720880 PMZ720880:PNC720880 PWV720880:PWY720880 QGR720880:QGU720880 QQN720880:QQQ720880 RAJ720880:RAM720880 RKF720880:RKI720880 RUB720880:RUE720880 SDX720880:SEA720880 SNT720880:SNW720880 SXP720880:SXS720880 THL720880:THO720880 TRH720880:TRK720880 UBD720880:UBG720880 UKZ720880:ULC720880 UUV720880:UUY720880 VER720880:VEU720880 VON720880:VOQ720880 VYJ720880:VYM720880 WIF720880:WII720880 WSB720880:WSE720880 FP786416:FS786416 PL786416:PO786416 ZH786416:ZK786416 AJD786416:AJG786416 ASZ786416:ATC786416 BCV786416:BCY786416 BMR786416:BMU786416 BWN786416:BWQ786416 CGJ786416:CGM786416 CQF786416:CQI786416 DAB786416:DAE786416 DJX786416:DKA786416 DTT786416:DTW786416 EDP786416:EDS786416 ENL786416:ENO786416 EXH786416:EXK786416 FHD786416:FHG786416 FQZ786416:FRC786416 GAV786416:GAY786416 GKR786416:GKU786416 GUN786416:GUQ786416 HEJ786416:HEM786416 HOF786416:HOI786416 HYB786416:HYE786416 IHX786416:IIA786416 IRT786416:IRW786416 JBP786416:JBS786416 JLL786416:JLO786416 JVH786416:JVK786416 KFD786416:KFG786416 KOZ786416:KPC786416 KYV786416:KYY786416 LIR786416:LIU786416 LSN786416:LSQ786416 MCJ786416:MCM786416 MMF786416:MMI786416 MWB786416:MWE786416 NFX786416:NGA786416 NPT786416:NPW786416 NZP786416:NZS786416 OJL786416:OJO786416 OTH786416:OTK786416 PDD786416:PDG786416 PMZ786416:PNC786416 PWV786416:PWY786416 QGR786416:QGU786416 QQN786416:QQQ786416 RAJ786416:RAM786416 RKF786416:RKI786416 RUB786416:RUE786416 SDX786416:SEA786416 SNT786416:SNW786416 SXP786416:SXS786416 THL786416:THO786416 TRH786416:TRK786416 UBD786416:UBG786416 UKZ786416:ULC786416 UUV786416:UUY786416 VER786416:VEU786416 VON786416:VOQ786416 VYJ786416:VYM786416 WIF786416:WII786416 WSB786416:WSE786416 FP851952:FS851952 PL851952:PO851952 ZH851952:ZK851952 AJD851952:AJG851952 ASZ851952:ATC851952 BCV851952:BCY851952 BMR851952:BMU851952 BWN851952:BWQ851952 CGJ851952:CGM851952 CQF851952:CQI851952 DAB851952:DAE851952 DJX851952:DKA851952 DTT851952:DTW851952 EDP851952:EDS851952 ENL851952:ENO851952 EXH851952:EXK851952 FHD851952:FHG851952 FQZ851952:FRC851952 GAV851952:GAY851952 GKR851952:GKU851952 GUN851952:GUQ851952 HEJ851952:HEM851952 HOF851952:HOI851952 HYB851952:HYE851952 IHX851952:IIA851952 IRT851952:IRW851952 JBP851952:JBS851952 JLL851952:JLO851952 JVH851952:JVK851952 KFD851952:KFG851952 KOZ851952:KPC851952 KYV851952:KYY851952 LIR851952:LIU851952 LSN851952:LSQ851952 MCJ851952:MCM851952 MMF851952:MMI851952 MWB851952:MWE851952 NFX851952:NGA851952 NPT851952:NPW851952 NZP851952:NZS851952 OJL851952:OJO851952 OTH851952:OTK851952 PDD851952:PDG851952 PMZ851952:PNC851952 PWV851952:PWY851952 QGR851952:QGU851952 QQN851952:QQQ851952 RAJ851952:RAM851952 RKF851952:RKI851952 RUB851952:RUE851952 SDX851952:SEA851952 SNT851952:SNW851952 SXP851952:SXS851952 THL851952:THO851952 TRH851952:TRK851952 UBD851952:UBG851952 UKZ851952:ULC851952 UUV851952:UUY851952 VER851952:VEU851952 VON851952:VOQ851952 VYJ851952:VYM851952 WIF851952:WII851952 WSB851952:WSE851952 FP917488:FS917488 PL917488:PO917488 ZH917488:ZK917488 AJD917488:AJG917488 ASZ917488:ATC917488 BCV917488:BCY917488 BMR917488:BMU917488 BWN917488:BWQ917488 CGJ917488:CGM917488 CQF917488:CQI917488 DAB917488:DAE917488 DJX917488:DKA917488 DTT917488:DTW917488 EDP917488:EDS917488 ENL917488:ENO917488 EXH917488:EXK917488 FHD917488:FHG917488 FQZ917488:FRC917488 GAV917488:GAY917488 GKR917488:GKU917488 GUN917488:GUQ917488 HEJ917488:HEM917488 HOF917488:HOI917488 HYB917488:HYE917488 IHX917488:IIA917488 IRT917488:IRW917488 JBP917488:JBS917488 JLL917488:JLO917488 JVH917488:JVK917488 KFD917488:KFG917488 KOZ917488:KPC917488 KYV917488:KYY917488 LIR917488:LIU917488 LSN917488:LSQ917488 MCJ917488:MCM917488 MMF917488:MMI917488 MWB917488:MWE917488 NFX917488:NGA917488 NPT917488:NPW917488 NZP917488:NZS917488 OJL917488:OJO917488 OTH917488:OTK917488 PDD917488:PDG917488 PMZ917488:PNC917488 PWV917488:PWY917488 QGR917488:QGU917488 QQN917488:QQQ917488 RAJ917488:RAM917488 RKF917488:RKI917488 RUB917488:RUE917488 SDX917488:SEA917488 SNT917488:SNW917488 SXP917488:SXS917488 THL917488:THO917488 TRH917488:TRK917488 UBD917488:UBG917488 UKZ917488:ULC917488 UUV917488:UUY917488 VER917488:VEU917488 VON917488:VOQ917488 VYJ917488:VYM917488 WIF917488:WII917488 WSB917488:WSE917488 FP983024:FS983024 PL983024:PO983024 ZH983024:ZK983024 AJD983024:AJG983024 ASZ983024:ATC983024 BCV983024:BCY983024 BMR983024:BMU983024 BWN983024:BWQ983024 CGJ983024:CGM983024 CQF983024:CQI983024 DAB983024:DAE983024 DJX983024:DKA983024 DTT983024:DTW983024 EDP983024:EDS983024 ENL983024:ENO983024 EXH983024:EXK983024 FHD983024:FHG983024 FQZ983024:FRC983024 GAV983024:GAY983024 GKR983024:GKU983024 GUN983024:GUQ983024 HEJ983024:HEM983024 HOF983024:HOI983024 HYB983024:HYE983024 IHX983024:IIA983024 IRT983024:IRW983024 JBP983024:JBS983024 JLL983024:JLO983024 JVH983024:JVK983024 KFD983024:KFG983024 KOZ983024:KPC983024 KYV983024:KYY983024 LIR983024:LIU983024 LSN983024:LSQ983024 MCJ983024:MCM983024 MMF983024:MMI983024 MWB983024:MWE983024 NFX983024:NGA983024 NPT983024:NPW983024 NZP983024:NZS983024 OJL983024:OJO983024 OTH983024:OTK983024 PDD983024:PDG983024 PMZ983024:PNC983024 PWV983024:PWY983024 QGR983024:QGU983024 QQN983024:QQQ983024 RAJ983024:RAM983024 RKF983024:RKI983024 RUB983024:RUE983024 SDX983024:SEA983024 SNT983024:SNW983024 SXP983024:SXS983024 THL983024:THO983024 TRH983024:TRK983024 UBD983024:UBG983024 UKZ983024:ULC983024 UUV983024:UUY983024 VER983024:VEU983024 VON983024:VOQ983024 VYJ983024:VYM983024 WIF983024:WII983024 WSB983024:WSE983024 FK983023:FN983023 PG983023:PJ983023 ZC983023:ZF983023 AIY983023:AJB983023 ASU983023:ASX983023 BCQ983023:BCT983023 BMM983023:BMP983023 BWI983023:BWL983023 CGE983023:CGH983023 CQA983023:CQD983023 CZW983023:CZZ983023 DJS983023:DJV983023 DTO983023:DTR983023 EDK983023:EDN983023 ENG983023:ENJ983023 EXC983023:EXF983023 FGY983023:FHB983023 FQU983023:FQX983023 GAQ983023:GAT983023 GKM983023:GKP983023 GUI983023:GUL983023 HEE983023:HEH983023 HOA983023:HOD983023 HXW983023:HXZ983023 IHS983023:IHV983023 IRO983023:IRR983023 JBK983023:JBN983023 JLG983023:JLJ983023 JVC983023:JVF983023 KEY983023:KFB983023 KOU983023:KOX983023 KYQ983023:KYT983023 LIM983023:LIP983023 LSI983023:LSL983023 MCE983023:MCH983023 MMA983023:MMD983023 MVW983023:MVZ983023 NFS983023:NFV983023 NPO983023:NPR983023 NZK983023:NZN983023 OJG983023:OJJ983023 OTC983023:OTF983023 PCY983023:PDB983023 PMU983023:PMX983023 PWQ983023:PWT983023 QGM983023:QGP983023 QQI983023:QQL983023 RAE983023:RAH983023 RKA983023:RKD983023 RTW983023:RTZ983023 SDS983023:SDV983023 SNO983023:SNR983023 SXK983023:SXN983023 THG983023:THJ983023 TRC983023:TRF983023 UAY983023:UBB983023 UKU983023:UKX983023 UUQ983023:UUT983023 VEM983023:VEP983023 VOI983023:VOL983023 VYE983023:VYH983023 WIA983023:WID983023 WRW983023:WRZ983023 FK65519:FN65519 PG65519:PJ65519 ZC65519:ZF65519 AIY65519:AJB65519 ASU65519:ASX65519 BCQ65519:BCT65519 BMM65519:BMP65519 BWI65519:BWL65519 CGE65519:CGH65519 CQA65519:CQD65519 CZW65519:CZZ65519 DJS65519:DJV65519 DTO65519:DTR65519 EDK65519:EDN65519 ENG65519:ENJ65519 EXC65519:EXF65519 FGY65519:FHB65519 FQU65519:FQX65519 GAQ65519:GAT65519 GKM65519:GKP65519 GUI65519:GUL65519 HEE65519:HEH65519 HOA65519:HOD65519 HXW65519:HXZ65519 IHS65519:IHV65519 IRO65519:IRR65519 JBK65519:JBN65519 JLG65519:JLJ65519 JVC65519:JVF65519 KEY65519:KFB65519 KOU65519:KOX65519 KYQ65519:KYT65519 LIM65519:LIP65519 LSI65519:LSL65519 MCE65519:MCH65519 MMA65519:MMD65519 MVW65519:MVZ65519 NFS65519:NFV65519 NPO65519:NPR65519 NZK65519:NZN65519 OJG65519:OJJ65519 OTC65519:OTF65519 PCY65519:PDB65519 PMU65519:PMX65519 PWQ65519:PWT65519 QGM65519:QGP65519 QQI65519:QQL65519 RAE65519:RAH65519 RKA65519:RKD65519 RTW65519:RTZ65519 SDS65519:SDV65519 SNO65519:SNR65519 SXK65519:SXN65519 THG65519:THJ65519 TRC65519:TRF65519 UAY65519:UBB65519 UKU65519:UKX65519 UUQ65519:UUT65519 VEM65519:VEP65519 VOI65519:VOL65519 VYE65519:VYH65519 WIA65519:WID65519 WRW65519:WRZ65519 FK131055:FN131055 PG131055:PJ131055 ZC131055:ZF131055 AIY131055:AJB131055 ASU131055:ASX131055 BCQ131055:BCT131055 BMM131055:BMP131055 BWI131055:BWL131055 CGE131055:CGH131055 CQA131055:CQD131055 CZW131055:CZZ131055 DJS131055:DJV131055 DTO131055:DTR131055 EDK131055:EDN131055 ENG131055:ENJ131055 EXC131055:EXF131055 FGY131055:FHB131055 FQU131055:FQX131055 GAQ131055:GAT131055 GKM131055:GKP131055 GUI131055:GUL131055 HEE131055:HEH131055 HOA131055:HOD131055 HXW131055:HXZ131055 IHS131055:IHV131055 IRO131055:IRR131055 JBK131055:JBN131055 JLG131055:JLJ131055 JVC131055:JVF131055 KEY131055:KFB131055 KOU131055:KOX131055 KYQ131055:KYT131055 LIM131055:LIP131055 LSI131055:LSL131055 MCE131055:MCH131055 MMA131055:MMD131055 MVW131055:MVZ131055 NFS131055:NFV131055 NPO131055:NPR131055 NZK131055:NZN131055 OJG131055:OJJ131055 OTC131055:OTF131055 PCY131055:PDB131055 PMU131055:PMX131055 PWQ131055:PWT131055 QGM131055:QGP131055 QQI131055:QQL131055 RAE131055:RAH131055 RKA131055:RKD131055 RTW131055:RTZ131055 SDS131055:SDV131055 SNO131055:SNR131055 SXK131055:SXN131055 THG131055:THJ131055 TRC131055:TRF131055 UAY131055:UBB131055 UKU131055:UKX131055 UUQ131055:UUT131055 VEM131055:VEP131055 VOI131055:VOL131055 VYE131055:VYH131055 WIA131055:WID131055 WRW131055:WRZ131055 FK196591:FN196591 PG196591:PJ196591 ZC196591:ZF196591 AIY196591:AJB196591 ASU196591:ASX196591 BCQ196591:BCT196591 BMM196591:BMP196591 BWI196591:BWL196591 CGE196591:CGH196591 CQA196591:CQD196591 CZW196591:CZZ196591 DJS196591:DJV196591 DTO196591:DTR196591 EDK196591:EDN196591 ENG196591:ENJ196591 EXC196591:EXF196591 FGY196591:FHB196591 FQU196591:FQX196591 GAQ196591:GAT196591 GKM196591:GKP196591 GUI196591:GUL196591 HEE196591:HEH196591 HOA196591:HOD196591 HXW196591:HXZ196591 IHS196591:IHV196591 IRO196591:IRR196591 JBK196591:JBN196591 JLG196591:JLJ196591 JVC196591:JVF196591 KEY196591:KFB196591 KOU196591:KOX196591 KYQ196591:KYT196591 LIM196591:LIP196591 LSI196591:LSL196591 MCE196591:MCH196591 MMA196591:MMD196591 MVW196591:MVZ196591 NFS196591:NFV196591 NPO196591:NPR196591 NZK196591:NZN196591 OJG196591:OJJ196591 OTC196591:OTF196591 PCY196591:PDB196591 PMU196591:PMX196591 PWQ196591:PWT196591 QGM196591:QGP196591 QQI196591:QQL196591 RAE196591:RAH196591 RKA196591:RKD196591 RTW196591:RTZ196591 SDS196591:SDV196591 SNO196591:SNR196591 SXK196591:SXN196591 THG196591:THJ196591 TRC196591:TRF196591 UAY196591:UBB196591 UKU196591:UKX196591 UUQ196591:UUT196591 VEM196591:VEP196591 VOI196591:VOL196591 VYE196591:VYH196591 WIA196591:WID196591 WRW196591:WRZ196591 FK262127:FN262127 PG262127:PJ262127 ZC262127:ZF262127 AIY262127:AJB262127 ASU262127:ASX262127 BCQ262127:BCT262127 BMM262127:BMP262127 BWI262127:BWL262127 CGE262127:CGH262127 CQA262127:CQD262127 CZW262127:CZZ262127 DJS262127:DJV262127 DTO262127:DTR262127 EDK262127:EDN262127 ENG262127:ENJ262127 EXC262127:EXF262127 FGY262127:FHB262127 FQU262127:FQX262127 GAQ262127:GAT262127 GKM262127:GKP262127 GUI262127:GUL262127 HEE262127:HEH262127 HOA262127:HOD262127 HXW262127:HXZ262127 IHS262127:IHV262127 IRO262127:IRR262127 JBK262127:JBN262127 JLG262127:JLJ262127 JVC262127:JVF262127 KEY262127:KFB262127 KOU262127:KOX262127 KYQ262127:KYT262127 LIM262127:LIP262127 LSI262127:LSL262127 MCE262127:MCH262127 MMA262127:MMD262127 MVW262127:MVZ262127 NFS262127:NFV262127 NPO262127:NPR262127 NZK262127:NZN262127 OJG262127:OJJ262127 OTC262127:OTF262127 PCY262127:PDB262127 PMU262127:PMX262127 PWQ262127:PWT262127 QGM262127:QGP262127 QQI262127:QQL262127 RAE262127:RAH262127 RKA262127:RKD262127 RTW262127:RTZ262127 SDS262127:SDV262127 SNO262127:SNR262127 SXK262127:SXN262127 THG262127:THJ262127 TRC262127:TRF262127 UAY262127:UBB262127 UKU262127:UKX262127 UUQ262127:UUT262127 VEM262127:VEP262127 VOI262127:VOL262127 VYE262127:VYH262127 WIA262127:WID262127 WRW262127:WRZ262127 FK327663:FN327663 PG327663:PJ327663 ZC327663:ZF327663 AIY327663:AJB327663 ASU327663:ASX327663 BCQ327663:BCT327663 BMM327663:BMP327663 BWI327663:BWL327663 CGE327663:CGH327663 CQA327663:CQD327663 CZW327663:CZZ327663 DJS327663:DJV327663 DTO327663:DTR327663 EDK327663:EDN327663 ENG327663:ENJ327663 EXC327663:EXF327663 FGY327663:FHB327663 FQU327663:FQX327663 GAQ327663:GAT327663 GKM327663:GKP327663 GUI327663:GUL327663 HEE327663:HEH327663 HOA327663:HOD327663 HXW327663:HXZ327663 IHS327663:IHV327663 IRO327663:IRR327663 JBK327663:JBN327663 JLG327663:JLJ327663 JVC327663:JVF327663 KEY327663:KFB327663 KOU327663:KOX327663 KYQ327663:KYT327663 LIM327663:LIP327663 LSI327663:LSL327663 MCE327663:MCH327663 MMA327663:MMD327663 MVW327663:MVZ327663 NFS327663:NFV327663 NPO327663:NPR327663 NZK327663:NZN327663 OJG327663:OJJ327663 OTC327663:OTF327663 PCY327663:PDB327663 PMU327663:PMX327663 PWQ327663:PWT327663 QGM327663:QGP327663 QQI327663:QQL327663 RAE327663:RAH327663 RKA327663:RKD327663 RTW327663:RTZ327663 SDS327663:SDV327663 SNO327663:SNR327663 SXK327663:SXN327663 THG327663:THJ327663 TRC327663:TRF327663 UAY327663:UBB327663 UKU327663:UKX327663 UUQ327663:UUT327663 VEM327663:VEP327663 VOI327663:VOL327663 VYE327663:VYH327663 WIA327663:WID327663 WRW327663:WRZ327663 FK393199:FN393199 PG393199:PJ393199 ZC393199:ZF393199 AIY393199:AJB393199 ASU393199:ASX393199 BCQ393199:BCT393199 BMM393199:BMP393199 BWI393199:BWL393199 CGE393199:CGH393199 CQA393199:CQD393199 CZW393199:CZZ393199 DJS393199:DJV393199 DTO393199:DTR393199 EDK393199:EDN393199 ENG393199:ENJ393199 EXC393199:EXF393199 FGY393199:FHB393199 FQU393199:FQX393199 GAQ393199:GAT393199 GKM393199:GKP393199 GUI393199:GUL393199 HEE393199:HEH393199 HOA393199:HOD393199 HXW393199:HXZ393199 IHS393199:IHV393199 IRO393199:IRR393199 JBK393199:JBN393199 JLG393199:JLJ393199 JVC393199:JVF393199 KEY393199:KFB393199 KOU393199:KOX393199 KYQ393199:KYT393199 LIM393199:LIP393199 LSI393199:LSL393199 MCE393199:MCH393199 MMA393199:MMD393199 MVW393199:MVZ393199 NFS393199:NFV393199 NPO393199:NPR393199 NZK393199:NZN393199 OJG393199:OJJ393199 OTC393199:OTF393199 PCY393199:PDB393199 PMU393199:PMX393199 PWQ393199:PWT393199 QGM393199:QGP393199 QQI393199:QQL393199 RAE393199:RAH393199 RKA393199:RKD393199 RTW393199:RTZ393199 SDS393199:SDV393199 SNO393199:SNR393199 SXK393199:SXN393199 THG393199:THJ393199 TRC393199:TRF393199 UAY393199:UBB393199 UKU393199:UKX393199 UUQ393199:UUT393199 VEM393199:VEP393199 VOI393199:VOL393199 VYE393199:VYH393199 WIA393199:WID393199 WRW393199:WRZ393199 FK458735:FN458735 PG458735:PJ458735 ZC458735:ZF458735 AIY458735:AJB458735 ASU458735:ASX458735 BCQ458735:BCT458735 BMM458735:BMP458735 BWI458735:BWL458735 CGE458735:CGH458735 CQA458735:CQD458735 CZW458735:CZZ458735 DJS458735:DJV458735 DTO458735:DTR458735 EDK458735:EDN458735 ENG458735:ENJ458735 EXC458735:EXF458735 FGY458735:FHB458735 FQU458735:FQX458735 GAQ458735:GAT458735 GKM458735:GKP458735 GUI458735:GUL458735 HEE458735:HEH458735 HOA458735:HOD458735 HXW458735:HXZ458735 IHS458735:IHV458735 IRO458735:IRR458735 JBK458735:JBN458735 JLG458735:JLJ458735 JVC458735:JVF458735 KEY458735:KFB458735 KOU458735:KOX458735 KYQ458735:KYT458735 LIM458735:LIP458735 LSI458735:LSL458735 MCE458735:MCH458735 MMA458735:MMD458735 MVW458735:MVZ458735 NFS458735:NFV458735 NPO458735:NPR458735 NZK458735:NZN458735 OJG458735:OJJ458735 OTC458735:OTF458735 PCY458735:PDB458735 PMU458735:PMX458735 PWQ458735:PWT458735 QGM458735:QGP458735 QQI458735:QQL458735 RAE458735:RAH458735 RKA458735:RKD458735 RTW458735:RTZ458735 SDS458735:SDV458735 SNO458735:SNR458735 SXK458735:SXN458735 THG458735:THJ458735 TRC458735:TRF458735 UAY458735:UBB458735 UKU458735:UKX458735 UUQ458735:UUT458735 VEM458735:VEP458735 VOI458735:VOL458735 VYE458735:VYH458735 WIA458735:WID458735 WRW458735:WRZ458735 FK524271:FN524271 PG524271:PJ524271 ZC524271:ZF524271 AIY524271:AJB524271 ASU524271:ASX524271 BCQ524271:BCT524271 BMM524271:BMP524271 BWI524271:BWL524271 CGE524271:CGH524271 CQA524271:CQD524271 CZW524271:CZZ524271 DJS524271:DJV524271 DTO524271:DTR524271 EDK524271:EDN524271 ENG524271:ENJ524271 EXC524271:EXF524271 FGY524271:FHB524271 FQU524271:FQX524271 GAQ524271:GAT524271 GKM524271:GKP524271 GUI524271:GUL524271 HEE524271:HEH524271 HOA524271:HOD524271 HXW524271:HXZ524271 IHS524271:IHV524271 IRO524271:IRR524271 JBK524271:JBN524271 JLG524271:JLJ524271 JVC524271:JVF524271 KEY524271:KFB524271 KOU524271:KOX524271 KYQ524271:KYT524271 LIM524271:LIP524271 LSI524271:LSL524271 MCE524271:MCH524271 MMA524271:MMD524271 MVW524271:MVZ524271 NFS524271:NFV524271 NPO524271:NPR524271 NZK524271:NZN524271 OJG524271:OJJ524271 OTC524271:OTF524271 PCY524271:PDB524271 PMU524271:PMX524271 PWQ524271:PWT524271 QGM524271:QGP524271 QQI524271:QQL524271 RAE524271:RAH524271 RKA524271:RKD524271 RTW524271:RTZ524271 SDS524271:SDV524271 SNO524271:SNR524271 SXK524271:SXN524271 THG524271:THJ524271 TRC524271:TRF524271 UAY524271:UBB524271 UKU524271:UKX524271 UUQ524271:UUT524271 VEM524271:VEP524271 VOI524271:VOL524271 VYE524271:VYH524271 WIA524271:WID524271 WRW524271:WRZ524271 FK589807:FN589807 PG589807:PJ589807 ZC589807:ZF589807 AIY589807:AJB589807 ASU589807:ASX589807 BCQ589807:BCT589807 BMM589807:BMP589807 BWI589807:BWL589807 CGE589807:CGH589807 CQA589807:CQD589807 CZW589807:CZZ589807 DJS589807:DJV589807 DTO589807:DTR589807 EDK589807:EDN589807 ENG589807:ENJ589807 EXC589807:EXF589807 FGY589807:FHB589807 FQU589807:FQX589807 GAQ589807:GAT589807 GKM589807:GKP589807 GUI589807:GUL589807 HEE589807:HEH589807 HOA589807:HOD589807 HXW589807:HXZ589807 IHS589807:IHV589807 IRO589807:IRR589807 JBK589807:JBN589807 JLG589807:JLJ589807 JVC589807:JVF589807 KEY589807:KFB589807 KOU589807:KOX589807 KYQ589807:KYT589807 LIM589807:LIP589807 LSI589807:LSL589807 MCE589807:MCH589807 MMA589807:MMD589807 MVW589807:MVZ589807 NFS589807:NFV589807 NPO589807:NPR589807 NZK589807:NZN589807 OJG589807:OJJ589807 OTC589807:OTF589807 PCY589807:PDB589807 PMU589807:PMX589807 PWQ589807:PWT589807 QGM589807:QGP589807 QQI589807:QQL589807 RAE589807:RAH589807 RKA589807:RKD589807 RTW589807:RTZ589807 SDS589807:SDV589807 SNO589807:SNR589807 SXK589807:SXN589807 THG589807:THJ589807 TRC589807:TRF589807 UAY589807:UBB589807 UKU589807:UKX589807 UUQ589807:UUT589807 VEM589807:VEP589807 VOI589807:VOL589807 VYE589807:VYH589807 WIA589807:WID589807 WRW589807:WRZ589807 FK655343:FN655343 PG655343:PJ655343 ZC655343:ZF655343 AIY655343:AJB655343 ASU655343:ASX655343 BCQ655343:BCT655343 BMM655343:BMP655343 BWI655343:BWL655343 CGE655343:CGH655343 CQA655343:CQD655343 CZW655343:CZZ655343 DJS655343:DJV655343 DTO655343:DTR655343 EDK655343:EDN655343 ENG655343:ENJ655343 EXC655343:EXF655343 FGY655343:FHB655343 FQU655343:FQX655343 GAQ655343:GAT655343 GKM655343:GKP655343 GUI655343:GUL655343 HEE655343:HEH655343 HOA655343:HOD655343 HXW655343:HXZ655343 IHS655343:IHV655343 IRO655343:IRR655343 JBK655343:JBN655343 JLG655343:JLJ655343 JVC655343:JVF655343 KEY655343:KFB655343 KOU655343:KOX655343 KYQ655343:KYT655343 LIM655343:LIP655343 LSI655343:LSL655343 MCE655343:MCH655343 MMA655343:MMD655343 MVW655343:MVZ655343 NFS655343:NFV655343 NPO655343:NPR655343 NZK655343:NZN655343 OJG655343:OJJ655343 OTC655343:OTF655343 PCY655343:PDB655343 PMU655343:PMX655343 PWQ655343:PWT655343 QGM655343:QGP655343 QQI655343:QQL655343 RAE655343:RAH655343 RKA655343:RKD655343 RTW655343:RTZ655343 SDS655343:SDV655343 SNO655343:SNR655343 SXK655343:SXN655343 THG655343:THJ655343 TRC655343:TRF655343 UAY655343:UBB655343 UKU655343:UKX655343 UUQ655343:UUT655343 VEM655343:VEP655343 VOI655343:VOL655343 VYE655343:VYH655343 WIA655343:WID655343 WRW655343:WRZ655343 FK720879:FN720879 PG720879:PJ720879 ZC720879:ZF720879 AIY720879:AJB720879 ASU720879:ASX720879 BCQ720879:BCT720879 BMM720879:BMP720879 BWI720879:BWL720879 CGE720879:CGH720879 CQA720879:CQD720879 CZW720879:CZZ720879 DJS720879:DJV720879 DTO720879:DTR720879 EDK720879:EDN720879 ENG720879:ENJ720879 EXC720879:EXF720879 FGY720879:FHB720879 FQU720879:FQX720879 GAQ720879:GAT720879 GKM720879:GKP720879 GUI720879:GUL720879 HEE720879:HEH720879 HOA720879:HOD720879 HXW720879:HXZ720879 IHS720879:IHV720879 IRO720879:IRR720879 JBK720879:JBN720879 JLG720879:JLJ720879 JVC720879:JVF720879 KEY720879:KFB720879 KOU720879:KOX720879 KYQ720879:KYT720879 LIM720879:LIP720879 LSI720879:LSL720879 MCE720879:MCH720879 MMA720879:MMD720879 MVW720879:MVZ720879 NFS720879:NFV720879 NPO720879:NPR720879 NZK720879:NZN720879 OJG720879:OJJ720879 OTC720879:OTF720879 PCY720879:PDB720879 PMU720879:PMX720879 PWQ720879:PWT720879 QGM720879:QGP720879 QQI720879:QQL720879 RAE720879:RAH720879 RKA720879:RKD720879 RTW720879:RTZ720879 SDS720879:SDV720879 SNO720879:SNR720879 SXK720879:SXN720879 THG720879:THJ720879 TRC720879:TRF720879 UAY720879:UBB720879 UKU720879:UKX720879 UUQ720879:UUT720879 VEM720879:VEP720879 VOI720879:VOL720879 VYE720879:VYH720879 WIA720879:WID720879 WRW720879:WRZ720879 FK786415:FN786415 PG786415:PJ786415 ZC786415:ZF786415 AIY786415:AJB786415 ASU786415:ASX786415 BCQ786415:BCT786415 BMM786415:BMP786415 BWI786415:BWL786415 CGE786415:CGH786415 CQA786415:CQD786415 CZW786415:CZZ786415 DJS786415:DJV786415 DTO786415:DTR786415 EDK786415:EDN786415 ENG786415:ENJ786415 EXC786415:EXF786415 FGY786415:FHB786415 FQU786415:FQX786415 GAQ786415:GAT786415 GKM786415:GKP786415 GUI786415:GUL786415 HEE786415:HEH786415 HOA786415:HOD786415 HXW786415:HXZ786415 IHS786415:IHV786415 IRO786415:IRR786415 JBK786415:JBN786415 JLG786415:JLJ786415 JVC786415:JVF786415 KEY786415:KFB786415 KOU786415:KOX786415 KYQ786415:KYT786415 LIM786415:LIP786415 LSI786415:LSL786415 MCE786415:MCH786415 MMA786415:MMD786415 MVW786415:MVZ786415 NFS786415:NFV786415 NPO786415:NPR786415 NZK786415:NZN786415 OJG786415:OJJ786415 OTC786415:OTF786415 PCY786415:PDB786415 PMU786415:PMX786415 PWQ786415:PWT786415 QGM786415:QGP786415 QQI786415:QQL786415 RAE786415:RAH786415 RKA786415:RKD786415 RTW786415:RTZ786415 SDS786415:SDV786415 SNO786415:SNR786415 SXK786415:SXN786415 THG786415:THJ786415 TRC786415:TRF786415 UAY786415:UBB786415 UKU786415:UKX786415 UUQ786415:UUT786415 VEM786415:VEP786415 VOI786415:VOL786415 VYE786415:VYH786415 WIA786415:WID786415 WRW786415:WRZ786415 FK851951:FN851951 PG851951:PJ851951 ZC851951:ZF851951 AIY851951:AJB851951 ASU851951:ASX851951 BCQ851951:BCT851951 BMM851951:BMP851951 BWI851951:BWL851951 CGE851951:CGH851951 CQA851951:CQD851951 CZW851951:CZZ851951 DJS851951:DJV851951 DTO851951:DTR851951 EDK851951:EDN851951 ENG851951:ENJ851951 EXC851951:EXF851951 FGY851951:FHB851951 FQU851951:FQX851951 GAQ851951:GAT851951 GKM851951:GKP851951 GUI851951:GUL851951 HEE851951:HEH851951 HOA851951:HOD851951 HXW851951:HXZ851951 IHS851951:IHV851951 IRO851951:IRR851951 JBK851951:JBN851951 JLG851951:JLJ851951 JVC851951:JVF851951 KEY851951:KFB851951 KOU851951:KOX851951 KYQ851951:KYT851951 LIM851951:LIP851951 LSI851951:LSL851951 MCE851951:MCH851951 MMA851951:MMD851951 MVW851951:MVZ851951 NFS851951:NFV851951 NPO851951:NPR851951 NZK851951:NZN851951 OJG851951:OJJ851951 OTC851951:OTF851951 PCY851951:PDB851951 PMU851951:PMX851951 PWQ851951:PWT851951 QGM851951:QGP851951 QQI851951:QQL851951 RAE851951:RAH851951 RKA851951:RKD851951 RTW851951:RTZ851951 SDS851951:SDV851951 SNO851951:SNR851951 SXK851951:SXN851951 THG851951:THJ851951 TRC851951:TRF851951 UAY851951:UBB851951 UKU851951:UKX851951 UUQ851951:UUT851951 VEM851951:VEP851951 VOI851951:VOL851951 VYE851951:VYH851951 WIA851951:WID851951 WRW851951:WRZ851951 FK917487:FN917487 PG917487:PJ917487 ZC917487:ZF917487 AIY917487:AJB917487 ASU917487:ASX917487 BCQ917487:BCT917487 BMM917487:BMP917487 BWI917487:BWL917487 CGE917487:CGH917487 CQA917487:CQD917487 CZW917487:CZZ917487 DJS917487:DJV917487 DTO917487:DTR917487 EDK917487:EDN917487 ENG917487:ENJ917487 EXC917487:EXF917487 FGY917487:FHB917487 FQU917487:FQX917487 GAQ917487:GAT917487 GKM917487:GKP917487 GUI917487:GUL917487 HEE917487:HEH917487 HOA917487:HOD917487 HXW917487:HXZ917487 IHS917487:IHV917487 IRO917487:IRR917487 JBK917487:JBN917487 JLG917487:JLJ917487 JVC917487:JVF917487 KEY917487:KFB917487 KOU917487:KOX917487 KYQ917487:KYT917487 LIM917487:LIP917487 LSI917487:LSL917487 MCE917487:MCH917487 MMA917487:MMD917487 MVW917487:MVZ917487 NFS917487:NFV917487 NPO917487:NPR917487 NZK917487:NZN917487 OJG917487:OJJ917487 OTC917487:OTF917487 PCY917487:PDB917487 PMU917487:PMX917487 PWQ917487:PWT917487 QGM917487:QGP917487 QQI917487:QQL917487 RAE917487:RAH917487 RKA917487:RKD917487 RTW917487:RTZ917487 SDS917487:SDV917487 SNO917487:SNR917487 SXK917487:SXN917487 THG917487:THJ917487 TRC917487:TRF917487 UAY917487:UBB917487 UKU917487:UKX917487 UUQ917487:UUT917487 VEM917487:VEP917487 VOI917487:VOL917487 VYE917487:VYH917487 WIA917487:WID917487 WRW917487:WRZ917487" xr:uid="{14D49F8C-9954-484F-BBA9-C0A70DEAE551}">
       <formula1>"○"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT65526:FW65526 PP65526:PS65526 ZL65526:ZO65526 AJH65526:AJK65526 ATD65526:ATG65526 BCZ65526:BDC65526 BMV65526:BMY65526 BWR65526:BWU65526 CGN65526:CGQ65526 CQJ65526:CQM65526 DAF65526:DAI65526 DKB65526:DKE65526 DTX65526:DUA65526 EDT65526:EDW65526 ENP65526:ENS65526 EXL65526:EXO65526 FHH65526:FHK65526 FRD65526:FRG65526 GAZ65526:GBC65526 GKV65526:GKY65526 GUR65526:GUU65526 HEN65526:HEQ65526 HOJ65526:HOM65526 HYF65526:HYI65526 IIB65526:IIE65526 IRX65526:ISA65526 JBT65526:JBW65526 JLP65526:JLS65526 JVL65526:JVO65526 KFH65526:KFK65526 KPD65526:KPG65526 KYZ65526:KZC65526 LIV65526:LIY65526 LSR65526:LSU65526 MCN65526:MCQ65526 MMJ65526:MMM65526 MWF65526:MWI65526 NGB65526:NGE65526 NPX65526:NQA65526 NZT65526:NZW65526 OJP65526:OJS65526 OTL65526:OTO65526 PDH65526:PDK65526 PND65526:PNG65526 PWZ65526:PXC65526 QGV65526:QGY65526 QQR65526:QQU65526 RAN65526:RAQ65526 RKJ65526:RKM65526 RUF65526:RUI65526 SEB65526:SEE65526 SNX65526:SOA65526 SXT65526:SXW65526 THP65526:THS65526 TRL65526:TRO65526 UBH65526:UBK65526 ULD65526:ULG65526 UUZ65526:UVC65526 VEV65526:VEY65526 VOR65526:VOU65526 VYN65526:VYQ65526 WIJ65526:WIM65526 WSF65526:WSI65526 FT131062:FW131062 PP131062:PS131062 ZL131062:ZO131062 AJH131062:AJK131062 ATD131062:ATG131062 BCZ131062:BDC131062 BMV131062:BMY131062 BWR131062:BWU131062 CGN131062:CGQ131062 CQJ131062:CQM131062 DAF131062:DAI131062 DKB131062:DKE131062 DTX131062:DUA131062 EDT131062:EDW131062 ENP131062:ENS131062 EXL131062:EXO131062 FHH131062:FHK131062 FRD131062:FRG131062 GAZ131062:GBC131062 GKV131062:GKY131062 GUR131062:GUU131062 HEN131062:HEQ131062 HOJ131062:HOM131062 HYF131062:HYI131062 IIB131062:IIE131062 IRX131062:ISA131062 JBT131062:JBW131062 JLP131062:JLS131062 JVL131062:JVO131062 KFH131062:KFK131062 KPD131062:KPG131062 KYZ131062:KZC131062 LIV131062:LIY131062 LSR131062:LSU131062 MCN131062:MCQ131062 MMJ131062:MMM131062 MWF131062:MWI131062 NGB131062:NGE131062 NPX131062:NQA131062 NZT131062:NZW131062 OJP131062:OJS131062 OTL131062:OTO131062 PDH131062:PDK131062 PND131062:PNG131062 PWZ131062:PXC131062 QGV131062:QGY131062 QQR131062:QQU131062 RAN131062:RAQ131062 RKJ131062:RKM131062 RUF131062:RUI131062 SEB131062:SEE131062 SNX131062:SOA131062 SXT131062:SXW131062 THP131062:THS131062 TRL131062:TRO131062 UBH131062:UBK131062 ULD131062:ULG131062 UUZ131062:UVC131062 VEV131062:VEY131062 VOR131062:VOU131062 VYN131062:VYQ131062 WIJ131062:WIM131062 WSF131062:WSI131062 FT196598:FW196598 PP196598:PS196598 ZL196598:ZO196598 AJH196598:AJK196598 ATD196598:ATG196598 BCZ196598:BDC196598 BMV196598:BMY196598 BWR196598:BWU196598 CGN196598:CGQ196598 CQJ196598:CQM196598 DAF196598:DAI196598 DKB196598:DKE196598 DTX196598:DUA196598 EDT196598:EDW196598 ENP196598:ENS196598 EXL196598:EXO196598 FHH196598:FHK196598 FRD196598:FRG196598 GAZ196598:GBC196598 GKV196598:GKY196598 GUR196598:GUU196598 HEN196598:HEQ196598 HOJ196598:HOM196598 HYF196598:HYI196598 IIB196598:IIE196598 IRX196598:ISA196598 JBT196598:JBW196598 JLP196598:JLS196598 JVL196598:JVO196598 KFH196598:KFK196598 KPD196598:KPG196598 KYZ196598:KZC196598 LIV196598:LIY196598 LSR196598:LSU196598 MCN196598:MCQ196598 MMJ196598:MMM196598 MWF196598:MWI196598 NGB196598:NGE196598 NPX196598:NQA196598 NZT196598:NZW196598 OJP196598:OJS196598 OTL196598:OTO196598 PDH196598:PDK196598 PND196598:PNG196598 PWZ196598:PXC196598 QGV196598:QGY196598 QQR196598:QQU196598 RAN196598:RAQ196598 RKJ196598:RKM196598 RUF196598:RUI196598 SEB196598:SEE196598 SNX196598:SOA196598 SXT196598:SXW196598 THP196598:THS196598 TRL196598:TRO196598 UBH196598:UBK196598 ULD196598:ULG196598 UUZ196598:UVC196598 VEV196598:VEY196598 VOR196598:VOU196598 VYN196598:VYQ196598 WIJ196598:WIM196598 WSF196598:WSI196598 FT262134:FW262134 PP262134:PS262134 ZL262134:ZO262134 AJH262134:AJK262134 ATD262134:ATG262134 BCZ262134:BDC262134 BMV262134:BMY262134 BWR262134:BWU262134 CGN262134:CGQ262134 CQJ262134:CQM262134 DAF262134:DAI262134 DKB262134:DKE262134 DTX262134:DUA262134 EDT262134:EDW262134 ENP262134:ENS262134 EXL262134:EXO262134 FHH262134:FHK262134 FRD262134:FRG262134 GAZ262134:GBC262134 GKV262134:GKY262134 GUR262134:GUU262134 HEN262134:HEQ262134 HOJ262134:HOM262134 HYF262134:HYI262134 IIB262134:IIE262134 IRX262134:ISA262134 JBT262134:JBW262134 JLP262134:JLS262134 JVL262134:JVO262134 KFH262134:KFK262134 KPD262134:KPG262134 KYZ262134:KZC262134 LIV262134:LIY262134 LSR262134:LSU262134 MCN262134:MCQ262134 MMJ262134:MMM262134 MWF262134:MWI262134 NGB262134:NGE262134 NPX262134:NQA262134 NZT262134:NZW262134 OJP262134:OJS262134 OTL262134:OTO262134 PDH262134:PDK262134 PND262134:PNG262134 PWZ262134:PXC262134 QGV262134:QGY262134 QQR262134:QQU262134 RAN262134:RAQ262134 RKJ262134:RKM262134 RUF262134:RUI262134 SEB262134:SEE262134 SNX262134:SOA262134 SXT262134:SXW262134 THP262134:THS262134 TRL262134:TRO262134 UBH262134:UBK262134 ULD262134:ULG262134 UUZ262134:UVC262134 VEV262134:VEY262134 VOR262134:VOU262134 VYN262134:VYQ262134 WIJ262134:WIM262134 WSF262134:WSI262134 FT327670:FW327670 PP327670:PS327670 ZL327670:ZO327670 AJH327670:AJK327670 ATD327670:ATG327670 BCZ327670:BDC327670 BMV327670:BMY327670 BWR327670:BWU327670 CGN327670:CGQ327670 CQJ327670:CQM327670 DAF327670:DAI327670 DKB327670:DKE327670 DTX327670:DUA327670 EDT327670:EDW327670 ENP327670:ENS327670 EXL327670:EXO327670 FHH327670:FHK327670 FRD327670:FRG327670 GAZ327670:GBC327670 GKV327670:GKY327670 GUR327670:GUU327670 HEN327670:HEQ327670 HOJ327670:HOM327670 HYF327670:HYI327670 IIB327670:IIE327670 IRX327670:ISA327670 JBT327670:JBW327670 JLP327670:JLS327670 JVL327670:JVO327670 KFH327670:KFK327670 KPD327670:KPG327670 KYZ327670:KZC327670 LIV327670:LIY327670 LSR327670:LSU327670 MCN327670:MCQ327670 MMJ327670:MMM327670 MWF327670:MWI327670 NGB327670:NGE327670 NPX327670:NQA327670 NZT327670:NZW327670 OJP327670:OJS327670 OTL327670:OTO327670 PDH327670:PDK327670 PND327670:PNG327670 PWZ327670:PXC327670 QGV327670:QGY327670 QQR327670:QQU327670 RAN327670:RAQ327670 RKJ327670:RKM327670 RUF327670:RUI327670 SEB327670:SEE327670 SNX327670:SOA327670 SXT327670:SXW327670 THP327670:THS327670 TRL327670:TRO327670 UBH327670:UBK327670 ULD327670:ULG327670 UUZ327670:UVC327670 VEV327670:VEY327670 VOR327670:VOU327670 VYN327670:VYQ327670 WIJ327670:WIM327670 WSF327670:WSI327670 FT393206:FW393206 PP393206:PS393206 ZL393206:ZO393206 AJH393206:AJK393206 ATD393206:ATG393206 BCZ393206:BDC393206 BMV393206:BMY393206 BWR393206:BWU393206 CGN393206:CGQ393206 CQJ393206:CQM393206 DAF393206:DAI393206 DKB393206:DKE393206 DTX393206:DUA393206 EDT393206:EDW393206 ENP393206:ENS393206 EXL393206:EXO393206 FHH393206:FHK393206 FRD393206:FRG393206 GAZ393206:GBC393206 GKV393206:GKY393206 GUR393206:GUU393206 HEN393206:HEQ393206 HOJ393206:HOM393206 HYF393206:HYI393206 IIB393206:IIE393206 IRX393206:ISA393206 JBT393206:JBW393206 JLP393206:JLS393206 JVL393206:JVO393206 KFH393206:KFK393206 KPD393206:KPG393206 KYZ393206:KZC393206 LIV393206:LIY393206 LSR393206:LSU393206 MCN393206:MCQ393206 MMJ393206:MMM393206 MWF393206:MWI393206 NGB393206:NGE393206 NPX393206:NQA393206 NZT393206:NZW393206 OJP393206:OJS393206 OTL393206:OTO393206 PDH393206:PDK393206 PND393206:PNG393206 PWZ393206:PXC393206 QGV393206:QGY393206 QQR393206:QQU393206 RAN393206:RAQ393206 RKJ393206:RKM393206 RUF393206:RUI393206 SEB393206:SEE393206 SNX393206:SOA393206 SXT393206:SXW393206 THP393206:THS393206 TRL393206:TRO393206 UBH393206:UBK393206 ULD393206:ULG393206 UUZ393206:UVC393206 VEV393206:VEY393206 VOR393206:VOU393206 VYN393206:VYQ393206 WIJ393206:WIM393206 WSF393206:WSI393206 FT458742:FW458742 PP458742:PS458742 ZL458742:ZO458742 AJH458742:AJK458742 ATD458742:ATG458742 BCZ458742:BDC458742 BMV458742:BMY458742 BWR458742:BWU458742 CGN458742:CGQ458742 CQJ458742:CQM458742 DAF458742:DAI458742 DKB458742:DKE458742 DTX458742:DUA458742 EDT458742:EDW458742 ENP458742:ENS458742 EXL458742:EXO458742 FHH458742:FHK458742 FRD458742:FRG458742 GAZ458742:GBC458742 GKV458742:GKY458742 GUR458742:GUU458742 HEN458742:HEQ458742 HOJ458742:HOM458742 HYF458742:HYI458742 IIB458742:IIE458742 IRX458742:ISA458742 JBT458742:JBW458742 JLP458742:JLS458742 JVL458742:JVO458742 KFH458742:KFK458742 KPD458742:KPG458742 KYZ458742:KZC458742 LIV458742:LIY458742 LSR458742:LSU458742 MCN458742:MCQ458742 MMJ458742:MMM458742 MWF458742:MWI458742 NGB458742:NGE458742 NPX458742:NQA458742 NZT458742:NZW458742 OJP458742:OJS458742 OTL458742:OTO458742 PDH458742:PDK458742 PND458742:PNG458742 PWZ458742:PXC458742 QGV458742:QGY458742 QQR458742:QQU458742 RAN458742:RAQ458742 RKJ458742:RKM458742 RUF458742:RUI458742 SEB458742:SEE458742 SNX458742:SOA458742 SXT458742:SXW458742 THP458742:THS458742 TRL458742:TRO458742 UBH458742:UBK458742 ULD458742:ULG458742 UUZ458742:UVC458742 VEV458742:VEY458742 VOR458742:VOU458742 VYN458742:VYQ458742 WIJ458742:WIM458742 WSF458742:WSI458742 FT524278:FW524278 PP524278:PS524278 ZL524278:ZO524278 AJH524278:AJK524278 ATD524278:ATG524278 BCZ524278:BDC524278 BMV524278:BMY524278 BWR524278:BWU524278 CGN524278:CGQ524278 CQJ524278:CQM524278 DAF524278:DAI524278 DKB524278:DKE524278 DTX524278:DUA524278 EDT524278:EDW524278 ENP524278:ENS524278 EXL524278:EXO524278 FHH524278:FHK524278 FRD524278:FRG524278 GAZ524278:GBC524278 GKV524278:GKY524278 GUR524278:GUU524278 HEN524278:HEQ524278 HOJ524278:HOM524278 HYF524278:HYI524278 IIB524278:IIE524278 IRX524278:ISA524278 JBT524278:JBW524278 JLP524278:JLS524278 JVL524278:JVO524278 KFH524278:KFK524278 KPD524278:KPG524278 KYZ524278:KZC524278 LIV524278:LIY524278 LSR524278:LSU524278 MCN524278:MCQ524278 MMJ524278:MMM524278 MWF524278:MWI524278 NGB524278:NGE524278 NPX524278:NQA524278 NZT524278:NZW524278 OJP524278:OJS524278 OTL524278:OTO524278 PDH524278:PDK524278 PND524278:PNG524278 PWZ524278:PXC524278 QGV524278:QGY524278 QQR524278:QQU524278 RAN524278:RAQ524278 RKJ524278:RKM524278 RUF524278:RUI524278 SEB524278:SEE524278 SNX524278:SOA524278 SXT524278:SXW524278 THP524278:THS524278 TRL524278:TRO524278 UBH524278:UBK524278 ULD524278:ULG524278 UUZ524278:UVC524278 VEV524278:VEY524278 VOR524278:VOU524278 VYN524278:VYQ524278 WIJ524278:WIM524278 WSF524278:WSI524278 FT589814:FW589814 PP589814:PS589814 ZL589814:ZO589814 AJH589814:AJK589814 ATD589814:ATG589814 BCZ589814:BDC589814 BMV589814:BMY589814 BWR589814:BWU589814 CGN589814:CGQ589814 CQJ589814:CQM589814 DAF589814:DAI589814 DKB589814:DKE589814 DTX589814:DUA589814 EDT589814:EDW589814 ENP589814:ENS589814 EXL589814:EXO589814 FHH589814:FHK589814 FRD589814:FRG589814 GAZ589814:GBC589814 GKV589814:GKY589814 GUR589814:GUU589814 HEN589814:HEQ589814 HOJ589814:HOM589814 HYF589814:HYI589814 IIB589814:IIE589814 IRX589814:ISA589814 JBT589814:JBW589814 JLP589814:JLS589814 JVL589814:JVO589814 KFH589814:KFK589814 KPD589814:KPG589814 KYZ589814:KZC589814 LIV589814:LIY589814 LSR589814:LSU589814 MCN589814:MCQ589814 MMJ589814:MMM589814 MWF589814:MWI589814 NGB589814:NGE589814 NPX589814:NQA589814 NZT589814:NZW589814 OJP589814:OJS589814 OTL589814:OTO589814 PDH589814:PDK589814 PND589814:PNG589814 PWZ589814:PXC589814 QGV589814:QGY589814 QQR589814:QQU589814 RAN589814:RAQ589814 RKJ589814:RKM589814 RUF589814:RUI589814 SEB589814:SEE589814 SNX589814:SOA589814 SXT589814:SXW589814 THP589814:THS589814 TRL589814:TRO589814 UBH589814:UBK589814 ULD589814:ULG589814 UUZ589814:UVC589814 VEV589814:VEY589814 VOR589814:VOU589814 VYN589814:VYQ589814 WIJ589814:WIM589814 WSF589814:WSI589814 FT655350:FW655350 PP655350:PS655350 ZL655350:ZO655350 AJH655350:AJK655350 ATD655350:ATG655350 BCZ655350:BDC655350 BMV655350:BMY655350 BWR655350:BWU655350 CGN655350:CGQ655350 CQJ655350:CQM655350 DAF655350:DAI655350 DKB655350:DKE655350 DTX655350:DUA655350 EDT655350:EDW655350 ENP655350:ENS655350 EXL655350:EXO655350 FHH655350:FHK655350 FRD655350:FRG655350 GAZ655350:GBC655350 GKV655350:GKY655350 GUR655350:GUU655350 HEN655350:HEQ655350 HOJ655350:HOM655350 HYF655350:HYI655350 IIB655350:IIE655350 IRX655350:ISA655350 JBT655350:JBW655350 JLP655350:JLS655350 JVL655350:JVO655350 KFH655350:KFK655350 KPD655350:KPG655350 KYZ655350:KZC655350 LIV655350:LIY655350 LSR655350:LSU655350 MCN655350:MCQ655350 MMJ655350:MMM655350 MWF655350:MWI655350 NGB655350:NGE655350 NPX655350:NQA655350 NZT655350:NZW655350 OJP655350:OJS655350 OTL655350:OTO655350 PDH655350:PDK655350 PND655350:PNG655350 PWZ655350:PXC655350 QGV655350:QGY655350 QQR655350:QQU655350 RAN655350:RAQ655350 RKJ655350:RKM655350 RUF655350:RUI655350 SEB655350:SEE655350 SNX655350:SOA655350 SXT655350:SXW655350 THP655350:THS655350 TRL655350:TRO655350 UBH655350:UBK655350 ULD655350:ULG655350 UUZ655350:UVC655350 VEV655350:VEY655350 VOR655350:VOU655350 VYN655350:VYQ655350 WIJ655350:WIM655350 WSF655350:WSI655350 FT720886:FW720886 PP720886:PS720886 ZL720886:ZO720886 AJH720886:AJK720886 ATD720886:ATG720886 BCZ720886:BDC720886 BMV720886:BMY720886 BWR720886:BWU720886 CGN720886:CGQ720886 CQJ720886:CQM720886 DAF720886:DAI720886 DKB720886:DKE720886 DTX720886:DUA720886 EDT720886:EDW720886 ENP720886:ENS720886 EXL720886:EXO720886 FHH720886:FHK720886 FRD720886:FRG720886 GAZ720886:GBC720886 GKV720886:GKY720886 GUR720886:GUU720886 HEN720886:HEQ720886 HOJ720886:HOM720886 HYF720886:HYI720886 IIB720886:IIE720886 IRX720886:ISA720886 JBT720886:JBW720886 JLP720886:JLS720886 JVL720886:JVO720886 KFH720886:KFK720886 KPD720886:KPG720886 KYZ720886:KZC720886 LIV720886:LIY720886 LSR720886:LSU720886 MCN720886:MCQ720886 MMJ720886:MMM720886 MWF720886:MWI720886 NGB720886:NGE720886 NPX720886:NQA720886 NZT720886:NZW720886 OJP720886:OJS720886 OTL720886:OTO720886 PDH720886:PDK720886 PND720886:PNG720886 PWZ720886:PXC720886 QGV720886:QGY720886 QQR720886:QQU720886 RAN720886:RAQ720886 RKJ720886:RKM720886 RUF720886:RUI720886 SEB720886:SEE720886 SNX720886:SOA720886 SXT720886:SXW720886 THP720886:THS720886 TRL720886:TRO720886 UBH720886:UBK720886 ULD720886:ULG720886 UUZ720886:UVC720886 VEV720886:VEY720886 VOR720886:VOU720886 VYN720886:VYQ720886 WIJ720886:WIM720886 WSF720886:WSI720886 FT786422:FW786422 PP786422:PS786422 ZL786422:ZO786422 AJH786422:AJK786422 ATD786422:ATG786422 BCZ786422:BDC786422 BMV786422:BMY786422 BWR786422:BWU786422 CGN786422:CGQ786422 CQJ786422:CQM786422 DAF786422:DAI786422 DKB786422:DKE786422 DTX786422:DUA786422 EDT786422:EDW786422 ENP786422:ENS786422 EXL786422:EXO786422 FHH786422:FHK786422 FRD786422:FRG786422 GAZ786422:GBC786422 GKV786422:GKY786422 GUR786422:GUU786422 HEN786422:HEQ786422 HOJ786422:HOM786422 HYF786422:HYI786422 IIB786422:IIE786422 IRX786422:ISA786422 JBT786422:JBW786422 JLP786422:JLS786422 JVL786422:JVO786422 KFH786422:KFK786422 KPD786422:KPG786422 KYZ786422:KZC786422 LIV786422:LIY786422 LSR786422:LSU786422 MCN786422:MCQ786422 MMJ786422:MMM786422 MWF786422:MWI786422 NGB786422:NGE786422 NPX786422:NQA786422 NZT786422:NZW786422 OJP786422:OJS786422 OTL786422:OTO786422 PDH786422:PDK786422 PND786422:PNG786422 PWZ786422:PXC786422 QGV786422:QGY786422 QQR786422:QQU786422 RAN786422:RAQ786422 RKJ786422:RKM786422 RUF786422:RUI786422 SEB786422:SEE786422 SNX786422:SOA786422 SXT786422:SXW786422 THP786422:THS786422 TRL786422:TRO786422 UBH786422:UBK786422 ULD786422:ULG786422 UUZ786422:UVC786422 VEV786422:VEY786422 VOR786422:VOU786422 VYN786422:VYQ786422 WIJ786422:WIM786422 WSF786422:WSI786422 FT851958:FW851958 PP851958:PS851958 ZL851958:ZO851958 AJH851958:AJK851958 ATD851958:ATG851958 BCZ851958:BDC851958 BMV851958:BMY851958 BWR851958:BWU851958 CGN851958:CGQ851958 CQJ851958:CQM851958 DAF851958:DAI851958 DKB851958:DKE851958 DTX851958:DUA851958 EDT851958:EDW851958 ENP851958:ENS851958 EXL851958:EXO851958 FHH851958:FHK851958 FRD851958:FRG851958 GAZ851958:GBC851958 GKV851958:GKY851958 GUR851958:GUU851958 HEN851958:HEQ851958 HOJ851958:HOM851958 HYF851958:HYI851958 IIB851958:IIE851958 IRX851958:ISA851958 JBT851958:JBW851958 JLP851958:JLS851958 JVL851958:JVO851958 KFH851958:KFK851958 KPD851958:KPG851958 KYZ851958:KZC851958 LIV851958:LIY851958 LSR851958:LSU851958 MCN851958:MCQ851958 MMJ851958:MMM851958 MWF851958:MWI851958 NGB851958:NGE851958 NPX851958:NQA851958 NZT851958:NZW851958 OJP851958:OJS851958 OTL851958:OTO851958 PDH851958:PDK851958 PND851958:PNG851958 PWZ851958:PXC851958 QGV851958:QGY851958 QQR851958:QQU851958 RAN851958:RAQ851958 RKJ851958:RKM851958 RUF851958:RUI851958 SEB851958:SEE851958 SNX851958:SOA851958 SXT851958:SXW851958 THP851958:THS851958 TRL851958:TRO851958 UBH851958:UBK851958 ULD851958:ULG851958 UUZ851958:UVC851958 VEV851958:VEY851958 VOR851958:VOU851958 VYN851958:VYQ851958 WIJ851958:WIM851958 WSF851958:WSI851958 FT917494:FW917494 PP917494:PS917494 ZL917494:ZO917494 AJH917494:AJK917494 ATD917494:ATG917494 BCZ917494:BDC917494 BMV917494:BMY917494 BWR917494:BWU917494 CGN917494:CGQ917494 CQJ917494:CQM917494 DAF917494:DAI917494 DKB917494:DKE917494 DTX917494:DUA917494 EDT917494:EDW917494 ENP917494:ENS917494 EXL917494:EXO917494 FHH917494:FHK917494 FRD917494:FRG917494 GAZ917494:GBC917494 GKV917494:GKY917494 GUR917494:GUU917494 HEN917494:HEQ917494 HOJ917494:HOM917494 HYF917494:HYI917494 IIB917494:IIE917494 IRX917494:ISA917494 JBT917494:JBW917494 JLP917494:JLS917494 JVL917494:JVO917494 KFH917494:KFK917494 KPD917494:KPG917494 KYZ917494:KZC917494 LIV917494:LIY917494 LSR917494:LSU917494 MCN917494:MCQ917494 MMJ917494:MMM917494 MWF917494:MWI917494 NGB917494:NGE917494 NPX917494:NQA917494 NZT917494:NZW917494 OJP917494:OJS917494 OTL917494:OTO917494 PDH917494:PDK917494 PND917494:PNG917494 PWZ917494:PXC917494 QGV917494:QGY917494 QQR917494:QQU917494 RAN917494:RAQ917494 RKJ917494:RKM917494 RUF917494:RUI917494 SEB917494:SEE917494 SNX917494:SOA917494 SXT917494:SXW917494 THP917494:THS917494 TRL917494:TRO917494 UBH917494:UBK917494 ULD917494:ULG917494 UUZ917494:UVC917494 VEV917494:VEY917494 VOR917494:VOU917494 VYN917494:VYQ917494 WIJ917494:WIM917494 WSF917494:WSI917494 FT983030:FW983030 PP983030:PS983030 ZL983030:ZO983030 AJH983030:AJK983030 ATD983030:ATG983030 BCZ983030:BDC983030 BMV983030:BMY983030 BWR983030:BWU983030 CGN983030:CGQ983030 CQJ983030:CQM983030 DAF983030:DAI983030 DKB983030:DKE983030 DTX983030:DUA983030 EDT983030:EDW983030 ENP983030:ENS983030 EXL983030:EXO983030 FHH983030:FHK983030 FRD983030:FRG983030 GAZ983030:GBC983030 GKV983030:GKY983030 GUR983030:GUU983030 HEN983030:HEQ983030 HOJ983030:HOM983030 HYF983030:HYI983030 IIB983030:IIE983030 IRX983030:ISA983030 JBT983030:JBW983030 JLP983030:JLS983030 JVL983030:JVO983030 KFH983030:KFK983030 KPD983030:KPG983030 KYZ983030:KZC983030 LIV983030:LIY983030 LSR983030:LSU983030 MCN983030:MCQ983030 MMJ983030:MMM983030 MWF983030:MWI983030 NGB983030:NGE983030 NPX983030:NQA983030 NZT983030:NZW983030 OJP983030:OJS983030 OTL983030:OTO983030 PDH983030:PDK983030 PND983030:PNG983030 PWZ983030:PXC983030 QGV983030:QGY983030 QQR983030:QQU983030 RAN983030:RAQ983030 RKJ983030:RKM983030 RUF983030:RUI983030 SEB983030:SEE983030 SNX983030:SOA983030 SXT983030:SXW983030 THP983030:THS983030 TRL983030:TRO983030 UBH983030:UBK983030 ULD983030:ULG983030 UUZ983030:UVC983030 VEV983030:VEY983030 VOR983030:VOU983030 VYN983030:VYQ983030 WIJ983030:WIM983030 WSF983030:WSI983030 FO983029:FR983029 PK983029:PN983029 ZG983029:ZJ983029 AJC983029:AJF983029 ASY983029:ATB983029 BCU983029:BCX983029 BMQ983029:BMT983029 BWM983029:BWP983029 CGI983029:CGL983029 CQE983029:CQH983029 DAA983029:DAD983029 DJW983029:DJZ983029 DTS983029:DTV983029 EDO983029:EDR983029 ENK983029:ENN983029 EXG983029:EXJ983029 FHC983029:FHF983029 FQY983029:FRB983029 GAU983029:GAX983029 GKQ983029:GKT983029 GUM983029:GUP983029 HEI983029:HEL983029 HOE983029:HOH983029 HYA983029:HYD983029 IHW983029:IHZ983029 IRS983029:IRV983029 JBO983029:JBR983029 JLK983029:JLN983029 JVG983029:JVJ983029 KFC983029:KFF983029 KOY983029:KPB983029 KYU983029:KYX983029 LIQ983029:LIT983029 LSM983029:LSP983029 MCI983029:MCL983029 MME983029:MMH983029 MWA983029:MWD983029 NFW983029:NFZ983029 NPS983029:NPV983029 NZO983029:NZR983029 OJK983029:OJN983029 OTG983029:OTJ983029 PDC983029:PDF983029 PMY983029:PNB983029 PWU983029:PWX983029 QGQ983029:QGT983029 QQM983029:QQP983029 RAI983029:RAL983029 RKE983029:RKH983029 RUA983029:RUD983029 SDW983029:SDZ983029 SNS983029:SNV983029 SXO983029:SXR983029 THK983029:THN983029 TRG983029:TRJ983029 UBC983029:UBF983029 UKY983029:ULB983029 UUU983029:UUX983029 VEQ983029:VET983029 VOM983029:VOP983029 VYI983029:VYL983029 WIE983029:WIH983029 WSA983029:WSD983029 FO65525:FR65525 PK65525:PN65525 ZG65525:ZJ65525 AJC65525:AJF65525 ASY65525:ATB65525 BCU65525:BCX65525 BMQ65525:BMT65525 BWM65525:BWP65525 CGI65525:CGL65525 CQE65525:CQH65525 DAA65525:DAD65525 DJW65525:DJZ65525 DTS65525:DTV65525 EDO65525:EDR65525 ENK65525:ENN65525 EXG65525:EXJ65525 FHC65525:FHF65525 FQY65525:FRB65525 GAU65525:GAX65525 GKQ65525:GKT65525 GUM65525:GUP65525 HEI65525:HEL65525 HOE65525:HOH65525 HYA65525:HYD65525 IHW65525:IHZ65525 IRS65525:IRV65525 JBO65525:JBR65525 JLK65525:JLN65525 JVG65525:JVJ65525 KFC65525:KFF65525 KOY65525:KPB65525 KYU65525:KYX65525 LIQ65525:LIT65525 LSM65525:LSP65525 MCI65525:MCL65525 MME65525:MMH65525 MWA65525:MWD65525 NFW65525:NFZ65525 NPS65525:NPV65525 NZO65525:NZR65525 OJK65525:OJN65525 OTG65525:OTJ65525 PDC65525:PDF65525 PMY65525:PNB65525 PWU65525:PWX65525 QGQ65525:QGT65525 QQM65525:QQP65525 RAI65525:RAL65525 RKE65525:RKH65525 RUA65525:RUD65525 SDW65525:SDZ65525 SNS65525:SNV65525 SXO65525:SXR65525 THK65525:THN65525 TRG65525:TRJ65525 UBC65525:UBF65525 UKY65525:ULB65525 UUU65525:UUX65525 VEQ65525:VET65525 VOM65525:VOP65525 VYI65525:VYL65525 WIE65525:WIH65525 WSA65525:WSD65525 FO131061:FR131061 PK131061:PN131061 ZG131061:ZJ131061 AJC131061:AJF131061 ASY131061:ATB131061 BCU131061:BCX131061 BMQ131061:BMT131061 BWM131061:BWP131061 CGI131061:CGL131061 CQE131061:CQH131061 DAA131061:DAD131061 DJW131061:DJZ131061 DTS131061:DTV131061 EDO131061:EDR131061 ENK131061:ENN131061 EXG131061:EXJ131061 FHC131061:FHF131061 FQY131061:FRB131061 GAU131061:GAX131061 GKQ131061:GKT131061 GUM131061:GUP131061 HEI131061:HEL131061 HOE131061:HOH131061 HYA131061:HYD131061 IHW131061:IHZ131061 IRS131061:IRV131061 JBO131061:JBR131061 JLK131061:JLN131061 JVG131061:JVJ131061 KFC131061:KFF131061 KOY131061:KPB131061 KYU131061:KYX131061 LIQ131061:LIT131061 LSM131061:LSP131061 MCI131061:MCL131061 MME131061:MMH131061 MWA131061:MWD131061 NFW131061:NFZ131061 NPS131061:NPV131061 NZO131061:NZR131061 OJK131061:OJN131061 OTG131061:OTJ131061 PDC131061:PDF131061 PMY131061:PNB131061 PWU131061:PWX131061 QGQ131061:QGT131061 QQM131061:QQP131061 RAI131061:RAL131061 RKE131061:RKH131061 RUA131061:RUD131061 SDW131061:SDZ131061 SNS131061:SNV131061 SXO131061:SXR131061 THK131061:THN131061 TRG131061:TRJ131061 UBC131061:UBF131061 UKY131061:ULB131061 UUU131061:UUX131061 VEQ131061:VET131061 VOM131061:VOP131061 VYI131061:VYL131061 WIE131061:WIH131061 WSA131061:WSD131061 FO196597:FR196597 PK196597:PN196597 ZG196597:ZJ196597 AJC196597:AJF196597 ASY196597:ATB196597 BCU196597:BCX196597 BMQ196597:BMT196597 BWM196597:BWP196597 CGI196597:CGL196597 CQE196597:CQH196597 DAA196597:DAD196597 DJW196597:DJZ196597 DTS196597:DTV196597 EDO196597:EDR196597 ENK196597:ENN196597 EXG196597:EXJ196597 FHC196597:FHF196597 FQY196597:FRB196597 GAU196597:GAX196597 GKQ196597:GKT196597 GUM196597:GUP196597 HEI196597:HEL196597 HOE196597:HOH196597 HYA196597:HYD196597 IHW196597:IHZ196597 IRS196597:IRV196597 JBO196597:JBR196597 JLK196597:JLN196597 JVG196597:JVJ196597 KFC196597:KFF196597 KOY196597:KPB196597 KYU196597:KYX196597 LIQ196597:LIT196597 LSM196597:LSP196597 MCI196597:MCL196597 MME196597:MMH196597 MWA196597:MWD196597 NFW196597:NFZ196597 NPS196597:NPV196597 NZO196597:NZR196597 OJK196597:OJN196597 OTG196597:OTJ196597 PDC196597:PDF196597 PMY196597:PNB196597 PWU196597:PWX196597 QGQ196597:QGT196597 QQM196597:QQP196597 RAI196597:RAL196597 RKE196597:RKH196597 RUA196597:RUD196597 SDW196597:SDZ196597 SNS196597:SNV196597 SXO196597:SXR196597 THK196597:THN196597 TRG196597:TRJ196597 UBC196597:UBF196597 UKY196597:ULB196597 UUU196597:UUX196597 VEQ196597:VET196597 VOM196597:VOP196597 VYI196597:VYL196597 WIE196597:WIH196597 WSA196597:WSD196597 FO262133:FR262133 PK262133:PN262133 ZG262133:ZJ262133 AJC262133:AJF262133 ASY262133:ATB262133 BCU262133:BCX262133 BMQ262133:BMT262133 BWM262133:BWP262133 CGI262133:CGL262133 CQE262133:CQH262133 DAA262133:DAD262133 DJW262133:DJZ262133 DTS262133:DTV262133 EDO262133:EDR262133 ENK262133:ENN262133 EXG262133:EXJ262133 FHC262133:FHF262133 FQY262133:FRB262133 GAU262133:GAX262133 GKQ262133:GKT262133 GUM262133:GUP262133 HEI262133:HEL262133 HOE262133:HOH262133 HYA262133:HYD262133 IHW262133:IHZ262133 IRS262133:IRV262133 JBO262133:JBR262133 JLK262133:JLN262133 JVG262133:JVJ262133 KFC262133:KFF262133 KOY262133:KPB262133 KYU262133:KYX262133 LIQ262133:LIT262133 LSM262133:LSP262133 MCI262133:MCL262133 MME262133:MMH262133 MWA262133:MWD262133 NFW262133:NFZ262133 NPS262133:NPV262133 NZO262133:NZR262133 OJK262133:OJN262133 OTG262133:OTJ262133 PDC262133:PDF262133 PMY262133:PNB262133 PWU262133:PWX262133 QGQ262133:QGT262133 QQM262133:QQP262133 RAI262133:RAL262133 RKE262133:RKH262133 RUA262133:RUD262133 SDW262133:SDZ262133 SNS262133:SNV262133 SXO262133:SXR262133 THK262133:THN262133 TRG262133:TRJ262133 UBC262133:UBF262133 UKY262133:ULB262133 UUU262133:UUX262133 VEQ262133:VET262133 VOM262133:VOP262133 VYI262133:VYL262133 WIE262133:WIH262133 WSA262133:WSD262133 FO327669:FR327669 PK327669:PN327669 ZG327669:ZJ327669 AJC327669:AJF327669 ASY327669:ATB327669 BCU327669:BCX327669 BMQ327669:BMT327669 BWM327669:BWP327669 CGI327669:CGL327669 CQE327669:CQH327669 DAA327669:DAD327669 DJW327669:DJZ327669 DTS327669:DTV327669 EDO327669:EDR327669 ENK327669:ENN327669 EXG327669:EXJ327669 FHC327669:FHF327669 FQY327669:FRB327669 GAU327669:GAX327669 GKQ327669:GKT327669 GUM327669:GUP327669 HEI327669:HEL327669 HOE327669:HOH327669 HYA327669:HYD327669 IHW327669:IHZ327669 IRS327669:IRV327669 JBO327669:JBR327669 JLK327669:JLN327669 JVG327669:JVJ327669 KFC327669:KFF327669 KOY327669:KPB327669 KYU327669:KYX327669 LIQ327669:LIT327669 LSM327669:LSP327669 MCI327669:MCL327669 MME327669:MMH327669 MWA327669:MWD327669 NFW327669:NFZ327669 NPS327669:NPV327669 NZO327669:NZR327669 OJK327669:OJN327669 OTG327669:OTJ327669 PDC327669:PDF327669 PMY327669:PNB327669 PWU327669:PWX327669 QGQ327669:QGT327669 QQM327669:QQP327669 RAI327669:RAL327669 RKE327669:RKH327669 RUA327669:RUD327669 SDW327669:SDZ327669 SNS327669:SNV327669 SXO327669:SXR327669 THK327669:THN327669 TRG327669:TRJ327669 UBC327669:UBF327669 UKY327669:ULB327669 UUU327669:UUX327669 VEQ327669:VET327669 VOM327669:VOP327669 VYI327669:VYL327669 WIE327669:WIH327669 WSA327669:WSD327669 FO393205:FR393205 PK393205:PN393205 ZG393205:ZJ393205 AJC393205:AJF393205 ASY393205:ATB393205 BCU393205:BCX393205 BMQ393205:BMT393205 BWM393205:BWP393205 CGI393205:CGL393205 CQE393205:CQH393205 DAA393205:DAD393205 DJW393205:DJZ393205 DTS393205:DTV393205 EDO393205:EDR393205 ENK393205:ENN393205 EXG393205:EXJ393205 FHC393205:FHF393205 FQY393205:FRB393205 GAU393205:GAX393205 GKQ393205:GKT393205 GUM393205:GUP393205 HEI393205:HEL393205 HOE393205:HOH393205 HYA393205:HYD393205 IHW393205:IHZ393205 IRS393205:IRV393205 JBO393205:JBR393205 JLK393205:JLN393205 JVG393205:JVJ393205 KFC393205:KFF393205 KOY393205:KPB393205 KYU393205:KYX393205 LIQ393205:LIT393205 LSM393205:LSP393205 MCI393205:MCL393205 MME393205:MMH393205 MWA393205:MWD393205 NFW393205:NFZ393205 NPS393205:NPV393205 NZO393205:NZR393205 OJK393205:OJN393205 OTG393205:OTJ393205 PDC393205:PDF393205 PMY393205:PNB393205 PWU393205:PWX393205 QGQ393205:QGT393205 QQM393205:QQP393205 RAI393205:RAL393205 RKE393205:RKH393205 RUA393205:RUD393205 SDW393205:SDZ393205 SNS393205:SNV393205 SXO393205:SXR393205 THK393205:THN393205 TRG393205:TRJ393205 UBC393205:UBF393205 UKY393205:ULB393205 UUU393205:UUX393205 VEQ393205:VET393205 VOM393205:VOP393205 VYI393205:VYL393205 WIE393205:WIH393205 WSA393205:WSD393205 FO458741:FR458741 PK458741:PN458741 ZG458741:ZJ458741 AJC458741:AJF458741 ASY458741:ATB458741 BCU458741:BCX458741 BMQ458741:BMT458741 BWM458741:BWP458741 CGI458741:CGL458741 CQE458741:CQH458741 DAA458741:DAD458741 DJW458741:DJZ458741 DTS458741:DTV458741 EDO458741:EDR458741 ENK458741:ENN458741 EXG458741:EXJ458741 FHC458741:FHF458741 FQY458741:FRB458741 GAU458741:GAX458741 GKQ458741:GKT458741 GUM458741:GUP458741 HEI458741:HEL458741 HOE458741:HOH458741 HYA458741:HYD458741 IHW458741:IHZ458741 IRS458741:IRV458741 JBO458741:JBR458741 JLK458741:JLN458741 JVG458741:JVJ458741 KFC458741:KFF458741 KOY458741:KPB458741 KYU458741:KYX458741 LIQ458741:LIT458741 LSM458741:LSP458741 MCI458741:MCL458741 MME458741:MMH458741 MWA458741:MWD458741 NFW458741:NFZ458741 NPS458741:NPV458741 NZO458741:NZR458741 OJK458741:OJN458741 OTG458741:OTJ458741 PDC458741:PDF458741 PMY458741:PNB458741 PWU458741:PWX458741 QGQ458741:QGT458741 QQM458741:QQP458741 RAI458741:RAL458741 RKE458741:RKH458741 RUA458741:RUD458741 SDW458741:SDZ458741 SNS458741:SNV458741 SXO458741:SXR458741 THK458741:THN458741 TRG458741:TRJ458741 UBC458741:UBF458741 UKY458741:ULB458741 UUU458741:UUX458741 VEQ458741:VET458741 VOM458741:VOP458741 VYI458741:VYL458741 WIE458741:WIH458741 WSA458741:WSD458741 FO524277:FR524277 PK524277:PN524277 ZG524277:ZJ524277 AJC524277:AJF524277 ASY524277:ATB524277 BCU524277:BCX524277 BMQ524277:BMT524277 BWM524277:BWP524277 CGI524277:CGL524277 CQE524277:CQH524277 DAA524277:DAD524277 DJW524277:DJZ524277 DTS524277:DTV524277 EDO524277:EDR524277 ENK524277:ENN524277 EXG524277:EXJ524277 FHC524277:FHF524277 FQY524277:FRB524277 GAU524277:GAX524277 GKQ524277:GKT524277 GUM524277:GUP524277 HEI524277:HEL524277 HOE524277:HOH524277 HYA524277:HYD524277 IHW524277:IHZ524277 IRS524277:IRV524277 JBO524277:JBR524277 JLK524277:JLN524277 JVG524277:JVJ524277 KFC524277:KFF524277 KOY524277:KPB524277 KYU524277:KYX524277 LIQ524277:LIT524277 LSM524277:LSP524277 MCI524277:MCL524277 MME524277:MMH524277 MWA524277:MWD524277 NFW524277:NFZ524277 NPS524277:NPV524277 NZO524277:NZR524277 OJK524277:OJN524277 OTG524277:OTJ524277 PDC524277:PDF524277 PMY524277:PNB524277 PWU524277:PWX524277 QGQ524277:QGT524277 QQM524277:QQP524277 RAI524277:RAL524277 RKE524277:RKH524277 RUA524277:RUD524277 SDW524277:SDZ524277 SNS524277:SNV524277 SXO524277:SXR524277 THK524277:THN524277 TRG524277:TRJ524277 UBC524277:UBF524277 UKY524277:ULB524277 UUU524277:UUX524277 VEQ524277:VET524277 VOM524277:VOP524277 VYI524277:VYL524277 WIE524277:WIH524277 WSA524277:WSD524277 FO589813:FR589813 PK589813:PN589813 ZG589813:ZJ589813 AJC589813:AJF589813 ASY589813:ATB589813 BCU589813:BCX589813 BMQ589813:BMT589813 BWM589813:BWP589813 CGI589813:CGL589813 CQE589813:CQH589813 DAA589813:DAD589813 DJW589813:DJZ589813 DTS589813:DTV589813 EDO589813:EDR589813 ENK589813:ENN589813 EXG589813:EXJ589813 FHC589813:FHF589813 FQY589813:FRB589813 GAU589813:GAX589813 GKQ589813:GKT589813 GUM589813:GUP589813 HEI589813:HEL589813 HOE589813:HOH589813 HYA589813:HYD589813 IHW589813:IHZ589813 IRS589813:IRV589813 JBO589813:JBR589813 JLK589813:JLN589813 JVG589813:JVJ589813 KFC589813:KFF589813 KOY589813:KPB589813 KYU589813:KYX589813 LIQ589813:LIT589813 LSM589813:LSP589813 MCI589813:MCL589813 MME589813:MMH589813 MWA589813:MWD589813 NFW589813:NFZ589813 NPS589813:NPV589813 NZO589813:NZR589813 OJK589813:OJN589813 OTG589813:OTJ589813 PDC589813:PDF589813 PMY589813:PNB589813 PWU589813:PWX589813 QGQ589813:QGT589813 QQM589813:QQP589813 RAI589813:RAL589813 RKE589813:RKH589813 RUA589813:RUD589813 SDW589813:SDZ589813 SNS589813:SNV589813 SXO589813:SXR589813 THK589813:THN589813 TRG589813:TRJ589813 UBC589813:UBF589813 UKY589813:ULB589813 UUU589813:UUX589813 VEQ589813:VET589813 VOM589813:VOP589813 VYI589813:VYL589813 WIE589813:WIH589813 WSA589813:WSD589813 FO655349:FR655349 PK655349:PN655349 ZG655349:ZJ655349 AJC655349:AJF655349 ASY655349:ATB655349 BCU655349:BCX655349 BMQ655349:BMT655349 BWM655349:BWP655349 CGI655349:CGL655349 CQE655349:CQH655349 DAA655349:DAD655349 DJW655349:DJZ655349 DTS655349:DTV655349 EDO655349:EDR655349 ENK655349:ENN655349 EXG655349:EXJ655349 FHC655349:FHF655349 FQY655349:FRB655349 GAU655349:GAX655349 GKQ655349:GKT655349 GUM655349:GUP655349 HEI655349:HEL655349 HOE655349:HOH655349 HYA655349:HYD655349 IHW655349:IHZ655349 IRS655349:IRV655349 JBO655349:JBR655349 JLK655349:JLN655349 JVG655349:JVJ655349 KFC655349:KFF655349 KOY655349:KPB655349 KYU655349:KYX655349 LIQ655349:LIT655349 LSM655349:LSP655349 MCI655349:MCL655349 MME655349:MMH655349 MWA655349:MWD655349 NFW655349:NFZ655349 NPS655349:NPV655349 NZO655349:NZR655349 OJK655349:OJN655349 OTG655349:OTJ655349 PDC655349:PDF655349 PMY655349:PNB655349 PWU655349:PWX655349 QGQ655349:QGT655349 QQM655349:QQP655349 RAI655349:RAL655349 RKE655349:RKH655349 RUA655349:RUD655349 SDW655349:SDZ655349 SNS655349:SNV655349 SXO655349:SXR655349 THK655349:THN655349 TRG655349:TRJ655349 UBC655349:UBF655349 UKY655349:ULB655349 UUU655349:UUX655349 VEQ655349:VET655349 VOM655349:VOP655349 VYI655349:VYL655349 WIE655349:WIH655349 WSA655349:WSD655349 FO720885:FR720885 PK720885:PN720885 ZG720885:ZJ720885 AJC720885:AJF720885 ASY720885:ATB720885 BCU720885:BCX720885 BMQ720885:BMT720885 BWM720885:BWP720885 CGI720885:CGL720885 CQE720885:CQH720885 DAA720885:DAD720885 DJW720885:DJZ720885 DTS720885:DTV720885 EDO720885:EDR720885 ENK720885:ENN720885 EXG720885:EXJ720885 FHC720885:FHF720885 FQY720885:FRB720885 GAU720885:GAX720885 GKQ720885:GKT720885 GUM720885:GUP720885 HEI720885:HEL720885 HOE720885:HOH720885 HYA720885:HYD720885 IHW720885:IHZ720885 IRS720885:IRV720885 JBO720885:JBR720885 JLK720885:JLN720885 JVG720885:JVJ720885 KFC720885:KFF720885 KOY720885:KPB720885 KYU720885:KYX720885 LIQ720885:LIT720885 LSM720885:LSP720885 MCI720885:MCL720885 MME720885:MMH720885 MWA720885:MWD720885 NFW720885:NFZ720885 NPS720885:NPV720885 NZO720885:NZR720885 OJK720885:OJN720885 OTG720885:OTJ720885 PDC720885:PDF720885 PMY720885:PNB720885 PWU720885:PWX720885 QGQ720885:QGT720885 QQM720885:QQP720885 RAI720885:RAL720885 RKE720885:RKH720885 RUA720885:RUD720885 SDW720885:SDZ720885 SNS720885:SNV720885 SXO720885:SXR720885 THK720885:THN720885 TRG720885:TRJ720885 UBC720885:UBF720885 UKY720885:ULB720885 UUU720885:UUX720885 VEQ720885:VET720885 VOM720885:VOP720885 VYI720885:VYL720885 WIE720885:WIH720885 WSA720885:WSD720885 FO786421:FR786421 PK786421:PN786421 ZG786421:ZJ786421 AJC786421:AJF786421 ASY786421:ATB786421 BCU786421:BCX786421 BMQ786421:BMT786421 BWM786421:BWP786421 CGI786421:CGL786421 CQE786421:CQH786421 DAA786421:DAD786421 DJW786421:DJZ786421 DTS786421:DTV786421 EDO786421:EDR786421 ENK786421:ENN786421 EXG786421:EXJ786421 FHC786421:FHF786421 FQY786421:FRB786421 GAU786421:GAX786421 GKQ786421:GKT786421 GUM786421:GUP786421 HEI786421:HEL786421 HOE786421:HOH786421 HYA786421:HYD786421 IHW786421:IHZ786421 IRS786421:IRV786421 JBO786421:JBR786421 JLK786421:JLN786421 JVG786421:JVJ786421 KFC786421:KFF786421 KOY786421:KPB786421 KYU786421:KYX786421 LIQ786421:LIT786421 LSM786421:LSP786421 MCI786421:MCL786421 MME786421:MMH786421 MWA786421:MWD786421 NFW786421:NFZ786421 NPS786421:NPV786421 NZO786421:NZR786421 OJK786421:OJN786421 OTG786421:OTJ786421 PDC786421:PDF786421 PMY786421:PNB786421 PWU786421:PWX786421 QGQ786421:QGT786421 QQM786421:QQP786421 RAI786421:RAL786421 RKE786421:RKH786421 RUA786421:RUD786421 SDW786421:SDZ786421 SNS786421:SNV786421 SXO786421:SXR786421 THK786421:THN786421 TRG786421:TRJ786421 UBC786421:UBF786421 UKY786421:ULB786421 UUU786421:UUX786421 VEQ786421:VET786421 VOM786421:VOP786421 VYI786421:VYL786421 WIE786421:WIH786421 WSA786421:WSD786421 FO851957:FR851957 PK851957:PN851957 ZG851957:ZJ851957 AJC851957:AJF851957 ASY851957:ATB851957 BCU851957:BCX851957 BMQ851957:BMT851957 BWM851957:BWP851957 CGI851957:CGL851957 CQE851957:CQH851957 DAA851957:DAD851957 DJW851957:DJZ851957 DTS851957:DTV851957 EDO851957:EDR851957 ENK851957:ENN851957 EXG851957:EXJ851957 FHC851957:FHF851957 FQY851957:FRB851957 GAU851957:GAX851957 GKQ851957:GKT851957 GUM851957:GUP851957 HEI851957:HEL851957 HOE851957:HOH851957 HYA851957:HYD851957 IHW851957:IHZ851957 IRS851957:IRV851957 JBO851957:JBR851957 JLK851957:JLN851957 JVG851957:JVJ851957 KFC851957:KFF851957 KOY851957:KPB851957 KYU851957:KYX851957 LIQ851957:LIT851957 LSM851957:LSP851957 MCI851957:MCL851957 MME851957:MMH851957 MWA851957:MWD851957 NFW851957:NFZ851957 NPS851957:NPV851957 NZO851957:NZR851957 OJK851957:OJN851957 OTG851957:OTJ851957 PDC851957:PDF851957 PMY851957:PNB851957 PWU851957:PWX851957 QGQ851957:QGT851957 QQM851957:QQP851957 RAI851957:RAL851957 RKE851957:RKH851957 RUA851957:RUD851957 SDW851957:SDZ851957 SNS851957:SNV851957 SXO851957:SXR851957 THK851957:THN851957 TRG851957:TRJ851957 UBC851957:UBF851957 UKY851957:ULB851957 UUU851957:UUX851957 VEQ851957:VET851957 VOM851957:VOP851957 VYI851957:VYL851957 WIE851957:WIH851957 WSA851957:WSD851957 FO917493:FR917493 PK917493:PN917493 ZG917493:ZJ917493 AJC917493:AJF917493 ASY917493:ATB917493 BCU917493:BCX917493 BMQ917493:BMT917493 BWM917493:BWP917493 CGI917493:CGL917493 CQE917493:CQH917493 DAA917493:DAD917493 DJW917493:DJZ917493 DTS917493:DTV917493 EDO917493:EDR917493 ENK917493:ENN917493 EXG917493:EXJ917493 FHC917493:FHF917493 FQY917493:FRB917493 GAU917493:GAX917493 GKQ917493:GKT917493 GUM917493:GUP917493 HEI917493:HEL917493 HOE917493:HOH917493 HYA917493:HYD917493 IHW917493:IHZ917493 IRS917493:IRV917493 JBO917493:JBR917493 JLK917493:JLN917493 JVG917493:JVJ917493 KFC917493:KFF917493 KOY917493:KPB917493 KYU917493:KYX917493 LIQ917493:LIT917493 LSM917493:LSP917493 MCI917493:MCL917493 MME917493:MMH917493 MWA917493:MWD917493 NFW917493:NFZ917493 NPS917493:NPV917493 NZO917493:NZR917493 OJK917493:OJN917493 OTG917493:OTJ917493 PDC917493:PDF917493 PMY917493:PNB917493 PWU917493:PWX917493 QGQ917493:QGT917493 QQM917493:QQP917493 RAI917493:RAL917493 RKE917493:RKH917493 RUA917493:RUD917493 SDW917493:SDZ917493 SNS917493:SNV917493 SXO917493:SXR917493 THK917493:THN917493 TRG917493:TRJ917493 UBC917493:UBF917493 UKY917493:ULB917493 UUU917493:UUX917493 VEQ917493:VET917493 VOM917493:VOP917493 VYI917493:VYL917493 WIE917493:WIH917493 WSA917493:WSD917493" xr:uid="{21369424-5F25-4207-AE77-270DAFEFE719}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT65520:FW65520 PP65520:PS65520 ZL65520:ZO65520 AJH65520:AJK65520 ATD65520:ATG65520 BCZ65520:BDC65520 BMV65520:BMY65520 BWR65520:BWU65520 CGN65520:CGQ65520 CQJ65520:CQM65520 DAF65520:DAI65520 DKB65520:DKE65520 DTX65520:DUA65520 EDT65520:EDW65520 ENP65520:ENS65520 EXL65520:EXO65520 FHH65520:FHK65520 FRD65520:FRG65520 GAZ65520:GBC65520 GKV65520:GKY65520 GUR65520:GUU65520 HEN65520:HEQ65520 HOJ65520:HOM65520 HYF65520:HYI65520 IIB65520:IIE65520 IRX65520:ISA65520 JBT65520:JBW65520 JLP65520:JLS65520 JVL65520:JVO65520 KFH65520:KFK65520 KPD65520:KPG65520 KYZ65520:KZC65520 LIV65520:LIY65520 LSR65520:LSU65520 MCN65520:MCQ65520 MMJ65520:MMM65520 MWF65520:MWI65520 NGB65520:NGE65520 NPX65520:NQA65520 NZT65520:NZW65520 OJP65520:OJS65520 OTL65520:OTO65520 PDH65520:PDK65520 PND65520:PNG65520 PWZ65520:PXC65520 QGV65520:QGY65520 QQR65520:QQU65520 RAN65520:RAQ65520 RKJ65520:RKM65520 RUF65520:RUI65520 SEB65520:SEE65520 SNX65520:SOA65520 SXT65520:SXW65520 THP65520:THS65520 TRL65520:TRO65520 UBH65520:UBK65520 ULD65520:ULG65520 UUZ65520:UVC65520 VEV65520:VEY65520 VOR65520:VOU65520 VYN65520:VYQ65520 WIJ65520:WIM65520 WSF65520:WSI65520 FT131056:FW131056 PP131056:PS131056 ZL131056:ZO131056 AJH131056:AJK131056 ATD131056:ATG131056 BCZ131056:BDC131056 BMV131056:BMY131056 BWR131056:BWU131056 CGN131056:CGQ131056 CQJ131056:CQM131056 DAF131056:DAI131056 DKB131056:DKE131056 DTX131056:DUA131056 EDT131056:EDW131056 ENP131056:ENS131056 EXL131056:EXO131056 FHH131056:FHK131056 FRD131056:FRG131056 GAZ131056:GBC131056 GKV131056:GKY131056 GUR131056:GUU131056 HEN131056:HEQ131056 HOJ131056:HOM131056 HYF131056:HYI131056 IIB131056:IIE131056 IRX131056:ISA131056 JBT131056:JBW131056 JLP131056:JLS131056 JVL131056:JVO131056 KFH131056:KFK131056 KPD131056:KPG131056 KYZ131056:KZC131056 LIV131056:LIY131056 LSR131056:LSU131056 MCN131056:MCQ131056 MMJ131056:MMM131056 MWF131056:MWI131056 NGB131056:NGE131056 NPX131056:NQA131056 NZT131056:NZW131056 OJP131056:OJS131056 OTL131056:OTO131056 PDH131056:PDK131056 PND131056:PNG131056 PWZ131056:PXC131056 QGV131056:QGY131056 QQR131056:QQU131056 RAN131056:RAQ131056 RKJ131056:RKM131056 RUF131056:RUI131056 SEB131056:SEE131056 SNX131056:SOA131056 SXT131056:SXW131056 THP131056:THS131056 TRL131056:TRO131056 UBH131056:UBK131056 ULD131056:ULG131056 UUZ131056:UVC131056 VEV131056:VEY131056 VOR131056:VOU131056 VYN131056:VYQ131056 WIJ131056:WIM131056 WSF131056:WSI131056 FT196592:FW196592 PP196592:PS196592 ZL196592:ZO196592 AJH196592:AJK196592 ATD196592:ATG196592 BCZ196592:BDC196592 BMV196592:BMY196592 BWR196592:BWU196592 CGN196592:CGQ196592 CQJ196592:CQM196592 DAF196592:DAI196592 DKB196592:DKE196592 DTX196592:DUA196592 EDT196592:EDW196592 ENP196592:ENS196592 EXL196592:EXO196592 FHH196592:FHK196592 FRD196592:FRG196592 GAZ196592:GBC196592 GKV196592:GKY196592 GUR196592:GUU196592 HEN196592:HEQ196592 HOJ196592:HOM196592 HYF196592:HYI196592 IIB196592:IIE196592 IRX196592:ISA196592 JBT196592:JBW196592 JLP196592:JLS196592 JVL196592:JVO196592 KFH196592:KFK196592 KPD196592:KPG196592 KYZ196592:KZC196592 LIV196592:LIY196592 LSR196592:LSU196592 MCN196592:MCQ196592 MMJ196592:MMM196592 MWF196592:MWI196592 NGB196592:NGE196592 NPX196592:NQA196592 NZT196592:NZW196592 OJP196592:OJS196592 OTL196592:OTO196592 PDH196592:PDK196592 PND196592:PNG196592 PWZ196592:PXC196592 QGV196592:QGY196592 QQR196592:QQU196592 RAN196592:RAQ196592 RKJ196592:RKM196592 RUF196592:RUI196592 SEB196592:SEE196592 SNX196592:SOA196592 SXT196592:SXW196592 THP196592:THS196592 TRL196592:TRO196592 UBH196592:UBK196592 ULD196592:ULG196592 UUZ196592:UVC196592 VEV196592:VEY196592 VOR196592:VOU196592 VYN196592:VYQ196592 WIJ196592:WIM196592 WSF196592:WSI196592 FT262128:FW262128 PP262128:PS262128 ZL262128:ZO262128 AJH262128:AJK262128 ATD262128:ATG262128 BCZ262128:BDC262128 BMV262128:BMY262128 BWR262128:BWU262128 CGN262128:CGQ262128 CQJ262128:CQM262128 DAF262128:DAI262128 DKB262128:DKE262128 DTX262128:DUA262128 EDT262128:EDW262128 ENP262128:ENS262128 EXL262128:EXO262128 FHH262128:FHK262128 FRD262128:FRG262128 GAZ262128:GBC262128 GKV262128:GKY262128 GUR262128:GUU262128 HEN262128:HEQ262128 HOJ262128:HOM262128 HYF262128:HYI262128 IIB262128:IIE262128 IRX262128:ISA262128 JBT262128:JBW262128 JLP262128:JLS262128 JVL262128:JVO262128 KFH262128:KFK262128 KPD262128:KPG262128 KYZ262128:KZC262128 LIV262128:LIY262128 LSR262128:LSU262128 MCN262128:MCQ262128 MMJ262128:MMM262128 MWF262128:MWI262128 NGB262128:NGE262128 NPX262128:NQA262128 NZT262128:NZW262128 OJP262128:OJS262128 OTL262128:OTO262128 PDH262128:PDK262128 PND262128:PNG262128 PWZ262128:PXC262128 QGV262128:QGY262128 QQR262128:QQU262128 RAN262128:RAQ262128 RKJ262128:RKM262128 RUF262128:RUI262128 SEB262128:SEE262128 SNX262128:SOA262128 SXT262128:SXW262128 THP262128:THS262128 TRL262128:TRO262128 UBH262128:UBK262128 ULD262128:ULG262128 UUZ262128:UVC262128 VEV262128:VEY262128 VOR262128:VOU262128 VYN262128:VYQ262128 WIJ262128:WIM262128 WSF262128:WSI262128 FT327664:FW327664 PP327664:PS327664 ZL327664:ZO327664 AJH327664:AJK327664 ATD327664:ATG327664 BCZ327664:BDC327664 BMV327664:BMY327664 BWR327664:BWU327664 CGN327664:CGQ327664 CQJ327664:CQM327664 DAF327664:DAI327664 DKB327664:DKE327664 DTX327664:DUA327664 EDT327664:EDW327664 ENP327664:ENS327664 EXL327664:EXO327664 FHH327664:FHK327664 FRD327664:FRG327664 GAZ327664:GBC327664 GKV327664:GKY327664 GUR327664:GUU327664 HEN327664:HEQ327664 HOJ327664:HOM327664 HYF327664:HYI327664 IIB327664:IIE327664 IRX327664:ISA327664 JBT327664:JBW327664 JLP327664:JLS327664 JVL327664:JVO327664 KFH327664:KFK327664 KPD327664:KPG327664 KYZ327664:KZC327664 LIV327664:LIY327664 LSR327664:LSU327664 MCN327664:MCQ327664 MMJ327664:MMM327664 MWF327664:MWI327664 NGB327664:NGE327664 NPX327664:NQA327664 NZT327664:NZW327664 OJP327664:OJS327664 OTL327664:OTO327664 PDH327664:PDK327664 PND327664:PNG327664 PWZ327664:PXC327664 QGV327664:QGY327664 QQR327664:QQU327664 RAN327664:RAQ327664 RKJ327664:RKM327664 RUF327664:RUI327664 SEB327664:SEE327664 SNX327664:SOA327664 SXT327664:SXW327664 THP327664:THS327664 TRL327664:TRO327664 UBH327664:UBK327664 ULD327664:ULG327664 UUZ327664:UVC327664 VEV327664:VEY327664 VOR327664:VOU327664 VYN327664:VYQ327664 WIJ327664:WIM327664 WSF327664:WSI327664 FT393200:FW393200 PP393200:PS393200 ZL393200:ZO393200 AJH393200:AJK393200 ATD393200:ATG393200 BCZ393200:BDC393200 BMV393200:BMY393200 BWR393200:BWU393200 CGN393200:CGQ393200 CQJ393200:CQM393200 DAF393200:DAI393200 DKB393200:DKE393200 DTX393200:DUA393200 EDT393200:EDW393200 ENP393200:ENS393200 EXL393200:EXO393200 FHH393200:FHK393200 FRD393200:FRG393200 GAZ393200:GBC393200 GKV393200:GKY393200 GUR393200:GUU393200 HEN393200:HEQ393200 HOJ393200:HOM393200 HYF393200:HYI393200 IIB393200:IIE393200 IRX393200:ISA393200 JBT393200:JBW393200 JLP393200:JLS393200 JVL393200:JVO393200 KFH393200:KFK393200 KPD393200:KPG393200 KYZ393200:KZC393200 LIV393200:LIY393200 LSR393200:LSU393200 MCN393200:MCQ393200 MMJ393200:MMM393200 MWF393200:MWI393200 NGB393200:NGE393200 NPX393200:NQA393200 NZT393200:NZW393200 OJP393200:OJS393200 OTL393200:OTO393200 PDH393200:PDK393200 PND393200:PNG393200 PWZ393200:PXC393200 QGV393200:QGY393200 QQR393200:QQU393200 RAN393200:RAQ393200 RKJ393200:RKM393200 RUF393200:RUI393200 SEB393200:SEE393200 SNX393200:SOA393200 SXT393200:SXW393200 THP393200:THS393200 TRL393200:TRO393200 UBH393200:UBK393200 ULD393200:ULG393200 UUZ393200:UVC393200 VEV393200:VEY393200 VOR393200:VOU393200 VYN393200:VYQ393200 WIJ393200:WIM393200 WSF393200:WSI393200 FT458736:FW458736 PP458736:PS458736 ZL458736:ZO458736 AJH458736:AJK458736 ATD458736:ATG458736 BCZ458736:BDC458736 BMV458736:BMY458736 BWR458736:BWU458736 CGN458736:CGQ458736 CQJ458736:CQM458736 DAF458736:DAI458736 DKB458736:DKE458736 DTX458736:DUA458736 EDT458736:EDW458736 ENP458736:ENS458736 EXL458736:EXO458736 FHH458736:FHK458736 FRD458736:FRG458736 GAZ458736:GBC458736 GKV458736:GKY458736 GUR458736:GUU458736 HEN458736:HEQ458736 HOJ458736:HOM458736 HYF458736:HYI458736 IIB458736:IIE458736 IRX458736:ISA458736 JBT458736:JBW458736 JLP458736:JLS458736 JVL458736:JVO458736 KFH458736:KFK458736 KPD458736:KPG458736 KYZ458736:KZC458736 LIV458736:LIY458736 LSR458736:LSU458736 MCN458736:MCQ458736 MMJ458736:MMM458736 MWF458736:MWI458736 NGB458736:NGE458736 NPX458736:NQA458736 NZT458736:NZW458736 OJP458736:OJS458736 OTL458736:OTO458736 PDH458736:PDK458736 PND458736:PNG458736 PWZ458736:PXC458736 QGV458736:QGY458736 QQR458736:QQU458736 RAN458736:RAQ458736 RKJ458736:RKM458736 RUF458736:RUI458736 SEB458736:SEE458736 SNX458736:SOA458736 SXT458736:SXW458736 THP458736:THS458736 TRL458736:TRO458736 UBH458736:UBK458736 ULD458736:ULG458736 UUZ458736:UVC458736 VEV458736:VEY458736 VOR458736:VOU458736 VYN458736:VYQ458736 WIJ458736:WIM458736 WSF458736:WSI458736 FT524272:FW524272 PP524272:PS524272 ZL524272:ZO524272 AJH524272:AJK524272 ATD524272:ATG524272 BCZ524272:BDC524272 BMV524272:BMY524272 BWR524272:BWU524272 CGN524272:CGQ524272 CQJ524272:CQM524272 DAF524272:DAI524272 DKB524272:DKE524272 DTX524272:DUA524272 EDT524272:EDW524272 ENP524272:ENS524272 EXL524272:EXO524272 FHH524272:FHK524272 FRD524272:FRG524272 GAZ524272:GBC524272 GKV524272:GKY524272 GUR524272:GUU524272 HEN524272:HEQ524272 HOJ524272:HOM524272 HYF524272:HYI524272 IIB524272:IIE524272 IRX524272:ISA524272 JBT524272:JBW524272 JLP524272:JLS524272 JVL524272:JVO524272 KFH524272:KFK524272 KPD524272:KPG524272 KYZ524272:KZC524272 LIV524272:LIY524272 LSR524272:LSU524272 MCN524272:MCQ524272 MMJ524272:MMM524272 MWF524272:MWI524272 NGB524272:NGE524272 NPX524272:NQA524272 NZT524272:NZW524272 OJP524272:OJS524272 OTL524272:OTO524272 PDH524272:PDK524272 PND524272:PNG524272 PWZ524272:PXC524272 QGV524272:QGY524272 QQR524272:QQU524272 RAN524272:RAQ524272 RKJ524272:RKM524272 RUF524272:RUI524272 SEB524272:SEE524272 SNX524272:SOA524272 SXT524272:SXW524272 THP524272:THS524272 TRL524272:TRO524272 UBH524272:UBK524272 ULD524272:ULG524272 UUZ524272:UVC524272 VEV524272:VEY524272 VOR524272:VOU524272 VYN524272:VYQ524272 WIJ524272:WIM524272 WSF524272:WSI524272 FT589808:FW589808 PP589808:PS589808 ZL589808:ZO589808 AJH589808:AJK589808 ATD589808:ATG589808 BCZ589808:BDC589808 BMV589808:BMY589808 BWR589808:BWU589808 CGN589808:CGQ589808 CQJ589808:CQM589808 DAF589808:DAI589808 DKB589808:DKE589808 DTX589808:DUA589808 EDT589808:EDW589808 ENP589808:ENS589808 EXL589808:EXO589808 FHH589808:FHK589808 FRD589808:FRG589808 GAZ589808:GBC589808 GKV589808:GKY589808 GUR589808:GUU589808 HEN589808:HEQ589808 HOJ589808:HOM589808 HYF589808:HYI589808 IIB589808:IIE589808 IRX589808:ISA589808 JBT589808:JBW589808 JLP589808:JLS589808 JVL589808:JVO589808 KFH589808:KFK589808 KPD589808:KPG589808 KYZ589808:KZC589808 LIV589808:LIY589808 LSR589808:LSU589808 MCN589808:MCQ589808 MMJ589808:MMM589808 MWF589808:MWI589808 NGB589808:NGE589808 NPX589808:NQA589808 NZT589808:NZW589808 OJP589808:OJS589808 OTL589808:OTO589808 PDH589808:PDK589808 PND589808:PNG589808 PWZ589808:PXC589808 QGV589808:QGY589808 QQR589808:QQU589808 RAN589808:RAQ589808 RKJ589808:RKM589808 RUF589808:RUI589808 SEB589808:SEE589808 SNX589808:SOA589808 SXT589808:SXW589808 THP589808:THS589808 TRL589808:TRO589808 UBH589808:UBK589808 ULD589808:ULG589808 UUZ589808:UVC589808 VEV589808:VEY589808 VOR589808:VOU589808 VYN589808:VYQ589808 WIJ589808:WIM589808 WSF589808:WSI589808 FT655344:FW655344 PP655344:PS655344 ZL655344:ZO655344 AJH655344:AJK655344 ATD655344:ATG655344 BCZ655344:BDC655344 BMV655344:BMY655344 BWR655344:BWU655344 CGN655344:CGQ655344 CQJ655344:CQM655344 DAF655344:DAI655344 DKB655344:DKE655344 DTX655344:DUA655344 EDT655344:EDW655344 ENP655344:ENS655344 EXL655344:EXO655344 FHH655344:FHK655344 FRD655344:FRG655344 GAZ655344:GBC655344 GKV655344:GKY655344 GUR655344:GUU655344 HEN655344:HEQ655344 HOJ655344:HOM655344 HYF655344:HYI655344 IIB655344:IIE655344 IRX655344:ISA655344 JBT655344:JBW655344 JLP655344:JLS655344 JVL655344:JVO655344 KFH655344:KFK655344 KPD655344:KPG655344 KYZ655344:KZC655344 LIV655344:LIY655344 LSR655344:LSU655344 MCN655344:MCQ655344 MMJ655344:MMM655344 MWF655344:MWI655344 NGB655344:NGE655344 NPX655344:NQA655344 NZT655344:NZW655344 OJP655344:OJS655344 OTL655344:OTO655344 PDH655344:PDK655344 PND655344:PNG655344 PWZ655344:PXC655344 QGV655344:QGY655344 QQR655344:QQU655344 RAN655344:RAQ655344 RKJ655344:RKM655344 RUF655344:RUI655344 SEB655344:SEE655344 SNX655344:SOA655344 SXT655344:SXW655344 THP655344:THS655344 TRL655344:TRO655344 UBH655344:UBK655344 ULD655344:ULG655344 UUZ655344:UVC655344 VEV655344:VEY655344 VOR655344:VOU655344 VYN655344:VYQ655344 WIJ655344:WIM655344 WSF655344:WSI655344 FT720880:FW720880 PP720880:PS720880 ZL720880:ZO720880 AJH720880:AJK720880 ATD720880:ATG720880 BCZ720880:BDC720880 BMV720880:BMY720880 BWR720880:BWU720880 CGN720880:CGQ720880 CQJ720880:CQM720880 DAF720880:DAI720880 DKB720880:DKE720880 DTX720880:DUA720880 EDT720880:EDW720880 ENP720880:ENS720880 EXL720880:EXO720880 FHH720880:FHK720880 FRD720880:FRG720880 GAZ720880:GBC720880 GKV720880:GKY720880 GUR720880:GUU720880 HEN720880:HEQ720880 HOJ720880:HOM720880 HYF720880:HYI720880 IIB720880:IIE720880 IRX720880:ISA720880 JBT720880:JBW720880 JLP720880:JLS720880 JVL720880:JVO720880 KFH720880:KFK720880 KPD720880:KPG720880 KYZ720880:KZC720880 LIV720880:LIY720880 LSR720880:LSU720880 MCN720880:MCQ720880 MMJ720880:MMM720880 MWF720880:MWI720880 NGB720880:NGE720880 NPX720880:NQA720880 NZT720880:NZW720880 OJP720880:OJS720880 OTL720880:OTO720880 PDH720880:PDK720880 PND720880:PNG720880 PWZ720880:PXC720880 QGV720880:QGY720880 QQR720880:QQU720880 RAN720880:RAQ720880 RKJ720880:RKM720880 RUF720880:RUI720880 SEB720880:SEE720880 SNX720880:SOA720880 SXT720880:SXW720880 THP720880:THS720880 TRL720880:TRO720880 UBH720880:UBK720880 ULD720880:ULG720880 UUZ720880:UVC720880 VEV720880:VEY720880 VOR720880:VOU720880 VYN720880:VYQ720880 WIJ720880:WIM720880 WSF720880:WSI720880 FT786416:FW786416 PP786416:PS786416 ZL786416:ZO786416 AJH786416:AJK786416 ATD786416:ATG786416 BCZ786416:BDC786416 BMV786416:BMY786416 BWR786416:BWU786416 CGN786416:CGQ786416 CQJ786416:CQM786416 DAF786416:DAI786416 DKB786416:DKE786416 DTX786416:DUA786416 EDT786416:EDW786416 ENP786416:ENS786416 EXL786416:EXO786416 FHH786416:FHK786416 FRD786416:FRG786416 GAZ786416:GBC786416 GKV786416:GKY786416 GUR786416:GUU786416 HEN786416:HEQ786416 HOJ786416:HOM786416 HYF786416:HYI786416 IIB786416:IIE786416 IRX786416:ISA786416 JBT786416:JBW786416 JLP786416:JLS786416 JVL786416:JVO786416 KFH786416:KFK786416 KPD786416:KPG786416 KYZ786416:KZC786416 LIV786416:LIY786416 LSR786416:LSU786416 MCN786416:MCQ786416 MMJ786416:MMM786416 MWF786416:MWI786416 NGB786416:NGE786416 NPX786416:NQA786416 NZT786416:NZW786416 OJP786416:OJS786416 OTL786416:OTO786416 PDH786416:PDK786416 PND786416:PNG786416 PWZ786416:PXC786416 QGV786416:QGY786416 QQR786416:QQU786416 RAN786416:RAQ786416 RKJ786416:RKM786416 RUF786416:RUI786416 SEB786416:SEE786416 SNX786416:SOA786416 SXT786416:SXW786416 THP786416:THS786416 TRL786416:TRO786416 UBH786416:UBK786416 ULD786416:ULG786416 UUZ786416:UVC786416 VEV786416:VEY786416 VOR786416:VOU786416 VYN786416:VYQ786416 WIJ786416:WIM786416 WSF786416:WSI786416 FT851952:FW851952 PP851952:PS851952 ZL851952:ZO851952 AJH851952:AJK851952 ATD851952:ATG851952 BCZ851952:BDC851952 BMV851952:BMY851952 BWR851952:BWU851952 CGN851952:CGQ851952 CQJ851952:CQM851952 DAF851952:DAI851952 DKB851952:DKE851952 DTX851952:DUA851952 EDT851952:EDW851952 ENP851952:ENS851952 EXL851952:EXO851952 FHH851952:FHK851952 FRD851952:FRG851952 GAZ851952:GBC851952 GKV851952:GKY851952 GUR851952:GUU851952 HEN851952:HEQ851952 HOJ851952:HOM851952 HYF851952:HYI851952 IIB851952:IIE851952 IRX851952:ISA851952 JBT851952:JBW851952 JLP851952:JLS851952 JVL851952:JVO851952 KFH851952:KFK851952 KPD851952:KPG851952 KYZ851952:KZC851952 LIV851952:LIY851952 LSR851952:LSU851952 MCN851952:MCQ851952 MMJ851952:MMM851952 MWF851952:MWI851952 NGB851952:NGE851952 NPX851952:NQA851952 NZT851952:NZW851952 OJP851952:OJS851952 OTL851952:OTO851952 PDH851952:PDK851952 PND851952:PNG851952 PWZ851952:PXC851952 QGV851952:QGY851952 QQR851952:QQU851952 RAN851952:RAQ851952 RKJ851952:RKM851952 RUF851952:RUI851952 SEB851952:SEE851952 SNX851952:SOA851952 SXT851952:SXW851952 THP851952:THS851952 TRL851952:TRO851952 UBH851952:UBK851952 ULD851952:ULG851952 UUZ851952:UVC851952 VEV851952:VEY851952 VOR851952:VOU851952 VYN851952:VYQ851952 WIJ851952:WIM851952 WSF851952:WSI851952 FT917488:FW917488 PP917488:PS917488 ZL917488:ZO917488 AJH917488:AJK917488 ATD917488:ATG917488 BCZ917488:BDC917488 BMV917488:BMY917488 BWR917488:BWU917488 CGN917488:CGQ917488 CQJ917488:CQM917488 DAF917488:DAI917488 DKB917488:DKE917488 DTX917488:DUA917488 EDT917488:EDW917488 ENP917488:ENS917488 EXL917488:EXO917488 FHH917488:FHK917488 FRD917488:FRG917488 GAZ917488:GBC917488 GKV917488:GKY917488 GUR917488:GUU917488 HEN917488:HEQ917488 HOJ917488:HOM917488 HYF917488:HYI917488 IIB917488:IIE917488 IRX917488:ISA917488 JBT917488:JBW917488 JLP917488:JLS917488 JVL917488:JVO917488 KFH917488:KFK917488 KPD917488:KPG917488 KYZ917488:KZC917488 LIV917488:LIY917488 LSR917488:LSU917488 MCN917488:MCQ917488 MMJ917488:MMM917488 MWF917488:MWI917488 NGB917488:NGE917488 NPX917488:NQA917488 NZT917488:NZW917488 OJP917488:OJS917488 OTL917488:OTO917488 PDH917488:PDK917488 PND917488:PNG917488 PWZ917488:PXC917488 QGV917488:QGY917488 QQR917488:QQU917488 RAN917488:RAQ917488 RKJ917488:RKM917488 RUF917488:RUI917488 SEB917488:SEE917488 SNX917488:SOA917488 SXT917488:SXW917488 THP917488:THS917488 TRL917488:TRO917488 UBH917488:UBK917488 ULD917488:ULG917488 UUZ917488:UVC917488 VEV917488:VEY917488 VOR917488:VOU917488 VYN917488:VYQ917488 WIJ917488:WIM917488 WSF917488:WSI917488 FT983024:FW983024 PP983024:PS983024 ZL983024:ZO983024 AJH983024:AJK983024 ATD983024:ATG983024 BCZ983024:BDC983024 BMV983024:BMY983024 BWR983024:BWU983024 CGN983024:CGQ983024 CQJ983024:CQM983024 DAF983024:DAI983024 DKB983024:DKE983024 DTX983024:DUA983024 EDT983024:EDW983024 ENP983024:ENS983024 EXL983024:EXO983024 FHH983024:FHK983024 FRD983024:FRG983024 GAZ983024:GBC983024 GKV983024:GKY983024 GUR983024:GUU983024 HEN983024:HEQ983024 HOJ983024:HOM983024 HYF983024:HYI983024 IIB983024:IIE983024 IRX983024:ISA983024 JBT983024:JBW983024 JLP983024:JLS983024 JVL983024:JVO983024 KFH983024:KFK983024 KPD983024:KPG983024 KYZ983024:KZC983024 LIV983024:LIY983024 LSR983024:LSU983024 MCN983024:MCQ983024 MMJ983024:MMM983024 MWF983024:MWI983024 NGB983024:NGE983024 NPX983024:NQA983024 NZT983024:NZW983024 OJP983024:OJS983024 OTL983024:OTO983024 PDH983024:PDK983024 PND983024:PNG983024 PWZ983024:PXC983024 QGV983024:QGY983024 QQR983024:QQU983024 RAN983024:RAQ983024 RKJ983024:RKM983024 RUF983024:RUI983024 SEB983024:SEE983024 SNX983024:SOA983024 SXT983024:SXW983024 THP983024:THS983024 TRL983024:TRO983024 UBH983024:UBK983024 ULD983024:ULG983024 UUZ983024:UVC983024 VEV983024:VEY983024 VOR983024:VOU983024 VYN983024:VYQ983024 WIJ983024:WIM983024 WSF983024:WSI983024 FO983023:FR983023 PK983023:PN983023 ZG983023:ZJ983023 AJC983023:AJF983023 ASY983023:ATB983023 BCU983023:BCX983023 BMQ983023:BMT983023 BWM983023:BWP983023 CGI983023:CGL983023 CQE983023:CQH983023 DAA983023:DAD983023 DJW983023:DJZ983023 DTS983023:DTV983023 EDO983023:EDR983023 ENK983023:ENN983023 EXG983023:EXJ983023 FHC983023:FHF983023 FQY983023:FRB983023 GAU983023:GAX983023 GKQ983023:GKT983023 GUM983023:GUP983023 HEI983023:HEL983023 HOE983023:HOH983023 HYA983023:HYD983023 IHW983023:IHZ983023 IRS983023:IRV983023 JBO983023:JBR983023 JLK983023:JLN983023 JVG983023:JVJ983023 KFC983023:KFF983023 KOY983023:KPB983023 KYU983023:KYX983023 LIQ983023:LIT983023 LSM983023:LSP983023 MCI983023:MCL983023 MME983023:MMH983023 MWA983023:MWD983023 NFW983023:NFZ983023 NPS983023:NPV983023 NZO983023:NZR983023 OJK983023:OJN983023 OTG983023:OTJ983023 PDC983023:PDF983023 PMY983023:PNB983023 PWU983023:PWX983023 QGQ983023:QGT983023 QQM983023:QQP983023 RAI983023:RAL983023 RKE983023:RKH983023 RUA983023:RUD983023 SDW983023:SDZ983023 SNS983023:SNV983023 SXO983023:SXR983023 THK983023:THN983023 TRG983023:TRJ983023 UBC983023:UBF983023 UKY983023:ULB983023 UUU983023:UUX983023 VEQ983023:VET983023 VOM983023:VOP983023 VYI983023:VYL983023 WIE983023:WIH983023 WSA983023:WSD983023 FO65519:FR65519 PK65519:PN65519 ZG65519:ZJ65519 AJC65519:AJF65519 ASY65519:ATB65519 BCU65519:BCX65519 BMQ65519:BMT65519 BWM65519:BWP65519 CGI65519:CGL65519 CQE65519:CQH65519 DAA65519:DAD65519 DJW65519:DJZ65519 DTS65519:DTV65519 EDO65519:EDR65519 ENK65519:ENN65519 EXG65519:EXJ65519 FHC65519:FHF65519 FQY65519:FRB65519 GAU65519:GAX65519 GKQ65519:GKT65519 GUM65519:GUP65519 HEI65519:HEL65519 HOE65519:HOH65519 HYA65519:HYD65519 IHW65519:IHZ65519 IRS65519:IRV65519 JBO65519:JBR65519 JLK65519:JLN65519 JVG65519:JVJ65519 KFC65519:KFF65519 KOY65519:KPB65519 KYU65519:KYX65519 LIQ65519:LIT65519 LSM65519:LSP65519 MCI65519:MCL65519 MME65519:MMH65519 MWA65519:MWD65519 NFW65519:NFZ65519 NPS65519:NPV65519 NZO65519:NZR65519 OJK65519:OJN65519 OTG65519:OTJ65519 PDC65519:PDF65519 PMY65519:PNB65519 PWU65519:PWX65519 QGQ65519:QGT65519 QQM65519:QQP65519 RAI65519:RAL65519 RKE65519:RKH65519 RUA65519:RUD65519 SDW65519:SDZ65519 SNS65519:SNV65519 SXO65519:SXR65519 THK65519:THN65519 TRG65519:TRJ65519 UBC65519:UBF65519 UKY65519:ULB65519 UUU65519:UUX65519 VEQ65519:VET65519 VOM65519:VOP65519 VYI65519:VYL65519 WIE65519:WIH65519 WSA65519:WSD65519 FO131055:FR131055 PK131055:PN131055 ZG131055:ZJ131055 AJC131055:AJF131055 ASY131055:ATB131055 BCU131055:BCX131055 BMQ131055:BMT131055 BWM131055:BWP131055 CGI131055:CGL131055 CQE131055:CQH131055 DAA131055:DAD131055 DJW131055:DJZ131055 DTS131055:DTV131055 EDO131055:EDR131055 ENK131055:ENN131055 EXG131055:EXJ131055 FHC131055:FHF131055 FQY131055:FRB131055 GAU131055:GAX131055 GKQ131055:GKT131055 GUM131055:GUP131055 HEI131055:HEL131055 HOE131055:HOH131055 HYA131055:HYD131055 IHW131055:IHZ131055 IRS131055:IRV131055 JBO131055:JBR131055 JLK131055:JLN131055 JVG131055:JVJ131055 KFC131055:KFF131055 KOY131055:KPB131055 KYU131055:KYX131055 LIQ131055:LIT131055 LSM131055:LSP131055 MCI131055:MCL131055 MME131055:MMH131055 MWA131055:MWD131055 NFW131055:NFZ131055 NPS131055:NPV131055 NZO131055:NZR131055 OJK131055:OJN131055 OTG131055:OTJ131055 PDC131055:PDF131055 PMY131055:PNB131055 PWU131055:PWX131055 QGQ131055:QGT131055 QQM131055:QQP131055 RAI131055:RAL131055 RKE131055:RKH131055 RUA131055:RUD131055 SDW131055:SDZ131055 SNS131055:SNV131055 SXO131055:SXR131055 THK131055:THN131055 TRG131055:TRJ131055 UBC131055:UBF131055 UKY131055:ULB131055 UUU131055:UUX131055 VEQ131055:VET131055 VOM131055:VOP131055 VYI131055:VYL131055 WIE131055:WIH131055 WSA131055:WSD131055 FO196591:FR196591 PK196591:PN196591 ZG196591:ZJ196591 AJC196591:AJF196591 ASY196591:ATB196591 BCU196591:BCX196591 BMQ196591:BMT196591 BWM196591:BWP196591 CGI196591:CGL196591 CQE196591:CQH196591 DAA196591:DAD196591 DJW196591:DJZ196591 DTS196591:DTV196591 EDO196591:EDR196591 ENK196591:ENN196591 EXG196591:EXJ196591 FHC196591:FHF196591 FQY196591:FRB196591 GAU196591:GAX196591 GKQ196591:GKT196591 GUM196591:GUP196591 HEI196591:HEL196591 HOE196591:HOH196591 HYA196591:HYD196591 IHW196591:IHZ196591 IRS196591:IRV196591 JBO196591:JBR196591 JLK196591:JLN196591 JVG196591:JVJ196591 KFC196591:KFF196591 KOY196591:KPB196591 KYU196591:KYX196591 LIQ196591:LIT196591 LSM196591:LSP196591 MCI196591:MCL196591 MME196591:MMH196591 MWA196591:MWD196591 NFW196591:NFZ196591 NPS196591:NPV196591 NZO196591:NZR196591 OJK196591:OJN196591 OTG196591:OTJ196591 PDC196591:PDF196591 PMY196591:PNB196591 PWU196591:PWX196591 QGQ196591:QGT196591 QQM196591:QQP196591 RAI196591:RAL196591 RKE196591:RKH196591 RUA196591:RUD196591 SDW196591:SDZ196591 SNS196591:SNV196591 SXO196591:SXR196591 THK196591:THN196591 TRG196591:TRJ196591 UBC196591:UBF196591 UKY196591:ULB196591 UUU196591:UUX196591 VEQ196591:VET196591 VOM196591:VOP196591 VYI196591:VYL196591 WIE196591:WIH196591 WSA196591:WSD196591 FO262127:FR262127 PK262127:PN262127 ZG262127:ZJ262127 AJC262127:AJF262127 ASY262127:ATB262127 BCU262127:BCX262127 BMQ262127:BMT262127 BWM262127:BWP262127 CGI262127:CGL262127 CQE262127:CQH262127 DAA262127:DAD262127 DJW262127:DJZ262127 DTS262127:DTV262127 EDO262127:EDR262127 ENK262127:ENN262127 EXG262127:EXJ262127 FHC262127:FHF262127 FQY262127:FRB262127 GAU262127:GAX262127 GKQ262127:GKT262127 GUM262127:GUP262127 HEI262127:HEL262127 HOE262127:HOH262127 HYA262127:HYD262127 IHW262127:IHZ262127 IRS262127:IRV262127 JBO262127:JBR262127 JLK262127:JLN262127 JVG262127:JVJ262127 KFC262127:KFF262127 KOY262127:KPB262127 KYU262127:KYX262127 LIQ262127:LIT262127 LSM262127:LSP262127 MCI262127:MCL262127 MME262127:MMH262127 MWA262127:MWD262127 NFW262127:NFZ262127 NPS262127:NPV262127 NZO262127:NZR262127 OJK262127:OJN262127 OTG262127:OTJ262127 PDC262127:PDF262127 PMY262127:PNB262127 PWU262127:PWX262127 QGQ262127:QGT262127 QQM262127:QQP262127 RAI262127:RAL262127 RKE262127:RKH262127 RUA262127:RUD262127 SDW262127:SDZ262127 SNS262127:SNV262127 SXO262127:SXR262127 THK262127:THN262127 TRG262127:TRJ262127 UBC262127:UBF262127 UKY262127:ULB262127 UUU262127:UUX262127 VEQ262127:VET262127 VOM262127:VOP262127 VYI262127:VYL262127 WIE262127:WIH262127 WSA262127:WSD262127 FO327663:FR327663 PK327663:PN327663 ZG327663:ZJ327663 AJC327663:AJF327663 ASY327663:ATB327663 BCU327663:BCX327663 BMQ327663:BMT327663 BWM327663:BWP327663 CGI327663:CGL327663 CQE327663:CQH327663 DAA327663:DAD327663 DJW327663:DJZ327663 DTS327663:DTV327663 EDO327663:EDR327663 ENK327663:ENN327663 EXG327663:EXJ327663 FHC327663:FHF327663 FQY327663:FRB327663 GAU327663:GAX327663 GKQ327663:GKT327663 GUM327663:GUP327663 HEI327663:HEL327663 HOE327663:HOH327663 HYA327663:HYD327663 IHW327663:IHZ327663 IRS327663:IRV327663 JBO327663:JBR327663 JLK327663:JLN327663 JVG327663:JVJ327663 KFC327663:KFF327663 KOY327663:KPB327663 KYU327663:KYX327663 LIQ327663:LIT327663 LSM327663:LSP327663 MCI327663:MCL327663 MME327663:MMH327663 MWA327663:MWD327663 NFW327663:NFZ327663 NPS327663:NPV327663 NZO327663:NZR327663 OJK327663:OJN327663 OTG327663:OTJ327663 PDC327663:PDF327663 PMY327663:PNB327663 PWU327663:PWX327663 QGQ327663:QGT327663 QQM327663:QQP327663 RAI327663:RAL327663 RKE327663:RKH327663 RUA327663:RUD327663 SDW327663:SDZ327663 SNS327663:SNV327663 SXO327663:SXR327663 THK327663:THN327663 TRG327663:TRJ327663 UBC327663:UBF327663 UKY327663:ULB327663 UUU327663:UUX327663 VEQ327663:VET327663 VOM327663:VOP327663 VYI327663:VYL327663 WIE327663:WIH327663 WSA327663:WSD327663 FO393199:FR393199 PK393199:PN393199 ZG393199:ZJ393199 AJC393199:AJF393199 ASY393199:ATB393199 BCU393199:BCX393199 BMQ393199:BMT393199 BWM393199:BWP393199 CGI393199:CGL393199 CQE393199:CQH393199 DAA393199:DAD393199 DJW393199:DJZ393199 DTS393199:DTV393199 EDO393199:EDR393199 ENK393199:ENN393199 EXG393199:EXJ393199 FHC393199:FHF393199 FQY393199:FRB393199 GAU393199:GAX393199 GKQ393199:GKT393199 GUM393199:GUP393199 HEI393199:HEL393199 HOE393199:HOH393199 HYA393199:HYD393199 IHW393199:IHZ393199 IRS393199:IRV393199 JBO393199:JBR393199 JLK393199:JLN393199 JVG393199:JVJ393199 KFC393199:KFF393199 KOY393199:KPB393199 KYU393199:KYX393199 LIQ393199:LIT393199 LSM393199:LSP393199 MCI393199:MCL393199 MME393199:MMH393199 MWA393199:MWD393199 NFW393199:NFZ393199 NPS393199:NPV393199 NZO393199:NZR393199 OJK393199:OJN393199 OTG393199:OTJ393199 PDC393199:PDF393199 PMY393199:PNB393199 PWU393199:PWX393199 QGQ393199:QGT393199 QQM393199:QQP393199 RAI393199:RAL393199 RKE393199:RKH393199 RUA393199:RUD393199 SDW393199:SDZ393199 SNS393199:SNV393199 SXO393199:SXR393199 THK393199:THN393199 TRG393199:TRJ393199 UBC393199:UBF393199 UKY393199:ULB393199 UUU393199:UUX393199 VEQ393199:VET393199 VOM393199:VOP393199 VYI393199:VYL393199 WIE393199:WIH393199 WSA393199:WSD393199 FO458735:FR458735 PK458735:PN458735 ZG458735:ZJ458735 AJC458735:AJF458735 ASY458735:ATB458735 BCU458735:BCX458735 BMQ458735:BMT458735 BWM458735:BWP458735 CGI458735:CGL458735 CQE458735:CQH458735 DAA458735:DAD458735 DJW458735:DJZ458735 DTS458735:DTV458735 EDO458735:EDR458735 ENK458735:ENN458735 EXG458735:EXJ458735 FHC458735:FHF458735 FQY458735:FRB458735 GAU458735:GAX458735 GKQ458735:GKT458735 GUM458735:GUP458735 HEI458735:HEL458735 HOE458735:HOH458735 HYA458735:HYD458735 IHW458735:IHZ458735 IRS458735:IRV458735 JBO458735:JBR458735 JLK458735:JLN458735 JVG458735:JVJ458735 KFC458735:KFF458735 KOY458735:KPB458735 KYU458735:KYX458735 LIQ458735:LIT458735 LSM458735:LSP458735 MCI458735:MCL458735 MME458735:MMH458735 MWA458735:MWD458735 NFW458735:NFZ458735 NPS458735:NPV458735 NZO458735:NZR458735 OJK458735:OJN458735 OTG458735:OTJ458735 PDC458735:PDF458735 PMY458735:PNB458735 PWU458735:PWX458735 QGQ458735:QGT458735 QQM458735:QQP458735 RAI458735:RAL458735 RKE458735:RKH458735 RUA458735:RUD458735 SDW458735:SDZ458735 SNS458735:SNV458735 SXO458735:SXR458735 THK458735:THN458735 TRG458735:TRJ458735 UBC458735:UBF458735 UKY458735:ULB458735 UUU458735:UUX458735 VEQ458735:VET458735 VOM458735:VOP458735 VYI458735:VYL458735 WIE458735:WIH458735 WSA458735:WSD458735 FO524271:FR524271 PK524271:PN524271 ZG524271:ZJ524271 AJC524271:AJF524271 ASY524271:ATB524271 BCU524271:BCX524271 BMQ524271:BMT524271 BWM524271:BWP524271 CGI524271:CGL524271 CQE524271:CQH524271 DAA524271:DAD524271 DJW524271:DJZ524271 DTS524271:DTV524271 EDO524271:EDR524271 ENK524271:ENN524271 EXG524271:EXJ524271 FHC524271:FHF524271 FQY524271:FRB524271 GAU524271:GAX524271 GKQ524271:GKT524271 GUM524271:GUP524271 HEI524271:HEL524271 HOE524271:HOH524271 HYA524271:HYD524271 IHW524271:IHZ524271 IRS524271:IRV524271 JBO524271:JBR524271 JLK524271:JLN524271 JVG524271:JVJ524271 KFC524271:KFF524271 KOY524271:KPB524271 KYU524271:KYX524271 LIQ524271:LIT524271 LSM524271:LSP524271 MCI524271:MCL524271 MME524271:MMH524271 MWA524271:MWD524271 NFW524271:NFZ524271 NPS524271:NPV524271 NZO524271:NZR524271 OJK524271:OJN524271 OTG524271:OTJ524271 PDC524271:PDF524271 PMY524271:PNB524271 PWU524271:PWX524271 QGQ524271:QGT524271 QQM524271:QQP524271 RAI524271:RAL524271 RKE524271:RKH524271 RUA524271:RUD524271 SDW524271:SDZ524271 SNS524271:SNV524271 SXO524271:SXR524271 THK524271:THN524271 TRG524271:TRJ524271 UBC524271:UBF524271 UKY524271:ULB524271 UUU524271:UUX524271 VEQ524271:VET524271 VOM524271:VOP524271 VYI524271:VYL524271 WIE524271:WIH524271 WSA524271:WSD524271 FO589807:FR589807 PK589807:PN589807 ZG589807:ZJ589807 AJC589807:AJF589807 ASY589807:ATB589807 BCU589807:BCX589807 BMQ589807:BMT589807 BWM589807:BWP589807 CGI589807:CGL589807 CQE589807:CQH589807 DAA589807:DAD589807 DJW589807:DJZ589807 DTS589807:DTV589807 EDO589807:EDR589807 ENK589807:ENN589807 EXG589807:EXJ589807 FHC589807:FHF589807 FQY589807:FRB589807 GAU589807:GAX589807 GKQ589807:GKT589807 GUM589807:GUP589807 HEI589807:HEL589807 HOE589807:HOH589807 HYA589807:HYD589807 IHW589807:IHZ589807 IRS589807:IRV589807 JBO589807:JBR589807 JLK589807:JLN589807 JVG589807:JVJ589807 KFC589807:KFF589807 KOY589807:KPB589807 KYU589807:KYX589807 LIQ589807:LIT589807 LSM589807:LSP589807 MCI589807:MCL589807 MME589807:MMH589807 MWA589807:MWD589807 NFW589807:NFZ589807 NPS589807:NPV589807 NZO589807:NZR589807 OJK589807:OJN589807 OTG589807:OTJ589807 PDC589807:PDF589807 PMY589807:PNB589807 PWU589807:PWX589807 QGQ589807:QGT589807 QQM589807:QQP589807 RAI589807:RAL589807 RKE589807:RKH589807 RUA589807:RUD589807 SDW589807:SDZ589807 SNS589807:SNV589807 SXO589807:SXR589807 THK589807:THN589807 TRG589807:TRJ589807 UBC589807:UBF589807 UKY589807:ULB589807 UUU589807:UUX589807 VEQ589807:VET589807 VOM589807:VOP589807 VYI589807:VYL589807 WIE589807:WIH589807 WSA589807:WSD589807 FO655343:FR655343 PK655343:PN655343 ZG655343:ZJ655343 AJC655343:AJF655343 ASY655343:ATB655343 BCU655343:BCX655343 BMQ655343:BMT655343 BWM655343:BWP655343 CGI655343:CGL655343 CQE655343:CQH655343 DAA655343:DAD655343 DJW655343:DJZ655343 DTS655343:DTV655343 EDO655343:EDR655343 ENK655343:ENN655343 EXG655343:EXJ655343 FHC655343:FHF655343 FQY655343:FRB655343 GAU655343:GAX655343 GKQ655343:GKT655343 GUM655343:GUP655343 HEI655343:HEL655343 HOE655343:HOH655343 HYA655343:HYD655343 IHW655343:IHZ655343 IRS655343:IRV655343 JBO655343:JBR655343 JLK655343:JLN655343 JVG655343:JVJ655343 KFC655343:KFF655343 KOY655343:KPB655343 KYU655343:KYX655343 LIQ655343:LIT655343 LSM655343:LSP655343 MCI655343:MCL655343 MME655343:MMH655343 MWA655343:MWD655343 NFW655343:NFZ655343 NPS655343:NPV655343 NZO655343:NZR655343 OJK655343:OJN655343 OTG655343:OTJ655343 PDC655343:PDF655343 PMY655343:PNB655343 PWU655343:PWX655343 QGQ655343:QGT655343 QQM655343:QQP655343 RAI655343:RAL655343 RKE655343:RKH655343 RUA655343:RUD655343 SDW655343:SDZ655343 SNS655343:SNV655343 SXO655343:SXR655343 THK655343:THN655343 TRG655343:TRJ655343 UBC655343:UBF655343 UKY655343:ULB655343 UUU655343:UUX655343 VEQ655343:VET655343 VOM655343:VOP655343 VYI655343:VYL655343 WIE655343:WIH655343 WSA655343:WSD655343 FO720879:FR720879 PK720879:PN720879 ZG720879:ZJ720879 AJC720879:AJF720879 ASY720879:ATB720879 BCU720879:BCX720879 BMQ720879:BMT720879 BWM720879:BWP720879 CGI720879:CGL720879 CQE720879:CQH720879 DAA720879:DAD720879 DJW720879:DJZ720879 DTS720879:DTV720879 EDO720879:EDR720879 ENK720879:ENN720879 EXG720879:EXJ720879 FHC720879:FHF720879 FQY720879:FRB720879 GAU720879:GAX720879 GKQ720879:GKT720879 GUM720879:GUP720879 HEI720879:HEL720879 HOE720879:HOH720879 HYA720879:HYD720879 IHW720879:IHZ720879 IRS720879:IRV720879 JBO720879:JBR720879 JLK720879:JLN720879 JVG720879:JVJ720879 KFC720879:KFF720879 KOY720879:KPB720879 KYU720879:KYX720879 LIQ720879:LIT720879 LSM720879:LSP720879 MCI720879:MCL720879 MME720879:MMH720879 MWA720879:MWD720879 NFW720879:NFZ720879 NPS720879:NPV720879 NZO720879:NZR720879 OJK720879:OJN720879 OTG720879:OTJ720879 PDC720879:PDF720879 PMY720879:PNB720879 PWU720879:PWX720879 QGQ720879:QGT720879 QQM720879:QQP720879 RAI720879:RAL720879 RKE720879:RKH720879 RUA720879:RUD720879 SDW720879:SDZ720879 SNS720879:SNV720879 SXO720879:SXR720879 THK720879:THN720879 TRG720879:TRJ720879 UBC720879:UBF720879 UKY720879:ULB720879 UUU720879:UUX720879 VEQ720879:VET720879 VOM720879:VOP720879 VYI720879:VYL720879 WIE720879:WIH720879 WSA720879:WSD720879 FO786415:FR786415 PK786415:PN786415 ZG786415:ZJ786415 AJC786415:AJF786415 ASY786415:ATB786415 BCU786415:BCX786415 BMQ786415:BMT786415 BWM786415:BWP786415 CGI786415:CGL786415 CQE786415:CQH786415 DAA786415:DAD786415 DJW786415:DJZ786415 DTS786415:DTV786415 EDO786415:EDR786415 ENK786415:ENN786415 EXG786415:EXJ786415 FHC786415:FHF786415 FQY786415:FRB786415 GAU786415:GAX786415 GKQ786415:GKT786415 GUM786415:GUP786415 HEI786415:HEL786415 HOE786415:HOH786415 HYA786415:HYD786415 IHW786415:IHZ786415 IRS786415:IRV786415 JBO786415:JBR786415 JLK786415:JLN786415 JVG786415:JVJ786415 KFC786415:KFF786415 KOY786415:KPB786415 KYU786415:KYX786415 LIQ786415:LIT786415 LSM786415:LSP786415 MCI786415:MCL786415 MME786415:MMH786415 MWA786415:MWD786415 NFW786415:NFZ786415 NPS786415:NPV786415 NZO786415:NZR786415 OJK786415:OJN786415 OTG786415:OTJ786415 PDC786415:PDF786415 PMY786415:PNB786415 PWU786415:PWX786415 QGQ786415:QGT786415 QQM786415:QQP786415 RAI786415:RAL786415 RKE786415:RKH786415 RUA786415:RUD786415 SDW786415:SDZ786415 SNS786415:SNV786415 SXO786415:SXR786415 THK786415:THN786415 TRG786415:TRJ786415 UBC786415:UBF786415 UKY786415:ULB786415 UUU786415:UUX786415 VEQ786415:VET786415 VOM786415:VOP786415 VYI786415:VYL786415 WIE786415:WIH786415 WSA786415:WSD786415 FO851951:FR851951 PK851951:PN851951 ZG851951:ZJ851951 AJC851951:AJF851951 ASY851951:ATB851951 BCU851951:BCX851951 BMQ851951:BMT851951 BWM851951:BWP851951 CGI851951:CGL851951 CQE851951:CQH851951 DAA851951:DAD851951 DJW851951:DJZ851951 DTS851951:DTV851951 EDO851951:EDR851951 ENK851951:ENN851951 EXG851951:EXJ851951 FHC851951:FHF851951 FQY851951:FRB851951 GAU851951:GAX851951 GKQ851951:GKT851951 GUM851951:GUP851951 HEI851951:HEL851951 HOE851951:HOH851951 HYA851951:HYD851951 IHW851951:IHZ851951 IRS851951:IRV851951 JBO851951:JBR851951 JLK851951:JLN851951 JVG851951:JVJ851951 KFC851951:KFF851951 KOY851951:KPB851951 KYU851951:KYX851951 LIQ851951:LIT851951 LSM851951:LSP851951 MCI851951:MCL851951 MME851951:MMH851951 MWA851951:MWD851951 NFW851951:NFZ851951 NPS851951:NPV851951 NZO851951:NZR851951 OJK851951:OJN851951 OTG851951:OTJ851951 PDC851951:PDF851951 PMY851951:PNB851951 PWU851951:PWX851951 QGQ851951:QGT851951 QQM851951:QQP851951 RAI851951:RAL851951 RKE851951:RKH851951 RUA851951:RUD851951 SDW851951:SDZ851951 SNS851951:SNV851951 SXO851951:SXR851951 THK851951:THN851951 TRG851951:TRJ851951 UBC851951:UBF851951 UKY851951:ULB851951 UUU851951:UUX851951 VEQ851951:VET851951 VOM851951:VOP851951 VYI851951:VYL851951 WIE851951:WIH851951 WSA851951:WSD851951 FO917487:FR917487 PK917487:PN917487 ZG917487:ZJ917487 AJC917487:AJF917487 ASY917487:ATB917487 BCU917487:BCX917487 BMQ917487:BMT917487 BWM917487:BWP917487 CGI917487:CGL917487 CQE917487:CQH917487 DAA917487:DAD917487 DJW917487:DJZ917487 DTS917487:DTV917487 EDO917487:EDR917487 ENK917487:ENN917487 EXG917487:EXJ917487 FHC917487:FHF917487 FQY917487:FRB917487 GAU917487:GAX917487 GKQ917487:GKT917487 GUM917487:GUP917487 HEI917487:HEL917487 HOE917487:HOH917487 HYA917487:HYD917487 IHW917487:IHZ917487 IRS917487:IRV917487 JBO917487:JBR917487 JLK917487:JLN917487 JVG917487:JVJ917487 KFC917487:KFF917487 KOY917487:KPB917487 KYU917487:KYX917487 LIQ917487:LIT917487 LSM917487:LSP917487 MCI917487:MCL917487 MME917487:MMH917487 MWA917487:MWD917487 NFW917487:NFZ917487 NPS917487:NPV917487 NZO917487:NZR917487 OJK917487:OJN917487 OTG917487:OTJ917487 PDC917487:PDF917487 PMY917487:PNB917487 PWU917487:PWX917487 QGQ917487:QGT917487 QQM917487:QQP917487 RAI917487:RAL917487 RKE917487:RKH917487 RUA917487:RUD917487 SDW917487:SDZ917487 SNS917487:SNV917487 SXO917487:SXR917487 THK917487:THN917487 TRG917487:TRJ917487 UBC917487:UBF917487 UKY917487:ULB917487 UUU917487:UUX917487 VEQ917487:VET917487 VOM917487:VOP917487 VYI917487:VYL917487 WIE917487:WIH917487 WSA917487:WSD917487" xr:uid="{21369424-5F25-4207-AE77-270DAFEFE719}">
       <formula1>"○, ○（オンライン処理設計書なし）"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7831,164 +11123,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="27" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="29.5" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="27" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="27" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="27" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="27" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="27" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="E8" s="79" t="s">
+      <c r="E8" s="27" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="79" t="s">
+      <c r="E9" s="27" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="77"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
@@ -8283,405 +11575,405 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="23" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="77" t="s">
+      <c r="F2" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G2" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="27" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="27" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="27" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="79" t="s">
+      <c r="G5" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="H5" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="79"/>
+      <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9" ht="15.5" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="E6" s="76" t="s">
+      <c r="E6" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F6" s="78" t="s">
+      <c r="F6" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="27" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="I7" s="79" t="s">
+      <c r="I7" s="27" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.5" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="76" t="s">
+      <c r="E8" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="H8" s="79" t="s">
+      <c r="H8" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I8" s="27" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="79" t="s">
+      <c r="G9" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="79" t="s">
+      <c r="H9" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="I9" s="79" t="s">
+      <c r="I9" s="27" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="20" customHeight="1">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="79" t="s">
+      <c r="G10" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="79" t="s">
+      <c r="H10" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="I10" s="79" t="s">
+      <c r="I10" s="27" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="H11" s="79" t="s">
+      <c r="H11" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="I11" s="79" t="s">
+      <c r="I11" s="27" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="79" t="s">
+      <c r="H12" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="I12" s="79" t="s">
+      <c r="I12" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="79" t="s">
+      <c r="D13" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="H13" s="79" t="s">
+      <c r="H13" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="I13" s="79" t="s">
+      <c r="I13" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A15" s="77"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
@@ -8709,7 +12001,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="21" customWidth="1"/>
@@ -8975,213 +12267,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="23" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="77" t="s">
+      <c r="F2" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="G2" s="79"/>
-    </row>
-    <row r="3" spans="1:7" ht="27">
-      <c r="A3" s="76" t="s">
+      <c r="G2" s="27"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="G3" s="79"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="27" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="G5" s="79"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="1:7" ht="15.5" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="76" t="s">
+      <c r="E6" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="F6" s="78" t="s">
+      <c r="F6" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="27" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27">
-      <c r="A7" s="76" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="G7" s="79"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:7" ht="15.5" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="76" t="s">
+      <c r="E8" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="G8" s="79"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:7" ht="27">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="79"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:7" ht="20" customHeight="1">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="79"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A11" s="77"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="79"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="27"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="22" t="s">
+        <v>251</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
@@ -9201,6 +12498,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9473,109 +12771,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="79"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="27" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="79"/>
+      <c r="E4" s="27"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="27" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="27" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="76"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
@@ -9868,156 +13166,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="23" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="27" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="27" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="F4" s="79"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="79"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="15.5" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="15.5" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>

--- a/20_設計書/ログインシステム.xlsx
+++ b/20_設計書/ログインシステム.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150AAC9-405B-448D-8539-2065B6F3E92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9F9438-2A28-44AA-9CA3-62DCA9016BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34440" yWindow="1425" windowWidth="18720" windowHeight="13845" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -366,12 +366,6 @@
     <phoneticPr fontId="52"/>
   </si>
   <si>
-    <t>新ヒロセWebから環境証明書システムへ遷移</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>①</t>
     <phoneticPr fontId="52"/>
   </si>
@@ -406,40 +400,6 @@
     <phoneticPr fontId="52"/>
   </si>
   <si>
-    <t>認証用ハッシュコード取得</t>
-    <rPh sb="0" eb="3">
-      <t>ニンショウヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="52"/>
-  </si>
-  <si>
-    <t>ログインAPIを実行</t>
-    <phoneticPr fontId="52"/>
-  </si>
-  <si>
-    <t>ユーザ情報取得</t>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="52"/>
-  </si>
-  <si>
-    <t>トップ画面表示</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="52"/>
-  </si>
-  <si>
     <t>入力</t>
     <rPh sb="0" eb="2">
       <t>ニュウリョク</t>
@@ -447,55 +407,130 @@
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>出力</t>
-    <rPh sb="0" eb="2">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="52"/>
-  </si>
-  <si>
-    <t>認証用URL</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
     <t>ハッシュコード</t>
-  </si>
-  <si>
-    <t>ユーザ情報</t>
   </si>
   <si>
     <t>API応答</t>
   </si>
   <si>
-    <t>メールアドレス・氏名・代理店名</t>
-  </si>
-  <si>
     <t>ログイン状態</t>
   </si>
   <si>
-    <t>トップ画面</t>
+    <t>新A社Webから環境証明書システムへ遷移する。</t>
   </si>
   <si>
-    <t>取得した情報をセッションに格納する</t>
-    <rPh sb="0" eb="2">
-      <t>シュトク</t>
+    <t>URLのGETパラメータからハッシュコードを取得する。</t>
+  </si>
+  <si>
+    <t>ユーザー情報取得API（3-4相当）を実行する。</t>
+  </si>
+  <si>
+    <t>API応答からユーザー情報を取得する。</t>
+  </si>
+  <si>
+    <t>取得したユーザー情報をセッションへ格納する。</t>
+  </si>
+  <si>
+    <t>ログイン状態でトップ画面を表示する。</t>
+  </si>
+  <si>
+    <t>ハッシュコード付きURL</t>
+  </si>
+  <si>
+    <t>GETパラメータ</t>
+  </si>
+  <si>
+    <t>ユーザー情報</t>
+  </si>
+  <si>
+    <t>セッション情報</t>
+  </si>
+  <si>
+    <t>出力・結果</t>
+  </si>
+  <si>
+    <t>環境証明書システム起動</t>
+  </si>
+  <si>
+    <t>API実行結果</t>
+  </si>
+  <si>
+    <t>トップ画面表示</t>
+  </si>
+  <si>
+    <t>ユーザーID、メールアドレス、氏名等</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>ログイン画面は表示しない。</t>
+  </si>
+  <si>
+    <t>ハッシュコードを後続APIのパラメータとして使用する。</t>
+  </si>
+  <si>
+    <t>Web側で用意するAPIは3-4相当のみ。</t>
+  </si>
+  <si>
+    <t>取得項目はAPI応答仕様に従う。</t>
+  </si>
+  <si>
+    <t>セッション有効期限は1日。</t>
+  </si>
+  <si>
+    <t>セッションが無効な場合はエラー表示等を行う。</t>
+  </si>
+  <si>
+    <t>dr1.1</t>
+    <phoneticPr fontId="49"/>
+  </si>
+  <si>
+    <t>「ログイン処理」シート</t>
+    <rPh sb="5" eb="7">
+      <t>ショリ</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
+    <phoneticPr fontId="49"/>
+  </si>
+  <si>
+    <t>ログインシステムの未決事項が確定したので内容を反映</t>
+    <rPh sb="9" eb="13">
+      <t>ミケツジコウ</t>
     </rPh>
-    <rPh sb="13" eb="15">
-      <t>カクノウ</t>
+    <rPh sb="14" eb="16">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="49"/>
+  </si>
+  <si>
+    <t>※システム詳細は「新環境証明書　概要設計」を確認。</t>
+    <rPh sb="5" eb="7">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="52"/>
   </si>
   <si>
-    <t>※システム詳細は「新環境証明書　概要設計」を確認</t>
-    <rPh sb="5" eb="7">
+    <t>※③のユーザ情報取得APIの詳細は「functional-design.md」の3-4を確認</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
       <t>ショウサイ</t>
     </rPh>
-    <rPh sb="22" eb="24">
+    <rPh sb="44" eb="46">
       <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="52"/>
@@ -1814,160 +1849,160 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="55" fillId="12" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="55" fillId="12" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="15" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="14" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="8" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="13" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="13" borderId="15" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="14" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2595,15 +2630,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>239811</xdr:colOff>
+      <xdr:colOff>236636</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>44823</xdr:rowOff>
+      <xdr:rowOff>47998</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1714318</xdr:colOff>
+      <xdr:colOff>593912</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>161738</xdr:rowOff>
+      <xdr:rowOff>164913</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2618,8 +2653,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5865164" y="2655794"/>
-          <a:ext cx="5306919" cy="8879915"/>
+          <a:off x="5861989" y="2658969"/>
+          <a:ext cx="7831599" cy="8879915"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2691,100 +2726,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>657604</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>84791</xdr:rowOff>
+      <xdr:colOff>90956</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>140439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>276416</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>107203</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC5FF3FD-754D-77D5-8C28-1CA72F809A24}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7257869" y="3267262"/>
-          <a:ext cx="2476312" cy="784412"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="12700"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>③ログイン処理</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>627347</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2569005</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>142312</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>277909</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>27268</xdr:rowOff>
+      <xdr:rowOff>19045</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2799,8 +2749,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7227612" y="4658283"/>
-          <a:ext cx="2508062" cy="837456"/>
+          <a:off x="7251515" y="3703910"/>
+          <a:ext cx="4887314" cy="831106"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2846,10 +2796,10 @@
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>https://zzzzz.com/api</a:t>
+            <a:t>② GET</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -2858,10 +2808,17 @@
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> </a:t>
+            <a:t>パラメータから</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -2870,31 +2827,7 @@
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>ハッシュコード</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>)</a:t>
+            <a:t>ハッシュコード取得</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
             <a:solidFill>
@@ -2911,15 +2844,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>657603</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>47996</xdr:rowOff>
+      <xdr:colOff>106831</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>30248</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>276415</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>68727</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2547181</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38279</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2934,8 +2867,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7257868" y="6659467"/>
-          <a:ext cx="2476312" cy="973231"/>
+          <a:off x="7267390" y="5689219"/>
+          <a:ext cx="4849615" cy="960531"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2982,52 +2915,28 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>ユーザ情報を取得</a:t>
+            <a:t>③ ユーザー情報取得</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1" spc="20" baseline="0">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-            <a:spcAft>
-              <a:spcPts val="200"/>
-            </a:spcAft>
-          </a:pPr>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" spc="20" baseline="0">
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1" spc="20" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>メールアドレス、名前を取得</a:t>
+            <a:t>API</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-            <a:spcAft>
-              <a:spcPts val="200"/>
-            </a:spcAft>
-          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>を実行</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" spc="20" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
@@ -3043,15 +2952,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>657603</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>64253</xdr:rowOff>
+      <xdr:colOff>106831</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>46505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>276415</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>104034</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2547181</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>105336</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3066,8 +2975,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7257868" y="8390224"/>
-          <a:ext cx="2476312" cy="992281"/>
+          <a:off x="7267390" y="7419976"/>
+          <a:ext cx="4849615" cy="1011331"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3128,15 +3037,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>657603</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>152597</xdr:rowOff>
+      <xdr:colOff>106831</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>144374</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>276415</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>36803</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2547181</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>19055</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3151,8 +3060,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7257868" y="10193068"/>
-          <a:ext cx="2476312" cy="1027206"/>
+          <a:off x="7267390" y="9232345"/>
+          <a:ext cx="4849615" cy="1017681"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3215,35 +3124,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898935</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>104028</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>119199</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19045</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898935</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>142312</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123761</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>27073</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
+        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4E054F-B333-8ACC-ACF2-E3B41C819BF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0BEF063-7EFF-43D4-ACDB-1022BE6A7A33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="5" idx="0"/>
+          <a:stCxn id="5" idx="2"/>
+          <a:endCxn id="9" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8499200" y="4048499"/>
-          <a:ext cx="0" cy="609784"/>
+        <a:xfrm flipH="1">
+          <a:off x="9689023" y="4535016"/>
+          <a:ext cx="4562" cy="1151028"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3271,35 +3180,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898934</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>27268</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144599</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38279</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898934</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>44821</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144599</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>46505</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0BEF063-7EFF-43D4-ACDB-1022BE6A7A33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5308BC0E-5C03-47C0-A0AA-9E35F0B53A97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="2"/>
-          <a:endCxn id="9" idx="0"/>
+          <a:stCxn id="9" idx="2"/>
+          <a:endCxn id="12" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="8499199" y="5495739"/>
-          <a:ext cx="0" cy="1160553"/>
+        <a:xfrm>
+          <a:off x="9714423" y="6649750"/>
+          <a:ext cx="0" cy="770226"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3327,72 +3236,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898934</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>65552</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144599</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>105336</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898934</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>67428</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5308BC0E-5C03-47C0-A0AA-9E35F0B53A97}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="9" idx="2"/>
-          <a:endCxn id="12" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8499199" y="7629523"/>
-          <a:ext cx="0" cy="763876"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898934</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>107209</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1898934</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>152597</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144599</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>144374</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3410,8 +3263,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8499199" y="9385680"/>
-          <a:ext cx="0" cy="807388"/>
+          <a:off x="9714423" y="8431307"/>
+          <a:ext cx="0" cy="801038"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3440,15 +3293,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2285266</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
+      <xdr:colOff>1744019</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>102718</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>106282</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>8030</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>50249</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>121768</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3463,8 +3316,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11743031" y="4146176"/>
-          <a:ext cx="5351369" cy="2282825"/>
+          <a:off x="14843695" y="5190189"/>
+          <a:ext cx="5332319" cy="2305050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3538,16 +3391,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>277909</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>183215</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2569005</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>122328</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1123768</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>596902</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>142313</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3558,14 +3411,12 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="3"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9735674" y="5080186"/>
-          <a:ext cx="3322359" cy="7285"/>
+          <a:off x="12138829" y="6162299"/>
+          <a:ext cx="4034249" cy="19985"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3597,15 +3448,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1161689</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>142311</xdr:rowOff>
+      <xdr:colOff>620442</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>84981</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>3657051</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>28760</xdr:rowOff>
+      <xdr:colOff>3115804</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>161548</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3620,8 +3471,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13095954" y="4658282"/>
-          <a:ext cx="2495362" cy="1600949"/>
+          <a:off x="16196618" y="5934452"/>
+          <a:ext cx="2495362" cy="1410067"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3667,10 +3518,17 @@
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>ログイン用</a:t>
+            <a:t>④ ハッシュコードを元に</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3679,7 +3537,7 @@
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>API</a:t>
+            <a:t>ユーザー情報を返却</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
             <a:solidFill>
@@ -3696,15 +3554,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2247345</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123266</xdr:rowOff>
+      <xdr:colOff>1787904</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>64066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>582151</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>25588</xdr:rowOff>
+      <xdr:colOff>119535</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>160063</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3719,8 +3577,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11705110" y="4829737"/>
-          <a:ext cx="811306" cy="283322"/>
+          <a:off x="14887580" y="5913537"/>
+          <a:ext cx="808131" cy="286497"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3770,16 +3628,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1896227</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>936</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>134470</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>130549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1209867</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>936</xdr:rowOff>
+      <xdr:colOff>655920</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3794,8 +3652,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="8496492" y="5850407"/>
-          <a:ext cx="4647640" cy="0"/>
+          <a:off x="9704294" y="6932520"/>
+          <a:ext cx="6527802" cy="15127"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3826,16 +3684,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>468035</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>38477</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>349625</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>8035</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>856133</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>124949</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3220573</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>84982</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3850,8 +3708,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9925800" y="5887948"/>
-          <a:ext cx="2864598" cy="276972"/>
+          <a:off x="9919449" y="7000506"/>
+          <a:ext cx="2870948" cy="267447"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3934,13 +3792,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>30253</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
+      <xdr:rowOff>44825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>4544729</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3955,8 +3813,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30253" y="2655795"/>
-          <a:ext cx="5310094" cy="4437529"/>
+          <a:off x="30253" y="2655796"/>
+          <a:ext cx="5310094" cy="2991970"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4137,7 +3995,24 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>ボタン押下で証明書</a:t>
+            <a:t>① リンク押下</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ハッシュコード付き</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
@@ -4147,7 +4022,7 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>WEB</a:t>
+            <a:t>URL</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4157,59 +4032,7 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>認証用ハッシュコードを生成</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>https://xxxxx.com/login/3xXadsdewqfUI633sjcww</a:t>
+            <a:t>で遷移</a:t>
           </a:r>
           <a:endParaRPr lang="ja-JP" altLang="ja-JP" b="0">
             <a:effectLst/>
@@ -4222,182 +4045,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>640598</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3170885</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>112058</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="正方形/長方形 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{880C16C8-23E4-4D30-B694-2E6789EBA552}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1436216" y="6051176"/>
-          <a:ext cx="2530287" cy="672353"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="12700"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>証明書</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>WEB</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>認証用ハッシュコードを渡す</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1905742</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>8030</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1916206</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="直線矢印コネクタ 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785EFD9B-3788-4019-8399-309DF13336C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="32" idx="2"/>
-          <a:endCxn id="34" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2701360" y="5286001"/>
-          <a:ext cx="10464" cy="765175"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3182470</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>183215</xdr:rowOff>
+      <xdr:colOff>4026086</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>176580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>627347</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>8030</xdr:rowOff>
+      <xdr:colOff>87781</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>85633</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4409,13 +4065,15 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="32" idx="3"/>
           <a:endCxn id="5" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3978088" y="5080186"/>
-          <a:ext cx="3249524" cy="1348815"/>
+          <a:off x="4821704" y="4121051"/>
+          <a:ext cx="2426636" cy="861553"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4817,16 +4475,16 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="21" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B22" s="30" t="str">
+      <c r="B22" s="28" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 22日 dr1.0</v>
-      </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+        <v>2026年 06月 26日 dr1.1</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="24" spans="2:8" ht="14.25" customHeight="1"/>
@@ -4834,15 +4492,15 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="27" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="28" spans="2:8" ht="14.25" customHeight="1">
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32" t="s">
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="G28" s="32"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="2:8" ht="14.25" customHeight="1">
       <c r="C29" s="3" t="s">
@@ -4877,11 +4535,11 @@
     </row>
     <row r="32" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="33" spans="3:20" ht="14.25" customHeight="1">
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
@@ -4928,7 +4586,7 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
       <c r="S38" s="16"/>
-      <c r="T38" s="28"/>
+      <c r="T38" s="30"/>
     </row>
     <row r="39" spans="3:20" ht="14.25" customHeight="1">
       <c r="K39" s="17"/>
@@ -4940,7 +4598,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="14"/>
       <c r="S39" s="19"/>
-      <c r="T39" s="29"/>
+      <c r="T39" s="33"/>
     </row>
     <row r="40" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="41" spans="3:20" ht="14.25" customHeight="1">
@@ -4964,7 +4622,7 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
       <c r="S42" s="16"/>
-      <c r="T42" s="28"/>
+      <c r="T42" s="30"/>
     </row>
     <row r="43" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K43" s="17"/>
@@ -4972,7 +4630,7 @@
       <c r="N43" s="12"/>
       <c r="R43" s="14"/>
       <c r="S43" s="19"/>
-      <c r="T43" s="28"/>
+      <c r="T43" s="30"/>
     </row>
     <row r="44" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K44" s="1"/>
@@ -5008,7 +4666,7 @@
       <c r="Q46" s="15"/>
       <c r="R46" s="14"/>
       <c r="S46" s="16"/>
-      <c r="T46" s="28"/>
+      <c r="T46" s="30"/>
     </row>
     <row r="47" spans="3:20" ht="14.25" customHeight="1">
       <c r="K47" s="17"/>
@@ -5020,7 +4678,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="14"/>
       <c r="S47" s="19"/>
-      <c r="T47" s="28"/>
+      <c r="T47" s="30"/>
     </row>
     <row r="48" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="49" spans="11:20" ht="14.25" customHeight="1">
@@ -5045,7 +4703,7 @@
       <c r="Q50" s="15"/>
       <c r="R50" s="14"/>
       <c r="S50" s="16"/>
-      <c r="T50" s="28"/>
+      <c r="T50" s="30"/>
     </row>
     <row r="51" spans="11:20" ht="14.25" customHeight="1">
       <c r="K51" s="17"/>
@@ -5057,7 +4715,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="14"/>
       <c r="S51" s="19"/>
-      <c r="T51" s="28"/>
+      <c r="T51" s="30"/>
     </row>
     <row r="52" spans="11:20" ht="14.25" customHeight="1"/>
     <row r="53" spans="11:20" ht="14.25" customHeight="1">
@@ -5082,7 +4740,7 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="28"/>
+      <c r="T54" s="30"/>
     </row>
     <row r="55" spans="11:20">
       <c r="K55" s="17"/>
@@ -5094,7 +4752,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="14"/>
       <c r="S55" s="19"/>
-      <c r="T55" s="29"/>
+      <c r="T55" s="33"/>
     </row>
     <row r="57" spans="11:20">
       <c r="K57" s="11"/>
@@ -5118,7 +4776,7 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
       <c r="S58" s="16"/>
-      <c r="T58" s="28"/>
+      <c r="T58" s="30"/>
     </row>
     <row r="59" spans="11:20">
       <c r="K59" s="17"/>
@@ -5130,7 +4788,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="14"/>
       <c r="S59" s="19"/>
-      <c r="T59" s="29"/>
+      <c r="T59" s="33"/>
     </row>
     <row r="61" spans="11:20">
       <c r="K61" s="11"/>
@@ -5154,7 +4812,7 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
       <c r="S62" s="16"/>
-      <c r="T62" s="28"/>
+      <c r="T62" s="30"/>
     </row>
     <row r="63" spans="11:20">
       <c r="K63" s="17"/>
@@ -5166,7 +4824,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="14"/>
       <c r="S63" s="19"/>
-      <c r="T63" s="29"/>
+      <c r="T63" s="33"/>
     </row>
     <row r="65" spans="11:20">
       <c r="K65" s="11"/>
@@ -5190,7 +4848,7 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
       <c r="S66" s="16"/>
-      <c r="T66" s="28"/>
+      <c r="T66" s="30"/>
     </row>
     <row r="67" spans="11:20">
       <c r="K67" s="17"/>
@@ -5202,7 +4860,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="14"/>
       <c r="S67" s="19"/>
-      <c r="T67" s="29"/>
+      <c r="T67" s="33"/>
     </row>
     <row r="69" spans="11:20">
       <c r="K69" s="11"/>
@@ -5226,7 +4884,7 @@
       <c r="Q70" s="15"/>
       <c r="R70" s="14"/>
       <c r="S70" s="16"/>
-      <c r="T70" s="28"/>
+      <c r="T70" s="30"/>
     </row>
     <row r="71" spans="11:20">
       <c r="K71" s="17"/>
@@ -5238,7 +4896,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="14"/>
       <c r="S71" s="19"/>
-      <c r="T71" s="29"/>
+      <c r="T71" s="33"/>
     </row>
     <row r="73" spans="11:20">
       <c r="K73" s="11"/>
@@ -5262,7 +4920,7 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
       <c r="S74" s="16"/>
-      <c r="T74" s="28"/>
+      <c r="T74" s="30"/>
     </row>
     <row r="75" spans="11:20">
       <c r="K75" s="17"/>
@@ -5274,7 +4932,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="14"/>
       <c r="S75" s="19"/>
-      <c r="T75" s="29"/>
+      <c r="T75" s="33"/>
     </row>
     <row r="77" spans="11:20">
       <c r="K77" s="11"/>
@@ -5298,7 +4956,7 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
       <c r="S78" s="16"/>
-      <c r="T78" s="28"/>
+      <c r="T78" s="30"/>
     </row>
     <row r="79" spans="11:20">
       <c r="K79" s="17"/>
@@ -5310,7 +4968,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="14"/>
       <c r="S79" s="19"/>
-      <c r="T79" s="29"/>
+      <c r="T79" s="33"/>
     </row>
     <row r="81" spans="11:20">
       <c r="K81" s="11"/>
@@ -5334,7 +4992,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
       <c r="S82" s="16"/>
-      <c r="T82" s="28"/>
+      <c r="T82" s="30"/>
     </row>
     <row r="83" spans="11:20">
       <c r="K83" s="17"/>
@@ -5346,7 +5004,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="14"/>
       <c r="S83" s="19"/>
-      <c r="T83" s="29"/>
+      <c r="T83" s="33"/>
     </row>
     <row r="85" spans="11:20">
       <c r="K85" s="11"/>
@@ -5370,7 +5028,7 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
       <c r="S86" s="16"/>
-      <c r="T86" s="28"/>
+      <c r="T86" s="30"/>
     </row>
     <row r="87" spans="11:20">
       <c r="K87" s="17"/>
@@ -5382,7 +5040,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="14"/>
       <c r="S87" s="19"/>
-      <c r="T87" s="29"/>
+      <c r="T87" s="33"/>
     </row>
     <row r="89" spans="11:20">
       <c r="K89" s="11"/>
@@ -5406,7 +5064,7 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="28"/>
+      <c r="T90" s="30"/>
     </row>
     <row r="91" spans="11:20">
       <c r="K91" s="17"/>
@@ -5418,7 +5076,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="14"/>
       <c r="S91" s="19"/>
-      <c r="T91" s="29"/>
+      <c r="T91" s="33"/>
     </row>
     <row r="93" spans="11:20">
       <c r="K93" s="11"/>
@@ -5442,7 +5100,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="28"/>
+      <c r="T94" s="30"/>
     </row>
     <row r="95" spans="11:20">
       <c r="K95" s="17"/>
@@ -5454,7 +5112,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="14"/>
       <c r="S95" s="19"/>
-      <c r="T95" s="29"/>
+      <c r="T95" s="33"/>
     </row>
     <row r="97" spans="11:20">
       <c r="K97" s="11"/>
@@ -5478,7 +5136,7 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
       <c r="S98" s="16"/>
-      <c r="T98" s="28"/>
+      <c r="T98" s="30"/>
     </row>
     <row r="99" spans="11:20">
       <c r="K99" s="17"/>
@@ -5490,7 +5148,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="14"/>
       <c r="S99" s="19"/>
-      <c r="T99" s="29"/>
+      <c r="T99" s="33"/>
     </row>
     <row r="101" spans="11:20">
       <c r="K101" s="11"/>
@@ -5514,7 +5172,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
       <c r="S102" s="16"/>
-      <c r="T102" s="28"/>
+      <c r="T102" s="30"/>
     </row>
     <row r="103" spans="11:20">
       <c r="K103" s="17"/>
@@ -5526,7 +5184,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="14"/>
       <c r="S103" s="19"/>
-      <c r="T103" s="29"/>
+      <c r="T103" s="33"/>
     </row>
     <row r="105" spans="11:20">
       <c r="K105" s="11"/>
@@ -5550,7 +5208,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
       <c r="S106" s="16"/>
-      <c r="T106" s="28"/>
+      <c r="T106" s="30"/>
     </row>
     <row r="107" spans="11:20">
       <c r="K107" s="17"/>
@@ -5562,7 +5220,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="14"/>
       <c r="S107" s="19"/>
-      <c r="T107" s="29"/>
+      <c r="T107" s="33"/>
     </row>
     <row r="109" spans="11:20">
       <c r="K109" s="11"/>
@@ -5586,7 +5244,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
       <c r="S110" s="16"/>
-      <c r="T110" s="28"/>
+      <c r="T110" s="30"/>
     </row>
     <row r="111" spans="11:20">
       <c r="K111" s="17"/>
@@ -5598,7 +5256,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="14"/>
       <c r="S111" s="19"/>
-      <c r="T111" s="29"/>
+      <c r="T111" s="33"/>
     </row>
     <row r="113" spans="11:20">
       <c r="K113" s="11"/>
@@ -5622,7 +5280,7 @@
       <c r="Q114" s="15"/>
       <c r="R114" s="14"/>
       <c r="S114" s="16"/>
-      <c r="T114" s="28"/>
+      <c r="T114" s="30"/>
     </row>
     <row r="115" spans="11:20">
       <c r="K115" s="17"/>
@@ -5634,7 +5292,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="14"/>
       <c r="S115" s="19"/>
-      <c r="T115" s="29"/>
+      <c r="T115" s="33"/>
     </row>
     <row r="117" spans="11:20">
       <c r="K117" s="11"/>
@@ -5658,7 +5316,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
       <c r="S118" s="16"/>
-      <c r="T118" s="28"/>
+      <c r="T118" s="30"/>
     </row>
     <row r="119" spans="11:20">
       <c r="K119" s="17"/>
@@ -5670,7 +5328,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="14"/>
       <c r="S119" s="19"/>
-      <c r="T119" s="29"/>
+      <c r="T119" s="33"/>
     </row>
     <row r="121" spans="11:20">
       <c r="K121" s="11"/>
@@ -5694,7 +5352,7 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
       <c r="S122" s="16"/>
-      <c r="T122" s="28"/>
+      <c r="T122" s="30"/>
     </row>
     <row r="123" spans="11:20">
       <c r="K123" s="17"/>
@@ -5706,17 +5364,18 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="14"/>
       <c r="S123" s="19"/>
-      <c r="T123" s="29"/>
+      <c r="T123" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="T42:T43"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="T118:T119"/>
+    <mergeCell ref="T122:T123"/>
+    <mergeCell ref="T94:T95"/>
+    <mergeCell ref="T98:T99"/>
+    <mergeCell ref="T102:T103"/>
+    <mergeCell ref="T106:T107"/>
+    <mergeCell ref="T110:T111"/>
+    <mergeCell ref="T114:T115"/>
     <mergeCell ref="T90:T91"/>
     <mergeCell ref="T46:T47"/>
     <mergeCell ref="T50:T51"/>
@@ -5729,14 +5388,13 @@
     <mergeCell ref="T78:T79"/>
     <mergeCell ref="T82:T83"/>
     <mergeCell ref="T86:T87"/>
-    <mergeCell ref="T118:T119"/>
-    <mergeCell ref="T122:T123"/>
-    <mergeCell ref="T94:T95"/>
-    <mergeCell ref="T98:T99"/>
-    <mergeCell ref="T102:T103"/>
-    <mergeCell ref="T106:T107"/>
-    <mergeCell ref="T110:T111"/>
-    <mergeCell ref="T114:T115"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="T42:T43"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="T38:T39"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>
@@ -5759,1925 +5417,2084 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="45" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="56" t="s">
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="45" t="s">
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="60" t="s">
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+      <c r="AA1" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="60"/>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="60"/>
-      <c r="AF1" s="60"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="60"/>
-      <c r="AK1" s="34" t="s">
+      <c r="AB1" s="76"/>
+      <c r="AC1" s="76"/>
+      <c r="AD1" s="76"/>
+      <c r="AE1" s="76"/>
+      <c r="AF1" s="76"/>
+      <c r="AG1" s="76"/>
+      <c r="AH1" s="76"/>
+      <c r="AI1" s="76"/>
+      <c r="AJ1" s="76"/>
+      <c r="AK1" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="36" t="s">
+      <c r="AL1" s="61"/>
+      <c r="AM1" s="61"/>
+      <c r="AN1" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="36"/>
-      <c r="AQ1" s="34" t="s">
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="34"/>
-      <c r="AT1" s="37">
+      <c r="AR1" s="61"/>
+      <c r="AS1" s="61"/>
+      <c r="AT1" s="64">
         <f>AL7</f>
         <v>46195</v>
       </c>
-      <c r="AU1" s="37"/>
-      <c r="AV1" s="37"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="41" t="s">
+      <c r="AU1" s="64"/>
+      <c r="AV1" s="64"/>
+      <c r="AW1" s="64"/>
+      <c r="AX1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="42"/>
-      <c r="AZ1" s="42"/>
-      <c r="BA1" s="43"/>
+      <c r="AY1" s="54"/>
+      <c r="AZ1" s="54"/>
+      <c r="BA1" s="55"/>
     </row>
     <row r="2" spans="1:53">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="45" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46" t="s">
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="34" t="s">
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="76"/>
+      <c r="AB2" s="76"/>
+      <c r="AC2" s="76"/>
+      <c r="AD2" s="76"/>
+      <c r="AE2" s="76"/>
+      <c r="AF2" s="76"/>
+      <c r="AG2" s="76"/>
+      <c r="AH2" s="76"/>
+      <c r="AI2" s="76"/>
+      <c r="AJ2" s="76"/>
+      <c r="AK2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="34"/>
-      <c r="AM2" s="34"/>
-      <c r="AN2" s="36" t="s">
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AO2" s="36"/>
-      <c r="AP2" s="36"/>
-      <c r="AQ2" s="34" t="s">
+      <c r="AO2" s="62"/>
+      <c r="AP2" s="62"/>
+      <c r="AQ2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="AR2" s="34"/>
-      <c r="AS2" s="34"/>
-      <c r="AT2" s="37">
-        <v>46195</v>
-      </c>
-      <c r="AU2" s="37"/>
-      <c r="AV2" s="37"/>
-      <c r="AW2" s="37"/>
-      <c r="AX2" s="49" t="s">
+      <c r="AR2" s="61"/>
+      <c r="AS2" s="61"/>
+      <c r="AT2" s="64">
+        <v>46199</v>
+      </c>
+      <c r="AU2" s="64"/>
+      <c r="AV2" s="64"/>
+      <c r="AW2" s="64"/>
+      <c r="AX2" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="AY2" s="50"/>
-      <c r="AZ2" s="50"/>
-      <c r="BA2" s="51"/>
+      <c r="AY2" s="66"/>
+      <c r="AZ2" s="66"/>
+      <c r="BA2" s="67"/>
     </row>
     <row r="3" spans="1:53" ht="12" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="45" t="s">
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="45" t="s">
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="57" t="s">
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="34" t="s">
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="73"/>
+      <c r="AD3" s="73"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73"/>
+      <c r="AH3" s="73"/>
+      <c r="AI3" s="73"/>
+      <c r="AJ3" s="73"/>
+      <c r="AK3" s="73"/>
+      <c r="AL3" s="73"/>
+      <c r="AM3" s="73"/>
+      <c r="AN3" s="73"/>
+      <c r="AO3" s="73"/>
+      <c r="AP3" s="73"/>
+      <c r="AQ3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="34"/>
-      <c r="AS3" s="34"/>
-      <c r="AT3" s="35" t="str">
+      <c r="AR3" s="61"/>
+      <c r="AS3" s="61"/>
+      <c r="AT3" s="77" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>dr1.0</v>
-      </c>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="53"/>
-      <c r="AZ3" s="53"/>
-      <c r="BA3" s="54"/>
+        <v>dr1.1</v>
+      </c>
+      <c r="AU3" s="77"/>
+      <c r="AV3" s="77"/>
+      <c r="AW3" s="77"/>
+      <c r="AX3" s="68"/>
+      <c r="AY3" s="69"/>
+      <c r="AZ3" s="69"/>
+      <c r="BA3" s="70"/>
     </row>
     <row r="4" spans="1:53" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:53" ht="14">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="59"/>
-      <c r="S5" s="59"/>
-      <c r="T5" s="59"/>
-      <c r="U5" s="59"/>
-      <c r="V5" s="59"/>
-      <c r="W5" s="59"/>
-      <c r="X5" s="59"/>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="59"/>
-      <c r="AB5" s="59"/>
-      <c r="AC5" s="59"/>
-      <c r="AD5" s="59"/>
-      <c r="AE5" s="59"/>
-      <c r="AF5" s="59"/>
-      <c r="AG5" s="59"/>
-      <c r="AH5" s="59"/>
-      <c r="AI5" s="59"/>
-      <c r="AJ5" s="59"/>
-      <c r="AK5" s="59"/>
-      <c r="AL5" s="59"/>
-      <c r="AM5" s="59"/>
-      <c r="AN5" s="59"/>
-      <c r="AO5" s="59"/>
-      <c r="AP5" s="59"/>
-      <c r="AQ5" s="59"/>
-      <c r="AR5" s="59"/>
-      <c r="AS5" s="59"/>
-      <c r="AT5" s="59"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="59"/>
-      <c r="AW5" s="59"/>
-      <c r="AX5" s="59"/>
-      <c r="AY5" s="59"/>
-      <c r="AZ5" s="59"/>
-      <c r="BA5" s="59"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="75"/>
+      <c r="U5" s="75"/>
+      <c r="V5" s="75"/>
+      <c r="W5" s="75"/>
+      <c r="X5" s="75"/>
+      <c r="Y5" s="75"/>
+      <c r="Z5" s="75"/>
+      <c r="AA5" s="75"/>
+      <c r="AB5" s="75"/>
+      <c r="AC5" s="75"/>
+      <c r="AD5" s="75"/>
+      <c r="AE5" s="75"/>
+      <c r="AF5" s="75"/>
+      <c r="AG5" s="75"/>
+      <c r="AH5" s="75"/>
+      <c r="AI5" s="75"/>
+      <c r="AJ5" s="75"/>
+      <c r="AK5" s="75"/>
+      <c r="AL5" s="75"/>
+      <c r="AM5" s="75"/>
+      <c r="AN5" s="75"/>
+      <c r="AO5" s="75"/>
+      <c r="AP5" s="75"/>
+      <c r="AQ5" s="75"/>
+      <c r="AR5" s="75"/>
+      <c r="AS5" s="75"/>
+      <c r="AT5" s="75"/>
+      <c r="AU5" s="75"/>
+      <c r="AV5" s="75"/>
+      <c r="AW5" s="75"/>
+      <c r="AX5" s="75"/>
+      <c r="AY5" s="75"/>
+      <c r="AZ5" s="75"/>
+      <c r="BA5" s="75"/>
     </row>
     <row r="6" spans="1:53">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40" t="s">
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="40"/>
-      <c r="AB6" s="40"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="40" t="s">
+      <c r="R6" s="63"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="63"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="63"/>
+      <c r="W6" s="63"/>
+      <c r="X6" s="63"/>
+      <c r="Y6" s="63"/>
+      <c r="Z6" s="63"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
+      <c r="AH6" s="63"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
+      <c r="AL6" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="AM6" s="40"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="40"/>
-      <c r="AP6" s="40" t="s">
+      <c r="AM6" s="63"/>
+      <c r="AN6" s="63"/>
+      <c r="AO6" s="63"/>
+      <c r="AP6" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="40"/>
-      <c r="AS6" s="40" t="s">
+      <c r="AQ6" s="63"/>
+      <c r="AR6" s="63"/>
+      <c r="AS6" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="AT6" s="40"/>
-      <c r="AU6" s="40"/>
-      <c r="AV6" s="40" t="s">
+      <c r="AT6" s="63"/>
+      <c r="AU6" s="63"/>
+      <c r="AV6" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="AW6" s="40"/>
-      <c r="AX6" s="40"/>
-      <c r="AY6" s="40"/>
-      <c r="AZ6" s="40"/>
-      <c r="BA6" s="40"/>
+      <c r="AW6" s="63"/>
+      <c r="AX6" s="63"/>
+      <c r="AY6" s="63"/>
+      <c r="AZ6" s="63"/>
+      <c r="BA6" s="63"/>
     </row>
     <row r="7" spans="1:53">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="66" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="66"/>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66"/>
-      <c r="T7" s="66"/>
-      <c r="U7" s="66"/>
-      <c r="V7" s="66"/>
-      <c r="W7" s="66"/>
-      <c r="X7" s="66"/>
-      <c r="Y7" s="66"/>
-      <c r="Z7" s="66"/>
-      <c r="AA7" s="66"/>
-      <c r="AB7" s="66"/>
-      <c r="AC7" s="66"/>
-      <c r="AD7" s="66"/>
-      <c r="AE7" s="66"/>
-      <c r="AF7" s="66"/>
-      <c r="AG7" s="66"/>
-      <c r="AH7" s="66"/>
-      <c r="AI7" s="66"/>
-      <c r="AJ7" s="66"/>
-      <c r="AK7" s="66"/>
-      <c r="AL7" s="74">
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="36"/>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="36"/>
+      <c r="AH7" s="36"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="36"/>
+      <c r="AK7" s="36"/>
+      <c r="AL7" s="40">
         <v>46195</v>
       </c>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="66" t="s">
+      <c r="AM7" s="41"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="41"/>
+      <c r="AP7" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="AQ7" s="66"/>
-      <c r="AR7" s="66"/>
-      <c r="AS7" s="66"/>
-      <c r="AT7" s="66"/>
-      <c r="AU7" s="66"/>
-      <c r="AV7" s="66"/>
-      <c r="AW7" s="66"/>
-      <c r="AX7" s="66"/>
-      <c r="AY7" s="66"/>
-      <c r="AZ7" s="66"/>
-      <c r="BA7" s="66"/>
-    </row>
-    <row r="8" spans="1:53" ht="44.5" customHeight="1">
-      <c r="A8" s="61"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="70"/>
-      <c r="S8" s="70"/>
-      <c r="T8" s="70"/>
-      <c r="U8" s="70"/>
-      <c r="V8" s="70"/>
-      <c r="W8" s="70"/>
-      <c r="X8" s="70"/>
-      <c r="Y8" s="70"/>
-      <c r="Z8" s="70"/>
-      <c r="AA8" s="70"/>
-      <c r="AB8" s="70"/>
-      <c r="AC8" s="70"/>
-      <c r="AD8" s="70"/>
-      <c r="AE8" s="70"/>
-      <c r="AF8" s="70"/>
-      <c r="AG8" s="70"/>
-      <c r="AH8" s="70"/>
-      <c r="AI8" s="70"/>
-      <c r="AJ8" s="70"/>
-      <c r="AK8" s="71"/>
-      <c r="AL8" s="76"/>
-      <c r="AM8" s="77"/>
-      <c r="AN8" s="77"/>
-      <c r="AO8" s="78"/>
-      <c r="AP8" s="66"/>
-      <c r="AQ8" s="66"/>
-      <c r="AR8" s="66"/>
-      <c r="AS8" s="66"/>
-      <c r="AT8" s="66"/>
-      <c r="AU8" s="66"/>
-      <c r="AV8" s="66"/>
-      <c r="AW8" s="66"/>
-      <c r="AX8" s="66"/>
-      <c r="AY8" s="66"/>
-      <c r="AZ8" s="66"/>
-      <c r="BA8" s="66"/>
-    </row>
-    <row r="9" spans="1:53" ht="23.5" customHeight="1">
-      <c r="A9" s="61"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="67"/>
-      <c r="P9" s="67"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="70"/>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="70"/>
-      <c r="AC9" s="70"/>
-      <c r="AD9" s="70"/>
-      <c r="AE9" s="70"/>
-      <c r="AF9" s="70"/>
-      <c r="AG9" s="70"/>
-      <c r="AH9" s="70"/>
-      <c r="AI9" s="70"/>
-      <c r="AJ9" s="70"/>
-      <c r="AK9" s="71"/>
-      <c r="AL9" s="76"/>
-      <c r="AM9" s="77"/>
-      <c r="AN9" s="77"/>
-      <c r="AO9" s="78"/>
-      <c r="AP9" s="66"/>
-      <c r="AQ9" s="66"/>
-      <c r="AR9" s="66"/>
-      <c r="AS9" s="66"/>
-      <c r="AT9" s="66"/>
-      <c r="AU9" s="66"/>
-      <c r="AV9" s="66"/>
-      <c r="AW9" s="66"/>
-      <c r="AX9" s="66"/>
-      <c r="AY9" s="66"/>
-      <c r="AZ9" s="66"/>
-      <c r="BA9" s="66"/>
-    </row>
-    <row r="10" spans="1:53" ht="51" customHeight="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="67"/>
-      <c r="P10" s="67"/>
-      <c r="Q10" s="67"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-      <c r="T10" s="66"/>
-      <c r="U10" s="66"/>
-      <c r="V10" s="66"/>
-      <c r="W10" s="66"/>
-      <c r="X10" s="66"/>
-      <c r="Y10" s="66"/>
-      <c r="Z10" s="66"/>
-      <c r="AA10" s="66"/>
-      <c r="AB10" s="66"/>
-      <c r="AC10" s="66"/>
-      <c r="AD10" s="66"/>
-      <c r="AE10" s="66"/>
-      <c r="AF10" s="66"/>
-      <c r="AG10" s="66"/>
-      <c r="AH10" s="66"/>
-      <c r="AI10" s="66"/>
-      <c r="AJ10" s="66"/>
-      <c r="AK10" s="66"/>
-      <c r="AL10" s="73"/>
-      <c r="AM10" s="63"/>
-      <c r="AN10" s="63"/>
-      <c r="AO10" s="63"/>
-      <c r="AP10" s="66"/>
-      <c r="AQ10" s="66"/>
-      <c r="AR10" s="66"/>
-      <c r="AS10" s="66"/>
-      <c r="AT10" s="66"/>
-      <c r="AU10" s="66"/>
-      <c r="AV10" s="66"/>
-      <c r="AW10" s="66"/>
-      <c r="AX10" s="66"/>
-      <c r="AY10" s="66"/>
-      <c r="AZ10" s="66"/>
-      <c r="BA10" s="66"/>
-    </row>
-    <row r="11" spans="1:53" ht="37.5" customHeight="1">
-      <c r="A11" s="61"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
-      <c r="Q11" s="67"/>
-      <c r="R11" s="66"/>
-      <c r="S11" s="66"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="66"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="66"/>
-      <c r="Z11" s="66"/>
-      <c r="AA11" s="66"/>
-      <c r="AB11" s="66"/>
-      <c r="AC11" s="66"/>
-      <c r="AD11" s="66"/>
-      <c r="AE11" s="66"/>
-      <c r="AF11" s="66"/>
-      <c r="AG11" s="66"/>
-      <c r="AH11" s="66"/>
-      <c r="AI11" s="66"/>
-      <c r="AJ11" s="66"/>
-      <c r="AK11" s="66"/>
-      <c r="AL11" s="73"/>
-      <c r="AM11" s="63"/>
-      <c r="AN11" s="63"/>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="66"/>
-      <c r="AQ11" s="66"/>
-      <c r="AR11" s="66"/>
-      <c r="AS11" s="66"/>
-      <c r="AT11" s="66"/>
-      <c r="AU11" s="66"/>
-      <c r="AV11" s="66"/>
-      <c r="AW11" s="66"/>
-      <c r="AX11" s="66"/>
-      <c r="AY11" s="66"/>
-      <c r="AZ11" s="66"/>
-      <c r="BA11" s="66"/>
+      <c r="AQ7" s="36"/>
+      <c r="AR7" s="36"/>
+      <c r="AS7" s="36"/>
+      <c r="AT7" s="36"/>
+      <c r="AU7" s="36"/>
+      <c r="AV7" s="36"/>
+      <c r="AW7" s="36"/>
+      <c r="AX7" s="36"/>
+      <c r="AY7" s="36"/>
+      <c r="AZ7" s="36"/>
+      <c r="BA7" s="36"/>
+    </row>
+    <row r="8" spans="1:53">
+      <c r="A8" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="48"/>
+      <c r="AB8" s="48"/>
+      <c r="AC8" s="48"/>
+      <c r="AD8" s="48"/>
+      <c r="AE8" s="48"/>
+      <c r="AF8" s="48"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="48"/>
+      <c r="AI8" s="48"/>
+      <c r="AJ8" s="48"/>
+      <c r="AK8" s="49"/>
+      <c r="AL8" s="42">
+        <v>46199</v>
+      </c>
+      <c r="AM8" s="43"/>
+      <c r="AN8" s="43"/>
+      <c r="AO8" s="44"/>
+      <c r="AP8" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="AQ8" s="36"/>
+      <c r="AR8" s="36"/>
+      <c r="AS8" s="36"/>
+      <c r="AT8" s="36"/>
+      <c r="AU8" s="36"/>
+      <c r="AV8" s="36"/>
+      <c r="AW8" s="36"/>
+      <c r="AX8" s="36"/>
+      <c r="AY8" s="36"/>
+      <c r="AZ8" s="36"/>
+      <c r="BA8" s="36"/>
+    </row>
+    <row r="9" spans="1:53">
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="48"/>
+      <c r="AJ9" s="48"/>
+      <c r="AK9" s="49"/>
+      <c r="AL9" s="42"/>
+      <c r="AM9" s="43"/>
+      <c r="AN9" s="43"/>
+      <c r="AO9" s="44"/>
+      <c r="AP9" s="36"/>
+      <c r="AQ9" s="36"/>
+      <c r="AR9" s="36"/>
+      <c r="AS9" s="36"/>
+      <c r="AT9" s="36"/>
+      <c r="AU9" s="36"/>
+      <c r="AV9" s="36"/>
+      <c r="AW9" s="36"/>
+      <c r="AX9" s="36"/>
+      <c r="AY9" s="36"/>
+      <c r="AZ9" s="36"/>
+      <c r="BA9" s="36"/>
+    </row>
+    <row r="10" spans="1:53">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="36"/>
+      <c r="AE10" s="36"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="36"/>
+      <c r="AH10" s="36"/>
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="36"/>
+      <c r="AK10" s="36"/>
+      <c r="AL10" s="34"/>
+      <c r="AM10" s="35"/>
+      <c r="AN10" s="35"/>
+      <c r="AO10" s="35"/>
+      <c r="AP10" s="36"/>
+      <c r="AQ10" s="36"/>
+      <c r="AR10" s="36"/>
+      <c r="AS10" s="36"/>
+      <c r="AT10" s="36"/>
+      <c r="AU10" s="36"/>
+      <c r="AV10" s="36"/>
+      <c r="AW10" s="36"/>
+      <c r="AX10" s="36"/>
+      <c r="AY10" s="36"/>
+      <c r="AZ10" s="36"/>
+      <c r="BA10" s="36"/>
+    </row>
+    <row r="11" spans="1:53">
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="36"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="36"/>
+      <c r="AE11" s="36"/>
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="36"/>
+      <c r="AH11" s="36"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="36"/>
+      <c r="AK11" s="36"/>
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="36"/>
+      <c r="AQ11" s="36"/>
+      <c r="AR11" s="36"/>
+      <c r="AS11" s="36"/>
+      <c r="AT11" s="36"/>
+      <c r="AU11" s="36"/>
+      <c r="AV11" s="36"/>
+      <c r="AW11" s="36"/>
+      <c r="AX11" s="36"/>
+      <c r="AY11" s="36"/>
+      <c r="AZ11" s="36"/>
+      <c r="BA11" s="36"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="63"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="66"/>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="66"/>
-      <c r="AA12" s="66"/>
-      <c r="AB12" s="66"/>
-      <c r="AC12" s="66"/>
-      <c r="AD12" s="66"/>
-      <c r="AE12" s="66"/>
-      <c r="AF12" s="66"/>
-      <c r="AG12" s="66"/>
-      <c r="AH12" s="66"/>
-      <c r="AI12" s="66"/>
-      <c r="AJ12" s="66"/>
-      <c r="AK12" s="66"/>
-      <c r="AL12" s="73"/>
-      <c r="AM12" s="63"/>
-      <c r="AN12" s="63"/>
-      <c r="AO12" s="63"/>
-      <c r="AP12" s="66"/>
-      <c r="AQ12" s="66"/>
-      <c r="AR12" s="66"/>
-      <c r="AS12" s="66"/>
-      <c r="AT12" s="66"/>
-      <c r="AU12" s="66"/>
-      <c r="AV12" s="66"/>
-      <c r="AW12" s="66"/>
-      <c r="AX12" s="66"/>
-      <c r="AY12" s="66"/>
-      <c r="AZ12" s="66"/>
-      <c r="BA12" s="66"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="36"/>
+      <c r="AE12" s="36"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="36"/>
+      <c r="AH12" s="36"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="36"/>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="34"/>
+      <c r="AM12" s="35"/>
+      <c r="AN12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="36"/>
+      <c r="AQ12" s="36"/>
+      <c r="AR12" s="36"/>
+      <c r="AS12" s="36"/>
+      <c r="AT12" s="36"/>
+      <c r="AU12" s="36"/>
+      <c r="AV12" s="36"/>
+      <c r="AW12" s="36"/>
+      <c r="AX12" s="36"/>
+      <c r="AY12" s="36"/>
+      <c r="AZ12" s="36"/>
+      <c r="BA12" s="36"/>
     </row>
     <row r="13" spans="1:53">
-      <c r="A13" s="65"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="67"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-      <c r="U13" s="66"/>
-      <c r="V13" s="66"/>
-      <c r="W13" s="66"/>
-      <c r="X13" s="66"/>
-      <c r="Y13" s="66"/>
-      <c r="Z13" s="66"/>
-      <c r="AA13" s="66"/>
-      <c r="AB13" s="66"/>
-      <c r="AC13" s="66"/>
-      <c r="AD13" s="66"/>
-      <c r="AE13" s="66"/>
-      <c r="AF13" s="66"/>
-      <c r="AG13" s="66"/>
-      <c r="AH13" s="66"/>
-      <c r="AI13" s="66"/>
-      <c r="AJ13" s="66"/>
-      <c r="AK13" s="66"/>
-      <c r="AL13" s="79"/>
-      <c r="AM13" s="65"/>
-      <c r="AN13" s="65"/>
-      <c r="AO13" s="65"/>
-      <c r="AP13" s="66"/>
-      <c r="AQ13" s="66"/>
-      <c r="AR13" s="66"/>
-      <c r="AS13" s="68"/>
-      <c r="AT13" s="68"/>
-      <c r="AU13" s="68"/>
-      <c r="AV13" s="68"/>
-      <c r="AW13" s="68"/>
-      <c r="AX13" s="68"/>
-      <c r="AY13" s="68"/>
-      <c r="AZ13" s="68"/>
-      <c r="BA13" s="68"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="36"/>
+      <c r="AE13" s="36"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="36"/>
+      <c r="AH13" s="36"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="36"/>
+      <c r="AL13" s="45"/>
+      <c r="AM13" s="46"/>
+      <c r="AN13" s="46"/>
+      <c r="AO13" s="46"/>
+      <c r="AP13" s="36"/>
+      <c r="AQ13" s="36"/>
+      <c r="AR13" s="36"/>
+      <c r="AS13" s="38"/>
+      <c r="AT13" s="38"/>
+      <c r="AU13" s="38"/>
+      <c r="AV13" s="38"/>
+      <c r="AW13" s="38"/>
+      <c r="AX13" s="38"/>
+      <c r="AY13" s="38"/>
+      <c r="AZ13" s="38"/>
+      <c r="BA13" s="38"/>
     </row>
     <row r="14" spans="1:53">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="67"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="66"/>
-      <c r="V14" s="66"/>
-      <c r="W14" s="66"/>
-      <c r="X14" s="66"/>
-      <c r="Y14" s="66"/>
-      <c r="Z14" s="66"/>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="66"/>
-      <c r="AC14" s="66"/>
-      <c r="AD14" s="66"/>
-      <c r="AE14" s="66"/>
-      <c r="AF14" s="66"/>
-      <c r="AG14" s="66"/>
-      <c r="AH14" s="66"/>
-      <c r="AI14" s="66"/>
-      <c r="AJ14" s="66"/>
-      <c r="AK14" s="66"/>
-      <c r="AL14" s="73"/>
-      <c r="AM14" s="63"/>
-      <c r="AN14" s="63"/>
-      <c r="AO14" s="63"/>
-      <c r="AP14" s="66"/>
-      <c r="AQ14" s="66"/>
-      <c r="AR14" s="66"/>
-      <c r="AS14" s="66"/>
-      <c r="AT14" s="66"/>
-      <c r="AU14" s="66"/>
-      <c r="AV14" s="66"/>
-      <c r="AW14" s="66"/>
-      <c r="AX14" s="66"/>
-      <c r="AY14" s="66"/>
-      <c r="AZ14" s="66"/>
-      <c r="BA14" s="66"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="36"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="36"/>
+      <c r="AH14" s="36"/>
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="36"/>
+      <c r="AK14" s="36"/>
+      <c r="AL14" s="34"/>
+      <c r="AM14" s="35"/>
+      <c r="AN14" s="35"/>
+      <c r="AO14" s="35"/>
+      <c r="AP14" s="36"/>
+      <c r="AQ14" s="36"/>
+      <c r="AR14" s="36"/>
+      <c r="AS14" s="36"/>
+      <c r="AT14" s="36"/>
+      <c r="AU14" s="36"/>
+      <c r="AV14" s="36"/>
+      <c r="AW14" s="36"/>
+      <c r="AX14" s="36"/>
+      <c r="AY14" s="36"/>
+      <c r="AZ14" s="36"/>
+      <c r="BA14" s="36"/>
     </row>
     <row r="15" spans="1:53">
-      <c r="A15" s="63"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="66"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66"/>
-      <c r="Z15" s="66"/>
-      <c r="AA15" s="66"/>
-      <c r="AB15" s="66"/>
-      <c r="AC15" s="66"/>
-      <c r="AD15" s="66"/>
-      <c r="AE15" s="66"/>
-      <c r="AF15" s="66"/>
-      <c r="AG15" s="66"/>
-      <c r="AH15" s="66"/>
-      <c r="AI15" s="66"/>
-      <c r="AJ15" s="66"/>
-      <c r="AK15" s="66"/>
-      <c r="AL15" s="73"/>
-      <c r="AM15" s="63"/>
-      <c r="AN15" s="63"/>
-      <c r="AO15" s="63"/>
-      <c r="AP15" s="66"/>
-      <c r="AQ15" s="66"/>
-      <c r="AR15" s="66"/>
-      <c r="AS15" s="66"/>
-      <c r="AT15" s="66"/>
-      <c r="AU15" s="66"/>
-      <c r="AV15" s="66"/>
-      <c r="AW15" s="66"/>
-      <c r="AX15" s="66"/>
-      <c r="AY15" s="66"/>
-      <c r="AZ15" s="66"/>
-      <c r="BA15" s="66"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="36"/>
+      <c r="Y15" s="36"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="36"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="36"/>
+      <c r="AE15" s="36"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="36"/>
+      <c r="AH15" s="36"/>
+      <c r="AI15" s="36"/>
+      <c r="AJ15" s="36"/>
+      <c r="AK15" s="36"/>
+      <c r="AL15" s="34"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="36"/>
+      <c r="AQ15" s="36"/>
+      <c r="AR15" s="36"/>
+      <c r="AS15" s="36"/>
+      <c r="AT15" s="36"/>
+      <c r="AU15" s="36"/>
+      <c r="AV15" s="36"/>
+      <c r="AW15" s="36"/>
+      <c r="AX15" s="36"/>
+      <c r="AY15" s="36"/>
+      <c r="AZ15" s="36"/>
+      <c r="BA15" s="36"/>
     </row>
     <row r="16" spans="1:53">
-      <c r="A16" s="63"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
-      <c r="V16" s="66"/>
-      <c r="W16" s="66"/>
-      <c r="X16" s="66"/>
-      <c r="Y16" s="66"/>
-      <c r="Z16" s="66"/>
-      <c r="AA16" s="66"/>
-      <c r="AB16" s="66"/>
-      <c r="AC16" s="66"/>
-      <c r="AD16" s="66"/>
-      <c r="AE16" s="66"/>
-      <c r="AF16" s="66"/>
-      <c r="AG16" s="66"/>
-      <c r="AH16" s="66"/>
-      <c r="AI16" s="66"/>
-      <c r="AJ16" s="66"/>
-      <c r="AK16" s="66"/>
-      <c r="AL16" s="73"/>
-      <c r="AM16" s="63"/>
-      <c r="AN16" s="63"/>
-      <c r="AO16" s="63"/>
-      <c r="AP16" s="66"/>
-      <c r="AQ16" s="66"/>
-      <c r="AR16" s="66"/>
-      <c r="AS16" s="66"/>
-      <c r="AT16" s="66"/>
-      <c r="AU16" s="66"/>
-      <c r="AV16" s="66"/>
-      <c r="AW16" s="66"/>
-      <c r="AX16" s="66"/>
-      <c r="AY16" s="66"/>
-      <c r="AZ16" s="66"/>
-      <c r="BA16" s="66"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="36"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="36"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="36"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="36"/>
+      <c r="AE16" s="36"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="36"/>
+      <c r="AH16" s="36"/>
+      <c r="AI16" s="36"/>
+      <c r="AJ16" s="36"/>
+      <c r="AK16" s="36"/>
+      <c r="AL16" s="34"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="36"/>
+      <c r="AQ16" s="36"/>
+      <c r="AR16" s="36"/>
+      <c r="AS16" s="36"/>
+      <c r="AT16" s="36"/>
+      <c r="AU16" s="36"/>
+      <c r="AV16" s="36"/>
+      <c r="AW16" s="36"/>
+      <c r="AX16" s="36"/>
+      <c r="AY16" s="36"/>
+      <c r="AZ16" s="36"/>
+      <c r="BA16" s="36"/>
     </row>
     <row r="17" spans="1:53">
-      <c r="A17" s="64"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="72"/>
-      <c r="V17" s="72"/>
-      <c r="W17" s="72"/>
-      <c r="X17" s="72"/>
-      <c r="Y17" s="72"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="72"/>
-      <c r="AC17" s="72"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="72"/>
-      <c r="AL17" s="73"/>
-      <c r="AM17" s="63"/>
-      <c r="AN17" s="63"/>
-      <c r="AO17" s="63"/>
-      <c r="AP17" s="66"/>
-      <c r="AQ17" s="72"/>
-      <c r="AR17" s="72"/>
-      <c r="AS17" s="72"/>
-      <c r="AT17" s="72"/>
-      <c r="AU17" s="72"/>
-      <c r="AV17" s="72"/>
-      <c r="AW17" s="72"/>
-      <c r="AX17" s="72"/>
-      <c r="AY17" s="72"/>
-      <c r="AZ17" s="72"/>
-      <c r="BA17" s="72"/>
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="39"/>
+      <c r="X17" s="39"/>
+      <c r="Y17" s="39"/>
+      <c r="Z17" s="39"/>
+      <c r="AA17" s="39"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
+      <c r="AE17" s="39"/>
+      <c r="AF17" s="39"/>
+      <c r="AG17" s="39"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="39"/>
+      <c r="AJ17" s="39"/>
+      <c r="AK17" s="39"/>
+      <c r="AL17" s="34"/>
+      <c r="AM17" s="35"/>
+      <c r="AN17" s="35"/>
+      <c r="AO17" s="35"/>
+      <c r="AP17" s="36"/>
+      <c r="AQ17" s="39"/>
+      <c r="AR17" s="39"/>
+      <c r="AS17" s="39"/>
+      <c r="AT17" s="39"/>
+      <c r="AU17" s="39"/>
+      <c r="AV17" s="39"/>
+      <c r="AW17" s="39"/>
+      <c r="AX17" s="39"/>
+      <c r="AY17" s="39"/>
+      <c r="AZ17" s="39"/>
+      <c r="BA17" s="39"/>
     </row>
     <row r="18" spans="1:53">
-      <c r="A18" s="64"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
-      <c r="U18" s="72"/>
-      <c r="V18" s="72"/>
-      <c r="W18" s="72"/>
-      <c r="X18" s="72"/>
-      <c r="Y18" s="72"/>
-      <c r="Z18" s="72"/>
-      <c r="AA18" s="72"/>
-      <c r="AB18" s="72"/>
-      <c r="AC18" s="72"/>
-      <c r="AD18" s="72"/>
-      <c r="AE18" s="72"/>
-      <c r="AF18" s="72"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="72"/>
-      <c r="AJ18" s="72"/>
-      <c r="AK18" s="72"/>
-      <c r="AL18" s="73"/>
-      <c r="AM18" s="63"/>
-      <c r="AN18" s="63"/>
-      <c r="AO18" s="63"/>
-      <c r="AP18" s="66"/>
-      <c r="AQ18" s="72"/>
-      <c r="AR18" s="72"/>
-      <c r="AS18" s="72"/>
-      <c r="AT18" s="72"/>
-      <c r="AU18" s="72"/>
-      <c r="AV18" s="72"/>
-      <c r="AW18" s="72"/>
-      <c r="AX18" s="72"/>
-      <c r="AY18" s="72"/>
-      <c r="AZ18" s="72"/>
-      <c r="BA18" s="72"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="39"/>
+      <c r="V18" s="39"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="39"/>
+      <c r="Y18" s="39"/>
+      <c r="Z18" s="39"/>
+      <c r="AA18" s="39"/>
+      <c r="AB18" s="39"/>
+      <c r="AC18" s="39"/>
+      <c r="AD18" s="39"/>
+      <c r="AE18" s="39"/>
+      <c r="AF18" s="39"/>
+      <c r="AG18" s="39"/>
+      <c r="AH18" s="39"/>
+      <c r="AI18" s="39"/>
+      <c r="AJ18" s="39"/>
+      <c r="AK18" s="39"/>
+      <c r="AL18" s="34"/>
+      <c r="AM18" s="35"/>
+      <c r="AN18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="36"/>
+      <c r="AQ18" s="39"/>
+      <c r="AR18" s="39"/>
+      <c r="AS18" s="39"/>
+      <c r="AT18" s="39"/>
+      <c r="AU18" s="39"/>
+      <c r="AV18" s="39"/>
+      <c r="AW18" s="39"/>
+      <c r="AX18" s="39"/>
+      <c r="AY18" s="39"/>
+      <c r="AZ18" s="39"/>
+      <c r="BA18" s="39"/>
     </row>
     <row r="19" spans="1:53">
-      <c r="A19" s="63"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="66"/>
-      <c r="V19" s="66"/>
-      <c r="W19" s="66"/>
-      <c r="X19" s="66"/>
-      <c r="Y19" s="66"/>
-      <c r="Z19" s="66"/>
-      <c r="AA19" s="66"/>
-      <c r="AB19" s="66"/>
-      <c r="AC19" s="66"/>
-      <c r="AD19" s="66"/>
-      <c r="AE19" s="66"/>
-      <c r="AF19" s="66"/>
-      <c r="AG19" s="66"/>
-      <c r="AH19" s="66"/>
-      <c r="AI19" s="66"/>
-      <c r="AJ19" s="66"/>
-      <c r="AK19" s="66"/>
-      <c r="AL19" s="73"/>
-      <c r="AM19" s="73"/>
-      <c r="AN19" s="73"/>
-      <c r="AO19" s="73"/>
-      <c r="AP19" s="66"/>
-      <c r="AQ19" s="66"/>
-      <c r="AR19" s="66"/>
-      <c r="AS19" s="66"/>
-      <c r="AT19" s="66"/>
-      <c r="AU19" s="66"/>
-      <c r="AV19" s="66"/>
-      <c r="AW19" s="66"/>
-      <c r="AX19" s="66"/>
-      <c r="AY19" s="66"/>
-      <c r="AZ19" s="66"/>
-      <c r="BA19" s="66"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="36"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="36"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="36"/>
+      <c r="AE19" s="36"/>
+      <c r="AF19" s="36"/>
+      <c r="AG19" s="36"/>
+      <c r="AH19" s="36"/>
+      <c r="AI19" s="36"/>
+      <c r="AJ19" s="36"/>
+      <c r="AK19" s="36"/>
+      <c r="AL19" s="34"/>
+      <c r="AM19" s="34"/>
+      <c r="AN19" s="34"/>
+      <c r="AO19" s="34"/>
+      <c r="AP19" s="36"/>
+      <c r="AQ19" s="36"/>
+      <c r="AR19" s="36"/>
+      <c r="AS19" s="36"/>
+      <c r="AT19" s="36"/>
+      <c r="AU19" s="36"/>
+      <c r="AV19" s="36"/>
+      <c r="AW19" s="36"/>
+      <c r="AX19" s="36"/>
+      <c r="AY19" s="36"/>
+      <c r="AZ19" s="36"/>
+      <c r="BA19" s="36"/>
     </row>
     <row r="20" spans="1:53">
-      <c r="A20" s="63"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="66"/>
-      <c r="V20" s="66"/>
-      <c r="W20" s="66"/>
-      <c r="X20" s="66"/>
-      <c r="Y20" s="66"/>
-      <c r="Z20" s="66"/>
-      <c r="AA20" s="66"/>
-      <c r="AB20" s="66"/>
-      <c r="AC20" s="66"/>
-      <c r="AD20" s="66"/>
-      <c r="AE20" s="66"/>
-      <c r="AF20" s="66"/>
-      <c r="AG20" s="66"/>
-      <c r="AH20" s="66"/>
-      <c r="AI20" s="66"/>
-      <c r="AJ20" s="66"/>
-      <c r="AK20" s="66"/>
-      <c r="AL20" s="73"/>
-      <c r="AM20" s="73"/>
-      <c r="AN20" s="73"/>
-      <c r="AO20" s="73"/>
-      <c r="AP20" s="66"/>
-      <c r="AQ20" s="66"/>
-      <c r="AR20" s="66"/>
-      <c r="AS20" s="66"/>
-      <c r="AT20" s="66"/>
-      <c r="AU20" s="66"/>
-      <c r="AV20" s="66"/>
-      <c r="AW20" s="66"/>
-      <c r="AX20" s="66"/>
-      <c r="AY20" s="66"/>
-      <c r="AZ20" s="66"/>
-      <c r="BA20" s="66"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="36"/>
+      <c r="AE20" s="36"/>
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="36"/>
+      <c r="AH20" s="36"/>
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="36"/>
+      <c r="AK20" s="36"/>
+      <c r="AL20" s="34"/>
+      <c r="AM20" s="34"/>
+      <c r="AN20" s="34"/>
+      <c r="AO20" s="34"/>
+      <c r="AP20" s="36"/>
+      <c r="AQ20" s="36"/>
+      <c r="AR20" s="36"/>
+      <c r="AS20" s="36"/>
+      <c r="AT20" s="36"/>
+      <c r="AU20" s="36"/>
+      <c r="AV20" s="36"/>
+      <c r="AW20" s="36"/>
+      <c r="AX20" s="36"/>
+      <c r="AY20" s="36"/>
+      <c r="AZ20" s="36"/>
+      <c r="BA20" s="36"/>
     </row>
     <row r="21" spans="1:53" ht="13.5" customHeight="1">
-      <c r="A21" s="63"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="72"/>
-      <c r="V21" s="72"/>
-      <c r="W21" s="72"/>
-      <c r="X21" s="72"/>
-      <c r="Y21" s="72"/>
-      <c r="Z21" s="72"/>
-      <c r="AA21" s="72"/>
-      <c r="AB21" s="72"/>
-      <c r="AC21" s="72"/>
-      <c r="AD21" s="72"/>
-      <c r="AE21" s="72"/>
-      <c r="AF21" s="72"/>
-      <c r="AG21" s="72"/>
-      <c r="AH21" s="72"/>
-      <c r="AI21" s="72"/>
-      <c r="AJ21" s="72"/>
-      <c r="AK21" s="72"/>
-      <c r="AL21" s="73"/>
-      <c r="AM21" s="73"/>
-      <c r="AN21" s="73"/>
-      <c r="AO21" s="73"/>
-      <c r="AP21" s="66"/>
-      <c r="AQ21" s="66"/>
-      <c r="AR21" s="66"/>
-      <c r="AS21" s="66"/>
-      <c r="AT21" s="66"/>
-      <c r="AU21" s="66"/>
-      <c r="AV21" s="66"/>
-      <c r="AW21" s="66"/>
-      <c r="AX21" s="66"/>
-      <c r="AY21" s="66"/>
-      <c r="AZ21" s="66"/>
-      <c r="BA21" s="66"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="39"/>
+      <c r="V21" s="39"/>
+      <c r="W21" s="39"/>
+      <c r="X21" s="39"/>
+      <c r="Y21" s="39"/>
+      <c r="Z21" s="39"/>
+      <c r="AA21" s="39"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="39"/>
+      <c r="AE21" s="39"/>
+      <c r="AF21" s="39"/>
+      <c r="AG21" s="39"/>
+      <c r="AH21" s="39"/>
+      <c r="AI21" s="39"/>
+      <c r="AJ21" s="39"/>
+      <c r="AK21" s="39"/>
+      <c r="AL21" s="34"/>
+      <c r="AM21" s="34"/>
+      <c r="AN21" s="34"/>
+      <c r="AO21" s="34"/>
+      <c r="AP21" s="36"/>
+      <c r="AQ21" s="36"/>
+      <c r="AR21" s="36"/>
+      <c r="AS21" s="36"/>
+      <c r="AT21" s="36"/>
+      <c r="AU21" s="36"/>
+      <c r="AV21" s="36"/>
+      <c r="AW21" s="36"/>
+      <c r="AX21" s="36"/>
+      <c r="AY21" s="36"/>
+      <c r="AZ21" s="36"/>
+      <c r="BA21" s="36"/>
     </row>
     <row r="22" spans="1:53">
-      <c r="A22" s="63"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="66"/>
-      <c r="AE22" s="66"/>
-      <c r="AF22" s="66"/>
-      <c r="AG22" s="66"/>
-      <c r="AH22" s="66"/>
-      <c r="AI22" s="66"/>
-      <c r="AJ22" s="66"/>
-      <c r="AK22" s="66"/>
-      <c r="AL22" s="73"/>
-      <c r="AM22" s="73"/>
-      <c r="AN22" s="73"/>
-      <c r="AO22" s="73"/>
-      <c r="AP22" s="66"/>
-      <c r="AQ22" s="66"/>
-      <c r="AR22" s="66"/>
-      <c r="AS22" s="66"/>
-      <c r="AT22" s="66"/>
-      <c r="AU22" s="66"/>
-      <c r="AV22" s="66"/>
-      <c r="AW22" s="66"/>
-      <c r="AX22" s="66"/>
-      <c r="AY22" s="66"/>
-      <c r="AZ22" s="66"/>
-      <c r="BA22" s="66"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
+      <c r="AE22" s="36"/>
+      <c r="AF22" s="36"/>
+      <c r="AG22" s="36"/>
+      <c r="AH22" s="36"/>
+      <c r="AI22" s="36"/>
+      <c r="AJ22" s="36"/>
+      <c r="AK22" s="36"/>
+      <c r="AL22" s="34"/>
+      <c r="AM22" s="34"/>
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="34"/>
+      <c r="AP22" s="36"/>
+      <c r="AQ22" s="36"/>
+      <c r="AR22" s="36"/>
+      <c r="AS22" s="36"/>
+      <c r="AT22" s="36"/>
+      <c r="AU22" s="36"/>
+      <c r="AV22" s="36"/>
+      <c r="AW22" s="36"/>
+      <c r="AX22" s="36"/>
+      <c r="AY22" s="36"/>
+      <c r="AZ22" s="36"/>
+      <c r="BA22" s="36"/>
     </row>
     <row r="23" spans="1:53">
-      <c r="A23" s="63"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="72"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="72"/>
-      <c r="X23" s="72"/>
-      <c r="Y23" s="72"/>
-      <c r="Z23" s="72"/>
-      <c r="AA23" s="72"/>
-      <c r="AB23" s="72"/>
-      <c r="AC23" s="72"/>
-      <c r="AD23" s="72"/>
-      <c r="AE23" s="72"/>
-      <c r="AF23" s="72"/>
-      <c r="AG23" s="72"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="72"/>
-      <c r="AJ23" s="72"/>
-      <c r="AK23" s="72"/>
-      <c r="AL23" s="73"/>
-      <c r="AM23" s="73"/>
-      <c r="AN23" s="73"/>
-      <c r="AO23" s="73"/>
-      <c r="AP23" s="66"/>
-      <c r="AQ23" s="66"/>
-      <c r="AR23" s="66"/>
-      <c r="AS23" s="66"/>
-      <c r="AT23" s="66"/>
-      <c r="AU23" s="66"/>
-      <c r="AV23" s="66"/>
-      <c r="AW23" s="66"/>
-      <c r="AX23" s="66"/>
-      <c r="AY23" s="66"/>
-      <c r="AZ23" s="66"/>
-      <c r="BA23" s="66"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="39"/>
+      <c r="V23" s="39"/>
+      <c r="W23" s="39"/>
+      <c r="X23" s="39"/>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="39"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="39"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="39"/>
+      <c r="AJ23" s="39"/>
+      <c r="AK23" s="39"/>
+      <c r="AL23" s="34"/>
+      <c r="AM23" s="34"/>
+      <c r="AN23" s="34"/>
+      <c r="AO23" s="34"/>
+      <c r="AP23" s="36"/>
+      <c r="AQ23" s="36"/>
+      <c r="AR23" s="36"/>
+      <c r="AS23" s="36"/>
+      <c r="AT23" s="36"/>
+      <c r="AU23" s="36"/>
+      <c r="AV23" s="36"/>
+      <c r="AW23" s="36"/>
+      <c r="AX23" s="36"/>
+      <c r="AY23" s="36"/>
+      <c r="AZ23" s="36"/>
+      <c r="BA23" s="36"/>
     </row>
     <row r="24" spans="1:53">
-      <c r="A24" s="63"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
-      <c r="V24" s="66"/>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="66"/>
-      <c r="Z24" s="66"/>
-      <c r="AA24" s="66"/>
-      <c r="AB24" s="66"/>
-      <c r="AC24" s="66"/>
-      <c r="AD24" s="66"/>
-      <c r="AE24" s="66"/>
-      <c r="AF24" s="66"/>
-      <c r="AG24" s="66"/>
-      <c r="AH24" s="66"/>
-      <c r="AI24" s="66"/>
-      <c r="AJ24" s="66"/>
-      <c r="AK24" s="66"/>
-      <c r="AL24" s="73"/>
-      <c r="AM24" s="73"/>
-      <c r="AN24" s="73"/>
-      <c r="AO24" s="73"/>
-      <c r="AP24" s="66"/>
-      <c r="AQ24" s="66"/>
-      <c r="AR24" s="66"/>
-      <c r="AS24" s="66"/>
-      <c r="AT24" s="66"/>
-      <c r="AU24" s="66"/>
-      <c r="AV24" s="66"/>
-      <c r="AW24" s="66"/>
-      <c r="AX24" s="66"/>
-      <c r="AY24" s="66"/>
-      <c r="AZ24" s="66"/>
-      <c r="BA24" s="66"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="36"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="36"/>
+      <c r="AE24" s="36"/>
+      <c r="AF24" s="36"/>
+      <c r="AG24" s="36"/>
+      <c r="AH24" s="36"/>
+      <c r="AI24" s="36"/>
+      <c r="AJ24" s="36"/>
+      <c r="AK24" s="36"/>
+      <c r="AL24" s="34"/>
+      <c r="AM24" s="34"/>
+      <c r="AN24" s="34"/>
+      <c r="AO24" s="34"/>
+      <c r="AP24" s="36"/>
+      <c r="AQ24" s="36"/>
+      <c r="AR24" s="36"/>
+      <c r="AS24" s="36"/>
+      <c r="AT24" s="36"/>
+      <c r="AU24" s="36"/>
+      <c r="AV24" s="36"/>
+      <c r="AW24" s="36"/>
+      <c r="AX24" s="36"/>
+      <c r="AY24" s="36"/>
+      <c r="AZ24" s="36"/>
+      <c r="BA24" s="36"/>
     </row>
     <row r="25" spans="1:53">
-      <c r="A25" s="63"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="66"/>
-      <c r="Y25" s="66"/>
-      <c r="Z25" s="66"/>
-      <c r="AA25" s="66"/>
-      <c r="AB25" s="66"/>
-      <c r="AC25" s="66"/>
-      <c r="AD25" s="66"/>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
-      <c r="AI25" s="66"/>
-      <c r="AJ25" s="66"/>
-      <c r="AK25" s="66"/>
-      <c r="AL25" s="73"/>
-      <c r="AM25" s="63"/>
-      <c r="AN25" s="63"/>
-      <c r="AO25" s="63"/>
-      <c r="AP25" s="66"/>
-      <c r="AQ25" s="66"/>
-      <c r="AR25" s="66"/>
-      <c r="AS25" s="66"/>
-      <c r="AT25" s="66"/>
-      <c r="AU25" s="66"/>
-      <c r="AV25" s="66"/>
-      <c r="AW25" s="66"/>
-      <c r="AX25" s="66"/>
-      <c r="AY25" s="66"/>
-      <c r="AZ25" s="66"/>
-      <c r="BA25" s="66"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="36"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="36"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="36"/>
+      <c r="AE25" s="36"/>
+      <c r="AF25" s="36"/>
+      <c r="AG25" s="36"/>
+      <c r="AH25" s="36"/>
+      <c r="AI25" s="36"/>
+      <c r="AJ25" s="36"/>
+      <c r="AK25" s="36"/>
+      <c r="AL25" s="34"/>
+      <c r="AM25" s="35"/>
+      <c r="AN25" s="35"/>
+      <c r="AO25" s="35"/>
+      <c r="AP25" s="36"/>
+      <c r="AQ25" s="36"/>
+      <c r="AR25" s="36"/>
+      <c r="AS25" s="36"/>
+      <c r="AT25" s="36"/>
+      <c r="AU25" s="36"/>
+      <c r="AV25" s="36"/>
+      <c r="AW25" s="36"/>
+      <c r="AX25" s="36"/>
+      <c r="AY25" s="36"/>
+      <c r="AZ25" s="36"/>
+      <c r="BA25" s="36"/>
     </row>
     <row r="26" spans="1:53">
-      <c r="A26" s="63"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="66"/>
-      <c r="Z26" s="66"/>
-      <c r="AA26" s="66"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="66"/>
-      <c r="AD26" s="66"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="66"/>
-      <c r="AI26" s="66"/>
-      <c r="AJ26" s="66"/>
-      <c r="AK26" s="66"/>
-      <c r="AL26" s="73"/>
-      <c r="AM26" s="63"/>
-      <c r="AN26" s="63"/>
-      <c r="AO26" s="63"/>
-      <c r="AP26" s="66"/>
-      <c r="AQ26" s="66"/>
-      <c r="AR26" s="66"/>
-      <c r="AS26" s="66"/>
-      <c r="AT26" s="66"/>
-      <c r="AU26" s="66"/>
-      <c r="AV26" s="66"/>
-      <c r="AW26" s="66"/>
-      <c r="AX26" s="66"/>
-      <c r="AY26" s="66"/>
-      <c r="AZ26" s="66"/>
-      <c r="BA26" s="66"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="36"/>
+      <c r="AA26" s="36"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="36"/>
+      <c r="AD26" s="36"/>
+      <c r="AE26" s="36"/>
+      <c r="AF26" s="36"/>
+      <c r="AG26" s="36"/>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="36"/>
+      <c r="AJ26" s="36"/>
+      <c r="AK26" s="36"/>
+      <c r="AL26" s="34"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="35"/>
+      <c r="AO26" s="35"/>
+      <c r="AP26" s="36"/>
+      <c r="AQ26" s="36"/>
+      <c r="AR26" s="36"/>
+      <c r="AS26" s="36"/>
+      <c r="AT26" s="36"/>
+      <c r="AU26" s="36"/>
+      <c r="AV26" s="36"/>
+      <c r="AW26" s="36"/>
+      <c r="AX26" s="36"/>
+      <c r="AY26" s="36"/>
+      <c r="AZ26" s="36"/>
+      <c r="BA26" s="36"/>
     </row>
     <row r="27" spans="1:53">
-      <c r="A27" s="63"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
-      <c r="U27" s="66"/>
-      <c r="V27" s="66"/>
-      <c r="W27" s="66"/>
-      <c r="X27" s="66"/>
-      <c r="Y27" s="66"/>
-      <c r="Z27" s="66"/>
-      <c r="AA27" s="66"/>
-      <c r="AB27" s="66"/>
-      <c r="AC27" s="66"/>
-      <c r="AD27" s="66"/>
-      <c r="AE27" s="66"/>
-      <c r="AF27" s="66"/>
-      <c r="AG27" s="66"/>
-      <c r="AH27" s="66"/>
-      <c r="AI27" s="66"/>
-      <c r="AJ27" s="66"/>
-      <c r="AK27" s="66"/>
-      <c r="AL27" s="73"/>
-      <c r="AM27" s="63"/>
-      <c r="AN27" s="63"/>
-      <c r="AO27" s="63"/>
-      <c r="AP27" s="66"/>
-      <c r="AQ27" s="66"/>
-      <c r="AR27" s="66"/>
-      <c r="AS27" s="66"/>
-      <c r="AT27" s="66"/>
-      <c r="AU27" s="66"/>
-      <c r="AV27" s="66"/>
-      <c r="AW27" s="66"/>
-      <c r="AX27" s="66"/>
-      <c r="AY27" s="66"/>
-      <c r="AZ27" s="66"/>
-      <c r="BA27" s="66"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="36"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="36"/>
+      <c r="AE27" s="36"/>
+      <c r="AF27" s="36"/>
+      <c r="AG27" s="36"/>
+      <c r="AH27" s="36"/>
+      <c r="AI27" s="36"/>
+      <c r="AJ27" s="36"/>
+      <c r="AK27" s="36"/>
+      <c r="AL27" s="34"/>
+      <c r="AM27" s="35"/>
+      <c r="AN27" s="35"/>
+      <c r="AO27" s="35"/>
+      <c r="AP27" s="36"/>
+      <c r="AQ27" s="36"/>
+      <c r="AR27" s="36"/>
+      <c r="AS27" s="36"/>
+      <c r="AT27" s="36"/>
+      <c r="AU27" s="36"/>
+      <c r="AV27" s="36"/>
+      <c r="AW27" s="36"/>
+      <c r="AX27" s="36"/>
+      <c r="AY27" s="36"/>
+      <c r="AZ27" s="36"/>
+      <c r="BA27" s="36"/>
     </row>
     <row r="28" spans="1:53">
-      <c r="A28" s="63"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-      <c r="V28" s="66"/>
-      <c r="W28" s="66"/>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
-      <c r="Z28" s="66"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
-      <c r="AC28" s="66"/>
-      <c r="AD28" s="66"/>
-      <c r="AE28" s="66"/>
-      <c r="AF28" s="66"/>
-      <c r="AG28" s="66"/>
-      <c r="AH28" s="66"/>
-      <c r="AI28" s="66"/>
-      <c r="AJ28" s="66"/>
-      <c r="AK28" s="66"/>
-      <c r="AL28" s="73"/>
-      <c r="AM28" s="63"/>
-      <c r="AN28" s="63"/>
-      <c r="AO28" s="63"/>
-      <c r="AP28" s="66"/>
-      <c r="AQ28" s="66"/>
-      <c r="AR28" s="66"/>
-      <c r="AS28" s="66"/>
-      <c r="AT28" s="66"/>
-      <c r="AU28" s="66"/>
-      <c r="AV28" s="66"/>
-      <c r="AW28" s="66"/>
-      <c r="AX28" s="66"/>
-      <c r="AY28" s="66"/>
-      <c r="AZ28" s="66"/>
-      <c r="BA28" s="66"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="36"/>
+      <c r="AE28" s="36"/>
+      <c r="AF28" s="36"/>
+      <c r="AG28" s="36"/>
+      <c r="AH28" s="36"/>
+      <c r="AI28" s="36"/>
+      <c r="AJ28" s="36"/>
+      <c r="AK28" s="36"/>
+      <c r="AL28" s="34"/>
+      <c r="AM28" s="35"/>
+      <c r="AN28" s="35"/>
+      <c r="AO28" s="35"/>
+      <c r="AP28" s="36"/>
+      <c r="AQ28" s="36"/>
+      <c r="AR28" s="36"/>
+      <c r="AS28" s="36"/>
+      <c r="AT28" s="36"/>
+      <c r="AU28" s="36"/>
+      <c r="AV28" s="36"/>
+      <c r="AW28" s="36"/>
+      <c r="AX28" s="36"/>
+      <c r="AY28" s="36"/>
+      <c r="AZ28" s="36"/>
+      <c r="BA28" s="36"/>
     </row>
     <row r="29" spans="1:53">
-      <c r="A29" s="63"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
-      <c r="U29" s="66"/>
-      <c r="V29" s="66"/>
-      <c r="W29" s="66"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="66"/>
-      <c r="Z29" s="66"/>
-      <c r="AA29" s="66"/>
-      <c r="AB29" s="66"/>
-      <c r="AC29" s="66"/>
-      <c r="AD29" s="66"/>
-      <c r="AE29" s="66"/>
-      <c r="AF29" s="66"/>
-      <c r="AG29" s="66"/>
-      <c r="AH29" s="66"/>
-      <c r="AI29" s="66"/>
-      <c r="AJ29" s="66"/>
-      <c r="AK29" s="66"/>
-      <c r="AL29" s="73"/>
-      <c r="AM29" s="63"/>
-      <c r="AN29" s="63"/>
-      <c r="AO29" s="63"/>
-      <c r="AP29" s="66"/>
-      <c r="AQ29" s="66"/>
-      <c r="AR29" s="66"/>
-      <c r="AS29" s="66"/>
-      <c r="AT29" s="66"/>
-      <c r="AU29" s="66"/>
-      <c r="AV29" s="66"/>
-      <c r="AW29" s="66"/>
-      <c r="AX29" s="66"/>
-      <c r="AY29" s="66"/>
-      <c r="AZ29" s="66"/>
-      <c r="BA29" s="66"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="36"/>
+      <c r="R29" s="36"/>
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="36"/>
+      <c r="W29" s="36"/>
+      <c r="X29" s="36"/>
+      <c r="Y29" s="36"/>
+      <c r="Z29" s="36"/>
+      <c r="AA29" s="36"/>
+      <c r="AB29" s="36"/>
+      <c r="AC29" s="36"/>
+      <c r="AD29" s="36"/>
+      <c r="AE29" s="36"/>
+      <c r="AF29" s="36"/>
+      <c r="AG29" s="36"/>
+      <c r="AH29" s="36"/>
+      <c r="AI29" s="36"/>
+      <c r="AJ29" s="36"/>
+      <c r="AK29" s="36"/>
+      <c r="AL29" s="34"/>
+      <c r="AM29" s="35"/>
+      <c r="AN29" s="35"/>
+      <c r="AO29" s="35"/>
+      <c r="AP29" s="36"/>
+      <c r="AQ29" s="36"/>
+      <c r="AR29" s="36"/>
+      <c r="AS29" s="36"/>
+      <c r="AT29" s="36"/>
+      <c r="AU29" s="36"/>
+      <c r="AV29" s="36"/>
+      <c r="AW29" s="36"/>
+      <c r="AX29" s="36"/>
+      <c r="AY29" s="36"/>
+      <c r="AZ29" s="36"/>
+      <c r="BA29" s="36"/>
     </row>
     <row r="30" spans="1:53">
-      <c r="A30" s="63"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="66"/>
-      <c r="V30" s="66"/>
-      <c r="W30" s="66"/>
-      <c r="X30" s="66"/>
-      <c r="Y30" s="66"/>
-      <c r="Z30" s="66"/>
-      <c r="AA30" s="66"/>
-      <c r="AB30" s="66"/>
-      <c r="AC30" s="66"/>
-      <c r="AD30" s="66"/>
-      <c r="AE30" s="66"/>
-      <c r="AF30" s="66"/>
-      <c r="AG30" s="66"/>
-      <c r="AH30" s="66"/>
-      <c r="AI30" s="66"/>
-      <c r="AJ30" s="66"/>
-      <c r="AK30" s="66"/>
-      <c r="AL30" s="63"/>
-      <c r="AM30" s="63"/>
-      <c r="AN30" s="63"/>
-      <c r="AO30" s="63"/>
-      <c r="AP30" s="66"/>
-      <c r="AQ30" s="66"/>
-      <c r="AR30" s="66"/>
-      <c r="AS30" s="66"/>
-      <c r="AT30" s="66"/>
-      <c r="AU30" s="66"/>
-      <c r="AV30" s="66"/>
-      <c r="AW30" s="66"/>
-      <c r="AX30" s="66"/>
-      <c r="AY30" s="66"/>
-      <c r="AZ30" s="66"/>
-      <c r="BA30" s="66"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="36"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="36"/>
+      <c r="Z30" s="36"/>
+      <c r="AA30" s="36"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="36"/>
+      <c r="AD30" s="36"/>
+      <c r="AE30" s="36"/>
+      <c r="AF30" s="36"/>
+      <c r="AG30" s="36"/>
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="36"/>
+      <c r="AJ30" s="36"/>
+      <c r="AK30" s="36"/>
+      <c r="AL30" s="35"/>
+      <c r="AM30" s="35"/>
+      <c r="AN30" s="35"/>
+      <c r="AO30" s="35"/>
+      <c r="AP30" s="36"/>
+      <c r="AQ30" s="36"/>
+      <c r="AR30" s="36"/>
+      <c r="AS30" s="36"/>
+      <c r="AT30" s="36"/>
+      <c r="AU30" s="36"/>
+      <c r="AV30" s="36"/>
+      <c r="AW30" s="36"/>
+      <c r="AX30" s="36"/>
+      <c r="AY30" s="36"/>
+      <c r="AZ30" s="36"/>
+      <c r="BA30" s="36"/>
     </row>
     <row r="31" spans="1:53">
-      <c r="A31" s="63"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="66"/>
-      <c r="O31" s="66"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-      <c r="V31" s="66"/>
-      <c r="W31" s="66"/>
-      <c r="X31" s="66"/>
-      <c r="Y31" s="66"/>
-      <c r="Z31" s="66"/>
-      <c r="AA31" s="66"/>
-      <c r="AB31" s="66"/>
-      <c r="AC31" s="66"/>
-      <c r="AD31" s="66"/>
-      <c r="AE31" s="66"/>
-      <c r="AF31" s="66"/>
-      <c r="AG31" s="66"/>
-      <c r="AH31" s="66"/>
-      <c r="AI31" s="66"/>
-      <c r="AJ31" s="66"/>
-      <c r="AK31" s="66"/>
-      <c r="AL31" s="63"/>
-      <c r="AM31" s="63"/>
-      <c r="AN31" s="63"/>
-      <c r="AO31" s="63"/>
-      <c r="AP31" s="66"/>
-      <c r="AQ31" s="66"/>
-      <c r="AR31" s="66"/>
-      <c r="AS31" s="66"/>
-      <c r="AT31" s="66"/>
-      <c r="AU31" s="66"/>
-      <c r="AV31" s="66"/>
-      <c r="AW31" s="66"/>
-      <c r="AX31" s="66"/>
-      <c r="AY31" s="66"/>
-      <c r="AZ31" s="66"/>
-      <c r="BA31" s="66"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
+      <c r="Z31" s="36"/>
+      <c r="AA31" s="36"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="36"/>
+      <c r="AE31" s="36"/>
+      <c r="AF31" s="36"/>
+      <c r="AG31" s="36"/>
+      <c r="AH31" s="36"/>
+      <c r="AI31" s="36"/>
+      <c r="AJ31" s="36"/>
+      <c r="AK31" s="36"/>
+      <c r="AL31" s="35"/>
+      <c r="AM31" s="35"/>
+      <c r="AN31" s="35"/>
+      <c r="AO31" s="35"/>
+      <c r="AP31" s="36"/>
+      <c r="AQ31" s="36"/>
+      <c r="AR31" s="36"/>
+      <c r="AS31" s="36"/>
+      <c r="AT31" s="36"/>
+      <c r="AU31" s="36"/>
+      <c r="AV31" s="36"/>
+      <c r="AW31" s="36"/>
+      <c r="AX31" s="36"/>
+      <c r="AY31" s="36"/>
+      <c r="AZ31" s="36"/>
+      <c r="BA31" s="36"/>
     </row>
     <row r="32" spans="1:53">
-      <c r="A32" s="63"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="66"/>
-      <c r="X32" s="66"/>
-      <c r="Y32" s="66"/>
-      <c r="Z32" s="66"/>
-      <c r="AA32" s="66"/>
-      <c r="AB32" s="66"/>
-      <c r="AC32" s="66"/>
-      <c r="AD32" s="66"/>
-      <c r="AE32" s="66"/>
-      <c r="AF32" s="66"/>
-      <c r="AG32" s="66"/>
-      <c r="AH32" s="66"/>
-      <c r="AI32" s="66"/>
-      <c r="AJ32" s="66"/>
-      <c r="AK32" s="66"/>
-      <c r="AL32" s="63"/>
-      <c r="AM32" s="63"/>
-      <c r="AN32" s="63"/>
-      <c r="AO32" s="63"/>
-      <c r="AP32" s="66"/>
-      <c r="AQ32" s="66"/>
-      <c r="AR32" s="66"/>
-      <c r="AS32" s="66"/>
-      <c r="AT32" s="66"/>
-      <c r="AU32" s="66"/>
-      <c r="AV32" s="66"/>
-      <c r="AW32" s="66"/>
-      <c r="AX32" s="66"/>
-      <c r="AY32" s="66"/>
-      <c r="AZ32" s="66"/>
-      <c r="BA32" s="66"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="36"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="36"/>
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="36"/>
+      <c r="V32" s="36"/>
+      <c r="W32" s="36"/>
+      <c r="X32" s="36"/>
+      <c r="Y32" s="36"/>
+      <c r="Z32" s="36"/>
+      <c r="AA32" s="36"/>
+      <c r="AB32" s="36"/>
+      <c r="AC32" s="36"/>
+      <c r="AD32" s="36"/>
+      <c r="AE32" s="36"/>
+      <c r="AF32" s="36"/>
+      <c r="AG32" s="36"/>
+      <c r="AH32" s="36"/>
+      <c r="AI32" s="36"/>
+      <c r="AJ32" s="36"/>
+      <c r="AK32" s="36"/>
+      <c r="AL32" s="35"/>
+      <c r="AM32" s="35"/>
+      <c r="AN32" s="35"/>
+      <c r="AO32" s="35"/>
+      <c r="AP32" s="36"/>
+      <c r="AQ32" s="36"/>
+      <c r="AR32" s="36"/>
+      <c r="AS32" s="36"/>
+      <c r="AT32" s="36"/>
+      <c r="AU32" s="36"/>
+      <c r="AV32" s="36"/>
+      <c r="AW32" s="36"/>
+      <c r="AX32" s="36"/>
+      <c r="AY32" s="36"/>
+      <c r="AZ32" s="36"/>
+      <c r="BA32" s="36"/>
     </row>
     <row r="33" spans="1:53">
-      <c r="A33" s="63"/>
-      <c r="B33" s="63"/>
-      <c r="C33" s="66"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="66"/>
-      <c r="M33" s="66"/>
-      <c r="N33" s="66"/>
-      <c r="O33" s="66"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="66"/>
-      <c r="T33" s="66"/>
-      <c r="U33" s="66"/>
-      <c r="V33" s="66"/>
-      <c r="W33" s="66"/>
-      <c r="X33" s="66"/>
-      <c r="Y33" s="66"/>
-      <c r="Z33" s="66"/>
-      <c r="AA33" s="66"/>
-      <c r="AB33" s="66"/>
-      <c r="AC33" s="66"/>
-      <c r="AD33" s="66"/>
-      <c r="AE33" s="66"/>
-      <c r="AF33" s="66"/>
-      <c r="AG33" s="66"/>
-      <c r="AH33" s="66"/>
-      <c r="AI33" s="66"/>
-      <c r="AJ33" s="66"/>
-      <c r="AK33" s="66"/>
-      <c r="AL33" s="63"/>
-      <c r="AM33" s="63"/>
-      <c r="AN33" s="63"/>
-      <c r="AO33" s="63"/>
-      <c r="AP33" s="66"/>
-      <c r="AQ33" s="66"/>
-      <c r="AR33" s="66"/>
-      <c r="AS33" s="66"/>
-      <c r="AT33" s="66"/>
-      <c r="AU33" s="66"/>
-      <c r="AV33" s="66"/>
-      <c r="AW33" s="66"/>
-      <c r="AX33" s="66"/>
-      <c r="AY33" s="66"/>
-      <c r="AZ33" s="66"/>
-      <c r="BA33" s="66"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="36"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="36"/>
+      <c r="W33" s="36"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="36"/>
+      <c r="Z33" s="36"/>
+      <c r="AA33" s="36"/>
+      <c r="AB33" s="36"/>
+      <c r="AC33" s="36"/>
+      <c r="AD33" s="36"/>
+      <c r="AE33" s="36"/>
+      <c r="AF33" s="36"/>
+      <c r="AG33" s="36"/>
+      <c r="AH33" s="36"/>
+      <c r="AI33" s="36"/>
+      <c r="AJ33" s="36"/>
+      <c r="AK33" s="36"/>
+      <c r="AL33" s="35"/>
+      <c r="AM33" s="35"/>
+      <c r="AN33" s="35"/>
+      <c r="AO33" s="35"/>
+      <c r="AP33" s="36"/>
+      <c r="AQ33" s="36"/>
+      <c r="AR33" s="36"/>
+      <c r="AS33" s="36"/>
+      <c r="AT33" s="36"/>
+      <c r="AU33" s="36"/>
+      <c r="AV33" s="36"/>
+      <c r="AW33" s="36"/>
+      <c r="AX33" s="36"/>
+      <c r="AY33" s="36"/>
+      <c r="AZ33" s="36"/>
+      <c r="BA33" s="36"/>
     </row>
     <row r="34" spans="1:53">
-      <c r="A34" s="63"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="66"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="66"/>
-      <c r="K34" s="66"/>
-      <c r="L34" s="66"/>
-      <c r="M34" s="66"/>
-      <c r="N34" s="66"/>
-      <c r="O34" s="66"/>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="66"/>
-      <c r="S34" s="66"/>
-      <c r="T34" s="66"/>
-      <c r="U34" s="66"/>
-      <c r="V34" s="66"/>
-      <c r="W34" s="66"/>
-      <c r="X34" s="66"/>
-      <c r="Y34" s="66"/>
-      <c r="Z34" s="66"/>
-      <c r="AA34" s="66"/>
-      <c r="AB34" s="66"/>
-      <c r="AC34" s="66"/>
-      <c r="AD34" s="66"/>
-      <c r="AE34" s="66"/>
-      <c r="AF34" s="66"/>
-      <c r="AG34" s="66"/>
-      <c r="AH34" s="66"/>
-      <c r="AI34" s="66"/>
-      <c r="AJ34" s="66"/>
-      <c r="AK34" s="66"/>
-      <c r="AL34" s="63"/>
-      <c r="AM34" s="63"/>
-      <c r="AN34" s="63"/>
-      <c r="AO34" s="63"/>
-      <c r="AP34" s="66"/>
-      <c r="AQ34" s="66"/>
-      <c r="AR34" s="66"/>
-      <c r="AS34" s="66"/>
-      <c r="AT34" s="66"/>
-      <c r="AU34" s="66"/>
-      <c r="AV34" s="66"/>
-      <c r="AW34" s="66"/>
-      <c r="AX34" s="66"/>
-      <c r="AY34" s="66"/>
-      <c r="AZ34" s="66"/>
-      <c r="BA34" s="66"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="36"/>
+      <c r="AA34" s="36"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="36"/>
+      <c r="AG34" s="36"/>
+      <c r="AH34" s="36"/>
+      <c r="AI34" s="36"/>
+      <c r="AJ34" s="36"/>
+      <c r="AK34" s="36"/>
+      <c r="AL34" s="35"/>
+      <c r="AM34" s="35"/>
+      <c r="AN34" s="35"/>
+      <c r="AO34" s="35"/>
+      <c r="AP34" s="36"/>
+      <c r="AQ34" s="36"/>
+      <c r="AR34" s="36"/>
+      <c r="AS34" s="36"/>
+      <c r="AT34" s="36"/>
+      <c r="AU34" s="36"/>
+      <c r="AV34" s="36"/>
+      <c r="AW34" s="36"/>
+      <c r="AX34" s="36"/>
+      <c r="AY34" s="36"/>
+      <c r="AZ34" s="36"/>
+      <c r="BA34" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="229">
-    <mergeCell ref="AL22:AO22"/>
-    <mergeCell ref="AL23:AO23"/>
-    <mergeCell ref="AL24:AO24"/>
-    <mergeCell ref="AL25:AO25"/>
-    <mergeCell ref="AL26:AO26"/>
-    <mergeCell ref="Q24:AK24"/>
-    <mergeCell ref="Q25:AK25"/>
-    <mergeCell ref="Q26:AK26"/>
-    <mergeCell ref="AP14:AR14"/>
-    <mergeCell ref="Q16:AK16"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="AP16:AR16"/>
-    <mergeCell ref="AV20:BA20"/>
-    <mergeCell ref="AV21:BA21"/>
-    <mergeCell ref="AV14:BA14"/>
-    <mergeCell ref="AV15:BA15"/>
-    <mergeCell ref="AS28:AU28"/>
-    <mergeCell ref="AS30:AU30"/>
-    <mergeCell ref="AS31:AU31"/>
-    <mergeCell ref="AS25:AU25"/>
-    <mergeCell ref="AP31:AR31"/>
-    <mergeCell ref="AP27:AR27"/>
-    <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS16:AU16"/>
-    <mergeCell ref="AP15:AR15"/>
-    <mergeCell ref="AS26:AU26"/>
-    <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="AK1:AM1"/>
+    <mergeCell ref="AT3:AW3"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="Q6:AK6"/>
+    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AX1:BA1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:W2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AP6:AR6"/>
+    <mergeCell ref="AS6:AU6"/>
+    <mergeCell ref="AT2:AW2"/>
+    <mergeCell ref="AX2:BA3"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AA3:AP3"/>
+    <mergeCell ref="AQ3:AS3"/>
+    <mergeCell ref="AV6:BA6"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A5:BA5"/>
+    <mergeCell ref="M1:W1"/>
+    <mergeCell ref="X1:Z2"/>
+    <mergeCell ref="AA1:AJ2"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C33:P33"/>
+    <mergeCell ref="C27:P27"/>
+    <mergeCell ref="C28:P28"/>
+    <mergeCell ref="C24:P24"/>
+    <mergeCell ref="C25:P25"/>
+    <mergeCell ref="C26:P26"/>
+    <mergeCell ref="C29:P29"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="C23:P23"/>
+    <mergeCell ref="C7:P7"/>
+    <mergeCell ref="C8:P8"/>
+    <mergeCell ref="C9:P9"/>
+    <mergeCell ref="C10:P10"/>
+    <mergeCell ref="C18:P18"/>
+    <mergeCell ref="C19:P19"/>
+    <mergeCell ref="C20:P20"/>
+    <mergeCell ref="C21:P21"/>
+    <mergeCell ref="C11:P11"/>
+    <mergeCell ref="C12:P12"/>
+    <mergeCell ref="C13:P13"/>
+    <mergeCell ref="C34:P34"/>
+    <mergeCell ref="Q7:AK7"/>
+    <mergeCell ref="Q8:AK8"/>
+    <mergeCell ref="Q9:AK9"/>
+    <mergeCell ref="Q10:AK10"/>
+    <mergeCell ref="Q11:AK11"/>
+    <mergeCell ref="Q12:AK12"/>
+    <mergeCell ref="Q19:AK19"/>
+    <mergeCell ref="Q20:AK20"/>
+    <mergeCell ref="Q21:AK21"/>
+    <mergeCell ref="Q13:AK13"/>
+    <mergeCell ref="Q34:AK34"/>
+    <mergeCell ref="Q30:AK30"/>
+    <mergeCell ref="Q31:AK31"/>
+    <mergeCell ref="Q32:AK32"/>
+    <mergeCell ref="Q33:AK33"/>
+    <mergeCell ref="Q23:AK23"/>
+    <mergeCell ref="C17:P17"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="C15:P15"/>
+    <mergeCell ref="C16:P16"/>
+    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C31:P31"/>
+    <mergeCell ref="C32:P32"/>
+    <mergeCell ref="AL29:AO29"/>
+    <mergeCell ref="AL27:AO27"/>
+    <mergeCell ref="AL28:AO28"/>
+    <mergeCell ref="Q29:AK29"/>
+    <mergeCell ref="Q27:AK27"/>
+    <mergeCell ref="Q28:AK28"/>
+    <mergeCell ref="AL7:AO7"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL17:AO17"/>
+    <mergeCell ref="AL18:AO18"/>
+    <mergeCell ref="AL19:AO19"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="AL10:AO10"/>
+    <mergeCell ref="AL11:AO11"/>
+    <mergeCell ref="AL12:AO12"/>
+    <mergeCell ref="AL13:AO13"/>
+    <mergeCell ref="AL21:AO21"/>
+    <mergeCell ref="Q17:AK17"/>
+    <mergeCell ref="Q18:AK18"/>
+    <mergeCell ref="Q22:AK22"/>
+    <mergeCell ref="Q14:AK14"/>
+    <mergeCell ref="AL14:AO14"/>
+    <mergeCell ref="Q15:AK15"/>
+    <mergeCell ref="AL15:AO15"/>
+    <mergeCell ref="AL32:AO32"/>
+    <mergeCell ref="AL33:AO33"/>
+    <mergeCell ref="AL34:AO34"/>
+    <mergeCell ref="AP7:AR7"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AP20:AR20"/>
+    <mergeCell ref="AP21:AR21"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AP12:AR12"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AL30:AO30"/>
+    <mergeCell ref="AL31:AO31"/>
+    <mergeCell ref="AL20:AO20"/>
+    <mergeCell ref="AP26:AR26"/>
+    <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="AP34:AR34"/>
+    <mergeCell ref="AS7:AU7"/>
+    <mergeCell ref="AS8:AU8"/>
+    <mergeCell ref="AS9:AU9"/>
+    <mergeCell ref="AS10:AU10"/>
+    <mergeCell ref="AS11:AU11"/>
+    <mergeCell ref="AS12:AU12"/>
+    <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="AS17:AU17"/>
+    <mergeCell ref="AS18:AU18"/>
+    <mergeCell ref="AS22:AU22"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AS24:AU24"/>
+    <mergeCell ref="AS29:AU29"/>
+    <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="AS32:AU32"/>
+    <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="AV7:BA7"/>
     <mergeCell ref="AV8:BA8"/>
     <mergeCell ref="AV9:BA9"/>
@@ -7702,183 +7519,34 @@
     <mergeCell ref="AV18:BA18"/>
     <mergeCell ref="AV19:BA19"/>
     <mergeCell ref="AV16:BA16"/>
-    <mergeCell ref="AS34:AU34"/>
-    <mergeCell ref="AP34:AR34"/>
-    <mergeCell ref="AS7:AU7"/>
-    <mergeCell ref="AS8:AU8"/>
-    <mergeCell ref="AS9:AU9"/>
-    <mergeCell ref="AS10:AU10"/>
-    <mergeCell ref="AS11:AU11"/>
-    <mergeCell ref="AS12:AU12"/>
-    <mergeCell ref="AS19:AU19"/>
-    <mergeCell ref="AS20:AU20"/>
-    <mergeCell ref="AS21:AU21"/>
-    <mergeCell ref="AS13:AU13"/>
-    <mergeCell ref="AS17:AU17"/>
-    <mergeCell ref="AS18:AU18"/>
-    <mergeCell ref="AS22:AU22"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AS24:AU24"/>
-    <mergeCell ref="AS29:AU29"/>
-    <mergeCell ref="AS27:AU27"/>
-    <mergeCell ref="AS32:AU32"/>
-    <mergeCell ref="AS33:AU33"/>
-    <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="AP25:AR25"/>
-    <mergeCell ref="AP32:AR32"/>
-    <mergeCell ref="AL32:AO32"/>
-    <mergeCell ref="AL33:AO33"/>
-    <mergeCell ref="AL34:AO34"/>
-    <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AP20:AR20"/>
-    <mergeCell ref="AP21:AR21"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="AP12:AR12"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="AP17:AR17"/>
-    <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AL30:AO30"/>
-    <mergeCell ref="AL31:AO31"/>
-    <mergeCell ref="AL20:AO20"/>
-    <mergeCell ref="AP26:AR26"/>
-    <mergeCell ref="AP29:AR29"/>
-    <mergeCell ref="AP30:AR30"/>
-    <mergeCell ref="AP33:AR33"/>
-    <mergeCell ref="AL29:AO29"/>
-    <mergeCell ref="AL27:AO27"/>
-    <mergeCell ref="AL28:AO28"/>
-    <mergeCell ref="Q29:AK29"/>
-    <mergeCell ref="Q27:AK27"/>
-    <mergeCell ref="Q28:AK28"/>
-    <mergeCell ref="AL7:AO7"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AL18:AO18"/>
-    <mergeCell ref="AL19:AO19"/>
-    <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="AL10:AO10"/>
-    <mergeCell ref="AL11:AO11"/>
-    <mergeCell ref="AL12:AO12"/>
-    <mergeCell ref="AL13:AO13"/>
-    <mergeCell ref="AL21:AO21"/>
-    <mergeCell ref="Q17:AK17"/>
-    <mergeCell ref="Q18:AK18"/>
-    <mergeCell ref="Q22:AK22"/>
-    <mergeCell ref="Q14:AK14"/>
-    <mergeCell ref="AL14:AO14"/>
-    <mergeCell ref="Q15:AK15"/>
-    <mergeCell ref="AL15:AO15"/>
-    <mergeCell ref="C34:P34"/>
-    <mergeCell ref="Q7:AK7"/>
-    <mergeCell ref="Q8:AK8"/>
-    <mergeCell ref="Q9:AK9"/>
-    <mergeCell ref="Q10:AK10"/>
-    <mergeCell ref="Q11:AK11"/>
-    <mergeCell ref="Q12:AK12"/>
-    <mergeCell ref="Q19:AK19"/>
-    <mergeCell ref="Q20:AK20"/>
-    <mergeCell ref="Q21:AK21"/>
-    <mergeCell ref="Q13:AK13"/>
-    <mergeCell ref="Q34:AK34"/>
-    <mergeCell ref="Q30:AK30"/>
-    <mergeCell ref="Q31:AK31"/>
-    <mergeCell ref="Q32:AK32"/>
-    <mergeCell ref="Q33:AK33"/>
-    <mergeCell ref="Q23:AK23"/>
-    <mergeCell ref="C17:P17"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="C15:P15"/>
-    <mergeCell ref="C16:P16"/>
-    <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C31:P31"/>
-    <mergeCell ref="C32:P32"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C33:P33"/>
-    <mergeCell ref="C27:P27"/>
-    <mergeCell ref="C28:P28"/>
-    <mergeCell ref="C24:P24"/>
-    <mergeCell ref="C25:P25"/>
-    <mergeCell ref="C26:P26"/>
-    <mergeCell ref="C29:P29"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="C23:P23"/>
-    <mergeCell ref="C7:P7"/>
-    <mergeCell ref="C8:P8"/>
-    <mergeCell ref="C9:P9"/>
-    <mergeCell ref="C10:P10"/>
-    <mergeCell ref="C18:P18"/>
-    <mergeCell ref="C19:P19"/>
-    <mergeCell ref="C20:P20"/>
-    <mergeCell ref="C21:P21"/>
-    <mergeCell ref="C11:P11"/>
-    <mergeCell ref="C12:P12"/>
-    <mergeCell ref="C13:P13"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="AX1:BA1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:W2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AP6:AR6"/>
-    <mergeCell ref="AS6:AU6"/>
-    <mergeCell ref="AT2:AW2"/>
-    <mergeCell ref="AX2:BA3"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AA3:AP3"/>
-    <mergeCell ref="AQ3:AS3"/>
-    <mergeCell ref="AV6:BA6"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A5:BA5"/>
-    <mergeCell ref="M1:W1"/>
-    <mergeCell ref="X1:Z2"/>
-    <mergeCell ref="AA1:AJ2"/>
-    <mergeCell ref="AK1:AM1"/>
-    <mergeCell ref="AT3:AW3"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="Q6:AK6"/>
-    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AV20:BA20"/>
+    <mergeCell ref="AV21:BA21"/>
+    <mergeCell ref="AV14:BA14"/>
+    <mergeCell ref="AV15:BA15"/>
+    <mergeCell ref="AS28:AU28"/>
+    <mergeCell ref="AS30:AU30"/>
+    <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AS25:AU25"/>
+    <mergeCell ref="AP31:AR31"/>
+    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AS16:AU16"/>
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="AL22:AO22"/>
+    <mergeCell ref="AL23:AO23"/>
+    <mergeCell ref="AL24:AO24"/>
+    <mergeCell ref="AL25:AO25"/>
+    <mergeCell ref="AL26:AO26"/>
+    <mergeCell ref="Q24:AK24"/>
+    <mergeCell ref="Q25:AK25"/>
+    <mergeCell ref="Q26:AK26"/>
+    <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="Q16:AK16"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="AP16:AR16"/>
   </mergeCells>
   <phoneticPr fontId="49"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7894,14 +7562,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69.1796875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.453125" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.26953125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="21.90625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.453125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.453125" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.453125" style="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="65.1796875" style="21" customWidth="1"/>
     <col min="8" max="168" width="2.453125" style="21"/>
@@ -8159,7 +7827,7 @@
     <col min="16075" max="16384" width="2.453125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.75" customHeight="1">
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>35</v>
       </c>
@@ -8167,110 +7835,137 @@
         <v>36</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="C4" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="27" t="s">
+      <c r="C5" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="27" t="s">
+      <c r="C6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="27" t="s">
+      <c r="C7" s="27" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.5" customHeight="1">
-      <c r="A6" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>58</v>
-      </c>
       <c r="D7" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>61</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="24"/>
       <c r="B8" s="24"/>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
-    </row>
-    <row r="11" spans="1:4" ht="27">
+      <c r="E8" s="26"/>
+    </row>
+    <row r="11" spans="1:5" ht="27">
       <c r="A11" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="21" t="s">
-        <v>61</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="21" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -8290,7 +7985,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="44" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/20_設計書/ログインシステム.xlsx
+++ b/20_設計書/ログインシステム.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9F9438-2A28-44AA-9CA3-62DCA9016BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F041117F-5BA5-4DE3-9CCB-0400BF5592EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34440" yWindow="1425" windowWidth="18720" windowHeight="13845" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28965" yWindow="540" windowWidth="16245" windowHeight="10095" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <definedName name="IBD00110チェック仕様" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="IBE09000チェック仕様" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ooo" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">ログイン処理!$A$1:$L$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">ログイン処理!$A$1:$L$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$I$36</definedName>
     <definedName name="s" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="txtDatabaseName">"テキスト 8"</definedName>
@@ -2629,16 +2629,109 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30253</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>44825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4544729</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="正方形/長方形 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E77CBA84-D259-41D4-8C63-3CC86DAF3D2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30253" y="2655796"/>
+          <a:ext cx="5310094" cy="5188322"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="252000" rIns="0" bIns="36000" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>新ヒロセ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>WEB</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>236636</xdr:colOff>
+      <xdr:colOff>239811</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>47998</xdr:rowOff>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>593912</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>164913</xdr:rowOff>
+      <xdr:colOff>597087</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2653,8 +2746,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5861989" y="2658969"/>
-          <a:ext cx="7831599" cy="8879915"/>
+          <a:off x="5865164" y="2655795"/>
+          <a:ext cx="7831599" cy="8169088"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3292,115 +3385,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1744019</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>102718</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2969558</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>127926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>50249</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>121768</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="正方形/長方形 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89DEAEAE-3414-4EA8-87E9-EA30A9CC1EE5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14843695" y="5190189"/>
-          <a:ext cx="5332319" cy="2305050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="12700"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="252000" rIns="0" bIns="36000" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>新環境</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>証明書</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>WEB</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2569005</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>103656</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>122328</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>596902</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>142313</xdr:rowOff>
+      <xdr:rowOff>134470</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3411,12 +3405,14 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12138829" y="6162299"/>
-          <a:ext cx="4034249" cy="19985"/>
+        <a:xfrm flipH="1">
+          <a:off x="3765176" y="6167897"/>
+          <a:ext cx="3499039" cy="6544"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3447,16 +3443,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>620442</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>513025</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>84981</xdr:rowOff>
+      <xdr:rowOff>88156</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3115804</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2989337</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>161548</xdr:rowOff>
+      <xdr:rowOff>164723</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3471,8 +3467,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16196618" y="5934452"/>
-          <a:ext cx="2495362" cy="1410067"/>
+          <a:off x="1308643" y="5937627"/>
+          <a:ext cx="2476312" cy="1410067"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3553,16 +3549,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1787904</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3177433</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>64066</xdr:rowOff>
+      <xdr:rowOff>33623</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>119535</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3988739</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>160063</xdr:rowOff>
+      <xdr:rowOff>129620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3577,8 +3573,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14887580" y="5913537"/>
-          <a:ext cx="808131" cy="286497"/>
+          <a:off x="3973051" y="5883094"/>
+          <a:ext cx="811306" cy="286497"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3628,16 +3624,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3003176</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>142501</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>134470</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>130549</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>655920</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>145676</xdr:rowOff>
+      <xdr:rowOff>156882</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3651,9 +3647,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="9704294" y="6932520"/>
-          <a:ext cx="6527802" cy="15127"/>
+        <a:xfrm flipV="1">
+          <a:off x="3798794" y="6944472"/>
+          <a:ext cx="5905500" cy="14381"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3684,16 +3680,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>349625</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>655360</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>8035</xdr:rowOff>
+      <xdr:rowOff>44828</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3220573</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1987927</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>84982</xdr:rowOff>
+      <xdr:rowOff>121775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3708,8 +3704,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9919449" y="7000506"/>
-          <a:ext cx="2870948" cy="267447"/>
+          <a:off x="6280713" y="7037299"/>
+          <a:ext cx="2867773" cy="267447"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3787,99 +3783,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>30253</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>44825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>4544729</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>179295</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="正方形/長方形 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E77CBA84-D259-41D4-8C63-3CC86DAF3D2D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30253" y="2655796"/>
-          <a:ext cx="5310094" cy="2991970"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent3">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="12700"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="252000" rIns="0" bIns="36000" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>新ヒロセ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>WEB</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3891,7 +3794,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>4018501</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>182469</xdr:rowOff>
+      <xdr:rowOff>179294</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7562,7 +7465,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="21" bestFit="1" customWidth="1"/>
@@ -7958,29 +7861,29 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="21" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" s="21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="21" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" s="21" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT65524:FW65524 PP65524:PS65524 ZL65524:ZO65524 AJH65524:AJK65524 ATD65524:ATG65524 BCZ65524:BDC65524 BMV65524:BMY65524 BWR65524:BWU65524 CGN65524:CGQ65524 CQJ65524:CQM65524 DAF65524:DAI65524 DKB65524:DKE65524 DTX65524:DUA65524 EDT65524:EDW65524 ENP65524:ENS65524 EXL65524:EXO65524 FHH65524:FHK65524 FRD65524:FRG65524 GAZ65524:GBC65524 GKV65524:GKY65524 GUR65524:GUU65524 HEN65524:HEQ65524 HOJ65524:HOM65524 HYF65524:HYI65524 IIB65524:IIE65524 IRX65524:ISA65524 JBT65524:JBW65524 JLP65524:JLS65524 JVL65524:JVO65524 KFH65524:KFK65524 KPD65524:KPG65524 KYZ65524:KZC65524 LIV65524:LIY65524 LSR65524:LSU65524 MCN65524:MCQ65524 MMJ65524:MMM65524 MWF65524:MWI65524 NGB65524:NGE65524 NPX65524:NQA65524 NZT65524:NZW65524 OJP65524:OJS65524 OTL65524:OTO65524 PDH65524:PDK65524 PND65524:PNG65524 PWZ65524:PXC65524 QGV65524:QGY65524 QQR65524:QQU65524 RAN65524:RAQ65524 RKJ65524:RKM65524 RUF65524:RUI65524 SEB65524:SEE65524 SNX65524:SOA65524 SXT65524:SXW65524 THP65524:THS65524 TRL65524:TRO65524 UBH65524:UBK65524 ULD65524:ULG65524 UUZ65524:UVC65524 VEV65524:VEY65524 VOR65524:VOU65524 VYN65524:VYQ65524 WIJ65524:WIM65524 WSF65524:WSI65524 FT131060:FW131060 PP131060:PS131060 ZL131060:ZO131060 AJH131060:AJK131060 ATD131060:ATG131060 BCZ131060:BDC131060 BMV131060:BMY131060 BWR131060:BWU131060 CGN131060:CGQ131060 CQJ131060:CQM131060 DAF131060:DAI131060 DKB131060:DKE131060 DTX131060:DUA131060 EDT131060:EDW131060 ENP131060:ENS131060 EXL131060:EXO131060 FHH131060:FHK131060 FRD131060:FRG131060 GAZ131060:GBC131060 GKV131060:GKY131060 GUR131060:GUU131060 HEN131060:HEQ131060 HOJ131060:HOM131060 HYF131060:HYI131060 IIB131060:IIE131060 IRX131060:ISA131060 JBT131060:JBW131060 JLP131060:JLS131060 JVL131060:JVO131060 KFH131060:KFK131060 KPD131060:KPG131060 KYZ131060:KZC131060 LIV131060:LIY131060 LSR131060:LSU131060 MCN131060:MCQ131060 MMJ131060:MMM131060 MWF131060:MWI131060 NGB131060:NGE131060 NPX131060:NQA131060 NZT131060:NZW131060 OJP131060:OJS131060 OTL131060:OTO131060 PDH131060:PDK131060 PND131060:PNG131060 PWZ131060:PXC131060 QGV131060:QGY131060 QQR131060:QQU131060 RAN131060:RAQ131060 RKJ131060:RKM131060 RUF131060:RUI131060 SEB131060:SEE131060 SNX131060:SOA131060 SXT131060:SXW131060 THP131060:THS131060 TRL131060:TRO131060 UBH131060:UBK131060 ULD131060:ULG131060 UUZ131060:UVC131060 VEV131060:VEY131060 VOR131060:VOU131060 VYN131060:VYQ131060 WIJ131060:WIM131060 WSF131060:WSI131060 FT196596:FW196596 PP196596:PS196596 ZL196596:ZO196596 AJH196596:AJK196596 ATD196596:ATG196596 BCZ196596:BDC196596 BMV196596:BMY196596 BWR196596:BWU196596 CGN196596:CGQ196596 CQJ196596:CQM196596 DAF196596:DAI196596 DKB196596:DKE196596 DTX196596:DUA196596 EDT196596:EDW196596 ENP196596:ENS196596 EXL196596:EXO196596 FHH196596:FHK196596 FRD196596:FRG196596 GAZ196596:GBC196596 GKV196596:GKY196596 GUR196596:GUU196596 HEN196596:HEQ196596 HOJ196596:HOM196596 HYF196596:HYI196596 IIB196596:IIE196596 IRX196596:ISA196596 JBT196596:JBW196596 JLP196596:JLS196596 JVL196596:JVO196596 KFH196596:KFK196596 KPD196596:KPG196596 KYZ196596:KZC196596 LIV196596:LIY196596 LSR196596:LSU196596 MCN196596:MCQ196596 MMJ196596:MMM196596 MWF196596:MWI196596 NGB196596:NGE196596 NPX196596:NQA196596 NZT196596:NZW196596 OJP196596:OJS196596 OTL196596:OTO196596 PDH196596:PDK196596 PND196596:PNG196596 PWZ196596:PXC196596 QGV196596:QGY196596 QQR196596:QQU196596 RAN196596:RAQ196596 RKJ196596:RKM196596 RUF196596:RUI196596 SEB196596:SEE196596 SNX196596:SOA196596 SXT196596:SXW196596 THP196596:THS196596 TRL196596:TRO196596 UBH196596:UBK196596 ULD196596:ULG196596 UUZ196596:UVC196596 VEV196596:VEY196596 VOR196596:VOU196596 VYN196596:VYQ196596 WIJ196596:WIM196596 WSF196596:WSI196596 FT262132:FW262132 PP262132:PS262132 ZL262132:ZO262132 AJH262132:AJK262132 ATD262132:ATG262132 BCZ262132:BDC262132 BMV262132:BMY262132 BWR262132:BWU262132 CGN262132:CGQ262132 CQJ262132:CQM262132 DAF262132:DAI262132 DKB262132:DKE262132 DTX262132:DUA262132 EDT262132:EDW262132 ENP262132:ENS262132 EXL262132:EXO262132 FHH262132:FHK262132 FRD262132:FRG262132 GAZ262132:GBC262132 GKV262132:GKY262132 GUR262132:GUU262132 HEN262132:HEQ262132 HOJ262132:HOM262132 HYF262132:HYI262132 IIB262132:IIE262132 IRX262132:ISA262132 JBT262132:JBW262132 JLP262132:JLS262132 JVL262132:JVO262132 KFH262132:KFK262132 KPD262132:KPG262132 KYZ262132:KZC262132 LIV262132:LIY262132 LSR262132:LSU262132 MCN262132:MCQ262132 MMJ262132:MMM262132 MWF262132:MWI262132 NGB262132:NGE262132 NPX262132:NQA262132 NZT262132:NZW262132 OJP262132:OJS262132 OTL262132:OTO262132 PDH262132:PDK262132 PND262132:PNG262132 PWZ262132:PXC262132 QGV262132:QGY262132 QQR262132:QQU262132 RAN262132:RAQ262132 RKJ262132:RKM262132 RUF262132:RUI262132 SEB262132:SEE262132 SNX262132:SOA262132 SXT262132:SXW262132 THP262132:THS262132 TRL262132:TRO262132 UBH262132:UBK262132 ULD262132:ULG262132 UUZ262132:UVC262132 VEV262132:VEY262132 VOR262132:VOU262132 VYN262132:VYQ262132 WIJ262132:WIM262132 WSF262132:WSI262132 FT327668:FW327668 PP327668:PS327668 ZL327668:ZO327668 AJH327668:AJK327668 ATD327668:ATG327668 BCZ327668:BDC327668 BMV327668:BMY327668 BWR327668:BWU327668 CGN327668:CGQ327668 CQJ327668:CQM327668 DAF327668:DAI327668 DKB327668:DKE327668 DTX327668:DUA327668 EDT327668:EDW327668 ENP327668:ENS327668 EXL327668:EXO327668 FHH327668:FHK327668 FRD327668:FRG327668 GAZ327668:GBC327668 GKV327668:GKY327668 GUR327668:GUU327668 HEN327668:HEQ327668 HOJ327668:HOM327668 HYF327668:HYI327668 IIB327668:IIE327668 IRX327668:ISA327668 JBT327668:JBW327668 JLP327668:JLS327668 JVL327668:JVO327668 KFH327668:KFK327668 KPD327668:KPG327668 KYZ327668:KZC327668 LIV327668:LIY327668 LSR327668:LSU327668 MCN327668:MCQ327668 MMJ327668:MMM327668 MWF327668:MWI327668 NGB327668:NGE327668 NPX327668:NQA327668 NZT327668:NZW327668 OJP327668:OJS327668 OTL327668:OTO327668 PDH327668:PDK327668 PND327668:PNG327668 PWZ327668:PXC327668 QGV327668:QGY327668 QQR327668:QQU327668 RAN327668:RAQ327668 RKJ327668:RKM327668 RUF327668:RUI327668 SEB327668:SEE327668 SNX327668:SOA327668 SXT327668:SXW327668 THP327668:THS327668 TRL327668:TRO327668 UBH327668:UBK327668 ULD327668:ULG327668 UUZ327668:UVC327668 VEV327668:VEY327668 VOR327668:VOU327668 VYN327668:VYQ327668 WIJ327668:WIM327668 WSF327668:WSI327668 FT393204:FW393204 PP393204:PS393204 ZL393204:ZO393204 AJH393204:AJK393204 ATD393204:ATG393204 BCZ393204:BDC393204 BMV393204:BMY393204 BWR393204:BWU393204 CGN393204:CGQ393204 CQJ393204:CQM393204 DAF393204:DAI393204 DKB393204:DKE393204 DTX393204:DUA393204 EDT393204:EDW393204 ENP393204:ENS393204 EXL393204:EXO393204 FHH393204:FHK393204 FRD393204:FRG393204 GAZ393204:GBC393204 GKV393204:GKY393204 GUR393204:GUU393204 HEN393204:HEQ393204 HOJ393204:HOM393204 HYF393204:HYI393204 IIB393204:IIE393204 IRX393204:ISA393204 JBT393204:JBW393204 JLP393204:JLS393204 JVL393204:JVO393204 KFH393204:KFK393204 KPD393204:KPG393204 KYZ393204:KZC393204 LIV393204:LIY393204 LSR393204:LSU393204 MCN393204:MCQ393204 MMJ393204:MMM393204 MWF393204:MWI393204 NGB393204:NGE393204 NPX393204:NQA393204 NZT393204:NZW393204 OJP393204:OJS393204 OTL393204:OTO393204 PDH393204:PDK393204 PND393204:PNG393204 PWZ393204:PXC393204 QGV393204:QGY393204 QQR393204:QQU393204 RAN393204:RAQ393204 RKJ393204:RKM393204 RUF393204:RUI393204 SEB393204:SEE393204 SNX393204:SOA393204 SXT393204:SXW393204 THP393204:THS393204 TRL393204:TRO393204 UBH393204:UBK393204 ULD393204:ULG393204 UUZ393204:UVC393204 VEV393204:VEY393204 VOR393204:VOU393204 VYN393204:VYQ393204 WIJ393204:WIM393204 WSF393204:WSI393204 FT458740:FW458740 PP458740:PS458740 ZL458740:ZO458740 AJH458740:AJK458740 ATD458740:ATG458740 BCZ458740:BDC458740 BMV458740:BMY458740 BWR458740:BWU458740 CGN458740:CGQ458740 CQJ458740:CQM458740 DAF458740:DAI458740 DKB458740:DKE458740 DTX458740:DUA458740 EDT458740:EDW458740 ENP458740:ENS458740 EXL458740:EXO458740 FHH458740:FHK458740 FRD458740:FRG458740 GAZ458740:GBC458740 GKV458740:GKY458740 GUR458740:GUU458740 HEN458740:HEQ458740 HOJ458740:HOM458740 HYF458740:HYI458740 IIB458740:IIE458740 IRX458740:ISA458740 JBT458740:JBW458740 JLP458740:JLS458740 JVL458740:JVO458740 KFH458740:KFK458740 KPD458740:KPG458740 KYZ458740:KZC458740 LIV458740:LIY458740 LSR458740:LSU458740 MCN458740:MCQ458740 MMJ458740:MMM458740 MWF458740:MWI458740 NGB458740:NGE458740 NPX458740:NQA458740 NZT458740:NZW458740 OJP458740:OJS458740 OTL458740:OTO458740 PDH458740:PDK458740 PND458740:PNG458740 PWZ458740:PXC458740 QGV458740:QGY458740 QQR458740:QQU458740 RAN458740:RAQ458740 RKJ458740:RKM458740 RUF458740:RUI458740 SEB458740:SEE458740 SNX458740:SOA458740 SXT458740:SXW458740 THP458740:THS458740 TRL458740:TRO458740 UBH458740:UBK458740 ULD458740:ULG458740 UUZ458740:UVC458740 VEV458740:VEY458740 VOR458740:VOU458740 VYN458740:VYQ458740 WIJ458740:WIM458740 WSF458740:WSI458740 FT524276:FW524276 PP524276:PS524276 ZL524276:ZO524276 AJH524276:AJK524276 ATD524276:ATG524276 BCZ524276:BDC524276 BMV524276:BMY524276 BWR524276:BWU524276 CGN524276:CGQ524276 CQJ524276:CQM524276 DAF524276:DAI524276 DKB524276:DKE524276 DTX524276:DUA524276 EDT524276:EDW524276 ENP524276:ENS524276 EXL524276:EXO524276 FHH524276:FHK524276 FRD524276:FRG524276 GAZ524276:GBC524276 GKV524276:GKY524276 GUR524276:GUU524276 HEN524276:HEQ524276 HOJ524276:HOM524276 HYF524276:HYI524276 IIB524276:IIE524276 IRX524276:ISA524276 JBT524276:JBW524276 JLP524276:JLS524276 JVL524276:JVO524276 KFH524276:KFK524276 KPD524276:KPG524276 KYZ524276:KZC524276 LIV524276:LIY524276 LSR524276:LSU524276 MCN524276:MCQ524276 MMJ524276:MMM524276 MWF524276:MWI524276 NGB524276:NGE524276 NPX524276:NQA524276 NZT524276:NZW524276 OJP524276:OJS524276 OTL524276:OTO524276 PDH524276:PDK524276 PND524276:PNG524276 PWZ524276:PXC524276 QGV524276:QGY524276 QQR524276:QQU524276 RAN524276:RAQ524276 RKJ524276:RKM524276 RUF524276:RUI524276 SEB524276:SEE524276 SNX524276:SOA524276 SXT524276:SXW524276 THP524276:THS524276 TRL524276:TRO524276 UBH524276:UBK524276 ULD524276:ULG524276 UUZ524276:UVC524276 VEV524276:VEY524276 VOR524276:VOU524276 VYN524276:VYQ524276 WIJ524276:WIM524276 WSF524276:WSI524276 FT589812:FW589812 PP589812:PS589812 ZL589812:ZO589812 AJH589812:AJK589812 ATD589812:ATG589812 BCZ589812:BDC589812 BMV589812:BMY589812 BWR589812:BWU589812 CGN589812:CGQ589812 CQJ589812:CQM589812 DAF589812:DAI589812 DKB589812:DKE589812 DTX589812:DUA589812 EDT589812:EDW589812 ENP589812:ENS589812 EXL589812:EXO589812 FHH589812:FHK589812 FRD589812:FRG589812 GAZ589812:GBC589812 GKV589812:GKY589812 GUR589812:GUU589812 HEN589812:HEQ589812 HOJ589812:HOM589812 HYF589812:HYI589812 IIB589812:IIE589812 IRX589812:ISA589812 JBT589812:JBW589812 JLP589812:JLS589812 JVL589812:JVO589812 KFH589812:KFK589812 KPD589812:KPG589812 KYZ589812:KZC589812 LIV589812:LIY589812 LSR589812:LSU589812 MCN589812:MCQ589812 MMJ589812:MMM589812 MWF589812:MWI589812 NGB589812:NGE589812 NPX589812:NQA589812 NZT589812:NZW589812 OJP589812:OJS589812 OTL589812:OTO589812 PDH589812:PDK589812 PND589812:PNG589812 PWZ589812:PXC589812 QGV589812:QGY589812 QQR589812:QQU589812 RAN589812:RAQ589812 RKJ589812:RKM589812 RUF589812:RUI589812 SEB589812:SEE589812 SNX589812:SOA589812 SXT589812:SXW589812 THP589812:THS589812 TRL589812:TRO589812 UBH589812:UBK589812 ULD589812:ULG589812 UUZ589812:UVC589812 VEV589812:VEY589812 VOR589812:VOU589812 VYN589812:VYQ589812 WIJ589812:WIM589812 WSF589812:WSI589812 FT655348:FW655348 PP655348:PS655348 ZL655348:ZO655348 AJH655348:AJK655348 ATD655348:ATG655348 BCZ655348:BDC655348 BMV655348:BMY655348 BWR655348:BWU655348 CGN655348:CGQ655348 CQJ655348:CQM655348 DAF655348:DAI655348 DKB655348:DKE655348 DTX655348:DUA655348 EDT655348:EDW655348 ENP655348:ENS655348 EXL655348:EXO655348 FHH655348:FHK655348 FRD655348:FRG655348 GAZ655348:GBC655348 GKV655348:GKY655348 GUR655348:GUU655348 HEN655348:HEQ655348 HOJ655348:HOM655348 HYF655348:HYI655348 IIB655348:IIE655348 IRX655348:ISA655348 JBT655348:JBW655348 JLP655348:JLS655348 JVL655348:JVO655348 KFH655348:KFK655348 KPD655348:KPG655348 KYZ655348:KZC655348 LIV655348:LIY655348 LSR655348:LSU655348 MCN655348:MCQ655348 MMJ655348:MMM655348 MWF655348:MWI655348 NGB655348:NGE655348 NPX655348:NQA655348 NZT655348:NZW655348 OJP655348:OJS655348 OTL655348:OTO655348 PDH655348:PDK655348 PND655348:PNG655348 PWZ655348:PXC655348 QGV655348:QGY655348 QQR655348:QQU655348 RAN655348:RAQ655348 RKJ655348:RKM655348 RUF655348:RUI655348 SEB655348:SEE655348 SNX655348:SOA655348 SXT655348:SXW655348 THP655348:THS655348 TRL655348:TRO655348 UBH655348:UBK655348 ULD655348:ULG655348 UUZ655348:UVC655348 VEV655348:VEY655348 VOR655348:VOU655348 VYN655348:VYQ655348 WIJ655348:WIM655348 WSF655348:WSI655348 FT720884:FW720884 PP720884:PS720884 ZL720884:ZO720884 AJH720884:AJK720884 ATD720884:ATG720884 BCZ720884:BDC720884 BMV720884:BMY720884 BWR720884:BWU720884 CGN720884:CGQ720884 CQJ720884:CQM720884 DAF720884:DAI720884 DKB720884:DKE720884 DTX720884:DUA720884 EDT720884:EDW720884 ENP720884:ENS720884 EXL720884:EXO720884 FHH720884:FHK720884 FRD720884:FRG720884 GAZ720884:GBC720884 GKV720884:GKY720884 GUR720884:GUU720884 HEN720884:HEQ720884 HOJ720884:HOM720884 HYF720884:HYI720884 IIB720884:IIE720884 IRX720884:ISA720884 JBT720884:JBW720884 JLP720884:JLS720884 JVL720884:JVO720884 KFH720884:KFK720884 KPD720884:KPG720884 KYZ720884:KZC720884 LIV720884:LIY720884 LSR720884:LSU720884 MCN720884:MCQ720884 MMJ720884:MMM720884 MWF720884:MWI720884 NGB720884:NGE720884 NPX720884:NQA720884 NZT720884:NZW720884 OJP720884:OJS720884 OTL720884:OTO720884 PDH720884:PDK720884 PND720884:PNG720884 PWZ720884:PXC720884 QGV720884:QGY720884 QQR720884:QQU720884 RAN720884:RAQ720884 RKJ720884:RKM720884 RUF720884:RUI720884 SEB720884:SEE720884 SNX720884:SOA720884 SXT720884:SXW720884 THP720884:THS720884 TRL720884:TRO720884 UBH720884:UBK720884 ULD720884:ULG720884 UUZ720884:UVC720884 VEV720884:VEY720884 VOR720884:VOU720884 VYN720884:VYQ720884 WIJ720884:WIM720884 WSF720884:WSI720884 FT786420:FW786420 PP786420:PS786420 ZL786420:ZO786420 AJH786420:AJK786420 ATD786420:ATG786420 BCZ786420:BDC786420 BMV786420:BMY786420 BWR786420:BWU786420 CGN786420:CGQ786420 CQJ786420:CQM786420 DAF786420:DAI786420 DKB786420:DKE786420 DTX786420:DUA786420 EDT786420:EDW786420 ENP786420:ENS786420 EXL786420:EXO786420 FHH786420:FHK786420 FRD786420:FRG786420 GAZ786420:GBC786420 GKV786420:GKY786420 GUR786420:GUU786420 HEN786420:HEQ786420 HOJ786420:HOM786420 HYF786420:HYI786420 IIB786420:IIE786420 IRX786420:ISA786420 JBT786420:JBW786420 JLP786420:JLS786420 JVL786420:JVO786420 KFH786420:KFK786420 KPD786420:KPG786420 KYZ786420:KZC786420 LIV786420:LIY786420 LSR786420:LSU786420 MCN786420:MCQ786420 MMJ786420:MMM786420 MWF786420:MWI786420 NGB786420:NGE786420 NPX786420:NQA786420 NZT786420:NZW786420 OJP786420:OJS786420 OTL786420:OTO786420 PDH786420:PDK786420 PND786420:PNG786420 PWZ786420:PXC786420 QGV786420:QGY786420 QQR786420:QQU786420 RAN786420:RAQ786420 RKJ786420:RKM786420 RUF786420:RUI786420 SEB786420:SEE786420 SNX786420:SOA786420 SXT786420:SXW786420 THP786420:THS786420 TRL786420:TRO786420 UBH786420:UBK786420 ULD786420:ULG786420 UUZ786420:UVC786420 VEV786420:VEY786420 VOR786420:VOU786420 VYN786420:VYQ786420 WIJ786420:WIM786420 WSF786420:WSI786420 FT851956:FW851956 PP851956:PS851956 ZL851956:ZO851956 AJH851956:AJK851956 ATD851956:ATG851956 BCZ851956:BDC851956 BMV851956:BMY851956 BWR851956:BWU851956 CGN851956:CGQ851956 CQJ851956:CQM851956 DAF851956:DAI851956 DKB851956:DKE851956 DTX851956:DUA851956 EDT851956:EDW851956 ENP851956:ENS851956 EXL851956:EXO851956 FHH851956:FHK851956 FRD851956:FRG851956 GAZ851956:GBC851956 GKV851956:GKY851956 GUR851956:GUU851956 HEN851956:HEQ851956 HOJ851956:HOM851956 HYF851956:HYI851956 IIB851956:IIE851956 IRX851956:ISA851956 JBT851956:JBW851956 JLP851956:JLS851956 JVL851956:JVO851956 KFH851956:KFK851956 KPD851956:KPG851956 KYZ851956:KZC851956 LIV851956:LIY851956 LSR851956:LSU851956 MCN851956:MCQ851956 MMJ851956:MMM851956 MWF851956:MWI851956 NGB851956:NGE851956 NPX851956:NQA851956 NZT851956:NZW851956 OJP851956:OJS851956 OTL851956:OTO851956 PDH851956:PDK851956 PND851956:PNG851956 PWZ851956:PXC851956 QGV851956:QGY851956 QQR851956:QQU851956 RAN851956:RAQ851956 RKJ851956:RKM851956 RUF851956:RUI851956 SEB851956:SEE851956 SNX851956:SOA851956 SXT851956:SXW851956 THP851956:THS851956 TRL851956:TRO851956 UBH851956:UBK851956 ULD851956:ULG851956 UUZ851956:UVC851956 VEV851956:VEY851956 VOR851956:VOU851956 VYN851956:VYQ851956 WIJ851956:WIM851956 WSF851956:WSI851956 FT917492:FW917492 PP917492:PS917492 ZL917492:ZO917492 AJH917492:AJK917492 ATD917492:ATG917492 BCZ917492:BDC917492 BMV917492:BMY917492 BWR917492:BWU917492 CGN917492:CGQ917492 CQJ917492:CQM917492 DAF917492:DAI917492 DKB917492:DKE917492 DTX917492:DUA917492 EDT917492:EDW917492 ENP917492:ENS917492 EXL917492:EXO917492 FHH917492:FHK917492 FRD917492:FRG917492 GAZ917492:GBC917492 GKV917492:GKY917492 GUR917492:GUU917492 HEN917492:HEQ917492 HOJ917492:HOM917492 HYF917492:HYI917492 IIB917492:IIE917492 IRX917492:ISA917492 JBT917492:JBW917492 JLP917492:JLS917492 JVL917492:JVO917492 KFH917492:KFK917492 KPD917492:KPG917492 KYZ917492:KZC917492 LIV917492:LIY917492 LSR917492:LSU917492 MCN917492:MCQ917492 MMJ917492:MMM917492 MWF917492:MWI917492 NGB917492:NGE917492 NPX917492:NQA917492 NZT917492:NZW917492 OJP917492:OJS917492 OTL917492:OTO917492 PDH917492:PDK917492 PND917492:PNG917492 PWZ917492:PXC917492 QGV917492:QGY917492 QQR917492:QQU917492 RAN917492:RAQ917492 RKJ917492:RKM917492 RUF917492:RUI917492 SEB917492:SEE917492 SNX917492:SOA917492 SXT917492:SXW917492 THP917492:THS917492 TRL917492:TRO917492 UBH917492:UBK917492 ULD917492:ULG917492 UUZ917492:UVC917492 VEV917492:VEY917492 VOR917492:VOU917492 VYN917492:VYQ917492 WIJ917492:WIM917492 WSF917492:WSI917492 FT983028:FW983028 PP983028:PS983028 ZL983028:ZO983028 AJH983028:AJK983028 ATD983028:ATG983028 BCZ983028:BDC983028 BMV983028:BMY983028 BWR983028:BWU983028 CGN983028:CGQ983028 CQJ983028:CQM983028 DAF983028:DAI983028 DKB983028:DKE983028 DTX983028:DUA983028 EDT983028:EDW983028 ENP983028:ENS983028 EXL983028:EXO983028 FHH983028:FHK983028 FRD983028:FRG983028 GAZ983028:GBC983028 GKV983028:GKY983028 GUR983028:GUU983028 HEN983028:HEQ983028 HOJ983028:HOM983028 HYF983028:HYI983028 IIB983028:IIE983028 IRX983028:ISA983028 JBT983028:JBW983028 JLP983028:JLS983028 JVL983028:JVO983028 KFH983028:KFK983028 KPD983028:KPG983028 KYZ983028:KZC983028 LIV983028:LIY983028 LSR983028:LSU983028 MCN983028:MCQ983028 MMJ983028:MMM983028 MWF983028:MWI983028 NGB983028:NGE983028 NPX983028:NQA983028 NZT983028:NZW983028 OJP983028:OJS983028 OTL983028:OTO983028 PDH983028:PDK983028 PND983028:PNG983028 PWZ983028:PXC983028 QGV983028:QGY983028 QQR983028:QQU983028 RAN983028:RAQ983028 RKJ983028:RKM983028 RUF983028:RUI983028 SEB983028:SEE983028 SNX983028:SOA983028 SXT983028:SXW983028 THP983028:THS983028 TRL983028:TRO983028 UBH983028:UBK983028 ULD983028:ULG983028 UUZ983028:UVC983028 VEV983028:VEY983028 VOR983028:VOU983028 VYN983028:VYQ983028 WIJ983028:WIM983028 WSF983028:WSI983028 FO983027:FR983027 PK983027:PN983027 ZG983027:ZJ983027 AJC983027:AJF983027 ASY983027:ATB983027 BCU983027:BCX983027 BMQ983027:BMT983027 BWM983027:BWP983027 CGI983027:CGL983027 CQE983027:CQH983027 DAA983027:DAD983027 DJW983027:DJZ983027 DTS983027:DTV983027 EDO983027:EDR983027 ENK983027:ENN983027 EXG983027:EXJ983027 FHC983027:FHF983027 FQY983027:FRB983027 GAU983027:GAX983027 GKQ983027:GKT983027 GUM983027:GUP983027 HEI983027:HEL983027 HOE983027:HOH983027 HYA983027:HYD983027 IHW983027:IHZ983027 IRS983027:IRV983027 JBO983027:JBR983027 JLK983027:JLN983027 JVG983027:JVJ983027 KFC983027:KFF983027 KOY983027:KPB983027 KYU983027:KYX983027 LIQ983027:LIT983027 LSM983027:LSP983027 MCI983027:MCL983027 MME983027:MMH983027 MWA983027:MWD983027 NFW983027:NFZ983027 NPS983027:NPV983027 NZO983027:NZR983027 OJK983027:OJN983027 OTG983027:OTJ983027 PDC983027:PDF983027 PMY983027:PNB983027 PWU983027:PWX983027 QGQ983027:QGT983027 QQM983027:QQP983027 RAI983027:RAL983027 RKE983027:RKH983027 RUA983027:RUD983027 SDW983027:SDZ983027 SNS983027:SNV983027 SXO983027:SXR983027 THK983027:THN983027 TRG983027:TRJ983027 UBC983027:UBF983027 UKY983027:ULB983027 UUU983027:UUX983027 VEQ983027:VET983027 VOM983027:VOP983027 VYI983027:VYL983027 WIE983027:WIH983027 WSA983027:WSD983027 FO65523:FR65523 PK65523:PN65523 ZG65523:ZJ65523 AJC65523:AJF65523 ASY65523:ATB65523 BCU65523:BCX65523 BMQ65523:BMT65523 BWM65523:BWP65523 CGI65523:CGL65523 CQE65523:CQH65523 DAA65523:DAD65523 DJW65523:DJZ65523 DTS65523:DTV65523 EDO65523:EDR65523 ENK65523:ENN65523 EXG65523:EXJ65523 FHC65523:FHF65523 FQY65523:FRB65523 GAU65523:GAX65523 GKQ65523:GKT65523 GUM65523:GUP65523 HEI65523:HEL65523 HOE65523:HOH65523 HYA65523:HYD65523 IHW65523:IHZ65523 IRS65523:IRV65523 JBO65523:JBR65523 JLK65523:JLN65523 JVG65523:JVJ65523 KFC65523:KFF65523 KOY65523:KPB65523 KYU65523:KYX65523 LIQ65523:LIT65523 LSM65523:LSP65523 MCI65523:MCL65523 MME65523:MMH65523 MWA65523:MWD65523 NFW65523:NFZ65523 NPS65523:NPV65523 NZO65523:NZR65523 OJK65523:OJN65523 OTG65523:OTJ65523 PDC65523:PDF65523 PMY65523:PNB65523 PWU65523:PWX65523 QGQ65523:QGT65523 QQM65523:QQP65523 RAI65523:RAL65523 RKE65523:RKH65523 RUA65523:RUD65523 SDW65523:SDZ65523 SNS65523:SNV65523 SXO65523:SXR65523 THK65523:THN65523 TRG65523:TRJ65523 UBC65523:UBF65523 UKY65523:ULB65523 UUU65523:UUX65523 VEQ65523:VET65523 VOM65523:VOP65523 VYI65523:VYL65523 WIE65523:WIH65523 WSA65523:WSD65523 FO131059:FR131059 PK131059:PN131059 ZG131059:ZJ131059 AJC131059:AJF131059 ASY131059:ATB131059 BCU131059:BCX131059 BMQ131059:BMT131059 BWM131059:BWP131059 CGI131059:CGL131059 CQE131059:CQH131059 DAA131059:DAD131059 DJW131059:DJZ131059 DTS131059:DTV131059 EDO131059:EDR131059 ENK131059:ENN131059 EXG131059:EXJ131059 FHC131059:FHF131059 FQY131059:FRB131059 GAU131059:GAX131059 GKQ131059:GKT131059 GUM131059:GUP131059 HEI131059:HEL131059 HOE131059:HOH131059 HYA131059:HYD131059 IHW131059:IHZ131059 IRS131059:IRV131059 JBO131059:JBR131059 JLK131059:JLN131059 JVG131059:JVJ131059 KFC131059:KFF131059 KOY131059:KPB131059 KYU131059:KYX131059 LIQ131059:LIT131059 LSM131059:LSP131059 MCI131059:MCL131059 MME131059:MMH131059 MWA131059:MWD131059 NFW131059:NFZ131059 NPS131059:NPV131059 NZO131059:NZR131059 OJK131059:OJN131059 OTG131059:OTJ131059 PDC131059:PDF131059 PMY131059:PNB131059 PWU131059:PWX131059 QGQ131059:QGT131059 QQM131059:QQP131059 RAI131059:RAL131059 RKE131059:RKH131059 RUA131059:RUD131059 SDW131059:SDZ131059 SNS131059:SNV131059 SXO131059:SXR131059 THK131059:THN131059 TRG131059:TRJ131059 UBC131059:UBF131059 UKY131059:ULB131059 UUU131059:UUX131059 VEQ131059:VET131059 VOM131059:VOP131059 VYI131059:VYL131059 WIE131059:WIH131059 WSA131059:WSD131059 FO196595:FR196595 PK196595:PN196595 ZG196595:ZJ196595 AJC196595:AJF196595 ASY196595:ATB196595 BCU196595:BCX196595 BMQ196595:BMT196595 BWM196595:BWP196595 CGI196595:CGL196595 CQE196595:CQH196595 DAA196595:DAD196595 DJW196595:DJZ196595 DTS196595:DTV196595 EDO196595:EDR196595 ENK196595:ENN196595 EXG196595:EXJ196595 FHC196595:FHF196595 FQY196595:FRB196595 GAU196595:GAX196595 GKQ196595:GKT196595 GUM196595:GUP196595 HEI196595:HEL196595 HOE196595:HOH196595 HYA196595:HYD196595 IHW196595:IHZ196595 IRS196595:IRV196595 JBO196595:JBR196595 JLK196595:JLN196595 JVG196595:JVJ196595 KFC196595:KFF196595 KOY196595:KPB196595 KYU196595:KYX196595 LIQ196595:LIT196595 LSM196595:LSP196595 MCI196595:MCL196595 MME196595:MMH196595 MWA196595:MWD196595 NFW196595:NFZ196595 NPS196595:NPV196595 NZO196595:NZR196595 OJK196595:OJN196595 OTG196595:OTJ196595 PDC196595:PDF196595 PMY196595:PNB196595 PWU196595:PWX196595 QGQ196595:QGT196595 QQM196595:QQP196595 RAI196595:RAL196595 RKE196595:RKH196595 RUA196595:RUD196595 SDW196595:SDZ196595 SNS196595:SNV196595 SXO196595:SXR196595 THK196595:THN196595 TRG196595:TRJ196595 UBC196595:UBF196595 UKY196595:ULB196595 UUU196595:UUX196595 VEQ196595:VET196595 VOM196595:VOP196595 VYI196595:VYL196595 WIE196595:WIH196595 WSA196595:WSD196595 FO262131:FR262131 PK262131:PN262131 ZG262131:ZJ262131 AJC262131:AJF262131 ASY262131:ATB262131 BCU262131:BCX262131 BMQ262131:BMT262131 BWM262131:BWP262131 CGI262131:CGL262131 CQE262131:CQH262131 DAA262131:DAD262131 DJW262131:DJZ262131 DTS262131:DTV262131 EDO262131:EDR262131 ENK262131:ENN262131 EXG262131:EXJ262131 FHC262131:FHF262131 FQY262131:FRB262131 GAU262131:GAX262131 GKQ262131:GKT262131 GUM262131:GUP262131 HEI262131:HEL262131 HOE262131:HOH262131 HYA262131:HYD262131 IHW262131:IHZ262131 IRS262131:IRV262131 JBO262131:JBR262131 JLK262131:JLN262131 JVG262131:JVJ262131 KFC262131:KFF262131 KOY262131:KPB262131 KYU262131:KYX262131 LIQ262131:LIT262131 LSM262131:LSP262131 MCI262131:MCL262131 MME262131:MMH262131 MWA262131:MWD262131 NFW262131:NFZ262131 NPS262131:NPV262131 NZO262131:NZR262131 OJK262131:OJN262131 OTG262131:OTJ262131 PDC262131:PDF262131 PMY262131:PNB262131 PWU262131:PWX262131 QGQ262131:QGT262131 QQM262131:QQP262131 RAI262131:RAL262131 RKE262131:RKH262131 RUA262131:RUD262131 SDW262131:SDZ262131 SNS262131:SNV262131 SXO262131:SXR262131 THK262131:THN262131 TRG262131:TRJ262131 UBC262131:UBF262131 UKY262131:ULB262131 UUU262131:UUX262131 VEQ262131:VET262131 VOM262131:VOP262131 VYI262131:VYL262131 WIE262131:WIH262131 WSA262131:WSD262131 FO327667:FR327667 PK327667:PN327667 ZG327667:ZJ327667 AJC327667:AJF327667 ASY327667:ATB327667 BCU327667:BCX327667 BMQ327667:BMT327667 BWM327667:BWP327667 CGI327667:CGL327667 CQE327667:CQH327667 DAA327667:DAD327667 DJW327667:DJZ327667 DTS327667:DTV327667 EDO327667:EDR327667 ENK327667:ENN327667 EXG327667:EXJ327667 FHC327667:FHF327667 FQY327667:FRB327667 GAU327667:GAX327667 GKQ327667:GKT327667 GUM327667:GUP327667 HEI327667:HEL327667 HOE327667:HOH327667 HYA327667:HYD327667 IHW327667:IHZ327667 IRS327667:IRV327667 JBO327667:JBR327667 JLK327667:JLN327667 JVG327667:JVJ327667 KFC327667:KFF327667 KOY327667:KPB327667 KYU327667:KYX327667 LIQ327667:LIT327667 LSM327667:LSP327667 MCI327667:MCL327667 MME327667:MMH327667 MWA327667:MWD327667 NFW327667:NFZ327667 NPS327667:NPV327667 NZO327667:NZR327667 OJK327667:OJN327667 OTG327667:OTJ327667 PDC327667:PDF327667 PMY327667:PNB327667 PWU327667:PWX327667 QGQ327667:QGT327667 QQM327667:QQP327667 RAI327667:RAL327667 RKE327667:RKH327667 RUA327667:RUD327667 SDW327667:SDZ327667 SNS327667:SNV327667 SXO327667:SXR327667 THK327667:THN327667 TRG327667:TRJ327667 UBC327667:UBF327667 UKY327667:ULB327667 UUU327667:UUX327667 VEQ327667:VET327667 VOM327667:VOP327667 VYI327667:VYL327667 WIE327667:WIH327667 WSA327667:WSD327667 FO393203:FR393203 PK393203:PN393203 ZG393203:ZJ393203 AJC393203:AJF393203 ASY393203:ATB393203 BCU393203:BCX393203 BMQ393203:BMT393203 BWM393203:BWP393203 CGI393203:CGL393203 CQE393203:CQH393203 DAA393203:DAD393203 DJW393203:DJZ393203 DTS393203:DTV393203 EDO393203:EDR393203 ENK393203:ENN393203 EXG393203:EXJ393203 FHC393203:FHF393203 FQY393203:FRB393203 GAU393203:GAX393203 GKQ393203:GKT393203 GUM393203:GUP393203 HEI393203:HEL393203 HOE393203:HOH393203 HYA393203:HYD393203 IHW393203:IHZ393203 IRS393203:IRV393203 JBO393203:JBR393203 JLK393203:JLN393203 JVG393203:JVJ393203 KFC393203:KFF393203 KOY393203:KPB393203 KYU393203:KYX393203 LIQ393203:LIT393203 LSM393203:LSP393203 MCI393203:MCL393203 MME393203:MMH393203 MWA393203:MWD393203 NFW393203:NFZ393203 NPS393203:NPV393203 NZO393203:NZR393203 OJK393203:OJN393203 OTG393203:OTJ393203 PDC393203:PDF393203 PMY393203:PNB393203 PWU393203:PWX393203 QGQ393203:QGT393203 QQM393203:QQP393203 RAI393203:RAL393203 RKE393203:RKH393203 RUA393203:RUD393203 SDW393203:SDZ393203 SNS393203:SNV393203 SXO393203:SXR393203 THK393203:THN393203 TRG393203:TRJ393203 UBC393203:UBF393203 UKY393203:ULB393203 UUU393203:UUX393203 VEQ393203:VET393203 VOM393203:VOP393203 VYI393203:VYL393203 WIE393203:WIH393203 WSA393203:WSD393203 FO458739:FR458739 PK458739:PN458739 ZG458739:ZJ458739 AJC458739:AJF458739 ASY458739:ATB458739 BCU458739:BCX458739 BMQ458739:BMT458739 BWM458739:BWP458739 CGI458739:CGL458739 CQE458739:CQH458739 DAA458739:DAD458739 DJW458739:DJZ458739 DTS458739:DTV458739 EDO458739:EDR458739 ENK458739:ENN458739 EXG458739:EXJ458739 FHC458739:FHF458739 FQY458739:FRB458739 GAU458739:GAX458739 GKQ458739:GKT458739 GUM458739:GUP458739 HEI458739:HEL458739 HOE458739:HOH458739 HYA458739:HYD458739 IHW458739:IHZ458739 IRS458739:IRV458739 JBO458739:JBR458739 JLK458739:JLN458739 JVG458739:JVJ458739 KFC458739:KFF458739 KOY458739:KPB458739 KYU458739:KYX458739 LIQ458739:LIT458739 LSM458739:LSP458739 MCI458739:MCL458739 MME458739:MMH458739 MWA458739:MWD458739 NFW458739:NFZ458739 NPS458739:NPV458739 NZO458739:NZR458739 OJK458739:OJN458739 OTG458739:OTJ458739 PDC458739:PDF458739 PMY458739:PNB458739 PWU458739:PWX458739 QGQ458739:QGT458739 QQM458739:QQP458739 RAI458739:RAL458739 RKE458739:RKH458739 RUA458739:RUD458739 SDW458739:SDZ458739 SNS458739:SNV458739 SXO458739:SXR458739 THK458739:THN458739 TRG458739:TRJ458739 UBC458739:UBF458739 UKY458739:ULB458739 UUU458739:UUX458739 VEQ458739:VET458739 VOM458739:VOP458739 VYI458739:VYL458739 WIE458739:WIH458739 WSA458739:WSD458739 FO524275:FR524275 PK524275:PN524275 ZG524275:ZJ524275 AJC524275:AJF524275 ASY524275:ATB524275 BCU524275:BCX524275 BMQ524275:BMT524275 BWM524275:BWP524275 CGI524275:CGL524275 CQE524275:CQH524275 DAA524275:DAD524275 DJW524275:DJZ524275 DTS524275:DTV524275 EDO524275:EDR524275 ENK524275:ENN524275 EXG524275:EXJ524275 FHC524275:FHF524275 FQY524275:FRB524275 GAU524275:GAX524275 GKQ524275:GKT524275 GUM524275:GUP524275 HEI524275:HEL524275 HOE524275:HOH524275 HYA524275:HYD524275 IHW524275:IHZ524275 IRS524275:IRV524275 JBO524275:JBR524275 JLK524275:JLN524275 JVG524275:JVJ524275 KFC524275:KFF524275 KOY524275:KPB524275 KYU524275:KYX524275 LIQ524275:LIT524275 LSM524275:LSP524275 MCI524275:MCL524275 MME524275:MMH524275 MWA524275:MWD524275 NFW524275:NFZ524275 NPS524275:NPV524275 NZO524275:NZR524275 OJK524275:OJN524275 OTG524275:OTJ524275 PDC524275:PDF524275 PMY524275:PNB524275 PWU524275:PWX524275 QGQ524275:QGT524275 QQM524275:QQP524275 RAI524275:RAL524275 RKE524275:RKH524275 RUA524275:RUD524275 SDW524275:SDZ524275 SNS524275:SNV524275 SXO524275:SXR524275 THK524275:THN524275 TRG524275:TRJ524275 UBC524275:UBF524275 UKY524275:ULB524275 UUU524275:UUX524275 VEQ524275:VET524275 VOM524275:VOP524275 VYI524275:VYL524275 WIE524275:WIH524275 WSA524275:WSD524275 FO589811:FR589811 PK589811:PN589811 ZG589811:ZJ589811 AJC589811:AJF589811 ASY589811:ATB589811 BCU589811:BCX589811 BMQ589811:BMT589811 BWM589811:BWP589811 CGI589811:CGL589811 CQE589811:CQH589811 DAA589811:DAD589811 DJW589811:DJZ589811 DTS589811:DTV589811 EDO589811:EDR589811 ENK589811:ENN589811 EXG589811:EXJ589811 FHC589811:FHF589811 FQY589811:FRB589811 GAU589811:GAX589811 GKQ589811:GKT589811 GUM589811:GUP589811 HEI589811:HEL589811 HOE589811:HOH589811 HYA589811:HYD589811 IHW589811:IHZ589811 IRS589811:IRV589811 JBO589811:JBR589811 JLK589811:JLN589811 JVG589811:JVJ589811 KFC589811:KFF589811 KOY589811:KPB589811 KYU589811:KYX589811 LIQ589811:LIT589811 LSM589811:LSP589811 MCI589811:MCL589811 MME589811:MMH589811 MWA589811:MWD589811 NFW589811:NFZ589811 NPS589811:NPV589811 NZO589811:NZR589811 OJK589811:OJN589811 OTG589811:OTJ589811 PDC589811:PDF589811 PMY589811:PNB589811 PWU589811:PWX589811 QGQ589811:QGT589811 QQM589811:QQP589811 RAI589811:RAL589811 RKE589811:RKH589811 RUA589811:RUD589811 SDW589811:SDZ589811 SNS589811:SNV589811 SXO589811:SXR589811 THK589811:THN589811 TRG589811:TRJ589811 UBC589811:UBF589811 UKY589811:ULB589811 UUU589811:UUX589811 VEQ589811:VET589811 VOM589811:VOP589811 VYI589811:VYL589811 WIE589811:WIH589811 WSA589811:WSD589811 FO655347:FR655347 PK655347:PN655347 ZG655347:ZJ655347 AJC655347:AJF655347 ASY655347:ATB655347 BCU655347:BCX655347 BMQ655347:BMT655347 BWM655347:BWP655347 CGI655347:CGL655347 CQE655347:CQH655347 DAA655347:DAD655347 DJW655347:DJZ655347 DTS655347:DTV655347 EDO655347:EDR655347 ENK655347:ENN655347 EXG655347:EXJ655347 FHC655347:FHF655347 FQY655347:FRB655347 GAU655347:GAX655347 GKQ655347:GKT655347 GUM655347:GUP655347 HEI655347:HEL655347 HOE655347:HOH655347 HYA655347:HYD655347 IHW655347:IHZ655347 IRS655347:IRV655347 JBO655347:JBR655347 JLK655347:JLN655347 JVG655347:JVJ655347 KFC655347:KFF655347 KOY655347:KPB655347 KYU655347:KYX655347 LIQ655347:LIT655347 LSM655347:LSP655347 MCI655347:MCL655347 MME655347:MMH655347 MWA655347:MWD655347 NFW655347:NFZ655347 NPS655347:NPV655347 NZO655347:NZR655347 OJK655347:OJN655347 OTG655347:OTJ655347 PDC655347:PDF655347 PMY655347:PNB655347 PWU655347:PWX655347 QGQ655347:QGT655347 QQM655347:QQP655347 RAI655347:RAL655347 RKE655347:RKH655347 RUA655347:RUD655347 SDW655347:SDZ655347 SNS655347:SNV655347 SXO655347:SXR655347 THK655347:THN655347 TRG655347:TRJ655347 UBC655347:UBF655347 UKY655347:ULB655347 UUU655347:UUX655347 VEQ655347:VET655347 VOM655347:VOP655347 VYI655347:VYL655347 WIE655347:WIH655347 WSA655347:WSD655347 FO720883:FR720883 PK720883:PN720883 ZG720883:ZJ720883 AJC720883:AJF720883 ASY720883:ATB720883 BCU720883:BCX720883 BMQ720883:BMT720883 BWM720883:BWP720883 CGI720883:CGL720883 CQE720883:CQH720883 DAA720883:DAD720883 DJW720883:DJZ720883 DTS720883:DTV720883 EDO720883:EDR720883 ENK720883:ENN720883 EXG720883:EXJ720883 FHC720883:FHF720883 FQY720883:FRB720883 GAU720883:GAX720883 GKQ720883:GKT720883 GUM720883:GUP720883 HEI720883:HEL720883 HOE720883:HOH720883 HYA720883:HYD720883 IHW720883:IHZ720883 IRS720883:IRV720883 JBO720883:JBR720883 JLK720883:JLN720883 JVG720883:JVJ720883 KFC720883:KFF720883 KOY720883:KPB720883 KYU720883:KYX720883 LIQ720883:LIT720883 LSM720883:LSP720883 MCI720883:MCL720883 MME720883:MMH720883 MWA720883:MWD720883 NFW720883:NFZ720883 NPS720883:NPV720883 NZO720883:NZR720883 OJK720883:OJN720883 OTG720883:OTJ720883 PDC720883:PDF720883 PMY720883:PNB720883 PWU720883:PWX720883 QGQ720883:QGT720883 QQM720883:QQP720883 RAI720883:RAL720883 RKE720883:RKH720883 RUA720883:RUD720883 SDW720883:SDZ720883 SNS720883:SNV720883 SXO720883:SXR720883 THK720883:THN720883 TRG720883:TRJ720883 UBC720883:UBF720883 UKY720883:ULB720883 UUU720883:UUX720883 VEQ720883:VET720883 VOM720883:VOP720883 VYI720883:VYL720883 WIE720883:WIH720883 WSA720883:WSD720883 FO786419:FR786419 PK786419:PN786419 ZG786419:ZJ786419 AJC786419:AJF786419 ASY786419:ATB786419 BCU786419:BCX786419 BMQ786419:BMT786419 BWM786419:BWP786419 CGI786419:CGL786419 CQE786419:CQH786419 DAA786419:DAD786419 DJW786419:DJZ786419 DTS786419:DTV786419 EDO786419:EDR786419 ENK786419:ENN786419 EXG786419:EXJ786419 FHC786419:FHF786419 FQY786419:FRB786419 GAU786419:GAX786419 GKQ786419:GKT786419 GUM786419:GUP786419 HEI786419:HEL786419 HOE786419:HOH786419 HYA786419:HYD786419 IHW786419:IHZ786419 IRS786419:IRV786419 JBO786419:JBR786419 JLK786419:JLN786419 JVG786419:JVJ786419 KFC786419:KFF786419 KOY786419:KPB786419 KYU786419:KYX786419 LIQ786419:LIT786419 LSM786419:LSP786419 MCI786419:MCL786419 MME786419:MMH786419 MWA786419:MWD786419 NFW786419:NFZ786419 NPS786419:NPV786419 NZO786419:NZR786419 OJK786419:OJN786419 OTG786419:OTJ786419 PDC786419:PDF786419 PMY786419:PNB786419 PWU786419:PWX786419 QGQ786419:QGT786419 QQM786419:QQP786419 RAI786419:RAL786419 RKE786419:RKH786419 RUA786419:RUD786419 SDW786419:SDZ786419 SNS786419:SNV786419 SXO786419:SXR786419 THK786419:THN786419 TRG786419:TRJ786419 UBC786419:UBF786419 UKY786419:ULB786419 UUU786419:UUX786419 VEQ786419:VET786419 VOM786419:VOP786419 VYI786419:VYL786419 WIE786419:WIH786419 WSA786419:WSD786419 FO851955:FR851955 PK851955:PN851955 ZG851955:ZJ851955 AJC851955:AJF851955 ASY851955:ATB851955 BCU851955:BCX851955 BMQ851955:BMT851955 BWM851955:BWP851955 CGI851955:CGL851955 CQE851955:CQH851955 DAA851955:DAD851955 DJW851955:DJZ851955 DTS851955:DTV851955 EDO851955:EDR851955 ENK851955:ENN851955 EXG851955:EXJ851955 FHC851955:FHF851955 FQY851955:FRB851955 GAU851955:GAX851955 GKQ851955:GKT851955 GUM851955:GUP851955 HEI851955:HEL851955 HOE851955:HOH851955 HYA851955:HYD851955 IHW851955:IHZ851955 IRS851955:IRV851955 JBO851955:JBR851955 JLK851955:JLN851955 JVG851955:JVJ851955 KFC851955:KFF851955 KOY851955:KPB851955 KYU851955:KYX851955 LIQ851955:LIT851955 LSM851955:LSP851955 MCI851955:MCL851955 MME851955:MMH851955 MWA851955:MWD851955 NFW851955:NFZ851955 NPS851955:NPV851955 NZO851955:NZR851955 OJK851955:OJN851955 OTG851955:OTJ851955 PDC851955:PDF851955 PMY851955:PNB851955 PWU851955:PWX851955 QGQ851955:QGT851955 QQM851955:QQP851955 RAI851955:RAL851955 RKE851955:RKH851955 RUA851955:RUD851955 SDW851955:SDZ851955 SNS851955:SNV851955 SXO851955:SXR851955 THK851955:THN851955 TRG851955:TRJ851955 UBC851955:UBF851955 UKY851955:ULB851955 UUU851955:UUX851955 VEQ851955:VET851955 VOM851955:VOP851955 VYI851955:VYL851955 WIE851955:WIH851955 WSA851955:WSD851955 FO917491:FR917491 PK917491:PN917491 ZG917491:ZJ917491 AJC917491:AJF917491 ASY917491:ATB917491 BCU917491:BCX917491 BMQ917491:BMT917491 BWM917491:BWP917491 CGI917491:CGL917491 CQE917491:CQH917491 DAA917491:DAD917491 DJW917491:DJZ917491 DTS917491:DTV917491 EDO917491:EDR917491 ENK917491:ENN917491 EXG917491:EXJ917491 FHC917491:FHF917491 FQY917491:FRB917491 GAU917491:GAX917491 GKQ917491:GKT917491 GUM917491:GUP917491 HEI917491:HEL917491 HOE917491:HOH917491 HYA917491:HYD917491 IHW917491:IHZ917491 IRS917491:IRV917491 JBO917491:JBR917491 JLK917491:JLN917491 JVG917491:JVJ917491 KFC917491:KFF917491 KOY917491:KPB917491 KYU917491:KYX917491 LIQ917491:LIT917491 LSM917491:LSP917491 MCI917491:MCL917491 MME917491:MMH917491 MWA917491:MWD917491 NFW917491:NFZ917491 NPS917491:NPV917491 NZO917491:NZR917491 OJK917491:OJN917491 OTG917491:OTJ917491 PDC917491:PDF917491 PMY917491:PNB917491 PWU917491:PWX917491 QGQ917491:QGT917491 QQM917491:QQP917491 RAI917491:RAL917491 RKE917491:RKH917491 RUA917491:RUD917491 SDW917491:SDZ917491 SNS917491:SNV917491 SXO917491:SXR917491 THK917491:THN917491 TRG917491:TRJ917491 UBC917491:UBF917491 UKY917491:ULB917491 UUU917491:UUX917491 VEQ917491:VET917491 VOM917491:VOP917491 VYI917491:VYL917491 WIE917491:WIH917491 WSA917491:WSD917491" xr:uid="{626B8BD6-E9F5-43BA-A8F9-8EFAF6D840B9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT65522:FW65522 PP65522:PS65522 ZL65522:ZO65522 AJH65522:AJK65522 ATD65522:ATG65522 BCZ65522:BDC65522 BMV65522:BMY65522 BWR65522:BWU65522 CGN65522:CGQ65522 CQJ65522:CQM65522 DAF65522:DAI65522 DKB65522:DKE65522 DTX65522:DUA65522 EDT65522:EDW65522 ENP65522:ENS65522 EXL65522:EXO65522 FHH65522:FHK65522 FRD65522:FRG65522 GAZ65522:GBC65522 GKV65522:GKY65522 GUR65522:GUU65522 HEN65522:HEQ65522 HOJ65522:HOM65522 HYF65522:HYI65522 IIB65522:IIE65522 IRX65522:ISA65522 JBT65522:JBW65522 JLP65522:JLS65522 JVL65522:JVO65522 KFH65522:KFK65522 KPD65522:KPG65522 KYZ65522:KZC65522 LIV65522:LIY65522 LSR65522:LSU65522 MCN65522:MCQ65522 MMJ65522:MMM65522 MWF65522:MWI65522 NGB65522:NGE65522 NPX65522:NQA65522 NZT65522:NZW65522 OJP65522:OJS65522 OTL65522:OTO65522 PDH65522:PDK65522 PND65522:PNG65522 PWZ65522:PXC65522 QGV65522:QGY65522 QQR65522:QQU65522 RAN65522:RAQ65522 RKJ65522:RKM65522 RUF65522:RUI65522 SEB65522:SEE65522 SNX65522:SOA65522 SXT65522:SXW65522 THP65522:THS65522 TRL65522:TRO65522 UBH65522:UBK65522 ULD65522:ULG65522 UUZ65522:UVC65522 VEV65522:VEY65522 VOR65522:VOU65522 VYN65522:VYQ65522 WIJ65522:WIM65522 WSF65522:WSI65522 FT131058:FW131058 PP131058:PS131058 ZL131058:ZO131058 AJH131058:AJK131058 ATD131058:ATG131058 BCZ131058:BDC131058 BMV131058:BMY131058 BWR131058:BWU131058 CGN131058:CGQ131058 CQJ131058:CQM131058 DAF131058:DAI131058 DKB131058:DKE131058 DTX131058:DUA131058 EDT131058:EDW131058 ENP131058:ENS131058 EXL131058:EXO131058 FHH131058:FHK131058 FRD131058:FRG131058 GAZ131058:GBC131058 GKV131058:GKY131058 GUR131058:GUU131058 HEN131058:HEQ131058 HOJ131058:HOM131058 HYF131058:HYI131058 IIB131058:IIE131058 IRX131058:ISA131058 JBT131058:JBW131058 JLP131058:JLS131058 JVL131058:JVO131058 KFH131058:KFK131058 KPD131058:KPG131058 KYZ131058:KZC131058 LIV131058:LIY131058 LSR131058:LSU131058 MCN131058:MCQ131058 MMJ131058:MMM131058 MWF131058:MWI131058 NGB131058:NGE131058 NPX131058:NQA131058 NZT131058:NZW131058 OJP131058:OJS131058 OTL131058:OTO131058 PDH131058:PDK131058 PND131058:PNG131058 PWZ131058:PXC131058 QGV131058:QGY131058 QQR131058:QQU131058 RAN131058:RAQ131058 RKJ131058:RKM131058 RUF131058:RUI131058 SEB131058:SEE131058 SNX131058:SOA131058 SXT131058:SXW131058 THP131058:THS131058 TRL131058:TRO131058 UBH131058:UBK131058 ULD131058:ULG131058 UUZ131058:UVC131058 VEV131058:VEY131058 VOR131058:VOU131058 VYN131058:VYQ131058 WIJ131058:WIM131058 WSF131058:WSI131058 FT196594:FW196594 PP196594:PS196594 ZL196594:ZO196594 AJH196594:AJK196594 ATD196594:ATG196594 BCZ196594:BDC196594 BMV196594:BMY196594 BWR196594:BWU196594 CGN196594:CGQ196594 CQJ196594:CQM196594 DAF196594:DAI196594 DKB196594:DKE196594 DTX196594:DUA196594 EDT196594:EDW196594 ENP196594:ENS196594 EXL196594:EXO196594 FHH196594:FHK196594 FRD196594:FRG196594 GAZ196594:GBC196594 GKV196594:GKY196594 GUR196594:GUU196594 HEN196594:HEQ196594 HOJ196594:HOM196594 HYF196594:HYI196594 IIB196594:IIE196594 IRX196594:ISA196594 JBT196594:JBW196594 JLP196594:JLS196594 JVL196594:JVO196594 KFH196594:KFK196594 KPD196594:KPG196594 KYZ196594:KZC196594 LIV196594:LIY196594 LSR196594:LSU196594 MCN196594:MCQ196594 MMJ196594:MMM196594 MWF196594:MWI196594 NGB196594:NGE196594 NPX196594:NQA196594 NZT196594:NZW196594 OJP196594:OJS196594 OTL196594:OTO196594 PDH196594:PDK196594 PND196594:PNG196594 PWZ196594:PXC196594 QGV196594:QGY196594 QQR196594:QQU196594 RAN196594:RAQ196594 RKJ196594:RKM196594 RUF196594:RUI196594 SEB196594:SEE196594 SNX196594:SOA196594 SXT196594:SXW196594 THP196594:THS196594 TRL196594:TRO196594 UBH196594:UBK196594 ULD196594:ULG196594 UUZ196594:UVC196594 VEV196594:VEY196594 VOR196594:VOU196594 VYN196594:VYQ196594 WIJ196594:WIM196594 WSF196594:WSI196594 FT262130:FW262130 PP262130:PS262130 ZL262130:ZO262130 AJH262130:AJK262130 ATD262130:ATG262130 BCZ262130:BDC262130 BMV262130:BMY262130 BWR262130:BWU262130 CGN262130:CGQ262130 CQJ262130:CQM262130 DAF262130:DAI262130 DKB262130:DKE262130 DTX262130:DUA262130 EDT262130:EDW262130 ENP262130:ENS262130 EXL262130:EXO262130 FHH262130:FHK262130 FRD262130:FRG262130 GAZ262130:GBC262130 GKV262130:GKY262130 GUR262130:GUU262130 HEN262130:HEQ262130 HOJ262130:HOM262130 HYF262130:HYI262130 IIB262130:IIE262130 IRX262130:ISA262130 JBT262130:JBW262130 JLP262130:JLS262130 JVL262130:JVO262130 KFH262130:KFK262130 KPD262130:KPG262130 KYZ262130:KZC262130 LIV262130:LIY262130 LSR262130:LSU262130 MCN262130:MCQ262130 MMJ262130:MMM262130 MWF262130:MWI262130 NGB262130:NGE262130 NPX262130:NQA262130 NZT262130:NZW262130 OJP262130:OJS262130 OTL262130:OTO262130 PDH262130:PDK262130 PND262130:PNG262130 PWZ262130:PXC262130 QGV262130:QGY262130 QQR262130:QQU262130 RAN262130:RAQ262130 RKJ262130:RKM262130 RUF262130:RUI262130 SEB262130:SEE262130 SNX262130:SOA262130 SXT262130:SXW262130 THP262130:THS262130 TRL262130:TRO262130 UBH262130:UBK262130 ULD262130:ULG262130 UUZ262130:UVC262130 VEV262130:VEY262130 VOR262130:VOU262130 VYN262130:VYQ262130 WIJ262130:WIM262130 WSF262130:WSI262130 FT327666:FW327666 PP327666:PS327666 ZL327666:ZO327666 AJH327666:AJK327666 ATD327666:ATG327666 BCZ327666:BDC327666 BMV327666:BMY327666 BWR327666:BWU327666 CGN327666:CGQ327666 CQJ327666:CQM327666 DAF327666:DAI327666 DKB327666:DKE327666 DTX327666:DUA327666 EDT327666:EDW327666 ENP327666:ENS327666 EXL327666:EXO327666 FHH327666:FHK327666 FRD327666:FRG327666 GAZ327666:GBC327666 GKV327666:GKY327666 GUR327666:GUU327666 HEN327666:HEQ327666 HOJ327666:HOM327666 HYF327666:HYI327666 IIB327666:IIE327666 IRX327666:ISA327666 JBT327666:JBW327666 JLP327666:JLS327666 JVL327666:JVO327666 KFH327666:KFK327666 KPD327666:KPG327666 KYZ327666:KZC327666 LIV327666:LIY327666 LSR327666:LSU327666 MCN327666:MCQ327666 MMJ327666:MMM327666 MWF327666:MWI327666 NGB327666:NGE327666 NPX327666:NQA327666 NZT327666:NZW327666 OJP327666:OJS327666 OTL327666:OTO327666 PDH327666:PDK327666 PND327666:PNG327666 PWZ327666:PXC327666 QGV327666:QGY327666 QQR327666:QQU327666 RAN327666:RAQ327666 RKJ327666:RKM327666 RUF327666:RUI327666 SEB327666:SEE327666 SNX327666:SOA327666 SXT327666:SXW327666 THP327666:THS327666 TRL327666:TRO327666 UBH327666:UBK327666 ULD327666:ULG327666 UUZ327666:UVC327666 VEV327666:VEY327666 VOR327666:VOU327666 VYN327666:VYQ327666 WIJ327666:WIM327666 WSF327666:WSI327666 FT393202:FW393202 PP393202:PS393202 ZL393202:ZO393202 AJH393202:AJK393202 ATD393202:ATG393202 BCZ393202:BDC393202 BMV393202:BMY393202 BWR393202:BWU393202 CGN393202:CGQ393202 CQJ393202:CQM393202 DAF393202:DAI393202 DKB393202:DKE393202 DTX393202:DUA393202 EDT393202:EDW393202 ENP393202:ENS393202 EXL393202:EXO393202 FHH393202:FHK393202 FRD393202:FRG393202 GAZ393202:GBC393202 GKV393202:GKY393202 GUR393202:GUU393202 HEN393202:HEQ393202 HOJ393202:HOM393202 HYF393202:HYI393202 IIB393202:IIE393202 IRX393202:ISA393202 JBT393202:JBW393202 JLP393202:JLS393202 JVL393202:JVO393202 KFH393202:KFK393202 KPD393202:KPG393202 KYZ393202:KZC393202 LIV393202:LIY393202 LSR393202:LSU393202 MCN393202:MCQ393202 MMJ393202:MMM393202 MWF393202:MWI393202 NGB393202:NGE393202 NPX393202:NQA393202 NZT393202:NZW393202 OJP393202:OJS393202 OTL393202:OTO393202 PDH393202:PDK393202 PND393202:PNG393202 PWZ393202:PXC393202 QGV393202:QGY393202 QQR393202:QQU393202 RAN393202:RAQ393202 RKJ393202:RKM393202 RUF393202:RUI393202 SEB393202:SEE393202 SNX393202:SOA393202 SXT393202:SXW393202 THP393202:THS393202 TRL393202:TRO393202 UBH393202:UBK393202 ULD393202:ULG393202 UUZ393202:UVC393202 VEV393202:VEY393202 VOR393202:VOU393202 VYN393202:VYQ393202 WIJ393202:WIM393202 WSF393202:WSI393202 FT458738:FW458738 PP458738:PS458738 ZL458738:ZO458738 AJH458738:AJK458738 ATD458738:ATG458738 BCZ458738:BDC458738 BMV458738:BMY458738 BWR458738:BWU458738 CGN458738:CGQ458738 CQJ458738:CQM458738 DAF458738:DAI458738 DKB458738:DKE458738 DTX458738:DUA458738 EDT458738:EDW458738 ENP458738:ENS458738 EXL458738:EXO458738 FHH458738:FHK458738 FRD458738:FRG458738 GAZ458738:GBC458738 GKV458738:GKY458738 GUR458738:GUU458738 HEN458738:HEQ458738 HOJ458738:HOM458738 HYF458738:HYI458738 IIB458738:IIE458738 IRX458738:ISA458738 JBT458738:JBW458738 JLP458738:JLS458738 JVL458738:JVO458738 KFH458738:KFK458738 KPD458738:KPG458738 KYZ458738:KZC458738 LIV458738:LIY458738 LSR458738:LSU458738 MCN458738:MCQ458738 MMJ458738:MMM458738 MWF458738:MWI458738 NGB458738:NGE458738 NPX458738:NQA458738 NZT458738:NZW458738 OJP458738:OJS458738 OTL458738:OTO458738 PDH458738:PDK458738 PND458738:PNG458738 PWZ458738:PXC458738 QGV458738:QGY458738 QQR458738:QQU458738 RAN458738:RAQ458738 RKJ458738:RKM458738 RUF458738:RUI458738 SEB458738:SEE458738 SNX458738:SOA458738 SXT458738:SXW458738 THP458738:THS458738 TRL458738:TRO458738 UBH458738:UBK458738 ULD458738:ULG458738 UUZ458738:UVC458738 VEV458738:VEY458738 VOR458738:VOU458738 VYN458738:VYQ458738 WIJ458738:WIM458738 WSF458738:WSI458738 FT524274:FW524274 PP524274:PS524274 ZL524274:ZO524274 AJH524274:AJK524274 ATD524274:ATG524274 BCZ524274:BDC524274 BMV524274:BMY524274 BWR524274:BWU524274 CGN524274:CGQ524274 CQJ524274:CQM524274 DAF524274:DAI524274 DKB524274:DKE524274 DTX524274:DUA524274 EDT524274:EDW524274 ENP524274:ENS524274 EXL524274:EXO524274 FHH524274:FHK524274 FRD524274:FRG524274 GAZ524274:GBC524274 GKV524274:GKY524274 GUR524274:GUU524274 HEN524274:HEQ524274 HOJ524274:HOM524274 HYF524274:HYI524274 IIB524274:IIE524274 IRX524274:ISA524274 JBT524274:JBW524274 JLP524274:JLS524274 JVL524274:JVO524274 KFH524274:KFK524274 KPD524274:KPG524274 KYZ524274:KZC524274 LIV524274:LIY524274 LSR524274:LSU524274 MCN524274:MCQ524274 MMJ524274:MMM524274 MWF524274:MWI524274 NGB524274:NGE524274 NPX524274:NQA524274 NZT524274:NZW524274 OJP524274:OJS524274 OTL524274:OTO524274 PDH524274:PDK524274 PND524274:PNG524274 PWZ524274:PXC524274 QGV524274:QGY524274 QQR524274:QQU524274 RAN524274:RAQ524274 RKJ524274:RKM524274 RUF524274:RUI524274 SEB524274:SEE524274 SNX524274:SOA524274 SXT524274:SXW524274 THP524274:THS524274 TRL524274:TRO524274 UBH524274:UBK524274 ULD524274:ULG524274 UUZ524274:UVC524274 VEV524274:VEY524274 VOR524274:VOU524274 VYN524274:VYQ524274 WIJ524274:WIM524274 WSF524274:WSI524274 FT589810:FW589810 PP589810:PS589810 ZL589810:ZO589810 AJH589810:AJK589810 ATD589810:ATG589810 BCZ589810:BDC589810 BMV589810:BMY589810 BWR589810:BWU589810 CGN589810:CGQ589810 CQJ589810:CQM589810 DAF589810:DAI589810 DKB589810:DKE589810 DTX589810:DUA589810 EDT589810:EDW589810 ENP589810:ENS589810 EXL589810:EXO589810 FHH589810:FHK589810 FRD589810:FRG589810 GAZ589810:GBC589810 GKV589810:GKY589810 GUR589810:GUU589810 HEN589810:HEQ589810 HOJ589810:HOM589810 HYF589810:HYI589810 IIB589810:IIE589810 IRX589810:ISA589810 JBT589810:JBW589810 JLP589810:JLS589810 JVL589810:JVO589810 KFH589810:KFK589810 KPD589810:KPG589810 KYZ589810:KZC589810 LIV589810:LIY589810 LSR589810:LSU589810 MCN589810:MCQ589810 MMJ589810:MMM589810 MWF589810:MWI589810 NGB589810:NGE589810 NPX589810:NQA589810 NZT589810:NZW589810 OJP589810:OJS589810 OTL589810:OTO589810 PDH589810:PDK589810 PND589810:PNG589810 PWZ589810:PXC589810 QGV589810:QGY589810 QQR589810:QQU589810 RAN589810:RAQ589810 RKJ589810:RKM589810 RUF589810:RUI589810 SEB589810:SEE589810 SNX589810:SOA589810 SXT589810:SXW589810 THP589810:THS589810 TRL589810:TRO589810 UBH589810:UBK589810 ULD589810:ULG589810 UUZ589810:UVC589810 VEV589810:VEY589810 VOR589810:VOU589810 VYN589810:VYQ589810 WIJ589810:WIM589810 WSF589810:WSI589810 FT655346:FW655346 PP655346:PS655346 ZL655346:ZO655346 AJH655346:AJK655346 ATD655346:ATG655346 BCZ655346:BDC655346 BMV655346:BMY655346 BWR655346:BWU655346 CGN655346:CGQ655346 CQJ655346:CQM655346 DAF655346:DAI655346 DKB655346:DKE655346 DTX655346:DUA655346 EDT655346:EDW655346 ENP655346:ENS655346 EXL655346:EXO655346 FHH655346:FHK655346 FRD655346:FRG655346 GAZ655346:GBC655346 GKV655346:GKY655346 GUR655346:GUU655346 HEN655346:HEQ655346 HOJ655346:HOM655346 HYF655346:HYI655346 IIB655346:IIE655346 IRX655346:ISA655346 JBT655346:JBW655346 JLP655346:JLS655346 JVL655346:JVO655346 KFH655346:KFK655346 KPD655346:KPG655346 KYZ655346:KZC655346 LIV655346:LIY655346 LSR655346:LSU655346 MCN655346:MCQ655346 MMJ655346:MMM655346 MWF655346:MWI655346 NGB655346:NGE655346 NPX655346:NQA655346 NZT655346:NZW655346 OJP655346:OJS655346 OTL655346:OTO655346 PDH655346:PDK655346 PND655346:PNG655346 PWZ655346:PXC655346 QGV655346:QGY655346 QQR655346:QQU655346 RAN655346:RAQ655346 RKJ655346:RKM655346 RUF655346:RUI655346 SEB655346:SEE655346 SNX655346:SOA655346 SXT655346:SXW655346 THP655346:THS655346 TRL655346:TRO655346 UBH655346:UBK655346 ULD655346:ULG655346 UUZ655346:UVC655346 VEV655346:VEY655346 VOR655346:VOU655346 VYN655346:VYQ655346 WIJ655346:WIM655346 WSF655346:WSI655346 FT720882:FW720882 PP720882:PS720882 ZL720882:ZO720882 AJH720882:AJK720882 ATD720882:ATG720882 BCZ720882:BDC720882 BMV720882:BMY720882 BWR720882:BWU720882 CGN720882:CGQ720882 CQJ720882:CQM720882 DAF720882:DAI720882 DKB720882:DKE720882 DTX720882:DUA720882 EDT720882:EDW720882 ENP720882:ENS720882 EXL720882:EXO720882 FHH720882:FHK720882 FRD720882:FRG720882 GAZ720882:GBC720882 GKV720882:GKY720882 GUR720882:GUU720882 HEN720882:HEQ720882 HOJ720882:HOM720882 HYF720882:HYI720882 IIB720882:IIE720882 IRX720882:ISA720882 JBT720882:JBW720882 JLP720882:JLS720882 JVL720882:JVO720882 KFH720882:KFK720882 KPD720882:KPG720882 KYZ720882:KZC720882 LIV720882:LIY720882 LSR720882:LSU720882 MCN720882:MCQ720882 MMJ720882:MMM720882 MWF720882:MWI720882 NGB720882:NGE720882 NPX720882:NQA720882 NZT720882:NZW720882 OJP720882:OJS720882 OTL720882:OTO720882 PDH720882:PDK720882 PND720882:PNG720882 PWZ720882:PXC720882 QGV720882:QGY720882 QQR720882:QQU720882 RAN720882:RAQ720882 RKJ720882:RKM720882 RUF720882:RUI720882 SEB720882:SEE720882 SNX720882:SOA720882 SXT720882:SXW720882 THP720882:THS720882 TRL720882:TRO720882 UBH720882:UBK720882 ULD720882:ULG720882 UUZ720882:UVC720882 VEV720882:VEY720882 VOR720882:VOU720882 VYN720882:VYQ720882 WIJ720882:WIM720882 WSF720882:WSI720882 FT786418:FW786418 PP786418:PS786418 ZL786418:ZO786418 AJH786418:AJK786418 ATD786418:ATG786418 BCZ786418:BDC786418 BMV786418:BMY786418 BWR786418:BWU786418 CGN786418:CGQ786418 CQJ786418:CQM786418 DAF786418:DAI786418 DKB786418:DKE786418 DTX786418:DUA786418 EDT786418:EDW786418 ENP786418:ENS786418 EXL786418:EXO786418 FHH786418:FHK786418 FRD786418:FRG786418 GAZ786418:GBC786418 GKV786418:GKY786418 GUR786418:GUU786418 HEN786418:HEQ786418 HOJ786418:HOM786418 HYF786418:HYI786418 IIB786418:IIE786418 IRX786418:ISA786418 JBT786418:JBW786418 JLP786418:JLS786418 JVL786418:JVO786418 KFH786418:KFK786418 KPD786418:KPG786418 KYZ786418:KZC786418 LIV786418:LIY786418 LSR786418:LSU786418 MCN786418:MCQ786418 MMJ786418:MMM786418 MWF786418:MWI786418 NGB786418:NGE786418 NPX786418:NQA786418 NZT786418:NZW786418 OJP786418:OJS786418 OTL786418:OTO786418 PDH786418:PDK786418 PND786418:PNG786418 PWZ786418:PXC786418 QGV786418:QGY786418 QQR786418:QQU786418 RAN786418:RAQ786418 RKJ786418:RKM786418 RUF786418:RUI786418 SEB786418:SEE786418 SNX786418:SOA786418 SXT786418:SXW786418 THP786418:THS786418 TRL786418:TRO786418 UBH786418:UBK786418 ULD786418:ULG786418 UUZ786418:UVC786418 VEV786418:VEY786418 VOR786418:VOU786418 VYN786418:VYQ786418 WIJ786418:WIM786418 WSF786418:WSI786418 FT851954:FW851954 PP851954:PS851954 ZL851954:ZO851954 AJH851954:AJK851954 ATD851954:ATG851954 BCZ851954:BDC851954 BMV851954:BMY851954 BWR851954:BWU851954 CGN851954:CGQ851954 CQJ851954:CQM851954 DAF851954:DAI851954 DKB851954:DKE851954 DTX851954:DUA851954 EDT851954:EDW851954 ENP851954:ENS851954 EXL851954:EXO851954 FHH851954:FHK851954 FRD851954:FRG851954 GAZ851954:GBC851954 GKV851954:GKY851954 GUR851954:GUU851954 HEN851954:HEQ851954 HOJ851954:HOM851954 HYF851954:HYI851954 IIB851954:IIE851954 IRX851954:ISA851954 JBT851954:JBW851954 JLP851954:JLS851954 JVL851954:JVO851954 KFH851954:KFK851954 KPD851954:KPG851954 KYZ851954:KZC851954 LIV851954:LIY851954 LSR851954:LSU851954 MCN851954:MCQ851954 MMJ851954:MMM851954 MWF851954:MWI851954 NGB851954:NGE851954 NPX851954:NQA851954 NZT851954:NZW851954 OJP851954:OJS851954 OTL851954:OTO851954 PDH851954:PDK851954 PND851954:PNG851954 PWZ851954:PXC851954 QGV851954:QGY851954 QQR851954:QQU851954 RAN851954:RAQ851954 RKJ851954:RKM851954 RUF851954:RUI851954 SEB851954:SEE851954 SNX851954:SOA851954 SXT851954:SXW851954 THP851954:THS851954 TRL851954:TRO851954 UBH851954:UBK851954 ULD851954:ULG851954 UUZ851954:UVC851954 VEV851954:VEY851954 VOR851954:VOU851954 VYN851954:VYQ851954 WIJ851954:WIM851954 WSF851954:WSI851954 FT917490:FW917490 PP917490:PS917490 ZL917490:ZO917490 AJH917490:AJK917490 ATD917490:ATG917490 BCZ917490:BDC917490 BMV917490:BMY917490 BWR917490:BWU917490 CGN917490:CGQ917490 CQJ917490:CQM917490 DAF917490:DAI917490 DKB917490:DKE917490 DTX917490:DUA917490 EDT917490:EDW917490 ENP917490:ENS917490 EXL917490:EXO917490 FHH917490:FHK917490 FRD917490:FRG917490 GAZ917490:GBC917490 GKV917490:GKY917490 GUR917490:GUU917490 HEN917490:HEQ917490 HOJ917490:HOM917490 HYF917490:HYI917490 IIB917490:IIE917490 IRX917490:ISA917490 JBT917490:JBW917490 JLP917490:JLS917490 JVL917490:JVO917490 KFH917490:KFK917490 KPD917490:KPG917490 KYZ917490:KZC917490 LIV917490:LIY917490 LSR917490:LSU917490 MCN917490:MCQ917490 MMJ917490:MMM917490 MWF917490:MWI917490 NGB917490:NGE917490 NPX917490:NQA917490 NZT917490:NZW917490 OJP917490:OJS917490 OTL917490:OTO917490 PDH917490:PDK917490 PND917490:PNG917490 PWZ917490:PXC917490 QGV917490:QGY917490 QQR917490:QQU917490 RAN917490:RAQ917490 RKJ917490:RKM917490 RUF917490:RUI917490 SEB917490:SEE917490 SNX917490:SOA917490 SXT917490:SXW917490 THP917490:THS917490 TRL917490:TRO917490 UBH917490:UBK917490 ULD917490:ULG917490 UUZ917490:UVC917490 VEV917490:VEY917490 VOR917490:VOU917490 VYN917490:VYQ917490 WIJ917490:WIM917490 WSF917490:WSI917490 FT983026:FW983026 PP983026:PS983026 ZL983026:ZO983026 AJH983026:AJK983026 ATD983026:ATG983026 BCZ983026:BDC983026 BMV983026:BMY983026 BWR983026:BWU983026 CGN983026:CGQ983026 CQJ983026:CQM983026 DAF983026:DAI983026 DKB983026:DKE983026 DTX983026:DUA983026 EDT983026:EDW983026 ENP983026:ENS983026 EXL983026:EXO983026 FHH983026:FHK983026 FRD983026:FRG983026 GAZ983026:GBC983026 GKV983026:GKY983026 GUR983026:GUU983026 HEN983026:HEQ983026 HOJ983026:HOM983026 HYF983026:HYI983026 IIB983026:IIE983026 IRX983026:ISA983026 JBT983026:JBW983026 JLP983026:JLS983026 JVL983026:JVO983026 KFH983026:KFK983026 KPD983026:KPG983026 KYZ983026:KZC983026 LIV983026:LIY983026 LSR983026:LSU983026 MCN983026:MCQ983026 MMJ983026:MMM983026 MWF983026:MWI983026 NGB983026:NGE983026 NPX983026:NQA983026 NZT983026:NZW983026 OJP983026:OJS983026 OTL983026:OTO983026 PDH983026:PDK983026 PND983026:PNG983026 PWZ983026:PXC983026 QGV983026:QGY983026 QQR983026:QQU983026 RAN983026:RAQ983026 RKJ983026:RKM983026 RUF983026:RUI983026 SEB983026:SEE983026 SNX983026:SOA983026 SXT983026:SXW983026 THP983026:THS983026 TRL983026:TRO983026 UBH983026:UBK983026 ULD983026:ULG983026 UUZ983026:UVC983026 VEV983026:VEY983026 VOR983026:VOU983026 VYN983026:VYQ983026 WIJ983026:WIM983026 WSF983026:WSI983026 FO983025:FR983025 PK983025:PN983025 ZG983025:ZJ983025 AJC983025:AJF983025 ASY983025:ATB983025 BCU983025:BCX983025 BMQ983025:BMT983025 BWM983025:BWP983025 CGI983025:CGL983025 CQE983025:CQH983025 DAA983025:DAD983025 DJW983025:DJZ983025 DTS983025:DTV983025 EDO983025:EDR983025 ENK983025:ENN983025 EXG983025:EXJ983025 FHC983025:FHF983025 FQY983025:FRB983025 GAU983025:GAX983025 GKQ983025:GKT983025 GUM983025:GUP983025 HEI983025:HEL983025 HOE983025:HOH983025 HYA983025:HYD983025 IHW983025:IHZ983025 IRS983025:IRV983025 JBO983025:JBR983025 JLK983025:JLN983025 JVG983025:JVJ983025 KFC983025:KFF983025 KOY983025:KPB983025 KYU983025:KYX983025 LIQ983025:LIT983025 LSM983025:LSP983025 MCI983025:MCL983025 MME983025:MMH983025 MWA983025:MWD983025 NFW983025:NFZ983025 NPS983025:NPV983025 NZO983025:NZR983025 OJK983025:OJN983025 OTG983025:OTJ983025 PDC983025:PDF983025 PMY983025:PNB983025 PWU983025:PWX983025 QGQ983025:QGT983025 QQM983025:QQP983025 RAI983025:RAL983025 RKE983025:RKH983025 RUA983025:RUD983025 SDW983025:SDZ983025 SNS983025:SNV983025 SXO983025:SXR983025 THK983025:THN983025 TRG983025:TRJ983025 UBC983025:UBF983025 UKY983025:ULB983025 UUU983025:UUX983025 VEQ983025:VET983025 VOM983025:VOP983025 VYI983025:VYL983025 WIE983025:WIH983025 WSA983025:WSD983025 FO65521:FR65521 PK65521:PN65521 ZG65521:ZJ65521 AJC65521:AJF65521 ASY65521:ATB65521 BCU65521:BCX65521 BMQ65521:BMT65521 BWM65521:BWP65521 CGI65521:CGL65521 CQE65521:CQH65521 DAA65521:DAD65521 DJW65521:DJZ65521 DTS65521:DTV65521 EDO65521:EDR65521 ENK65521:ENN65521 EXG65521:EXJ65521 FHC65521:FHF65521 FQY65521:FRB65521 GAU65521:GAX65521 GKQ65521:GKT65521 GUM65521:GUP65521 HEI65521:HEL65521 HOE65521:HOH65521 HYA65521:HYD65521 IHW65521:IHZ65521 IRS65521:IRV65521 JBO65521:JBR65521 JLK65521:JLN65521 JVG65521:JVJ65521 KFC65521:KFF65521 KOY65521:KPB65521 KYU65521:KYX65521 LIQ65521:LIT65521 LSM65521:LSP65521 MCI65521:MCL65521 MME65521:MMH65521 MWA65521:MWD65521 NFW65521:NFZ65521 NPS65521:NPV65521 NZO65521:NZR65521 OJK65521:OJN65521 OTG65521:OTJ65521 PDC65521:PDF65521 PMY65521:PNB65521 PWU65521:PWX65521 QGQ65521:QGT65521 QQM65521:QQP65521 RAI65521:RAL65521 RKE65521:RKH65521 RUA65521:RUD65521 SDW65521:SDZ65521 SNS65521:SNV65521 SXO65521:SXR65521 THK65521:THN65521 TRG65521:TRJ65521 UBC65521:UBF65521 UKY65521:ULB65521 UUU65521:UUX65521 VEQ65521:VET65521 VOM65521:VOP65521 VYI65521:VYL65521 WIE65521:WIH65521 WSA65521:WSD65521 FO131057:FR131057 PK131057:PN131057 ZG131057:ZJ131057 AJC131057:AJF131057 ASY131057:ATB131057 BCU131057:BCX131057 BMQ131057:BMT131057 BWM131057:BWP131057 CGI131057:CGL131057 CQE131057:CQH131057 DAA131057:DAD131057 DJW131057:DJZ131057 DTS131057:DTV131057 EDO131057:EDR131057 ENK131057:ENN131057 EXG131057:EXJ131057 FHC131057:FHF131057 FQY131057:FRB131057 GAU131057:GAX131057 GKQ131057:GKT131057 GUM131057:GUP131057 HEI131057:HEL131057 HOE131057:HOH131057 HYA131057:HYD131057 IHW131057:IHZ131057 IRS131057:IRV131057 JBO131057:JBR131057 JLK131057:JLN131057 JVG131057:JVJ131057 KFC131057:KFF131057 KOY131057:KPB131057 KYU131057:KYX131057 LIQ131057:LIT131057 LSM131057:LSP131057 MCI131057:MCL131057 MME131057:MMH131057 MWA131057:MWD131057 NFW131057:NFZ131057 NPS131057:NPV131057 NZO131057:NZR131057 OJK131057:OJN131057 OTG131057:OTJ131057 PDC131057:PDF131057 PMY131057:PNB131057 PWU131057:PWX131057 QGQ131057:QGT131057 QQM131057:QQP131057 RAI131057:RAL131057 RKE131057:RKH131057 RUA131057:RUD131057 SDW131057:SDZ131057 SNS131057:SNV131057 SXO131057:SXR131057 THK131057:THN131057 TRG131057:TRJ131057 UBC131057:UBF131057 UKY131057:ULB131057 UUU131057:UUX131057 VEQ131057:VET131057 VOM131057:VOP131057 VYI131057:VYL131057 WIE131057:WIH131057 WSA131057:WSD131057 FO196593:FR196593 PK196593:PN196593 ZG196593:ZJ196593 AJC196593:AJF196593 ASY196593:ATB196593 BCU196593:BCX196593 BMQ196593:BMT196593 BWM196593:BWP196593 CGI196593:CGL196593 CQE196593:CQH196593 DAA196593:DAD196593 DJW196593:DJZ196593 DTS196593:DTV196593 EDO196593:EDR196593 ENK196593:ENN196593 EXG196593:EXJ196593 FHC196593:FHF196593 FQY196593:FRB196593 GAU196593:GAX196593 GKQ196593:GKT196593 GUM196593:GUP196593 HEI196593:HEL196593 HOE196593:HOH196593 HYA196593:HYD196593 IHW196593:IHZ196593 IRS196593:IRV196593 JBO196593:JBR196593 JLK196593:JLN196593 JVG196593:JVJ196593 KFC196593:KFF196593 KOY196593:KPB196593 KYU196593:KYX196593 LIQ196593:LIT196593 LSM196593:LSP196593 MCI196593:MCL196593 MME196593:MMH196593 MWA196593:MWD196593 NFW196593:NFZ196593 NPS196593:NPV196593 NZO196593:NZR196593 OJK196593:OJN196593 OTG196593:OTJ196593 PDC196593:PDF196593 PMY196593:PNB196593 PWU196593:PWX196593 QGQ196593:QGT196593 QQM196593:QQP196593 RAI196593:RAL196593 RKE196593:RKH196593 RUA196593:RUD196593 SDW196593:SDZ196593 SNS196593:SNV196593 SXO196593:SXR196593 THK196593:THN196593 TRG196593:TRJ196593 UBC196593:UBF196593 UKY196593:ULB196593 UUU196593:UUX196593 VEQ196593:VET196593 VOM196593:VOP196593 VYI196593:VYL196593 WIE196593:WIH196593 WSA196593:WSD196593 FO262129:FR262129 PK262129:PN262129 ZG262129:ZJ262129 AJC262129:AJF262129 ASY262129:ATB262129 BCU262129:BCX262129 BMQ262129:BMT262129 BWM262129:BWP262129 CGI262129:CGL262129 CQE262129:CQH262129 DAA262129:DAD262129 DJW262129:DJZ262129 DTS262129:DTV262129 EDO262129:EDR262129 ENK262129:ENN262129 EXG262129:EXJ262129 FHC262129:FHF262129 FQY262129:FRB262129 GAU262129:GAX262129 GKQ262129:GKT262129 GUM262129:GUP262129 HEI262129:HEL262129 HOE262129:HOH262129 HYA262129:HYD262129 IHW262129:IHZ262129 IRS262129:IRV262129 JBO262129:JBR262129 JLK262129:JLN262129 JVG262129:JVJ262129 KFC262129:KFF262129 KOY262129:KPB262129 KYU262129:KYX262129 LIQ262129:LIT262129 LSM262129:LSP262129 MCI262129:MCL262129 MME262129:MMH262129 MWA262129:MWD262129 NFW262129:NFZ262129 NPS262129:NPV262129 NZO262129:NZR262129 OJK262129:OJN262129 OTG262129:OTJ262129 PDC262129:PDF262129 PMY262129:PNB262129 PWU262129:PWX262129 QGQ262129:QGT262129 QQM262129:QQP262129 RAI262129:RAL262129 RKE262129:RKH262129 RUA262129:RUD262129 SDW262129:SDZ262129 SNS262129:SNV262129 SXO262129:SXR262129 THK262129:THN262129 TRG262129:TRJ262129 UBC262129:UBF262129 UKY262129:ULB262129 UUU262129:UUX262129 VEQ262129:VET262129 VOM262129:VOP262129 VYI262129:VYL262129 WIE262129:WIH262129 WSA262129:WSD262129 FO327665:FR327665 PK327665:PN327665 ZG327665:ZJ327665 AJC327665:AJF327665 ASY327665:ATB327665 BCU327665:BCX327665 BMQ327665:BMT327665 BWM327665:BWP327665 CGI327665:CGL327665 CQE327665:CQH327665 DAA327665:DAD327665 DJW327665:DJZ327665 DTS327665:DTV327665 EDO327665:EDR327665 ENK327665:ENN327665 EXG327665:EXJ327665 FHC327665:FHF327665 FQY327665:FRB327665 GAU327665:GAX327665 GKQ327665:GKT327665 GUM327665:GUP327665 HEI327665:HEL327665 HOE327665:HOH327665 HYA327665:HYD327665 IHW327665:IHZ327665 IRS327665:IRV327665 JBO327665:JBR327665 JLK327665:JLN327665 JVG327665:JVJ327665 KFC327665:KFF327665 KOY327665:KPB327665 KYU327665:KYX327665 LIQ327665:LIT327665 LSM327665:LSP327665 MCI327665:MCL327665 MME327665:MMH327665 MWA327665:MWD327665 NFW327665:NFZ327665 NPS327665:NPV327665 NZO327665:NZR327665 OJK327665:OJN327665 OTG327665:OTJ327665 PDC327665:PDF327665 PMY327665:PNB327665 PWU327665:PWX327665 QGQ327665:QGT327665 QQM327665:QQP327665 RAI327665:RAL327665 RKE327665:RKH327665 RUA327665:RUD327665 SDW327665:SDZ327665 SNS327665:SNV327665 SXO327665:SXR327665 THK327665:THN327665 TRG327665:TRJ327665 UBC327665:UBF327665 UKY327665:ULB327665 UUU327665:UUX327665 VEQ327665:VET327665 VOM327665:VOP327665 VYI327665:VYL327665 WIE327665:WIH327665 WSA327665:WSD327665 FO393201:FR393201 PK393201:PN393201 ZG393201:ZJ393201 AJC393201:AJF393201 ASY393201:ATB393201 BCU393201:BCX393201 BMQ393201:BMT393201 BWM393201:BWP393201 CGI393201:CGL393201 CQE393201:CQH393201 DAA393201:DAD393201 DJW393201:DJZ393201 DTS393201:DTV393201 EDO393201:EDR393201 ENK393201:ENN393201 EXG393201:EXJ393201 FHC393201:FHF393201 FQY393201:FRB393201 GAU393201:GAX393201 GKQ393201:GKT393201 GUM393201:GUP393201 HEI393201:HEL393201 HOE393201:HOH393201 HYA393201:HYD393201 IHW393201:IHZ393201 IRS393201:IRV393201 JBO393201:JBR393201 JLK393201:JLN393201 JVG393201:JVJ393201 KFC393201:KFF393201 KOY393201:KPB393201 KYU393201:KYX393201 LIQ393201:LIT393201 LSM393201:LSP393201 MCI393201:MCL393201 MME393201:MMH393201 MWA393201:MWD393201 NFW393201:NFZ393201 NPS393201:NPV393201 NZO393201:NZR393201 OJK393201:OJN393201 OTG393201:OTJ393201 PDC393201:PDF393201 PMY393201:PNB393201 PWU393201:PWX393201 QGQ393201:QGT393201 QQM393201:QQP393201 RAI393201:RAL393201 RKE393201:RKH393201 RUA393201:RUD393201 SDW393201:SDZ393201 SNS393201:SNV393201 SXO393201:SXR393201 THK393201:THN393201 TRG393201:TRJ393201 UBC393201:UBF393201 UKY393201:ULB393201 UUU393201:UUX393201 VEQ393201:VET393201 VOM393201:VOP393201 VYI393201:VYL393201 WIE393201:WIH393201 WSA393201:WSD393201 FO458737:FR458737 PK458737:PN458737 ZG458737:ZJ458737 AJC458737:AJF458737 ASY458737:ATB458737 BCU458737:BCX458737 BMQ458737:BMT458737 BWM458737:BWP458737 CGI458737:CGL458737 CQE458737:CQH458737 DAA458737:DAD458737 DJW458737:DJZ458737 DTS458737:DTV458737 EDO458737:EDR458737 ENK458737:ENN458737 EXG458737:EXJ458737 FHC458737:FHF458737 FQY458737:FRB458737 GAU458737:GAX458737 GKQ458737:GKT458737 GUM458737:GUP458737 HEI458737:HEL458737 HOE458737:HOH458737 HYA458737:HYD458737 IHW458737:IHZ458737 IRS458737:IRV458737 JBO458737:JBR458737 JLK458737:JLN458737 JVG458737:JVJ458737 KFC458737:KFF458737 KOY458737:KPB458737 KYU458737:KYX458737 LIQ458737:LIT458737 LSM458737:LSP458737 MCI458737:MCL458737 MME458737:MMH458737 MWA458737:MWD458737 NFW458737:NFZ458737 NPS458737:NPV458737 NZO458737:NZR458737 OJK458737:OJN458737 OTG458737:OTJ458737 PDC458737:PDF458737 PMY458737:PNB458737 PWU458737:PWX458737 QGQ458737:QGT458737 QQM458737:QQP458737 RAI458737:RAL458737 RKE458737:RKH458737 RUA458737:RUD458737 SDW458737:SDZ458737 SNS458737:SNV458737 SXO458737:SXR458737 THK458737:THN458737 TRG458737:TRJ458737 UBC458737:UBF458737 UKY458737:ULB458737 UUU458737:UUX458737 VEQ458737:VET458737 VOM458737:VOP458737 VYI458737:VYL458737 WIE458737:WIH458737 WSA458737:WSD458737 FO524273:FR524273 PK524273:PN524273 ZG524273:ZJ524273 AJC524273:AJF524273 ASY524273:ATB524273 BCU524273:BCX524273 BMQ524273:BMT524273 BWM524273:BWP524273 CGI524273:CGL524273 CQE524273:CQH524273 DAA524273:DAD524273 DJW524273:DJZ524273 DTS524273:DTV524273 EDO524273:EDR524273 ENK524273:ENN524273 EXG524273:EXJ524273 FHC524273:FHF524273 FQY524273:FRB524273 GAU524273:GAX524273 GKQ524273:GKT524273 GUM524273:GUP524273 HEI524273:HEL524273 HOE524273:HOH524273 HYA524273:HYD524273 IHW524273:IHZ524273 IRS524273:IRV524273 JBO524273:JBR524273 JLK524273:JLN524273 JVG524273:JVJ524273 KFC524273:KFF524273 KOY524273:KPB524273 KYU524273:KYX524273 LIQ524273:LIT524273 LSM524273:LSP524273 MCI524273:MCL524273 MME524273:MMH524273 MWA524273:MWD524273 NFW524273:NFZ524273 NPS524273:NPV524273 NZO524273:NZR524273 OJK524273:OJN524273 OTG524273:OTJ524273 PDC524273:PDF524273 PMY524273:PNB524273 PWU524273:PWX524273 QGQ524273:QGT524273 QQM524273:QQP524273 RAI524273:RAL524273 RKE524273:RKH524273 RUA524273:RUD524273 SDW524273:SDZ524273 SNS524273:SNV524273 SXO524273:SXR524273 THK524273:THN524273 TRG524273:TRJ524273 UBC524273:UBF524273 UKY524273:ULB524273 UUU524273:UUX524273 VEQ524273:VET524273 VOM524273:VOP524273 VYI524273:VYL524273 WIE524273:WIH524273 WSA524273:WSD524273 FO589809:FR589809 PK589809:PN589809 ZG589809:ZJ589809 AJC589809:AJF589809 ASY589809:ATB589809 BCU589809:BCX589809 BMQ589809:BMT589809 BWM589809:BWP589809 CGI589809:CGL589809 CQE589809:CQH589809 DAA589809:DAD589809 DJW589809:DJZ589809 DTS589809:DTV589809 EDO589809:EDR589809 ENK589809:ENN589809 EXG589809:EXJ589809 FHC589809:FHF589809 FQY589809:FRB589809 GAU589809:GAX589809 GKQ589809:GKT589809 GUM589809:GUP589809 HEI589809:HEL589809 HOE589809:HOH589809 HYA589809:HYD589809 IHW589809:IHZ589809 IRS589809:IRV589809 JBO589809:JBR589809 JLK589809:JLN589809 JVG589809:JVJ589809 KFC589809:KFF589809 KOY589809:KPB589809 KYU589809:KYX589809 LIQ589809:LIT589809 LSM589809:LSP589809 MCI589809:MCL589809 MME589809:MMH589809 MWA589809:MWD589809 NFW589809:NFZ589809 NPS589809:NPV589809 NZO589809:NZR589809 OJK589809:OJN589809 OTG589809:OTJ589809 PDC589809:PDF589809 PMY589809:PNB589809 PWU589809:PWX589809 QGQ589809:QGT589809 QQM589809:QQP589809 RAI589809:RAL589809 RKE589809:RKH589809 RUA589809:RUD589809 SDW589809:SDZ589809 SNS589809:SNV589809 SXO589809:SXR589809 THK589809:THN589809 TRG589809:TRJ589809 UBC589809:UBF589809 UKY589809:ULB589809 UUU589809:UUX589809 VEQ589809:VET589809 VOM589809:VOP589809 VYI589809:VYL589809 WIE589809:WIH589809 WSA589809:WSD589809 FO655345:FR655345 PK655345:PN655345 ZG655345:ZJ655345 AJC655345:AJF655345 ASY655345:ATB655345 BCU655345:BCX655345 BMQ655345:BMT655345 BWM655345:BWP655345 CGI655345:CGL655345 CQE655345:CQH655345 DAA655345:DAD655345 DJW655345:DJZ655345 DTS655345:DTV655345 EDO655345:EDR655345 ENK655345:ENN655345 EXG655345:EXJ655345 FHC655345:FHF655345 FQY655345:FRB655345 GAU655345:GAX655345 GKQ655345:GKT655345 GUM655345:GUP655345 HEI655345:HEL655345 HOE655345:HOH655345 HYA655345:HYD655345 IHW655345:IHZ655345 IRS655345:IRV655345 JBO655345:JBR655345 JLK655345:JLN655345 JVG655345:JVJ655345 KFC655345:KFF655345 KOY655345:KPB655345 KYU655345:KYX655345 LIQ655345:LIT655345 LSM655345:LSP655345 MCI655345:MCL655345 MME655345:MMH655345 MWA655345:MWD655345 NFW655345:NFZ655345 NPS655345:NPV655345 NZO655345:NZR655345 OJK655345:OJN655345 OTG655345:OTJ655345 PDC655345:PDF655345 PMY655345:PNB655345 PWU655345:PWX655345 QGQ655345:QGT655345 QQM655345:QQP655345 RAI655345:RAL655345 RKE655345:RKH655345 RUA655345:RUD655345 SDW655345:SDZ655345 SNS655345:SNV655345 SXO655345:SXR655345 THK655345:THN655345 TRG655345:TRJ655345 UBC655345:UBF655345 UKY655345:ULB655345 UUU655345:UUX655345 VEQ655345:VET655345 VOM655345:VOP655345 VYI655345:VYL655345 WIE655345:WIH655345 WSA655345:WSD655345 FO720881:FR720881 PK720881:PN720881 ZG720881:ZJ720881 AJC720881:AJF720881 ASY720881:ATB720881 BCU720881:BCX720881 BMQ720881:BMT720881 BWM720881:BWP720881 CGI720881:CGL720881 CQE720881:CQH720881 DAA720881:DAD720881 DJW720881:DJZ720881 DTS720881:DTV720881 EDO720881:EDR720881 ENK720881:ENN720881 EXG720881:EXJ720881 FHC720881:FHF720881 FQY720881:FRB720881 GAU720881:GAX720881 GKQ720881:GKT720881 GUM720881:GUP720881 HEI720881:HEL720881 HOE720881:HOH720881 HYA720881:HYD720881 IHW720881:IHZ720881 IRS720881:IRV720881 JBO720881:JBR720881 JLK720881:JLN720881 JVG720881:JVJ720881 KFC720881:KFF720881 KOY720881:KPB720881 KYU720881:KYX720881 LIQ720881:LIT720881 LSM720881:LSP720881 MCI720881:MCL720881 MME720881:MMH720881 MWA720881:MWD720881 NFW720881:NFZ720881 NPS720881:NPV720881 NZO720881:NZR720881 OJK720881:OJN720881 OTG720881:OTJ720881 PDC720881:PDF720881 PMY720881:PNB720881 PWU720881:PWX720881 QGQ720881:QGT720881 QQM720881:QQP720881 RAI720881:RAL720881 RKE720881:RKH720881 RUA720881:RUD720881 SDW720881:SDZ720881 SNS720881:SNV720881 SXO720881:SXR720881 THK720881:THN720881 TRG720881:TRJ720881 UBC720881:UBF720881 UKY720881:ULB720881 UUU720881:UUX720881 VEQ720881:VET720881 VOM720881:VOP720881 VYI720881:VYL720881 WIE720881:WIH720881 WSA720881:WSD720881 FO786417:FR786417 PK786417:PN786417 ZG786417:ZJ786417 AJC786417:AJF786417 ASY786417:ATB786417 BCU786417:BCX786417 BMQ786417:BMT786417 BWM786417:BWP786417 CGI786417:CGL786417 CQE786417:CQH786417 DAA786417:DAD786417 DJW786417:DJZ786417 DTS786417:DTV786417 EDO786417:EDR786417 ENK786417:ENN786417 EXG786417:EXJ786417 FHC786417:FHF786417 FQY786417:FRB786417 GAU786417:GAX786417 GKQ786417:GKT786417 GUM786417:GUP786417 HEI786417:HEL786417 HOE786417:HOH786417 HYA786417:HYD786417 IHW786417:IHZ786417 IRS786417:IRV786417 JBO786417:JBR786417 JLK786417:JLN786417 JVG786417:JVJ786417 KFC786417:KFF786417 KOY786417:KPB786417 KYU786417:KYX786417 LIQ786417:LIT786417 LSM786417:LSP786417 MCI786417:MCL786417 MME786417:MMH786417 MWA786417:MWD786417 NFW786417:NFZ786417 NPS786417:NPV786417 NZO786417:NZR786417 OJK786417:OJN786417 OTG786417:OTJ786417 PDC786417:PDF786417 PMY786417:PNB786417 PWU786417:PWX786417 QGQ786417:QGT786417 QQM786417:QQP786417 RAI786417:RAL786417 RKE786417:RKH786417 RUA786417:RUD786417 SDW786417:SDZ786417 SNS786417:SNV786417 SXO786417:SXR786417 THK786417:THN786417 TRG786417:TRJ786417 UBC786417:UBF786417 UKY786417:ULB786417 UUU786417:UUX786417 VEQ786417:VET786417 VOM786417:VOP786417 VYI786417:VYL786417 WIE786417:WIH786417 WSA786417:WSD786417 FO851953:FR851953 PK851953:PN851953 ZG851953:ZJ851953 AJC851953:AJF851953 ASY851953:ATB851953 BCU851953:BCX851953 BMQ851953:BMT851953 BWM851953:BWP851953 CGI851953:CGL851953 CQE851953:CQH851953 DAA851953:DAD851953 DJW851953:DJZ851953 DTS851953:DTV851953 EDO851953:EDR851953 ENK851953:ENN851953 EXG851953:EXJ851953 FHC851953:FHF851953 FQY851953:FRB851953 GAU851953:GAX851953 GKQ851953:GKT851953 GUM851953:GUP851953 HEI851953:HEL851953 HOE851953:HOH851953 HYA851953:HYD851953 IHW851953:IHZ851953 IRS851953:IRV851953 JBO851953:JBR851953 JLK851953:JLN851953 JVG851953:JVJ851953 KFC851953:KFF851953 KOY851953:KPB851953 KYU851953:KYX851953 LIQ851953:LIT851953 LSM851953:LSP851953 MCI851953:MCL851953 MME851953:MMH851953 MWA851953:MWD851953 NFW851953:NFZ851953 NPS851953:NPV851953 NZO851953:NZR851953 OJK851953:OJN851953 OTG851953:OTJ851953 PDC851953:PDF851953 PMY851953:PNB851953 PWU851953:PWX851953 QGQ851953:QGT851953 QQM851953:QQP851953 RAI851953:RAL851953 RKE851953:RKH851953 RUA851953:RUD851953 SDW851953:SDZ851953 SNS851953:SNV851953 SXO851953:SXR851953 THK851953:THN851953 TRG851953:TRJ851953 UBC851953:UBF851953 UKY851953:ULB851953 UUU851953:UUX851953 VEQ851953:VET851953 VOM851953:VOP851953 VYI851953:VYL851953 WIE851953:WIH851953 WSA851953:WSD851953 FO917489:FR917489 PK917489:PN917489 ZG917489:ZJ917489 AJC917489:AJF917489 ASY917489:ATB917489 BCU917489:BCX917489 BMQ917489:BMT917489 BWM917489:BWP917489 CGI917489:CGL917489 CQE917489:CQH917489 DAA917489:DAD917489 DJW917489:DJZ917489 DTS917489:DTV917489 EDO917489:EDR917489 ENK917489:ENN917489 EXG917489:EXJ917489 FHC917489:FHF917489 FQY917489:FRB917489 GAU917489:GAX917489 GKQ917489:GKT917489 GUM917489:GUP917489 HEI917489:HEL917489 HOE917489:HOH917489 HYA917489:HYD917489 IHW917489:IHZ917489 IRS917489:IRV917489 JBO917489:JBR917489 JLK917489:JLN917489 JVG917489:JVJ917489 KFC917489:KFF917489 KOY917489:KPB917489 KYU917489:KYX917489 LIQ917489:LIT917489 LSM917489:LSP917489 MCI917489:MCL917489 MME917489:MMH917489 MWA917489:MWD917489 NFW917489:NFZ917489 NPS917489:NPV917489 NZO917489:NZR917489 OJK917489:OJN917489 OTG917489:OTJ917489 PDC917489:PDF917489 PMY917489:PNB917489 PWU917489:PWX917489 QGQ917489:QGT917489 QQM917489:QQP917489 RAI917489:RAL917489 RKE917489:RKH917489 RUA917489:RUD917489 SDW917489:SDZ917489 SNS917489:SNV917489 SXO917489:SXR917489 THK917489:THN917489 TRG917489:TRJ917489 UBC917489:UBF917489 UKY917489:ULB917489 UUU917489:UUX917489 VEQ917489:VET917489 VOM917489:VOP917489 VYI917489:VYL917489 WIE917489:WIH917489 WSA917489:WSD917489" xr:uid="{626B8BD6-E9F5-43BA-A8F9-8EFAF6D840B9}">
       <formula1>"○, ○（オンライン処理設計書なし）"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FU65530:FX65533 PQ65530:PT65533 ZM65530:ZP65533 AJI65530:AJL65533 ATE65530:ATH65533 BDA65530:BDD65533 BMW65530:BMZ65533 BWS65530:BWV65533 CGO65530:CGR65533 CQK65530:CQN65533 DAG65530:DAJ65533 DKC65530:DKF65533 DTY65530:DUB65533 EDU65530:EDX65533 ENQ65530:ENT65533 EXM65530:EXP65533 FHI65530:FHL65533 FRE65530:FRH65533 GBA65530:GBD65533 GKW65530:GKZ65533 GUS65530:GUV65533 HEO65530:HER65533 HOK65530:HON65533 HYG65530:HYJ65533 IIC65530:IIF65533 IRY65530:ISB65533 JBU65530:JBX65533 JLQ65530:JLT65533 JVM65530:JVP65533 KFI65530:KFL65533 KPE65530:KPH65533 KZA65530:KZD65533 LIW65530:LIZ65533 LSS65530:LSV65533 MCO65530:MCR65533 MMK65530:MMN65533 MWG65530:MWJ65533 NGC65530:NGF65533 NPY65530:NQB65533 NZU65530:NZX65533 OJQ65530:OJT65533 OTM65530:OTP65533 PDI65530:PDL65533 PNE65530:PNH65533 PXA65530:PXD65533 QGW65530:QGZ65533 QQS65530:QQV65533 RAO65530:RAR65533 RKK65530:RKN65533 RUG65530:RUJ65533 SEC65530:SEF65533 SNY65530:SOB65533 SXU65530:SXX65533 THQ65530:THT65533 TRM65530:TRP65533 UBI65530:UBL65533 ULE65530:ULH65533 UVA65530:UVD65533 VEW65530:VEZ65533 VOS65530:VOV65533 VYO65530:VYR65533 WIK65530:WIN65533 WSG65530:WSJ65533 FU131066:FX131069 PQ131066:PT131069 ZM131066:ZP131069 AJI131066:AJL131069 ATE131066:ATH131069 BDA131066:BDD131069 BMW131066:BMZ131069 BWS131066:BWV131069 CGO131066:CGR131069 CQK131066:CQN131069 DAG131066:DAJ131069 DKC131066:DKF131069 DTY131066:DUB131069 EDU131066:EDX131069 ENQ131066:ENT131069 EXM131066:EXP131069 FHI131066:FHL131069 FRE131066:FRH131069 GBA131066:GBD131069 GKW131066:GKZ131069 GUS131066:GUV131069 HEO131066:HER131069 HOK131066:HON131069 HYG131066:HYJ131069 IIC131066:IIF131069 IRY131066:ISB131069 JBU131066:JBX131069 JLQ131066:JLT131069 JVM131066:JVP131069 KFI131066:KFL131069 KPE131066:KPH131069 KZA131066:KZD131069 LIW131066:LIZ131069 LSS131066:LSV131069 MCO131066:MCR131069 MMK131066:MMN131069 MWG131066:MWJ131069 NGC131066:NGF131069 NPY131066:NQB131069 NZU131066:NZX131069 OJQ131066:OJT131069 OTM131066:OTP131069 PDI131066:PDL131069 PNE131066:PNH131069 PXA131066:PXD131069 QGW131066:QGZ131069 QQS131066:QQV131069 RAO131066:RAR131069 RKK131066:RKN131069 RUG131066:RUJ131069 SEC131066:SEF131069 SNY131066:SOB131069 SXU131066:SXX131069 THQ131066:THT131069 TRM131066:TRP131069 UBI131066:UBL131069 ULE131066:ULH131069 UVA131066:UVD131069 VEW131066:VEZ131069 VOS131066:VOV131069 VYO131066:VYR131069 WIK131066:WIN131069 WSG131066:WSJ131069 FU196602:FX196605 PQ196602:PT196605 ZM196602:ZP196605 AJI196602:AJL196605 ATE196602:ATH196605 BDA196602:BDD196605 BMW196602:BMZ196605 BWS196602:BWV196605 CGO196602:CGR196605 CQK196602:CQN196605 DAG196602:DAJ196605 DKC196602:DKF196605 DTY196602:DUB196605 EDU196602:EDX196605 ENQ196602:ENT196605 EXM196602:EXP196605 FHI196602:FHL196605 FRE196602:FRH196605 GBA196602:GBD196605 GKW196602:GKZ196605 GUS196602:GUV196605 HEO196602:HER196605 HOK196602:HON196605 HYG196602:HYJ196605 IIC196602:IIF196605 IRY196602:ISB196605 JBU196602:JBX196605 JLQ196602:JLT196605 JVM196602:JVP196605 KFI196602:KFL196605 KPE196602:KPH196605 KZA196602:KZD196605 LIW196602:LIZ196605 LSS196602:LSV196605 MCO196602:MCR196605 MMK196602:MMN196605 MWG196602:MWJ196605 NGC196602:NGF196605 NPY196602:NQB196605 NZU196602:NZX196605 OJQ196602:OJT196605 OTM196602:OTP196605 PDI196602:PDL196605 PNE196602:PNH196605 PXA196602:PXD196605 QGW196602:QGZ196605 QQS196602:QQV196605 RAO196602:RAR196605 RKK196602:RKN196605 RUG196602:RUJ196605 SEC196602:SEF196605 SNY196602:SOB196605 SXU196602:SXX196605 THQ196602:THT196605 TRM196602:TRP196605 UBI196602:UBL196605 ULE196602:ULH196605 UVA196602:UVD196605 VEW196602:VEZ196605 VOS196602:VOV196605 VYO196602:VYR196605 WIK196602:WIN196605 WSG196602:WSJ196605 FU262138:FX262141 PQ262138:PT262141 ZM262138:ZP262141 AJI262138:AJL262141 ATE262138:ATH262141 BDA262138:BDD262141 BMW262138:BMZ262141 BWS262138:BWV262141 CGO262138:CGR262141 CQK262138:CQN262141 DAG262138:DAJ262141 DKC262138:DKF262141 DTY262138:DUB262141 EDU262138:EDX262141 ENQ262138:ENT262141 EXM262138:EXP262141 FHI262138:FHL262141 FRE262138:FRH262141 GBA262138:GBD262141 GKW262138:GKZ262141 GUS262138:GUV262141 HEO262138:HER262141 HOK262138:HON262141 HYG262138:HYJ262141 IIC262138:IIF262141 IRY262138:ISB262141 JBU262138:JBX262141 JLQ262138:JLT262141 JVM262138:JVP262141 KFI262138:KFL262141 KPE262138:KPH262141 KZA262138:KZD262141 LIW262138:LIZ262141 LSS262138:LSV262141 MCO262138:MCR262141 MMK262138:MMN262141 MWG262138:MWJ262141 NGC262138:NGF262141 NPY262138:NQB262141 NZU262138:NZX262141 OJQ262138:OJT262141 OTM262138:OTP262141 PDI262138:PDL262141 PNE262138:PNH262141 PXA262138:PXD262141 QGW262138:QGZ262141 QQS262138:QQV262141 RAO262138:RAR262141 RKK262138:RKN262141 RUG262138:RUJ262141 SEC262138:SEF262141 SNY262138:SOB262141 SXU262138:SXX262141 THQ262138:THT262141 TRM262138:TRP262141 UBI262138:UBL262141 ULE262138:ULH262141 UVA262138:UVD262141 VEW262138:VEZ262141 VOS262138:VOV262141 VYO262138:VYR262141 WIK262138:WIN262141 WSG262138:WSJ262141 FU327674:FX327677 PQ327674:PT327677 ZM327674:ZP327677 AJI327674:AJL327677 ATE327674:ATH327677 BDA327674:BDD327677 BMW327674:BMZ327677 BWS327674:BWV327677 CGO327674:CGR327677 CQK327674:CQN327677 DAG327674:DAJ327677 DKC327674:DKF327677 DTY327674:DUB327677 EDU327674:EDX327677 ENQ327674:ENT327677 EXM327674:EXP327677 FHI327674:FHL327677 FRE327674:FRH327677 GBA327674:GBD327677 GKW327674:GKZ327677 GUS327674:GUV327677 HEO327674:HER327677 HOK327674:HON327677 HYG327674:HYJ327677 IIC327674:IIF327677 IRY327674:ISB327677 JBU327674:JBX327677 JLQ327674:JLT327677 JVM327674:JVP327677 KFI327674:KFL327677 KPE327674:KPH327677 KZA327674:KZD327677 LIW327674:LIZ327677 LSS327674:LSV327677 MCO327674:MCR327677 MMK327674:MMN327677 MWG327674:MWJ327677 NGC327674:NGF327677 NPY327674:NQB327677 NZU327674:NZX327677 OJQ327674:OJT327677 OTM327674:OTP327677 PDI327674:PDL327677 PNE327674:PNH327677 PXA327674:PXD327677 QGW327674:QGZ327677 QQS327674:QQV327677 RAO327674:RAR327677 RKK327674:RKN327677 RUG327674:RUJ327677 SEC327674:SEF327677 SNY327674:SOB327677 SXU327674:SXX327677 THQ327674:THT327677 TRM327674:TRP327677 UBI327674:UBL327677 ULE327674:ULH327677 UVA327674:UVD327677 VEW327674:VEZ327677 VOS327674:VOV327677 VYO327674:VYR327677 WIK327674:WIN327677 WSG327674:WSJ327677 FU393210:FX393213 PQ393210:PT393213 ZM393210:ZP393213 AJI393210:AJL393213 ATE393210:ATH393213 BDA393210:BDD393213 BMW393210:BMZ393213 BWS393210:BWV393213 CGO393210:CGR393213 CQK393210:CQN393213 DAG393210:DAJ393213 DKC393210:DKF393213 DTY393210:DUB393213 EDU393210:EDX393213 ENQ393210:ENT393213 EXM393210:EXP393213 FHI393210:FHL393213 FRE393210:FRH393213 GBA393210:GBD393213 GKW393210:GKZ393213 GUS393210:GUV393213 HEO393210:HER393213 HOK393210:HON393213 HYG393210:HYJ393213 IIC393210:IIF393213 IRY393210:ISB393213 JBU393210:JBX393213 JLQ393210:JLT393213 JVM393210:JVP393213 KFI393210:KFL393213 KPE393210:KPH393213 KZA393210:KZD393213 LIW393210:LIZ393213 LSS393210:LSV393213 MCO393210:MCR393213 MMK393210:MMN393213 MWG393210:MWJ393213 NGC393210:NGF393213 NPY393210:NQB393213 NZU393210:NZX393213 OJQ393210:OJT393213 OTM393210:OTP393213 PDI393210:PDL393213 PNE393210:PNH393213 PXA393210:PXD393213 QGW393210:QGZ393213 QQS393210:QQV393213 RAO393210:RAR393213 RKK393210:RKN393213 RUG393210:RUJ393213 SEC393210:SEF393213 SNY393210:SOB393213 SXU393210:SXX393213 THQ393210:THT393213 TRM393210:TRP393213 UBI393210:UBL393213 ULE393210:ULH393213 UVA393210:UVD393213 VEW393210:VEZ393213 VOS393210:VOV393213 VYO393210:VYR393213 WIK393210:WIN393213 WSG393210:WSJ393213 FU458746:FX458749 PQ458746:PT458749 ZM458746:ZP458749 AJI458746:AJL458749 ATE458746:ATH458749 BDA458746:BDD458749 BMW458746:BMZ458749 BWS458746:BWV458749 CGO458746:CGR458749 CQK458746:CQN458749 DAG458746:DAJ458749 DKC458746:DKF458749 DTY458746:DUB458749 EDU458746:EDX458749 ENQ458746:ENT458749 EXM458746:EXP458749 FHI458746:FHL458749 FRE458746:FRH458749 GBA458746:GBD458749 GKW458746:GKZ458749 GUS458746:GUV458749 HEO458746:HER458749 HOK458746:HON458749 HYG458746:HYJ458749 IIC458746:IIF458749 IRY458746:ISB458749 JBU458746:JBX458749 JLQ458746:JLT458749 JVM458746:JVP458749 KFI458746:KFL458749 KPE458746:KPH458749 KZA458746:KZD458749 LIW458746:LIZ458749 LSS458746:LSV458749 MCO458746:MCR458749 MMK458746:MMN458749 MWG458746:MWJ458749 NGC458746:NGF458749 NPY458746:NQB458749 NZU458746:NZX458749 OJQ458746:OJT458749 OTM458746:OTP458749 PDI458746:PDL458749 PNE458746:PNH458749 PXA458746:PXD458749 QGW458746:QGZ458749 QQS458746:QQV458749 RAO458746:RAR458749 RKK458746:RKN458749 RUG458746:RUJ458749 SEC458746:SEF458749 SNY458746:SOB458749 SXU458746:SXX458749 THQ458746:THT458749 TRM458746:TRP458749 UBI458746:UBL458749 ULE458746:ULH458749 UVA458746:UVD458749 VEW458746:VEZ458749 VOS458746:VOV458749 VYO458746:VYR458749 WIK458746:WIN458749 WSG458746:WSJ458749 FU524282:FX524285 PQ524282:PT524285 ZM524282:ZP524285 AJI524282:AJL524285 ATE524282:ATH524285 BDA524282:BDD524285 BMW524282:BMZ524285 BWS524282:BWV524285 CGO524282:CGR524285 CQK524282:CQN524285 DAG524282:DAJ524285 DKC524282:DKF524285 DTY524282:DUB524285 EDU524282:EDX524285 ENQ524282:ENT524285 EXM524282:EXP524285 FHI524282:FHL524285 FRE524282:FRH524285 GBA524282:GBD524285 GKW524282:GKZ524285 GUS524282:GUV524285 HEO524282:HER524285 HOK524282:HON524285 HYG524282:HYJ524285 IIC524282:IIF524285 IRY524282:ISB524285 JBU524282:JBX524285 JLQ524282:JLT524285 JVM524282:JVP524285 KFI524282:KFL524285 KPE524282:KPH524285 KZA524282:KZD524285 LIW524282:LIZ524285 LSS524282:LSV524285 MCO524282:MCR524285 MMK524282:MMN524285 MWG524282:MWJ524285 NGC524282:NGF524285 NPY524282:NQB524285 NZU524282:NZX524285 OJQ524282:OJT524285 OTM524282:OTP524285 PDI524282:PDL524285 PNE524282:PNH524285 PXA524282:PXD524285 QGW524282:QGZ524285 QQS524282:QQV524285 RAO524282:RAR524285 RKK524282:RKN524285 RUG524282:RUJ524285 SEC524282:SEF524285 SNY524282:SOB524285 SXU524282:SXX524285 THQ524282:THT524285 TRM524282:TRP524285 UBI524282:UBL524285 ULE524282:ULH524285 UVA524282:UVD524285 VEW524282:VEZ524285 VOS524282:VOV524285 VYO524282:VYR524285 WIK524282:WIN524285 WSG524282:WSJ524285 FU589818:FX589821 PQ589818:PT589821 ZM589818:ZP589821 AJI589818:AJL589821 ATE589818:ATH589821 BDA589818:BDD589821 BMW589818:BMZ589821 BWS589818:BWV589821 CGO589818:CGR589821 CQK589818:CQN589821 DAG589818:DAJ589821 DKC589818:DKF589821 DTY589818:DUB589821 EDU589818:EDX589821 ENQ589818:ENT589821 EXM589818:EXP589821 FHI589818:FHL589821 FRE589818:FRH589821 GBA589818:GBD589821 GKW589818:GKZ589821 GUS589818:GUV589821 HEO589818:HER589821 HOK589818:HON589821 HYG589818:HYJ589821 IIC589818:IIF589821 IRY589818:ISB589821 JBU589818:JBX589821 JLQ589818:JLT589821 JVM589818:JVP589821 KFI589818:KFL589821 KPE589818:KPH589821 KZA589818:KZD589821 LIW589818:LIZ589821 LSS589818:LSV589821 MCO589818:MCR589821 MMK589818:MMN589821 MWG589818:MWJ589821 NGC589818:NGF589821 NPY589818:NQB589821 NZU589818:NZX589821 OJQ589818:OJT589821 OTM589818:OTP589821 PDI589818:PDL589821 PNE589818:PNH589821 PXA589818:PXD589821 QGW589818:QGZ589821 QQS589818:QQV589821 RAO589818:RAR589821 RKK589818:RKN589821 RUG589818:RUJ589821 SEC589818:SEF589821 SNY589818:SOB589821 SXU589818:SXX589821 THQ589818:THT589821 TRM589818:TRP589821 UBI589818:UBL589821 ULE589818:ULH589821 UVA589818:UVD589821 VEW589818:VEZ589821 VOS589818:VOV589821 VYO589818:VYR589821 WIK589818:WIN589821 WSG589818:WSJ589821 FU655354:FX655357 PQ655354:PT655357 ZM655354:ZP655357 AJI655354:AJL655357 ATE655354:ATH655357 BDA655354:BDD655357 BMW655354:BMZ655357 BWS655354:BWV655357 CGO655354:CGR655357 CQK655354:CQN655357 DAG655354:DAJ655357 DKC655354:DKF655357 DTY655354:DUB655357 EDU655354:EDX655357 ENQ655354:ENT655357 EXM655354:EXP655357 FHI655354:FHL655357 FRE655354:FRH655357 GBA655354:GBD655357 GKW655354:GKZ655357 GUS655354:GUV655357 HEO655354:HER655357 HOK655354:HON655357 HYG655354:HYJ655357 IIC655354:IIF655357 IRY655354:ISB655357 JBU655354:JBX655357 JLQ655354:JLT655357 JVM655354:JVP655357 KFI655354:KFL655357 KPE655354:KPH655357 KZA655354:KZD655357 LIW655354:LIZ655357 LSS655354:LSV655357 MCO655354:MCR655357 MMK655354:MMN655357 MWG655354:MWJ655357 NGC655354:NGF655357 NPY655354:NQB655357 NZU655354:NZX655357 OJQ655354:OJT655357 OTM655354:OTP655357 PDI655354:PDL655357 PNE655354:PNH655357 PXA655354:PXD655357 QGW655354:QGZ655357 QQS655354:QQV655357 RAO655354:RAR655357 RKK655354:RKN655357 RUG655354:RUJ655357 SEC655354:SEF655357 SNY655354:SOB655357 SXU655354:SXX655357 THQ655354:THT655357 TRM655354:TRP655357 UBI655354:UBL655357 ULE655354:ULH655357 UVA655354:UVD655357 VEW655354:VEZ655357 VOS655354:VOV655357 VYO655354:VYR655357 WIK655354:WIN655357 WSG655354:WSJ655357 FU720890:FX720893 PQ720890:PT720893 ZM720890:ZP720893 AJI720890:AJL720893 ATE720890:ATH720893 BDA720890:BDD720893 BMW720890:BMZ720893 BWS720890:BWV720893 CGO720890:CGR720893 CQK720890:CQN720893 DAG720890:DAJ720893 DKC720890:DKF720893 DTY720890:DUB720893 EDU720890:EDX720893 ENQ720890:ENT720893 EXM720890:EXP720893 FHI720890:FHL720893 FRE720890:FRH720893 GBA720890:GBD720893 GKW720890:GKZ720893 GUS720890:GUV720893 HEO720890:HER720893 HOK720890:HON720893 HYG720890:HYJ720893 IIC720890:IIF720893 IRY720890:ISB720893 JBU720890:JBX720893 JLQ720890:JLT720893 JVM720890:JVP720893 KFI720890:KFL720893 KPE720890:KPH720893 KZA720890:KZD720893 LIW720890:LIZ720893 LSS720890:LSV720893 MCO720890:MCR720893 MMK720890:MMN720893 MWG720890:MWJ720893 NGC720890:NGF720893 NPY720890:NQB720893 NZU720890:NZX720893 OJQ720890:OJT720893 OTM720890:OTP720893 PDI720890:PDL720893 PNE720890:PNH720893 PXA720890:PXD720893 QGW720890:QGZ720893 QQS720890:QQV720893 RAO720890:RAR720893 RKK720890:RKN720893 RUG720890:RUJ720893 SEC720890:SEF720893 SNY720890:SOB720893 SXU720890:SXX720893 THQ720890:THT720893 TRM720890:TRP720893 UBI720890:UBL720893 ULE720890:ULH720893 UVA720890:UVD720893 VEW720890:VEZ720893 VOS720890:VOV720893 VYO720890:VYR720893 WIK720890:WIN720893 WSG720890:WSJ720893 FU786426:FX786429 PQ786426:PT786429 ZM786426:ZP786429 AJI786426:AJL786429 ATE786426:ATH786429 BDA786426:BDD786429 BMW786426:BMZ786429 BWS786426:BWV786429 CGO786426:CGR786429 CQK786426:CQN786429 DAG786426:DAJ786429 DKC786426:DKF786429 DTY786426:DUB786429 EDU786426:EDX786429 ENQ786426:ENT786429 EXM786426:EXP786429 FHI786426:FHL786429 FRE786426:FRH786429 GBA786426:GBD786429 GKW786426:GKZ786429 GUS786426:GUV786429 HEO786426:HER786429 HOK786426:HON786429 HYG786426:HYJ786429 IIC786426:IIF786429 IRY786426:ISB786429 JBU786426:JBX786429 JLQ786426:JLT786429 JVM786426:JVP786429 KFI786426:KFL786429 KPE786426:KPH786429 KZA786426:KZD786429 LIW786426:LIZ786429 LSS786426:LSV786429 MCO786426:MCR786429 MMK786426:MMN786429 MWG786426:MWJ786429 NGC786426:NGF786429 NPY786426:NQB786429 NZU786426:NZX786429 OJQ786426:OJT786429 OTM786426:OTP786429 PDI786426:PDL786429 PNE786426:PNH786429 PXA786426:PXD786429 QGW786426:QGZ786429 QQS786426:QQV786429 RAO786426:RAR786429 RKK786426:RKN786429 RUG786426:RUJ786429 SEC786426:SEF786429 SNY786426:SOB786429 SXU786426:SXX786429 THQ786426:THT786429 TRM786426:TRP786429 UBI786426:UBL786429 ULE786426:ULH786429 UVA786426:UVD786429 VEW786426:VEZ786429 VOS786426:VOV786429 VYO786426:VYR786429 WIK786426:WIN786429 WSG786426:WSJ786429 FU851962:FX851965 PQ851962:PT851965 ZM851962:ZP851965 AJI851962:AJL851965 ATE851962:ATH851965 BDA851962:BDD851965 BMW851962:BMZ851965 BWS851962:BWV851965 CGO851962:CGR851965 CQK851962:CQN851965 DAG851962:DAJ851965 DKC851962:DKF851965 DTY851962:DUB851965 EDU851962:EDX851965 ENQ851962:ENT851965 EXM851962:EXP851965 FHI851962:FHL851965 FRE851962:FRH851965 GBA851962:GBD851965 GKW851962:GKZ851965 GUS851962:GUV851965 HEO851962:HER851965 HOK851962:HON851965 HYG851962:HYJ851965 IIC851962:IIF851965 IRY851962:ISB851965 JBU851962:JBX851965 JLQ851962:JLT851965 JVM851962:JVP851965 KFI851962:KFL851965 KPE851962:KPH851965 KZA851962:KZD851965 LIW851962:LIZ851965 LSS851962:LSV851965 MCO851962:MCR851965 MMK851962:MMN851965 MWG851962:MWJ851965 NGC851962:NGF851965 NPY851962:NQB851965 NZU851962:NZX851965 OJQ851962:OJT851965 OTM851962:OTP851965 PDI851962:PDL851965 PNE851962:PNH851965 PXA851962:PXD851965 QGW851962:QGZ851965 QQS851962:QQV851965 RAO851962:RAR851965 RKK851962:RKN851965 RUG851962:RUJ851965 SEC851962:SEF851965 SNY851962:SOB851965 SXU851962:SXX851965 THQ851962:THT851965 TRM851962:TRP851965 UBI851962:UBL851965 ULE851962:ULH851965 UVA851962:UVD851965 VEW851962:VEZ851965 VOS851962:VOV851965 VYO851962:VYR851965 WIK851962:WIN851965 WSG851962:WSJ851965 FU917498:FX917501 PQ917498:PT917501 ZM917498:ZP917501 AJI917498:AJL917501 ATE917498:ATH917501 BDA917498:BDD917501 BMW917498:BMZ917501 BWS917498:BWV917501 CGO917498:CGR917501 CQK917498:CQN917501 DAG917498:DAJ917501 DKC917498:DKF917501 DTY917498:DUB917501 EDU917498:EDX917501 ENQ917498:ENT917501 EXM917498:EXP917501 FHI917498:FHL917501 FRE917498:FRH917501 GBA917498:GBD917501 GKW917498:GKZ917501 GUS917498:GUV917501 HEO917498:HER917501 HOK917498:HON917501 HYG917498:HYJ917501 IIC917498:IIF917501 IRY917498:ISB917501 JBU917498:JBX917501 JLQ917498:JLT917501 JVM917498:JVP917501 KFI917498:KFL917501 KPE917498:KPH917501 KZA917498:KZD917501 LIW917498:LIZ917501 LSS917498:LSV917501 MCO917498:MCR917501 MMK917498:MMN917501 MWG917498:MWJ917501 NGC917498:NGF917501 NPY917498:NQB917501 NZU917498:NZX917501 OJQ917498:OJT917501 OTM917498:OTP917501 PDI917498:PDL917501 PNE917498:PNH917501 PXA917498:PXD917501 QGW917498:QGZ917501 QQS917498:QQV917501 RAO917498:RAR917501 RKK917498:RKN917501 RUG917498:RUJ917501 SEC917498:SEF917501 SNY917498:SOB917501 SXU917498:SXX917501 THQ917498:THT917501 TRM917498:TRP917501 UBI917498:UBL917501 ULE917498:ULH917501 UVA917498:UVD917501 VEW917498:VEZ917501 VOS917498:VOV917501 VYO917498:VYR917501 WIK917498:WIN917501 WSG917498:WSJ917501 FU983034:FX983037 PQ983034:PT983037 ZM983034:ZP983037 AJI983034:AJL983037 ATE983034:ATH983037 BDA983034:BDD983037 BMW983034:BMZ983037 BWS983034:BWV983037 CGO983034:CGR983037 CQK983034:CQN983037 DAG983034:DAJ983037 DKC983034:DKF983037 DTY983034:DUB983037 EDU983034:EDX983037 ENQ983034:ENT983037 EXM983034:EXP983037 FHI983034:FHL983037 FRE983034:FRH983037 GBA983034:GBD983037 GKW983034:GKZ983037 GUS983034:GUV983037 HEO983034:HER983037 HOK983034:HON983037 HYG983034:HYJ983037 IIC983034:IIF983037 IRY983034:ISB983037 JBU983034:JBX983037 JLQ983034:JLT983037 JVM983034:JVP983037 KFI983034:KFL983037 KPE983034:KPH983037 KZA983034:KZD983037 LIW983034:LIZ983037 LSS983034:LSV983037 MCO983034:MCR983037 MMK983034:MMN983037 MWG983034:MWJ983037 NGC983034:NGF983037 NPY983034:NQB983037 NZU983034:NZX983037 OJQ983034:OJT983037 OTM983034:OTP983037 PDI983034:PDL983037 PNE983034:PNH983037 PXA983034:PXD983037 QGW983034:QGZ983037 QQS983034:QQV983037 RAO983034:RAR983037 RKK983034:RKN983037 RUG983034:RUJ983037 SEC983034:SEF983037 SNY983034:SOB983037 SXU983034:SXX983037 THQ983034:THT983037 TRM983034:TRP983037 UBI983034:UBL983037 ULE983034:ULH983037 UVA983034:UVD983037 VEW983034:VEZ983037 VOS983034:VOV983037 VYO983034:VYR983037 WIK983034:WIN983037 WSG983034:WSJ983037 FP65524:FS65524 PL65524:PO65524 ZH65524:ZK65524 AJD65524:AJG65524 ASZ65524:ATC65524 BCV65524:BCY65524 BMR65524:BMU65524 BWN65524:BWQ65524 CGJ65524:CGM65524 CQF65524:CQI65524 DAB65524:DAE65524 DJX65524:DKA65524 DTT65524:DTW65524 EDP65524:EDS65524 ENL65524:ENO65524 EXH65524:EXK65524 FHD65524:FHG65524 FQZ65524:FRC65524 GAV65524:GAY65524 GKR65524:GKU65524 GUN65524:GUQ65524 HEJ65524:HEM65524 HOF65524:HOI65524 HYB65524:HYE65524 IHX65524:IIA65524 IRT65524:IRW65524 JBP65524:JBS65524 JLL65524:JLO65524 JVH65524:JVK65524 KFD65524:KFG65524 KOZ65524:KPC65524 KYV65524:KYY65524 LIR65524:LIU65524 LSN65524:LSQ65524 MCJ65524:MCM65524 MMF65524:MMI65524 MWB65524:MWE65524 NFX65524:NGA65524 NPT65524:NPW65524 NZP65524:NZS65524 OJL65524:OJO65524 OTH65524:OTK65524 PDD65524:PDG65524 PMZ65524:PNC65524 PWV65524:PWY65524 QGR65524:QGU65524 QQN65524:QQQ65524 RAJ65524:RAM65524 RKF65524:RKI65524 RUB65524:RUE65524 SDX65524:SEA65524 SNT65524:SNW65524 SXP65524:SXS65524 THL65524:THO65524 TRH65524:TRK65524 UBD65524:UBG65524 UKZ65524:ULC65524 UUV65524:UUY65524 VER65524:VEU65524 VON65524:VOQ65524 VYJ65524:VYM65524 WIF65524:WII65524 WSB65524:WSE65524 FP131060:FS131060 PL131060:PO131060 ZH131060:ZK131060 AJD131060:AJG131060 ASZ131060:ATC131060 BCV131060:BCY131060 BMR131060:BMU131060 BWN131060:BWQ131060 CGJ131060:CGM131060 CQF131060:CQI131060 DAB131060:DAE131060 DJX131060:DKA131060 DTT131060:DTW131060 EDP131060:EDS131060 ENL131060:ENO131060 EXH131060:EXK131060 FHD131060:FHG131060 FQZ131060:FRC131060 GAV131060:GAY131060 GKR131060:GKU131060 GUN131060:GUQ131060 HEJ131060:HEM131060 HOF131060:HOI131060 HYB131060:HYE131060 IHX131060:IIA131060 IRT131060:IRW131060 JBP131060:JBS131060 JLL131060:JLO131060 JVH131060:JVK131060 KFD131060:KFG131060 KOZ131060:KPC131060 KYV131060:KYY131060 LIR131060:LIU131060 LSN131060:LSQ131060 MCJ131060:MCM131060 MMF131060:MMI131060 MWB131060:MWE131060 NFX131060:NGA131060 NPT131060:NPW131060 NZP131060:NZS131060 OJL131060:OJO131060 OTH131060:OTK131060 PDD131060:PDG131060 PMZ131060:PNC131060 PWV131060:PWY131060 QGR131060:QGU131060 QQN131060:QQQ131060 RAJ131060:RAM131060 RKF131060:RKI131060 RUB131060:RUE131060 SDX131060:SEA131060 SNT131060:SNW131060 SXP131060:SXS131060 THL131060:THO131060 TRH131060:TRK131060 UBD131060:UBG131060 UKZ131060:ULC131060 UUV131060:UUY131060 VER131060:VEU131060 VON131060:VOQ131060 VYJ131060:VYM131060 WIF131060:WII131060 WSB131060:WSE131060 FP196596:FS196596 PL196596:PO196596 ZH196596:ZK196596 AJD196596:AJG196596 ASZ196596:ATC196596 BCV196596:BCY196596 BMR196596:BMU196596 BWN196596:BWQ196596 CGJ196596:CGM196596 CQF196596:CQI196596 DAB196596:DAE196596 DJX196596:DKA196596 DTT196596:DTW196596 EDP196596:EDS196596 ENL196596:ENO196596 EXH196596:EXK196596 FHD196596:FHG196596 FQZ196596:FRC196596 GAV196596:GAY196596 GKR196596:GKU196596 GUN196596:GUQ196596 HEJ196596:HEM196596 HOF196596:HOI196596 HYB196596:HYE196596 IHX196596:IIA196596 IRT196596:IRW196596 JBP196596:JBS196596 JLL196596:JLO196596 JVH196596:JVK196596 KFD196596:KFG196596 KOZ196596:KPC196596 KYV196596:KYY196596 LIR196596:LIU196596 LSN196596:LSQ196596 MCJ196596:MCM196596 MMF196596:MMI196596 MWB196596:MWE196596 NFX196596:NGA196596 NPT196596:NPW196596 NZP196596:NZS196596 OJL196596:OJO196596 OTH196596:OTK196596 PDD196596:PDG196596 PMZ196596:PNC196596 PWV196596:PWY196596 QGR196596:QGU196596 QQN196596:QQQ196596 RAJ196596:RAM196596 RKF196596:RKI196596 RUB196596:RUE196596 SDX196596:SEA196596 SNT196596:SNW196596 SXP196596:SXS196596 THL196596:THO196596 TRH196596:TRK196596 UBD196596:UBG196596 UKZ196596:ULC196596 UUV196596:UUY196596 VER196596:VEU196596 VON196596:VOQ196596 VYJ196596:VYM196596 WIF196596:WII196596 WSB196596:WSE196596 FP262132:FS262132 PL262132:PO262132 ZH262132:ZK262132 AJD262132:AJG262132 ASZ262132:ATC262132 BCV262132:BCY262132 BMR262132:BMU262132 BWN262132:BWQ262132 CGJ262132:CGM262132 CQF262132:CQI262132 DAB262132:DAE262132 DJX262132:DKA262132 DTT262132:DTW262132 EDP262132:EDS262132 ENL262132:ENO262132 EXH262132:EXK262132 FHD262132:FHG262132 FQZ262132:FRC262132 GAV262132:GAY262132 GKR262132:GKU262132 GUN262132:GUQ262132 HEJ262132:HEM262132 HOF262132:HOI262132 HYB262132:HYE262132 IHX262132:IIA262132 IRT262132:IRW262132 JBP262132:JBS262132 JLL262132:JLO262132 JVH262132:JVK262132 KFD262132:KFG262132 KOZ262132:KPC262132 KYV262132:KYY262132 LIR262132:LIU262132 LSN262132:LSQ262132 MCJ262132:MCM262132 MMF262132:MMI262132 MWB262132:MWE262132 NFX262132:NGA262132 NPT262132:NPW262132 NZP262132:NZS262132 OJL262132:OJO262132 OTH262132:OTK262132 PDD262132:PDG262132 PMZ262132:PNC262132 PWV262132:PWY262132 QGR262132:QGU262132 QQN262132:QQQ262132 RAJ262132:RAM262132 RKF262132:RKI262132 RUB262132:RUE262132 SDX262132:SEA262132 SNT262132:SNW262132 SXP262132:SXS262132 THL262132:THO262132 TRH262132:TRK262132 UBD262132:UBG262132 UKZ262132:ULC262132 UUV262132:UUY262132 VER262132:VEU262132 VON262132:VOQ262132 VYJ262132:VYM262132 WIF262132:WII262132 WSB262132:WSE262132 FP327668:FS327668 PL327668:PO327668 ZH327668:ZK327668 AJD327668:AJG327668 ASZ327668:ATC327668 BCV327668:BCY327668 BMR327668:BMU327668 BWN327668:BWQ327668 CGJ327668:CGM327668 CQF327668:CQI327668 DAB327668:DAE327668 DJX327668:DKA327668 DTT327668:DTW327668 EDP327668:EDS327668 ENL327668:ENO327668 EXH327668:EXK327668 FHD327668:FHG327668 FQZ327668:FRC327668 GAV327668:GAY327668 GKR327668:GKU327668 GUN327668:GUQ327668 HEJ327668:HEM327668 HOF327668:HOI327668 HYB327668:HYE327668 IHX327668:IIA327668 IRT327668:IRW327668 JBP327668:JBS327668 JLL327668:JLO327668 JVH327668:JVK327668 KFD327668:KFG327668 KOZ327668:KPC327668 KYV327668:KYY327668 LIR327668:LIU327668 LSN327668:LSQ327668 MCJ327668:MCM327668 MMF327668:MMI327668 MWB327668:MWE327668 NFX327668:NGA327668 NPT327668:NPW327668 NZP327668:NZS327668 OJL327668:OJO327668 OTH327668:OTK327668 PDD327668:PDG327668 PMZ327668:PNC327668 PWV327668:PWY327668 QGR327668:QGU327668 QQN327668:QQQ327668 RAJ327668:RAM327668 RKF327668:RKI327668 RUB327668:RUE327668 SDX327668:SEA327668 SNT327668:SNW327668 SXP327668:SXS327668 THL327668:THO327668 TRH327668:TRK327668 UBD327668:UBG327668 UKZ327668:ULC327668 UUV327668:UUY327668 VER327668:VEU327668 VON327668:VOQ327668 VYJ327668:VYM327668 WIF327668:WII327668 WSB327668:WSE327668 FP393204:FS393204 PL393204:PO393204 ZH393204:ZK393204 AJD393204:AJG393204 ASZ393204:ATC393204 BCV393204:BCY393204 BMR393204:BMU393204 BWN393204:BWQ393204 CGJ393204:CGM393204 CQF393204:CQI393204 DAB393204:DAE393204 DJX393204:DKA393204 DTT393204:DTW393204 EDP393204:EDS393204 ENL393204:ENO393204 EXH393204:EXK393204 FHD393204:FHG393204 FQZ393204:FRC393204 GAV393204:GAY393204 GKR393204:GKU393204 GUN393204:GUQ393204 HEJ393204:HEM393204 HOF393204:HOI393204 HYB393204:HYE393204 IHX393204:IIA393204 IRT393204:IRW393204 JBP393204:JBS393204 JLL393204:JLO393204 JVH393204:JVK393204 KFD393204:KFG393204 KOZ393204:KPC393204 KYV393204:KYY393204 LIR393204:LIU393204 LSN393204:LSQ393204 MCJ393204:MCM393204 MMF393204:MMI393204 MWB393204:MWE393204 NFX393204:NGA393204 NPT393204:NPW393204 NZP393204:NZS393204 OJL393204:OJO393204 OTH393204:OTK393204 PDD393204:PDG393204 PMZ393204:PNC393204 PWV393204:PWY393204 QGR393204:QGU393204 QQN393204:QQQ393204 RAJ393204:RAM393204 RKF393204:RKI393204 RUB393204:RUE393204 SDX393204:SEA393204 SNT393204:SNW393204 SXP393204:SXS393204 THL393204:THO393204 TRH393204:TRK393204 UBD393204:UBG393204 UKZ393204:ULC393204 UUV393204:UUY393204 VER393204:VEU393204 VON393204:VOQ393204 VYJ393204:VYM393204 WIF393204:WII393204 WSB393204:WSE393204 FP458740:FS458740 PL458740:PO458740 ZH458740:ZK458740 AJD458740:AJG458740 ASZ458740:ATC458740 BCV458740:BCY458740 BMR458740:BMU458740 BWN458740:BWQ458740 CGJ458740:CGM458740 CQF458740:CQI458740 DAB458740:DAE458740 DJX458740:DKA458740 DTT458740:DTW458740 EDP458740:EDS458740 ENL458740:ENO458740 EXH458740:EXK458740 FHD458740:FHG458740 FQZ458740:FRC458740 GAV458740:GAY458740 GKR458740:GKU458740 GUN458740:GUQ458740 HEJ458740:HEM458740 HOF458740:HOI458740 HYB458740:HYE458740 IHX458740:IIA458740 IRT458740:IRW458740 JBP458740:JBS458740 JLL458740:JLO458740 JVH458740:JVK458740 KFD458740:KFG458740 KOZ458740:KPC458740 KYV458740:KYY458740 LIR458740:LIU458740 LSN458740:LSQ458740 MCJ458740:MCM458740 MMF458740:MMI458740 MWB458740:MWE458740 NFX458740:NGA458740 NPT458740:NPW458740 NZP458740:NZS458740 OJL458740:OJO458740 OTH458740:OTK458740 PDD458740:PDG458740 PMZ458740:PNC458740 PWV458740:PWY458740 QGR458740:QGU458740 QQN458740:QQQ458740 RAJ458740:RAM458740 RKF458740:RKI458740 RUB458740:RUE458740 SDX458740:SEA458740 SNT458740:SNW458740 SXP458740:SXS458740 THL458740:THO458740 TRH458740:TRK458740 UBD458740:UBG458740 UKZ458740:ULC458740 UUV458740:UUY458740 VER458740:VEU458740 VON458740:VOQ458740 VYJ458740:VYM458740 WIF458740:WII458740 WSB458740:WSE458740 FP524276:FS524276 PL524276:PO524276 ZH524276:ZK524276 AJD524276:AJG524276 ASZ524276:ATC524276 BCV524276:BCY524276 BMR524276:BMU524276 BWN524276:BWQ524276 CGJ524276:CGM524276 CQF524276:CQI524276 DAB524276:DAE524276 DJX524276:DKA524276 DTT524276:DTW524276 EDP524276:EDS524276 ENL524276:ENO524276 EXH524276:EXK524276 FHD524276:FHG524276 FQZ524276:FRC524276 GAV524276:GAY524276 GKR524276:GKU524276 GUN524276:GUQ524276 HEJ524276:HEM524276 HOF524276:HOI524276 HYB524276:HYE524276 IHX524276:IIA524276 IRT524276:IRW524276 JBP524276:JBS524276 JLL524276:JLO524276 JVH524276:JVK524276 KFD524276:KFG524276 KOZ524276:KPC524276 KYV524276:KYY524276 LIR524276:LIU524276 LSN524276:LSQ524276 MCJ524276:MCM524276 MMF524276:MMI524276 MWB524276:MWE524276 NFX524276:NGA524276 NPT524276:NPW524276 NZP524276:NZS524276 OJL524276:OJO524276 OTH524276:OTK524276 PDD524276:PDG524276 PMZ524276:PNC524276 PWV524276:PWY524276 QGR524276:QGU524276 QQN524276:QQQ524276 RAJ524276:RAM524276 RKF524276:RKI524276 RUB524276:RUE524276 SDX524276:SEA524276 SNT524276:SNW524276 SXP524276:SXS524276 THL524276:THO524276 TRH524276:TRK524276 UBD524276:UBG524276 UKZ524276:ULC524276 UUV524276:UUY524276 VER524276:VEU524276 VON524276:VOQ524276 VYJ524276:VYM524276 WIF524276:WII524276 WSB524276:WSE524276 FP589812:FS589812 PL589812:PO589812 ZH589812:ZK589812 AJD589812:AJG589812 ASZ589812:ATC589812 BCV589812:BCY589812 BMR589812:BMU589812 BWN589812:BWQ589812 CGJ589812:CGM589812 CQF589812:CQI589812 DAB589812:DAE589812 DJX589812:DKA589812 DTT589812:DTW589812 EDP589812:EDS589812 ENL589812:ENO589812 EXH589812:EXK589812 FHD589812:FHG589812 FQZ589812:FRC589812 GAV589812:GAY589812 GKR589812:GKU589812 GUN589812:GUQ589812 HEJ589812:HEM589812 HOF589812:HOI589812 HYB589812:HYE589812 IHX589812:IIA589812 IRT589812:IRW589812 JBP589812:JBS589812 JLL589812:JLO589812 JVH589812:JVK589812 KFD589812:KFG589812 KOZ589812:KPC589812 KYV589812:KYY589812 LIR589812:LIU589812 LSN589812:LSQ589812 MCJ589812:MCM589812 MMF589812:MMI589812 MWB589812:MWE589812 NFX589812:NGA589812 NPT589812:NPW589812 NZP589812:NZS589812 OJL589812:OJO589812 OTH589812:OTK589812 PDD589812:PDG589812 PMZ589812:PNC589812 PWV589812:PWY589812 QGR589812:QGU589812 QQN589812:QQQ589812 RAJ589812:RAM589812 RKF589812:RKI589812 RUB589812:RUE589812 SDX589812:SEA589812 SNT589812:SNW589812 SXP589812:SXS589812 THL589812:THO589812 TRH589812:TRK589812 UBD589812:UBG589812 UKZ589812:ULC589812 UUV589812:UUY589812 VER589812:VEU589812 VON589812:VOQ589812 VYJ589812:VYM589812 WIF589812:WII589812 WSB589812:WSE589812 FP655348:FS655348 PL655348:PO655348 ZH655348:ZK655348 AJD655348:AJG655348 ASZ655348:ATC655348 BCV655348:BCY655348 BMR655348:BMU655348 BWN655348:BWQ655348 CGJ655348:CGM655348 CQF655348:CQI655348 DAB655348:DAE655348 DJX655348:DKA655348 DTT655348:DTW655348 EDP655348:EDS655348 ENL655348:ENO655348 EXH655348:EXK655348 FHD655348:FHG655348 FQZ655348:FRC655348 GAV655348:GAY655348 GKR655348:GKU655348 GUN655348:GUQ655348 HEJ655348:HEM655348 HOF655348:HOI655348 HYB655348:HYE655348 IHX655348:IIA655348 IRT655348:IRW655348 JBP655348:JBS655348 JLL655348:JLO655348 JVH655348:JVK655348 KFD655348:KFG655348 KOZ655348:KPC655348 KYV655348:KYY655348 LIR655348:LIU655348 LSN655348:LSQ655348 MCJ655348:MCM655348 MMF655348:MMI655348 MWB655348:MWE655348 NFX655348:NGA655348 NPT655348:NPW655348 NZP655348:NZS655348 OJL655348:OJO655348 OTH655348:OTK655348 PDD655348:PDG655348 PMZ655348:PNC655348 PWV655348:PWY655348 QGR655348:QGU655348 QQN655348:QQQ655348 RAJ655348:RAM655348 RKF655348:RKI655348 RUB655348:RUE655348 SDX655348:SEA655348 SNT655348:SNW655348 SXP655348:SXS655348 THL655348:THO655348 TRH655348:TRK655348 UBD655348:UBG655348 UKZ655348:ULC655348 UUV655348:UUY655348 VER655348:VEU655348 VON655348:VOQ655348 VYJ655348:VYM655348 WIF655348:WII655348 WSB655348:WSE655348 FP720884:FS720884 PL720884:PO720884 ZH720884:ZK720884 AJD720884:AJG720884 ASZ720884:ATC720884 BCV720884:BCY720884 BMR720884:BMU720884 BWN720884:BWQ720884 CGJ720884:CGM720884 CQF720884:CQI720884 DAB720884:DAE720884 DJX720884:DKA720884 DTT720884:DTW720884 EDP720884:EDS720884 ENL720884:ENO720884 EXH720884:EXK720884 FHD720884:FHG720884 FQZ720884:FRC720884 GAV720884:GAY720884 GKR720884:GKU720884 GUN720884:GUQ720884 HEJ720884:HEM720884 HOF720884:HOI720884 HYB720884:HYE720884 IHX720884:IIA720884 IRT720884:IRW720884 JBP720884:JBS720884 JLL720884:JLO720884 JVH720884:JVK720884 KFD720884:KFG720884 KOZ720884:KPC720884 KYV720884:KYY720884 LIR720884:LIU720884 LSN720884:LSQ720884 MCJ720884:MCM720884 MMF720884:MMI720884 MWB720884:MWE720884 NFX720884:NGA720884 NPT720884:NPW720884 NZP720884:NZS720884 OJL720884:OJO720884 OTH720884:OTK720884 PDD720884:PDG720884 PMZ720884:PNC720884 PWV720884:PWY720884 QGR720884:QGU720884 QQN720884:QQQ720884 RAJ720884:RAM720884 RKF720884:RKI720884 RUB720884:RUE720884 SDX720884:SEA720884 SNT720884:SNW720884 SXP720884:SXS720884 THL720884:THO720884 TRH720884:TRK720884 UBD720884:UBG720884 UKZ720884:ULC720884 UUV720884:UUY720884 VER720884:VEU720884 VON720884:VOQ720884 VYJ720884:VYM720884 WIF720884:WII720884 WSB720884:WSE720884 FP786420:FS786420 PL786420:PO786420 ZH786420:ZK786420 AJD786420:AJG786420 ASZ786420:ATC786420 BCV786420:BCY786420 BMR786420:BMU786420 BWN786420:BWQ786420 CGJ786420:CGM786420 CQF786420:CQI786420 DAB786420:DAE786420 DJX786420:DKA786420 DTT786420:DTW786420 EDP786420:EDS786420 ENL786420:ENO786420 EXH786420:EXK786420 FHD786420:FHG786420 FQZ786420:FRC786420 GAV786420:GAY786420 GKR786420:GKU786420 GUN786420:GUQ786420 HEJ786420:HEM786420 HOF786420:HOI786420 HYB786420:HYE786420 IHX786420:IIA786420 IRT786420:IRW786420 JBP786420:JBS786420 JLL786420:JLO786420 JVH786420:JVK786420 KFD786420:KFG786420 KOZ786420:KPC786420 KYV786420:KYY786420 LIR786420:LIU786420 LSN786420:LSQ786420 MCJ786420:MCM786420 MMF786420:MMI786420 MWB786420:MWE786420 NFX786420:NGA786420 NPT786420:NPW786420 NZP786420:NZS786420 OJL786420:OJO786420 OTH786420:OTK786420 PDD786420:PDG786420 PMZ786420:PNC786420 PWV786420:PWY786420 QGR786420:QGU786420 QQN786420:QQQ786420 RAJ786420:RAM786420 RKF786420:RKI786420 RUB786420:RUE786420 SDX786420:SEA786420 SNT786420:SNW786420 SXP786420:SXS786420 THL786420:THO786420 TRH786420:TRK786420 UBD786420:UBG786420 UKZ786420:ULC786420 UUV786420:UUY786420 VER786420:VEU786420 VON786420:VOQ786420 VYJ786420:VYM786420 WIF786420:WII786420 WSB786420:WSE786420 FP851956:FS851956 PL851956:PO851956 ZH851956:ZK851956 AJD851956:AJG851956 ASZ851956:ATC851956 BCV851956:BCY851956 BMR851956:BMU851956 BWN851956:BWQ851956 CGJ851956:CGM851956 CQF851956:CQI851956 DAB851956:DAE851956 DJX851956:DKA851956 DTT851956:DTW851956 EDP851956:EDS851956 ENL851956:ENO851956 EXH851956:EXK851956 FHD851956:FHG851956 FQZ851956:FRC851956 GAV851956:GAY851956 GKR851956:GKU851956 GUN851956:GUQ851956 HEJ851956:HEM851956 HOF851956:HOI851956 HYB851956:HYE851956 IHX851956:IIA851956 IRT851956:IRW851956 JBP851956:JBS851956 JLL851956:JLO851956 JVH851956:JVK851956 KFD851956:KFG851956 KOZ851956:KPC851956 KYV851956:KYY851956 LIR851956:LIU851956 LSN851956:LSQ851956 MCJ851956:MCM851956 MMF851956:MMI851956 MWB851956:MWE851956 NFX851956:NGA851956 NPT851956:NPW851956 NZP851956:NZS851956 OJL851956:OJO851956 OTH851956:OTK851956 PDD851956:PDG851956 PMZ851956:PNC851956 PWV851956:PWY851956 QGR851956:QGU851956 QQN851956:QQQ851956 RAJ851956:RAM851956 RKF851956:RKI851956 RUB851956:RUE851956 SDX851956:SEA851956 SNT851956:SNW851956 SXP851956:SXS851956 THL851956:THO851956 TRH851956:TRK851956 UBD851956:UBG851956 UKZ851956:ULC851956 UUV851956:UUY851956 VER851956:VEU851956 VON851956:VOQ851956 VYJ851956:VYM851956 WIF851956:WII851956 WSB851956:WSE851956 FP917492:FS917492 PL917492:PO917492 ZH917492:ZK917492 AJD917492:AJG917492 ASZ917492:ATC917492 BCV917492:BCY917492 BMR917492:BMU917492 BWN917492:BWQ917492 CGJ917492:CGM917492 CQF917492:CQI917492 DAB917492:DAE917492 DJX917492:DKA917492 DTT917492:DTW917492 EDP917492:EDS917492 ENL917492:ENO917492 EXH917492:EXK917492 FHD917492:FHG917492 FQZ917492:FRC917492 GAV917492:GAY917492 GKR917492:GKU917492 GUN917492:GUQ917492 HEJ917492:HEM917492 HOF917492:HOI917492 HYB917492:HYE917492 IHX917492:IIA917492 IRT917492:IRW917492 JBP917492:JBS917492 JLL917492:JLO917492 JVH917492:JVK917492 KFD917492:KFG917492 KOZ917492:KPC917492 KYV917492:KYY917492 LIR917492:LIU917492 LSN917492:LSQ917492 MCJ917492:MCM917492 MMF917492:MMI917492 MWB917492:MWE917492 NFX917492:NGA917492 NPT917492:NPW917492 NZP917492:NZS917492 OJL917492:OJO917492 OTH917492:OTK917492 PDD917492:PDG917492 PMZ917492:PNC917492 PWV917492:PWY917492 QGR917492:QGU917492 QQN917492:QQQ917492 RAJ917492:RAM917492 RKF917492:RKI917492 RUB917492:RUE917492 SDX917492:SEA917492 SNT917492:SNW917492 SXP917492:SXS917492 THL917492:THO917492 TRH917492:TRK917492 UBD917492:UBG917492 UKZ917492:ULC917492 UUV917492:UUY917492 VER917492:VEU917492 VON917492:VOQ917492 VYJ917492:VYM917492 WIF917492:WII917492 WSB917492:WSE917492 FP983028:FS983028 PL983028:PO983028 ZH983028:ZK983028 AJD983028:AJG983028 ASZ983028:ATC983028 BCV983028:BCY983028 BMR983028:BMU983028 BWN983028:BWQ983028 CGJ983028:CGM983028 CQF983028:CQI983028 DAB983028:DAE983028 DJX983028:DKA983028 DTT983028:DTW983028 EDP983028:EDS983028 ENL983028:ENO983028 EXH983028:EXK983028 FHD983028:FHG983028 FQZ983028:FRC983028 GAV983028:GAY983028 GKR983028:GKU983028 GUN983028:GUQ983028 HEJ983028:HEM983028 HOF983028:HOI983028 HYB983028:HYE983028 IHX983028:IIA983028 IRT983028:IRW983028 JBP983028:JBS983028 JLL983028:JLO983028 JVH983028:JVK983028 KFD983028:KFG983028 KOZ983028:KPC983028 KYV983028:KYY983028 LIR983028:LIU983028 LSN983028:LSQ983028 MCJ983028:MCM983028 MMF983028:MMI983028 MWB983028:MWE983028 NFX983028:NGA983028 NPT983028:NPW983028 NZP983028:NZS983028 OJL983028:OJO983028 OTH983028:OTK983028 PDD983028:PDG983028 PMZ983028:PNC983028 PWV983028:PWY983028 QGR983028:QGU983028 QQN983028:QQQ983028 RAJ983028:RAM983028 RKF983028:RKI983028 RUB983028:RUE983028 SDX983028:SEA983028 SNT983028:SNW983028 SXP983028:SXS983028 THL983028:THO983028 TRH983028:TRK983028 UBD983028:UBG983028 UKZ983028:ULC983028 UUV983028:UUY983028 VER983028:VEU983028 VON983028:VOQ983028 VYJ983028:VYM983028 WIF983028:WII983028 WSB983028:WSE983028 FK983027:FN983027 PG983027:PJ983027 ZC983027:ZF983027 AIY983027:AJB983027 ASU983027:ASX983027 BCQ983027:BCT983027 BMM983027:BMP983027 BWI983027:BWL983027 CGE983027:CGH983027 CQA983027:CQD983027 CZW983027:CZZ983027 DJS983027:DJV983027 DTO983027:DTR983027 EDK983027:EDN983027 ENG983027:ENJ983027 EXC983027:EXF983027 FGY983027:FHB983027 FQU983027:FQX983027 GAQ983027:GAT983027 GKM983027:GKP983027 GUI983027:GUL983027 HEE983027:HEH983027 HOA983027:HOD983027 HXW983027:HXZ983027 IHS983027:IHV983027 IRO983027:IRR983027 JBK983027:JBN983027 JLG983027:JLJ983027 JVC983027:JVF983027 KEY983027:KFB983027 KOU983027:KOX983027 KYQ983027:KYT983027 LIM983027:LIP983027 LSI983027:LSL983027 MCE983027:MCH983027 MMA983027:MMD983027 MVW983027:MVZ983027 NFS983027:NFV983027 NPO983027:NPR983027 NZK983027:NZN983027 OJG983027:OJJ983027 OTC983027:OTF983027 PCY983027:PDB983027 PMU983027:PMX983027 PWQ983027:PWT983027 QGM983027:QGP983027 QQI983027:QQL983027 RAE983027:RAH983027 RKA983027:RKD983027 RTW983027:RTZ983027 SDS983027:SDV983027 SNO983027:SNR983027 SXK983027:SXN983027 THG983027:THJ983027 TRC983027:TRF983027 UAY983027:UBB983027 UKU983027:UKX983027 UUQ983027:UUT983027 VEM983027:VEP983027 VOI983027:VOL983027 VYE983027:VYH983027 WIA983027:WID983027 WRW983027:WRZ983027 FK65523:FN65523 PG65523:PJ65523 ZC65523:ZF65523 AIY65523:AJB65523 ASU65523:ASX65523 BCQ65523:BCT65523 BMM65523:BMP65523 BWI65523:BWL65523 CGE65523:CGH65523 CQA65523:CQD65523 CZW65523:CZZ65523 DJS65523:DJV65523 DTO65523:DTR65523 EDK65523:EDN65523 ENG65523:ENJ65523 EXC65523:EXF65523 FGY65523:FHB65523 FQU65523:FQX65523 GAQ65523:GAT65523 GKM65523:GKP65523 GUI65523:GUL65523 HEE65523:HEH65523 HOA65523:HOD65523 HXW65523:HXZ65523 IHS65523:IHV65523 IRO65523:IRR65523 JBK65523:JBN65523 JLG65523:JLJ65523 JVC65523:JVF65523 KEY65523:KFB65523 KOU65523:KOX65523 KYQ65523:KYT65523 LIM65523:LIP65523 LSI65523:LSL65523 MCE65523:MCH65523 MMA65523:MMD65523 MVW65523:MVZ65523 NFS65523:NFV65523 NPO65523:NPR65523 NZK65523:NZN65523 OJG65523:OJJ65523 OTC65523:OTF65523 PCY65523:PDB65523 PMU65523:PMX65523 PWQ65523:PWT65523 QGM65523:QGP65523 QQI65523:QQL65523 RAE65523:RAH65523 RKA65523:RKD65523 RTW65523:RTZ65523 SDS65523:SDV65523 SNO65523:SNR65523 SXK65523:SXN65523 THG65523:THJ65523 TRC65523:TRF65523 UAY65523:UBB65523 UKU65523:UKX65523 UUQ65523:UUT65523 VEM65523:VEP65523 VOI65523:VOL65523 VYE65523:VYH65523 WIA65523:WID65523 WRW65523:WRZ65523 FK131059:FN131059 PG131059:PJ131059 ZC131059:ZF131059 AIY131059:AJB131059 ASU131059:ASX131059 BCQ131059:BCT131059 BMM131059:BMP131059 BWI131059:BWL131059 CGE131059:CGH131059 CQA131059:CQD131059 CZW131059:CZZ131059 DJS131059:DJV131059 DTO131059:DTR131059 EDK131059:EDN131059 ENG131059:ENJ131059 EXC131059:EXF131059 FGY131059:FHB131059 FQU131059:FQX131059 GAQ131059:GAT131059 GKM131059:GKP131059 GUI131059:GUL131059 HEE131059:HEH131059 HOA131059:HOD131059 HXW131059:HXZ131059 IHS131059:IHV131059 IRO131059:IRR131059 JBK131059:JBN131059 JLG131059:JLJ131059 JVC131059:JVF131059 KEY131059:KFB131059 KOU131059:KOX131059 KYQ131059:KYT131059 LIM131059:LIP131059 LSI131059:LSL131059 MCE131059:MCH131059 MMA131059:MMD131059 MVW131059:MVZ131059 NFS131059:NFV131059 NPO131059:NPR131059 NZK131059:NZN131059 OJG131059:OJJ131059 OTC131059:OTF131059 PCY131059:PDB131059 PMU131059:PMX131059 PWQ131059:PWT131059 QGM131059:QGP131059 QQI131059:QQL131059 RAE131059:RAH131059 RKA131059:RKD131059 RTW131059:RTZ131059 SDS131059:SDV131059 SNO131059:SNR131059 SXK131059:SXN131059 THG131059:THJ131059 TRC131059:TRF131059 UAY131059:UBB131059 UKU131059:UKX131059 UUQ131059:UUT131059 VEM131059:VEP131059 VOI131059:VOL131059 VYE131059:VYH131059 WIA131059:WID131059 WRW131059:WRZ131059 FK196595:FN196595 PG196595:PJ196595 ZC196595:ZF196595 AIY196595:AJB196595 ASU196595:ASX196595 BCQ196595:BCT196595 BMM196595:BMP196595 BWI196595:BWL196595 CGE196595:CGH196595 CQA196595:CQD196595 CZW196595:CZZ196595 DJS196595:DJV196595 DTO196595:DTR196595 EDK196595:EDN196595 ENG196595:ENJ196595 EXC196595:EXF196595 FGY196595:FHB196595 FQU196595:FQX196595 GAQ196595:GAT196595 GKM196595:GKP196595 GUI196595:GUL196595 HEE196595:HEH196595 HOA196595:HOD196595 HXW196595:HXZ196595 IHS196595:IHV196595 IRO196595:IRR196595 JBK196595:JBN196595 JLG196595:JLJ196595 JVC196595:JVF196595 KEY196595:KFB196595 KOU196595:KOX196595 KYQ196595:KYT196595 LIM196595:LIP196595 LSI196595:LSL196595 MCE196595:MCH196595 MMA196595:MMD196595 MVW196595:MVZ196595 NFS196595:NFV196595 NPO196595:NPR196595 NZK196595:NZN196595 OJG196595:OJJ196595 OTC196595:OTF196595 PCY196595:PDB196595 PMU196595:PMX196595 PWQ196595:PWT196595 QGM196595:QGP196595 QQI196595:QQL196595 RAE196595:RAH196595 RKA196595:RKD196595 RTW196595:RTZ196595 SDS196595:SDV196595 SNO196595:SNR196595 SXK196595:SXN196595 THG196595:THJ196595 TRC196595:TRF196595 UAY196595:UBB196595 UKU196595:UKX196595 UUQ196595:UUT196595 VEM196595:VEP196595 VOI196595:VOL196595 VYE196595:VYH196595 WIA196595:WID196595 WRW196595:WRZ196595 FK262131:FN262131 PG262131:PJ262131 ZC262131:ZF262131 AIY262131:AJB262131 ASU262131:ASX262131 BCQ262131:BCT262131 BMM262131:BMP262131 BWI262131:BWL262131 CGE262131:CGH262131 CQA262131:CQD262131 CZW262131:CZZ262131 DJS262131:DJV262131 DTO262131:DTR262131 EDK262131:EDN262131 ENG262131:ENJ262131 EXC262131:EXF262131 FGY262131:FHB262131 FQU262131:FQX262131 GAQ262131:GAT262131 GKM262131:GKP262131 GUI262131:GUL262131 HEE262131:HEH262131 HOA262131:HOD262131 HXW262131:HXZ262131 IHS262131:IHV262131 IRO262131:IRR262131 JBK262131:JBN262131 JLG262131:JLJ262131 JVC262131:JVF262131 KEY262131:KFB262131 KOU262131:KOX262131 KYQ262131:KYT262131 LIM262131:LIP262131 LSI262131:LSL262131 MCE262131:MCH262131 MMA262131:MMD262131 MVW262131:MVZ262131 NFS262131:NFV262131 NPO262131:NPR262131 NZK262131:NZN262131 OJG262131:OJJ262131 OTC262131:OTF262131 PCY262131:PDB262131 PMU262131:PMX262131 PWQ262131:PWT262131 QGM262131:QGP262131 QQI262131:QQL262131 RAE262131:RAH262131 RKA262131:RKD262131 RTW262131:RTZ262131 SDS262131:SDV262131 SNO262131:SNR262131 SXK262131:SXN262131 THG262131:THJ262131 TRC262131:TRF262131 UAY262131:UBB262131 UKU262131:UKX262131 UUQ262131:UUT262131 VEM262131:VEP262131 VOI262131:VOL262131 VYE262131:VYH262131 WIA262131:WID262131 WRW262131:WRZ262131 FK327667:FN327667 PG327667:PJ327667 ZC327667:ZF327667 AIY327667:AJB327667 ASU327667:ASX327667 BCQ327667:BCT327667 BMM327667:BMP327667 BWI327667:BWL327667 CGE327667:CGH327667 CQA327667:CQD327667 CZW327667:CZZ327667 DJS327667:DJV327667 DTO327667:DTR327667 EDK327667:EDN327667 ENG327667:ENJ327667 EXC327667:EXF327667 FGY327667:FHB327667 FQU327667:FQX327667 GAQ327667:GAT327667 GKM327667:GKP327667 GUI327667:GUL327667 HEE327667:HEH327667 HOA327667:HOD327667 HXW327667:HXZ327667 IHS327667:IHV327667 IRO327667:IRR327667 JBK327667:JBN327667 JLG327667:JLJ327667 JVC327667:JVF327667 KEY327667:KFB327667 KOU327667:KOX327667 KYQ327667:KYT327667 LIM327667:LIP327667 LSI327667:LSL327667 MCE327667:MCH327667 MMA327667:MMD327667 MVW327667:MVZ327667 NFS327667:NFV327667 NPO327667:NPR327667 NZK327667:NZN327667 OJG327667:OJJ327667 OTC327667:OTF327667 PCY327667:PDB327667 PMU327667:PMX327667 PWQ327667:PWT327667 QGM327667:QGP327667 QQI327667:QQL327667 RAE327667:RAH327667 RKA327667:RKD327667 RTW327667:RTZ327667 SDS327667:SDV327667 SNO327667:SNR327667 SXK327667:SXN327667 THG327667:THJ327667 TRC327667:TRF327667 UAY327667:UBB327667 UKU327667:UKX327667 UUQ327667:UUT327667 VEM327667:VEP327667 VOI327667:VOL327667 VYE327667:VYH327667 WIA327667:WID327667 WRW327667:WRZ327667 FK393203:FN393203 PG393203:PJ393203 ZC393203:ZF393203 AIY393203:AJB393203 ASU393203:ASX393203 BCQ393203:BCT393203 BMM393203:BMP393203 BWI393203:BWL393203 CGE393203:CGH393203 CQA393203:CQD393203 CZW393203:CZZ393203 DJS393203:DJV393203 DTO393203:DTR393203 EDK393203:EDN393203 ENG393203:ENJ393203 EXC393203:EXF393203 FGY393203:FHB393203 FQU393203:FQX393203 GAQ393203:GAT393203 GKM393203:GKP393203 GUI393203:GUL393203 HEE393203:HEH393203 HOA393203:HOD393203 HXW393203:HXZ393203 IHS393203:IHV393203 IRO393203:IRR393203 JBK393203:JBN393203 JLG393203:JLJ393203 JVC393203:JVF393203 KEY393203:KFB393203 KOU393203:KOX393203 KYQ393203:KYT393203 LIM393203:LIP393203 LSI393203:LSL393203 MCE393203:MCH393203 MMA393203:MMD393203 MVW393203:MVZ393203 NFS393203:NFV393203 NPO393203:NPR393203 NZK393203:NZN393203 OJG393203:OJJ393203 OTC393203:OTF393203 PCY393203:PDB393203 PMU393203:PMX393203 PWQ393203:PWT393203 QGM393203:QGP393203 QQI393203:QQL393203 RAE393203:RAH393203 RKA393203:RKD393203 RTW393203:RTZ393203 SDS393203:SDV393203 SNO393203:SNR393203 SXK393203:SXN393203 THG393203:THJ393203 TRC393203:TRF393203 UAY393203:UBB393203 UKU393203:UKX393203 UUQ393203:UUT393203 VEM393203:VEP393203 VOI393203:VOL393203 VYE393203:VYH393203 WIA393203:WID393203 WRW393203:WRZ393203 FK458739:FN458739 PG458739:PJ458739 ZC458739:ZF458739 AIY458739:AJB458739 ASU458739:ASX458739 BCQ458739:BCT458739 BMM458739:BMP458739 BWI458739:BWL458739 CGE458739:CGH458739 CQA458739:CQD458739 CZW458739:CZZ458739 DJS458739:DJV458739 DTO458739:DTR458739 EDK458739:EDN458739 ENG458739:ENJ458739 EXC458739:EXF458739 FGY458739:FHB458739 FQU458739:FQX458739 GAQ458739:GAT458739 GKM458739:GKP458739 GUI458739:GUL458739 HEE458739:HEH458739 HOA458739:HOD458739 HXW458739:HXZ458739 IHS458739:IHV458739 IRO458739:IRR458739 JBK458739:JBN458739 JLG458739:JLJ458739 JVC458739:JVF458739 KEY458739:KFB458739 KOU458739:KOX458739 KYQ458739:KYT458739 LIM458739:LIP458739 LSI458739:LSL458739 MCE458739:MCH458739 MMA458739:MMD458739 MVW458739:MVZ458739 NFS458739:NFV458739 NPO458739:NPR458739 NZK458739:NZN458739 OJG458739:OJJ458739 OTC458739:OTF458739 PCY458739:PDB458739 PMU458739:PMX458739 PWQ458739:PWT458739 QGM458739:QGP458739 QQI458739:QQL458739 RAE458739:RAH458739 RKA458739:RKD458739 RTW458739:RTZ458739 SDS458739:SDV458739 SNO458739:SNR458739 SXK458739:SXN458739 THG458739:THJ458739 TRC458739:TRF458739 UAY458739:UBB458739 UKU458739:UKX458739 UUQ458739:UUT458739 VEM458739:VEP458739 VOI458739:VOL458739 VYE458739:VYH458739 WIA458739:WID458739 WRW458739:WRZ458739 FK524275:FN524275 PG524275:PJ524275 ZC524275:ZF524275 AIY524275:AJB524275 ASU524275:ASX524275 BCQ524275:BCT524275 BMM524275:BMP524275 BWI524275:BWL524275 CGE524275:CGH524275 CQA524275:CQD524275 CZW524275:CZZ524275 DJS524275:DJV524275 DTO524275:DTR524275 EDK524275:EDN524275 ENG524275:ENJ524275 EXC524275:EXF524275 FGY524275:FHB524275 FQU524275:FQX524275 GAQ524275:GAT524275 GKM524275:GKP524275 GUI524275:GUL524275 HEE524275:HEH524275 HOA524275:HOD524275 HXW524275:HXZ524275 IHS524275:IHV524275 IRO524275:IRR524275 JBK524275:JBN524275 JLG524275:JLJ524275 JVC524275:JVF524275 KEY524275:KFB524275 KOU524275:KOX524275 KYQ524275:KYT524275 LIM524275:LIP524275 LSI524275:LSL524275 MCE524275:MCH524275 MMA524275:MMD524275 MVW524275:MVZ524275 NFS524275:NFV524275 NPO524275:NPR524275 NZK524275:NZN524275 OJG524275:OJJ524275 OTC524275:OTF524275 PCY524275:PDB524275 PMU524275:PMX524275 PWQ524275:PWT524275 QGM524275:QGP524275 QQI524275:QQL524275 RAE524275:RAH524275 RKA524275:RKD524275 RTW524275:RTZ524275 SDS524275:SDV524275 SNO524275:SNR524275 SXK524275:SXN524275 THG524275:THJ524275 TRC524275:TRF524275 UAY524275:UBB524275 UKU524275:UKX524275 UUQ524275:UUT524275 VEM524275:VEP524275 VOI524275:VOL524275 VYE524275:VYH524275 WIA524275:WID524275 WRW524275:WRZ524275 FK589811:FN589811 PG589811:PJ589811 ZC589811:ZF589811 AIY589811:AJB589811 ASU589811:ASX589811 BCQ589811:BCT589811 BMM589811:BMP589811 BWI589811:BWL589811 CGE589811:CGH589811 CQA589811:CQD589811 CZW589811:CZZ589811 DJS589811:DJV589811 DTO589811:DTR589811 EDK589811:EDN589811 ENG589811:ENJ589811 EXC589811:EXF589811 FGY589811:FHB589811 FQU589811:FQX589811 GAQ589811:GAT589811 GKM589811:GKP589811 GUI589811:GUL589811 HEE589811:HEH589811 HOA589811:HOD589811 HXW589811:HXZ589811 IHS589811:IHV589811 IRO589811:IRR589811 JBK589811:JBN589811 JLG589811:JLJ589811 JVC589811:JVF589811 KEY589811:KFB589811 KOU589811:KOX589811 KYQ589811:KYT589811 LIM589811:LIP589811 LSI589811:LSL589811 MCE589811:MCH589811 MMA589811:MMD589811 MVW589811:MVZ589811 NFS589811:NFV589811 NPO589811:NPR589811 NZK589811:NZN589811 OJG589811:OJJ589811 OTC589811:OTF589811 PCY589811:PDB589811 PMU589811:PMX589811 PWQ589811:PWT589811 QGM589811:QGP589811 QQI589811:QQL589811 RAE589811:RAH589811 RKA589811:RKD589811 RTW589811:RTZ589811 SDS589811:SDV589811 SNO589811:SNR589811 SXK589811:SXN589811 THG589811:THJ589811 TRC589811:TRF589811 UAY589811:UBB589811 UKU589811:UKX589811 UUQ589811:UUT589811 VEM589811:VEP589811 VOI589811:VOL589811 VYE589811:VYH589811 WIA589811:WID589811 WRW589811:WRZ589811 FK655347:FN655347 PG655347:PJ655347 ZC655347:ZF655347 AIY655347:AJB655347 ASU655347:ASX655347 BCQ655347:BCT655347 BMM655347:BMP655347 BWI655347:BWL655347 CGE655347:CGH655347 CQA655347:CQD655347 CZW655347:CZZ655347 DJS655347:DJV655347 DTO655347:DTR655347 EDK655347:EDN655347 ENG655347:ENJ655347 EXC655347:EXF655347 FGY655347:FHB655347 FQU655347:FQX655347 GAQ655347:GAT655347 GKM655347:GKP655347 GUI655347:GUL655347 HEE655347:HEH655347 HOA655347:HOD655347 HXW655347:HXZ655347 IHS655347:IHV655347 IRO655347:IRR655347 JBK655347:JBN655347 JLG655347:JLJ655347 JVC655347:JVF655347 KEY655347:KFB655347 KOU655347:KOX655347 KYQ655347:KYT655347 LIM655347:LIP655347 LSI655347:LSL655347 MCE655347:MCH655347 MMA655347:MMD655347 MVW655347:MVZ655347 NFS655347:NFV655347 NPO655347:NPR655347 NZK655347:NZN655347 OJG655347:OJJ655347 OTC655347:OTF655347 PCY655347:PDB655347 PMU655347:PMX655347 PWQ655347:PWT655347 QGM655347:QGP655347 QQI655347:QQL655347 RAE655347:RAH655347 RKA655347:RKD655347 RTW655347:RTZ655347 SDS655347:SDV655347 SNO655347:SNR655347 SXK655347:SXN655347 THG655347:THJ655347 TRC655347:TRF655347 UAY655347:UBB655347 UKU655347:UKX655347 UUQ655347:UUT655347 VEM655347:VEP655347 VOI655347:VOL655347 VYE655347:VYH655347 WIA655347:WID655347 WRW655347:WRZ655347 FK720883:FN720883 PG720883:PJ720883 ZC720883:ZF720883 AIY720883:AJB720883 ASU720883:ASX720883 BCQ720883:BCT720883 BMM720883:BMP720883 BWI720883:BWL720883 CGE720883:CGH720883 CQA720883:CQD720883 CZW720883:CZZ720883 DJS720883:DJV720883 DTO720883:DTR720883 EDK720883:EDN720883 ENG720883:ENJ720883 EXC720883:EXF720883 FGY720883:FHB720883 FQU720883:FQX720883 GAQ720883:GAT720883 GKM720883:GKP720883 GUI720883:GUL720883 HEE720883:HEH720883 HOA720883:HOD720883 HXW720883:HXZ720883 IHS720883:IHV720883 IRO720883:IRR720883 JBK720883:JBN720883 JLG720883:JLJ720883 JVC720883:JVF720883 KEY720883:KFB720883 KOU720883:KOX720883 KYQ720883:KYT720883 LIM720883:LIP720883 LSI720883:LSL720883 MCE720883:MCH720883 MMA720883:MMD720883 MVW720883:MVZ720883 NFS720883:NFV720883 NPO720883:NPR720883 NZK720883:NZN720883 OJG720883:OJJ720883 OTC720883:OTF720883 PCY720883:PDB720883 PMU720883:PMX720883 PWQ720883:PWT720883 QGM720883:QGP720883 QQI720883:QQL720883 RAE720883:RAH720883 RKA720883:RKD720883 RTW720883:RTZ720883 SDS720883:SDV720883 SNO720883:SNR720883 SXK720883:SXN720883 THG720883:THJ720883 TRC720883:TRF720883 UAY720883:UBB720883 UKU720883:UKX720883 UUQ720883:UUT720883 VEM720883:VEP720883 VOI720883:VOL720883 VYE720883:VYH720883 WIA720883:WID720883 WRW720883:WRZ720883 FK786419:FN786419 PG786419:PJ786419 ZC786419:ZF786419 AIY786419:AJB786419 ASU786419:ASX786419 BCQ786419:BCT786419 BMM786419:BMP786419 BWI786419:BWL786419 CGE786419:CGH786419 CQA786419:CQD786419 CZW786419:CZZ786419 DJS786419:DJV786419 DTO786419:DTR786419 EDK786419:EDN786419 ENG786419:ENJ786419 EXC786419:EXF786419 FGY786419:FHB786419 FQU786419:FQX786419 GAQ786419:GAT786419 GKM786419:GKP786419 GUI786419:GUL786419 HEE786419:HEH786419 HOA786419:HOD786419 HXW786419:HXZ786419 IHS786419:IHV786419 IRO786419:IRR786419 JBK786419:JBN786419 JLG786419:JLJ786419 JVC786419:JVF786419 KEY786419:KFB786419 KOU786419:KOX786419 KYQ786419:KYT786419 LIM786419:LIP786419 LSI786419:LSL786419 MCE786419:MCH786419 MMA786419:MMD786419 MVW786419:MVZ786419 NFS786419:NFV786419 NPO786419:NPR786419 NZK786419:NZN786419 OJG786419:OJJ786419 OTC786419:OTF786419 PCY786419:PDB786419 PMU786419:PMX786419 PWQ786419:PWT786419 QGM786419:QGP786419 QQI786419:QQL786419 RAE786419:RAH786419 RKA786419:RKD786419 RTW786419:RTZ786419 SDS786419:SDV786419 SNO786419:SNR786419 SXK786419:SXN786419 THG786419:THJ786419 TRC786419:TRF786419 UAY786419:UBB786419 UKU786419:UKX786419 UUQ786419:UUT786419 VEM786419:VEP786419 VOI786419:VOL786419 VYE786419:VYH786419 WIA786419:WID786419 WRW786419:WRZ786419 FK851955:FN851955 PG851955:PJ851955 ZC851955:ZF851955 AIY851955:AJB851955 ASU851955:ASX851955 BCQ851955:BCT851955 BMM851955:BMP851955 BWI851955:BWL851955 CGE851955:CGH851955 CQA851955:CQD851955 CZW851955:CZZ851955 DJS851955:DJV851955 DTO851955:DTR851955 EDK851955:EDN851955 ENG851955:ENJ851955 EXC851955:EXF851955 FGY851955:FHB851955 FQU851955:FQX851955 GAQ851955:GAT851955 GKM851955:GKP851955 GUI851955:GUL851955 HEE851955:HEH851955 HOA851955:HOD851955 HXW851955:HXZ851955 IHS851955:IHV851955 IRO851955:IRR851955 JBK851955:JBN851955 JLG851955:JLJ851955 JVC851955:JVF851955 KEY851955:KFB851955 KOU851955:KOX851955 KYQ851955:KYT851955 LIM851955:LIP851955 LSI851955:LSL851955 MCE851955:MCH851955 MMA851955:MMD851955 MVW851955:MVZ851955 NFS851955:NFV851955 NPO851955:NPR851955 NZK851955:NZN851955 OJG851955:OJJ851955 OTC851955:OTF851955 PCY851955:PDB851955 PMU851955:PMX851955 PWQ851955:PWT851955 QGM851955:QGP851955 QQI851955:QQL851955 RAE851955:RAH851955 RKA851955:RKD851955 RTW851955:RTZ851955 SDS851955:SDV851955 SNO851955:SNR851955 SXK851955:SXN851955 THG851955:THJ851955 TRC851955:TRF851955 UAY851955:UBB851955 UKU851955:UKX851955 UUQ851955:UUT851955 VEM851955:VEP851955 VOI851955:VOL851955 VYE851955:VYH851955 WIA851955:WID851955 WRW851955:WRZ851955 FK917491:FN917491 PG917491:PJ917491 ZC917491:ZF917491 AIY917491:AJB917491 ASU917491:ASX917491 BCQ917491:BCT917491 BMM917491:BMP917491 BWI917491:BWL917491 CGE917491:CGH917491 CQA917491:CQD917491 CZW917491:CZZ917491 DJS917491:DJV917491 DTO917491:DTR917491 EDK917491:EDN917491 ENG917491:ENJ917491 EXC917491:EXF917491 FGY917491:FHB917491 FQU917491:FQX917491 GAQ917491:GAT917491 GKM917491:GKP917491 GUI917491:GUL917491 HEE917491:HEH917491 HOA917491:HOD917491 HXW917491:HXZ917491 IHS917491:IHV917491 IRO917491:IRR917491 JBK917491:JBN917491 JLG917491:JLJ917491 JVC917491:JVF917491 KEY917491:KFB917491 KOU917491:KOX917491 KYQ917491:KYT917491 LIM917491:LIP917491 LSI917491:LSL917491 MCE917491:MCH917491 MMA917491:MMD917491 MVW917491:MVZ917491 NFS917491:NFV917491 NPO917491:NPR917491 NZK917491:NZN917491 OJG917491:OJJ917491 OTC917491:OTF917491 PCY917491:PDB917491 PMU917491:PMX917491 PWQ917491:PWT917491 QGM917491:QGP917491 QQI917491:QQL917491 RAE917491:RAH917491 RKA917491:RKD917491 RTW917491:RTZ917491 SDS917491:SDV917491 SNO917491:SNR917491 SXK917491:SXN917491 THG917491:THJ917491 TRC917491:TRF917491 UAY917491:UBB917491 UKU917491:UKX917491 UUQ917491:UUT917491 VEM917491:VEP917491 VOI917491:VOL917491 VYE917491:VYH917491 WIA917491:WID917491 WRW917491:WRZ917491" xr:uid="{1F423F3A-416F-4E97-8D9A-05CEEFB5D039}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FU65528:FX65531 PQ65528:PT65531 ZM65528:ZP65531 AJI65528:AJL65531 ATE65528:ATH65531 BDA65528:BDD65531 BMW65528:BMZ65531 BWS65528:BWV65531 CGO65528:CGR65531 CQK65528:CQN65531 DAG65528:DAJ65531 DKC65528:DKF65531 DTY65528:DUB65531 EDU65528:EDX65531 ENQ65528:ENT65531 EXM65528:EXP65531 FHI65528:FHL65531 FRE65528:FRH65531 GBA65528:GBD65531 GKW65528:GKZ65531 GUS65528:GUV65531 HEO65528:HER65531 HOK65528:HON65531 HYG65528:HYJ65531 IIC65528:IIF65531 IRY65528:ISB65531 JBU65528:JBX65531 JLQ65528:JLT65531 JVM65528:JVP65531 KFI65528:KFL65531 KPE65528:KPH65531 KZA65528:KZD65531 LIW65528:LIZ65531 LSS65528:LSV65531 MCO65528:MCR65531 MMK65528:MMN65531 MWG65528:MWJ65531 NGC65528:NGF65531 NPY65528:NQB65531 NZU65528:NZX65531 OJQ65528:OJT65531 OTM65528:OTP65531 PDI65528:PDL65531 PNE65528:PNH65531 PXA65528:PXD65531 QGW65528:QGZ65531 QQS65528:QQV65531 RAO65528:RAR65531 RKK65528:RKN65531 RUG65528:RUJ65531 SEC65528:SEF65531 SNY65528:SOB65531 SXU65528:SXX65531 THQ65528:THT65531 TRM65528:TRP65531 UBI65528:UBL65531 ULE65528:ULH65531 UVA65528:UVD65531 VEW65528:VEZ65531 VOS65528:VOV65531 VYO65528:VYR65531 WIK65528:WIN65531 WSG65528:WSJ65531 FU131064:FX131067 PQ131064:PT131067 ZM131064:ZP131067 AJI131064:AJL131067 ATE131064:ATH131067 BDA131064:BDD131067 BMW131064:BMZ131067 BWS131064:BWV131067 CGO131064:CGR131067 CQK131064:CQN131067 DAG131064:DAJ131067 DKC131064:DKF131067 DTY131064:DUB131067 EDU131064:EDX131067 ENQ131064:ENT131067 EXM131064:EXP131067 FHI131064:FHL131067 FRE131064:FRH131067 GBA131064:GBD131067 GKW131064:GKZ131067 GUS131064:GUV131067 HEO131064:HER131067 HOK131064:HON131067 HYG131064:HYJ131067 IIC131064:IIF131067 IRY131064:ISB131067 JBU131064:JBX131067 JLQ131064:JLT131067 JVM131064:JVP131067 KFI131064:KFL131067 KPE131064:KPH131067 KZA131064:KZD131067 LIW131064:LIZ131067 LSS131064:LSV131067 MCO131064:MCR131067 MMK131064:MMN131067 MWG131064:MWJ131067 NGC131064:NGF131067 NPY131064:NQB131067 NZU131064:NZX131067 OJQ131064:OJT131067 OTM131064:OTP131067 PDI131064:PDL131067 PNE131064:PNH131067 PXA131064:PXD131067 QGW131064:QGZ131067 QQS131064:QQV131067 RAO131064:RAR131067 RKK131064:RKN131067 RUG131064:RUJ131067 SEC131064:SEF131067 SNY131064:SOB131067 SXU131064:SXX131067 THQ131064:THT131067 TRM131064:TRP131067 UBI131064:UBL131067 ULE131064:ULH131067 UVA131064:UVD131067 VEW131064:VEZ131067 VOS131064:VOV131067 VYO131064:VYR131067 WIK131064:WIN131067 WSG131064:WSJ131067 FU196600:FX196603 PQ196600:PT196603 ZM196600:ZP196603 AJI196600:AJL196603 ATE196600:ATH196603 BDA196600:BDD196603 BMW196600:BMZ196603 BWS196600:BWV196603 CGO196600:CGR196603 CQK196600:CQN196603 DAG196600:DAJ196603 DKC196600:DKF196603 DTY196600:DUB196603 EDU196600:EDX196603 ENQ196600:ENT196603 EXM196600:EXP196603 FHI196600:FHL196603 FRE196600:FRH196603 GBA196600:GBD196603 GKW196600:GKZ196603 GUS196600:GUV196603 HEO196600:HER196603 HOK196600:HON196603 HYG196600:HYJ196603 IIC196600:IIF196603 IRY196600:ISB196603 JBU196600:JBX196603 JLQ196600:JLT196603 JVM196600:JVP196603 KFI196600:KFL196603 KPE196600:KPH196603 KZA196600:KZD196603 LIW196600:LIZ196603 LSS196600:LSV196603 MCO196600:MCR196603 MMK196600:MMN196603 MWG196600:MWJ196603 NGC196600:NGF196603 NPY196600:NQB196603 NZU196600:NZX196603 OJQ196600:OJT196603 OTM196600:OTP196603 PDI196600:PDL196603 PNE196600:PNH196603 PXA196600:PXD196603 QGW196600:QGZ196603 QQS196600:QQV196603 RAO196600:RAR196603 RKK196600:RKN196603 RUG196600:RUJ196603 SEC196600:SEF196603 SNY196600:SOB196603 SXU196600:SXX196603 THQ196600:THT196603 TRM196600:TRP196603 UBI196600:UBL196603 ULE196600:ULH196603 UVA196600:UVD196603 VEW196600:VEZ196603 VOS196600:VOV196603 VYO196600:VYR196603 WIK196600:WIN196603 WSG196600:WSJ196603 FU262136:FX262139 PQ262136:PT262139 ZM262136:ZP262139 AJI262136:AJL262139 ATE262136:ATH262139 BDA262136:BDD262139 BMW262136:BMZ262139 BWS262136:BWV262139 CGO262136:CGR262139 CQK262136:CQN262139 DAG262136:DAJ262139 DKC262136:DKF262139 DTY262136:DUB262139 EDU262136:EDX262139 ENQ262136:ENT262139 EXM262136:EXP262139 FHI262136:FHL262139 FRE262136:FRH262139 GBA262136:GBD262139 GKW262136:GKZ262139 GUS262136:GUV262139 HEO262136:HER262139 HOK262136:HON262139 HYG262136:HYJ262139 IIC262136:IIF262139 IRY262136:ISB262139 JBU262136:JBX262139 JLQ262136:JLT262139 JVM262136:JVP262139 KFI262136:KFL262139 KPE262136:KPH262139 KZA262136:KZD262139 LIW262136:LIZ262139 LSS262136:LSV262139 MCO262136:MCR262139 MMK262136:MMN262139 MWG262136:MWJ262139 NGC262136:NGF262139 NPY262136:NQB262139 NZU262136:NZX262139 OJQ262136:OJT262139 OTM262136:OTP262139 PDI262136:PDL262139 PNE262136:PNH262139 PXA262136:PXD262139 QGW262136:QGZ262139 QQS262136:QQV262139 RAO262136:RAR262139 RKK262136:RKN262139 RUG262136:RUJ262139 SEC262136:SEF262139 SNY262136:SOB262139 SXU262136:SXX262139 THQ262136:THT262139 TRM262136:TRP262139 UBI262136:UBL262139 ULE262136:ULH262139 UVA262136:UVD262139 VEW262136:VEZ262139 VOS262136:VOV262139 VYO262136:VYR262139 WIK262136:WIN262139 WSG262136:WSJ262139 FU327672:FX327675 PQ327672:PT327675 ZM327672:ZP327675 AJI327672:AJL327675 ATE327672:ATH327675 BDA327672:BDD327675 BMW327672:BMZ327675 BWS327672:BWV327675 CGO327672:CGR327675 CQK327672:CQN327675 DAG327672:DAJ327675 DKC327672:DKF327675 DTY327672:DUB327675 EDU327672:EDX327675 ENQ327672:ENT327675 EXM327672:EXP327675 FHI327672:FHL327675 FRE327672:FRH327675 GBA327672:GBD327675 GKW327672:GKZ327675 GUS327672:GUV327675 HEO327672:HER327675 HOK327672:HON327675 HYG327672:HYJ327675 IIC327672:IIF327675 IRY327672:ISB327675 JBU327672:JBX327675 JLQ327672:JLT327675 JVM327672:JVP327675 KFI327672:KFL327675 KPE327672:KPH327675 KZA327672:KZD327675 LIW327672:LIZ327675 LSS327672:LSV327675 MCO327672:MCR327675 MMK327672:MMN327675 MWG327672:MWJ327675 NGC327672:NGF327675 NPY327672:NQB327675 NZU327672:NZX327675 OJQ327672:OJT327675 OTM327672:OTP327675 PDI327672:PDL327675 PNE327672:PNH327675 PXA327672:PXD327675 QGW327672:QGZ327675 QQS327672:QQV327675 RAO327672:RAR327675 RKK327672:RKN327675 RUG327672:RUJ327675 SEC327672:SEF327675 SNY327672:SOB327675 SXU327672:SXX327675 THQ327672:THT327675 TRM327672:TRP327675 UBI327672:UBL327675 ULE327672:ULH327675 UVA327672:UVD327675 VEW327672:VEZ327675 VOS327672:VOV327675 VYO327672:VYR327675 WIK327672:WIN327675 WSG327672:WSJ327675 FU393208:FX393211 PQ393208:PT393211 ZM393208:ZP393211 AJI393208:AJL393211 ATE393208:ATH393211 BDA393208:BDD393211 BMW393208:BMZ393211 BWS393208:BWV393211 CGO393208:CGR393211 CQK393208:CQN393211 DAG393208:DAJ393211 DKC393208:DKF393211 DTY393208:DUB393211 EDU393208:EDX393211 ENQ393208:ENT393211 EXM393208:EXP393211 FHI393208:FHL393211 FRE393208:FRH393211 GBA393208:GBD393211 GKW393208:GKZ393211 GUS393208:GUV393211 HEO393208:HER393211 HOK393208:HON393211 HYG393208:HYJ393211 IIC393208:IIF393211 IRY393208:ISB393211 JBU393208:JBX393211 JLQ393208:JLT393211 JVM393208:JVP393211 KFI393208:KFL393211 KPE393208:KPH393211 KZA393208:KZD393211 LIW393208:LIZ393211 LSS393208:LSV393211 MCO393208:MCR393211 MMK393208:MMN393211 MWG393208:MWJ393211 NGC393208:NGF393211 NPY393208:NQB393211 NZU393208:NZX393211 OJQ393208:OJT393211 OTM393208:OTP393211 PDI393208:PDL393211 PNE393208:PNH393211 PXA393208:PXD393211 QGW393208:QGZ393211 QQS393208:QQV393211 RAO393208:RAR393211 RKK393208:RKN393211 RUG393208:RUJ393211 SEC393208:SEF393211 SNY393208:SOB393211 SXU393208:SXX393211 THQ393208:THT393211 TRM393208:TRP393211 UBI393208:UBL393211 ULE393208:ULH393211 UVA393208:UVD393211 VEW393208:VEZ393211 VOS393208:VOV393211 VYO393208:VYR393211 WIK393208:WIN393211 WSG393208:WSJ393211 FU458744:FX458747 PQ458744:PT458747 ZM458744:ZP458747 AJI458744:AJL458747 ATE458744:ATH458747 BDA458744:BDD458747 BMW458744:BMZ458747 BWS458744:BWV458747 CGO458744:CGR458747 CQK458744:CQN458747 DAG458744:DAJ458747 DKC458744:DKF458747 DTY458744:DUB458747 EDU458744:EDX458747 ENQ458744:ENT458747 EXM458744:EXP458747 FHI458744:FHL458747 FRE458744:FRH458747 GBA458744:GBD458747 GKW458744:GKZ458747 GUS458744:GUV458747 HEO458744:HER458747 HOK458744:HON458747 HYG458744:HYJ458747 IIC458744:IIF458747 IRY458744:ISB458747 JBU458744:JBX458747 JLQ458744:JLT458747 JVM458744:JVP458747 KFI458744:KFL458747 KPE458744:KPH458747 KZA458744:KZD458747 LIW458744:LIZ458747 LSS458744:LSV458747 MCO458744:MCR458747 MMK458744:MMN458747 MWG458744:MWJ458747 NGC458744:NGF458747 NPY458744:NQB458747 NZU458744:NZX458747 OJQ458744:OJT458747 OTM458744:OTP458747 PDI458744:PDL458747 PNE458744:PNH458747 PXA458744:PXD458747 QGW458744:QGZ458747 QQS458744:QQV458747 RAO458744:RAR458747 RKK458744:RKN458747 RUG458744:RUJ458747 SEC458744:SEF458747 SNY458744:SOB458747 SXU458744:SXX458747 THQ458744:THT458747 TRM458744:TRP458747 UBI458744:UBL458747 ULE458744:ULH458747 UVA458744:UVD458747 VEW458744:VEZ458747 VOS458744:VOV458747 VYO458744:VYR458747 WIK458744:WIN458747 WSG458744:WSJ458747 FU524280:FX524283 PQ524280:PT524283 ZM524280:ZP524283 AJI524280:AJL524283 ATE524280:ATH524283 BDA524280:BDD524283 BMW524280:BMZ524283 BWS524280:BWV524283 CGO524280:CGR524283 CQK524280:CQN524283 DAG524280:DAJ524283 DKC524280:DKF524283 DTY524280:DUB524283 EDU524280:EDX524283 ENQ524280:ENT524283 EXM524280:EXP524283 FHI524280:FHL524283 FRE524280:FRH524283 GBA524280:GBD524283 GKW524280:GKZ524283 GUS524280:GUV524283 HEO524280:HER524283 HOK524280:HON524283 HYG524280:HYJ524283 IIC524280:IIF524283 IRY524280:ISB524283 JBU524280:JBX524283 JLQ524280:JLT524283 JVM524280:JVP524283 KFI524280:KFL524283 KPE524280:KPH524283 KZA524280:KZD524283 LIW524280:LIZ524283 LSS524280:LSV524283 MCO524280:MCR524283 MMK524280:MMN524283 MWG524280:MWJ524283 NGC524280:NGF524283 NPY524280:NQB524283 NZU524280:NZX524283 OJQ524280:OJT524283 OTM524280:OTP524283 PDI524280:PDL524283 PNE524280:PNH524283 PXA524280:PXD524283 QGW524280:QGZ524283 QQS524280:QQV524283 RAO524280:RAR524283 RKK524280:RKN524283 RUG524280:RUJ524283 SEC524280:SEF524283 SNY524280:SOB524283 SXU524280:SXX524283 THQ524280:THT524283 TRM524280:TRP524283 UBI524280:UBL524283 ULE524280:ULH524283 UVA524280:UVD524283 VEW524280:VEZ524283 VOS524280:VOV524283 VYO524280:VYR524283 WIK524280:WIN524283 WSG524280:WSJ524283 FU589816:FX589819 PQ589816:PT589819 ZM589816:ZP589819 AJI589816:AJL589819 ATE589816:ATH589819 BDA589816:BDD589819 BMW589816:BMZ589819 BWS589816:BWV589819 CGO589816:CGR589819 CQK589816:CQN589819 DAG589816:DAJ589819 DKC589816:DKF589819 DTY589816:DUB589819 EDU589816:EDX589819 ENQ589816:ENT589819 EXM589816:EXP589819 FHI589816:FHL589819 FRE589816:FRH589819 GBA589816:GBD589819 GKW589816:GKZ589819 GUS589816:GUV589819 HEO589816:HER589819 HOK589816:HON589819 HYG589816:HYJ589819 IIC589816:IIF589819 IRY589816:ISB589819 JBU589816:JBX589819 JLQ589816:JLT589819 JVM589816:JVP589819 KFI589816:KFL589819 KPE589816:KPH589819 KZA589816:KZD589819 LIW589816:LIZ589819 LSS589816:LSV589819 MCO589816:MCR589819 MMK589816:MMN589819 MWG589816:MWJ589819 NGC589816:NGF589819 NPY589816:NQB589819 NZU589816:NZX589819 OJQ589816:OJT589819 OTM589816:OTP589819 PDI589816:PDL589819 PNE589816:PNH589819 PXA589816:PXD589819 QGW589816:QGZ589819 QQS589816:QQV589819 RAO589816:RAR589819 RKK589816:RKN589819 RUG589816:RUJ589819 SEC589816:SEF589819 SNY589816:SOB589819 SXU589816:SXX589819 THQ589816:THT589819 TRM589816:TRP589819 UBI589816:UBL589819 ULE589816:ULH589819 UVA589816:UVD589819 VEW589816:VEZ589819 VOS589816:VOV589819 VYO589816:VYR589819 WIK589816:WIN589819 WSG589816:WSJ589819 FU655352:FX655355 PQ655352:PT655355 ZM655352:ZP655355 AJI655352:AJL655355 ATE655352:ATH655355 BDA655352:BDD655355 BMW655352:BMZ655355 BWS655352:BWV655355 CGO655352:CGR655355 CQK655352:CQN655355 DAG655352:DAJ655355 DKC655352:DKF655355 DTY655352:DUB655355 EDU655352:EDX655355 ENQ655352:ENT655355 EXM655352:EXP655355 FHI655352:FHL655355 FRE655352:FRH655355 GBA655352:GBD655355 GKW655352:GKZ655355 GUS655352:GUV655355 HEO655352:HER655355 HOK655352:HON655355 HYG655352:HYJ655355 IIC655352:IIF655355 IRY655352:ISB655355 JBU655352:JBX655355 JLQ655352:JLT655355 JVM655352:JVP655355 KFI655352:KFL655355 KPE655352:KPH655355 KZA655352:KZD655355 LIW655352:LIZ655355 LSS655352:LSV655355 MCO655352:MCR655355 MMK655352:MMN655355 MWG655352:MWJ655355 NGC655352:NGF655355 NPY655352:NQB655355 NZU655352:NZX655355 OJQ655352:OJT655355 OTM655352:OTP655355 PDI655352:PDL655355 PNE655352:PNH655355 PXA655352:PXD655355 QGW655352:QGZ655355 QQS655352:QQV655355 RAO655352:RAR655355 RKK655352:RKN655355 RUG655352:RUJ655355 SEC655352:SEF655355 SNY655352:SOB655355 SXU655352:SXX655355 THQ655352:THT655355 TRM655352:TRP655355 UBI655352:UBL655355 ULE655352:ULH655355 UVA655352:UVD655355 VEW655352:VEZ655355 VOS655352:VOV655355 VYO655352:VYR655355 WIK655352:WIN655355 WSG655352:WSJ655355 FU720888:FX720891 PQ720888:PT720891 ZM720888:ZP720891 AJI720888:AJL720891 ATE720888:ATH720891 BDA720888:BDD720891 BMW720888:BMZ720891 BWS720888:BWV720891 CGO720888:CGR720891 CQK720888:CQN720891 DAG720888:DAJ720891 DKC720888:DKF720891 DTY720888:DUB720891 EDU720888:EDX720891 ENQ720888:ENT720891 EXM720888:EXP720891 FHI720888:FHL720891 FRE720888:FRH720891 GBA720888:GBD720891 GKW720888:GKZ720891 GUS720888:GUV720891 HEO720888:HER720891 HOK720888:HON720891 HYG720888:HYJ720891 IIC720888:IIF720891 IRY720888:ISB720891 JBU720888:JBX720891 JLQ720888:JLT720891 JVM720888:JVP720891 KFI720888:KFL720891 KPE720888:KPH720891 KZA720888:KZD720891 LIW720888:LIZ720891 LSS720888:LSV720891 MCO720888:MCR720891 MMK720888:MMN720891 MWG720888:MWJ720891 NGC720888:NGF720891 NPY720888:NQB720891 NZU720888:NZX720891 OJQ720888:OJT720891 OTM720888:OTP720891 PDI720888:PDL720891 PNE720888:PNH720891 PXA720888:PXD720891 QGW720888:QGZ720891 QQS720888:QQV720891 RAO720888:RAR720891 RKK720888:RKN720891 RUG720888:RUJ720891 SEC720888:SEF720891 SNY720888:SOB720891 SXU720888:SXX720891 THQ720888:THT720891 TRM720888:TRP720891 UBI720888:UBL720891 ULE720888:ULH720891 UVA720888:UVD720891 VEW720888:VEZ720891 VOS720888:VOV720891 VYO720888:VYR720891 WIK720888:WIN720891 WSG720888:WSJ720891 FU786424:FX786427 PQ786424:PT786427 ZM786424:ZP786427 AJI786424:AJL786427 ATE786424:ATH786427 BDA786424:BDD786427 BMW786424:BMZ786427 BWS786424:BWV786427 CGO786424:CGR786427 CQK786424:CQN786427 DAG786424:DAJ786427 DKC786424:DKF786427 DTY786424:DUB786427 EDU786424:EDX786427 ENQ786424:ENT786427 EXM786424:EXP786427 FHI786424:FHL786427 FRE786424:FRH786427 GBA786424:GBD786427 GKW786424:GKZ786427 GUS786424:GUV786427 HEO786424:HER786427 HOK786424:HON786427 HYG786424:HYJ786427 IIC786424:IIF786427 IRY786424:ISB786427 JBU786424:JBX786427 JLQ786424:JLT786427 JVM786424:JVP786427 KFI786424:KFL786427 KPE786424:KPH786427 KZA786424:KZD786427 LIW786424:LIZ786427 LSS786424:LSV786427 MCO786424:MCR786427 MMK786424:MMN786427 MWG786424:MWJ786427 NGC786424:NGF786427 NPY786424:NQB786427 NZU786424:NZX786427 OJQ786424:OJT786427 OTM786424:OTP786427 PDI786424:PDL786427 PNE786424:PNH786427 PXA786424:PXD786427 QGW786424:QGZ786427 QQS786424:QQV786427 RAO786424:RAR786427 RKK786424:RKN786427 RUG786424:RUJ786427 SEC786424:SEF786427 SNY786424:SOB786427 SXU786424:SXX786427 THQ786424:THT786427 TRM786424:TRP786427 UBI786424:UBL786427 ULE786424:ULH786427 UVA786424:UVD786427 VEW786424:VEZ786427 VOS786424:VOV786427 VYO786424:VYR786427 WIK786424:WIN786427 WSG786424:WSJ786427 FU851960:FX851963 PQ851960:PT851963 ZM851960:ZP851963 AJI851960:AJL851963 ATE851960:ATH851963 BDA851960:BDD851963 BMW851960:BMZ851963 BWS851960:BWV851963 CGO851960:CGR851963 CQK851960:CQN851963 DAG851960:DAJ851963 DKC851960:DKF851963 DTY851960:DUB851963 EDU851960:EDX851963 ENQ851960:ENT851963 EXM851960:EXP851963 FHI851960:FHL851963 FRE851960:FRH851963 GBA851960:GBD851963 GKW851960:GKZ851963 GUS851960:GUV851963 HEO851960:HER851963 HOK851960:HON851963 HYG851960:HYJ851963 IIC851960:IIF851963 IRY851960:ISB851963 JBU851960:JBX851963 JLQ851960:JLT851963 JVM851960:JVP851963 KFI851960:KFL851963 KPE851960:KPH851963 KZA851960:KZD851963 LIW851960:LIZ851963 LSS851960:LSV851963 MCO851960:MCR851963 MMK851960:MMN851963 MWG851960:MWJ851963 NGC851960:NGF851963 NPY851960:NQB851963 NZU851960:NZX851963 OJQ851960:OJT851963 OTM851960:OTP851963 PDI851960:PDL851963 PNE851960:PNH851963 PXA851960:PXD851963 QGW851960:QGZ851963 QQS851960:QQV851963 RAO851960:RAR851963 RKK851960:RKN851963 RUG851960:RUJ851963 SEC851960:SEF851963 SNY851960:SOB851963 SXU851960:SXX851963 THQ851960:THT851963 TRM851960:TRP851963 UBI851960:UBL851963 ULE851960:ULH851963 UVA851960:UVD851963 VEW851960:VEZ851963 VOS851960:VOV851963 VYO851960:VYR851963 WIK851960:WIN851963 WSG851960:WSJ851963 FU917496:FX917499 PQ917496:PT917499 ZM917496:ZP917499 AJI917496:AJL917499 ATE917496:ATH917499 BDA917496:BDD917499 BMW917496:BMZ917499 BWS917496:BWV917499 CGO917496:CGR917499 CQK917496:CQN917499 DAG917496:DAJ917499 DKC917496:DKF917499 DTY917496:DUB917499 EDU917496:EDX917499 ENQ917496:ENT917499 EXM917496:EXP917499 FHI917496:FHL917499 FRE917496:FRH917499 GBA917496:GBD917499 GKW917496:GKZ917499 GUS917496:GUV917499 HEO917496:HER917499 HOK917496:HON917499 HYG917496:HYJ917499 IIC917496:IIF917499 IRY917496:ISB917499 JBU917496:JBX917499 JLQ917496:JLT917499 JVM917496:JVP917499 KFI917496:KFL917499 KPE917496:KPH917499 KZA917496:KZD917499 LIW917496:LIZ917499 LSS917496:LSV917499 MCO917496:MCR917499 MMK917496:MMN917499 MWG917496:MWJ917499 NGC917496:NGF917499 NPY917496:NQB917499 NZU917496:NZX917499 OJQ917496:OJT917499 OTM917496:OTP917499 PDI917496:PDL917499 PNE917496:PNH917499 PXA917496:PXD917499 QGW917496:QGZ917499 QQS917496:QQV917499 RAO917496:RAR917499 RKK917496:RKN917499 RUG917496:RUJ917499 SEC917496:SEF917499 SNY917496:SOB917499 SXU917496:SXX917499 THQ917496:THT917499 TRM917496:TRP917499 UBI917496:UBL917499 ULE917496:ULH917499 UVA917496:UVD917499 VEW917496:VEZ917499 VOS917496:VOV917499 VYO917496:VYR917499 WIK917496:WIN917499 WSG917496:WSJ917499 FU983032:FX983035 PQ983032:PT983035 ZM983032:ZP983035 AJI983032:AJL983035 ATE983032:ATH983035 BDA983032:BDD983035 BMW983032:BMZ983035 BWS983032:BWV983035 CGO983032:CGR983035 CQK983032:CQN983035 DAG983032:DAJ983035 DKC983032:DKF983035 DTY983032:DUB983035 EDU983032:EDX983035 ENQ983032:ENT983035 EXM983032:EXP983035 FHI983032:FHL983035 FRE983032:FRH983035 GBA983032:GBD983035 GKW983032:GKZ983035 GUS983032:GUV983035 HEO983032:HER983035 HOK983032:HON983035 HYG983032:HYJ983035 IIC983032:IIF983035 IRY983032:ISB983035 JBU983032:JBX983035 JLQ983032:JLT983035 JVM983032:JVP983035 KFI983032:KFL983035 KPE983032:KPH983035 KZA983032:KZD983035 LIW983032:LIZ983035 LSS983032:LSV983035 MCO983032:MCR983035 MMK983032:MMN983035 MWG983032:MWJ983035 NGC983032:NGF983035 NPY983032:NQB983035 NZU983032:NZX983035 OJQ983032:OJT983035 OTM983032:OTP983035 PDI983032:PDL983035 PNE983032:PNH983035 PXA983032:PXD983035 QGW983032:QGZ983035 QQS983032:QQV983035 RAO983032:RAR983035 RKK983032:RKN983035 RUG983032:RUJ983035 SEC983032:SEF983035 SNY983032:SOB983035 SXU983032:SXX983035 THQ983032:THT983035 TRM983032:TRP983035 UBI983032:UBL983035 ULE983032:ULH983035 UVA983032:UVD983035 VEW983032:VEZ983035 VOS983032:VOV983035 VYO983032:VYR983035 WIK983032:WIN983035 WSG983032:WSJ983035 FP65522:FS65522 PL65522:PO65522 ZH65522:ZK65522 AJD65522:AJG65522 ASZ65522:ATC65522 BCV65522:BCY65522 BMR65522:BMU65522 BWN65522:BWQ65522 CGJ65522:CGM65522 CQF65522:CQI65522 DAB65522:DAE65522 DJX65522:DKA65522 DTT65522:DTW65522 EDP65522:EDS65522 ENL65522:ENO65522 EXH65522:EXK65522 FHD65522:FHG65522 FQZ65522:FRC65522 GAV65522:GAY65522 GKR65522:GKU65522 GUN65522:GUQ65522 HEJ65522:HEM65522 HOF65522:HOI65522 HYB65522:HYE65522 IHX65522:IIA65522 IRT65522:IRW65522 JBP65522:JBS65522 JLL65522:JLO65522 JVH65522:JVK65522 KFD65522:KFG65522 KOZ65522:KPC65522 KYV65522:KYY65522 LIR65522:LIU65522 LSN65522:LSQ65522 MCJ65522:MCM65522 MMF65522:MMI65522 MWB65522:MWE65522 NFX65522:NGA65522 NPT65522:NPW65522 NZP65522:NZS65522 OJL65522:OJO65522 OTH65522:OTK65522 PDD65522:PDG65522 PMZ65522:PNC65522 PWV65522:PWY65522 QGR65522:QGU65522 QQN65522:QQQ65522 RAJ65522:RAM65522 RKF65522:RKI65522 RUB65522:RUE65522 SDX65522:SEA65522 SNT65522:SNW65522 SXP65522:SXS65522 THL65522:THO65522 TRH65522:TRK65522 UBD65522:UBG65522 UKZ65522:ULC65522 UUV65522:UUY65522 VER65522:VEU65522 VON65522:VOQ65522 VYJ65522:VYM65522 WIF65522:WII65522 WSB65522:WSE65522 FP131058:FS131058 PL131058:PO131058 ZH131058:ZK131058 AJD131058:AJG131058 ASZ131058:ATC131058 BCV131058:BCY131058 BMR131058:BMU131058 BWN131058:BWQ131058 CGJ131058:CGM131058 CQF131058:CQI131058 DAB131058:DAE131058 DJX131058:DKA131058 DTT131058:DTW131058 EDP131058:EDS131058 ENL131058:ENO131058 EXH131058:EXK131058 FHD131058:FHG131058 FQZ131058:FRC131058 GAV131058:GAY131058 GKR131058:GKU131058 GUN131058:GUQ131058 HEJ131058:HEM131058 HOF131058:HOI131058 HYB131058:HYE131058 IHX131058:IIA131058 IRT131058:IRW131058 JBP131058:JBS131058 JLL131058:JLO131058 JVH131058:JVK131058 KFD131058:KFG131058 KOZ131058:KPC131058 KYV131058:KYY131058 LIR131058:LIU131058 LSN131058:LSQ131058 MCJ131058:MCM131058 MMF131058:MMI131058 MWB131058:MWE131058 NFX131058:NGA131058 NPT131058:NPW131058 NZP131058:NZS131058 OJL131058:OJO131058 OTH131058:OTK131058 PDD131058:PDG131058 PMZ131058:PNC131058 PWV131058:PWY131058 QGR131058:QGU131058 QQN131058:QQQ131058 RAJ131058:RAM131058 RKF131058:RKI131058 RUB131058:RUE131058 SDX131058:SEA131058 SNT131058:SNW131058 SXP131058:SXS131058 THL131058:THO131058 TRH131058:TRK131058 UBD131058:UBG131058 UKZ131058:ULC131058 UUV131058:UUY131058 VER131058:VEU131058 VON131058:VOQ131058 VYJ131058:VYM131058 WIF131058:WII131058 WSB131058:WSE131058 FP196594:FS196594 PL196594:PO196594 ZH196594:ZK196594 AJD196594:AJG196594 ASZ196594:ATC196594 BCV196594:BCY196594 BMR196594:BMU196594 BWN196594:BWQ196594 CGJ196594:CGM196594 CQF196594:CQI196594 DAB196594:DAE196594 DJX196594:DKA196594 DTT196594:DTW196594 EDP196594:EDS196594 ENL196594:ENO196594 EXH196594:EXK196594 FHD196594:FHG196594 FQZ196594:FRC196594 GAV196594:GAY196594 GKR196594:GKU196594 GUN196594:GUQ196594 HEJ196594:HEM196594 HOF196594:HOI196594 HYB196594:HYE196594 IHX196594:IIA196594 IRT196594:IRW196594 JBP196594:JBS196594 JLL196594:JLO196594 JVH196594:JVK196594 KFD196594:KFG196594 KOZ196594:KPC196594 KYV196594:KYY196594 LIR196594:LIU196594 LSN196594:LSQ196594 MCJ196594:MCM196594 MMF196594:MMI196594 MWB196594:MWE196594 NFX196594:NGA196594 NPT196594:NPW196594 NZP196594:NZS196594 OJL196594:OJO196594 OTH196594:OTK196594 PDD196594:PDG196594 PMZ196594:PNC196594 PWV196594:PWY196594 QGR196594:QGU196594 QQN196594:QQQ196594 RAJ196594:RAM196594 RKF196594:RKI196594 RUB196594:RUE196594 SDX196594:SEA196594 SNT196594:SNW196594 SXP196594:SXS196594 THL196594:THO196594 TRH196594:TRK196594 UBD196594:UBG196594 UKZ196594:ULC196594 UUV196594:UUY196594 VER196594:VEU196594 VON196594:VOQ196594 VYJ196594:VYM196594 WIF196594:WII196594 WSB196594:WSE196594 FP262130:FS262130 PL262130:PO262130 ZH262130:ZK262130 AJD262130:AJG262130 ASZ262130:ATC262130 BCV262130:BCY262130 BMR262130:BMU262130 BWN262130:BWQ262130 CGJ262130:CGM262130 CQF262130:CQI262130 DAB262130:DAE262130 DJX262130:DKA262130 DTT262130:DTW262130 EDP262130:EDS262130 ENL262130:ENO262130 EXH262130:EXK262130 FHD262130:FHG262130 FQZ262130:FRC262130 GAV262130:GAY262130 GKR262130:GKU262130 GUN262130:GUQ262130 HEJ262130:HEM262130 HOF262130:HOI262130 HYB262130:HYE262130 IHX262130:IIA262130 IRT262130:IRW262130 JBP262130:JBS262130 JLL262130:JLO262130 JVH262130:JVK262130 KFD262130:KFG262130 KOZ262130:KPC262130 KYV262130:KYY262130 LIR262130:LIU262130 LSN262130:LSQ262130 MCJ262130:MCM262130 MMF262130:MMI262130 MWB262130:MWE262130 NFX262130:NGA262130 NPT262130:NPW262130 NZP262130:NZS262130 OJL262130:OJO262130 OTH262130:OTK262130 PDD262130:PDG262130 PMZ262130:PNC262130 PWV262130:PWY262130 QGR262130:QGU262130 QQN262130:QQQ262130 RAJ262130:RAM262130 RKF262130:RKI262130 RUB262130:RUE262130 SDX262130:SEA262130 SNT262130:SNW262130 SXP262130:SXS262130 THL262130:THO262130 TRH262130:TRK262130 UBD262130:UBG262130 UKZ262130:ULC262130 UUV262130:UUY262130 VER262130:VEU262130 VON262130:VOQ262130 VYJ262130:VYM262130 WIF262130:WII262130 WSB262130:WSE262130 FP327666:FS327666 PL327666:PO327666 ZH327666:ZK327666 AJD327666:AJG327666 ASZ327666:ATC327666 BCV327666:BCY327666 BMR327666:BMU327666 BWN327666:BWQ327666 CGJ327666:CGM327666 CQF327666:CQI327666 DAB327666:DAE327666 DJX327666:DKA327666 DTT327666:DTW327666 EDP327666:EDS327666 ENL327666:ENO327666 EXH327666:EXK327666 FHD327666:FHG327666 FQZ327666:FRC327666 GAV327666:GAY327666 GKR327666:GKU327666 GUN327666:GUQ327666 HEJ327666:HEM327666 HOF327666:HOI327666 HYB327666:HYE327666 IHX327666:IIA327666 IRT327666:IRW327666 JBP327666:JBS327666 JLL327666:JLO327666 JVH327666:JVK327666 KFD327666:KFG327666 KOZ327666:KPC327666 KYV327666:KYY327666 LIR327666:LIU327666 LSN327666:LSQ327666 MCJ327666:MCM327666 MMF327666:MMI327666 MWB327666:MWE327666 NFX327666:NGA327666 NPT327666:NPW327666 NZP327666:NZS327666 OJL327666:OJO327666 OTH327666:OTK327666 PDD327666:PDG327666 PMZ327666:PNC327666 PWV327666:PWY327666 QGR327666:QGU327666 QQN327666:QQQ327666 RAJ327666:RAM327666 RKF327666:RKI327666 RUB327666:RUE327666 SDX327666:SEA327666 SNT327666:SNW327666 SXP327666:SXS327666 THL327666:THO327666 TRH327666:TRK327666 UBD327666:UBG327666 UKZ327666:ULC327666 UUV327666:UUY327666 VER327666:VEU327666 VON327666:VOQ327666 VYJ327666:VYM327666 WIF327666:WII327666 WSB327666:WSE327666 FP393202:FS393202 PL393202:PO393202 ZH393202:ZK393202 AJD393202:AJG393202 ASZ393202:ATC393202 BCV393202:BCY393202 BMR393202:BMU393202 BWN393202:BWQ393202 CGJ393202:CGM393202 CQF393202:CQI393202 DAB393202:DAE393202 DJX393202:DKA393202 DTT393202:DTW393202 EDP393202:EDS393202 ENL393202:ENO393202 EXH393202:EXK393202 FHD393202:FHG393202 FQZ393202:FRC393202 GAV393202:GAY393202 GKR393202:GKU393202 GUN393202:GUQ393202 HEJ393202:HEM393202 HOF393202:HOI393202 HYB393202:HYE393202 IHX393202:IIA393202 IRT393202:IRW393202 JBP393202:JBS393202 JLL393202:JLO393202 JVH393202:JVK393202 KFD393202:KFG393202 KOZ393202:KPC393202 KYV393202:KYY393202 LIR393202:LIU393202 LSN393202:LSQ393202 MCJ393202:MCM393202 MMF393202:MMI393202 MWB393202:MWE393202 NFX393202:NGA393202 NPT393202:NPW393202 NZP393202:NZS393202 OJL393202:OJO393202 OTH393202:OTK393202 PDD393202:PDG393202 PMZ393202:PNC393202 PWV393202:PWY393202 QGR393202:QGU393202 QQN393202:QQQ393202 RAJ393202:RAM393202 RKF393202:RKI393202 RUB393202:RUE393202 SDX393202:SEA393202 SNT393202:SNW393202 SXP393202:SXS393202 THL393202:THO393202 TRH393202:TRK393202 UBD393202:UBG393202 UKZ393202:ULC393202 UUV393202:UUY393202 VER393202:VEU393202 VON393202:VOQ393202 VYJ393202:VYM393202 WIF393202:WII393202 WSB393202:WSE393202 FP458738:FS458738 PL458738:PO458738 ZH458738:ZK458738 AJD458738:AJG458738 ASZ458738:ATC458738 BCV458738:BCY458738 BMR458738:BMU458738 BWN458738:BWQ458738 CGJ458738:CGM458738 CQF458738:CQI458738 DAB458738:DAE458738 DJX458738:DKA458738 DTT458738:DTW458738 EDP458738:EDS458738 ENL458738:ENO458738 EXH458738:EXK458738 FHD458738:FHG458738 FQZ458738:FRC458738 GAV458738:GAY458738 GKR458738:GKU458738 GUN458738:GUQ458738 HEJ458738:HEM458738 HOF458738:HOI458738 HYB458738:HYE458738 IHX458738:IIA458738 IRT458738:IRW458738 JBP458738:JBS458738 JLL458738:JLO458738 JVH458738:JVK458738 KFD458738:KFG458738 KOZ458738:KPC458738 KYV458738:KYY458738 LIR458738:LIU458738 LSN458738:LSQ458738 MCJ458738:MCM458738 MMF458738:MMI458738 MWB458738:MWE458738 NFX458738:NGA458738 NPT458738:NPW458738 NZP458738:NZS458738 OJL458738:OJO458738 OTH458738:OTK458738 PDD458738:PDG458738 PMZ458738:PNC458738 PWV458738:PWY458738 QGR458738:QGU458738 QQN458738:QQQ458738 RAJ458738:RAM458738 RKF458738:RKI458738 RUB458738:RUE458738 SDX458738:SEA458738 SNT458738:SNW458738 SXP458738:SXS458738 THL458738:THO458738 TRH458738:TRK458738 UBD458738:UBG458738 UKZ458738:ULC458738 UUV458738:UUY458738 VER458738:VEU458738 VON458738:VOQ458738 VYJ458738:VYM458738 WIF458738:WII458738 WSB458738:WSE458738 FP524274:FS524274 PL524274:PO524274 ZH524274:ZK524274 AJD524274:AJG524274 ASZ524274:ATC524274 BCV524274:BCY524274 BMR524274:BMU524274 BWN524274:BWQ524274 CGJ524274:CGM524274 CQF524274:CQI524274 DAB524274:DAE524274 DJX524274:DKA524274 DTT524274:DTW524274 EDP524274:EDS524274 ENL524274:ENO524274 EXH524274:EXK524274 FHD524274:FHG524274 FQZ524274:FRC524274 GAV524274:GAY524274 GKR524274:GKU524274 GUN524274:GUQ524274 HEJ524274:HEM524274 HOF524274:HOI524274 HYB524274:HYE524274 IHX524274:IIA524274 IRT524274:IRW524274 JBP524274:JBS524274 JLL524274:JLO524274 JVH524274:JVK524274 KFD524274:KFG524274 KOZ524274:KPC524274 KYV524274:KYY524274 LIR524274:LIU524274 LSN524274:LSQ524274 MCJ524274:MCM524274 MMF524274:MMI524274 MWB524274:MWE524274 NFX524274:NGA524274 NPT524274:NPW524274 NZP524274:NZS524274 OJL524274:OJO524274 OTH524274:OTK524274 PDD524274:PDG524274 PMZ524274:PNC524274 PWV524274:PWY524274 QGR524274:QGU524274 QQN524274:QQQ524274 RAJ524274:RAM524274 RKF524274:RKI524274 RUB524274:RUE524274 SDX524274:SEA524274 SNT524274:SNW524274 SXP524274:SXS524274 THL524274:THO524274 TRH524274:TRK524274 UBD524274:UBG524274 UKZ524274:ULC524274 UUV524274:UUY524274 VER524274:VEU524274 VON524274:VOQ524274 VYJ524274:VYM524274 WIF524274:WII524274 WSB524274:WSE524274 FP589810:FS589810 PL589810:PO589810 ZH589810:ZK589810 AJD589810:AJG589810 ASZ589810:ATC589810 BCV589810:BCY589810 BMR589810:BMU589810 BWN589810:BWQ589810 CGJ589810:CGM589810 CQF589810:CQI589810 DAB589810:DAE589810 DJX589810:DKA589810 DTT589810:DTW589810 EDP589810:EDS589810 ENL589810:ENO589810 EXH589810:EXK589810 FHD589810:FHG589810 FQZ589810:FRC589810 GAV589810:GAY589810 GKR589810:GKU589810 GUN589810:GUQ589810 HEJ589810:HEM589810 HOF589810:HOI589810 HYB589810:HYE589810 IHX589810:IIA589810 IRT589810:IRW589810 JBP589810:JBS589810 JLL589810:JLO589810 JVH589810:JVK589810 KFD589810:KFG589810 KOZ589810:KPC589810 KYV589810:KYY589810 LIR589810:LIU589810 LSN589810:LSQ589810 MCJ589810:MCM589810 MMF589810:MMI589810 MWB589810:MWE589810 NFX589810:NGA589810 NPT589810:NPW589810 NZP589810:NZS589810 OJL589810:OJO589810 OTH589810:OTK589810 PDD589810:PDG589810 PMZ589810:PNC589810 PWV589810:PWY589810 QGR589810:QGU589810 QQN589810:QQQ589810 RAJ589810:RAM589810 RKF589810:RKI589810 RUB589810:RUE589810 SDX589810:SEA589810 SNT589810:SNW589810 SXP589810:SXS589810 THL589810:THO589810 TRH589810:TRK589810 UBD589810:UBG589810 UKZ589810:ULC589810 UUV589810:UUY589810 VER589810:VEU589810 VON589810:VOQ589810 VYJ589810:VYM589810 WIF589810:WII589810 WSB589810:WSE589810 FP655346:FS655346 PL655346:PO655346 ZH655346:ZK655346 AJD655346:AJG655346 ASZ655346:ATC655346 BCV655346:BCY655346 BMR655346:BMU655346 BWN655346:BWQ655346 CGJ655346:CGM655346 CQF655346:CQI655346 DAB655346:DAE655346 DJX655346:DKA655346 DTT655346:DTW655346 EDP655346:EDS655346 ENL655346:ENO655346 EXH655346:EXK655346 FHD655346:FHG655346 FQZ655346:FRC655346 GAV655346:GAY655346 GKR655346:GKU655346 GUN655346:GUQ655346 HEJ655346:HEM655346 HOF655346:HOI655346 HYB655346:HYE655346 IHX655346:IIA655346 IRT655346:IRW655346 JBP655346:JBS655346 JLL655346:JLO655346 JVH655346:JVK655346 KFD655346:KFG655346 KOZ655346:KPC655346 KYV655346:KYY655346 LIR655346:LIU655346 LSN655346:LSQ655346 MCJ655346:MCM655346 MMF655346:MMI655346 MWB655346:MWE655346 NFX655346:NGA655346 NPT655346:NPW655346 NZP655346:NZS655346 OJL655346:OJO655346 OTH655346:OTK655346 PDD655346:PDG655346 PMZ655346:PNC655346 PWV655346:PWY655346 QGR655346:QGU655346 QQN655346:QQQ655346 RAJ655346:RAM655346 RKF655346:RKI655346 RUB655346:RUE655346 SDX655346:SEA655346 SNT655346:SNW655346 SXP655346:SXS655346 THL655346:THO655346 TRH655346:TRK655346 UBD655346:UBG655346 UKZ655346:ULC655346 UUV655346:UUY655346 VER655346:VEU655346 VON655346:VOQ655346 VYJ655346:VYM655346 WIF655346:WII655346 WSB655346:WSE655346 FP720882:FS720882 PL720882:PO720882 ZH720882:ZK720882 AJD720882:AJG720882 ASZ720882:ATC720882 BCV720882:BCY720882 BMR720882:BMU720882 BWN720882:BWQ720882 CGJ720882:CGM720882 CQF720882:CQI720882 DAB720882:DAE720882 DJX720882:DKA720882 DTT720882:DTW720882 EDP720882:EDS720882 ENL720882:ENO720882 EXH720882:EXK720882 FHD720882:FHG720882 FQZ720882:FRC720882 GAV720882:GAY720882 GKR720882:GKU720882 GUN720882:GUQ720882 HEJ720882:HEM720882 HOF720882:HOI720882 HYB720882:HYE720882 IHX720882:IIA720882 IRT720882:IRW720882 JBP720882:JBS720882 JLL720882:JLO720882 JVH720882:JVK720882 KFD720882:KFG720882 KOZ720882:KPC720882 KYV720882:KYY720882 LIR720882:LIU720882 LSN720882:LSQ720882 MCJ720882:MCM720882 MMF720882:MMI720882 MWB720882:MWE720882 NFX720882:NGA720882 NPT720882:NPW720882 NZP720882:NZS720882 OJL720882:OJO720882 OTH720882:OTK720882 PDD720882:PDG720882 PMZ720882:PNC720882 PWV720882:PWY720882 QGR720882:QGU720882 QQN720882:QQQ720882 RAJ720882:RAM720882 RKF720882:RKI720882 RUB720882:RUE720882 SDX720882:SEA720882 SNT720882:SNW720882 SXP720882:SXS720882 THL720882:THO720882 TRH720882:TRK720882 UBD720882:UBG720882 UKZ720882:ULC720882 UUV720882:UUY720882 VER720882:VEU720882 VON720882:VOQ720882 VYJ720882:VYM720882 WIF720882:WII720882 WSB720882:WSE720882 FP786418:FS786418 PL786418:PO786418 ZH786418:ZK786418 AJD786418:AJG786418 ASZ786418:ATC786418 BCV786418:BCY786418 BMR786418:BMU786418 BWN786418:BWQ786418 CGJ786418:CGM786418 CQF786418:CQI786418 DAB786418:DAE786418 DJX786418:DKA786418 DTT786418:DTW786418 EDP786418:EDS786418 ENL786418:ENO786418 EXH786418:EXK786418 FHD786418:FHG786418 FQZ786418:FRC786418 GAV786418:GAY786418 GKR786418:GKU786418 GUN786418:GUQ786418 HEJ786418:HEM786418 HOF786418:HOI786418 HYB786418:HYE786418 IHX786418:IIA786418 IRT786418:IRW786418 JBP786418:JBS786418 JLL786418:JLO786418 JVH786418:JVK786418 KFD786418:KFG786418 KOZ786418:KPC786418 KYV786418:KYY786418 LIR786418:LIU786418 LSN786418:LSQ786418 MCJ786418:MCM786418 MMF786418:MMI786418 MWB786418:MWE786418 NFX786418:NGA786418 NPT786418:NPW786418 NZP786418:NZS786418 OJL786418:OJO786418 OTH786418:OTK786418 PDD786418:PDG786418 PMZ786418:PNC786418 PWV786418:PWY786418 QGR786418:QGU786418 QQN786418:QQQ786418 RAJ786418:RAM786418 RKF786418:RKI786418 RUB786418:RUE786418 SDX786418:SEA786418 SNT786418:SNW786418 SXP786418:SXS786418 THL786418:THO786418 TRH786418:TRK786418 UBD786418:UBG786418 UKZ786418:ULC786418 UUV786418:UUY786418 VER786418:VEU786418 VON786418:VOQ786418 VYJ786418:VYM786418 WIF786418:WII786418 WSB786418:WSE786418 FP851954:FS851954 PL851954:PO851954 ZH851954:ZK851954 AJD851954:AJG851954 ASZ851954:ATC851954 BCV851954:BCY851954 BMR851954:BMU851954 BWN851954:BWQ851954 CGJ851954:CGM851954 CQF851954:CQI851954 DAB851954:DAE851954 DJX851954:DKA851954 DTT851954:DTW851954 EDP851954:EDS851954 ENL851954:ENO851954 EXH851954:EXK851954 FHD851954:FHG851954 FQZ851954:FRC851954 GAV851954:GAY851954 GKR851954:GKU851954 GUN851954:GUQ851954 HEJ851954:HEM851954 HOF851954:HOI851954 HYB851954:HYE851954 IHX851954:IIA851954 IRT851954:IRW851954 JBP851954:JBS851954 JLL851954:JLO851954 JVH851954:JVK851954 KFD851954:KFG851954 KOZ851954:KPC851954 KYV851954:KYY851954 LIR851954:LIU851954 LSN851954:LSQ851954 MCJ851954:MCM851954 MMF851954:MMI851954 MWB851954:MWE851954 NFX851954:NGA851954 NPT851954:NPW851954 NZP851954:NZS851954 OJL851954:OJO851954 OTH851954:OTK851954 PDD851954:PDG851954 PMZ851954:PNC851954 PWV851954:PWY851954 QGR851954:QGU851954 QQN851954:QQQ851954 RAJ851954:RAM851954 RKF851954:RKI851954 RUB851954:RUE851954 SDX851954:SEA851954 SNT851954:SNW851954 SXP851954:SXS851954 THL851954:THO851954 TRH851954:TRK851954 UBD851954:UBG851954 UKZ851954:ULC851954 UUV851954:UUY851954 VER851954:VEU851954 VON851954:VOQ851954 VYJ851954:VYM851954 WIF851954:WII851954 WSB851954:WSE851954 FP917490:FS917490 PL917490:PO917490 ZH917490:ZK917490 AJD917490:AJG917490 ASZ917490:ATC917490 BCV917490:BCY917490 BMR917490:BMU917490 BWN917490:BWQ917490 CGJ917490:CGM917490 CQF917490:CQI917490 DAB917490:DAE917490 DJX917490:DKA917490 DTT917490:DTW917490 EDP917490:EDS917490 ENL917490:ENO917490 EXH917490:EXK917490 FHD917490:FHG917490 FQZ917490:FRC917490 GAV917490:GAY917490 GKR917490:GKU917490 GUN917490:GUQ917490 HEJ917490:HEM917490 HOF917490:HOI917490 HYB917490:HYE917490 IHX917490:IIA917490 IRT917490:IRW917490 JBP917490:JBS917490 JLL917490:JLO917490 JVH917490:JVK917490 KFD917490:KFG917490 KOZ917490:KPC917490 KYV917490:KYY917490 LIR917490:LIU917490 LSN917490:LSQ917490 MCJ917490:MCM917490 MMF917490:MMI917490 MWB917490:MWE917490 NFX917490:NGA917490 NPT917490:NPW917490 NZP917490:NZS917490 OJL917490:OJO917490 OTH917490:OTK917490 PDD917490:PDG917490 PMZ917490:PNC917490 PWV917490:PWY917490 QGR917490:QGU917490 QQN917490:QQQ917490 RAJ917490:RAM917490 RKF917490:RKI917490 RUB917490:RUE917490 SDX917490:SEA917490 SNT917490:SNW917490 SXP917490:SXS917490 THL917490:THO917490 TRH917490:TRK917490 UBD917490:UBG917490 UKZ917490:ULC917490 UUV917490:UUY917490 VER917490:VEU917490 VON917490:VOQ917490 VYJ917490:VYM917490 WIF917490:WII917490 WSB917490:WSE917490 FP983026:FS983026 PL983026:PO983026 ZH983026:ZK983026 AJD983026:AJG983026 ASZ983026:ATC983026 BCV983026:BCY983026 BMR983026:BMU983026 BWN983026:BWQ983026 CGJ983026:CGM983026 CQF983026:CQI983026 DAB983026:DAE983026 DJX983026:DKA983026 DTT983026:DTW983026 EDP983026:EDS983026 ENL983026:ENO983026 EXH983026:EXK983026 FHD983026:FHG983026 FQZ983026:FRC983026 GAV983026:GAY983026 GKR983026:GKU983026 GUN983026:GUQ983026 HEJ983026:HEM983026 HOF983026:HOI983026 HYB983026:HYE983026 IHX983026:IIA983026 IRT983026:IRW983026 JBP983026:JBS983026 JLL983026:JLO983026 JVH983026:JVK983026 KFD983026:KFG983026 KOZ983026:KPC983026 KYV983026:KYY983026 LIR983026:LIU983026 LSN983026:LSQ983026 MCJ983026:MCM983026 MMF983026:MMI983026 MWB983026:MWE983026 NFX983026:NGA983026 NPT983026:NPW983026 NZP983026:NZS983026 OJL983026:OJO983026 OTH983026:OTK983026 PDD983026:PDG983026 PMZ983026:PNC983026 PWV983026:PWY983026 QGR983026:QGU983026 QQN983026:QQQ983026 RAJ983026:RAM983026 RKF983026:RKI983026 RUB983026:RUE983026 SDX983026:SEA983026 SNT983026:SNW983026 SXP983026:SXS983026 THL983026:THO983026 TRH983026:TRK983026 UBD983026:UBG983026 UKZ983026:ULC983026 UUV983026:UUY983026 VER983026:VEU983026 VON983026:VOQ983026 VYJ983026:VYM983026 WIF983026:WII983026 WSB983026:WSE983026 FK983025:FN983025 PG983025:PJ983025 ZC983025:ZF983025 AIY983025:AJB983025 ASU983025:ASX983025 BCQ983025:BCT983025 BMM983025:BMP983025 BWI983025:BWL983025 CGE983025:CGH983025 CQA983025:CQD983025 CZW983025:CZZ983025 DJS983025:DJV983025 DTO983025:DTR983025 EDK983025:EDN983025 ENG983025:ENJ983025 EXC983025:EXF983025 FGY983025:FHB983025 FQU983025:FQX983025 GAQ983025:GAT983025 GKM983025:GKP983025 GUI983025:GUL983025 HEE983025:HEH983025 HOA983025:HOD983025 HXW983025:HXZ983025 IHS983025:IHV983025 IRO983025:IRR983025 JBK983025:JBN983025 JLG983025:JLJ983025 JVC983025:JVF983025 KEY983025:KFB983025 KOU983025:KOX983025 KYQ983025:KYT983025 LIM983025:LIP983025 LSI983025:LSL983025 MCE983025:MCH983025 MMA983025:MMD983025 MVW983025:MVZ983025 NFS983025:NFV983025 NPO983025:NPR983025 NZK983025:NZN983025 OJG983025:OJJ983025 OTC983025:OTF983025 PCY983025:PDB983025 PMU983025:PMX983025 PWQ983025:PWT983025 QGM983025:QGP983025 QQI983025:QQL983025 RAE983025:RAH983025 RKA983025:RKD983025 RTW983025:RTZ983025 SDS983025:SDV983025 SNO983025:SNR983025 SXK983025:SXN983025 THG983025:THJ983025 TRC983025:TRF983025 UAY983025:UBB983025 UKU983025:UKX983025 UUQ983025:UUT983025 VEM983025:VEP983025 VOI983025:VOL983025 VYE983025:VYH983025 WIA983025:WID983025 WRW983025:WRZ983025 FK65521:FN65521 PG65521:PJ65521 ZC65521:ZF65521 AIY65521:AJB65521 ASU65521:ASX65521 BCQ65521:BCT65521 BMM65521:BMP65521 BWI65521:BWL65521 CGE65521:CGH65521 CQA65521:CQD65521 CZW65521:CZZ65521 DJS65521:DJV65521 DTO65521:DTR65521 EDK65521:EDN65521 ENG65521:ENJ65521 EXC65521:EXF65521 FGY65521:FHB65521 FQU65521:FQX65521 GAQ65521:GAT65521 GKM65521:GKP65521 GUI65521:GUL65521 HEE65521:HEH65521 HOA65521:HOD65521 HXW65521:HXZ65521 IHS65521:IHV65521 IRO65521:IRR65521 JBK65521:JBN65521 JLG65521:JLJ65521 JVC65521:JVF65521 KEY65521:KFB65521 KOU65521:KOX65521 KYQ65521:KYT65521 LIM65521:LIP65521 LSI65521:LSL65521 MCE65521:MCH65521 MMA65521:MMD65521 MVW65521:MVZ65521 NFS65521:NFV65521 NPO65521:NPR65521 NZK65521:NZN65521 OJG65521:OJJ65521 OTC65521:OTF65521 PCY65521:PDB65521 PMU65521:PMX65521 PWQ65521:PWT65521 QGM65521:QGP65521 QQI65521:QQL65521 RAE65521:RAH65521 RKA65521:RKD65521 RTW65521:RTZ65521 SDS65521:SDV65521 SNO65521:SNR65521 SXK65521:SXN65521 THG65521:THJ65521 TRC65521:TRF65521 UAY65521:UBB65521 UKU65521:UKX65521 UUQ65521:UUT65521 VEM65521:VEP65521 VOI65521:VOL65521 VYE65521:VYH65521 WIA65521:WID65521 WRW65521:WRZ65521 FK131057:FN131057 PG131057:PJ131057 ZC131057:ZF131057 AIY131057:AJB131057 ASU131057:ASX131057 BCQ131057:BCT131057 BMM131057:BMP131057 BWI131057:BWL131057 CGE131057:CGH131057 CQA131057:CQD131057 CZW131057:CZZ131057 DJS131057:DJV131057 DTO131057:DTR131057 EDK131057:EDN131057 ENG131057:ENJ131057 EXC131057:EXF131057 FGY131057:FHB131057 FQU131057:FQX131057 GAQ131057:GAT131057 GKM131057:GKP131057 GUI131057:GUL131057 HEE131057:HEH131057 HOA131057:HOD131057 HXW131057:HXZ131057 IHS131057:IHV131057 IRO131057:IRR131057 JBK131057:JBN131057 JLG131057:JLJ131057 JVC131057:JVF131057 KEY131057:KFB131057 KOU131057:KOX131057 KYQ131057:KYT131057 LIM131057:LIP131057 LSI131057:LSL131057 MCE131057:MCH131057 MMA131057:MMD131057 MVW131057:MVZ131057 NFS131057:NFV131057 NPO131057:NPR131057 NZK131057:NZN131057 OJG131057:OJJ131057 OTC131057:OTF131057 PCY131057:PDB131057 PMU131057:PMX131057 PWQ131057:PWT131057 QGM131057:QGP131057 QQI131057:QQL131057 RAE131057:RAH131057 RKA131057:RKD131057 RTW131057:RTZ131057 SDS131057:SDV131057 SNO131057:SNR131057 SXK131057:SXN131057 THG131057:THJ131057 TRC131057:TRF131057 UAY131057:UBB131057 UKU131057:UKX131057 UUQ131057:UUT131057 VEM131057:VEP131057 VOI131057:VOL131057 VYE131057:VYH131057 WIA131057:WID131057 WRW131057:WRZ131057 FK196593:FN196593 PG196593:PJ196593 ZC196593:ZF196593 AIY196593:AJB196593 ASU196593:ASX196593 BCQ196593:BCT196593 BMM196593:BMP196593 BWI196593:BWL196593 CGE196593:CGH196593 CQA196593:CQD196593 CZW196593:CZZ196593 DJS196593:DJV196593 DTO196593:DTR196593 EDK196593:EDN196593 ENG196593:ENJ196593 EXC196593:EXF196593 FGY196593:FHB196593 FQU196593:FQX196593 GAQ196593:GAT196593 GKM196593:GKP196593 GUI196593:GUL196593 HEE196593:HEH196593 HOA196593:HOD196593 HXW196593:HXZ196593 IHS196593:IHV196593 IRO196593:IRR196593 JBK196593:JBN196593 JLG196593:JLJ196593 JVC196593:JVF196593 KEY196593:KFB196593 KOU196593:KOX196593 KYQ196593:KYT196593 LIM196593:LIP196593 LSI196593:LSL196593 MCE196593:MCH196593 MMA196593:MMD196593 MVW196593:MVZ196593 NFS196593:NFV196593 NPO196593:NPR196593 NZK196593:NZN196593 OJG196593:OJJ196593 OTC196593:OTF196593 PCY196593:PDB196593 PMU196593:PMX196593 PWQ196593:PWT196593 QGM196593:QGP196593 QQI196593:QQL196593 RAE196593:RAH196593 RKA196593:RKD196593 RTW196593:RTZ196593 SDS196593:SDV196593 SNO196593:SNR196593 SXK196593:SXN196593 THG196593:THJ196593 TRC196593:TRF196593 UAY196593:UBB196593 UKU196593:UKX196593 UUQ196593:UUT196593 VEM196593:VEP196593 VOI196593:VOL196593 VYE196593:VYH196593 WIA196593:WID196593 WRW196593:WRZ196593 FK262129:FN262129 PG262129:PJ262129 ZC262129:ZF262129 AIY262129:AJB262129 ASU262129:ASX262129 BCQ262129:BCT262129 BMM262129:BMP262129 BWI262129:BWL262129 CGE262129:CGH262129 CQA262129:CQD262129 CZW262129:CZZ262129 DJS262129:DJV262129 DTO262129:DTR262129 EDK262129:EDN262129 ENG262129:ENJ262129 EXC262129:EXF262129 FGY262129:FHB262129 FQU262129:FQX262129 GAQ262129:GAT262129 GKM262129:GKP262129 GUI262129:GUL262129 HEE262129:HEH262129 HOA262129:HOD262129 HXW262129:HXZ262129 IHS262129:IHV262129 IRO262129:IRR262129 JBK262129:JBN262129 JLG262129:JLJ262129 JVC262129:JVF262129 KEY262129:KFB262129 KOU262129:KOX262129 KYQ262129:KYT262129 LIM262129:LIP262129 LSI262129:LSL262129 MCE262129:MCH262129 MMA262129:MMD262129 MVW262129:MVZ262129 NFS262129:NFV262129 NPO262129:NPR262129 NZK262129:NZN262129 OJG262129:OJJ262129 OTC262129:OTF262129 PCY262129:PDB262129 PMU262129:PMX262129 PWQ262129:PWT262129 QGM262129:QGP262129 QQI262129:QQL262129 RAE262129:RAH262129 RKA262129:RKD262129 RTW262129:RTZ262129 SDS262129:SDV262129 SNO262129:SNR262129 SXK262129:SXN262129 THG262129:THJ262129 TRC262129:TRF262129 UAY262129:UBB262129 UKU262129:UKX262129 UUQ262129:UUT262129 VEM262129:VEP262129 VOI262129:VOL262129 VYE262129:VYH262129 WIA262129:WID262129 WRW262129:WRZ262129 FK327665:FN327665 PG327665:PJ327665 ZC327665:ZF327665 AIY327665:AJB327665 ASU327665:ASX327665 BCQ327665:BCT327665 BMM327665:BMP327665 BWI327665:BWL327665 CGE327665:CGH327665 CQA327665:CQD327665 CZW327665:CZZ327665 DJS327665:DJV327665 DTO327665:DTR327665 EDK327665:EDN327665 ENG327665:ENJ327665 EXC327665:EXF327665 FGY327665:FHB327665 FQU327665:FQX327665 GAQ327665:GAT327665 GKM327665:GKP327665 GUI327665:GUL327665 HEE327665:HEH327665 HOA327665:HOD327665 HXW327665:HXZ327665 IHS327665:IHV327665 IRO327665:IRR327665 JBK327665:JBN327665 JLG327665:JLJ327665 JVC327665:JVF327665 KEY327665:KFB327665 KOU327665:KOX327665 KYQ327665:KYT327665 LIM327665:LIP327665 LSI327665:LSL327665 MCE327665:MCH327665 MMA327665:MMD327665 MVW327665:MVZ327665 NFS327665:NFV327665 NPO327665:NPR327665 NZK327665:NZN327665 OJG327665:OJJ327665 OTC327665:OTF327665 PCY327665:PDB327665 PMU327665:PMX327665 PWQ327665:PWT327665 QGM327665:QGP327665 QQI327665:QQL327665 RAE327665:RAH327665 RKA327665:RKD327665 RTW327665:RTZ327665 SDS327665:SDV327665 SNO327665:SNR327665 SXK327665:SXN327665 THG327665:THJ327665 TRC327665:TRF327665 UAY327665:UBB327665 UKU327665:UKX327665 UUQ327665:UUT327665 VEM327665:VEP327665 VOI327665:VOL327665 VYE327665:VYH327665 WIA327665:WID327665 WRW327665:WRZ327665 FK393201:FN393201 PG393201:PJ393201 ZC393201:ZF393201 AIY393201:AJB393201 ASU393201:ASX393201 BCQ393201:BCT393201 BMM393201:BMP393201 BWI393201:BWL393201 CGE393201:CGH393201 CQA393201:CQD393201 CZW393201:CZZ393201 DJS393201:DJV393201 DTO393201:DTR393201 EDK393201:EDN393201 ENG393201:ENJ393201 EXC393201:EXF393201 FGY393201:FHB393201 FQU393201:FQX393201 GAQ393201:GAT393201 GKM393201:GKP393201 GUI393201:GUL393201 HEE393201:HEH393201 HOA393201:HOD393201 HXW393201:HXZ393201 IHS393201:IHV393201 IRO393201:IRR393201 JBK393201:JBN393201 JLG393201:JLJ393201 JVC393201:JVF393201 KEY393201:KFB393201 KOU393201:KOX393201 KYQ393201:KYT393201 LIM393201:LIP393201 LSI393201:LSL393201 MCE393201:MCH393201 MMA393201:MMD393201 MVW393201:MVZ393201 NFS393201:NFV393201 NPO393201:NPR393201 NZK393201:NZN393201 OJG393201:OJJ393201 OTC393201:OTF393201 PCY393201:PDB393201 PMU393201:PMX393201 PWQ393201:PWT393201 QGM393201:QGP393201 QQI393201:QQL393201 RAE393201:RAH393201 RKA393201:RKD393201 RTW393201:RTZ393201 SDS393201:SDV393201 SNO393201:SNR393201 SXK393201:SXN393201 THG393201:THJ393201 TRC393201:TRF393201 UAY393201:UBB393201 UKU393201:UKX393201 UUQ393201:UUT393201 VEM393201:VEP393201 VOI393201:VOL393201 VYE393201:VYH393201 WIA393201:WID393201 WRW393201:WRZ393201 FK458737:FN458737 PG458737:PJ458737 ZC458737:ZF458737 AIY458737:AJB458737 ASU458737:ASX458737 BCQ458737:BCT458737 BMM458737:BMP458737 BWI458737:BWL458737 CGE458737:CGH458737 CQA458737:CQD458737 CZW458737:CZZ458737 DJS458737:DJV458737 DTO458737:DTR458737 EDK458737:EDN458737 ENG458737:ENJ458737 EXC458737:EXF458737 FGY458737:FHB458737 FQU458737:FQX458737 GAQ458737:GAT458737 GKM458737:GKP458737 GUI458737:GUL458737 HEE458737:HEH458737 HOA458737:HOD458737 HXW458737:HXZ458737 IHS458737:IHV458737 IRO458737:IRR458737 JBK458737:JBN458737 JLG458737:JLJ458737 JVC458737:JVF458737 KEY458737:KFB458737 KOU458737:KOX458737 KYQ458737:KYT458737 LIM458737:LIP458737 LSI458737:LSL458737 MCE458737:MCH458737 MMA458737:MMD458737 MVW458737:MVZ458737 NFS458737:NFV458737 NPO458737:NPR458737 NZK458737:NZN458737 OJG458737:OJJ458737 OTC458737:OTF458737 PCY458737:PDB458737 PMU458737:PMX458737 PWQ458737:PWT458737 QGM458737:QGP458737 QQI458737:QQL458737 RAE458737:RAH458737 RKA458737:RKD458737 RTW458737:RTZ458737 SDS458737:SDV458737 SNO458737:SNR458737 SXK458737:SXN458737 THG458737:THJ458737 TRC458737:TRF458737 UAY458737:UBB458737 UKU458737:UKX458737 UUQ458737:UUT458737 VEM458737:VEP458737 VOI458737:VOL458737 VYE458737:VYH458737 WIA458737:WID458737 WRW458737:WRZ458737 FK524273:FN524273 PG524273:PJ524273 ZC524273:ZF524273 AIY524273:AJB524273 ASU524273:ASX524273 BCQ524273:BCT524273 BMM524273:BMP524273 BWI524273:BWL524273 CGE524273:CGH524273 CQA524273:CQD524273 CZW524273:CZZ524273 DJS524273:DJV524273 DTO524273:DTR524273 EDK524273:EDN524273 ENG524273:ENJ524273 EXC524273:EXF524273 FGY524273:FHB524273 FQU524273:FQX524273 GAQ524273:GAT524273 GKM524273:GKP524273 GUI524273:GUL524273 HEE524273:HEH524273 HOA524273:HOD524273 HXW524273:HXZ524273 IHS524273:IHV524273 IRO524273:IRR524273 JBK524273:JBN524273 JLG524273:JLJ524273 JVC524273:JVF524273 KEY524273:KFB524273 KOU524273:KOX524273 KYQ524273:KYT524273 LIM524273:LIP524273 LSI524273:LSL524273 MCE524273:MCH524273 MMA524273:MMD524273 MVW524273:MVZ524273 NFS524273:NFV524273 NPO524273:NPR524273 NZK524273:NZN524273 OJG524273:OJJ524273 OTC524273:OTF524273 PCY524273:PDB524273 PMU524273:PMX524273 PWQ524273:PWT524273 QGM524273:QGP524273 QQI524273:QQL524273 RAE524273:RAH524273 RKA524273:RKD524273 RTW524273:RTZ524273 SDS524273:SDV524273 SNO524273:SNR524273 SXK524273:SXN524273 THG524273:THJ524273 TRC524273:TRF524273 UAY524273:UBB524273 UKU524273:UKX524273 UUQ524273:UUT524273 VEM524273:VEP524273 VOI524273:VOL524273 VYE524273:VYH524273 WIA524273:WID524273 WRW524273:WRZ524273 FK589809:FN589809 PG589809:PJ589809 ZC589809:ZF589809 AIY589809:AJB589809 ASU589809:ASX589809 BCQ589809:BCT589809 BMM589809:BMP589809 BWI589809:BWL589809 CGE589809:CGH589809 CQA589809:CQD589809 CZW589809:CZZ589809 DJS589809:DJV589809 DTO589809:DTR589809 EDK589809:EDN589809 ENG589809:ENJ589809 EXC589809:EXF589809 FGY589809:FHB589809 FQU589809:FQX589809 GAQ589809:GAT589809 GKM589809:GKP589809 GUI589809:GUL589809 HEE589809:HEH589809 HOA589809:HOD589809 HXW589809:HXZ589809 IHS589809:IHV589809 IRO589809:IRR589809 JBK589809:JBN589809 JLG589809:JLJ589809 JVC589809:JVF589809 KEY589809:KFB589809 KOU589809:KOX589809 KYQ589809:KYT589809 LIM589809:LIP589809 LSI589809:LSL589809 MCE589809:MCH589809 MMA589809:MMD589809 MVW589809:MVZ589809 NFS589809:NFV589809 NPO589809:NPR589809 NZK589809:NZN589809 OJG589809:OJJ589809 OTC589809:OTF589809 PCY589809:PDB589809 PMU589809:PMX589809 PWQ589809:PWT589809 QGM589809:QGP589809 QQI589809:QQL589809 RAE589809:RAH589809 RKA589809:RKD589809 RTW589809:RTZ589809 SDS589809:SDV589809 SNO589809:SNR589809 SXK589809:SXN589809 THG589809:THJ589809 TRC589809:TRF589809 UAY589809:UBB589809 UKU589809:UKX589809 UUQ589809:UUT589809 VEM589809:VEP589809 VOI589809:VOL589809 VYE589809:VYH589809 WIA589809:WID589809 WRW589809:WRZ589809 FK655345:FN655345 PG655345:PJ655345 ZC655345:ZF655345 AIY655345:AJB655345 ASU655345:ASX655345 BCQ655345:BCT655345 BMM655345:BMP655345 BWI655345:BWL655345 CGE655345:CGH655345 CQA655345:CQD655345 CZW655345:CZZ655345 DJS655345:DJV655345 DTO655345:DTR655345 EDK655345:EDN655345 ENG655345:ENJ655345 EXC655345:EXF655345 FGY655345:FHB655345 FQU655345:FQX655345 GAQ655345:GAT655345 GKM655345:GKP655345 GUI655345:GUL655345 HEE655345:HEH655345 HOA655345:HOD655345 HXW655345:HXZ655345 IHS655345:IHV655345 IRO655345:IRR655345 JBK655345:JBN655345 JLG655345:JLJ655345 JVC655345:JVF655345 KEY655345:KFB655345 KOU655345:KOX655345 KYQ655345:KYT655345 LIM655345:LIP655345 LSI655345:LSL655345 MCE655345:MCH655345 MMA655345:MMD655345 MVW655345:MVZ655345 NFS655345:NFV655345 NPO655345:NPR655345 NZK655345:NZN655345 OJG655345:OJJ655345 OTC655345:OTF655345 PCY655345:PDB655345 PMU655345:PMX655345 PWQ655345:PWT655345 QGM655345:QGP655345 QQI655345:QQL655345 RAE655345:RAH655345 RKA655345:RKD655345 RTW655345:RTZ655345 SDS655345:SDV655345 SNO655345:SNR655345 SXK655345:SXN655345 THG655345:THJ655345 TRC655345:TRF655345 UAY655345:UBB655345 UKU655345:UKX655345 UUQ655345:UUT655345 VEM655345:VEP655345 VOI655345:VOL655345 VYE655345:VYH655345 WIA655345:WID655345 WRW655345:WRZ655345 FK720881:FN720881 PG720881:PJ720881 ZC720881:ZF720881 AIY720881:AJB720881 ASU720881:ASX720881 BCQ720881:BCT720881 BMM720881:BMP720881 BWI720881:BWL720881 CGE720881:CGH720881 CQA720881:CQD720881 CZW720881:CZZ720881 DJS720881:DJV720881 DTO720881:DTR720881 EDK720881:EDN720881 ENG720881:ENJ720881 EXC720881:EXF720881 FGY720881:FHB720881 FQU720881:FQX720881 GAQ720881:GAT720881 GKM720881:GKP720881 GUI720881:GUL720881 HEE720881:HEH720881 HOA720881:HOD720881 HXW720881:HXZ720881 IHS720881:IHV720881 IRO720881:IRR720881 JBK720881:JBN720881 JLG720881:JLJ720881 JVC720881:JVF720881 KEY720881:KFB720881 KOU720881:KOX720881 KYQ720881:KYT720881 LIM720881:LIP720881 LSI720881:LSL720881 MCE720881:MCH720881 MMA720881:MMD720881 MVW720881:MVZ720881 NFS720881:NFV720881 NPO720881:NPR720881 NZK720881:NZN720881 OJG720881:OJJ720881 OTC720881:OTF720881 PCY720881:PDB720881 PMU720881:PMX720881 PWQ720881:PWT720881 QGM720881:QGP720881 QQI720881:QQL720881 RAE720881:RAH720881 RKA720881:RKD720881 RTW720881:RTZ720881 SDS720881:SDV720881 SNO720881:SNR720881 SXK720881:SXN720881 THG720881:THJ720881 TRC720881:TRF720881 UAY720881:UBB720881 UKU720881:UKX720881 UUQ720881:UUT720881 VEM720881:VEP720881 VOI720881:VOL720881 VYE720881:VYH720881 WIA720881:WID720881 WRW720881:WRZ720881 FK786417:FN786417 PG786417:PJ786417 ZC786417:ZF786417 AIY786417:AJB786417 ASU786417:ASX786417 BCQ786417:BCT786417 BMM786417:BMP786417 BWI786417:BWL786417 CGE786417:CGH786417 CQA786417:CQD786417 CZW786417:CZZ786417 DJS786417:DJV786417 DTO786417:DTR786417 EDK786417:EDN786417 ENG786417:ENJ786417 EXC786417:EXF786417 FGY786417:FHB786417 FQU786417:FQX786417 GAQ786417:GAT786417 GKM786417:GKP786417 GUI786417:GUL786417 HEE786417:HEH786417 HOA786417:HOD786417 HXW786417:HXZ786417 IHS786417:IHV786417 IRO786417:IRR786417 JBK786417:JBN786417 JLG786417:JLJ786417 JVC786417:JVF786417 KEY786417:KFB786417 KOU786417:KOX786417 KYQ786417:KYT786417 LIM786417:LIP786417 LSI786417:LSL786417 MCE786417:MCH786417 MMA786417:MMD786417 MVW786417:MVZ786417 NFS786417:NFV786417 NPO786417:NPR786417 NZK786417:NZN786417 OJG786417:OJJ786417 OTC786417:OTF786417 PCY786417:PDB786417 PMU786417:PMX786417 PWQ786417:PWT786417 QGM786417:QGP786417 QQI786417:QQL786417 RAE786417:RAH786417 RKA786417:RKD786417 RTW786417:RTZ786417 SDS786417:SDV786417 SNO786417:SNR786417 SXK786417:SXN786417 THG786417:THJ786417 TRC786417:TRF786417 UAY786417:UBB786417 UKU786417:UKX786417 UUQ786417:UUT786417 VEM786417:VEP786417 VOI786417:VOL786417 VYE786417:VYH786417 WIA786417:WID786417 WRW786417:WRZ786417 FK851953:FN851953 PG851953:PJ851953 ZC851953:ZF851953 AIY851953:AJB851953 ASU851953:ASX851953 BCQ851953:BCT851953 BMM851953:BMP851953 BWI851953:BWL851953 CGE851953:CGH851953 CQA851953:CQD851953 CZW851953:CZZ851953 DJS851953:DJV851953 DTO851953:DTR851953 EDK851953:EDN851953 ENG851953:ENJ851953 EXC851953:EXF851953 FGY851953:FHB851953 FQU851953:FQX851953 GAQ851953:GAT851953 GKM851953:GKP851953 GUI851953:GUL851953 HEE851953:HEH851953 HOA851953:HOD851953 HXW851953:HXZ851953 IHS851953:IHV851953 IRO851953:IRR851953 JBK851953:JBN851953 JLG851953:JLJ851953 JVC851953:JVF851953 KEY851953:KFB851953 KOU851953:KOX851953 KYQ851953:KYT851953 LIM851953:LIP851953 LSI851953:LSL851953 MCE851953:MCH851953 MMA851953:MMD851953 MVW851953:MVZ851953 NFS851953:NFV851953 NPO851953:NPR851953 NZK851953:NZN851953 OJG851953:OJJ851953 OTC851953:OTF851953 PCY851953:PDB851953 PMU851953:PMX851953 PWQ851953:PWT851953 QGM851953:QGP851953 QQI851953:QQL851953 RAE851953:RAH851953 RKA851953:RKD851953 RTW851953:RTZ851953 SDS851953:SDV851953 SNO851953:SNR851953 SXK851953:SXN851953 THG851953:THJ851953 TRC851953:TRF851953 UAY851953:UBB851953 UKU851953:UKX851953 UUQ851953:UUT851953 VEM851953:VEP851953 VOI851953:VOL851953 VYE851953:VYH851953 WIA851953:WID851953 WRW851953:WRZ851953 FK917489:FN917489 PG917489:PJ917489 ZC917489:ZF917489 AIY917489:AJB917489 ASU917489:ASX917489 BCQ917489:BCT917489 BMM917489:BMP917489 BWI917489:BWL917489 CGE917489:CGH917489 CQA917489:CQD917489 CZW917489:CZZ917489 DJS917489:DJV917489 DTO917489:DTR917489 EDK917489:EDN917489 ENG917489:ENJ917489 EXC917489:EXF917489 FGY917489:FHB917489 FQU917489:FQX917489 GAQ917489:GAT917489 GKM917489:GKP917489 GUI917489:GUL917489 HEE917489:HEH917489 HOA917489:HOD917489 HXW917489:HXZ917489 IHS917489:IHV917489 IRO917489:IRR917489 JBK917489:JBN917489 JLG917489:JLJ917489 JVC917489:JVF917489 KEY917489:KFB917489 KOU917489:KOX917489 KYQ917489:KYT917489 LIM917489:LIP917489 LSI917489:LSL917489 MCE917489:MCH917489 MMA917489:MMD917489 MVW917489:MVZ917489 NFS917489:NFV917489 NPO917489:NPR917489 NZK917489:NZN917489 OJG917489:OJJ917489 OTC917489:OTF917489 PCY917489:PDB917489 PMU917489:PMX917489 PWQ917489:PWT917489 QGM917489:QGP917489 QQI917489:QQL917489 RAE917489:RAH917489 RKA917489:RKD917489 RTW917489:RTZ917489 SDS917489:SDV917489 SNO917489:SNR917489 SXK917489:SXN917489 THG917489:THJ917489 TRC917489:TRF917489 UAY917489:UBB917489 UKU917489:UKX917489 UUQ917489:UUT917489 VEM917489:VEP917489 VOI917489:VOL917489 VYE917489:VYH917489 WIA917489:WID917489 WRW917489:WRZ917489" xr:uid="{1F423F3A-416F-4E97-8D9A-05CEEFB5D039}">
       <formula1>"○"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WRC982980:WRQ983017 VNO982980:VOC983017 VDS982980:VEG983017 UTW982980:UUK983017 UKA982980:UKO983017 UAE982980:UAS983017 TQI982980:TQW983017 TGM982980:THA983017 SWQ982980:SXE983017 SMU982980:SNI983017 SCY982980:SDM983017 RTC982980:RTQ983017 RJG982980:RJU983017 QZK982980:QZY983017 QPO982980:QQC983017 QFS982980:QGG983017 PVW982980:PWK983017 PMA982980:PMO983017 PCE982980:PCS983017 OSI982980:OSW983017 OIM982980:OJA983017 NYQ982980:NZE983017 NOU982980:NPI983017 NEY982980:NFM983017 MVC982980:MVQ983017 MLG982980:MLU983017 MBK982980:MBY983017 LRO982980:LSC983017 LHS982980:LIG983017 KXW982980:KYK983017 KOA982980:KOO983017 KEE982980:KES983017 JUI982980:JUW983017 JKM982980:JLA983017 JAQ982980:JBE983017 IQU982980:IRI983017 IGY982980:IHM983017 HXC982980:HXQ983017 HNG982980:HNU983017 HDK982980:HDY983017 GTO982980:GUC983017 GJS982980:GKG983017 FZW982980:GAK983017 FQA982980:FQO983017 FGE982980:FGS983017 EWI982980:EWW983017 EMM982980:ENA983017 ECQ982980:EDE983017 DSU982980:DTI983017 DIY982980:DJM983017 CZC982980:CZQ983017 CPG982980:CPU983017 CFK982980:CFY983017 BVO982980:BWC983017 BLS982980:BMG983017 BBW982980:BCK983017 ASA982980:ASO983017 AIE982980:AIS983017 YI982980:YW983017 OM982980:PA983017 EQ982980:FE983017 WRC917444:WRQ917481 WHG917444:WHU917481 VXK917444:VXY917481 VNO917444:VOC917481 VDS917444:VEG917481 UTW917444:UUK917481 UKA917444:UKO917481 UAE917444:UAS917481 TQI917444:TQW917481 TGM917444:THA917481 SWQ917444:SXE917481 SMU917444:SNI917481 SCY917444:SDM917481 RTC917444:RTQ917481 RJG917444:RJU917481 QZK917444:QZY917481 QPO917444:QQC917481 QFS917444:QGG917481 PVW917444:PWK917481 PMA917444:PMO917481 PCE917444:PCS917481 OSI917444:OSW917481 OIM917444:OJA917481 NYQ917444:NZE917481 NOU917444:NPI917481 NEY917444:NFM917481 MVC917444:MVQ917481 MLG917444:MLU917481 MBK917444:MBY917481 LRO917444:LSC917481 LHS917444:LIG917481 KXW917444:KYK917481 KOA917444:KOO917481 KEE917444:KES917481 JUI917444:JUW917481 JKM917444:JLA917481 JAQ917444:JBE917481 IQU917444:IRI917481 IGY917444:IHM917481 HXC917444:HXQ917481 HNG917444:HNU917481 HDK917444:HDY917481 GTO917444:GUC917481 GJS917444:GKG917481 FZW917444:GAK917481 FQA917444:FQO917481 FGE917444:FGS917481 EWI917444:EWW917481 EMM917444:ENA917481 ECQ917444:EDE917481 DSU917444:DTI917481 DIY917444:DJM917481 CZC917444:CZQ917481 CPG917444:CPU917481 CFK917444:CFY917481 BVO917444:BWC917481 BLS917444:BMG917481 BBW917444:BCK917481 ASA917444:ASO917481 AIE917444:AIS917481 YI917444:YW917481 OM917444:PA917481 EQ917444:FE917481 WRC851908:WRQ851945 WHG851908:WHU851945 VXK851908:VXY851945 VNO851908:VOC851945 VDS851908:VEG851945 UTW851908:UUK851945 UKA851908:UKO851945 UAE851908:UAS851945 TQI851908:TQW851945 TGM851908:THA851945 SWQ851908:SXE851945 SMU851908:SNI851945 SCY851908:SDM851945 RTC851908:RTQ851945 RJG851908:RJU851945 QZK851908:QZY851945 QPO851908:QQC851945 QFS851908:QGG851945 PVW851908:PWK851945 PMA851908:PMO851945 PCE851908:PCS851945 OSI851908:OSW851945 OIM851908:OJA851945 NYQ851908:NZE851945 NOU851908:NPI851945 NEY851908:NFM851945 MVC851908:MVQ851945 MLG851908:MLU851945 MBK851908:MBY851945 LRO851908:LSC851945 LHS851908:LIG851945 KXW851908:KYK851945 KOA851908:KOO851945 KEE851908:KES851945 JUI851908:JUW851945 JKM851908:JLA851945 JAQ851908:JBE851945 IQU851908:IRI851945 IGY851908:IHM851945 HXC851908:HXQ851945 HNG851908:HNU851945 HDK851908:HDY851945 GTO851908:GUC851945 GJS851908:GKG851945 FZW851908:GAK851945 FQA851908:FQO851945 FGE851908:FGS851945 EWI851908:EWW851945 EMM851908:ENA851945 ECQ851908:EDE851945 DSU851908:DTI851945 DIY851908:DJM851945 CZC851908:CZQ851945 CPG851908:CPU851945 CFK851908:CFY851945 BVO851908:BWC851945 BLS851908:BMG851945 BBW851908:BCK851945 ASA851908:ASO851945 AIE851908:AIS851945 YI851908:YW851945 OM851908:PA851945 EQ851908:FE851945 WRC786372:WRQ786409 WHG786372:WHU786409 VXK786372:VXY786409 VNO786372:VOC786409 VDS786372:VEG786409 UTW786372:UUK786409 UKA786372:UKO786409 UAE786372:UAS786409 TQI786372:TQW786409 TGM786372:THA786409 SWQ786372:SXE786409 SMU786372:SNI786409 SCY786372:SDM786409 RTC786372:RTQ786409 RJG786372:RJU786409 QZK786372:QZY786409 QPO786372:QQC786409 QFS786372:QGG786409 PVW786372:PWK786409 PMA786372:PMO786409 PCE786372:PCS786409 OSI786372:OSW786409 OIM786372:OJA786409 NYQ786372:NZE786409 NOU786372:NPI786409 NEY786372:NFM786409 MVC786372:MVQ786409 MLG786372:MLU786409 MBK786372:MBY786409 LRO786372:LSC786409 LHS786372:LIG786409 KXW786372:KYK786409 KOA786372:KOO786409 KEE786372:KES786409 JUI786372:JUW786409 JKM786372:JLA786409 JAQ786372:JBE786409 IQU786372:IRI786409 IGY786372:IHM786409 HXC786372:HXQ786409 HNG786372:HNU786409 HDK786372:HDY786409 GTO786372:GUC786409 GJS786372:GKG786409 FZW786372:GAK786409 FQA786372:FQO786409 FGE786372:FGS786409 EWI786372:EWW786409 EMM786372:ENA786409 ECQ786372:EDE786409 DSU786372:DTI786409 DIY786372:DJM786409 CZC786372:CZQ786409 CPG786372:CPU786409 CFK786372:CFY786409 BVO786372:BWC786409 BLS786372:BMG786409 BBW786372:BCK786409 ASA786372:ASO786409 AIE786372:AIS786409 YI786372:YW786409 OM786372:PA786409 EQ786372:FE786409 WRC720836:WRQ720873 WHG720836:WHU720873 VXK720836:VXY720873 VNO720836:VOC720873 VDS720836:VEG720873 UTW720836:UUK720873 UKA720836:UKO720873 UAE720836:UAS720873 TQI720836:TQW720873 TGM720836:THA720873 SWQ720836:SXE720873 SMU720836:SNI720873 SCY720836:SDM720873 RTC720836:RTQ720873 RJG720836:RJU720873 QZK720836:QZY720873 QPO720836:QQC720873 QFS720836:QGG720873 PVW720836:PWK720873 PMA720836:PMO720873 PCE720836:PCS720873 OSI720836:OSW720873 OIM720836:OJA720873 NYQ720836:NZE720873 NOU720836:NPI720873 NEY720836:NFM720873 MVC720836:MVQ720873 MLG720836:MLU720873 MBK720836:MBY720873 LRO720836:LSC720873 LHS720836:LIG720873 KXW720836:KYK720873 KOA720836:KOO720873 KEE720836:KES720873 JUI720836:JUW720873 JKM720836:JLA720873 JAQ720836:JBE720873 IQU720836:IRI720873 IGY720836:IHM720873 HXC720836:HXQ720873 HNG720836:HNU720873 HDK720836:HDY720873 GTO720836:GUC720873 GJS720836:GKG720873 FZW720836:GAK720873 FQA720836:FQO720873 FGE720836:FGS720873 EWI720836:EWW720873 EMM720836:ENA720873 ECQ720836:EDE720873 DSU720836:DTI720873 DIY720836:DJM720873 CZC720836:CZQ720873 CPG720836:CPU720873 CFK720836:CFY720873 BVO720836:BWC720873 BLS720836:BMG720873 BBW720836:BCK720873 ASA720836:ASO720873 AIE720836:AIS720873 YI720836:YW720873 OM720836:PA720873 EQ720836:FE720873 WRC655300:WRQ655337 WHG655300:WHU655337 VXK655300:VXY655337 VNO655300:VOC655337 VDS655300:VEG655337 UTW655300:UUK655337 UKA655300:UKO655337 UAE655300:UAS655337 TQI655300:TQW655337 TGM655300:THA655337 SWQ655300:SXE655337 SMU655300:SNI655337 SCY655300:SDM655337 RTC655300:RTQ655337 RJG655300:RJU655337 QZK655300:QZY655337 QPO655300:QQC655337 QFS655300:QGG655337 PVW655300:PWK655337 PMA655300:PMO655337 PCE655300:PCS655337 OSI655300:OSW655337 OIM655300:OJA655337 NYQ655300:NZE655337 NOU655300:NPI655337 NEY655300:NFM655337 MVC655300:MVQ655337 MLG655300:MLU655337 MBK655300:MBY655337 LRO655300:LSC655337 LHS655300:LIG655337 KXW655300:KYK655337 KOA655300:KOO655337 KEE655300:KES655337 JUI655300:JUW655337 JKM655300:JLA655337 JAQ655300:JBE655337 IQU655300:IRI655337 IGY655300:IHM655337 HXC655300:HXQ655337 HNG655300:HNU655337 HDK655300:HDY655337 GTO655300:GUC655337 GJS655300:GKG655337 FZW655300:GAK655337 FQA655300:FQO655337 FGE655300:FGS655337 EWI655300:EWW655337 EMM655300:ENA655337 ECQ655300:EDE655337 DSU655300:DTI655337 DIY655300:DJM655337 CZC655300:CZQ655337 CPG655300:CPU655337 CFK655300:CFY655337 BVO655300:BWC655337 BLS655300:BMG655337 BBW655300:BCK655337 ASA655300:ASO655337 AIE655300:AIS655337 YI655300:YW655337 OM655300:PA655337 EQ655300:FE655337 WRC589764:WRQ589801 WHG589764:WHU589801 VXK589764:VXY589801 VNO589764:VOC589801 VDS589764:VEG589801 UTW589764:UUK589801 UKA589764:UKO589801 UAE589764:UAS589801 TQI589764:TQW589801 TGM589764:THA589801 SWQ589764:SXE589801 SMU589764:SNI589801 SCY589764:SDM589801 RTC589764:RTQ589801 RJG589764:RJU589801 QZK589764:QZY589801 QPO589764:QQC589801 QFS589764:QGG589801 PVW589764:PWK589801 PMA589764:PMO589801 PCE589764:PCS589801 OSI589764:OSW589801 OIM589764:OJA589801 NYQ589764:NZE589801 NOU589764:NPI589801 NEY589764:NFM589801 MVC589764:MVQ589801 MLG589764:MLU589801 MBK589764:MBY589801 LRO589764:LSC589801 LHS589764:LIG589801 KXW589764:KYK589801 KOA589764:KOO589801 KEE589764:KES589801 JUI589764:JUW589801 JKM589764:JLA589801 JAQ589764:JBE589801 IQU589764:IRI589801 IGY589764:IHM589801 HXC589764:HXQ589801 HNG589764:HNU589801 HDK589764:HDY589801 GTO589764:GUC589801 GJS589764:GKG589801 FZW589764:GAK589801 FQA589764:FQO589801 FGE589764:FGS589801 EWI589764:EWW589801 EMM589764:ENA589801 ECQ589764:EDE589801 DSU589764:DTI589801 DIY589764:DJM589801 CZC589764:CZQ589801 CPG589764:CPU589801 CFK589764:CFY589801 BVO589764:BWC589801 BLS589764:BMG589801 BBW589764:BCK589801 ASA589764:ASO589801 AIE589764:AIS589801 YI589764:YW589801 OM589764:PA589801 EQ589764:FE589801 WRC524228:WRQ524265 WHG524228:WHU524265 VXK524228:VXY524265 VNO524228:VOC524265 VDS524228:VEG524265 UTW524228:UUK524265 UKA524228:UKO524265 UAE524228:UAS524265 TQI524228:TQW524265 TGM524228:THA524265 SWQ524228:SXE524265 SMU524228:SNI524265 SCY524228:SDM524265 RTC524228:RTQ524265 RJG524228:RJU524265 QZK524228:QZY524265 QPO524228:QQC524265 QFS524228:QGG524265 PVW524228:PWK524265 PMA524228:PMO524265 PCE524228:PCS524265 OSI524228:OSW524265 OIM524228:OJA524265 NYQ524228:NZE524265 NOU524228:NPI524265 NEY524228:NFM524265 MVC524228:MVQ524265 MLG524228:MLU524265 MBK524228:MBY524265 LRO524228:LSC524265 LHS524228:LIG524265 KXW524228:KYK524265 KOA524228:KOO524265 KEE524228:KES524265 JUI524228:JUW524265 JKM524228:JLA524265 JAQ524228:JBE524265 IQU524228:IRI524265 IGY524228:IHM524265 HXC524228:HXQ524265 HNG524228:HNU524265 HDK524228:HDY524265 GTO524228:GUC524265 GJS524228:GKG524265 FZW524228:GAK524265 FQA524228:FQO524265 FGE524228:FGS524265 EWI524228:EWW524265 EMM524228:ENA524265 ECQ524228:EDE524265 DSU524228:DTI524265 DIY524228:DJM524265 CZC524228:CZQ524265 CPG524228:CPU524265 CFK524228:CFY524265 BVO524228:BWC524265 BLS524228:BMG524265 BBW524228:BCK524265 ASA524228:ASO524265 AIE524228:AIS524265 YI524228:YW524265 OM524228:PA524265 EQ524228:FE524265 WRC458692:WRQ458729 WHG458692:WHU458729 VXK458692:VXY458729 VNO458692:VOC458729 VDS458692:VEG458729 UTW458692:UUK458729 UKA458692:UKO458729 UAE458692:UAS458729 TQI458692:TQW458729 TGM458692:THA458729 SWQ458692:SXE458729 SMU458692:SNI458729 SCY458692:SDM458729 RTC458692:RTQ458729 RJG458692:RJU458729 QZK458692:QZY458729 QPO458692:QQC458729 QFS458692:QGG458729 PVW458692:PWK458729 PMA458692:PMO458729 PCE458692:PCS458729 OSI458692:OSW458729 OIM458692:OJA458729 NYQ458692:NZE458729 NOU458692:NPI458729 NEY458692:NFM458729 MVC458692:MVQ458729 MLG458692:MLU458729 MBK458692:MBY458729 LRO458692:LSC458729 LHS458692:LIG458729 KXW458692:KYK458729 KOA458692:KOO458729 KEE458692:KES458729 JUI458692:JUW458729 JKM458692:JLA458729 JAQ458692:JBE458729 IQU458692:IRI458729 IGY458692:IHM458729 HXC458692:HXQ458729 HNG458692:HNU458729 HDK458692:HDY458729 GTO458692:GUC458729 GJS458692:GKG458729 FZW458692:GAK458729 FQA458692:FQO458729 FGE458692:FGS458729 EWI458692:EWW458729 EMM458692:ENA458729 ECQ458692:EDE458729 DSU458692:DTI458729 DIY458692:DJM458729 CZC458692:CZQ458729 CPG458692:CPU458729 CFK458692:CFY458729 BVO458692:BWC458729 BLS458692:BMG458729 BBW458692:BCK458729 ASA458692:ASO458729 AIE458692:AIS458729 YI458692:YW458729 OM458692:PA458729 EQ458692:FE458729 WRC393156:WRQ393193 WHG393156:WHU393193 VXK393156:VXY393193 VNO393156:VOC393193 VDS393156:VEG393193 UTW393156:UUK393193 UKA393156:UKO393193 UAE393156:UAS393193 TQI393156:TQW393193 TGM393156:THA393193 SWQ393156:SXE393193 SMU393156:SNI393193 SCY393156:SDM393193 RTC393156:RTQ393193 RJG393156:RJU393193 QZK393156:QZY393193 QPO393156:QQC393193 QFS393156:QGG393193 PVW393156:PWK393193 PMA393156:PMO393193 PCE393156:PCS393193 OSI393156:OSW393193 OIM393156:OJA393193 NYQ393156:NZE393193 NOU393156:NPI393193 NEY393156:NFM393193 MVC393156:MVQ393193 MLG393156:MLU393193 MBK393156:MBY393193 LRO393156:LSC393193 LHS393156:LIG393193 KXW393156:KYK393193 KOA393156:KOO393193 KEE393156:KES393193 JUI393156:JUW393193 JKM393156:JLA393193 JAQ393156:JBE393193 IQU393156:IRI393193 IGY393156:IHM393193 HXC393156:HXQ393193 HNG393156:HNU393193 HDK393156:HDY393193 GTO393156:GUC393193 GJS393156:GKG393193 FZW393156:GAK393193 FQA393156:FQO393193 FGE393156:FGS393193 EWI393156:EWW393193 EMM393156:ENA393193 ECQ393156:EDE393193 DSU393156:DTI393193 DIY393156:DJM393193 CZC393156:CZQ393193 CPG393156:CPU393193 CFK393156:CFY393193 BVO393156:BWC393193 BLS393156:BMG393193 BBW393156:BCK393193 ASA393156:ASO393193 AIE393156:AIS393193 YI393156:YW393193 OM393156:PA393193 EQ393156:FE393193 WRC327620:WRQ327657 WHG327620:WHU327657 VXK327620:VXY327657 VNO327620:VOC327657 VDS327620:VEG327657 UTW327620:UUK327657 UKA327620:UKO327657 UAE327620:UAS327657 TQI327620:TQW327657 TGM327620:THA327657 SWQ327620:SXE327657 SMU327620:SNI327657 SCY327620:SDM327657 RTC327620:RTQ327657 RJG327620:RJU327657 QZK327620:QZY327657 QPO327620:QQC327657 QFS327620:QGG327657 PVW327620:PWK327657 PMA327620:PMO327657 PCE327620:PCS327657 OSI327620:OSW327657 OIM327620:OJA327657 NYQ327620:NZE327657 NOU327620:NPI327657 NEY327620:NFM327657 MVC327620:MVQ327657 MLG327620:MLU327657 MBK327620:MBY327657 LRO327620:LSC327657 LHS327620:LIG327657 KXW327620:KYK327657 KOA327620:KOO327657 KEE327620:KES327657 JUI327620:JUW327657 JKM327620:JLA327657 JAQ327620:JBE327657 IQU327620:IRI327657 IGY327620:IHM327657 HXC327620:HXQ327657 HNG327620:HNU327657 HDK327620:HDY327657 GTO327620:GUC327657 GJS327620:GKG327657 FZW327620:GAK327657 FQA327620:FQO327657 FGE327620:FGS327657 EWI327620:EWW327657 EMM327620:ENA327657 ECQ327620:EDE327657 DSU327620:DTI327657 DIY327620:DJM327657 CZC327620:CZQ327657 CPG327620:CPU327657 CFK327620:CFY327657 BVO327620:BWC327657 BLS327620:BMG327657 BBW327620:BCK327657 ASA327620:ASO327657 AIE327620:AIS327657 YI327620:YW327657 OM327620:PA327657 EQ327620:FE327657 WRC262084:WRQ262121 WHG262084:WHU262121 VXK262084:VXY262121 VNO262084:VOC262121 VDS262084:VEG262121 UTW262084:UUK262121 UKA262084:UKO262121 UAE262084:UAS262121 TQI262084:TQW262121 TGM262084:THA262121 SWQ262084:SXE262121 SMU262084:SNI262121 SCY262084:SDM262121 RTC262084:RTQ262121 RJG262084:RJU262121 QZK262084:QZY262121 QPO262084:QQC262121 QFS262084:QGG262121 PVW262084:PWK262121 PMA262084:PMO262121 PCE262084:PCS262121 OSI262084:OSW262121 OIM262084:OJA262121 NYQ262084:NZE262121 NOU262084:NPI262121 NEY262084:NFM262121 MVC262084:MVQ262121 MLG262084:MLU262121 MBK262084:MBY262121 LRO262084:LSC262121 LHS262084:LIG262121 KXW262084:KYK262121 KOA262084:KOO262121 KEE262084:KES262121 JUI262084:JUW262121 JKM262084:JLA262121 JAQ262084:JBE262121 IQU262084:IRI262121 IGY262084:IHM262121 HXC262084:HXQ262121 HNG262084:HNU262121 HDK262084:HDY262121 GTO262084:GUC262121 GJS262084:GKG262121 FZW262084:GAK262121 FQA262084:FQO262121 FGE262084:FGS262121 EWI262084:EWW262121 EMM262084:ENA262121 ECQ262084:EDE262121 DSU262084:DTI262121 DIY262084:DJM262121 CZC262084:CZQ262121 CPG262084:CPU262121 CFK262084:CFY262121 BVO262084:BWC262121 BLS262084:BMG262121 BBW262084:BCK262121 ASA262084:ASO262121 AIE262084:AIS262121 YI262084:YW262121 OM262084:PA262121 EQ262084:FE262121 WRC196548:WRQ196585 WHG196548:WHU196585 VXK196548:VXY196585 VNO196548:VOC196585 VDS196548:VEG196585 UTW196548:UUK196585 UKA196548:UKO196585 UAE196548:UAS196585 TQI196548:TQW196585 TGM196548:THA196585 SWQ196548:SXE196585 SMU196548:SNI196585 SCY196548:SDM196585 RTC196548:RTQ196585 RJG196548:RJU196585 QZK196548:QZY196585 QPO196548:QQC196585 QFS196548:QGG196585 PVW196548:PWK196585 PMA196548:PMO196585 PCE196548:PCS196585 OSI196548:OSW196585 OIM196548:OJA196585 NYQ196548:NZE196585 NOU196548:NPI196585 NEY196548:NFM196585 MVC196548:MVQ196585 MLG196548:MLU196585 MBK196548:MBY196585 LRO196548:LSC196585 LHS196548:LIG196585 KXW196548:KYK196585 KOA196548:KOO196585 KEE196548:KES196585 JUI196548:JUW196585 JKM196548:JLA196585 JAQ196548:JBE196585 IQU196548:IRI196585 IGY196548:IHM196585 HXC196548:HXQ196585 HNG196548:HNU196585 HDK196548:HDY196585 GTO196548:GUC196585 GJS196548:GKG196585 FZW196548:GAK196585 FQA196548:FQO196585 FGE196548:FGS196585 EWI196548:EWW196585 EMM196548:ENA196585 ECQ196548:EDE196585 DSU196548:DTI196585 DIY196548:DJM196585 CZC196548:CZQ196585 CPG196548:CPU196585 CFK196548:CFY196585 BVO196548:BWC196585 BLS196548:BMG196585 BBW196548:BCK196585 ASA196548:ASO196585 AIE196548:AIS196585 YI196548:YW196585 OM196548:PA196585 EQ196548:FE196585 WRC131012:WRQ131049 WHG131012:WHU131049 VXK131012:VXY131049 VNO131012:VOC131049 VDS131012:VEG131049 UTW131012:UUK131049 UKA131012:UKO131049 UAE131012:UAS131049 TQI131012:TQW131049 TGM131012:THA131049 SWQ131012:SXE131049 SMU131012:SNI131049 SCY131012:SDM131049 RTC131012:RTQ131049 RJG131012:RJU131049 QZK131012:QZY131049 QPO131012:QQC131049 QFS131012:QGG131049 PVW131012:PWK131049 PMA131012:PMO131049 PCE131012:PCS131049 OSI131012:OSW131049 OIM131012:OJA131049 NYQ131012:NZE131049 NOU131012:NPI131049 NEY131012:NFM131049 MVC131012:MVQ131049 MLG131012:MLU131049 MBK131012:MBY131049 LRO131012:LSC131049 LHS131012:LIG131049 KXW131012:KYK131049 KOA131012:KOO131049 KEE131012:KES131049 JUI131012:JUW131049 JKM131012:JLA131049 JAQ131012:JBE131049 IQU131012:IRI131049 IGY131012:IHM131049 HXC131012:HXQ131049 HNG131012:HNU131049 HDK131012:HDY131049 GTO131012:GUC131049 GJS131012:GKG131049 FZW131012:GAK131049 FQA131012:FQO131049 FGE131012:FGS131049 EWI131012:EWW131049 EMM131012:ENA131049 ECQ131012:EDE131049 DSU131012:DTI131049 DIY131012:DJM131049 CZC131012:CZQ131049 CPG131012:CPU131049 CFK131012:CFY131049 BVO131012:BWC131049 BLS131012:BMG131049 BBW131012:BCK131049 ASA131012:ASO131049 AIE131012:AIS131049 YI131012:YW131049 OM131012:PA131049 EQ131012:FE131049 WRC65476:WRQ65513 WHG65476:WHU65513 VXK65476:VXY65513 VNO65476:VOC65513 VDS65476:VEG65513 UTW65476:UUK65513 UKA65476:UKO65513 UAE65476:UAS65513 TQI65476:TQW65513 TGM65476:THA65513 SWQ65476:SXE65513 SMU65476:SNI65513 SCY65476:SDM65513 RTC65476:RTQ65513 RJG65476:RJU65513 QZK65476:QZY65513 QPO65476:QQC65513 QFS65476:QGG65513 PVW65476:PWK65513 PMA65476:PMO65513 PCE65476:PCS65513 OSI65476:OSW65513 OIM65476:OJA65513 NYQ65476:NZE65513 NOU65476:NPI65513 NEY65476:NFM65513 MVC65476:MVQ65513 MLG65476:MLU65513 MBK65476:MBY65513 LRO65476:LSC65513 LHS65476:LIG65513 KXW65476:KYK65513 KOA65476:KOO65513 KEE65476:KES65513 JUI65476:JUW65513 JKM65476:JLA65513 JAQ65476:JBE65513 IQU65476:IRI65513 IGY65476:IHM65513 HXC65476:HXQ65513 HNG65476:HNU65513 HDK65476:HDY65513 GTO65476:GUC65513 GJS65476:GKG65513 FZW65476:GAK65513 FQA65476:FQO65513 FGE65476:FGS65513 EWI65476:EWW65513 EMM65476:ENA65513 ECQ65476:EDE65513 DSU65476:DTI65513 DIY65476:DJM65513 CZC65476:CZQ65513 CPG65476:CPU65513 CFK65476:CFY65513 BVO65476:BWC65513 BLS65476:BMG65513 BBW65476:BCK65513 ASA65476:ASO65513 AIE65476:AIS65513 YI65476:YW65513 OM65476:PA65513 EQ65476:FE65513 WHG982980:WHU983017 VXK982980:VXY983017 VXH2:VXV8 VNL2:VNZ8 VDP2:VED8 UTT2:UUH8 UJX2:UKL8 UAB2:UAP8 TQF2:TQT8 TGJ2:TGX8 SWN2:SXB8 SMR2:SNF8 SCV2:SDJ8 RSZ2:RTN8 RJD2:RJR8 QZH2:QZV8 QPL2:QPZ8 QFP2:QGD8 PVT2:PWH8 PLX2:PML8 PCB2:PCP8 OSF2:OST8 OIJ2:OIX8 NYN2:NZB8 NOR2:NPF8 NEV2:NFJ8 MUZ2:MVN8 MLD2:MLR8 MBH2:MBV8 LRL2:LRZ8 LHP2:LID8 KXT2:KYH8 KNX2:KOL8 KEB2:KEP8 JUF2:JUT8 JKJ2:JKX8 JAN2:JBB8 IQR2:IRF8 IGV2:IHJ8 HWZ2:HXN8 HND2:HNR8 HDH2:HDV8 GTL2:GTZ8 GJP2:GKD8 FZT2:GAH8 FPX2:FQL8 FGB2:FGP8 EWF2:EWT8 EMJ2:EMX8 ECN2:EDB8 DSR2:DTF8 DIV2:DJJ8 CYZ2:CZN8 CPD2:CPR8 CFH2:CFV8 BVL2:BVZ8 BLP2:BMD8 BBT2:BCH8 ARX2:ASL8 AIB2:AIP8 YF2:YT8 OJ2:OX8 EN2:FB8 WQZ2:WRN8 WHD2:WHR8" xr:uid="{6E1062E8-DB94-47CF-976E-796A7CF30995}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WRC982978:WRQ983015 VNO982978:VOC983015 VDS982978:VEG983015 UTW982978:UUK983015 UKA982978:UKO983015 UAE982978:UAS983015 TQI982978:TQW983015 TGM982978:THA983015 SWQ982978:SXE983015 SMU982978:SNI983015 SCY982978:SDM983015 RTC982978:RTQ983015 RJG982978:RJU983015 QZK982978:QZY983015 QPO982978:QQC983015 QFS982978:QGG983015 PVW982978:PWK983015 PMA982978:PMO983015 PCE982978:PCS983015 OSI982978:OSW983015 OIM982978:OJA983015 NYQ982978:NZE983015 NOU982978:NPI983015 NEY982978:NFM983015 MVC982978:MVQ983015 MLG982978:MLU983015 MBK982978:MBY983015 LRO982978:LSC983015 LHS982978:LIG983015 KXW982978:KYK983015 KOA982978:KOO983015 KEE982978:KES983015 JUI982978:JUW983015 JKM982978:JLA983015 JAQ982978:JBE983015 IQU982978:IRI983015 IGY982978:IHM983015 HXC982978:HXQ983015 HNG982978:HNU983015 HDK982978:HDY983015 GTO982978:GUC983015 GJS982978:GKG983015 FZW982978:GAK983015 FQA982978:FQO983015 FGE982978:FGS983015 EWI982978:EWW983015 EMM982978:ENA983015 ECQ982978:EDE983015 DSU982978:DTI983015 DIY982978:DJM983015 CZC982978:CZQ983015 CPG982978:CPU983015 CFK982978:CFY983015 BVO982978:BWC983015 BLS982978:BMG983015 BBW982978:BCK983015 ASA982978:ASO983015 AIE982978:AIS983015 YI982978:YW983015 OM982978:PA983015 EQ982978:FE983015 WRC917442:WRQ917479 WHG917442:WHU917479 VXK917442:VXY917479 VNO917442:VOC917479 VDS917442:VEG917479 UTW917442:UUK917479 UKA917442:UKO917479 UAE917442:UAS917479 TQI917442:TQW917479 TGM917442:THA917479 SWQ917442:SXE917479 SMU917442:SNI917479 SCY917442:SDM917479 RTC917442:RTQ917479 RJG917442:RJU917479 QZK917442:QZY917479 QPO917442:QQC917479 QFS917442:QGG917479 PVW917442:PWK917479 PMA917442:PMO917479 PCE917442:PCS917479 OSI917442:OSW917479 OIM917442:OJA917479 NYQ917442:NZE917479 NOU917442:NPI917479 NEY917442:NFM917479 MVC917442:MVQ917479 MLG917442:MLU917479 MBK917442:MBY917479 LRO917442:LSC917479 LHS917442:LIG917479 KXW917442:KYK917479 KOA917442:KOO917479 KEE917442:KES917479 JUI917442:JUW917479 JKM917442:JLA917479 JAQ917442:JBE917479 IQU917442:IRI917479 IGY917442:IHM917479 HXC917442:HXQ917479 HNG917442:HNU917479 HDK917442:HDY917479 GTO917442:GUC917479 GJS917442:GKG917479 FZW917442:GAK917479 FQA917442:FQO917479 FGE917442:FGS917479 EWI917442:EWW917479 EMM917442:ENA917479 ECQ917442:EDE917479 DSU917442:DTI917479 DIY917442:DJM917479 CZC917442:CZQ917479 CPG917442:CPU917479 CFK917442:CFY917479 BVO917442:BWC917479 BLS917442:BMG917479 BBW917442:BCK917479 ASA917442:ASO917479 AIE917442:AIS917479 YI917442:YW917479 OM917442:PA917479 EQ917442:FE917479 WRC851906:WRQ851943 WHG851906:WHU851943 VXK851906:VXY851943 VNO851906:VOC851943 VDS851906:VEG851943 UTW851906:UUK851943 UKA851906:UKO851943 UAE851906:UAS851943 TQI851906:TQW851943 TGM851906:THA851943 SWQ851906:SXE851943 SMU851906:SNI851943 SCY851906:SDM851943 RTC851906:RTQ851943 RJG851906:RJU851943 QZK851906:QZY851943 QPO851906:QQC851943 QFS851906:QGG851943 PVW851906:PWK851943 PMA851906:PMO851943 PCE851906:PCS851943 OSI851906:OSW851943 OIM851906:OJA851943 NYQ851906:NZE851943 NOU851906:NPI851943 NEY851906:NFM851943 MVC851906:MVQ851943 MLG851906:MLU851943 MBK851906:MBY851943 LRO851906:LSC851943 LHS851906:LIG851943 KXW851906:KYK851943 KOA851906:KOO851943 KEE851906:KES851943 JUI851906:JUW851943 JKM851906:JLA851943 JAQ851906:JBE851943 IQU851906:IRI851943 IGY851906:IHM851943 HXC851906:HXQ851943 HNG851906:HNU851943 HDK851906:HDY851943 GTO851906:GUC851943 GJS851906:GKG851943 FZW851906:GAK851943 FQA851906:FQO851943 FGE851906:FGS851943 EWI851906:EWW851943 EMM851906:ENA851943 ECQ851906:EDE851943 DSU851906:DTI851943 DIY851906:DJM851943 CZC851906:CZQ851943 CPG851906:CPU851943 CFK851906:CFY851943 BVO851906:BWC851943 BLS851906:BMG851943 BBW851906:BCK851943 ASA851906:ASO851943 AIE851906:AIS851943 YI851906:YW851943 OM851906:PA851943 EQ851906:FE851943 WRC786370:WRQ786407 WHG786370:WHU786407 VXK786370:VXY786407 VNO786370:VOC786407 VDS786370:VEG786407 UTW786370:UUK786407 UKA786370:UKO786407 UAE786370:UAS786407 TQI786370:TQW786407 TGM786370:THA786407 SWQ786370:SXE786407 SMU786370:SNI786407 SCY786370:SDM786407 RTC786370:RTQ786407 RJG786370:RJU786407 QZK786370:QZY786407 QPO786370:QQC786407 QFS786370:QGG786407 PVW786370:PWK786407 PMA786370:PMO786407 PCE786370:PCS786407 OSI786370:OSW786407 OIM786370:OJA786407 NYQ786370:NZE786407 NOU786370:NPI786407 NEY786370:NFM786407 MVC786370:MVQ786407 MLG786370:MLU786407 MBK786370:MBY786407 LRO786370:LSC786407 LHS786370:LIG786407 KXW786370:KYK786407 KOA786370:KOO786407 KEE786370:KES786407 JUI786370:JUW786407 JKM786370:JLA786407 JAQ786370:JBE786407 IQU786370:IRI786407 IGY786370:IHM786407 HXC786370:HXQ786407 HNG786370:HNU786407 HDK786370:HDY786407 GTO786370:GUC786407 GJS786370:GKG786407 FZW786370:GAK786407 FQA786370:FQO786407 FGE786370:FGS786407 EWI786370:EWW786407 EMM786370:ENA786407 ECQ786370:EDE786407 DSU786370:DTI786407 DIY786370:DJM786407 CZC786370:CZQ786407 CPG786370:CPU786407 CFK786370:CFY786407 BVO786370:BWC786407 BLS786370:BMG786407 BBW786370:BCK786407 ASA786370:ASO786407 AIE786370:AIS786407 YI786370:YW786407 OM786370:PA786407 EQ786370:FE786407 WRC720834:WRQ720871 WHG720834:WHU720871 VXK720834:VXY720871 VNO720834:VOC720871 VDS720834:VEG720871 UTW720834:UUK720871 UKA720834:UKO720871 UAE720834:UAS720871 TQI720834:TQW720871 TGM720834:THA720871 SWQ720834:SXE720871 SMU720834:SNI720871 SCY720834:SDM720871 RTC720834:RTQ720871 RJG720834:RJU720871 QZK720834:QZY720871 QPO720834:QQC720871 QFS720834:QGG720871 PVW720834:PWK720871 PMA720834:PMO720871 PCE720834:PCS720871 OSI720834:OSW720871 OIM720834:OJA720871 NYQ720834:NZE720871 NOU720834:NPI720871 NEY720834:NFM720871 MVC720834:MVQ720871 MLG720834:MLU720871 MBK720834:MBY720871 LRO720834:LSC720871 LHS720834:LIG720871 KXW720834:KYK720871 KOA720834:KOO720871 KEE720834:KES720871 JUI720834:JUW720871 JKM720834:JLA720871 JAQ720834:JBE720871 IQU720834:IRI720871 IGY720834:IHM720871 HXC720834:HXQ720871 HNG720834:HNU720871 HDK720834:HDY720871 GTO720834:GUC720871 GJS720834:GKG720871 FZW720834:GAK720871 FQA720834:FQO720871 FGE720834:FGS720871 EWI720834:EWW720871 EMM720834:ENA720871 ECQ720834:EDE720871 DSU720834:DTI720871 DIY720834:DJM720871 CZC720834:CZQ720871 CPG720834:CPU720871 CFK720834:CFY720871 BVO720834:BWC720871 BLS720834:BMG720871 BBW720834:BCK720871 ASA720834:ASO720871 AIE720834:AIS720871 YI720834:YW720871 OM720834:PA720871 EQ720834:FE720871 WRC655298:WRQ655335 WHG655298:WHU655335 VXK655298:VXY655335 VNO655298:VOC655335 VDS655298:VEG655335 UTW655298:UUK655335 UKA655298:UKO655335 UAE655298:UAS655335 TQI655298:TQW655335 TGM655298:THA655335 SWQ655298:SXE655335 SMU655298:SNI655335 SCY655298:SDM655335 RTC655298:RTQ655335 RJG655298:RJU655335 QZK655298:QZY655335 QPO655298:QQC655335 QFS655298:QGG655335 PVW655298:PWK655335 PMA655298:PMO655335 PCE655298:PCS655335 OSI655298:OSW655335 OIM655298:OJA655335 NYQ655298:NZE655335 NOU655298:NPI655335 NEY655298:NFM655335 MVC655298:MVQ655335 MLG655298:MLU655335 MBK655298:MBY655335 LRO655298:LSC655335 LHS655298:LIG655335 KXW655298:KYK655335 KOA655298:KOO655335 KEE655298:KES655335 JUI655298:JUW655335 JKM655298:JLA655335 JAQ655298:JBE655335 IQU655298:IRI655335 IGY655298:IHM655335 HXC655298:HXQ655335 HNG655298:HNU655335 HDK655298:HDY655335 GTO655298:GUC655335 GJS655298:GKG655335 FZW655298:GAK655335 FQA655298:FQO655335 FGE655298:FGS655335 EWI655298:EWW655335 EMM655298:ENA655335 ECQ655298:EDE655335 DSU655298:DTI655335 DIY655298:DJM655335 CZC655298:CZQ655335 CPG655298:CPU655335 CFK655298:CFY655335 BVO655298:BWC655335 BLS655298:BMG655335 BBW655298:BCK655335 ASA655298:ASO655335 AIE655298:AIS655335 YI655298:YW655335 OM655298:PA655335 EQ655298:FE655335 WRC589762:WRQ589799 WHG589762:WHU589799 VXK589762:VXY589799 VNO589762:VOC589799 VDS589762:VEG589799 UTW589762:UUK589799 UKA589762:UKO589799 UAE589762:UAS589799 TQI589762:TQW589799 TGM589762:THA589799 SWQ589762:SXE589799 SMU589762:SNI589799 SCY589762:SDM589799 RTC589762:RTQ589799 RJG589762:RJU589799 QZK589762:QZY589799 QPO589762:QQC589799 QFS589762:QGG589799 PVW589762:PWK589799 PMA589762:PMO589799 PCE589762:PCS589799 OSI589762:OSW589799 OIM589762:OJA589799 NYQ589762:NZE589799 NOU589762:NPI589799 NEY589762:NFM589799 MVC589762:MVQ589799 MLG589762:MLU589799 MBK589762:MBY589799 LRO589762:LSC589799 LHS589762:LIG589799 KXW589762:KYK589799 KOA589762:KOO589799 KEE589762:KES589799 JUI589762:JUW589799 JKM589762:JLA589799 JAQ589762:JBE589799 IQU589762:IRI589799 IGY589762:IHM589799 HXC589762:HXQ589799 HNG589762:HNU589799 HDK589762:HDY589799 GTO589762:GUC589799 GJS589762:GKG589799 FZW589762:GAK589799 FQA589762:FQO589799 FGE589762:FGS589799 EWI589762:EWW589799 EMM589762:ENA589799 ECQ589762:EDE589799 DSU589762:DTI589799 DIY589762:DJM589799 CZC589762:CZQ589799 CPG589762:CPU589799 CFK589762:CFY589799 BVO589762:BWC589799 BLS589762:BMG589799 BBW589762:BCK589799 ASA589762:ASO589799 AIE589762:AIS589799 YI589762:YW589799 OM589762:PA589799 EQ589762:FE589799 WRC524226:WRQ524263 WHG524226:WHU524263 VXK524226:VXY524263 VNO524226:VOC524263 VDS524226:VEG524263 UTW524226:UUK524263 UKA524226:UKO524263 UAE524226:UAS524263 TQI524226:TQW524263 TGM524226:THA524263 SWQ524226:SXE524263 SMU524226:SNI524263 SCY524226:SDM524263 RTC524226:RTQ524263 RJG524226:RJU524263 QZK524226:QZY524263 QPO524226:QQC524263 QFS524226:QGG524263 PVW524226:PWK524263 PMA524226:PMO524263 PCE524226:PCS524263 OSI524226:OSW524263 OIM524226:OJA524263 NYQ524226:NZE524263 NOU524226:NPI524263 NEY524226:NFM524263 MVC524226:MVQ524263 MLG524226:MLU524263 MBK524226:MBY524263 LRO524226:LSC524263 LHS524226:LIG524263 KXW524226:KYK524263 KOA524226:KOO524263 KEE524226:KES524263 JUI524226:JUW524263 JKM524226:JLA524263 JAQ524226:JBE524263 IQU524226:IRI524263 IGY524226:IHM524263 HXC524226:HXQ524263 HNG524226:HNU524263 HDK524226:HDY524263 GTO524226:GUC524263 GJS524226:GKG524263 FZW524226:GAK524263 FQA524226:FQO524263 FGE524226:FGS524263 EWI524226:EWW524263 EMM524226:ENA524263 ECQ524226:EDE524263 DSU524226:DTI524263 DIY524226:DJM524263 CZC524226:CZQ524263 CPG524226:CPU524263 CFK524226:CFY524263 BVO524226:BWC524263 BLS524226:BMG524263 BBW524226:BCK524263 ASA524226:ASO524263 AIE524226:AIS524263 YI524226:YW524263 OM524226:PA524263 EQ524226:FE524263 WRC458690:WRQ458727 WHG458690:WHU458727 VXK458690:VXY458727 VNO458690:VOC458727 VDS458690:VEG458727 UTW458690:UUK458727 UKA458690:UKO458727 UAE458690:UAS458727 TQI458690:TQW458727 TGM458690:THA458727 SWQ458690:SXE458727 SMU458690:SNI458727 SCY458690:SDM458727 RTC458690:RTQ458727 RJG458690:RJU458727 QZK458690:QZY458727 QPO458690:QQC458727 QFS458690:QGG458727 PVW458690:PWK458727 PMA458690:PMO458727 PCE458690:PCS458727 OSI458690:OSW458727 OIM458690:OJA458727 NYQ458690:NZE458727 NOU458690:NPI458727 NEY458690:NFM458727 MVC458690:MVQ458727 MLG458690:MLU458727 MBK458690:MBY458727 LRO458690:LSC458727 LHS458690:LIG458727 KXW458690:KYK458727 KOA458690:KOO458727 KEE458690:KES458727 JUI458690:JUW458727 JKM458690:JLA458727 JAQ458690:JBE458727 IQU458690:IRI458727 IGY458690:IHM458727 HXC458690:HXQ458727 HNG458690:HNU458727 HDK458690:HDY458727 GTO458690:GUC458727 GJS458690:GKG458727 FZW458690:GAK458727 FQA458690:FQO458727 FGE458690:FGS458727 EWI458690:EWW458727 EMM458690:ENA458727 ECQ458690:EDE458727 DSU458690:DTI458727 DIY458690:DJM458727 CZC458690:CZQ458727 CPG458690:CPU458727 CFK458690:CFY458727 BVO458690:BWC458727 BLS458690:BMG458727 BBW458690:BCK458727 ASA458690:ASO458727 AIE458690:AIS458727 YI458690:YW458727 OM458690:PA458727 EQ458690:FE458727 WRC393154:WRQ393191 WHG393154:WHU393191 VXK393154:VXY393191 VNO393154:VOC393191 VDS393154:VEG393191 UTW393154:UUK393191 UKA393154:UKO393191 UAE393154:UAS393191 TQI393154:TQW393191 TGM393154:THA393191 SWQ393154:SXE393191 SMU393154:SNI393191 SCY393154:SDM393191 RTC393154:RTQ393191 RJG393154:RJU393191 QZK393154:QZY393191 QPO393154:QQC393191 QFS393154:QGG393191 PVW393154:PWK393191 PMA393154:PMO393191 PCE393154:PCS393191 OSI393154:OSW393191 OIM393154:OJA393191 NYQ393154:NZE393191 NOU393154:NPI393191 NEY393154:NFM393191 MVC393154:MVQ393191 MLG393154:MLU393191 MBK393154:MBY393191 LRO393154:LSC393191 LHS393154:LIG393191 KXW393154:KYK393191 KOA393154:KOO393191 KEE393154:KES393191 JUI393154:JUW393191 JKM393154:JLA393191 JAQ393154:JBE393191 IQU393154:IRI393191 IGY393154:IHM393191 HXC393154:HXQ393191 HNG393154:HNU393191 HDK393154:HDY393191 GTO393154:GUC393191 GJS393154:GKG393191 FZW393154:GAK393191 FQA393154:FQO393191 FGE393154:FGS393191 EWI393154:EWW393191 EMM393154:ENA393191 ECQ393154:EDE393191 DSU393154:DTI393191 DIY393154:DJM393191 CZC393154:CZQ393191 CPG393154:CPU393191 CFK393154:CFY393191 BVO393154:BWC393191 BLS393154:BMG393191 BBW393154:BCK393191 ASA393154:ASO393191 AIE393154:AIS393191 YI393154:YW393191 OM393154:PA393191 EQ393154:FE393191 WRC327618:WRQ327655 WHG327618:WHU327655 VXK327618:VXY327655 VNO327618:VOC327655 VDS327618:VEG327655 UTW327618:UUK327655 UKA327618:UKO327655 UAE327618:UAS327655 TQI327618:TQW327655 TGM327618:THA327655 SWQ327618:SXE327655 SMU327618:SNI327655 SCY327618:SDM327655 RTC327618:RTQ327655 RJG327618:RJU327655 QZK327618:QZY327655 QPO327618:QQC327655 QFS327618:QGG327655 PVW327618:PWK327655 PMA327618:PMO327655 PCE327618:PCS327655 OSI327618:OSW327655 OIM327618:OJA327655 NYQ327618:NZE327655 NOU327618:NPI327655 NEY327618:NFM327655 MVC327618:MVQ327655 MLG327618:MLU327655 MBK327618:MBY327655 LRO327618:LSC327655 LHS327618:LIG327655 KXW327618:KYK327655 KOA327618:KOO327655 KEE327618:KES327655 JUI327618:JUW327655 JKM327618:JLA327655 JAQ327618:JBE327655 IQU327618:IRI327655 IGY327618:IHM327655 HXC327618:HXQ327655 HNG327618:HNU327655 HDK327618:HDY327655 GTO327618:GUC327655 GJS327618:GKG327655 FZW327618:GAK327655 FQA327618:FQO327655 FGE327618:FGS327655 EWI327618:EWW327655 EMM327618:ENA327655 ECQ327618:EDE327655 DSU327618:DTI327655 DIY327618:DJM327655 CZC327618:CZQ327655 CPG327618:CPU327655 CFK327618:CFY327655 BVO327618:BWC327655 BLS327618:BMG327655 BBW327618:BCK327655 ASA327618:ASO327655 AIE327618:AIS327655 YI327618:YW327655 OM327618:PA327655 EQ327618:FE327655 WRC262082:WRQ262119 WHG262082:WHU262119 VXK262082:VXY262119 VNO262082:VOC262119 VDS262082:VEG262119 UTW262082:UUK262119 UKA262082:UKO262119 UAE262082:UAS262119 TQI262082:TQW262119 TGM262082:THA262119 SWQ262082:SXE262119 SMU262082:SNI262119 SCY262082:SDM262119 RTC262082:RTQ262119 RJG262082:RJU262119 QZK262082:QZY262119 QPO262082:QQC262119 QFS262082:QGG262119 PVW262082:PWK262119 PMA262082:PMO262119 PCE262082:PCS262119 OSI262082:OSW262119 OIM262082:OJA262119 NYQ262082:NZE262119 NOU262082:NPI262119 NEY262082:NFM262119 MVC262082:MVQ262119 MLG262082:MLU262119 MBK262082:MBY262119 LRO262082:LSC262119 LHS262082:LIG262119 KXW262082:KYK262119 KOA262082:KOO262119 KEE262082:KES262119 JUI262082:JUW262119 JKM262082:JLA262119 JAQ262082:JBE262119 IQU262082:IRI262119 IGY262082:IHM262119 HXC262082:HXQ262119 HNG262082:HNU262119 HDK262082:HDY262119 GTO262082:GUC262119 GJS262082:GKG262119 FZW262082:GAK262119 FQA262082:FQO262119 FGE262082:FGS262119 EWI262082:EWW262119 EMM262082:ENA262119 ECQ262082:EDE262119 DSU262082:DTI262119 DIY262082:DJM262119 CZC262082:CZQ262119 CPG262082:CPU262119 CFK262082:CFY262119 BVO262082:BWC262119 BLS262082:BMG262119 BBW262082:BCK262119 ASA262082:ASO262119 AIE262082:AIS262119 YI262082:YW262119 OM262082:PA262119 EQ262082:FE262119 WRC196546:WRQ196583 WHG196546:WHU196583 VXK196546:VXY196583 VNO196546:VOC196583 VDS196546:VEG196583 UTW196546:UUK196583 UKA196546:UKO196583 UAE196546:UAS196583 TQI196546:TQW196583 TGM196546:THA196583 SWQ196546:SXE196583 SMU196546:SNI196583 SCY196546:SDM196583 RTC196546:RTQ196583 RJG196546:RJU196583 QZK196546:QZY196583 QPO196546:QQC196583 QFS196546:QGG196583 PVW196546:PWK196583 PMA196546:PMO196583 PCE196546:PCS196583 OSI196546:OSW196583 OIM196546:OJA196583 NYQ196546:NZE196583 NOU196546:NPI196583 NEY196546:NFM196583 MVC196546:MVQ196583 MLG196546:MLU196583 MBK196546:MBY196583 LRO196546:LSC196583 LHS196546:LIG196583 KXW196546:KYK196583 KOA196546:KOO196583 KEE196546:KES196583 JUI196546:JUW196583 JKM196546:JLA196583 JAQ196546:JBE196583 IQU196546:IRI196583 IGY196546:IHM196583 HXC196546:HXQ196583 HNG196546:HNU196583 HDK196546:HDY196583 GTO196546:GUC196583 GJS196546:GKG196583 FZW196546:GAK196583 FQA196546:FQO196583 FGE196546:FGS196583 EWI196546:EWW196583 EMM196546:ENA196583 ECQ196546:EDE196583 DSU196546:DTI196583 DIY196546:DJM196583 CZC196546:CZQ196583 CPG196546:CPU196583 CFK196546:CFY196583 BVO196546:BWC196583 BLS196546:BMG196583 BBW196546:BCK196583 ASA196546:ASO196583 AIE196546:AIS196583 YI196546:YW196583 OM196546:PA196583 EQ196546:FE196583 WRC131010:WRQ131047 WHG131010:WHU131047 VXK131010:VXY131047 VNO131010:VOC131047 VDS131010:VEG131047 UTW131010:UUK131047 UKA131010:UKO131047 UAE131010:UAS131047 TQI131010:TQW131047 TGM131010:THA131047 SWQ131010:SXE131047 SMU131010:SNI131047 SCY131010:SDM131047 RTC131010:RTQ131047 RJG131010:RJU131047 QZK131010:QZY131047 QPO131010:QQC131047 QFS131010:QGG131047 PVW131010:PWK131047 PMA131010:PMO131047 PCE131010:PCS131047 OSI131010:OSW131047 OIM131010:OJA131047 NYQ131010:NZE131047 NOU131010:NPI131047 NEY131010:NFM131047 MVC131010:MVQ131047 MLG131010:MLU131047 MBK131010:MBY131047 LRO131010:LSC131047 LHS131010:LIG131047 KXW131010:KYK131047 KOA131010:KOO131047 KEE131010:KES131047 JUI131010:JUW131047 JKM131010:JLA131047 JAQ131010:JBE131047 IQU131010:IRI131047 IGY131010:IHM131047 HXC131010:HXQ131047 HNG131010:HNU131047 HDK131010:HDY131047 GTO131010:GUC131047 GJS131010:GKG131047 FZW131010:GAK131047 FQA131010:FQO131047 FGE131010:FGS131047 EWI131010:EWW131047 EMM131010:ENA131047 ECQ131010:EDE131047 DSU131010:DTI131047 DIY131010:DJM131047 CZC131010:CZQ131047 CPG131010:CPU131047 CFK131010:CFY131047 BVO131010:BWC131047 BLS131010:BMG131047 BBW131010:BCK131047 ASA131010:ASO131047 AIE131010:AIS131047 YI131010:YW131047 OM131010:PA131047 EQ131010:FE131047 WRC65474:WRQ65511 WHG65474:WHU65511 VXK65474:VXY65511 VNO65474:VOC65511 VDS65474:VEG65511 UTW65474:UUK65511 UKA65474:UKO65511 UAE65474:UAS65511 TQI65474:TQW65511 TGM65474:THA65511 SWQ65474:SXE65511 SMU65474:SNI65511 SCY65474:SDM65511 RTC65474:RTQ65511 RJG65474:RJU65511 QZK65474:QZY65511 QPO65474:QQC65511 QFS65474:QGG65511 PVW65474:PWK65511 PMA65474:PMO65511 PCE65474:PCS65511 OSI65474:OSW65511 OIM65474:OJA65511 NYQ65474:NZE65511 NOU65474:NPI65511 NEY65474:NFM65511 MVC65474:MVQ65511 MLG65474:MLU65511 MBK65474:MBY65511 LRO65474:LSC65511 LHS65474:LIG65511 KXW65474:KYK65511 KOA65474:KOO65511 KEE65474:KES65511 JUI65474:JUW65511 JKM65474:JLA65511 JAQ65474:JBE65511 IQU65474:IRI65511 IGY65474:IHM65511 HXC65474:HXQ65511 HNG65474:HNU65511 HDK65474:HDY65511 GTO65474:GUC65511 GJS65474:GKG65511 FZW65474:GAK65511 FQA65474:FQO65511 FGE65474:FGS65511 EWI65474:EWW65511 EMM65474:ENA65511 ECQ65474:EDE65511 DSU65474:DTI65511 DIY65474:DJM65511 CZC65474:CZQ65511 CPG65474:CPU65511 CFK65474:CFY65511 BVO65474:BWC65511 BLS65474:BMG65511 BBW65474:BCK65511 ASA65474:ASO65511 AIE65474:AIS65511 YI65474:YW65511 OM65474:PA65511 EQ65474:FE65511 WHG982978:WHU983015 VXK982978:VXY983015 VXH2:VXV8 VNL2:VNZ8 VDP2:VED8 UTT2:UUH8 UJX2:UKL8 UAB2:UAP8 TQF2:TQT8 TGJ2:TGX8 SWN2:SXB8 SMR2:SNF8 SCV2:SDJ8 RSZ2:RTN8 RJD2:RJR8 QZH2:QZV8 QPL2:QPZ8 QFP2:QGD8 PVT2:PWH8 PLX2:PML8 PCB2:PCP8 OSF2:OST8 OIJ2:OIX8 NYN2:NZB8 NOR2:NPF8 NEV2:NFJ8 MUZ2:MVN8 MLD2:MLR8 MBH2:MBV8 LRL2:LRZ8 LHP2:LID8 KXT2:KYH8 KNX2:KOL8 KEB2:KEP8 JUF2:JUT8 JKJ2:JKX8 JAN2:JBB8 IQR2:IRF8 IGV2:IHJ8 HWZ2:HXN8 HND2:HNR8 HDH2:HDV8 GTL2:GTZ8 GJP2:GKD8 FZT2:GAH8 FPX2:FQL8 FGB2:FGP8 EWF2:EWT8 EMJ2:EMX8 ECN2:EDB8 DSR2:DTF8 DIV2:DJJ8 CYZ2:CZN8 CPD2:CPR8 CFH2:CFV8 BVL2:BVZ8 BLP2:BMD8 BBT2:BCH8 ARX2:ASL8 AIB2:AIP8 YF2:YT8 OJ2:OX8 EN2:FB8 WQZ2:WRN8 WHD2:WHR8" xr:uid="{6E1062E8-DB94-47CF-976E-796A7CF30995}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FE983021:FL983026 PA983021:PH983026 YW983021:ZD983026 AIS983021:AIZ983026 ASO983021:ASV983026 BCK983021:BCR983026 BMG983021:BMN983026 BWC983021:BWJ983026 CFY983021:CGF983026 CPU983021:CQB983026 CZQ983021:CZX983026 DJM983021:DJT983026 DTI983021:DTP983026 EDE983021:EDL983026 ENA983021:ENH983026 EWW983021:EXD983026 FGS983021:FGZ983026 FQO983021:FQV983026 GAK983021:GAR983026 GKG983021:GKN983026 GUC983021:GUJ983026 HDY983021:HEF983026 HNU983021:HOB983026 HXQ983021:HXX983026 IHM983021:IHT983026 IRI983021:IRP983026 JBE983021:JBL983026 JLA983021:JLH983026 JUW983021:JVD983026 KES983021:KEZ983026 KOO983021:KOV983026 KYK983021:KYR983026 LIG983021:LIN983026 LSC983021:LSJ983026 MBY983021:MCF983026 MLU983021:MMB983026 MVQ983021:MVX983026 NFM983021:NFT983026 NPI983021:NPP983026 NZE983021:NZL983026 OJA983021:OJH983026 OSW983021:OTD983026 PCS983021:PCZ983026 PMO983021:PMV983026 PWK983021:PWR983026 QGG983021:QGN983026 QQC983021:QQJ983026 QZY983021:RAF983026 RJU983021:RKB983026 RTQ983021:RTX983026 SDM983021:SDT983026 SNI983021:SNP983026 SXE983021:SXL983026 THA983021:THH983026 TQW983021:TRD983026 UAS983021:UAZ983026 UKO983021:UKV983026 UUK983021:UUR983026 VEG983021:VEN983026 VOC983021:VOJ983026 VXY983021:VYF983026 WHU983021:WIB983026 WRQ983021:WRX983026 FE65517:FL65522 PA65517:PH65522 YW65517:ZD65522 AIS65517:AIZ65522 ASO65517:ASV65522 BCK65517:BCR65522 BMG65517:BMN65522 BWC65517:BWJ65522 CFY65517:CGF65522 CPU65517:CQB65522 CZQ65517:CZX65522 DJM65517:DJT65522 DTI65517:DTP65522 EDE65517:EDL65522 ENA65517:ENH65522 EWW65517:EXD65522 FGS65517:FGZ65522 FQO65517:FQV65522 GAK65517:GAR65522 GKG65517:GKN65522 GUC65517:GUJ65522 HDY65517:HEF65522 HNU65517:HOB65522 HXQ65517:HXX65522 IHM65517:IHT65522 IRI65517:IRP65522 JBE65517:JBL65522 JLA65517:JLH65522 JUW65517:JVD65522 KES65517:KEZ65522 KOO65517:KOV65522 KYK65517:KYR65522 LIG65517:LIN65522 LSC65517:LSJ65522 MBY65517:MCF65522 MLU65517:MMB65522 MVQ65517:MVX65522 NFM65517:NFT65522 NPI65517:NPP65522 NZE65517:NZL65522 OJA65517:OJH65522 OSW65517:OTD65522 PCS65517:PCZ65522 PMO65517:PMV65522 PWK65517:PWR65522 QGG65517:QGN65522 QQC65517:QQJ65522 QZY65517:RAF65522 RJU65517:RKB65522 RTQ65517:RTX65522 SDM65517:SDT65522 SNI65517:SNP65522 SXE65517:SXL65522 THA65517:THH65522 TQW65517:TRD65522 UAS65517:UAZ65522 UKO65517:UKV65522 UUK65517:UUR65522 VEG65517:VEN65522 VOC65517:VOJ65522 VXY65517:VYF65522 WHU65517:WIB65522 WRQ65517:WRX65522 FE131053:FL131058 PA131053:PH131058 YW131053:ZD131058 AIS131053:AIZ131058 ASO131053:ASV131058 BCK131053:BCR131058 BMG131053:BMN131058 BWC131053:BWJ131058 CFY131053:CGF131058 CPU131053:CQB131058 CZQ131053:CZX131058 DJM131053:DJT131058 DTI131053:DTP131058 EDE131053:EDL131058 ENA131053:ENH131058 EWW131053:EXD131058 FGS131053:FGZ131058 FQO131053:FQV131058 GAK131053:GAR131058 GKG131053:GKN131058 GUC131053:GUJ131058 HDY131053:HEF131058 HNU131053:HOB131058 HXQ131053:HXX131058 IHM131053:IHT131058 IRI131053:IRP131058 JBE131053:JBL131058 JLA131053:JLH131058 JUW131053:JVD131058 KES131053:KEZ131058 KOO131053:KOV131058 KYK131053:KYR131058 LIG131053:LIN131058 LSC131053:LSJ131058 MBY131053:MCF131058 MLU131053:MMB131058 MVQ131053:MVX131058 NFM131053:NFT131058 NPI131053:NPP131058 NZE131053:NZL131058 OJA131053:OJH131058 OSW131053:OTD131058 PCS131053:PCZ131058 PMO131053:PMV131058 PWK131053:PWR131058 QGG131053:QGN131058 QQC131053:QQJ131058 QZY131053:RAF131058 RJU131053:RKB131058 RTQ131053:RTX131058 SDM131053:SDT131058 SNI131053:SNP131058 SXE131053:SXL131058 THA131053:THH131058 TQW131053:TRD131058 UAS131053:UAZ131058 UKO131053:UKV131058 UUK131053:UUR131058 VEG131053:VEN131058 VOC131053:VOJ131058 VXY131053:VYF131058 WHU131053:WIB131058 WRQ131053:WRX131058 FE196589:FL196594 PA196589:PH196594 YW196589:ZD196594 AIS196589:AIZ196594 ASO196589:ASV196594 BCK196589:BCR196594 BMG196589:BMN196594 BWC196589:BWJ196594 CFY196589:CGF196594 CPU196589:CQB196594 CZQ196589:CZX196594 DJM196589:DJT196594 DTI196589:DTP196594 EDE196589:EDL196594 ENA196589:ENH196594 EWW196589:EXD196594 FGS196589:FGZ196594 FQO196589:FQV196594 GAK196589:GAR196594 GKG196589:GKN196594 GUC196589:GUJ196594 HDY196589:HEF196594 HNU196589:HOB196594 HXQ196589:HXX196594 IHM196589:IHT196594 IRI196589:IRP196594 JBE196589:JBL196594 JLA196589:JLH196594 JUW196589:JVD196594 KES196589:KEZ196594 KOO196589:KOV196594 KYK196589:KYR196594 LIG196589:LIN196594 LSC196589:LSJ196594 MBY196589:MCF196594 MLU196589:MMB196594 MVQ196589:MVX196594 NFM196589:NFT196594 NPI196589:NPP196594 NZE196589:NZL196594 OJA196589:OJH196594 OSW196589:OTD196594 PCS196589:PCZ196594 PMO196589:PMV196594 PWK196589:PWR196594 QGG196589:QGN196594 QQC196589:QQJ196594 QZY196589:RAF196594 RJU196589:RKB196594 RTQ196589:RTX196594 SDM196589:SDT196594 SNI196589:SNP196594 SXE196589:SXL196594 THA196589:THH196594 TQW196589:TRD196594 UAS196589:UAZ196594 UKO196589:UKV196594 UUK196589:UUR196594 VEG196589:VEN196594 VOC196589:VOJ196594 VXY196589:VYF196594 WHU196589:WIB196594 WRQ196589:WRX196594 FE262125:FL262130 PA262125:PH262130 YW262125:ZD262130 AIS262125:AIZ262130 ASO262125:ASV262130 BCK262125:BCR262130 BMG262125:BMN262130 BWC262125:BWJ262130 CFY262125:CGF262130 CPU262125:CQB262130 CZQ262125:CZX262130 DJM262125:DJT262130 DTI262125:DTP262130 EDE262125:EDL262130 ENA262125:ENH262130 EWW262125:EXD262130 FGS262125:FGZ262130 FQO262125:FQV262130 GAK262125:GAR262130 GKG262125:GKN262130 GUC262125:GUJ262130 HDY262125:HEF262130 HNU262125:HOB262130 HXQ262125:HXX262130 IHM262125:IHT262130 IRI262125:IRP262130 JBE262125:JBL262130 JLA262125:JLH262130 JUW262125:JVD262130 KES262125:KEZ262130 KOO262125:KOV262130 KYK262125:KYR262130 LIG262125:LIN262130 LSC262125:LSJ262130 MBY262125:MCF262130 MLU262125:MMB262130 MVQ262125:MVX262130 NFM262125:NFT262130 NPI262125:NPP262130 NZE262125:NZL262130 OJA262125:OJH262130 OSW262125:OTD262130 PCS262125:PCZ262130 PMO262125:PMV262130 PWK262125:PWR262130 QGG262125:QGN262130 QQC262125:QQJ262130 QZY262125:RAF262130 RJU262125:RKB262130 RTQ262125:RTX262130 SDM262125:SDT262130 SNI262125:SNP262130 SXE262125:SXL262130 THA262125:THH262130 TQW262125:TRD262130 UAS262125:UAZ262130 UKO262125:UKV262130 UUK262125:UUR262130 VEG262125:VEN262130 VOC262125:VOJ262130 VXY262125:VYF262130 WHU262125:WIB262130 WRQ262125:WRX262130 FE327661:FL327666 PA327661:PH327666 YW327661:ZD327666 AIS327661:AIZ327666 ASO327661:ASV327666 BCK327661:BCR327666 BMG327661:BMN327666 BWC327661:BWJ327666 CFY327661:CGF327666 CPU327661:CQB327666 CZQ327661:CZX327666 DJM327661:DJT327666 DTI327661:DTP327666 EDE327661:EDL327666 ENA327661:ENH327666 EWW327661:EXD327666 FGS327661:FGZ327666 FQO327661:FQV327666 GAK327661:GAR327666 GKG327661:GKN327666 GUC327661:GUJ327666 HDY327661:HEF327666 HNU327661:HOB327666 HXQ327661:HXX327666 IHM327661:IHT327666 IRI327661:IRP327666 JBE327661:JBL327666 JLA327661:JLH327666 JUW327661:JVD327666 KES327661:KEZ327666 KOO327661:KOV327666 KYK327661:KYR327666 LIG327661:LIN327666 LSC327661:LSJ327666 MBY327661:MCF327666 MLU327661:MMB327666 MVQ327661:MVX327666 NFM327661:NFT327666 NPI327661:NPP327666 NZE327661:NZL327666 OJA327661:OJH327666 OSW327661:OTD327666 PCS327661:PCZ327666 PMO327661:PMV327666 PWK327661:PWR327666 QGG327661:QGN327666 QQC327661:QQJ327666 QZY327661:RAF327666 RJU327661:RKB327666 RTQ327661:RTX327666 SDM327661:SDT327666 SNI327661:SNP327666 SXE327661:SXL327666 THA327661:THH327666 TQW327661:TRD327666 UAS327661:UAZ327666 UKO327661:UKV327666 UUK327661:UUR327666 VEG327661:VEN327666 VOC327661:VOJ327666 VXY327661:VYF327666 WHU327661:WIB327666 WRQ327661:WRX327666 FE393197:FL393202 PA393197:PH393202 YW393197:ZD393202 AIS393197:AIZ393202 ASO393197:ASV393202 BCK393197:BCR393202 BMG393197:BMN393202 BWC393197:BWJ393202 CFY393197:CGF393202 CPU393197:CQB393202 CZQ393197:CZX393202 DJM393197:DJT393202 DTI393197:DTP393202 EDE393197:EDL393202 ENA393197:ENH393202 EWW393197:EXD393202 FGS393197:FGZ393202 FQO393197:FQV393202 GAK393197:GAR393202 GKG393197:GKN393202 GUC393197:GUJ393202 HDY393197:HEF393202 HNU393197:HOB393202 HXQ393197:HXX393202 IHM393197:IHT393202 IRI393197:IRP393202 JBE393197:JBL393202 JLA393197:JLH393202 JUW393197:JVD393202 KES393197:KEZ393202 KOO393197:KOV393202 KYK393197:KYR393202 LIG393197:LIN393202 LSC393197:LSJ393202 MBY393197:MCF393202 MLU393197:MMB393202 MVQ393197:MVX393202 NFM393197:NFT393202 NPI393197:NPP393202 NZE393197:NZL393202 OJA393197:OJH393202 OSW393197:OTD393202 PCS393197:PCZ393202 PMO393197:PMV393202 PWK393197:PWR393202 QGG393197:QGN393202 QQC393197:QQJ393202 QZY393197:RAF393202 RJU393197:RKB393202 RTQ393197:RTX393202 SDM393197:SDT393202 SNI393197:SNP393202 SXE393197:SXL393202 THA393197:THH393202 TQW393197:TRD393202 UAS393197:UAZ393202 UKO393197:UKV393202 UUK393197:UUR393202 VEG393197:VEN393202 VOC393197:VOJ393202 VXY393197:VYF393202 WHU393197:WIB393202 WRQ393197:WRX393202 FE458733:FL458738 PA458733:PH458738 YW458733:ZD458738 AIS458733:AIZ458738 ASO458733:ASV458738 BCK458733:BCR458738 BMG458733:BMN458738 BWC458733:BWJ458738 CFY458733:CGF458738 CPU458733:CQB458738 CZQ458733:CZX458738 DJM458733:DJT458738 DTI458733:DTP458738 EDE458733:EDL458738 ENA458733:ENH458738 EWW458733:EXD458738 FGS458733:FGZ458738 FQO458733:FQV458738 GAK458733:GAR458738 GKG458733:GKN458738 GUC458733:GUJ458738 HDY458733:HEF458738 HNU458733:HOB458738 HXQ458733:HXX458738 IHM458733:IHT458738 IRI458733:IRP458738 JBE458733:JBL458738 JLA458733:JLH458738 JUW458733:JVD458738 KES458733:KEZ458738 KOO458733:KOV458738 KYK458733:KYR458738 LIG458733:LIN458738 LSC458733:LSJ458738 MBY458733:MCF458738 MLU458733:MMB458738 MVQ458733:MVX458738 NFM458733:NFT458738 NPI458733:NPP458738 NZE458733:NZL458738 OJA458733:OJH458738 OSW458733:OTD458738 PCS458733:PCZ458738 PMO458733:PMV458738 PWK458733:PWR458738 QGG458733:QGN458738 QQC458733:QQJ458738 QZY458733:RAF458738 RJU458733:RKB458738 RTQ458733:RTX458738 SDM458733:SDT458738 SNI458733:SNP458738 SXE458733:SXL458738 THA458733:THH458738 TQW458733:TRD458738 UAS458733:UAZ458738 UKO458733:UKV458738 UUK458733:UUR458738 VEG458733:VEN458738 VOC458733:VOJ458738 VXY458733:VYF458738 WHU458733:WIB458738 WRQ458733:WRX458738 FE524269:FL524274 PA524269:PH524274 YW524269:ZD524274 AIS524269:AIZ524274 ASO524269:ASV524274 BCK524269:BCR524274 BMG524269:BMN524274 BWC524269:BWJ524274 CFY524269:CGF524274 CPU524269:CQB524274 CZQ524269:CZX524274 DJM524269:DJT524274 DTI524269:DTP524274 EDE524269:EDL524274 ENA524269:ENH524274 EWW524269:EXD524274 FGS524269:FGZ524274 FQO524269:FQV524274 GAK524269:GAR524274 GKG524269:GKN524274 GUC524269:GUJ524274 HDY524269:HEF524274 HNU524269:HOB524274 HXQ524269:HXX524274 IHM524269:IHT524274 IRI524269:IRP524274 JBE524269:JBL524274 JLA524269:JLH524274 JUW524269:JVD524274 KES524269:KEZ524274 KOO524269:KOV524274 KYK524269:KYR524274 LIG524269:LIN524274 LSC524269:LSJ524274 MBY524269:MCF524274 MLU524269:MMB524274 MVQ524269:MVX524274 NFM524269:NFT524274 NPI524269:NPP524274 NZE524269:NZL524274 OJA524269:OJH524274 OSW524269:OTD524274 PCS524269:PCZ524274 PMO524269:PMV524274 PWK524269:PWR524274 QGG524269:QGN524274 QQC524269:QQJ524274 QZY524269:RAF524274 RJU524269:RKB524274 RTQ524269:RTX524274 SDM524269:SDT524274 SNI524269:SNP524274 SXE524269:SXL524274 THA524269:THH524274 TQW524269:TRD524274 UAS524269:UAZ524274 UKO524269:UKV524274 UUK524269:UUR524274 VEG524269:VEN524274 VOC524269:VOJ524274 VXY524269:VYF524274 WHU524269:WIB524274 WRQ524269:WRX524274 FE589805:FL589810 PA589805:PH589810 YW589805:ZD589810 AIS589805:AIZ589810 ASO589805:ASV589810 BCK589805:BCR589810 BMG589805:BMN589810 BWC589805:BWJ589810 CFY589805:CGF589810 CPU589805:CQB589810 CZQ589805:CZX589810 DJM589805:DJT589810 DTI589805:DTP589810 EDE589805:EDL589810 ENA589805:ENH589810 EWW589805:EXD589810 FGS589805:FGZ589810 FQO589805:FQV589810 GAK589805:GAR589810 GKG589805:GKN589810 GUC589805:GUJ589810 HDY589805:HEF589810 HNU589805:HOB589810 HXQ589805:HXX589810 IHM589805:IHT589810 IRI589805:IRP589810 JBE589805:JBL589810 JLA589805:JLH589810 JUW589805:JVD589810 KES589805:KEZ589810 KOO589805:KOV589810 KYK589805:KYR589810 LIG589805:LIN589810 LSC589805:LSJ589810 MBY589805:MCF589810 MLU589805:MMB589810 MVQ589805:MVX589810 NFM589805:NFT589810 NPI589805:NPP589810 NZE589805:NZL589810 OJA589805:OJH589810 OSW589805:OTD589810 PCS589805:PCZ589810 PMO589805:PMV589810 PWK589805:PWR589810 QGG589805:QGN589810 QQC589805:QQJ589810 QZY589805:RAF589810 RJU589805:RKB589810 RTQ589805:RTX589810 SDM589805:SDT589810 SNI589805:SNP589810 SXE589805:SXL589810 THA589805:THH589810 TQW589805:TRD589810 UAS589805:UAZ589810 UKO589805:UKV589810 UUK589805:UUR589810 VEG589805:VEN589810 VOC589805:VOJ589810 VXY589805:VYF589810 WHU589805:WIB589810 WRQ589805:WRX589810 FE655341:FL655346 PA655341:PH655346 YW655341:ZD655346 AIS655341:AIZ655346 ASO655341:ASV655346 BCK655341:BCR655346 BMG655341:BMN655346 BWC655341:BWJ655346 CFY655341:CGF655346 CPU655341:CQB655346 CZQ655341:CZX655346 DJM655341:DJT655346 DTI655341:DTP655346 EDE655341:EDL655346 ENA655341:ENH655346 EWW655341:EXD655346 FGS655341:FGZ655346 FQO655341:FQV655346 GAK655341:GAR655346 GKG655341:GKN655346 GUC655341:GUJ655346 HDY655341:HEF655346 HNU655341:HOB655346 HXQ655341:HXX655346 IHM655341:IHT655346 IRI655341:IRP655346 JBE655341:JBL655346 JLA655341:JLH655346 JUW655341:JVD655346 KES655341:KEZ655346 KOO655341:KOV655346 KYK655341:KYR655346 LIG655341:LIN655346 LSC655341:LSJ655346 MBY655341:MCF655346 MLU655341:MMB655346 MVQ655341:MVX655346 NFM655341:NFT655346 NPI655341:NPP655346 NZE655341:NZL655346 OJA655341:OJH655346 OSW655341:OTD655346 PCS655341:PCZ655346 PMO655341:PMV655346 PWK655341:PWR655346 QGG655341:QGN655346 QQC655341:QQJ655346 QZY655341:RAF655346 RJU655341:RKB655346 RTQ655341:RTX655346 SDM655341:SDT655346 SNI655341:SNP655346 SXE655341:SXL655346 THA655341:THH655346 TQW655341:TRD655346 UAS655341:UAZ655346 UKO655341:UKV655346 UUK655341:UUR655346 VEG655341:VEN655346 VOC655341:VOJ655346 VXY655341:VYF655346 WHU655341:WIB655346 WRQ655341:WRX655346 FE720877:FL720882 PA720877:PH720882 YW720877:ZD720882 AIS720877:AIZ720882 ASO720877:ASV720882 BCK720877:BCR720882 BMG720877:BMN720882 BWC720877:BWJ720882 CFY720877:CGF720882 CPU720877:CQB720882 CZQ720877:CZX720882 DJM720877:DJT720882 DTI720877:DTP720882 EDE720877:EDL720882 ENA720877:ENH720882 EWW720877:EXD720882 FGS720877:FGZ720882 FQO720877:FQV720882 GAK720877:GAR720882 GKG720877:GKN720882 GUC720877:GUJ720882 HDY720877:HEF720882 HNU720877:HOB720882 HXQ720877:HXX720882 IHM720877:IHT720882 IRI720877:IRP720882 JBE720877:JBL720882 JLA720877:JLH720882 JUW720877:JVD720882 KES720877:KEZ720882 KOO720877:KOV720882 KYK720877:KYR720882 LIG720877:LIN720882 LSC720877:LSJ720882 MBY720877:MCF720882 MLU720877:MMB720882 MVQ720877:MVX720882 NFM720877:NFT720882 NPI720877:NPP720882 NZE720877:NZL720882 OJA720877:OJH720882 OSW720877:OTD720882 PCS720877:PCZ720882 PMO720877:PMV720882 PWK720877:PWR720882 QGG720877:QGN720882 QQC720877:QQJ720882 QZY720877:RAF720882 RJU720877:RKB720882 RTQ720877:RTX720882 SDM720877:SDT720882 SNI720877:SNP720882 SXE720877:SXL720882 THA720877:THH720882 TQW720877:TRD720882 UAS720877:UAZ720882 UKO720877:UKV720882 UUK720877:UUR720882 VEG720877:VEN720882 VOC720877:VOJ720882 VXY720877:VYF720882 WHU720877:WIB720882 WRQ720877:WRX720882 FE786413:FL786418 PA786413:PH786418 YW786413:ZD786418 AIS786413:AIZ786418 ASO786413:ASV786418 BCK786413:BCR786418 BMG786413:BMN786418 BWC786413:BWJ786418 CFY786413:CGF786418 CPU786413:CQB786418 CZQ786413:CZX786418 DJM786413:DJT786418 DTI786413:DTP786418 EDE786413:EDL786418 ENA786413:ENH786418 EWW786413:EXD786418 FGS786413:FGZ786418 FQO786413:FQV786418 GAK786413:GAR786418 GKG786413:GKN786418 GUC786413:GUJ786418 HDY786413:HEF786418 HNU786413:HOB786418 HXQ786413:HXX786418 IHM786413:IHT786418 IRI786413:IRP786418 JBE786413:JBL786418 JLA786413:JLH786418 JUW786413:JVD786418 KES786413:KEZ786418 KOO786413:KOV786418 KYK786413:KYR786418 LIG786413:LIN786418 LSC786413:LSJ786418 MBY786413:MCF786418 MLU786413:MMB786418 MVQ786413:MVX786418 NFM786413:NFT786418 NPI786413:NPP786418 NZE786413:NZL786418 OJA786413:OJH786418 OSW786413:OTD786418 PCS786413:PCZ786418 PMO786413:PMV786418 PWK786413:PWR786418 QGG786413:QGN786418 QQC786413:QQJ786418 QZY786413:RAF786418 RJU786413:RKB786418 RTQ786413:RTX786418 SDM786413:SDT786418 SNI786413:SNP786418 SXE786413:SXL786418 THA786413:THH786418 TQW786413:TRD786418 UAS786413:UAZ786418 UKO786413:UKV786418 UUK786413:UUR786418 VEG786413:VEN786418 VOC786413:VOJ786418 VXY786413:VYF786418 WHU786413:WIB786418 WRQ786413:WRX786418 FE851949:FL851954 PA851949:PH851954 YW851949:ZD851954 AIS851949:AIZ851954 ASO851949:ASV851954 BCK851949:BCR851954 BMG851949:BMN851954 BWC851949:BWJ851954 CFY851949:CGF851954 CPU851949:CQB851954 CZQ851949:CZX851954 DJM851949:DJT851954 DTI851949:DTP851954 EDE851949:EDL851954 ENA851949:ENH851954 EWW851949:EXD851954 FGS851949:FGZ851954 FQO851949:FQV851954 GAK851949:GAR851954 GKG851949:GKN851954 GUC851949:GUJ851954 HDY851949:HEF851954 HNU851949:HOB851954 HXQ851949:HXX851954 IHM851949:IHT851954 IRI851949:IRP851954 JBE851949:JBL851954 JLA851949:JLH851954 JUW851949:JVD851954 KES851949:KEZ851954 KOO851949:KOV851954 KYK851949:KYR851954 LIG851949:LIN851954 LSC851949:LSJ851954 MBY851949:MCF851954 MLU851949:MMB851954 MVQ851949:MVX851954 NFM851949:NFT851954 NPI851949:NPP851954 NZE851949:NZL851954 OJA851949:OJH851954 OSW851949:OTD851954 PCS851949:PCZ851954 PMO851949:PMV851954 PWK851949:PWR851954 QGG851949:QGN851954 QQC851949:QQJ851954 QZY851949:RAF851954 RJU851949:RKB851954 RTQ851949:RTX851954 SDM851949:SDT851954 SNI851949:SNP851954 SXE851949:SXL851954 THA851949:THH851954 TQW851949:TRD851954 UAS851949:UAZ851954 UKO851949:UKV851954 UUK851949:UUR851954 VEG851949:VEN851954 VOC851949:VOJ851954 VXY851949:VYF851954 WHU851949:WIB851954 WRQ851949:WRX851954 FE917485:FL917490 PA917485:PH917490 YW917485:ZD917490 AIS917485:AIZ917490 ASO917485:ASV917490 BCK917485:BCR917490 BMG917485:BMN917490 BWC917485:BWJ917490 CFY917485:CGF917490 CPU917485:CQB917490 CZQ917485:CZX917490 DJM917485:DJT917490 DTI917485:DTP917490 EDE917485:EDL917490 ENA917485:ENH917490 EWW917485:EXD917490 FGS917485:FGZ917490 FQO917485:FQV917490 GAK917485:GAR917490 GKG917485:GKN917490 GUC917485:GUJ917490 HDY917485:HEF917490 HNU917485:HOB917490 HXQ917485:HXX917490 IHM917485:IHT917490 IRI917485:IRP917490 JBE917485:JBL917490 JLA917485:JLH917490 JUW917485:JVD917490 KES917485:KEZ917490 KOO917485:KOV917490 KYK917485:KYR917490 LIG917485:LIN917490 LSC917485:LSJ917490 MBY917485:MCF917490 MLU917485:MMB917490 MVQ917485:MVX917490 NFM917485:NFT917490 NPI917485:NPP917490 NZE917485:NZL917490 OJA917485:OJH917490 OSW917485:OTD917490 PCS917485:PCZ917490 PMO917485:PMV917490 PWK917485:PWR917490 QGG917485:QGN917490 QQC917485:QQJ917490 QZY917485:RAF917490 RJU917485:RKB917490 RTQ917485:RTX917490 SDM917485:SDT917490 SNI917485:SNP917490 SXE917485:SXL917490 THA917485:THH917490 TQW917485:TRD917490 UAS917485:UAZ917490 UKO917485:UKV917490 UUK917485:UUR917490 VEG917485:VEN917490 VOC917485:VOJ917490 VXY917485:VYF917490 WHU917485:WIB917490 WRQ917485:WRX917490" xr:uid="{FAB87F88-CF7B-481E-835D-3D47857FF214}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FE983019:FL983024 PA983019:PH983024 YW983019:ZD983024 AIS983019:AIZ983024 ASO983019:ASV983024 BCK983019:BCR983024 BMG983019:BMN983024 BWC983019:BWJ983024 CFY983019:CGF983024 CPU983019:CQB983024 CZQ983019:CZX983024 DJM983019:DJT983024 DTI983019:DTP983024 EDE983019:EDL983024 ENA983019:ENH983024 EWW983019:EXD983024 FGS983019:FGZ983024 FQO983019:FQV983024 GAK983019:GAR983024 GKG983019:GKN983024 GUC983019:GUJ983024 HDY983019:HEF983024 HNU983019:HOB983024 HXQ983019:HXX983024 IHM983019:IHT983024 IRI983019:IRP983024 JBE983019:JBL983024 JLA983019:JLH983024 JUW983019:JVD983024 KES983019:KEZ983024 KOO983019:KOV983024 KYK983019:KYR983024 LIG983019:LIN983024 LSC983019:LSJ983024 MBY983019:MCF983024 MLU983019:MMB983024 MVQ983019:MVX983024 NFM983019:NFT983024 NPI983019:NPP983024 NZE983019:NZL983024 OJA983019:OJH983024 OSW983019:OTD983024 PCS983019:PCZ983024 PMO983019:PMV983024 PWK983019:PWR983024 QGG983019:QGN983024 QQC983019:QQJ983024 QZY983019:RAF983024 RJU983019:RKB983024 RTQ983019:RTX983024 SDM983019:SDT983024 SNI983019:SNP983024 SXE983019:SXL983024 THA983019:THH983024 TQW983019:TRD983024 UAS983019:UAZ983024 UKO983019:UKV983024 UUK983019:UUR983024 VEG983019:VEN983024 VOC983019:VOJ983024 VXY983019:VYF983024 WHU983019:WIB983024 WRQ983019:WRX983024 FE65515:FL65520 PA65515:PH65520 YW65515:ZD65520 AIS65515:AIZ65520 ASO65515:ASV65520 BCK65515:BCR65520 BMG65515:BMN65520 BWC65515:BWJ65520 CFY65515:CGF65520 CPU65515:CQB65520 CZQ65515:CZX65520 DJM65515:DJT65520 DTI65515:DTP65520 EDE65515:EDL65520 ENA65515:ENH65520 EWW65515:EXD65520 FGS65515:FGZ65520 FQO65515:FQV65520 GAK65515:GAR65520 GKG65515:GKN65520 GUC65515:GUJ65520 HDY65515:HEF65520 HNU65515:HOB65520 HXQ65515:HXX65520 IHM65515:IHT65520 IRI65515:IRP65520 JBE65515:JBL65520 JLA65515:JLH65520 JUW65515:JVD65520 KES65515:KEZ65520 KOO65515:KOV65520 KYK65515:KYR65520 LIG65515:LIN65520 LSC65515:LSJ65520 MBY65515:MCF65520 MLU65515:MMB65520 MVQ65515:MVX65520 NFM65515:NFT65520 NPI65515:NPP65520 NZE65515:NZL65520 OJA65515:OJH65520 OSW65515:OTD65520 PCS65515:PCZ65520 PMO65515:PMV65520 PWK65515:PWR65520 QGG65515:QGN65520 QQC65515:QQJ65520 QZY65515:RAF65520 RJU65515:RKB65520 RTQ65515:RTX65520 SDM65515:SDT65520 SNI65515:SNP65520 SXE65515:SXL65520 THA65515:THH65520 TQW65515:TRD65520 UAS65515:UAZ65520 UKO65515:UKV65520 UUK65515:UUR65520 VEG65515:VEN65520 VOC65515:VOJ65520 VXY65515:VYF65520 WHU65515:WIB65520 WRQ65515:WRX65520 FE131051:FL131056 PA131051:PH131056 YW131051:ZD131056 AIS131051:AIZ131056 ASO131051:ASV131056 BCK131051:BCR131056 BMG131051:BMN131056 BWC131051:BWJ131056 CFY131051:CGF131056 CPU131051:CQB131056 CZQ131051:CZX131056 DJM131051:DJT131056 DTI131051:DTP131056 EDE131051:EDL131056 ENA131051:ENH131056 EWW131051:EXD131056 FGS131051:FGZ131056 FQO131051:FQV131056 GAK131051:GAR131056 GKG131051:GKN131056 GUC131051:GUJ131056 HDY131051:HEF131056 HNU131051:HOB131056 HXQ131051:HXX131056 IHM131051:IHT131056 IRI131051:IRP131056 JBE131051:JBL131056 JLA131051:JLH131056 JUW131051:JVD131056 KES131051:KEZ131056 KOO131051:KOV131056 KYK131051:KYR131056 LIG131051:LIN131056 LSC131051:LSJ131056 MBY131051:MCF131056 MLU131051:MMB131056 MVQ131051:MVX131056 NFM131051:NFT131056 NPI131051:NPP131056 NZE131051:NZL131056 OJA131051:OJH131056 OSW131051:OTD131056 PCS131051:PCZ131056 PMO131051:PMV131056 PWK131051:PWR131056 QGG131051:QGN131056 QQC131051:QQJ131056 QZY131051:RAF131056 RJU131051:RKB131056 RTQ131051:RTX131056 SDM131051:SDT131056 SNI131051:SNP131056 SXE131051:SXL131056 THA131051:THH131056 TQW131051:TRD131056 UAS131051:UAZ131056 UKO131051:UKV131056 UUK131051:UUR131056 VEG131051:VEN131056 VOC131051:VOJ131056 VXY131051:VYF131056 WHU131051:WIB131056 WRQ131051:WRX131056 FE196587:FL196592 PA196587:PH196592 YW196587:ZD196592 AIS196587:AIZ196592 ASO196587:ASV196592 BCK196587:BCR196592 BMG196587:BMN196592 BWC196587:BWJ196592 CFY196587:CGF196592 CPU196587:CQB196592 CZQ196587:CZX196592 DJM196587:DJT196592 DTI196587:DTP196592 EDE196587:EDL196592 ENA196587:ENH196592 EWW196587:EXD196592 FGS196587:FGZ196592 FQO196587:FQV196592 GAK196587:GAR196592 GKG196587:GKN196592 GUC196587:GUJ196592 HDY196587:HEF196592 HNU196587:HOB196592 HXQ196587:HXX196592 IHM196587:IHT196592 IRI196587:IRP196592 JBE196587:JBL196592 JLA196587:JLH196592 JUW196587:JVD196592 KES196587:KEZ196592 KOO196587:KOV196592 KYK196587:KYR196592 LIG196587:LIN196592 LSC196587:LSJ196592 MBY196587:MCF196592 MLU196587:MMB196592 MVQ196587:MVX196592 NFM196587:NFT196592 NPI196587:NPP196592 NZE196587:NZL196592 OJA196587:OJH196592 OSW196587:OTD196592 PCS196587:PCZ196592 PMO196587:PMV196592 PWK196587:PWR196592 QGG196587:QGN196592 QQC196587:QQJ196592 QZY196587:RAF196592 RJU196587:RKB196592 RTQ196587:RTX196592 SDM196587:SDT196592 SNI196587:SNP196592 SXE196587:SXL196592 THA196587:THH196592 TQW196587:TRD196592 UAS196587:UAZ196592 UKO196587:UKV196592 UUK196587:UUR196592 VEG196587:VEN196592 VOC196587:VOJ196592 VXY196587:VYF196592 WHU196587:WIB196592 WRQ196587:WRX196592 FE262123:FL262128 PA262123:PH262128 YW262123:ZD262128 AIS262123:AIZ262128 ASO262123:ASV262128 BCK262123:BCR262128 BMG262123:BMN262128 BWC262123:BWJ262128 CFY262123:CGF262128 CPU262123:CQB262128 CZQ262123:CZX262128 DJM262123:DJT262128 DTI262123:DTP262128 EDE262123:EDL262128 ENA262123:ENH262128 EWW262123:EXD262128 FGS262123:FGZ262128 FQO262123:FQV262128 GAK262123:GAR262128 GKG262123:GKN262128 GUC262123:GUJ262128 HDY262123:HEF262128 HNU262123:HOB262128 HXQ262123:HXX262128 IHM262123:IHT262128 IRI262123:IRP262128 JBE262123:JBL262128 JLA262123:JLH262128 JUW262123:JVD262128 KES262123:KEZ262128 KOO262123:KOV262128 KYK262123:KYR262128 LIG262123:LIN262128 LSC262123:LSJ262128 MBY262123:MCF262128 MLU262123:MMB262128 MVQ262123:MVX262128 NFM262123:NFT262128 NPI262123:NPP262128 NZE262123:NZL262128 OJA262123:OJH262128 OSW262123:OTD262128 PCS262123:PCZ262128 PMO262123:PMV262128 PWK262123:PWR262128 QGG262123:QGN262128 QQC262123:QQJ262128 QZY262123:RAF262128 RJU262123:RKB262128 RTQ262123:RTX262128 SDM262123:SDT262128 SNI262123:SNP262128 SXE262123:SXL262128 THA262123:THH262128 TQW262123:TRD262128 UAS262123:UAZ262128 UKO262123:UKV262128 UUK262123:UUR262128 VEG262123:VEN262128 VOC262123:VOJ262128 VXY262123:VYF262128 WHU262123:WIB262128 WRQ262123:WRX262128 FE327659:FL327664 PA327659:PH327664 YW327659:ZD327664 AIS327659:AIZ327664 ASO327659:ASV327664 BCK327659:BCR327664 BMG327659:BMN327664 BWC327659:BWJ327664 CFY327659:CGF327664 CPU327659:CQB327664 CZQ327659:CZX327664 DJM327659:DJT327664 DTI327659:DTP327664 EDE327659:EDL327664 ENA327659:ENH327664 EWW327659:EXD327664 FGS327659:FGZ327664 FQO327659:FQV327664 GAK327659:GAR327664 GKG327659:GKN327664 GUC327659:GUJ327664 HDY327659:HEF327664 HNU327659:HOB327664 HXQ327659:HXX327664 IHM327659:IHT327664 IRI327659:IRP327664 JBE327659:JBL327664 JLA327659:JLH327664 JUW327659:JVD327664 KES327659:KEZ327664 KOO327659:KOV327664 KYK327659:KYR327664 LIG327659:LIN327664 LSC327659:LSJ327664 MBY327659:MCF327664 MLU327659:MMB327664 MVQ327659:MVX327664 NFM327659:NFT327664 NPI327659:NPP327664 NZE327659:NZL327664 OJA327659:OJH327664 OSW327659:OTD327664 PCS327659:PCZ327664 PMO327659:PMV327664 PWK327659:PWR327664 QGG327659:QGN327664 QQC327659:QQJ327664 QZY327659:RAF327664 RJU327659:RKB327664 RTQ327659:RTX327664 SDM327659:SDT327664 SNI327659:SNP327664 SXE327659:SXL327664 THA327659:THH327664 TQW327659:TRD327664 UAS327659:UAZ327664 UKO327659:UKV327664 UUK327659:UUR327664 VEG327659:VEN327664 VOC327659:VOJ327664 VXY327659:VYF327664 WHU327659:WIB327664 WRQ327659:WRX327664 FE393195:FL393200 PA393195:PH393200 YW393195:ZD393200 AIS393195:AIZ393200 ASO393195:ASV393200 BCK393195:BCR393200 BMG393195:BMN393200 BWC393195:BWJ393200 CFY393195:CGF393200 CPU393195:CQB393200 CZQ393195:CZX393200 DJM393195:DJT393200 DTI393195:DTP393200 EDE393195:EDL393200 ENA393195:ENH393200 EWW393195:EXD393200 FGS393195:FGZ393200 FQO393195:FQV393200 GAK393195:GAR393200 GKG393195:GKN393200 GUC393195:GUJ393200 HDY393195:HEF393200 HNU393195:HOB393200 HXQ393195:HXX393200 IHM393195:IHT393200 IRI393195:IRP393200 JBE393195:JBL393200 JLA393195:JLH393200 JUW393195:JVD393200 KES393195:KEZ393200 KOO393195:KOV393200 KYK393195:KYR393200 LIG393195:LIN393200 LSC393195:LSJ393200 MBY393195:MCF393200 MLU393195:MMB393200 MVQ393195:MVX393200 NFM393195:NFT393200 NPI393195:NPP393200 NZE393195:NZL393200 OJA393195:OJH393200 OSW393195:OTD393200 PCS393195:PCZ393200 PMO393195:PMV393200 PWK393195:PWR393200 QGG393195:QGN393200 QQC393195:QQJ393200 QZY393195:RAF393200 RJU393195:RKB393200 RTQ393195:RTX393200 SDM393195:SDT393200 SNI393195:SNP393200 SXE393195:SXL393200 THA393195:THH393200 TQW393195:TRD393200 UAS393195:UAZ393200 UKO393195:UKV393200 UUK393195:UUR393200 VEG393195:VEN393200 VOC393195:VOJ393200 VXY393195:VYF393200 WHU393195:WIB393200 WRQ393195:WRX393200 FE458731:FL458736 PA458731:PH458736 YW458731:ZD458736 AIS458731:AIZ458736 ASO458731:ASV458736 BCK458731:BCR458736 BMG458731:BMN458736 BWC458731:BWJ458736 CFY458731:CGF458736 CPU458731:CQB458736 CZQ458731:CZX458736 DJM458731:DJT458736 DTI458731:DTP458736 EDE458731:EDL458736 ENA458731:ENH458736 EWW458731:EXD458736 FGS458731:FGZ458736 FQO458731:FQV458736 GAK458731:GAR458736 GKG458731:GKN458736 GUC458731:GUJ458736 HDY458731:HEF458736 HNU458731:HOB458736 HXQ458731:HXX458736 IHM458731:IHT458736 IRI458731:IRP458736 JBE458731:JBL458736 JLA458731:JLH458736 JUW458731:JVD458736 KES458731:KEZ458736 KOO458731:KOV458736 KYK458731:KYR458736 LIG458731:LIN458736 LSC458731:LSJ458736 MBY458731:MCF458736 MLU458731:MMB458736 MVQ458731:MVX458736 NFM458731:NFT458736 NPI458731:NPP458736 NZE458731:NZL458736 OJA458731:OJH458736 OSW458731:OTD458736 PCS458731:PCZ458736 PMO458731:PMV458736 PWK458731:PWR458736 QGG458731:QGN458736 QQC458731:QQJ458736 QZY458731:RAF458736 RJU458731:RKB458736 RTQ458731:RTX458736 SDM458731:SDT458736 SNI458731:SNP458736 SXE458731:SXL458736 THA458731:THH458736 TQW458731:TRD458736 UAS458731:UAZ458736 UKO458731:UKV458736 UUK458731:UUR458736 VEG458731:VEN458736 VOC458731:VOJ458736 VXY458731:VYF458736 WHU458731:WIB458736 WRQ458731:WRX458736 FE524267:FL524272 PA524267:PH524272 YW524267:ZD524272 AIS524267:AIZ524272 ASO524267:ASV524272 BCK524267:BCR524272 BMG524267:BMN524272 BWC524267:BWJ524272 CFY524267:CGF524272 CPU524267:CQB524272 CZQ524267:CZX524272 DJM524267:DJT524272 DTI524267:DTP524272 EDE524267:EDL524272 ENA524267:ENH524272 EWW524267:EXD524272 FGS524267:FGZ524272 FQO524267:FQV524272 GAK524267:GAR524272 GKG524267:GKN524272 GUC524267:GUJ524272 HDY524267:HEF524272 HNU524267:HOB524272 HXQ524267:HXX524272 IHM524267:IHT524272 IRI524267:IRP524272 JBE524267:JBL524272 JLA524267:JLH524272 JUW524267:JVD524272 KES524267:KEZ524272 KOO524267:KOV524272 KYK524267:KYR524272 LIG524267:LIN524272 LSC524267:LSJ524272 MBY524267:MCF524272 MLU524267:MMB524272 MVQ524267:MVX524272 NFM524267:NFT524272 NPI524267:NPP524272 NZE524267:NZL524272 OJA524267:OJH524272 OSW524267:OTD524272 PCS524267:PCZ524272 PMO524267:PMV524272 PWK524267:PWR524272 QGG524267:QGN524272 QQC524267:QQJ524272 QZY524267:RAF524272 RJU524267:RKB524272 RTQ524267:RTX524272 SDM524267:SDT524272 SNI524267:SNP524272 SXE524267:SXL524272 THA524267:THH524272 TQW524267:TRD524272 UAS524267:UAZ524272 UKO524267:UKV524272 UUK524267:UUR524272 VEG524267:VEN524272 VOC524267:VOJ524272 VXY524267:VYF524272 WHU524267:WIB524272 WRQ524267:WRX524272 FE589803:FL589808 PA589803:PH589808 YW589803:ZD589808 AIS589803:AIZ589808 ASO589803:ASV589808 BCK589803:BCR589808 BMG589803:BMN589808 BWC589803:BWJ589808 CFY589803:CGF589808 CPU589803:CQB589808 CZQ589803:CZX589808 DJM589803:DJT589808 DTI589803:DTP589808 EDE589803:EDL589808 ENA589803:ENH589808 EWW589803:EXD589808 FGS589803:FGZ589808 FQO589803:FQV589808 GAK589803:GAR589808 GKG589803:GKN589808 GUC589803:GUJ589808 HDY589803:HEF589808 HNU589803:HOB589808 HXQ589803:HXX589808 IHM589803:IHT589808 IRI589803:IRP589808 JBE589803:JBL589808 JLA589803:JLH589808 JUW589803:JVD589808 KES589803:KEZ589808 KOO589803:KOV589808 KYK589803:KYR589808 LIG589803:LIN589808 LSC589803:LSJ589808 MBY589803:MCF589808 MLU589803:MMB589808 MVQ589803:MVX589808 NFM589803:NFT589808 NPI589803:NPP589808 NZE589803:NZL589808 OJA589803:OJH589808 OSW589803:OTD589808 PCS589803:PCZ589808 PMO589803:PMV589808 PWK589803:PWR589808 QGG589803:QGN589808 QQC589803:QQJ589808 QZY589803:RAF589808 RJU589803:RKB589808 RTQ589803:RTX589808 SDM589803:SDT589808 SNI589803:SNP589808 SXE589803:SXL589808 THA589803:THH589808 TQW589803:TRD589808 UAS589803:UAZ589808 UKO589803:UKV589808 UUK589803:UUR589808 VEG589803:VEN589808 VOC589803:VOJ589808 VXY589803:VYF589808 WHU589803:WIB589808 WRQ589803:WRX589808 FE655339:FL655344 PA655339:PH655344 YW655339:ZD655344 AIS655339:AIZ655344 ASO655339:ASV655344 BCK655339:BCR655344 BMG655339:BMN655344 BWC655339:BWJ655344 CFY655339:CGF655344 CPU655339:CQB655344 CZQ655339:CZX655344 DJM655339:DJT655344 DTI655339:DTP655344 EDE655339:EDL655344 ENA655339:ENH655344 EWW655339:EXD655344 FGS655339:FGZ655344 FQO655339:FQV655344 GAK655339:GAR655344 GKG655339:GKN655344 GUC655339:GUJ655344 HDY655339:HEF655344 HNU655339:HOB655344 HXQ655339:HXX655344 IHM655339:IHT655344 IRI655339:IRP655344 JBE655339:JBL655344 JLA655339:JLH655344 JUW655339:JVD655344 KES655339:KEZ655344 KOO655339:KOV655344 KYK655339:KYR655344 LIG655339:LIN655344 LSC655339:LSJ655344 MBY655339:MCF655344 MLU655339:MMB655344 MVQ655339:MVX655344 NFM655339:NFT655344 NPI655339:NPP655344 NZE655339:NZL655344 OJA655339:OJH655344 OSW655339:OTD655344 PCS655339:PCZ655344 PMO655339:PMV655344 PWK655339:PWR655344 QGG655339:QGN655344 QQC655339:QQJ655344 QZY655339:RAF655344 RJU655339:RKB655344 RTQ655339:RTX655344 SDM655339:SDT655344 SNI655339:SNP655344 SXE655339:SXL655344 THA655339:THH655344 TQW655339:TRD655344 UAS655339:UAZ655344 UKO655339:UKV655344 UUK655339:UUR655344 VEG655339:VEN655344 VOC655339:VOJ655344 VXY655339:VYF655344 WHU655339:WIB655344 WRQ655339:WRX655344 FE720875:FL720880 PA720875:PH720880 YW720875:ZD720880 AIS720875:AIZ720880 ASO720875:ASV720880 BCK720875:BCR720880 BMG720875:BMN720880 BWC720875:BWJ720880 CFY720875:CGF720880 CPU720875:CQB720880 CZQ720875:CZX720880 DJM720875:DJT720880 DTI720875:DTP720880 EDE720875:EDL720880 ENA720875:ENH720880 EWW720875:EXD720880 FGS720875:FGZ720880 FQO720875:FQV720880 GAK720875:GAR720880 GKG720875:GKN720880 GUC720875:GUJ720880 HDY720875:HEF720880 HNU720875:HOB720880 HXQ720875:HXX720880 IHM720875:IHT720880 IRI720875:IRP720880 JBE720875:JBL720880 JLA720875:JLH720880 JUW720875:JVD720880 KES720875:KEZ720880 KOO720875:KOV720880 KYK720875:KYR720880 LIG720875:LIN720880 LSC720875:LSJ720880 MBY720875:MCF720880 MLU720875:MMB720880 MVQ720875:MVX720880 NFM720875:NFT720880 NPI720875:NPP720880 NZE720875:NZL720880 OJA720875:OJH720880 OSW720875:OTD720880 PCS720875:PCZ720880 PMO720875:PMV720880 PWK720875:PWR720880 QGG720875:QGN720880 QQC720875:QQJ720880 QZY720875:RAF720880 RJU720875:RKB720880 RTQ720875:RTX720880 SDM720875:SDT720880 SNI720875:SNP720880 SXE720875:SXL720880 THA720875:THH720880 TQW720875:TRD720880 UAS720875:UAZ720880 UKO720875:UKV720880 UUK720875:UUR720880 VEG720875:VEN720880 VOC720875:VOJ720880 VXY720875:VYF720880 WHU720875:WIB720880 WRQ720875:WRX720880 FE786411:FL786416 PA786411:PH786416 YW786411:ZD786416 AIS786411:AIZ786416 ASO786411:ASV786416 BCK786411:BCR786416 BMG786411:BMN786416 BWC786411:BWJ786416 CFY786411:CGF786416 CPU786411:CQB786416 CZQ786411:CZX786416 DJM786411:DJT786416 DTI786411:DTP786416 EDE786411:EDL786416 ENA786411:ENH786416 EWW786411:EXD786416 FGS786411:FGZ786416 FQO786411:FQV786416 GAK786411:GAR786416 GKG786411:GKN786416 GUC786411:GUJ786416 HDY786411:HEF786416 HNU786411:HOB786416 HXQ786411:HXX786416 IHM786411:IHT786416 IRI786411:IRP786416 JBE786411:JBL786416 JLA786411:JLH786416 JUW786411:JVD786416 KES786411:KEZ786416 KOO786411:KOV786416 KYK786411:KYR786416 LIG786411:LIN786416 LSC786411:LSJ786416 MBY786411:MCF786416 MLU786411:MMB786416 MVQ786411:MVX786416 NFM786411:NFT786416 NPI786411:NPP786416 NZE786411:NZL786416 OJA786411:OJH786416 OSW786411:OTD786416 PCS786411:PCZ786416 PMO786411:PMV786416 PWK786411:PWR786416 QGG786411:QGN786416 QQC786411:QQJ786416 QZY786411:RAF786416 RJU786411:RKB786416 RTQ786411:RTX786416 SDM786411:SDT786416 SNI786411:SNP786416 SXE786411:SXL786416 THA786411:THH786416 TQW786411:TRD786416 UAS786411:UAZ786416 UKO786411:UKV786416 UUK786411:UUR786416 VEG786411:VEN786416 VOC786411:VOJ786416 VXY786411:VYF786416 WHU786411:WIB786416 WRQ786411:WRX786416 FE851947:FL851952 PA851947:PH851952 YW851947:ZD851952 AIS851947:AIZ851952 ASO851947:ASV851952 BCK851947:BCR851952 BMG851947:BMN851952 BWC851947:BWJ851952 CFY851947:CGF851952 CPU851947:CQB851952 CZQ851947:CZX851952 DJM851947:DJT851952 DTI851947:DTP851952 EDE851947:EDL851952 ENA851947:ENH851952 EWW851947:EXD851952 FGS851947:FGZ851952 FQO851947:FQV851952 GAK851947:GAR851952 GKG851947:GKN851952 GUC851947:GUJ851952 HDY851947:HEF851952 HNU851947:HOB851952 HXQ851947:HXX851952 IHM851947:IHT851952 IRI851947:IRP851952 JBE851947:JBL851952 JLA851947:JLH851952 JUW851947:JVD851952 KES851947:KEZ851952 KOO851947:KOV851952 KYK851947:KYR851952 LIG851947:LIN851952 LSC851947:LSJ851952 MBY851947:MCF851952 MLU851947:MMB851952 MVQ851947:MVX851952 NFM851947:NFT851952 NPI851947:NPP851952 NZE851947:NZL851952 OJA851947:OJH851952 OSW851947:OTD851952 PCS851947:PCZ851952 PMO851947:PMV851952 PWK851947:PWR851952 QGG851947:QGN851952 QQC851947:QQJ851952 QZY851947:RAF851952 RJU851947:RKB851952 RTQ851947:RTX851952 SDM851947:SDT851952 SNI851947:SNP851952 SXE851947:SXL851952 THA851947:THH851952 TQW851947:TRD851952 UAS851947:UAZ851952 UKO851947:UKV851952 UUK851947:UUR851952 VEG851947:VEN851952 VOC851947:VOJ851952 VXY851947:VYF851952 WHU851947:WIB851952 WRQ851947:WRX851952 FE917483:FL917488 PA917483:PH917488 YW917483:ZD917488 AIS917483:AIZ917488 ASO917483:ASV917488 BCK917483:BCR917488 BMG917483:BMN917488 BWC917483:BWJ917488 CFY917483:CGF917488 CPU917483:CQB917488 CZQ917483:CZX917488 DJM917483:DJT917488 DTI917483:DTP917488 EDE917483:EDL917488 ENA917483:ENH917488 EWW917483:EXD917488 FGS917483:FGZ917488 FQO917483:FQV917488 GAK917483:GAR917488 GKG917483:GKN917488 GUC917483:GUJ917488 HDY917483:HEF917488 HNU917483:HOB917488 HXQ917483:HXX917488 IHM917483:IHT917488 IRI917483:IRP917488 JBE917483:JBL917488 JLA917483:JLH917488 JUW917483:JVD917488 KES917483:KEZ917488 KOO917483:KOV917488 KYK917483:KYR917488 LIG917483:LIN917488 LSC917483:LSJ917488 MBY917483:MCF917488 MLU917483:MMB917488 MVQ917483:MVX917488 NFM917483:NFT917488 NPI917483:NPP917488 NZE917483:NZL917488 OJA917483:OJH917488 OSW917483:OTD917488 PCS917483:PCZ917488 PMO917483:PMV917488 PWK917483:PWR917488 QGG917483:QGN917488 QQC917483:QQJ917488 QZY917483:RAF917488 RJU917483:RKB917488 RTQ917483:RTX917488 SDM917483:SDT917488 SNI917483:SNP917488 SXE917483:SXL917488 THA917483:THH917488 TQW917483:TRD917488 UAS917483:UAZ917488 UKO917483:UKV917488 UUK917483:UUR917488 VEG917483:VEN917488 VOC917483:VOJ917488 VXY917483:VYF917488 WHU917483:WIB917488 WRQ917483:WRX917488" xr:uid="{FAB87F88-CF7B-481E-835D-3D47857FF214}">
       <formula1>"サーバ,クライアント"</formula1>
     </dataValidation>
   </dataValidations>
